--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -17,7 +17,7 @@
     <sheet sheetId="15" name="Hoja1" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase">SALDOS!$F$1:$F$511</definedName>
+    <definedName name="_xlnm._FilterDatabase">SALDOS!$F$1:$F$510</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Balance'!$A1:$L34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Anexo I'!$O15:$O23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Anexo II'!$A2:$J113</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="873">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="872">
   <si>
     <t>ESTADO DE SITUACION PATRIMONIAL</t>
   </si>
@@ -2196,9 +2196,6 @@
   </si>
   <si>
     <t>42433000 - Gs. Importación</t>
-  </si>
-  <si>
-    <t>42433000 - PLOTEOS</t>
   </si>
   <si>
     <t>42434000 - HABILITACIÓN COMERCIAL</t>
@@ -4383,7 +4380,7 @@
     <col min="6" max="6" width="19.88671875" style="1" customWidth="1"/>
     <col min="7" max="8" width="20" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.109375" style="1" customWidth="1"/>
-    <col min="10" max="10" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="1" hidden="1" customWidth="1"/>
     <col min="11" max="16384" width="11.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4652,7 +4649,7 @@
       <c r="F15" s="124"/>
       <c r="G15" s="16"/>
       <c r="H15" s="19">
-        <f>+SALDOS!G404</f>
+        <f>+SALDOS!G403</f>
       </c>
       <c r="I15" s="125"/>
       <c r="J15" s="123"/>
@@ -4716,7 +4713,7 @@
       <c r="F18" s="124"/>
       <c r="G18" s="16"/>
       <c r="H18" s="19">
-        <f>+SALDOS!G359+SALDOS!G399</f>
+        <f>+SALDOS!G359+SALDOS!G398</f>
       </c>
       <c r="I18" s="125"/>
       <c r="J18" s="123"/>
@@ -4783,7 +4780,7 @@
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="19">
-        <f>+SALDOS!G426</f>
+        <f>+SALDOS!G425</f>
         <v>51916602.99</v>
       </c>
       <c r="I21" s="125"/>
@@ -4928,7 +4925,7 @@
         <v>7955308.800000001</v>
       </c>
       <c r="F28" s="124">
-        <f>+SALDOS!G343+SALDOS!G497+SALDOS!G498</f>
+        <f>+SALDOS!G343+SALDOS!G496+SALDOS!G497</f>
         <v>7955308.800000001</v>
       </c>
       <c r="G28" s="16"/>
@@ -5013,7 +5010,7 @@
       <c r="F32" s="124"/>
       <c r="G32" s="16"/>
       <c r="H32" s="19">
-        <f>+SALDOS!G441</f>
+        <f>+SALDOS!G440</f>
       </c>
       <c r="I32" s="125"/>
       <c r="J32" s="123"/>
@@ -5032,7 +5029,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="124">
-        <f>+SALDOS!G473</f>
+        <f>+SALDOS!G472</f>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="19"/>
@@ -5053,7 +5050,7 @@
         <v>489482.99</v>
       </c>
       <c r="F34" s="126">
-        <f>+SALDOS!G408</f>
+        <f>+SALDOS!G407</f>
         <v>489482.99</v>
       </c>
       <c r="G34" s="16"/>
@@ -5102,7 +5099,7 @@
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="19">
-        <f>+SALDOS!G214+SALDOS!G395+SALDOS!G459</f>
+        <f>+SALDOS!G214+SALDOS!G394+SALDOS!G458</f>
         <v>5887375.78</v>
       </c>
       <c r="I36" s="125"/>
@@ -5122,7 +5119,7 @@
         <v>15451043.76</v>
       </c>
       <c r="F37" s="124">
-        <f>+SALDOS!G464</f>
+        <f>+SALDOS!G463</f>
         <v>15451043.76</v>
       </c>
       <c r="G37" s="16"/>
@@ -5146,7 +5143,7 @@
       <c r="F38" s="124"/>
       <c r="G38" s="16"/>
       <c r="H38" s="19">
-        <f>+SALDOS!G401+SALDOS!G442</f>
+        <f>+SALDOS!G400+SALDOS!G441</f>
       </c>
       <c r="I38" s="125"/>
       <c r="J38" s="123"/>
@@ -5167,7 +5164,7 @@
       <c r="F39" s="124"/>
       <c r="G39" s="16"/>
       <c r="H39" s="19">
-        <f>+SALDOS!G450</f>
+        <f>+SALDOS!G449</f>
         <v>8441197.290000001</v>
       </c>
       <c r="I39" s="125"/>
@@ -5316,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="124">
-        <f>+SALDOS!G461</f>
+        <f>+SALDOS!G460</f>
       </c>
       <c r="G46" s="16"/>
       <c r="H46" s="19"/>
@@ -5360,7 +5357,7 @@
       <c r="F48" s="124"/>
       <c r="G48" s="16"/>
       <c r="H48" s="19">
-        <f>+SALDOS!G415</f>
+        <f>+SALDOS!G414</f>
         <v>236115665.5</v>
       </c>
       <c r="I48" s="125"/>
@@ -5401,7 +5398,7 @@
         <v>14667167.22</v>
       </c>
       <c r="F50" s="124">
-        <f>+SALDOS!G454</f>
+        <f>+SALDOS!G453</f>
         <v>14667167.22</v>
       </c>
       <c r="G50" s="16"/>
@@ -5444,12 +5441,12 @@
         <v>9103800</v>
       </c>
       <c r="F52" s="124">
-        <f>+SALDOS!G186+SALDOS!G231+SALDOS!G368+SALDOS!G388</f>
+        <f>+SALDOS!G186+SALDOS!G231+SALDOS!G368+SALDOS!G387</f>
         <v>39000</v>
       </c>
       <c r="G52" s="16"/>
       <c r="H52" s="19">
-        <f>+SALDOS!G392</f>
+        <f>+SALDOS!G391</f>
         <v>9064800</v>
       </c>
       <c r="I52" s="125"/>
@@ -5599,7 +5596,7 @@
         <v>11619112.85</v>
       </c>
       <c r="F59" s="124">
-        <f>+SALDOS!G168+SALDOS!G284+SALDOS!G285+SALDOS!G495+SALDOS!F500</f>
+        <f>+SALDOS!G168+SALDOS!G284+SALDOS!G285+SALDOS!G494+SALDOS!F499</f>
         <v>11619112.85</v>
       </c>
       <c r="G59" s="17"/>
@@ -5621,7 +5618,7 @@
         <v>768315.33</v>
       </c>
       <c r="F60" s="124">
-        <f>+SALDOS!G427</f>
+        <f>+SALDOS!G426</f>
         <v>768315.33</v>
       </c>
       <c r="G60" s="16"/>
@@ -5686,7 +5683,7 @@
         <v>88381242.3</v>
       </c>
       <c r="F63" s="124">
-        <f>+SALDOS!G171+SALDOS!G339+SALDOS!G391+SALDOS!G340</f>
+        <f>+SALDOS!G171+SALDOS!G339+SALDOS!G390+SALDOS!G340</f>
         <v>1068794.41</v>
       </c>
       <c r="G63" s="16"/>
@@ -5733,7 +5730,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="124">
-        <f>+SALDOS!G479</f>
+        <f>+SALDOS!G478</f>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="19"/>
@@ -5816,7 +5813,7 @@
       <c r="F69" s="124"/>
       <c r="G69" s="16"/>
       <c r="H69" s="19">
-        <f>+SALDOS!G389</f>
+        <f>+SALDOS!G388</f>
       </c>
       <c r="I69" s="125"/>
       <c r="J69" s="123"/>
@@ -5875,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="124">
-        <f>+SALDOS!G489</f>
+        <f>+SALDOS!G488</f>
       </c>
       <c r="G72" s="16"/>
       <c r="H72" s="19"/>
@@ -5918,7 +5915,7 @@
         <v>4013596.99</v>
       </c>
       <c r="F74" s="19">
-        <f>+SALDOS!G482</f>
+        <f>+SALDOS!G481</f>
         <v>4013596.99</v>
       </c>
       <c r="G74" s="16"/>
@@ -5961,7 +5958,7 @@
         <v>17921832.18</v>
       </c>
       <c r="F76" s="124">
-        <f>+SALDOS!G436</f>
+        <f>+SALDOS!G435</f>
         <v>17921832.18</v>
       </c>
       <c r="G76" s="16"/>
@@ -5983,7 +5980,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="124">
-        <f>+SALDOS!G490</f>
+        <f>+SALDOS!G489</f>
       </c>
       <c r="G77" s="16"/>
       <c r="H77" s="19"/>
@@ -6027,7 +6024,7 @@
       <c r="F79" s="124"/>
       <c r="G79" s="16"/>
       <c r="H79" s="19">
-        <f>+SALDOS!G487</f>
+        <f>+SALDOS!G486</f>
       </c>
       <c r="I79" s="125"/>
       <c r="J79" s="123"/>
@@ -6048,7 +6045,7 @@
       <c r="F80" s="124"/>
       <c r="G80" s="16"/>
       <c r="H80" s="19">
-        <f>+SALDOS!G488</f>
+        <f>+SALDOS!G487</f>
         <v>4150213.41</v>
       </c>
       <c r="I80" s="125"/>
@@ -6073,7 +6070,7 @@
       </c>
       <c r="G81" s="16"/>
       <c r="H81" s="19">
-        <f>+SALDOS!G403</f>
+        <f>+SALDOS!G402</f>
         <v>276280951</v>
       </c>
       <c r="I81" s="125"/>
@@ -6097,7 +6094,7 @@
       </c>
       <c r="G82" s="16"/>
       <c r="H82" s="19">
-        <f>+SALDOS!G418</f>
+        <f>+SALDOS!G417</f>
         <v>3499846.7</v>
       </c>
       <c r="I82" s="125"/>
@@ -6227,7 +6224,7 @@
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
       <c r="H88" s="19">
-        <f>+SALDOS!G417</f>
+        <f>+SALDOS!G416</f>
       </c>
       <c r="I88" s="125"/>
       <c r="J88" s="123"/>
@@ -6246,7 +6243,7 @@
         <v>101483.28</v>
       </c>
       <c r="F89" s="16">
-        <f>+SALDOS!G445</f>
+        <f>+SALDOS!G444</f>
         <v>101483.28</v>
       </c>
       <c r="G89" s="16"/>
@@ -6270,7 +6267,7 @@
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
       <c r="H90" s="19">
-        <f>+SALDOS!G477</f>
+        <f>+SALDOS!G476</f>
       </c>
       <c r="I90" s="125"/>
       <c r="J90" s="123"/>
@@ -6332,7 +6329,7 @@
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
       <c r="H93" s="19">
-        <f>+SALDOS!G491</f>
+        <f>+SALDOS!G490</f>
         <v>226987</v>
       </c>
       <c r="I93" s="125"/>
@@ -6354,7 +6351,7 @@
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
       <c r="H94" s="19">
-        <f>+SALDOS!G492+SALDOS!G493</f>
+        <f>+SALDOS!G491+SALDOS!G492</f>
         <v>914304.7000000001</v>
       </c>
       <c r="I94" s="125"/>
@@ -6398,7 +6395,7 @@
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
       <c r="H96" s="19">
-        <f>+SALDOS!G496</f>
+        <f>+SALDOS!G495</f>
       </c>
       <c r="I96" s="125"/>
       <c r="J96" s="123"/>
@@ -6419,7 +6416,7 @@
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
       <c r="H97" s="19">
-        <f>+SALDOS!F494</f>
+        <f>+SALDOS!F493</f>
       </c>
       <c r="I97" s="125"/>
       <c r="J97" s="123"/>
@@ -6440,7 +6437,7 @@
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="19">
-        <f>+SALDOS!G499</f>
+        <f>+SALDOS!G498</f>
       </c>
       <c r="I98" s="125"/>
       <c r="J98" s="123"/>
@@ -6461,7 +6458,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="19">
-        <f>+SALDOS!G501</f>
+        <f>+SALDOS!G500</f>
       </c>
       <c r="I99" s="125"/>
       <c r="J99" s="123"/>
@@ -6482,7 +6479,7 @@
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="19">
-        <f>+SALDOS!G502</f>
+        <f>+SALDOS!G501</f>
       </c>
       <c r="I100" s="125"/>
       <c r="J100" s="123"/>
@@ -6503,7 +6500,7 @@
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="19">
-        <f>+SALDOS!G503</f>
+        <f>+SALDOS!G502</f>
       </c>
       <c r="I101" s="125"/>
       <c r="J101" s="123"/>
@@ -6524,7 +6521,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="19">
-        <f>+SALDOS!G504</f>
+        <f>+SALDOS!G503</f>
       </c>
       <c r="I102" s="125"/>
       <c r="J102" s="123"/>
@@ -7528,7 +7525,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1922"/>
+  <dimension ref="A1:O1921"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11.44140625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="76" customWidth="1"/>
@@ -12107,6 +12104,7 @@
       </c>
       <c r="H270" s="68"/>
       <c r="I270" s="189"/>
+      <c r="J270" s="132"/>
       <c r="K270" s="190"/>
     </row>
     <row r="271" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -12123,6 +12121,7 @@
       <c r="G271" s="138"/>
       <c r="H271" s="68"/>
       <c r="I271" s="189"/>
+      <c r="J271" s="132"/>
       <c r="K271" s="190"/>
     </row>
     <row r="272" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -12140,6 +12139,7 @@
       <c r="G272" s="138"/>
       <c r="H272" s="68"/>
       <c r="I272" s="164"/>
+      <c r="J272" s="132"/>
       <c r="K272" s="190"/>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
@@ -13914,10 +13914,14 @@
       <c r="D388" s="71" t="s">
         <v>724</v>
       </c>
-      <c r="E388" s="71"/>
-      <c r="F388" s="140"/>
+      <c r="E388" s="72" t="s">
+        <v>725</v>
+      </c>
+      <c r="F388" s="140">
+        <f>IFERROR(VLOOKUP(E388,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
       <c r="G388" s="138">
-        <f>+F388</f>
+        <f>+F388+F389</f>
       </c>
       <c r="H388" s="132"/>
     </row>
@@ -13925,35 +13929,31 @@
       <c r="A389" s="76"/>
       <c r="B389" s="76"/>
       <c r="C389" s="34"/>
-      <c r="D389" s="71" t="s">
-        <v>725</v>
-      </c>
+      <c r="D389" s="71"/>
       <c r="E389" s="72" t="s">
         <v>726</v>
       </c>
       <c r="F389" s="140">
         <f>IFERROR(VLOOKUP(E389,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G389" s="138">
-        <f>+F389+F390</f>
-      </c>
+      <c r="G389" s="138"/>
       <c r="H389" s="132"/>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" s="76"/>
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
-      <c r="D390" s="71"/>
-      <c r="E390" s="72" t="s">
+      <c r="D390" s="71" t="s">
         <v>727</v>
       </c>
-      <c r="F390" s="140">
-        <f>IFERROR(VLOOKUP(E390,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G390" s="138"/>
+      <c r="E390" s="71"/>
+      <c r="F390" s="140"/>
+      <c r="G390" s="138">
+        <f>+F390</f>
+      </c>
       <c r="H390" s="132"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" s="76"/>
       <c r="B391" s="76"/>
       <c r="C391" s="34"/>
@@ -13962,24 +13962,31 @@
       </c>
       <c r="E391" s="71"/>
       <c r="F391" s="140"/>
-      <c r="G391" s="138">
-        <f>+F391</f>
+      <c r="G391" s="187">
+        <f>SUM(F391:F393)</f>
+        <v>9064800</v>
       </c>
       <c r="H391" s="132"/>
+      <c r="I391" s="134"/>
+      <c r="J391" s="132"/>
+      <c r="K391" s="72"/>
+      <c r="L391" s="72"/>
+      <c r="M391" s="72"/>
+      <c r="N391" s="72"/>
+      <c r="O391" s="72"/>
     </row>
     <row r="392" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A392" s="76"/>
       <c r="B392" s="76"/>
       <c r="C392" s="34"/>
-      <c r="D392" s="71" t="s">
+      <c r="D392" s="71"/>
+      <c r="E392" s="72" t="s">
         <v>729</v>
       </c>
-      <c r="E392" s="71"/>
-      <c r="F392" s="140"/>
-      <c r="G392" s="187">
-        <f>SUM(F392:F394)</f>
-        <v>9064800</v>
-      </c>
+      <c r="F392" s="140">
+        <f>IFERROR(VLOOKUP(E392,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G392" s="138"/>
       <c r="H392" s="132"/>
       <c r="I392" s="134"/>
       <c r="J392" s="132"/>
@@ -13999,6 +14006,7 @@
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>9064800</v>
       </c>
       <c r="G393" s="138"/>
       <c r="H393" s="132"/>
@@ -14010,46 +14018,38 @@
       <c r="N393" s="72"/>
       <c r="O393" s="72"/>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="76"/>
       <c r="B394" s="76"/>
       <c r="C394" s="34"/>
-      <c r="D394" s="71"/>
+      <c r="D394" s="71" t="s">
+        <v>731</v>
+      </c>
       <c r="E394" s="72" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>9064800</v>
-      </c>
-      <c r="G394" s="138"/>
+        <v>5598557</v>
+      </c>
+      <c r="G394" s="138">
+        <f>+F394+F395+F396+F397</f>
+        <v>5598557</v>
+      </c>
       <c r="H394" s="132"/>
-      <c r="I394" s="134"/>
-      <c r="J394" s="132"/>
-      <c r="K394" s="72"/>
-      <c r="L394" s="72"/>
-      <c r="M394" s="72"/>
-      <c r="N394" s="72"/>
-      <c r="O394" s="72"/>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" s="76"/>
       <c r="B395" s="76"/>
       <c r="C395" s="34"/>
-      <c r="D395" s="71" t="s">
-        <v>732</v>
-      </c>
+      <c r="D395" s="71"/>
       <c r="E395" s="72" t="s">
         <v>733</v>
       </c>
       <c r="F395" s="140">
         <f>IFERROR(VLOOKUP(E395,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>5598557</v>
-      </c>
-      <c r="G395" s="138">
-        <f>+F395+F396+F397+F398</f>
-        <v>5598557</v>
-      </c>
+      </c>
+      <c r="G395" s="138"/>
       <c r="H395" s="132"/>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.25">
@@ -14084,89 +14084,89 @@
       <c r="A398" s="76"/>
       <c r="B398" s="76"/>
       <c r="C398" s="34"/>
-      <c r="D398" s="71"/>
-      <c r="E398" s="72" t="s">
+      <c r="D398" s="71" t="s">
         <v>736</v>
       </c>
-      <c r="F398" s="140">
-        <f>IFERROR(VLOOKUP(E398,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G398" s="138"/>
+      <c r="E398" s="188"/>
+      <c r="F398" s="140"/>
+      <c r="G398" s="138">
+        <f>SUM(F398:F399)</f>
+      </c>
       <c r="H398" s="132"/>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="76"/>
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
-      <c r="D399" s="71" t="s">
+      <c r="D399" s="139"/>
+      <c r="E399" s="72" t="s">
         <v>737</v>
       </c>
-      <c r="E399" s="188"/>
-      <c r="F399" s="140"/>
-      <c r="G399" s="138">
-        <f>SUM(F399:F400)</f>
-      </c>
-      <c r="H399" s="132"/>
+      <c r="F399" s="140">
+        <f>IFERROR(VLOOKUP(E399,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G399" s="138"/>
+      <c r="H399" s="72"/>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="76"/>
       <c r="B400" s="76"/>
       <c r="C400" s="34"/>
-      <c r="D400" s="139"/>
-      <c r="E400" s="72" t="s">
+      <c r="D400" s="71" t="s">
         <v>738</v>
       </c>
-      <c r="F400" s="140">
-        <f>IFERROR(VLOOKUP(E400,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G400" s="138"/>
-      <c r="H400" s="72"/>
+      <c r="E400" s="188"/>
+      <c r="F400" s="140"/>
+      <c r="G400" s="138">
+        <f>+F400+F401</f>
+      </c>
+      <c r="H400" s="132"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="76"/>
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
-      <c r="D401" s="71" t="s">
+      <c r="D401" s="71"/>
+      <c r="E401" s="72" t="s">
         <v>739</v>
       </c>
-      <c r="E401" s="188"/>
-      <c r="F401" s="140"/>
-      <c r="G401" s="138">
-        <f>+F401+F402</f>
-      </c>
+      <c r="F401" s="140">
+        <f>IFERROR(VLOOKUP(E401,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G401" s="138"/>
       <c r="H401" s="132"/>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="76"/>
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
-      <c r="D402" s="71"/>
-      <c r="E402" s="72" t="s">
+      <c r="D402" s="71" t="s">
         <v>740</v>
+      </c>
+      <c r="E402" s="71" t="s">
+        <v>741</v>
       </c>
       <c r="F402" s="140">
         <f>IFERROR(VLOOKUP(E402,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G402" s="138"/>
+        <v>276280951</v>
+      </c>
+      <c r="G402" s="187">
+        <f>+F402</f>
+        <v>276280951</v>
+      </c>
       <c r="H402" s="132"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" s="76"/>
       <c r="B403" s="76"/>
       <c r="C403" s="34"/>
       <c r="D403" s="71" t="s">
-        <v>741</v>
-      </c>
-      <c r="E403" s="71" t="s">
         <v>742</v>
       </c>
-      <c r="F403" s="140">
-        <f>IFERROR(VLOOKUP(E403,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>276280951</v>
-      </c>
-      <c r="G403" s="187">
-        <f>+F403</f>
-        <v>276280951</v>
+      <c r="E403" s="188"/>
+      <c r="F403" s="140"/>
+      <c r="G403" s="138">
+        <f>+F404+F405</f>
       </c>
       <c r="H403" s="132"/>
     </row>
@@ -14174,21 +14174,21 @@
       <c r="A404" s="76"/>
       <c r="B404" s="76"/>
       <c r="C404" s="34"/>
-      <c r="D404" s="71" t="s">
+      <c r="D404" s="71"/>
+      <c r="E404" s="72" t="s">
         <v>743</v>
       </c>
-      <c r="E404" s="188"/>
-      <c r="F404" s="140"/>
-      <c r="G404" s="138">
-        <f>+F405+F406</f>
-      </c>
+      <c r="F404" s="140">
+        <f>IFERROR(VLOOKUP(E404,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G404" s="138"/>
       <c r="H404" s="132"/>
     </row>
     <row r="405" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" s="76"/>
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
-      <c r="D405" s="71"/>
+      <c r="D405" s="76"/>
       <c r="E405" s="72" t="s">
         <v>744</v>
       </c>
@@ -14202,27 +14202,28 @@
       <c r="A406" s="76"/>
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
-      <c r="D406" s="76"/>
-      <c r="E406" s="72" t="s">
+      <c r="D406" s="71" t="s">
         <v>745</v>
       </c>
-      <c r="F406" s="140">
-        <f>IFERROR(VLOOKUP(E406,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G406" s="138"/>
+      <c r="E406" s="72"/>
+      <c r="F406" s="140"/>
+      <c r="G406" s="138">
+        <f>+F406</f>
+      </c>
       <c r="H406" s="132"/>
     </row>
-    <row r="407" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" s="76"/>
       <c r="B407" s="76"/>
       <c r="C407" s="34"/>
       <c r="D407" s="71" t="s">
         <v>746</v>
       </c>
-      <c r="E407" s="72"/>
+      <c r="E407" s="71"/>
       <c r="F407" s="140"/>
-      <c r="G407" s="138">
-        <f>+F407</f>
+      <c r="G407" s="187">
+        <f>SUM(F407:F413)</f>
+        <v>489482.99</v>
       </c>
       <c r="H407" s="132"/>
     </row>
@@ -14230,15 +14231,14 @@
       <c r="A408" s="76"/>
       <c r="B408" s="76"/>
       <c r="C408" s="34"/>
-      <c r="D408" s="71" t="s">
+      <c r="D408" s="71"/>
+      <c r="E408" s="151" t="s">
         <v>747</v>
       </c>
-      <c r="E408" s="71"/>
-      <c r="F408" s="140"/>
-      <c r="G408" s="187">
-        <f>SUM(F408:F414)</f>
-        <v>489482.99</v>
-      </c>
+      <c r="F408" s="140">
+        <f>IFERROR(VLOOKUP(E408,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G408" s="138"/>
       <c r="H408" s="132"/>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
@@ -14246,7 +14246,7 @@
       <c r="B409" s="76"/>
       <c r="C409" s="34"/>
       <c r="D409" s="71"/>
-      <c r="E409" s="151" t="s">
+      <c r="E409" s="72" t="s">
         <v>748</v>
       </c>
       <c r="F409" s="140">
@@ -14265,6 +14265,7 @@
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>489482.99</v>
       </c>
       <c r="G410" s="138"/>
       <c r="H410" s="132"/>
@@ -14279,7 +14280,6 @@
       </c>
       <c r="F411" s="140">
         <f>IFERROR(VLOOKUP(E411,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>489482.99</v>
       </c>
       <c r="G411" s="138"/>
       <c r="H411" s="132"/>
@@ -14289,7 +14289,7 @@
       <c r="B412" s="76"/>
       <c r="C412" s="34"/>
       <c r="D412" s="71"/>
-      <c r="E412" s="72" t="s">
+      <c r="E412" s="151" t="s">
         <v>751</v>
       </c>
       <c r="F412" s="140">
@@ -14303,7 +14303,7 @@
       <c r="B413" s="76"/>
       <c r="C413" s="34"/>
       <c r="D413" s="71"/>
-      <c r="E413" s="151" t="s">
+      <c r="E413" s="72" t="s">
         <v>752</v>
       </c>
       <c r="F413" s="140">
@@ -14312,37 +14312,44 @@
       <c r="G413" s="138"/>
       <c r="H413" s="132"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A414" s="76"/>
       <c r="B414" s="76"/>
       <c r="C414" s="34"/>
-      <c r="D414" s="71"/>
+      <c r="D414" s="139" t="s">
+        <v>753</v>
+      </c>
       <c r="E414" s="72" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G414" s="138"/>
+      <c r="G414" s="187">
+        <f>+F414+F415</f>
+        <v>236115665.5</v>
+      </c>
       <c r="H414" s="132"/>
+      <c r="I414" s="134"/>
+      <c r="J414" s="72"/>
+      <c r="K414" s="72"/>
+      <c r="L414" s="72"/>
+      <c r="M414" s="72"/>
+      <c r="N414" s="72"/>
     </row>
     <row r="415" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A415" s="76"/>
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
-      <c r="D415" s="139" t="s">
-        <v>754</v>
-      </c>
+      <c r="D415" s="139"/>
       <c r="E415" s="72" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="F415" s="140">
         <f>IFERROR(VLOOKUP(E415,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G415" s="187">
-        <f>+F415+F416</f>
         <v>236115665.5</v>
       </c>
+      <c r="G415" s="138"/>
       <c r="H415" s="132"/>
       <c r="I415" s="134"/>
       <c r="J415" s="72"/>
@@ -14351,26 +14358,19 @@
       <c r="M415" s="72"/>
       <c r="N415" s="72"/>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="76"/>
       <c r="B416" s="76"/>
       <c r="C416" s="34"/>
-      <c r="D416" s="139"/>
-      <c r="E416" s="72" t="s">
-        <v>754</v>
-      </c>
-      <c r="F416" s="140">
-        <f>IFERROR(VLOOKUP(E416,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>236115665.5</v>
-      </c>
-      <c r="G416" s="138"/>
+      <c r="D416" s="139" t="s">
+        <v>755</v>
+      </c>
+      <c r="E416" s="72"/>
+      <c r="F416" s="140"/>
+      <c r="G416" s="138">
+        <f>+F416</f>
+      </c>
       <c r="H416" s="132"/>
-      <c r="I416" s="134"/>
-      <c r="J416" s="72"/>
-      <c r="K416" s="72"/>
-      <c r="L416" s="72"/>
-      <c r="M416" s="72"/>
-      <c r="N416" s="72"/>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="76"/>
@@ -14379,31 +14379,33 @@
       <c r="D417" s="139" t="s">
         <v>756</v>
       </c>
-      <c r="E417" s="72"/>
-      <c r="F417" s="140"/>
-      <c r="G417" s="138">
-        <f>+F417</f>
+      <c r="E417" s="151" t="s">
+        <v>757</v>
+      </c>
+      <c r="F417" s="140">
+        <f>IFERROR(VLOOKUP(E417,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G417" s="187">
+        <f>SUM(F417:F424)</f>
+        <v>3499846.7</v>
       </c>
       <c r="H417" s="132"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" s="76"/>
       <c r="B418" s="76"/>
       <c r="C418" s="34"/>
-      <c r="D418" s="139" t="s">
-        <v>757</v>
-      </c>
-      <c r="E418" s="151" t="s">
+      <c r="D418" s="139"/>
+      <c r="E418" s="72" t="s">
         <v>758</v>
       </c>
       <c r="F418" s="140">
         <f>IFERROR(VLOOKUP(E418,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G418" s="187">
-        <f>SUM(F418:F425)</f>
-        <v>3499846.7</v>
-      </c>
-      <c r="H418" s="132"/>
+        <v>3013363</v>
+      </c>
+      <c r="G418" s="138"/>
+      <c r="H418" s="72"/>
+      <c r="I418" s="164"/>
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" s="76"/>
@@ -14415,7 +14417,6 @@
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>3013363</v>
       </c>
       <c r="G419" s="138"/>
       <c r="H419" s="72"/>
@@ -14431,6 +14432,7 @@
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>442383.7</v>
       </c>
       <c r="G420" s="138"/>
       <c r="H420" s="72"/>
@@ -14446,7 +14448,6 @@
       </c>
       <c r="F421" s="140">
         <f>IFERROR(VLOOKUP(E421,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>442383.7</v>
       </c>
       <c r="G421" s="138"/>
       <c r="H421" s="72"/>
@@ -14487,32 +14488,35 @@
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
       <c r="D424" s="139"/>
-      <c r="E424" s="72" t="s">
-        <v>764</v>
+      <c r="E424" s="72" t="str">
+        <f>+Hoja1!A267</f>
+        <v>426880000 - Tasas Municipales Gs Campo</v>
       </c>
       <c r="F424" s="140">
         <f>IFERROR(VLOOKUP(E424,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>44100</v>
       </c>
       <c r="G424" s="138"/>
       <c r="H424" s="72"/>
       <c r="I424" s="164"/>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="76"/>
       <c r="B425" s="76"/>
       <c r="C425" s="34"/>
-      <c r="D425" s="139"/>
-      <c r="E425" s="72" t="str">
-        <f>+Hoja1!A267</f>
-        <v>426880000 - Tasas Municipales Gs Campo</v>
-      </c>
+      <c r="D425" s="71" t="s">
+        <v>764</v>
+      </c>
+      <c r="E425" s="71"/>
       <c r="F425" s="140">
-        <f>IFERROR(VLOOKUP(E425,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>44100</v>
-      </c>
-      <c r="G425" s="138"/>
-      <c r="H425" s="72"/>
-      <c r="I425" s="164"/>
+        <f>IFERROR(VLOOKUP(D425,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>51916602.99</v>
+      </c>
+      <c r="G425" s="187">
+        <f>+F425</f>
+        <v>51916602.99</v>
+      </c>
+      <c r="H425" s="132"/>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" s="76"/>
@@ -14522,13 +14526,10 @@
         <v>765</v>
       </c>
       <c r="E426" s="71"/>
-      <c r="F426" s="140">
-        <f>IFERROR(VLOOKUP(D426,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>51916602.99</v>
-      </c>
+      <c r="F426" s="140"/>
       <c r="G426" s="187">
-        <f>+F426</f>
-        <v>51916602.99</v>
+        <f>SUM(F427:F434)</f>
+        <v>768315.33</v>
       </c>
       <c r="H426" s="132"/>
     </row>
@@ -14536,27 +14537,27 @@
       <c r="A427" s="76"/>
       <c r="B427" s="76"/>
       <c r="C427" s="34"/>
-      <c r="D427" s="71" t="s">
+      <c r="D427" s="71"/>
+      <c r="E427" s="72" t="s">
         <v>766</v>
       </c>
-      <c r="E427" s="71"/>
-      <c r="F427" s="140"/>
-      <c r="G427" s="187">
-        <f>SUM(F428:F435)</f>
-        <v>768315.33</v>
-      </c>
+      <c r="F427" s="140">
+        <f>IFERROR(VLOOKUP(E427,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G427" s="138"/>
       <c r="H427" s="132"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" s="76"/>
       <c r="B428" s="76"/>
       <c r="C428" s="34"/>
-      <c r="D428" s="71"/>
-      <c r="E428" s="72" t="s">
+      <c r="D428" s="76"/>
+      <c r="E428" s="71" t="s">
         <v>767</v>
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>615911.61</v>
       </c>
       <c r="G428" s="138"/>
       <c r="H428" s="132"/>
@@ -14571,7 +14572,7 @@
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>615911.61</v>
+        <v>152403.72</v>
       </c>
       <c r="G429" s="138"/>
       <c r="H429" s="132"/>
@@ -14586,7 +14587,6 @@
       </c>
       <c r="F430" s="140">
         <f>IFERROR(VLOOKUP(E430,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>152403.72</v>
       </c>
       <c r="G430" s="138"/>
       <c r="H430" s="132"/>
@@ -14596,7 +14596,7 @@
       <c r="B431" s="76"/>
       <c r="C431" s="34"/>
       <c r="D431" s="76"/>
-      <c r="E431" s="71" t="s">
+      <c r="E431" s="72" t="s">
         <v>770</v>
       </c>
       <c r="F431" s="140">
@@ -14651,29 +14651,30 @@
       <c r="A435" s="76"/>
       <c r="B435" s="76"/>
       <c r="C435" s="34"/>
-      <c r="D435" s="76"/>
-      <c r="E435" s="72" t="s">
+      <c r="D435" s="71" t="s">
         <v>774</v>
       </c>
-      <c r="F435" s="140">
-        <f>IFERROR(VLOOKUP(E435,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G435" s="138"/>
+      <c r="E435" s="71"/>
+      <c r="F435" s="140"/>
+      <c r="G435" s="187">
+        <f>SUM(F435:F439)</f>
+        <v>17921832.18</v>
+      </c>
       <c r="H435" s="132"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" s="76"/>
       <c r="B436" s="76"/>
       <c r="C436" s="34"/>
-      <c r="D436" s="71" t="s">
+      <c r="D436" s="71"/>
+      <c r="E436" s="72" t="s">
         <v>775</v>
       </c>
-      <c r="E436" s="71"/>
-      <c r="F436" s="140"/>
-      <c r="G436" s="187">
-        <f>SUM(F436:F440)</f>
-        <v>17921832.18</v>
-      </c>
+      <c r="F436" s="140">
+        <f>IFERROR(VLOOKUP(E436,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>1413626.44</v>
+      </c>
+      <c r="G436" s="138"/>
       <c r="H436" s="132"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.25">
@@ -14686,7 +14687,7 @@
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>1413626.44</v>
+        <v>16508205.74</v>
       </c>
       <c r="G437" s="138"/>
       <c r="H437" s="132"/>
@@ -14701,7 +14702,6 @@
       </c>
       <c r="F438" s="140">
         <f>IFERROR(VLOOKUP(E438,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>16508205.74</v>
       </c>
       <c r="G438" s="138"/>
       <c r="H438" s="132"/>
@@ -14724,45 +14724,45 @@
       <c r="A440" s="76"/>
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
-      <c r="D440" s="71"/>
-      <c r="E440" s="72" t="s">
+      <c r="D440" s="71" t="s">
         <v>779</v>
       </c>
-      <c r="F440" s="140">
-        <f>IFERROR(VLOOKUP(E440,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G440" s="138"/>
+      <c r="E440" s="188"/>
+      <c r="F440" s="140"/>
+      <c r="G440" s="138">
+        <f>+F440</f>
+      </c>
       <c r="H440" s="132"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="76"/>
       <c r="B441" s="76"/>
       <c r="C441" s="34"/>
-      <c r="D441" s="71" t="s">
+      <c r="D441" s="139" t="s">
         <v>780</v>
       </c>
-      <c r="E441" s="188"/>
+      <c r="E441" s="76"/>
       <c r="F441" s="140"/>
       <c r="G441" s="138">
-        <f>+F441</f>
+        <f>SUM(F441:F443)</f>
       </c>
       <c r="H441" s="132"/>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="76"/>
       <c r="B442" s="76"/>
       <c r="C442" s="34"/>
-      <c r="D442" s="139" t="s">
+      <c r="D442" s="139"/>
+      <c r="E442" s="72" t="s">
         <v>781</v>
       </c>
-      <c r="E442" s="76"/>
-      <c r="F442" s="140"/>
-      <c r="G442" s="138">
-        <f>SUM(F442:F444)</f>
-      </c>
+      <c r="F442" s="140">
+        <f>IFERROR(VLOOKUP(E442,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G442" s="138"/>
       <c r="H442" s="132"/>
     </row>
-    <row r="443" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" s="76"/>
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
@@ -14780,44 +14780,46 @@
       <c r="A444" s="76"/>
       <c r="B444" s="76"/>
       <c r="C444" s="34"/>
-      <c r="D444" s="139"/>
-      <c r="E444" s="72" t="s">
+      <c r="D444" s="71" t="s">
         <v>783</v>
       </c>
-      <c r="F444" s="140">
-        <f>IFERROR(VLOOKUP(E444,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G444" s="138"/>
+      <c r="E444" s="188"/>
+      <c r="F444" s="140"/>
+      <c r="G444" s="187">
+        <f>SUM(F445:F448)</f>
+        <v>101483.28</v>
+      </c>
       <c r="H444" s="132"/>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" s="76"/>
       <c r="B445" s="76"/>
       <c r="C445" s="34"/>
-      <c r="D445" s="71" t="s">
+      <c r="D445" s="71"/>
+      <c r="E445" s="151" t="s">
         <v>784</v>
       </c>
-      <c r="E445" s="188"/>
-      <c r="F445" s="140"/>
-      <c r="G445" s="187">
-        <f>SUM(F446:F449)</f>
-        <v>101483.28</v>
-      </c>
+      <c r="F445" s="140">
+        <f>IFERROR(VLOOKUP(E445,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G445" s="138"/>
       <c r="H445" s="132"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" s="76"/>
       <c r="B446" s="76"/>
       <c r="C446" s="34"/>
       <c r="D446" s="71"/>
-      <c r="E446" s="151" t="s">
+      <c r="E446" s="72" t="s">
         <v>785</v>
       </c>
       <c r="F446" s="140">
         <f>IFERROR(VLOOKUP(E446,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>101483.28</v>
       </c>
       <c r="G446" s="138"/>
-      <c r="H446" s="132"/>
+      <c r="H446" s="72"/>
+      <c r="I446" s="164"/>
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" s="76"/>
@@ -14829,7 +14831,6 @@
       </c>
       <c r="F447" s="140">
         <f>IFERROR(VLOOKUP(E447,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>101483.28</v>
       </c>
       <c r="G447" s="138"/>
       <c r="H447" s="72"/>
@@ -14850,34 +14851,33 @@
       <c r="H448" s="72"/>
       <c r="I448" s="164"/>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="76"/>
       <c r="B449" s="76"/>
       <c r="C449" s="34"/>
-      <c r="D449" s="71"/>
-      <c r="E449" s="72" t="s">
+      <c r="D449" s="196" t="s">
         <v>788</v>
       </c>
-      <c r="F449" s="140">
-        <f>IFERROR(VLOOKUP(E449,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G449" s="138"/>
-      <c r="H449" s="72"/>
-      <c r="I449" s="164"/>
+      <c r="E449" s="197"/>
+      <c r="F449" s="198"/>
+      <c r="G449" s="187">
+        <f>+F450+F451+F452</f>
+        <v>8441197.290000001</v>
+      </c>
+      <c r="H449" s="132"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" s="76"/>
       <c r="B450" s="76"/>
       <c r="C450" s="34"/>
-      <c r="D450" s="196" t="s">
+      <c r="D450" s="71"/>
+      <c r="E450" s="72" t="s">
         <v>789</v>
       </c>
-      <c r="E450" s="197"/>
-      <c r="F450" s="198"/>
-      <c r="G450" s="187">
-        <f>+F451+F452+F453</f>
-        <v>8441197.290000001</v>
-      </c>
+      <c r="F450" s="140">
+        <f>IFERROR(VLOOKUP(E450,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G450" s="138"/>
       <c r="H450" s="132"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.25">
@@ -14904,6 +14904,7 @@
       </c>
       <c r="F452" s="140">
         <f>IFERROR(VLOOKUP(E452,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>8441197.290000001</v>
       </c>
       <c r="G452" s="138"/>
       <c r="H452" s="132"/>
@@ -14912,30 +14913,30 @@
       <c r="A453" s="76"/>
       <c r="B453" s="76"/>
       <c r="C453" s="34"/>
-      <c r="D453" s="71"/>
-      <c r="E453" s="72" t="s">
+      <c r="D453" s="71" t="s">
         <v>792</v>
       </c>
-      <c r="F453" s="140">
-        <f>IFERROR(VLOOKUP(E453,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>8441197.290000001</v>
-      </c>
-      <c r="G453" s="138"/>
+      <c r="E453" s="188"/>
+      <c r="F453" s="140"/>
+      <c r="G453" s="187">
+        <f>SUM(F454:F457)</f>
+        <v>14667167.22</v>
+      </c>
       <c r="H453" s="132"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" s="76"/>
       <c r="B454" s="76"/>
       <c r="C454" s="34"/>
-      <c r="D454" s="71" t="s">
+      <c r="D454" s="71"/>
+      <c r="E454" s="72" t="s">
         <v>793</v>
       </c>
-      <c r="E454" s="188"/>
-      <c r="F454" s="140"/>
-      <c r="G454" s="187">
-        <f>SUM(F455:F458)</f>
-        <v>14667167.22</v>
-      </c>
+      <c r="F454" s="140">
+        <f>IFERROR(VLOOKUP(E454,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>299800</v>
+      </c>
+      <c r="G454" s="138"/>
       <c r="H454" s="132"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.25">
@@ -14948,7 +14949,7 @@
       </c>
       <c r="F455" s="140">
         <f>IFERROR(VLOOKUP(E455,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>299800</v>
+        <v>14367367.22</v>
       </c>
       <c r="G455" s="138"/>
       <c r="H455" s="132"/>
@@ -14963,7 +14964,6 @@
       </c>
       <c r="F456" s="140">
         <f>IFERROR(VLOOKUP(E456,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>14367367.22</v>
       </c>
       <c r="G456" s="138"/>
       <c r="H456" s="132"/>
@@ -14986,14 +14986,16 @@
       <c r="A458" s="76"/>
       <c r="B458" s="76"/>
       <c r="C458" s="34"/>
-      <c r="D458" s="71"/>
-      <c r="E458" s="72" t="s">
+      <c r="D458" s="71" t="s">
         <v>797</v>
       </c>
+      <c r="E458" s="71"/>
       <c r="F458" s="140">
-        <f>IFERROR(VLOOKUP(E458,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G458" s="138"/>
+        <f>IFERROR(VLOOKUP(D458,Hoja1!$A$86:$C$353,3,FALSE),)</f>
+      </c>
+      <c r="G458" s="138">
+        <f>+F458</f>
+      </c>
       <c r="H458" s="132"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.25">
@@ -15016,15 +15018,13 @@
       <c r="A460" s="76"/>
       <c r="B460" s="76"/>
       <c r="C460" s="34"/>
-      <c r="D460" s="71" t="s">
+      <c r="D460" s="139" t="s">
         <v>799</v>
       </c>
-      <c r="E460" s="71"/>
-      <c r="F460" s="140">
-        <f>IFERROR(VLOOKUP(D460,Hoja1!$A$86:$C$353,3,FALSE),)</f>
-      </c>
+      <c r="E460" s="72"/>
+      <c r="F460" s="140"/>
       <c r="G460" s="138">
-        <f>+F460</f>
+        <f>+SUM(F461:F462)</f>
       </c>
       <c r="H460" s="132"/>
     </row>
@@ -15032,14 +15032,14 @@
       <c r="A461" s="76"/>
       <c r="B461" s="76"/>
       <c r="C461" s="34"/>
-      <c r="D461" s="139" t="s">
+      <c r="D461" s="139"/>
+      <c r="E461" s="72" t="s">
         <v>800</v>
       </c>
-      <c r="E461" s="72"/>
-      <c r="F461" s="140"/>
-      <c r="G461" s="138">
-        <f>+SUM(F462:F463)</f>
-      </c>
+      <c r="F461" s="140">
+        <f>IFERROR(VLOOKUP(E461,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G461" s="138"/>
       <c r="H461" s="132"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.25">
@@ -15060,33 +15060,34 @@
       <c r="A463" s="76"/>
       <c r="B463" s="76"/>
       <c r="C463" s="34"/>
-      <c r="D463" s="139"/>
-      <c r="E463" s="72" t="s">
+      <c r="D463" s="71" t="s">
         <v>802</v>
+      </c>
+      <c r="E463" s="71" t="s">
+        <v>803</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G463" s="138"/>
-      <c r="H463" s="132"/>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G463" s="187">
+        <f>SUM(F463:F471)</f>
+        <v>15451043.76</v>
+      </c>
+      <c r="H463" s="150"/>
+    </row>
+    <row r="464" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" s="76"/>
       <c r="B464" s="76"/>
       <c r="C464" s="34"/>
-      <c r="D464" s="71" t="s">
-        <v>803</v>
-      </c>
-      <c r="E464" s="71" t="s">
+      <c r="D464" s="71"/>
+      <c r="E464" s="72" t="s">
         <v>804</v>
       </c>
       <c r="F464" s="140">
         <f>IFERROR(VLOOKUP(E464,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G464" s="187">
-        <f>SUM(F464:F472)</f>
-        <v>15451043.76</v>
-      </c>
+        <v>7468721</v>
+      </c>
+      <c r="G464" s="138"/>
       <c r="H464" s="150"/>
     </row>
     <row r="465" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -15099,12 +15100,12 @@
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>7468721</v>
+        <v>7982322.76</v>
       </c>
       <c r="G465" s="138"/>
       <c r="H465" s="150"/>
     </row>
-    <row r="466" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="76"/>
       <c r="B466" s="76"/>
       <c r="C466" s="34"/>
@@ -15114,10 +15115,10 @@
       </c>
       <c r="F466" s="140">
         <f>IFERROR(VLOOKUP(E466,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>7982322.76</v>
       </c>
       <c r="G466" s="138"/>
-      <c r="H466" s="150"/>
+      <c r="H466" s="72"/>
+      <c r="I466" s="164"/>
     </row>
     <row r="467" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A467" s="76"/>
@@ -15194,33 +15195,32 @@
       <c r="H471" s="72"/>
       <c r="I471" s="164"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="76"/>
       <c r="B472" s="76"/>
       <c r="C472" s="34"/>
-      <c r="D472" s="71"/>
-      <c r="E472" s="72" t="s">
+      <c r="D472" s="71" t="s">
         <v>812</v>
       </c>
-      <c r="F472" s="140">
-        <f>IFERROR(VLOOKUP(E472,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G472" s="138"/>
-      <c r="H472" s="72"/>
-      <c r="I472" s="164"/>
-    </row>
-    <row r="473" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E472" s="188"/>
+      <c r="F472" s="140"/>
+      <c r="G472" s="138">
+        <f>SUM(F472:F475)</f>
+      </c>
+      <c r="H472" s="132"/>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" s="76"/>
       <c r="B473" s="76"/>
       <c r="C473" s="34"/>
-      <c r="D473" s="71" t="s">
+      <c r="D473" s="71"/>
+      <c r="E473" s="72" t="s">
         <v>813</v>
       </c>
-      <c r="E473" s="188"/>
-      <c r="F473" s="140"/>
-      <c r="G473" s="138">
-        <f>SUM(F473:F476)</f>
-      </c>
+      <c r="F473" s="140">
+        <f>IFERROR(VLOOKUP(E473,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G473" s="138"/>
       <c r="H473" s="132"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.25">
@@ -15255,21 +15255,23 @@
       <c r="A476" s="76"/>
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
-      <c r="D476" s="71"/>
-      <c r="E476" s="72" t="s">
+      <c r="D476" s="139" t="s">
         <v>816</v>
       </c>
+      <c r="E476" s="188"/>
       <c r="F476" s="140">
-        <f>IFERROR(VLOOKUP(E476,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G476" s="138"/>
+        <f>IFERROR(VLOOKUP(D476,Hoja1!$A$86:$C$353,5,FALSE),)</f>
+      </c>
+      <c r="G476" s="138">
+        <f>+F476</f>
+      </c>
       <c r="H476" s="132"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" s="76"/>
       <c r="B477" s="76"/>
       <c r="C477" s="34"/>
-      <c r="D477" s="139" t="s">
+      <c r="D477" s="71" t="s">
         <v>817</v>
       </c>
       <c r="E477" s="188"/>
@@ -15289,26 +15291,24 @@
         <v>818</v>
       </c>
       <c r="E478" s="188"/>
-      <c r="F478" s="140">
-        <f>IFERROR(VLOOKUP(D478,Hoja1!$A$86:$C$353,5,FALSE),)</f>
-      </c>
+      <c r="F478" s="140"/>
       <c r="G478" s="138">
-        <f>+F478</f>
+        <f>+F478+F479+F480</f>
       </c>
       <c r="H478" s="132"/>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="479" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" s="76"/>
       <c r="B479" s="76"/>
       <c r="C479" s="34"/>
-      <c r="D479" s="71" t="s">
+      <c r="D479" s="71"/>
+      <c r="E479" s="72" t="s">
         <v>819</v>
       </c>
-      <c r="E479" s="188"/>
-      <c r="F479" s="140"/>
-      <c r="G479" s="138">
-        <f>+F479+F480+F481</f>
-      </c>
+      <c r="F479" s="140">
+        <f>IFERROR(VLOOKUP(E479,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G479" s="138"/>
       <c r="H479" s="132"/>
     </row>
     <row r="480" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -15329,33 +15329,33 @@
       <c r="A481" s="76"/>
       <c r="B481" s="76"/>
       <c r="C481" s="34"/>
-      <c r="D481" s="71"/>
+      <c r="D481" s="71" t="s">
+        <v>821</v>
+      </c>
       <c r="E481" s="72" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G481" s="138"/>
+      <c r="G481" s="187">
+        <f>SUM(F481:F483)</f>
+        <v>4013596.99</v>
+      </c>
       <c r="H481" s="132"/>
     </row>
-    <row r="482" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" s="76"/>
       <c r="B482" s="76"/>
       <c r="C482" s="34"/>
-      <c r="D482" s="71" t="s">
-        <v>822</v>
-      </c>
+      <c r="D482" s="71"/>
       <c r="E482" s="72" t="s">
         <v>823</v>
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G482" s="187">
-        <f>SUM(F482:F484)</f>
-        <v>4013596.99</v>
-      </c>
+      <c r="G482" s="138"/>
       <c r="H482" s="132"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.25">
@@ -15368,37 +15368,38 @@
       </c>
       <c r="F483" s="140">
         <f>IFERROR(VLOOKUP(E483,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>4013596.99</v>
       </c>
       <c r="G483" s="138"/>
       <c r="H483" s="132"/>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="76"/>
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
-      <c r="D484" s="71"/>
+      <c r="D484" s="71" t="s">
+        <v>825</v>
+      </c>
       <c r="E484" s="72" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F484" s="140">
         <f>IFERROR(VLOOKUP(E484,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>4013596.99</v>
-      </c>
-      <c r="G484" s="138"/>
-      <c r="H484" s="132"/>
+      </c>
+      <c r="G484" s="138">
+        <f>+F484</f>
+      </c>
     </row>
     <row r="485" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A485" s="76"/>
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
       <c r="D485" s="71" t="s">
-        <v>826</v>
-      </c>
-      <c r="E485" s="72" t="s">
         <v>827</v>
       </c>
+      <c r="E485" s="71"/>
       <c r="F485" s="140">
-        <f>IFERROR(VLOOKUP(E485,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D485,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
       <c r="G485" s="138">
         <f>+F485</f>
@@ -15408,10 +15409,10 @@
       <c r="A486" s="76"/>
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
-      <c r="D486" s="71" t="s">
+      <c r="D486" s="139" t="s">
         <v>828</v>
       </c>
-      <c r="E486" s="71"/>
+      <c r="E486" s="72"/>
       <c r="F486" s="140">
         <f>IFERROR(VLOOKUP(D486,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15423,15 +15424,17 @@
       <c r="A487" s="76"/>
       <c r="B487" s="76"/>
       <c r="C487" s="34"/>
-      <c r="D487" s="139" t="s">
+      <c r="D487" s="71" t="s">
         <v>829</v>
       </c>
-      <c r="E487" s="72"/>
+      <c r="E487" s="68"/>
       <c r="F487" s="140">
         <f>IFERROR(VLOOKUP(D487,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G487" s="138">
+        <v>4150213.41</v>
+      </c>
+      <c r="G487" s="187">
         <f>+F487</f>
+        <v>4150213.41</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
@@ -15441,14 +15444,12 @@
       <c r="D488" s="71" t="s">
         <v>830</v>
       </c>
-      <c r="E488" s="68"/>
+      <c r="E488" s="132"/>
       <c r="F488" s="140">
         <f>IFERROR(VLOOKUP(D488,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>4150213.41</v>
-      </c>
-      <c r="G488" s="187">
+      </c>
+      <c r="G488" s="138">
         <f>+F488</f>
-        <v>4150213.41</v>
       </c>
     </row>
     <row r="489" spans="1:7" x14ac:dyDescent="0.25">
@@ -15476,9 +15477,11 @@
       <c r="E490" s="132"/>
       <c r="F490" s="140">
         <f>IFERROR(VLOOKUP(D490,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G490" s="138">
+        <v>226987</v>
+      </c>
+      <c r="G490" s="187">
         <f>+F490</f>
+        <v>226987</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
@@ -15491,28 +15494,26 @@
       <c r="E491" s="132"/>
       <c r="F491" s="140">
         <f>IFERROR(VLOOKUP(D491,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>226987</v>
+        <v>914304.7000000001</v>
       </c>
       <c r="G491" s="187">
         <f>+F491</f>
-        <v>226987</v>
+        <v>914304.7000000001</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A492" s="76"/>
       <c r="B492" s="76"/>
       <c r="C492" s="34"/>
-      <c r="D492" s="71" t="s">
+      <c r="D492" s="139" t="s">
         <v>834</v>
       </c>
       <c r="E492" s="132"/>
       <c r="F492" s="140">
         <f>IFERROR(VLOOKUP(D492,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>914304.7000000001</v>
-      </c>
-      <c r="G492" s="187">
+      </c>
+      <c r="G492" s="138">
         <f>+F492</f>
-        <v>914304.7000000001</v>
       </c>
     </row>
     <row r="493" spans="1:7" x14ac:dyDescent="0.25">
@@ -15522,7 +15523,7 @@
       <c r="D493" s="139" t="s">
         <v>835</v>
       </c>
-      <c r="E493" s="132"/>
+      <c r="E493" s="68"/>
       <c r="F493" s="140">
         <f>IFERROR(VLOOKUP(D493,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15537,7 +15538,7 @@
       <c r="D494" s="139" t="s">
         <v>836</v>
       </c>
-      <c r="E494" s="68"/>
+      <c r="E494" s="132"/>
       <c r="F494" s="140">
         <f>IFERROR(VLOOKUP(D494,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15582,32 +15583,33 @@
       <c r="D497" s="139" t="s">
         <v>839</v>
       </c>
-      <c r="E497" s="132"/>
+      <c r="E497" s="72" t="s">
+        <v>839</v>
+      </c>
       <c r="F497" s="140">
         <f>IFERROR(VLOOKUP(D497,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G497" s="138">
+        <v>358719.18</v>
+      </c>
+      <c r="G497" s="187">
         <f>+F497</f>
-      </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+        <v>358719.18</v>
+      </c>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="76"/>
       <c r="B498" s="76"/>
       <c r="C498" s="34"/>
       <c r="D498" s="139" t="s">
         <v>840</v>
       </c>
-      <c r="E498" s="72" t="s">
-        <v>840</v>
-      </c>
+      <c r="E498" s="132"/>
       <c r="F498" s="140">
         <f>IFERROR(VLOOKUP(D498,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>358719.18</v>
-      </c>
-      <c r="G498" s="187">
+      </c>
+      <c r="G498" s="138">
         <f>+F498</f>
-        <v>358719.18</v>
-      </c>
+      </c>
+      <c r="H498" s="162"/>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" s="76"/>
@@ -15657,7 +15659,7 @@
       </c>
       <c r="H501" s="162"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="76"/>
       <c r="B502" s="76"/>
       <c r="C502" s="34"/>
@@ -15671,7 +15673,6 @@
       <c r="G502" s="138">
         <f>+F502</f>
       </c>
-      <c r="H502" s="162"/>
     </row>
     <row r="503" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A503" s="76"/>
@@ -15688,19 +15689,19 @@
         <f>+F503</f>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A504" s="76"/>
       <c r="B504" s="76"/>
       <c r="C504" s="34"/>
-      <c r="D504" s="139" t="s">
-        <v>846</v>
-      </c>
+      <c r="D504" s="132"/>
       <c r="E504" s="132"/>
-      <c r="F504" s="140">
-        <f>IFERROR(VLOOKUP(D504,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G504" s="138">
-        <f>+F504</f>
+      <c r="F504" s="162"/>
+      <c r="G504" s="133"/>
+      <c r="H504" s="199" t="s">
+        <v>55</v>
+      </c>
+      <c r="I504" s="199" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="505" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15708,123 +15709,117 @@
       <c r="B505" s="76"/>
       <c r="C505" s="34"/>
       <c r="D505" s="132"/>
-      <c r="E505" s="132"/>
-      <c r="F505" s="162"/>
-      <c r="G505" s="133"/>
-      <c r="H505" s="199" t="s">
-        <v>55</v>
-      </c>
-      <c r="I505" s="199" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="506" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E505" s="200" t="s">
+        <v>846</v>
+      </c>
+      <c r="F505" s="201">
+        <f>SUM(F146:F503)</f>
+        <v>1672589124.2600002</v>
+      </c>
+      <c r="G505" s="202">
+        <f>SUM(G146:G503)</f>
+        <v>1672589124.26</v>
+      </c>
+      <c r="H505" s="199">
+        <f>+Resultados!C26</f>
+        <v>-1672589124.26</v>
+      </c>
+      <c r="I505" s="199">
+        <f>+H505+G505</f>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A506" s="76"/>
       <c r="B506" s="76"/>
       <c r="C506" s="34"/>
       <c r="D506" s="132"/>
-      <c r="E506" s="200" t="s">
+      <c r="E506" s="203" t="s">
         <v>847</v>
       </c>
-      <c r="F506" s="201">
-        <f>SUM(F146:F504)</f>
-        <v>1672589124.2600002</v>
-      </c>
-      <c r="G506" s="202">
-        <f>SUM(G146:G504)</f>
-        <v>1672589124.26</v>
-      </c>
-      <c r="H506" s="199">
-        <f>+Resultados!C26</f>
-        <v>-1672589124.26</v>
-      </c>
-      <c r="I506" s="199">
-        <f>+H506+G506</f>
-      </c>
-    </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F506" s="204">
+        <f>+-'Anexo II'!E103</f>
+        <v>-1609778933.7700005</v>
+      </c>
+      <c r="G506" s="205">
+        <f>+Hoja1!E318</f>
+        <v>1672589124.2599998</v>
+      </c>
+      <c r="H506" s="199"/>
+      <c r="I506" s="206"/>
+    </row>
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" s="76"/>
       <c r="B507" s="76"/>
       <c r="C507" s="34"/>
       <c r="D507" s="132"/>
-      <c r="E507" s="203" t="s">
+      <c r="E507" s="207" t="s">
         <v>848</v>
       </c>
-      <c r="F507" s="204">
-        <f>+-'Anexo II'!E103</f>
-        <v>-1609778933.7700005</v>
-      </c>
-      <c r="G507" s="205">
-        <f>+Hoja1!E318</f>
-        <v>1672589124.2599998</v>
-      </c>
-      <c r="H507" s="199"/>
-      <c r="I507" s="206"/>
-    </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F507" s="208">
+        <f>+F505+F506</f>
+        <v>62810190.48999977</v>
+      </c>
+      <c r="G507" s="209">
+        <f>+G506-G505</f>
+      </c>
+      <c r="H507" s="208"/>
+    </row>
+    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="76"/>
       <c r="B508" s="76"/>
       <c r="C508" s="34"/>
       <c r="D508" s="132"/>
-      <c r="E508" s="207" t="s">
+      <c r="E508" s="132"/>
+      <c r="F508" s="162">
+        <f>+F507-F281</f>
+        <v>-2.3096799850463867e-7</v>
+      </c>
+      <c r="G508" s="133"/>
+    </row>
+    <row r="509" ht="10.8" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="210"/>
+      <c r="B509" s="210"/>
+      <c r="C509" s="211"/>
+      <c r="D509" s="211"/>
+      <c r="E509" s="211" t="s">
         <v>849</v>
       </c>
-      <c r="F508" s="208">
-        <f>+F506+F507</f>
-        <v>62810190.48999977</v>
-      </c>
-      <c r="G508" s="209">
-        <f>+G507-G506</f>
-      </c>
-      <c r="H508" s="208"/>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A509" s="76"/>
-      <c r="B509" s="76"/>
-      <c r="C509" s="34"/>
-      <c r="D509" s="132"/>
-      <c r="E509" s="132"/>
-      <c r="F509" s="162">
-        <f>+F508-F281</f>
-        <v>-2.3096799850463867e-7</v>
-      </c>
-      <c r="G509" s="133"/>
-    </row>
-    <row r="510" ht="10.8" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="210"/>
-      <c r="B510" s="210"/>
-      <c r="C510" s="211"/>
-      <c r="D510" s="211"/>
-      <c r="E510" s="211" t="s">
-        <v>850</v>
-      </c>
-      <c r="F510" s="211">
-        <f>+F281-F508</f>
+      <c r="F509" s="211">
+        <f>+F281-F507</f>
         <v>2.3096799850463867e-7</v>
       </c>
-      <c r="G510" s="212"/>
-      <c r="H510" s="211"/>
-      <c r="I510" s="213"/>
-      <c r="J510" s="211"/>
-      <c r="K510" s="211"/>
-    </row>
-    <row r="511" ht="13.8" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A511" s="215"/>
-      <c r="B511" s="214"/>
-      <c r="C511" s="216"/>
-      <c r="D511" s="214"/>
-      <c r="E511" s="217"/>
-      <c r="F511" s="217"/>
-      <c r="G511" s="218">
-        <f>SUM(G3:G505)</f>
+      <c r="G509" s="212"/>
+      <c r="H509" s="211"/>
+      <c r="I509" s="213"/>
+      <c r="J509" s="211"/>
+      <c r="K509" s="211"/>
+    </row>
+    <row r="510" ht="13.8" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="215"/>
+      <c r="B510" s="214"/>
+      <c r="C510" s="216"/>
+      <c r="D510" s="214"/>
+      <c r="E510" s="217"/>
+      <c r="F510" s="217"/>
+      <c r="G510" s="218">
+        <f>SUM(G3:G504)</f>
         <v>-5.651381798088551e-7</v>
       </c>
-      <c r="H511" s="217"/>
-      <c r="I511" s="219"/>
-      <c r="J511" s="217"/>
-      <c r="K511" s="217"/>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H510" s="217"/>
+      <c r="I510" s="219"/>
+      <c r="J510" s="217"/>
+      <c r="K510" s="217"/>
+    </row>
+    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A511" s="76"/>
+      <c r="B511" s="76"/>
+      <c r="C511" s="34"/>
+      <c r="D511" s="132"/>
+      <c r="E511" s="132"/>
+      <c r="F511" s="132"/>
+      <c r="G511" s="132"/>
+    </row>
+    <row r="512" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="76"/>
       <c r="B512" s="76"/>
       <c r="C512" s="34"/>
@@ -15832,6 +15827,10 @@
       <c r="E512" s="132"/>
       <c r="F512" s="132"/>
       <c r="G512" s="132"/>
+      <c r="H512" s="132"/>
+      <c r="I512" s="134"/>
+      <c r="J512" s="132"/>
+      <c r="K512" s="132"/>
     </row>
     <row r="513" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A513" s="76"/>
@@ -34149,19 +34148,6 @@
       <c r="I1921" s="134"/>
       <c r="J1921" s="132"/>
       <c r="K1921" s="132"/>
-    </row>
-    <row r="1922" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1922" s="76"/>
-      <c r="B1922" s="76"/>
-      <c r="C1922" s="34"/>
-      <c r="D1922" s="132"/>
-      <c r="E1922" s="132"/>
-      <c r="F1922" s="132"/>
-      <c r="G1922" s="132"/>
-      <c r="H1922" s="132"/>
-      <c r="I1922" s="134"/>
-      <c r="J1922" s="132"/>
-      <c r="K1922" s="132"/>
     </row>
   </sheetData>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -34193,7 +34179,7 @@
       <c r="C1" s="222"/>
       <c r="D1" s="222"/>
       <c r="E1" s="223" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F1" s="224"/>
       <c r="G1" s="224"/>
@@ -34211,7 +34197,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="195"/>
@@ -34277,7 +34263,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B9" s="151"/>
       <c r="C9" s="195"/>
@@ -34682,7 +34668,7 @@
       <c r="E45" s="220"/>
       <c r="F45" s="220"/>
       <c r="G45" s="226" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H45" s="227" t="s">
         <v>445</v>
@@ -34814,7 +34800,7 @@
       <c r="D56" s="232"/>
       <c r="E56" s="232"/>
       <c r="F56" s="232" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="G56" s="232"/>
     </row>
@@ -34838,7 +34824,7 @@
     </row>
     <row r="59" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="72" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="195"/>
@@ -35000,7 +34986,7 @@
     </row>
     <row r="77" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="72" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B77" s="151"/>
       <c r="C77" s="195"/>
@@ -35009,7 +34995,7 @@
     </row>
     <row r="78" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="72" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B78" s="151"/>
       <c r="C78" s="195"/>
@@ -35045,7 +35031,7 @@
     </row>
     <row r="82" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="72" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B82" s="151"/>
       <c r="C82" s="195"/>
@@ -35093,7 +35079,7 @@
     </row>
     <row r="87" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B87" s="151"/>
       <c r="C87" s="195"/>
@@ -35156,7 +35142,7 @@
     </row>
     <row r="94" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="72" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B94" s="151"/>
       <c r="C94" s="195"/>
@@ -35165,7 +35151,7 @@
     </row>
     <row r="95" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="72" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B95" s="151"/>
       <c r="C95" s="195"/>
@@ -35174,7 +35160,7 @@
     </row>
     <row r="96" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="72" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B96" s="151"/>
       <c r="C96" s="195"/>
@@ -35183,7 +35169,7 @@
     </row>
     <row r="97" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="72" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B97" s="151"/>
       <c r="C97" s="195"/>
@@ -35853,13 +35839,13 @@
     </row>
     <row r="191" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="221" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B191" s="233"/>
       <c r="C191" s="233"/>
       <c r="D191" s="233"/>
       <c r="E191" s="223" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="192" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
@@ -35930,7 +35916,7 @@
     </row>
     <row r="198" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="72" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B198" s="151"/>
       <c r="C198" s="195"/>
@@ -35974,7 +35960,7 @@
     </row>
     <row r="202" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="72" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B202" s="151"/>
       <c r="C202" s="195"/>
@@ -36018,7 +36004,7 @@
     </row>
     <row r="206" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="72" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B206" s="151"/>
       <c r="C206" s="195"/>
@@ -36040,7 +36026,7 @@
     </row>
     <row r="208" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="72" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B208" s="151"/>
       <c r="C208" s="195"/>
@@ -36051,7 +36037,7 @@
     </row>
     <row r="209" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="72" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B209" s="151"/>
       <c r="C209" s="195"/>
@@ -36108,7 +36094,7 @@
     </row>
     <row r="214" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="72" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B214" s="151"/>
       <c r="C214" s="195"/>
@@ -36229,7 +36215,7 @@
     </row>
     <row r="225" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="72" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B225" s="151"/>
       <c r="C225" s="195"/>
@@ -36240,7 +36226,7 @@
     </row>
     <row r="226" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="72" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B226" s="151"/>
       <c r="C226" s="195"/>
@@ -36262,7 +36248,7 @@
     </row>
     <row r="228" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="72" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B228" s="151"/>
       <c r="C228" s="195"/>
@@ -36284,7 +36270,7 @@
     </row>
     <row r="230" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="72" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B230" s="151"/>
       <c r="C230" s="195"/>
@@ -36328,7 +36314,7 @@
     </row>
     <row r="234" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="72" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B234" s="151"/>
       <c r="C234" s="195"/>
@@ -36339,7 +36325,7 @@
     </row>
     <row r="235" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="72" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B235" s="151"/>
       <c r="C235" s="195"/>
@@ -36383,7 +36369,7 @@
     </row>
     <row r="239" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="72" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B239" s="151"/>
       <c r="C239" s="195"/>
@@ -36394,7 +36380,7 @@
     </row>
     <row r="240" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="72" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B240" s="151"/>
       <c r="C240" s="195"/>
@@ -36416,7 +36402,7 @@
     </row>
     <row r="242" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="72" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B242" s="151"/>
       <c r="C242" s="195"/>
@@ -36471,7 +36457,7 @@
     </row>
     <row r="247" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B247" s="151"/>
       <c r="C247" s="195"/>
@@ -36482,7 +36468,7 @@
     </row>
     <row r="248" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="72" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B248" s="151"/>
       <c r="C248" s="195"/>
@@ -36592,7 +36578,7 @@
     </row>
     <row r="258" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="72" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B258" s="151"/>
       <c r="C258" s="195"/>
@@ -36603,7 +36589,7 @@
     </row>
     <row r="259" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="72" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B259" s="151"/>
       <c r="C259" s="195"/>
@@ -36614,7 +36600,7 @@
     </row>
     <row r="260" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="72" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B260" s="151"/>
       <c r="C260" s="195"/>
@@ -36625,7 +36611,7 @@
     </row>
     <row r="261" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="72" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B261" s="151"/>
       <c r="C261" s="195"/>
@@ -36669,7 +36655,7 @@
     </row>
     <row r="265" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="72" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B265" s="151"/>
       <c r="C265" s="195"/>
@@ -36680,7 +36666,7 @@
     </row>
     <row r="266" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="72" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B266" s="151"/>
       <c r="C266" s="195"/>
@@ -36691,7 +36677,7 @@
     </row>
     <row r="267" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="72" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B267" s="151"/>
       <c r="C267" s="195"/>
@@ -36702,7 +36688,7 @@
     </row>
     <row r="268" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="72" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B268" s="151"/>
       <c r="C268" s="195"/>
@@ -36790,7 +36776,7 @@
     </row>
     <row r="276" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="72" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B276" s="151"/>
       <c r="C276" s="195"/>
@@ -36812,7 +36798,7 @@
     </row>
     <row r="278" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="72" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B278" s="151"/>
       <c r="C278" s="195"/>
@@ -36845,7 +36831,7 @@
     </row>
     <row r="281" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="72" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="195"/>
@@ -36867,7 +36853,7 @@
     </row>
     <row r="283" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="72" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B283" s="151"/>
       <c r="C283" s="195"/>
@@ -36878,7 +36864,7 @@
     </row>
     <row r="284" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="72" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B284" s="151"/>
       <c r="C284" s="195"/>
@@ -36911,7 +36897,7 @@
     </row>
     <row r="287" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="72" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B287" s="151"/>
       <c r="C287" s="195"/>
@@ -36922,7 +36908,7 @@
     </row>
     <row r="288" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B288" s="151"/>
       <c r="C288" s="195"/>
@@ -36933,7 +36919,7 @@
     </row>
     <row r="289" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="72" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B289" s="151"/>
       <c r="C289" s="195"/>
@@ -36944,7 +36930,7 @@
     </row>
     <row r="290" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="72" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B290" s="151"/>
       <c r="C290" s="195"/>
@@ -36966,7 +36952,7 @@
     </row>
     <row r="292" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="72" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B292" s="151"/>
       <c r="C292" s="195"/>
@@ -36978,7 +36964,7 @@
     </row>
     <row r="293" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="72" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B293" s="151"/>
       <c r="C293" s="195"/>
@@ -37024,7 +37010,7 @@
     </row>
     <row r="297" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="72" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B297" s="151"/>
       <c r="C297" s="195"/>
@@ -37090,7 +37076,7 @@
     </row>
     <row r="303" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="72" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B303" s="151"/>
       <c r="C303" s="195"/>
@@ -37112,7 +37098,7 @@
     </row>
     <row r="305" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="72" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B305" s="151"/>
       <c r="C305" s="195"/>
@@ -37123,7 +37109,7 @@
     </row>
     <row r="306" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="72" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B306" s="151"/>
       <c r="C306" s="195"/>
@@ -37249,10 +37235,10 @@
       <c r="D317" s="225"/>
       <c r="E317" s="195"/>
       <c r="F317" s="238" t="s">
+        <v>868</v>
+      </c>
+      <c r="G317" s="239" t="s">
         <v>869</v>
-      </c>
-      <c r="G317" s="239" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="318" ht="10.2" customHeight="1" spans="1:7" s="235" customFormat="1" x14ac:dyDescent="0.25">
@@ -37477,7 +37463,7 @@
         <v>0</v>
       </c>
       <c r="H345" s="72" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
@@ -37507,7 +37493,7 @@
       <c r="F347" s="220"/>
       <c r="G347" s="225"/>
       <c r="H347" s="72" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -37525,10 +37511,10 @@
       <c r="E349" s="140"/>
       <c r="F349" s="220"/>
       <c r="G349" s="244" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H349" s="245" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
@@ -39852,7 +39838,7 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="18">
-        <f>-SALDOS!G485</f>
+        <f>-SALDOS!G484</f>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -17,7 +17,7 @@
     <sheet sheetId="15" name="Hoja1" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase">SALDOS!$F$1:$F$510</definedName>
+    <definedName name="_xlnm._FilterDatabase">SALDOS!$F$1:$F$509</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Balance'!$A1:$L34</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Anexo I'!$O15:$O23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Anexo II'!$A2:$J113</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="871">
   <si>
     <t>ESTADO DE SITUACION PATRIMONIAL</t>
   </si>
@@ -1602,9 +1602,6 @@
   </si>
   <si>
     <t>426360000 - Vacaciones Gs Campo</t>
-  </si>
-  <si>
-    <t>421170000 - Gastos Legales</t>
   </si>
   <si>
     <t>42202000 - Certificaciones</t>
@@ -4540,7 +4537,7 @@
       <c r="F10" s="124"/>
       <c r="G10" s="16"/>
       <c r="H10" s="19">
-        <f>+SALDOS!G323</f>
+        <f>+SALDOS!G322</f>
         <v>51970355.11</v>
       </c>
       <c r="I10" s="125"/>
@@ -4560,7 +4557,7 @@
         <v>262653256.83999997</v>
       </c>
       <c r="F11" s="124">
-        <f>+SALDOS!G369</f>
+        <f>+SALDOS!G368</f>
         <v>262653256.83999997</v>
       </c>
       <c r="G11" s="16"/>
@@ -4584,7 +4581,7 @@
       <c r="F12" s="124"/>
       <c r="G12" s="16"/>
       <c r="H12" s="19">
-        <f>+SALDOS!G375</f>
+        <f>+SALDOS!G374</f>
         <v>58572858.17</v>
       </c>
       <c r="I12" s="125"/>
@@ -4606,7 +4603,7 @@
       <c r="F13" s="124"/>
       <c r="G13" s="16"/>
       <c r="H13" s="19">
-        <f>+SALDOS!G258</f>
+        <f>+SALDOS!G257</f>
       </c>
       <c r="I13" s="125"/>
       <c r="J13" s="123"/>
@@ -4627,7 +4624,7 @@
       <c r="F14" s="124"/>
       <c r="G14" s="16"/>
       <c r="H14" s="19">
-        <f>+SALDOS!G303</f>
+        <f>+SALDOS!G302</f>
         <v>189946.28</v>
       </c>
       <c r="I14" s="125"/>
@@ -4649,7 +4646,7 @@
       <c r="F15" s="124"/>
       <c r="G15" s="16"/>
       <c r="H15" s="19">
-        <f>+SALDOS!G403</f>
+        <f>+SALDOS!G402</f>
       </c>
       <c r="I15" s="125"/>
       <c r="J15" s="123"/>
@@ -4692,7 +4689,7 @@
       <c r="F17" s="124"/>
       <c r="G17" s="16"/>
       <c r="H17" s="19">
-        <f>+SALDOS!G315</f>
+        <f>+SALDOS!G314</f>
       </c>
       <c r="I17" s="125"/>
       <c r="J17" s="123"/>
@@ -4713,7 +4710,7 @@
       <c r="F18" s="124"/>
       <c r="G18" s="16"/>
       <c r="H18" s="19">
-        <f>+SALDOS!G359+SALDOS!G398</f>
+        <f>+SALDOS!G358+SALDOS!G397</f>
       </c>
       <c r="I18" s="125"/>
       <c r="J18" s="123"/>
@@ -4734,7 +4731,7 @@
       <c r="F19" s="124"/>
       <c r="G19" s="16"/>
       <c r="H19" s="19">
-        <f>+SALDOS!G362</f>
+        <f>+SALDOS!G361</f>
       </c>
       <c r="I19" s="125"/>
       <c r="J19" s="123"/>
@@ -4780,7 +4777,7 @@
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="19">
-        <f>+SALDOS!G425</f>
+        <f>+SALDOS!G424</f>
         <v>51916602.99</v>
       </c>
       <c r="I21" s="125"/>
@@ -4802,7 +4799,7 @@
       <c r="F22" s="124"/>
       <c r="G22" s="16"/>
       <c r="H22" s="19">
-        <f>+SALDOS!G307+SALDOS!G309+SALDOS!G310+SALDOS!G308</f>
+        <f>+SALDOS!G306+SALDOS!G308+SALDOS!G309+SALDOS!G307</f>
         <v>48607846.6</v>
       </c>
       <c r="I22" s="125"/>
@@ -4841,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="124">
-        <f>+SALDOS!G203</f>
+        <f>+SALDOS!G202</f>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="19"/>
@@ -4864,7 +4861,7 @@
       <c r="F25" s="124"/>
       <c r="G25" s="16"/>
       <c r="H25" s="19">
-        <f>+SALDOS!G352</f>
+        <f>+SALDOS!G351</f>
         <v>8616654.57</v>
       </c>
       <c r="I25" s="125"/>
@@ -4886,7 +4883,7 @@
       <c r="F26" s="124"/>
       <c r="G26" s="16"/>
       <c r="H26" s="19">
-        <f>+SALDOS!G331</f>
+        <f>+SALDOS!G330</f>
         <v>27411009.17</v>
       </c>
       <c r="I26" s="125"/>
@@ -4925,7 +4922,7 @@
         <v>7955308.800000001</v>
       </c>
       <c r="F28" s="124">
-        <f>+SALDOS!G343+SALDOS!G496+SALDOS!G497</f>
+        <f>+SALDOS!G342+SALDOS!G495+SALDOS!G496</f>
         <v>7955308.800000001</v>
       </c>
       <c r="G28" s="16"/>
@@ -4968,7 +4965,7 @@
       <c r="F30" s="124"/>
       <c r="G30" s="16"/>
       <c r="H30" s="19">
-        <f>+SALDOS!G312</f>
+        <f>+SALDOS!G311</f>
       </c>
       <c r="I30" s="125"/>
       <c r="J30" s="123"/>
@@ -4987,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="124">
-        <f>+SALDOS!G240</f>
+        <f>+SALDOS!G239</f>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="19"/>
@@ -5010,7 +5007,7 @@
       <c r="F32" s="124"/>
       <c r="G32" s="16"/>
       <c r="H32" s="19">
-        <f>+SALDOS!G440</f>
+        <f>+SALDOS!G439</f>
       </c>
       <c r="I32" s="125"/>
       <c r="J32" s="123"/>
@@ -5029,7 +5026,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="124">
-        <f>+SALDOS!G472</f>
+        <f>+SALDOS!G471</f>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="19"/>
@@ -5050,7 +5047,7 @@
         <v>489482.99</v>
       </c>
       <c r="F34" s="126">
-        <f>+SALDOS!G407</f>
+        <f>+SALDOS!G406</f>
         <v>489482.99</v>
       </c>
       <c r="G34" s="16"/>
@@ -5072,7 +5069,7 @@
         <v>9664883.07</v>
       </c>
       <c r="F35" s="125">
-        <f>+SALDOS!G265</f>
+        <f>+SALDOS!G264</f>
         <v>9664883.07</v>
       </c>
       <c r="G35" s="16"/>
@@ -5099,7 +5096,7 @@
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="19">
-        <f>+SALDOS!G214+SALDOS!G394+SALDOS!G458</f>
+        <f>+SALDOS!G213+SALDOS!G393+SALDOS!G457</f>
         <v>5887375.78</v>
       </c>
       <c r="I36" s="125"/>
@@ -5119,7 +5116,7 @@
         <v>15451043.76</v>
       </c>
       <c r="F37" s="124">
-        <f>+SALDOS!G463</f>
+        <f>+SALDOS!G462</f>
         <v>15451043.76</v>
       </c>
       <c r="G37" s="16"/>
@@ -5143,7 +5140,7 @@
       <c r="F38" s="124"/>
       <c r="G38" s="16"/>
       <c r="H38" s="19">
-        <f>+SALDOS!G400+SALDOS!G441</f>
+        <f>+SALDOS!G399+SALDOS!G440</f>
       </c>
       <c r="I38" s="125"/>
       <c r="J38" s="123"/>
@@ -5164,7 +5161,7 @@
       <c r="F39" s="124"/>
       <c r="G39" s="16"/>
       <c r="H39" s="19">
-        <f>+SALDOS!G449</f>
+        <f>+SALDOS!G448</f>
         <v>8441197.290000001</v>
       </c>
       <c r="I39" s="125"/>
@@ -5184,7 +5181,7 @@
         <v>5034121.24</v>
       </c>
       <c r="F40" s="124">
-        <f>+SALDOS!G218</f>
+        <f>+SALDOS!G217</f>
         <v>5034121.24</v>
       </c>
       <c r="G40" s="16"/>
@@ -5206,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="124">
-        <f>+SALDOS!G239</f>
+        <f>+SALDOS!G238</f>
       </c>
       <c r="G41" s="16"/>
       <c r="H41" s="19"/>
@@ -5227,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="124">
-        <f>+SALDOS!G364</f>
+        <f>+SALDOS!G363</f>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="19"/>
@@ -5250,7 +5247,7 @@
       <c r="F43" s="124"/>
       <c r="G43" s="16"/>
       <c r="H43" s="19">
-        <f>+SALDOS!G316</f>
+        <f>+SALDOS!G315</f>
         <v>18512.4</v>
       </c>
       <c r="I43" s="125"/>
@@ -5272,7 +5269,7 @@
       <c r="F44" s="124"/>
       <c r="G44" s="16"/>
       <c r="H44" s="19">
-        <f>+SALDOS!G386</f>
+        <f>+SALDOS!G385</f>
       </c>
       <c r="I44" s="125"/>
       <c r="J44" s="123"/>
@@ -5313,7 +5310,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="124">
-        <f>+SALDOS!G460</f>
+        <f>+SALDOS!G459</f>
       </c>
       <c r="G46" s="16"/>
       <c r="H46" s="19"/>
@@ -5334,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="124">
-        <f>+SALDOS!G257</f>
+        <f>+SALDOS!G256</f>
       </c>
       <c r="G47" s="16"/>
       <c r="H47" s="19"/>
@@ -5357,7 +5354,7 @@
       <c r="F48" s="124"/>
       <c r="G48" s="16"/>
       <c r="H48" s="19">
-        <f>+SALDOS!G414</f>
+        <f>+SALDOS!G413</f>
         <v>236115665.5</v>
       </c>
       <c r="I48" s="125"/>
@@ -5377,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="124">
-        <f>+SALDOS!G234</f>
+        <f>+SALDOS!G233</f>
       </c>
       <c r="G49" s="16"/>
       <c r="H49" s="19"/>
@@ -5398,7 +5395,7 @@
         <v>14667167.22</v>
       </c>
       <c r="F50" s="124">
-        <f>+SALDOS!G453</f>
+        <f>+SALDOS!G452</f>
         <v>14667167.22</v>
       </c>
       <c r="G50" s="16"/>
@@ -5420,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="124">
-        <f>+SALDOS!G233</f>
+        <f>+SALDOS!G232</f>
       </c>
       <c r="G51" s="16"/>
       <c r="H51" s="19"/>
@@ -5441,12 +5438,12 @@
         <v>9103800</v>
       </c>
       <c r="F52" s="124">
-        <f>+SALDOS!G186+SALDOS!G231+SALDOS!G368+SALDOS!G387</f>
+        <f>+SALDOS!G186+SALDOS!G230+SALDOS!G367+SALDOS!G386</f>
         <v>39000</v>
       </c>
       <c r="G52" s="16"/>
       <c r="H52" s="19">
-        <f>+SALDOS!G391</f>
+        <f>+SALDOS!G390</f>
         <v>9064800</v>
       </c>
       <c r="I52" s="125"/>
@@ -5468,7 +5465,7 @@
       <c r="F53" s="124"/>
       <c r="G53" s="16"/>
       <c r="H53" s="19">
-        <f>+SALDOS!G295</f>
+        <f>+SALDOS!G294</f>
         <v>832331.1900000001</v>
       </c>
       <c r="I53" s="125"/>
@@ -5490,7 +5487,7 @@
       <c r="F54" s="124"/>
       <c r="G54" s="16"/>
       <c r="H54" s="19">
-        <f>+SALDOS!G311</f>
+        <f>+SALDOS!G310</f>
       </c>
       <c r="I54" s="125"/>
       <c r="J54" s="123"/>
@@ -5553,7 +5550,7 @@
         <v>22769032.28</v>
       </c>
       <c r="F57" s="124">
-        <f>+SALDOS!G270</f>
+        <f>+SALDOS!G269</f>
         <v>22769032.28</v>
       </c>
       <c r="G57" s="19"/>
@@ -5575,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="124">
-        <f>+SALDOS!G273+SALDOS!G283</f>
+        <f>+SALDOS!G272+SALDOS!G282</f>
       </c>
       <c r="G58" s="19"/>
       <c r="H58" s="16"/>
@@ -5596,7 +5593,7 @@
         <v>11619112.85</v>
       </c>
       <c r="F59" s="124">
-        <f>+SALDOS!G168+SALDOS!G284+SALDOS!G285+SALDOS!G494+SALDOS!F499</f>
+        <f>+SALDOS!G168+SALDOS!G283+SALDOS!G284+SALDOS!G493+SALDOS!F498</f>
         <v>11619112.85</v>
       </c>
       <c r="G59" s="17"/>
@@ -5618,7 +5615,7 @@
         <v>768315.33</v>
       </c>
       <c r="F60" s="124">
-        <f>+SALDOS!G426</f>
+        <f>+SALDOS!G425</f>
         <v>768315.33</v>
       </c>
       <c r="G60" s="16"/>
@@ -5642,7 +5639,7 @@
       <c r="F61" s="124"/>
       <c r="G61" s="16"/>
       <c r="H61" s="19">
-        <f>+SALDOS!G294</f>
+        <f>+SALDOS!G293</f>
       </c>
       <c r="I61" s="125"/>
       <c r="J61" s="123"/>
@@ -5661,7 +5658,7 @@
         <v>149263.11</v>
       </c>
       <c r="F62" s="124">
-        <f>+SALDOS!G247</f>
+        <f>+SALDOS!G246</f>
         <v>149263.11</v>
       </c>
       <c r="G62" s="16"/>
@@ -5683,12 +5680,12 @@
         <v>88381242.3</v>
       </c>
       <c r="F63" s="124">
-        <f>+SALDOS!G171+SALDOS!G339+SALDOS!G390+SALDOS!G340</f>
+        <f>+SALDOS!G171+SALDOS!G338+SALDOS!G389+SALDOS!G339</f>
         <v>1068794.41</v>
       </c>
       <c r="G63" s="16"/>
       <c r="H63" s="19">
-        <f>+SALDOS!G319</f>
+        <f>+SALDOS!G318</f>
         <v>87312447.89</v>
       </c>
       <c r="I63" s="125"/>
@@ -5710,7 +5707,7 @@
       <c r="F64" s="124"/>
       <c r="G64" s="16"/>
       <c r="H64" s="19">
-        <f>+SALDOS!G244</f>
+        <f>+SALDOS!G243</f>
         <v>101825.6</v>
       </c>
       <c r="I64" s="125"/>
@@ -5730,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="124">
-        <f>+SALDOS!G478</f>
+        <f>+SALDOS!G477</f>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="19"/>
@@ -5770,7 +5767,7 @@
         <v>2052084.4000000001</v>
       </c>
       <c r="F67" s="124">
-        <f>+SALDOS!G227</f>
+        <f>+SALDOS!G226</f>
         <v>2052084.4000000001</v>
       </c>
       <c r="G67" s="16"/>
@@ -5813,7 +5810,7 @@
       <c r="F69" s="124"/>
       <c r="G69" s="16"/>
       <c r="H69" s="19">
-        <f>+SALDOS!G388</f>
+        <f>+SALDOS!G387</f>
       </c>
       <c r="I69" s="125"/>
       <c r="J69" s="123"/>
@@ -5851,7 +5848,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="124">
-        <f>+SALDOS!G235</f>
+        <f>+SALDOS!G234</f>
       </c>
       <c r="G71" s="16"/>
       <c r="H71" s="19"/>
@@ -5872,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="124">
-        <f>+SALDOS!G488</f>
+        <f>+SALDOS!G487</f>
       </c>
       <c r="G72" s="16"/>
       <c r="H72" s="19"/>
@@ -5893,7 +5890,7 @@
         <v>700000</v>
       </c>
       <c r="F73" s="124">
-        <f>+SALDOS!G209</f>
+        <f>+SALDOS!G208</f>
         <v>700000</v>
       </c>
       <c r="G73" s="16"/>
@@ -5915,7 +5912,7 @@
         <v>4013596.99</v>
       </c>
       <c r="F74" s="19">
-        <f>+SALDOS!G481</f>
+        <f>+SALDOS!G480</f>
         <v>4013596.99</v>
       </c>
       <c r="G74" s="16"/>
@@ -5937,7 +5934,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="125">
-        <f>+SALDOS!G206</f>
+        <f>+SALDOS!G205</f>
       </c>
       <c r="G75" s="16"/>
       <c r="H75" s="16"/>
@@ -5958,7 +5955,7 @@
         <v>17921832.18</v>
       </c>
       <c r="F76" s="124">
-        <f>+SALDOS!G435</f>
+        <f>+SALDOS!G434</f>
         <v>17921832.18</v>
       </c>
       <c r="G76" s="16"/>
@@ -5980,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="124">
-        <f>+SALDOS!G489</f>
+        <f>+SALDOS!G488</f>
       </c>
       <c r="G77" s="16"/>
       <c r="H77" s="19"/>
@@ -6003,7 +6000,7 @@
       <c r="F78" s="124"/>
       <c r="G78" s="16"/>
       <c r="H78" s="19">
-        <f>+SALDOS!G318</f>
+        <f>+SALDOS!G317</f>
       </c>
       <c r="I78" s="125"/>
       <c r="J78" s="123"/>
@@ -6024,7 +6021,7 @@
       <c r="F79" s="124"/>
       <c r="G79" s="16"/>
       <c r="H79" s="19">
-        <f>+SALDOS!G486</f>
+        <f>+SALDOS!G485</f>
       </c>
       <c r="I79" s="125"/>
       <c r="J79" s="123"/>
@@ -6045,7 +6042,7 @@
       <c r="F80" s="124"/>
       <c r="G80" s="16"/>
       <c r="H80" s="19">
-        <f>+SALDOS!G487</f>
+        <f>+SALDOS!G486</f>
         <v>4150213.41</v>
       </c>
       <c r="I80" s="125"/>
@@ -6070,7 +6067,7 @@
       </c>
       <c r="G81" s="16"/>
       <c r="H81" s="19">
-        <f>+SALDOS!G402</f>
+        <f>+SALDOS!G401</f>
         <v>276280951</v>
       </c>
       <c r="I81" s="125"/>
@@ -6090,11 +6087,11 @@
         <v>3499846.7</v>
       </c>
       <c r="F82" s="124">
-        <f>+SALDOS!G282+SALDOS!G197</f>
+        <f>+SALDOS!G281+SALDOS!G197</f>
       </c>
       <c r="G82" s="16"/>
       <c r="H82" s="19">
-        <f>+SALDOS!G417</f>
+        <f>+SALDOS!G416</f>
         <v>3499846.7</v>
       </c>
       <c r="I82" s="125"/>
@@ -6138,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="124">
-        <f>+SALDOS!G264</f>
+        <f>+SALDOS!G263</f>
       </c>
       <c r="G84" s="16"/>
       <c r="H84" s="19"/>
@@ -6159,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="124">
-        <f>+SALDOS!G385</f>
+        <f>+SALDOS!G384</f>
       </c>
       <c r="G85" s="16"/>
       <c r="H85" s="19"/>
@@ -6180,7 +6177,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="124">
-        <f>+SALDOS!G246</f>
+        <f>+SALDOS!G245</f>
       </c>
       <c r="G86" s="16"/>
       <c r="H86" s="19"/>
@@ -6224,7 +6221,7 @@
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
       <c r="H88" s="19">
-        <f>+SALDOS!G416</f>
+        <f>+SALDOS!G415</f>
       </c>
       <c r="I88" s="125"/>
       <c r="J88" s="123"/>
@@ -6243,7 +6240,7 @@
         <v>101483.28</v>
       </c>
       <c r="F89" s="16">
-        <f>+SALDOS!G444</f>
+        <f>+SALDOS!G443</f>
         <v>101483.28</v>
       </c>
       <c r="G89" s="16"/>
@@ -6267,7 +6264,7 @@
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
       <c r="H90" s="19">
-        <f>+SALDOS!G476</f>
+        <f>+SALDOS!G475</f>
       </c>
       <c r="I90" s="125"/>
       <c r="J90" s="123"/>
@@ -6307,9 +6304,7 @@
         <f>SUM(F92:I92)</f>
         <v>0</v>
       </c>
-      <c r="F92" s="16">
-        <f>+SALDOS!G202</f>
-      </c>
+      <c r="F92" s="16"/>
       <c r="G92" s="16"/>
       <c r="H92" s="19"/>
       <c r="I92" s="125"/>
@@ -6329,7 +6324,7 @@
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
       <c r="H93" s="19">
-        <f>+SALDOS!G490</f>
+        <f>+SALDOS!G489</f>
         <v>226987</v>
       </c>
       <c r="I93" s="125"/>
@@ -6351,7 +6346,7 @@
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
       <c r="H94" s="19">
-        <f>+SALDOS!G491+SALDOS!G492</f>
+        <f>+SALDOS!G490+SALDOS!G491</f>
         <v>914304.7000000001</v>
       </c>
       <c r="I94" s="125"/>
@@ -6395,7 +6390,7 @@
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
       <c r="H96" s="19">
-        <f>+SALDOS!G495</f>
+        <f>+SALDOS!G494</f>
       </c>
       <c r="I96" s="125"/>
       <c r="J96" s="123"/>
@@ -6416,7 +6411,7 @@
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
       <c r="H97" s="19">
-        <f>+SALDOS!F493</f>
+        <f>+SALDOS!F492</f>
       </c>
       <c r="I97" s="125"/>
       <c r="J97" s="123"/>
@@ -6437,7 +6432,7 @@
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="19">
-        <f>+SALDOS!G498</f>
+        <f>+SALDOS!G497</f>
       </c>
       <c r="I98" s="125"/>
       <c r="J98" s="123"/>
@@ -6458,7 +6453,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="19">
-        <f>+SALDOS!G500</f>
+        <f>+SALDOS!G499</f>
       </c>
       <c r="I99" s="125"/>
       <c r="J99" s="123"/>
@@ -6479,7 +6474,7 @@
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="19">
-        <f>+SALDOS!G501</f>
+        <f>+SALDOS!G500</f>
       </c>
       <c r="I100" s="125"/>
       <c r="J100" s="123"/>
@@ -6500,7 +6495,7 @@
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="19">
-        <f>+SALDOS!G502</f>
+        <f>+SALDOS!G501</f>
       </c>
       <c r="I101" s="125"/>
       <c r="J101" s="123"/>
@@ -6521,7 +6516,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="19">
-        <f>+SALDOS!G503</f>
+        <f>+SALDOS!G502</f>
       </c>
       <c r="I102" s="125"/>
       <c r="J102" s="123"/>
@@ -7525,7 +7520,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1921"/>
+  <dimension ref="A1:O1920"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11.44140625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="76" customWidth="1"/>
@@ -11039,11 +11034,11 @@
       <c r="H201" s="72"/>
       <c r="I201" s="164"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" s="137"/>
       <c r="B202" s="137"/>
       <c r="C202" s="139"/>
-      <c r="D202" s="139" t="s">
+      <c r="D202" s="71" t="s">
         <v>525</v>
       </c>
       <c r="E202" s="188"/>
@@ -11052,74 +11047,74 @@
         <f>+F202</f>
       </c>
       <c r="H202" s="132"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I202" s="134"/>
+      <c r="J202" s="72"/>
+      <c r="K202" s="72"/>
+      <c r="L202" s="72"/>
+      <c r="M202" s="72"/>
+      <c r="N202" s="72"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="137"/>
       <c r="B203" s="137"/>
       <c r="C203" s="139"/>
       <c r="D203" s="71" t="s">
         <v>526</v>
       </c>
-      <c r="E203" s="188"/>
-      <c r="F203" s="140"/>
-      <c r="G203" s="138">
+      <c r="E203" s="72" t="s">
+        <v>527</v>
+      </c>
+      <c r="F203" s="140">
+        <f>IFERROR(VLOOKUP(E203,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>3502753.58</v>
+      </c>
+      <c r="G203" s="187">
         <f>+F203</f>
-      </c>
-      <c r="H203" s="132"/>
-      <c r="I203" s="134"/>
-      <c r="J203" s="72"/>
-      <c r="K203" s="72"/>
-      <c r="L203" s="72"/>
-      <c r="M203" s="72"/>
-      <c r="N203" s="72"/>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3502753.58</v>
+      </c>
+      <c r="H203" s="72"/>
+      <c r="I203" s="164"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="137"/>
       <c r="B204" s="137"/>
       <c r="C204" s="139"/>
-      <c r="D204" s="71" t="s">
-        <v>527</v>
-      </c>
-      <c r="E204" s="72" t="s">
-        <v>528</v>
+      <c r="D204" s="71"/>
+      <c r="E204" s="71" t="s">
+        <v>526</v>
       </c>
       <c r="F204" s="140">
         <f>IFERROR(VLOOKUP(E204,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>3502753.58</v>
-      </c>
-      <c r="G204" s="187">
-        <f>+F204</f>
-        <v>3502753.58</v>
-      </c>
-      <c r="H204" s="72"/>
-      <c r="I204" s="164"/>
+      </c>
+      <c r="G204" s="138"/>
+      <c r="H204" s="132"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="137"/>
       <c r="B205" s="137"/>
       <c r="C205" s="139"/>
-      <c r="D205" s="71"/>
-      <c r="E205" s="71" t="s">
-        <v>527</v>
-      </c>
-      <c r="F205" s="140">
-        <f>IFERROR(VLOOKUP(E205,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G205" s="138"/>
+      <c r="D205" s="71" t="s">
+        <v>528</v>
+      </c>
+      <c r="E205" s="188"/>
+      <c r="F205" s="140"/>
+      <c r="G205" s="138">
+        <f>+F206</f>
+      </c>
       <c r="H205" s="132"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="137"/>
       <c r="B206" s="137"/>
       <c r="C206" s="139"/>
-      <c r="D206" s="71" t="s">
+      <c r="D206" s="71"/>
+      <c r="E206" s="72" t="s">
         <v>529</v>
       </c>
-      <c r="E206" s="188"/>
-      <c r="F206" s="140"/>
-      <c r="G206" s="138">
-        <f>+F207</f>
-      </c>
+      <c r="F206" s="140">
+        <f>IFERROR(VLOOKUP(E206,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G206" s="138"/>
       <c r="H206" s="132"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -11127,7 +11122,7 @@
       <c r="B207" s="137"/>
       <c r="C207" s="139"/>
       <c r="D207" s="71"/>
-      <c r="E207" s="72" t="s">
+      <c r="E207" s="188" t="s">
         <v>530</v>
       </c>
       <c r="F207" s="140">
@@ -11140,32 +11135,32 @@
       <c r="A208" s="137"/>
       <c r="B208" s="137"/>
       <c r="C208" s="139"/>
-      <c r="D208" s="71"/>
-      <c r="E208" s="188" t="s">
+      <c r="D208" s="71" t="s">
         <v>531</v>
       </c>
-      <c r="F208" s="140">
-        <f>IFERROR(VLOOKUP(E208,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G208" s="138"/>
+      <c r="E208" s="188"/>
+      <c r="F208" s="140"/>
+      <c r="G208" s="138">
+        <f>SUM(F209:F212)</f>
+        <v>700000</v>
+      </c>
       <c r="H208" s="132"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="137"/>
       <c r="B209" s="137"/>
       <c r="C209" s="139"/>
-      <c r="D209" s="71" t="s">
+      <c r="D209" s="71"/>
+      <c r="E209" s="72" t="s">
         <v>532</v>
       </c>
-      <c r="E209" s="188"/>
-      <c r="F209" s="140"/>
-      <c r="G209" s="138">
-        <f>SUM(F210:F213)</f>
-        <v>700000</v>
-      </c>
+      <c r="F209" s="140">
+        <f>IFERROR(VLOOKUP(E209,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G209" s="138"/>
       <c r="H209" s="132"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="137"/>
       <c r="B210" s="137"/>
       <c r="C210" s="139"/>
@@ -11175,9 +11170,11 @@
       </c>
       <c r="F210" s="140">
         <f>IFERROR(VLOOKUP(E210,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>700000</v>
       </c>
       <c r="G210" s="138"/>
-      <c r="H210" s="132"/>
+      <c r="H210" s="72"/>
+      <c r="I210" s="164"/>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="137"/>
@@ -11189,7 +11186,6 @@
       </c>
       <c r="F211" s="140">
         <f>IFERROR(VLOOKUP(E211,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>700000</v>
       </c>
       <c r="G211" s="138"/>
       <c r="H211" s="72"/>
@@ -11210,34 +11206,34 @@
       <c r="H212" s="72"/>
       <c r="I212" s="164"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="137"/>
       <c r="B213" s="137"/>
       <c r="C213" s="139"/>
-      <c r="D213" s="71"/>
-      <c r="E213" s="72" t="s">
+      <c r="D213" s="71" t="s">
         <v>536</v>
       </c>
-      <c r="F213" s="140">
-        <f>IFERROR(VLOOKUP(E213,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G213" s="138"/>
-      <c r="H213" s="72"/>
-      <c r="I213" s="164"/>
+      <c r="E213" s="188"/>
+      <c r="F213" s="140"/>
+      <c r="G213" s="187">
+        <f>SUM(F213:F216)</f>
+        <v>288818.78</v>
+      </c>
+      <c r="H213" s="150"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="137"/>
       <c r="B214" s="137"/>
       <c r="C214" s="139"/>
-      <c r="D214" s="71" t="s">
+      <c r="D214" s="71"/>
+      <c r="E214" s="72" t="s">
         <v>537</v>
       </c>
-      <c r="E214" s="188"/>
-      <c r="F214" s="140"/>
-      <c r="G214" s="187">
-        <f>SUM(F214:F217)</f>
+      <c r="F214" s="140">
+        <f>IFERROR(VLOOKUP(E214,Hoja1!$A$86:$E$377,5,FALSE),)</f>
         <v>288818.78</v>
       </c>
+      <c r="G214" s="138"/>
       <c r="H214" s="150"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -11250,7 +11246,6 @@
       </c>
       <c r="F215" s="140">
         <f>IFERROR(VLOOKUP(E215,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>288818.78</v>
       </c>
       <c r="G215" s="138"/>
       <c r="H215" s="150"/>
@@ -11269,40 +11264,40 @@
       <c r="G216" s="138"/>
       <c r="H216" s="150"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" s="137"/>
       <c r="B217" s="137"/>
       <c r="C217" s="139"/>
-      <c r="D217" s="71"/>
-      <c r="E217" s="72" t="s">
+      <c r="D217" s="71" t="s">
         <v>540</v>
       </c>
-      <c r="F217" s="140">
-        <f>IFERROR(VLOOKUP(E217,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G217" s="138"/>
-      <c r="H217" s="150"/>
-    </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E217" s="188"/>
+      <c r="F217" s="140"/>
+      <c r="G217" s="187">
+        <f>SUM(F217:F224)</f>
+        <v>5034121.24</v>
+      </c>
+      <c r="H217" s="132"/>
+      <c r="I217" s="134"/>
+      <c r="J217" s="72"/>
+      <c r="K217" s="72"/>
+      <c r="L217" s="72"/>
+      <c r="M217" s="72"/>
+      <c r="N217" s="72"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="137"/>
       <c r="B218" s="137"/>
       <c r="C218" s="139"/>
-      <c r="D218" s="71" t="s">
+      <c r="D218" s="71"/>
+      <c r="E218" s="72" t="s">
         <v>541</v>
       </c>
-      <c r="E218" s="188"/>
-      <c r="F218" s="140"/>
-      <c r="G218" s="187">
-        <f>SUM(F218:F225)</f>
-        <v>5034121.24</v>
-      </c>
+      <c r="F218" s="140">
+        <f>IFERROR(VLOOKUP(E218,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G218" s="138"/>
       <c r="H218" s="132"/>
-      <c r="I218" s="134"/>
-      <c r="J218" s="72"/>
-      <c r="K218" s="72"/>
-      <c r="L218" s="72"/>
-      <c r="M218" s="72"/>
-      <c r="N218" s="72"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="137"/>
@@ -11314,6 +11309,7 @@
       </c>
       <c r="F219" s="140">
         <f>IFERROR(VLOOKUP(E219,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>3016013.02</v>
       </c>
       <c r="G219" s="138"/>
       <c r="H219" s="132"/>
@@ -11328,7 +11324,6 @@
       </c>
       <c r="F220" s="140">
         <f>IFERROR(VLOOKUP(E220,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>3016013.02</v>
       </c>
       <c r="G220" s="138"/>
       <c r="H220" s="132"/>
@@ -11343,6 +11338,7 @@
       </c>
       <c r="F221" s="140">
         <f>IFERROR(VLOOKUP(E221,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>1836290.04</v>
       </c>
       <c r="G221" s="138"/>
       <c r="H221" s="132"/>
@@ -11357,12 +11353,11 @@
       </c>
       <c r="F222" s="140">
         <f>IFERROR(VLOOKUP(E222,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>1836290.04</v>
       </c>
       <c r="G222" s="138"/>
       <c r="H222" s="132"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="137"/>
       <c r="B223" s="137"/>
       <c r="C223" s="139"/>
@@ -11372,9 +11367,11 @@
       </c>
       <c r="F223" s="140">
         <f>IFERROR(VLOOKUP(E223,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>181818.18</v>
       </c>
       <c r="G223" s="138"/>
-      <c r="H223" s="132"/>
+      <c r="H223" s="72"/>
+      <c r="I223" s="164"/>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="137"/>
@@ -11386,7 +11383,6 @@
       </c>
       <c r="F224" s="140">
         <f>IFERROR(VLOOKUP(E224,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>181818.18</v>
       </c>
       <c r="G224" s="138"/>
       <c r="H224" s="72"/>
@@ -11397,12 +11393,8 @@
       <c r="B225" s="137"/>
       <c r="C225" s="139"/>
       <c r="D225" s="71"/>
-      <c r="E225" s="72" t="s">
-        <v>548</v>
-      </c>
-      <c r="F225" s="140">
-        <f>IFERROR(VLOOKUP(E225,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
+      <c r="E225" s="72"/>
+      <c r="F225" s="140"/>
       <c r="G225" s="138"/>
       <c r="H225" s="72"/>
       <c r="I225" s="164"/>
@@ -11411,33 +11403,40 @@
       <c r="A226" s="137"/>
       <c r="B226" s="137"/>
       <c r="C226" s="139"/>
-      <c r="D226" s="71"/>
-      <c r="E226" s="72"/>
-      <c r="F226" s="140"/>
-      <c r="G226" s="138"/>
+      <c r="D226" s="71" t="s">
+        <v>548</v>
+      </c>
+      <c r="E226" s="72" t="s">
+        <v>549</v>
+      </c>
+      <c r="F226" s="140">
+        <f>IFERROR(VLOOKUP(E226,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>2052084.4000000001</v>
+      </c>
+      <c r="G226" s="187">
+        <f>SUM(F226:F228)</f>
+        <v>2052084.4000000001</v>
+      </c>
       <c r="H226" s="72"/>
       <c r="I226" s="164"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A227" s="137"/>
       <c r="B227" s="137"/>
       <c r="C227" s="139"/>
-      <c r="D227" s="71" t="s">
-        <v>549</v>
-      </c>
+      <c r="D227" s="71"/>
       <c r="E227" s="72" t="s">
         <v>550</v>
       </c>
       <c r="F227" s="140">
         <f>IFERROR(VLOOKUP(E227,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>2052084.4000000001</v>
-      </c>
-      <c r="G227" s="187">
-        <f>SUM(F227:F229)</f>
-        <v>2052084.4000000001</v>
-      </c>
+      </c>
+      <c r="G227" s="138"/>
       <c r="H227" s="72"/>
       <c r="I227" s="164"/>
+      <c r="J227" s="72"/>
+      <c r="K227" s="72"/>
+      <c r="L227" s="72"/>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A228" s="137"/>
@@ -11462,12 +11461,8 @@
       <c r="B229" s="137"/>
       <c r="C229" s="139"/>
       <c r="D229" s="71"/>
-      <c r="E229" s="72" t="s">
-        <v>552</v>
-      </c>
-      <c r="F229" s="140">
-        <f>IFERROR(VLOOKUP(E229,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
+      <c r="E229" s="72"/>
+      <c r="F229" s="140"/>
       <c r="G229" s="138"/>
       <c r="H229" s="72"/>
       <c r="I229" s="164"/>
@@ -11475,52 +11470,52 @@
       <c r="K229" s="72"/>
       <c r="L229" s="72"/>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="137"/>
       <c r="B230" s="137"/>
       <c r="C230" s="139"/>
-      <c r="D230" s="71"/>
-      <c r="E230" s="72"/>
-      <c r="F230" s="140"/>
-      <c r="G230" s="138"/>
-      <c r="H230" s="72"/>
-      <c r="I230" s="164"/>
-      <c r="J230" s="72"/>
-      <c r="K230" s="72"/>
-      <c r="L230" s="72"/>
+      <c r="D230" s="71" t="s">
+        <v>552</v>
+      </c>
+      <c r="E230" s="72" t="s">
+        <v>553</v>
+      </c>
+      <c r="F230" s="140">
+        <f>IFERROR(VLOOKUP(E230,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>39000</v>
+      </c>
+      <c r="G230" s="138">
+        <f>SUM(F230:F231)</f>
+        <v>39000</v>
+      </c>
+      <c r="H230" s="132"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="137"/>
       <c r="B231" s="137"/>
       <c r="C231" s="139"/>
-      <c r="D231" s="71" t="s">
-        <v>553</v>
-      </c>
+      <c r="D231" s="71"/>
       <c r="E231" s="72" t="s">
         <v>554</v>
       </c>
       <c r="F231" s="140">
         <f>IFERROR(VLOOKUP(E231,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>39000</v>
-      </c>
-      <c r="G231" s="138">
-        <f>SUM(F231:F232)</f>
-        <v>39000</v>
-      </c>
+      </c>
+      <c r="G231" s="138"/>
       <c r="H231" s="132"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="137"/>
       <c r="B232" s="137"/>
       <c r="C232" s="139"/>
-      <c r="D232" s="71"/>
-      <c r="E232" s="72" t="s">
+      <c r="D232" s="71" t="s">
         <v>555</v>
       </c>
-      <c r="F232" s="140">
-        <f>IFERROR(VLOOKUP(E232,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G232" s="138"/>
+      <c r="E232" s="71"/>
+      <c r="F232" s="140"/>
+      <c r="G232" s="138">
+        <f>+F232</f>
+      </c>
       <c r="H232" s="132"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
@@ -11537,40 +11532,41 @@
       </c>
       <c r="H233" s="132"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="137"/>
       <c r="B234" s="137"/>
       <c r="C234" s="139"/>
       <c r="D234" s="71" t="s">
         <v>557</v>
       </c>
-      <c r="E234" s="71"/>
-      <c r="F234" s="140"/>
+      <c r="E234" s="72" t="s">
+        <v>558</v>
+      </c>
+      <c r="F234" s="140">
+        <f>IFERROR(VLOOKUP(E234,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
       <c r="G234" s="138">
-        <f>+F234</f>
-      </c>
-      <c r="H234" s="132"/>
+        <f>+SUM(F234:F237)</f>
+      </c>
+      <c r="H234" s="72"/>
+      <c r="I234" s="164"/>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="137"/>
       <c r="B235" s="137"/>
       <c r="C235" s="139"/>
-      <c r="D235" s="71" t="s">
-        <v>558</v>
-      </c>
+      <c r="D235" s="71"/>
       <c r="E235" s="72" t="s">
         <v>559</v>
       </c>
       <c r="F235" s="140">
         <f>IFERROR(VLOOKUP(E235,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G235" s="138">
-        <f>+SUM(F235:F238)</f>
-      </c>
+      <c r="G235" s="138"/>
       <c r="H235" s="72"/>
       <c r="I235" s="164"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="137"/>
       <c r="B236" s="137"/>
       <c r="C236" s="139"/>
@@ -11585,33 +11581,32 @@
       <c r="H236" s="72"/>
       <c r="I236" s="164"/>
     </row>
-    <row r="237" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="137"/>
       <c r="B237" s="137"/>
       <c r="C237" s="139"/>
       <c r="D237" s="71"/>
-      <c r="E237" s="72" t="s">
-        <v>561</v>
-      </c>
+      <c r="E237" s="72"/>
       <c r="F237" s="140">
-        <f>IFERROR(VLOOKUP(E237,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E237,Hoja1!$A$86:$E$353,5,FALSE),)</f>
       </c>
       <c r="G237" s="138"/>
       <c r="H237" s="72"/>
       <c r="I237" s="164"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="137"/>
       <c r="B238" s="137"/>
       <c r="C238" s="139"/>
-      <c r="D238" s="71"/>
-      <c r="E238" s="72"/>
-      <c r="F238" s="140">
-        <f>IFERROR(VLOOKUP(E238,Hoja1!$A$86:$E$353,5,FALSE),)</f>
-      </c>
-      <c r="G238" s="138"/>
-      <c r="H238" s="72"/>
-      <c r="I238" s="164"/>
+      <c r="D238" s="71" t="s">
+        <v>561</v>
+      </c>
+      <c r="E238" s="71"/>
+      <c r="F238" s="140"/>
+      <c r="G238" s="138">
+        <f>+F238</f>
+      </c>
+      <c r="H238" s="132"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="137"/>
@@ -11620,10 +11615,14 @@
       <c r="D239" s="71" t="s">
         <v>562</v>
       </c>
-      <c r="E239" s="71"/>
-      <c r="F239" s="140"/>
+      <c r="E239" s="71" t="s">
+        <v>563</v>
+      </c>
+      <c r="F239" s="140">
+        <f>IFERROR(VLOOKUP(E239,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
       <c r="G239" s="138">
-        <f>+F239</f>
+        <f>SUM(F239:F242)</f>
       </c>
       <c r="H239" s="132"/>
     </row>
@@ -11631,18 +11630,14 @@
       <c r="A240" s="137"/>
       <c r="B240" s="137"/>
       <c r="C240" s="139"/>
-      <c r="D240" s="71" t="s">
-        <v>563</v>
-      </c>
-      <c r="E240" s="71" t="s">
+      <c r="D240" s="71"/>
+      <c r="E240" s="72" t="s">
         <v>564</v>
       </c>
       <c r="F240" s="140">
         <f>IFERROR(VLOOKUP(E240,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G240" s="138">
-        <f>SUM(F240:F243)</f>
-      </c>
+      <c r="G240" s="138"/>
       <c r="H240" s="132"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
@@ -11650,7 +11645,7 @@
       <c r="B241" s="137"/>
       <c r="C241" s="139"/>
       <c r="D241" s="71"/>
-      <c r="E241" s="72" t="s">
+      <c r="E241" s="151" t="s">
         <v>565</v>
       </c>
       <c r="F241" s="140">
@@ -11673,55 +11668,55 @@
       <c r="G242" s="138"/>
       <c r="H242" s="132"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="137"/>
       <c r="B243" s="137"/>
       <c r="C243" s="139"/>
-      <c r="D243" s="71"/>
-      <c r="E243" s="151" t="s">
+      <c r="D243" s="71" t="s">
         <v>567</v>
+      </c>
+      <c r="E243" s="72" t="s">
+        <v>568</v>
       </c>
       <c r="F243" s="140">
         <f>IFERROR(VLOOKUP(E243,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G243" s="138"/>
-      <c r="H243" s="132"/>
+        <v>101825.6</v>
+      </c>
+      <c r="G243" s="187">
+        <f>+F243+F244</f>
+        <v>101825.6</v>
+      </c>
+      <c r="H243" s="72"/>
+      <c r="I243" s="164"/>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="137"/>
       <c r="B244" s="137"/>
       <c r="C244" s="139"/>
-      <c r="D244" s="71" t="s">
-        <v>568</v>
-      </c>
+      <c r="D244" s="71"/>
       <c r="E244" s="72" t="s">
         <v>569</v>
       </c>
       <c r="F244" s="140">
         <f>IFERROR(VLOOKUP(E244,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>101825.6</v>
-      </c>
-      <c r="G244" s="187">
-        <f>+F244+F245</f>
-        <v>101825.6</v>
-      </c>
+      </c>
+      <c r="G244" s="138"/>
       <c r="H244" s="72"/>
       <c r="I244" s="164"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="137"/>
       <c r="B245" s="137"/>
       <c r="C245" s="139"/>
-      <c r="D245" s="71"/>
-      <c r="E245" s="72" t="s">
+      <c r="D245" s="71" t="s">
         <v>570</v>
       </c>
-      <c r="F245" s="140">
-        <f>IFERROR(VLOOKUP(E245,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G245" s="138"/>
-      <c r="H245" s="72"/>
-      <c r="I245" s="164"/>
+      <c r="E245" s="71"/>
+      <c r="F245" s="140"/>
+      <c r="G245" s="138">
+        <f>+F245</f>
+      </c>
+      <c r="H245" s="132"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="137"/>
@@ -11730,10 +11725,15 @@
       <c r="D246" s="71" t="s">
         <v>571</v>
       </c>
-      <c r="E246" s="71"/>
-      <c r="F246" s="140"/>
-      <c r="G246" s="138">
-        <f>+F246</f>
+      <c r="E246" s="72" t="s">
+        <v>572</v>
+      </c>
+      <c r="F246" s="140">
+        <f>IFERROR(VLOOKUP(E246,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G246" s="187">
+        <f>SUM(F246:F255)</f>
+        <v>149263.11</v>
       </c>
       <c r="H246" s="132"/>
     </row>
@@ -11741,19 +11741,14 @@
       <c r="A247" s="137"/>
       <c r="B247" s="137"/>
       <c r="C247" s="139"/>
-      <c r="D247" s="71" t="s">
-        <v>572</v>
-      </c>
+      <c r="D247" s="71"/>
       <c r="E247" s="72" t="s">
         <v>573</v>
       </c>
       <c r="F247" s="140">
         <f>IFERROR(VLOOKUP(E247,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G247" s="187">
-        <f>SUM(F247:F256)</f>
-        <v>149263.11</v>
-      </c>
+      <c r="G247" s="138"/>
       <c r="H247" s="132"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
@@ -11766,6 +11761,7 @@
       </c>
       <c r="F248" s="140">
         <f>IFERROR(VLOOKUP(E248,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>98618.72</v>
       </c>
       <c r="G248" s="138"/>
       <c r="H248" s="132"/>
@@ -11780,7 +11776,6 @@
       </c>
       <c r="F249" s="140">
         <f>IFERROR(VLOOKUP(E249,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>98618.72</v>
       </c>
       <c r="G249" s="138"/>
       <c r="H249" s="132"/>
@@ -11795,6 +11790,7 @@
       </c>
       <c r="F250" s="140">
         <f>IFERROR(VLOOKUP(E250,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>50644.39</v>
       </c>
       <c r="G250" s="138"/>
       <c r="H250" s="132"/>
@@ -11809,7 +11805,6 @@
       </c>
       <c r="F251" s="140">
         <f>IFERROR(VLOOKUP(E251,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>50644.39</v>
       </c>
       <c r="G251" s="138"/>
       <c r="H251" s="132"/>
@@ -11828,7 +11823,7 @@
       <c r="G252" s="138"/>
       <c r="H252" s="132"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="137"/>
       <c r="B253" s="137"/>
       <c r="C253" s="139"/>
@@ -11840,7 +11835,8 @@
         <f>IFERROR(VLOOKUP(E253,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
       <c r="G253" s="138"/>
-      <c r="H253" s="132"/>
+      <c r="H253" s="72"/>
+      <c r="I253" s="164"/>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="137"/>
@@ -11872,32 +11868,31 @@
       <c r="H255" s="72"/>
       <c r="I255" s="164"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="137"/>
       <c r="B256" s="137"/>
       <c r="C256" s="139"/>
-      <c r="D256" s="71"/>
-      <c r="E256" s="72" t="s">
+      <c r="D256" s="139" t="s">
         <v>582</v>
       </c>
-      <c r="F256" s="140">
-        <f>IFERROR(VLOOKUP(E256,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G256" s="138"/>
-      <c r="H256" s="72"/>
-      <c r="I256" s="164"/>
+      <c r="E256" s="188"/>
+      <c r="F256" s="140"/>
+      <c r="G256" s="138">
+        <f>+F256</f>
+      </c>
+      <c r="H256" s="132"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="137"/>
       <c r="B257" s="137"/>
       <c r="C257" s="139"/>
-      <c r="D257" s="139" t="s">
+      <c r="D257" s="71" t="s">
         <v>583</v>
       </c>
       <c r="E257" s="188"/>
       <c r="F257" s="140"/>
       <c r="G257" s="138">
-        <f>+F257</f>
+        <f>SUM(F257:F262)</f>
       </c>
       <c r="H257" s="132"/>
     </row>
@@ -11905,14 +11900,14 @@
       <c r="A258" s="137"/>
       <c r="B258" s="137"/>
       <c r="C258" s="139"/>
-      <c r="D258" s="71" t="s">
+      <c r="D258" s="71"/>
+      <c r="E258" s="151" t="s">
         <v>584</v>
       </c>
-      <c r="E258" s="188"/>
-      <c r="F258" s="140"/>
-      <c r="G258" s="138">
-        <f>SUM(F258:F263)</f>
-      </c>
+      <c r="F258" s="140">
+        <f>IFERROR(VLOOKUP(E258,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G258" s="138"/>
       <c r="H258" s="132"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
@@ -11920,7 +11915,7 @@
       <c r="B259" s="137"/>
       <c r="C259" s="139"/>
       <c r="D259" s="71"/>
-      <c r="E259" s="151" t="s">
+      <c r="E259" s="72" t="s">
         <v>585</v>
       </c>
       <c r="F259" s="140">
@@ -11943,7 +11938,7 @@
       <c r="G260" s="138"/>
       <c r="H260" s="132"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" ht="12" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="137"/>
       <c r="B261" s="137"/>
       <c r="C261" s="139"/>
@@ -11971,54 +11966,57 @@
       <c r="G262" s="138"/>
       <c r="H262" s="132"/>
     </row>
-    <row r="263" ht="12" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" ht="12" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="137"/>
       <c r="B263" s="137"/>
       <c r="C263" s="139"/>
-      <c r="D263" s="71"/>
-      <c r="E263" s="72" t="s">
+      <c r="D263" s="71" t="s">
         <v>589</v>
       </c>
-      <c r="F263" s="140">
-        <f>IFERROR(VLOOKUP(E263,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G263" s="138"/>
-      <c r="H263" s="132"/>
-    </row>
-    <row r="264" ht="12" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E263" s="188"/>
+      <c r="F263" s="140"/>
+      <c r="G263" s="138">
+        <f>+F263</f>
+      </c>
+      <c r="H263" s="142"/>
+      <c r="I263" s="134"/>
+      <c r="J263" s="142"/>
+      <c r="K263" s="142"/>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="137"/>
       <c r="B264" s="137"/>
       <c r="C264" s="139"/>
       <c r="D264" s="71" t="s">
         <v>590</v>
       </c>
-      <c r="E264" s="188"/>
-      <c r="F264" s="140"/>
-      <c r="G264" s="138">
-        <f>+F264</f>
-      </c>
-      <c r="H264" s="142"/>
+      <c r="E264" s="72" t="s">
+        <v>591</v>
+      </c>
+      <c r="F264" s="140">
+        <f>IFERROR(VLOOKUP(E264,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G264" s="187">
+        <f>SUM(F264:F268)</f>
+        <v>9664883.07</v>
+      </c>
+      <c r="H264" s="132"/>
       <c r="I264" s="134"/>
-      <c r="J264" s="142"/>
-      <c r="K264" s="142"/>
+      <c r="J264" s="152"/>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="137"/>
       <c r="B265" s="137"/>
       <c r="C265" s="139"/>
-      <c r="D265" s="71" t="s">
-        <v>591</v>
-      </c>
+      <c r="D265" s="71"/>
       <c r="E265" s="72" t="s">
         <v>592</v>
       </c>
       <c r="F265" s="140">
         <f>IFERROR(VLOOKUP(E265,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G265" s="187">
-        <f>SUM(F265:F269)</f>
-        <v>9664883.07</v>
-      </c>
+        <v>9612863.07</v>
+      </c>
+      <c r="G265" s="138"/>
       <c r="H265" s="132"/>
       <c r="I265" s="134"/>
       <c r="J265" s="152"/>
@@ -12033,7 +12031,7 @@
       </c>
       <c r="F266" s="140">
         <f>IFERROR(VLOOKUP(E266,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>9612863.07</v>
+        <v>52020</v>
       </c>
       <c r="G266" s="138"/>
       <c r="H266" s="132"/>
@@ -12050,7 +12048,6 @@
       </c>
       <c r="F267" s="140">
         <f>IFERROR(VLOOKUP(E267,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>52020</v>
       </c>
       <c r="G267" s="138"/>
       <c r="H267" s="132"/>
@@ -12073,35 +12070,36 @@
       <c r="I268" s="134"/>
       <c r="J268" s="152"/>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A269" s="137"/>
-      <c r="B269" s="137"/>
-      <c r="C269" s="139"/>
-      <c r="D269" s="71"/>
-      <c r="E269" s="72" t="s">
+    <row r="269" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A269" s="76"/>
+      <c r="B269" s="76"/>
+      <c r="C269" s="34"/>
+      <c r="D269" s="71" t="s">
         <v>596</v>
       </c>
-      <c r="F269" s="140">
-        <f>IFERROR(VLOOKUP(E269,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G269" s="138"/>
-      <c r="H269" s="132"/>
-      <c r="I269" s="134"/>
-      <c r="J269" s="152"/>
+      <c r="E269" s="188"/>
+      <c r="F269" s="140"/>
+      <c r="G269" s="187">
+        <f>SUM(F269:F271)</f>
+        <v>22769032.28</v>
+      </c>
+      <c r="H269" s="68"/>
+      <c r="I269" s="189"/>
+      <c r="J269" s="132"/>
+      <c r="K269" s="190"/>
     </row>
     <row r="270" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="76"/>
       <c r="B270" s="76"/>
       <c r="C270" s="34"/>
-      <c r="D270" s="71" t="s">
+      <c r="D270" s="139"/>
+      <c r="E270" s="72" t="s">
         <v>597</v>
       </c>
-      <c r="E270" s="188"/>
-      <c r="F270" s="140"/>
-      <c r="G270" s="187">
-        <f>SUM(F270:F272)</f>
-        <v>22769032.28</v>
-      </c>
+      <c r="F270" s="140">
+        <f>IFERROR(VLOOKUP(E270,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G270" s="138"/>
       <c r="H270" s="68"/>
       <c r="I270" s="189"/>
       <c r="J270" s="132"/>
@@ -12117,47 +12115,44 @@
       </c>
       <c r="F271" s="140">
         <f>IFERROR(VLOOKUP(E271,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>22769032.28</v>
       </c>
       <c r="G271" s="138"/>
       <c r="H271" s="68"/>
-      <c r="I271" s="189"/>
+      <c r="I271" s="164"/>
       <c r="J271" s="132"/>
       <c r="K271" s="190"/>
     </row>
-    <row r="272" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="76"/>
       <c r="B272" s="76"/>
       <c r="C272" s="34"/>
-      <c r="D272" s="139"/>
+      <c r="D272" s="71" t="s">
+        <v>599</v>
+      </c>
       <c r="E272" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F272" s="140">
         <f>IFERROR(VLOOKUP(E272,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>22769032.28</v>
-      </c>
-      <c r="G272" s="138"/>
-      <c r="H272" s="68"/>
-      <c r="I272" s="164"/>
-      <c r="J272" s="132"/>
-      <c r="K272" s="190"/>
+      </c>
+      <c r="G272" s="138">
+        <f>SUM(F272:F279)</f>
+      </c>
+      <c r="H272" s="132"/>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" s="76"/>
       <c r="B273" s="76"/>
       <c r="C273" s="34"/>
-      <c r="D273" s="71" t="s">
-        <v>600</v>
-      </c>
+      <c r="D273" s="71"/>
       <c r="E273" s="72" t="s">
         <v>601</v>
       </c>
       <c r="F273" s="140">
         <f>IFERROR(VLOOKUP(E273,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G273" s="138">
-        <f>SUM(F273:F280)</f>
-      </c>
+      <c r="G273" s="138"/>
       <c r="H273" s="132"/>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
@@ -12193,7 +12188,7 @@
       <c r="B276" s="76"/>
       <c r="C276" s="34"/>
       <c r="D276" s="71"/>
-      <c r="E276" s="72" t="s">
+      <c r="E276" s="151" t="s">
         <v>604</v>
       </c>
       <c r="F276" s="140">
@@ -12244,44 +12239,46 @@
       <c r="G279" s="138"/>
       <c r="H279" s="132"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" ht="12.6" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="76"/>
       <c r="B280" s="76"/>
       <c r="C280" s="34"/>
-      <c r="D280" s="71"/>
-      <c r="E280" s="151" t="s">
+      <c r="D280" s="191" t="s">
         <v>608</v>
       </c>
-      <c r="F280" s="140">
-        <f>IFERROR(VLOOKUP(E280,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G280" s="138"/>
-      <c r="H280" s="132"/>
-    </row>
-    <row r="281" ht="12.6" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E280" s="192" t="s">
+        <v>608</v>
+      </c>
+      <c r="F280" s="193">
+        <f>+Hoja1!E206+Hoja1!E207</f>
+        <v>62810190.49</v>
+      </c>
+      <c r="G280" s="194">
+        <f>+F280</f>
+        <v>62810190.49</v>
+      </c>
+      <c r="H280" s="195" t="s">
+        <v>609</v>
+      </c>
+      <c r="I280" s="134"/>
+      <c r="J280" s="142"/>
+      <c r="K280" s="142"/>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="76"/>
       <c r="B281" s="76"/>
       <c r="C281" s="34"/>
-      <c r="D281" s="191" t="s">
-        <v>609</v>
-      </c>
-      <c r="E281" s="192" t="s">
-        <v>609</v>
-      </c>
-      <c r="F281" s="193">
-        <f>+Hoja1!E206+Hoja1!E207</f>
-        <v>62810190.49</v>
-      </c>
-      <c r="G281" s="194">
+      <c r="D281" s="71" t="s">
+        <v>610</v>
+      </c>
+      <c r="E281" s="71"/>
+      <c r="F281" s="140">
+        <f>IFERROR(VLOOKUP(E281,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G281" s="138">
         <f>+F281</f>
-        <v>62810190.49</v>
-      </c>
-      <c r="H281" s="195" t="s">
-        <v>610</v>
-      </c>
-      <c r="I281" s="134"/>
-      <c r="J281" s="142"/>
-      <c r="K281" s="142"/>
+      </c>
+      <c r="H281" s="132"/>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" s="76"/>
@@ -12292,7 +12289,7 @@
       </c>
       <c r="E282" s="71"/>
       <c r="F282" s="140">
-        <f>IFERROR(VLOOKUP(E282,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D282,Hoja1!$A$86:$E$353,5,FALSE),)</f>
       </c>
       <c r="G282" s="138">
         <f>+F282</f>
@@ -12303,17 +12300,17 @@
       <c r="A283" s="76"/>
       <c r="B283" s="76"/>
       <c r="C283" s="34"/>
-      <c r="D283" s="71" t="s">
+      <c r="D283" s="139" t="s">
         <v>612</v>
       </c>
-      <c r="E283" s="71"/>
+      <c r="E283" s="139"/>
       <c r="F283" s="140">
         <f>IFERROR(VLOOKUP(D283,Hoja1!$A$86:$E$353,5,FALSE),)</f>
       </c>
       <c r="G283" s="138">
         <f>+F283</f>
       </c>
-      <c r="H283" s="132"/>
+      <c r="H283" s="152"/>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" s="76"/>
@@ -12323,26 +12320,24 @@
         <v>613</v>
       </c>
       <c r="E284" s="139"/>
-      <c r="F284" s="140">
-        <f>IFERROR(VLOOKUP(D284,Hoja1!$A$86:$E$353,5,FALSE),)</f>
-      </c>
+      <c r="F284" s="140"/>
       <c r="G284" s="138">
-        <f>+F284</f>
-      </c>
-      <c r="H284" s="152"/>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+        <f>SUM(F284:F292)</f>
+      </c>
+      <c r="H284" s="132"/>
+    </row>
+    <row r="285" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" s="76"/>
       <c r="B285" s="76"/>
       <c r="C285" s="34"/>
-      <c r="D285" s="139" t="s">
+      <c r="D285" s="139"/>
+      <c r="E285" s="72" t="s">
         <v>614</v>
       </c>
-      <c r="E285" s="139"/>
-      <c r="F285" s="140"/>
-      <c r="G285" s="138">
-        <f>SUM(F285:F293)</f>
-      </c>
+      <c r="F285" s="140">
+        <f>IFERROR(VLOOKUP(E285,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G285" s="138"/>
       <c r="H285" s="132"/>
     </row>
     <row r="286" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -12364,7 +12359,7 @@
       <c r="B287" s="76"/>
       <c r="C287" s="34"/>
       <c r="D287" s="139"/>
-      <c r="E287" s="72" t="s">
+      <c r="E287" s="139" t="s">
         <v>616</v>
       </c>
       <c r="F287" s="140">
@@ -12420,7 +12415,7 @@
       <c r="B291" s="76"/>
       <c r="C291" s="34"/>
       <c r="D291" s="139"/>
-      <c r="E291" s="139" t="s">
+      <c r="E291" s="72" t="s">
         <v>620</v>
       </c>
       <c r="F291" s="140">
@@ -12429,73 +12424,74 @@
       <c r="G291" s="138"/>
       <c r="H291" s="132"/>
     </row>
-    <row r="292" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" ht="13.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" s="76"/>
       <c r="B292" s="76"/>
       <c r="C292" s="34"/>
       <c r="D292" s="139"/>
-      <c r="E292" s="72" t="s">
+      <c r="E292" s="139" t="s">
         <v>621</v>
       </c>
       <c r="F292" s="140">
         <f>IFERROR(VLOOKUP(E292,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
       <c r="G292" s="138"/>
-      <c r="H292" s="132"/>
-    </row>
-    <row r="293" ht="13.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H292" s="142"/>
+      <c r="I292" s="134"/>
+      <c r="J292" s="142"/>
+      <c r="K292" s="142"/>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="76"/>
       <c r="B293" s="76"/>
       <c r="C293" s="34"/>
-      <c r="D293" s="139"/>
-      <c r="E293" s="139" t="s">
+      <c r="D293" s="71" t="s">
         <v>622</v>
       </c>
-      <c r="F293" s="140">
-        <f>IFERROR(VLOOKUP(E293,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G293" s="138"/>
-      <c r="H293" s="142"/>
-      <c r="I293" s="134"/>
-      <c r="J293" s="142"/>
-      <c r="K293" s="142"/>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E293" s="71"/>
+      <c r="F293" s="140"/>
+      <c r="G293" s="138">
+        <f>+F293</f>
+      </c>
+      <c r="H293" s="132"/>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A294" s="76"/>
       <c r="B294" s="76"/>
       <c r="C294" s="34"/>
       <c r="D294" s="71" t="s">
         <v>623</v>
       </c>
-      <c r="E294" s="71"/>
-      <c r="F294" s="140"/>
-      <c r="G294" s="138">
-        <f>+F294</f>
-      </c>
-      <c r="H294" s="132"/>
-    </row>
-    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="E294" s="72" t="s">
+        <v>624</v>
+      </c>
+      <c r="F294" s="140">
+        <f>IFERROR(VLOOKUP(E294,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G294" s="187">
+        <f>SUM(F294:F301)</f>
+        <v>832331.1900000001</v>
+      </c>
+      <c r="H294" s="72"/>
+      <c r="I294" s="164"/>
+      <c r="J294" s="72"/>
+      <c r="K294" s="72"/>
+      <c r="L294" s="72"/>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="76"/>
       <c r="B295" s="76"/>
       <c r="C295" s="34"/>
-      <c r="D295" s="71" t="s">
-        <v>624</v>
-      </c>
+      <c r="D295" s="71"/>
       <c r="E295" s="72" t="s">
         <v>625</v>
       </c>
       <c r="F295" s="140">
         <f>IFERROR(VLOOKUP(E295,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G295" s="187">
-        <f>SUM(F295:F302)</f>
         <v>832331.1900000001</v>
       </c>
-      <c r="H295" s="72"/>
-      <c r="I295" s="164"/>
-      <c r="J295" s="72"/>
-      <c r="K295" s="72"/>
-      <c r="L295" s="72"/>
+      <c r="G295" s="138"/>
+      <c r="H295" s="132"/>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="76"/>
@@ -12507,12 +12503,11 @@
       </c>
       <c r="F296" s="140">
         <f>IFERROR(VLOOKUP(E296,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>832331.1900000001</v>
       </c>
       <c r="G296" s="138"/>
       <c r="H296" s="132"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A297" s="76"/>
       <c r="B297" s="76"/>
       <c r="C297" s="34"/>
@@ -12525,6 +12520,11 @@
       </c>
       <c r="G297" s="138"/>
       <c r="H297" s="132"/>
+      <c r="I297" s="164"/>
+      <c r="J297" s="72"/>
+      <c r="K297" s="72"/>
+      <c r="L297" s="72"/>
+      <c r="M297" s="72"/>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A298" s="76"/>
@@ -12602,38 +12602,33 @@
       <c r="L301" s="72"/>
       <c r="M301" s="72"/>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" s="76"/>
       <c r="B302" s="76"/>
       <c r="C302" s="34"/>
-      <c r="D302" s="71"/>
-      <c r="E302" s="72" t="s">
+      <c r="D302" s="71" t="s">
         <v>632</v>
       </c>
-      <c r="F302" s="140">
-        <f>IFERROR(VLOOKUP(E302,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G302" s="138"/>
+      <c r="E302" s="188"/>
+      <c r="F302" s="140"/>
+      <c r="G302" s="187">
+        <f>SUM(F302:F305)</f>
+        <v>189946.28</v>
+      </c>
       <c r="H302" s="132"/>
-      <c r="I302" s="164"/>
-      <c r="J302" s="72"/>
-      <c r="K302" s="72"/>
-      <c r="L302" s="72"/>
-      <c r="M302" s="72"/>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" s="76"/>
       <c r="B303" s="76"/>
       <c r="C303" s="34"/>
-      <c r="D303" s="71" t="s">
+      <c r="D303" s="71"/>
+      <c r="E303" s="72" t="s">
         <v>633</v>
       </c>
-      <c r="E303" s="188"/>
-      <c r="F303" s="140"/>
-      <c r="G303" s="187">
-        <f>SUM(F303:F306)</f>
-        <v>189946.28</v>
-      </c>
+      <c r="F303" s="140">
+        <f>IFERROR(VLOOKUP(E303,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G303" s="138"/>
       <c r="H303" s="132"/>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
@@ -12646,6 +12641,7 @@
       </c>
       <c r="F304" s="140">
         <f>IFERROR(VLOOKUP(E304,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>189946.28</v>
       </c>
       <c r="G304" s="138"/>
       <c r="H304" s="132"/>
@@ -12660,7 +12656,6 @@
       </c>
       <c r="F305" s="140">
         <f>IFERROR(VLOOKUP(E305,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>189946.28</v>
       </c>
       <c r="G305" s="138"/>
       <c r="H305" s="132"/>
@@ -12669,44 +12664,49 @@
       <c r="A306" s="76"/>
       <c r="B306" s="76"/>
       <c r="C306" s="34"/>
-      <c r="D306" s="71"/>
-      <c r="E306" s="72" t="s">
+      <c r="D306" s="71" t="s">
         <v>636</v>
       </c>
+      <c r="E306" s="188"/>
       <c r="F306" s="140">
         <f>IFERROR(VLOOKUP(E306,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G306" s="138"/>
+      <c r="G306" s="138">
+        <f>+F307</f>
+      </c>
       <c r="H306" s="132"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" s="76"/>
       <c r="B307" s="76"/>
       <c r="C307" s="34"/>
-      <c r="D307" s="71" t="s">
+      <c r="D307" s="71"/>
+      <c r="E307" s="72" t="s">
         <v>637</v>
       </c>
-      <c r="E307" s="188"/>
       <c r="F307" s="140">
         <f>IFERROR(VLOOKUP(E307,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G307" s="138">
-        <f>+F308</f>
-      </c>
-      <c r="H307" s="132"/>
+      <c r="G307" s="138"/>
+      <c r="H307" s="72"/>
+      <c r="I307" s="164"/>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" s="76"/>
       <c r="B308" s="76"/>
       <c r="C308" s="34"/>
-      <c r="D308" s="71"/>
+      <c r="D308" s="139" t="s">
+        <v>638</v>
+      </c>
       <c r="E308" s="72" t="s">
         <v>638</v>
       </c>
       <c r="F308" s="140">
         <f>IFERROR(VLOOKUP(E308,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G308" s="138"/>
+      <c r="G308" s="138">
+        <f>+F308</f>
+      </c>
       <c r="H308" s="72"/>
       <c r="I308" s="164"/>
     </row>
@@ -12722,49 +12722,46 @@
       </c>
       <c r="F309" s="140">
         <f>IFERROR(VLOOKUP(E309,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G309" s="138">
+        <v>48607846.6</v>
+      </c>
+      <c r="G309" s="187">
         <f>+F309</f>
+        <v>48607846.6</v>
       </c>
       <c r="H309" s="72"/>
       <c r="I309" s="164"/>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" s="76"/>
       <c r="B310" s="76"/>
       <c r="C310" s="34"/>
-      <c r="D310" s="139" t="s">
+      <c r="D310" s="71" t="s">
         <v>640</v>
       </c>
       <c r="E310" s="72" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F310" s="140">
         <f>IFERROR(VLOOKUP(E310,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>48607846.6</v>
-      </c>
-      <c r="G310" s="187">
+      </c>
+      <c r="G310" s="138">
         <f>+F310</f>
-        <v>48607846.6</v>
-      </c>
-      <c r="H310" s="72"/>
-      <c r="I310" s="164"/>
+      </c>
+      <c r="H310" s="132"/>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" s="76"/>
       <c r="B311" s="76"/>
       <c r="C311" s="34"/>
       <c r="D311" s="71" t="s">
-        <v>641</v>
-      </c>
-      <c r="E311" s="72" t="s">
         <v>642</v>
       </c>
+      <c r="E311" s="188"/>
       <c r="F311" s="140">
         <f>IFERROR(VLOOKUP(E311,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
       <c r="G311" s="138">
-        <f>+F311</f>
+        <f>SUM(F311:F313)</f>
       </c>
       <c r="H311" s="132"/>
     </row>
@@ -12772,16 +12769,14 @@
       <c r="A312" s="76"/>
       <c r="B312" s="76"/>
       <c r="C312" s="34"/>
-      <c r="D312" s="71" t="s">
+      <c r="D312" s="71"/>
+      <c r="E312" s="72" t="s">
         <v>643</v>
       </c>
-      <c r="E312" s="188"/>
       <c r="F312" s="140">
         <f>IFERROR(VLOOKUP(E312,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G312" s="138">
-        <f>SUM(F312:F314)</f>
-      </c>
+      <c r="G312" s="138"/>
       <c r="H312" s="132"/>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -12802,14 +12797,16 @@
       <c r="A314" s="76"/>
       <c r="B314" s="76"/>
       <c r="C314" s="34"/>
-      <c r="D314" s="71"/>
-      <c r="E314" s="72" t="s">
+      <c r="D314" s="71" t="s">
         <v>645</v>
       </c>
+      <c r="E314" s="71"/>
       <c r="F314" s="140">
         <f>IFERROR(VLOOKUP(E314,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G314" s="138"/>
+      <c r="G314" s="138">
+        <f>+F314</f>
+      </c>
       <c r="H314" s="132"/>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
@@ -12819,12 +12816,15 @@
       <c r="D315" s="71" t="s">
         <v>646</v>
       </c>
-      <c r="E315" s="71"/>
+      <c r="E315" s="71" t="s">
+        <v>647</v>
+      </c>
       <c r="F315" s="140">
         <f>IFERROR(VLOOKUP(E315,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G315" s="138">
-        <f>+F315</f>
+      <c r="G315" s="187">
+        <f>+F315+F316</f>
+        <v>18512.4</v>
       </c>
       <c r="H315" s="132"/>
     </row>
@@ -12832,65 +12832,61 @@
       <c r="A316" s="76"/>
       <c r="B316" s="76"/>
       <c r="C316" s="34"/>
-      <c r="D316" s="71" t="s">
-        <v>647</v>
-      </c>
-      <c r="E316" s="71" t="s">
+      <c r="D316" s="71"/>
+      <c r="E316" s="72" t="s">
         <v>648</v>
       </c>
       <c r="F316" s="140">
         <f>IFERROR(VLOOKUP(E316,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G316" s="187">
-        <f>+F316+F317</f>
         <v>18512.4</v>
       </c>
+      <c r="G316" s="138"/>
       <c r="H316" s="132"/>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" s="76"/>
       <c r="B317" s="76"/>
       <c r="C317" s="34"/>
-      <c r="D317" s="71"/>
-      <c r="E317" s="72" t="s">
+      <c r="D317" s="139" t="s">
         <v>649</v>
       </c>
+      <c r="E317" s="72"/>
       <c r="F317" s="140">
         <f>IFERROR(VLOOKUP(E317,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>18512.4</v>
-      </c>
-      <c r="G317" s="138"/>
-      <c r="H317" s="132"/>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      </c>
+      <c r="G317" s="138">
+        <f>+F317</f>
+      </c>
+      <c r="H317" s="68"/>
+    </row>
+    <row r="318" ht="12.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" s="76"/>
       <c r="B318" s="76"/>
       <c r="C318" s="34"/>
-      <c r="D318" s="139" t="s">
+      <c r="D318" s="71" t="s">
         <v>650</v>
       </c>
-      <c r="E318" s="72"/>
-      <c r="F318" s="140">
-        <f>IFERROR(VLOOKUP(E318,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G318" s="138">
-        <f>+F318</f>
+      <c r="E318" s="71"/>
+      <c r="F318" s="140"/>
+      <c r="G318" s="187">
+        <f>SUM(F318:F321)</f>
+        <v>87312447.89</v>
       </c>
       <c r="H318" s="68"/>
     </row>
-    <row r="319" ht="12.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" s="76"/>
       <c r="B319" s="76"/>
       <c r="C319" s="34"/>
-      <c r="D319" s="71" t="s">
+      <c r="D319" s="71"/>
+      <c r="E319" s="72" t="s">
         <v>651</v>
       </c>
-      <c r="E319" s="71"/>
-      <c r="F319" s="140"/>
-      <c r="G319" s="187">
-        <f>SUM(F319:F322)</f>
+      <c r="F319" s="140">
+        <f>IFERROR(VLOOKUP(E319,Hoja1!$A$86:$E$377,5,FALSE),)</f>
         <v>87312447.89</v>
       </c>
+      <c r="G319" s="143"/>
       <c r="H319" s="68"/>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
@@ -12903,12 +12899,11 @@
       </c>
       <c r="F320" s="140">
         <f>IFERROR(VLOOKUP(E320,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>87312447.89</v>
-      </c>
-      <c r="G320" s="143"/>
+      </c>
+      <c r="G320" s="138"/>
       <c r="H320" s="68"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="76"/>
       <c r="B321" s="76"/>
       <c r="C321" s="34"/>
@@ -12921,35 +12916,36 @@
       </c>
       <c r="G321" s="138"/>
       <c r="H321" s="68"/>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I321" s="159"/>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" s="76"/>
       <c r="B322" s="76"/>
       <c r="C322" s="34"/>
-      <c r="D322" s="71"/>
-      <c r="E322" s="72" t="s">
+      <c r="D322" s="71" t="s">
         <v>654</v>
       </c>
-      <c r="F322" s="140">
-        <f>IFERROR(VLOOKUP(E322,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G322" s="138"/>
-      <c r="H322" s="68"/>
-      <c r="I322" s="159"/>
+      <c r="E322" s="188"/>
+      <c r="F322" s="140"/>
+      <c r="G322" s="187">
+        <f>SUM(F322:F329)</f>
+        <v>51970355.11</v>
+      </c>
+      <c r="H322" s="132"/>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" s="76"/>
       <c r="B323" s="76"/>
       <c r="C323" s="34"/>
-      <c r="D323" s="71" t="s">
+      <c r="D323" s="71"/>
+      <c r="E323" s="72" t="s">
         <v>655</v>
       </c>
-      <c r="E323" s="188"/>
-      <c r="F323" s="140"/>
-      <c r="G323" s="187">
-        <f>SUM(F323:F330)</f>
-        <v>51970355.11</v>
-      </c>
+      <c r="F323" s="140">
+        <f>IFERROR(VLOOKUP(E323,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>157000</v>
+      </c>
+      <c r="G323" s="138"/>
       <c r="H323" s="132"/>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
@@ -12962,7 +12958,6 @@
       </c>
       <c r="F324" s="140">
         <f>IFERROR(VLOOKUP(E324,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>157000</v>
       </c>
       <c r="G324" s="138"/>
       <c r="H324" s="132"/>
@@ -12977,6 +12972,7 @@
       </c>
       <c r="F325" s="140">
         <f>IFERROR(VLOOKUP(E325,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>51813355.11</v>
       </c>
       <c r="G325" s="138"/>
       <c r="H325" s="132"/>
@@ -12991,7 +12987,6 @@
       </c>
       <c r="F326" s="140">
         <f>IFERROR(VLOOKUP(E326,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>51813355.11</v>
       </c>
       <c r="G326" s="138"/>
       <c r="H326" s="132"/>
@@ -13042,51 +13037,52 @@
       <c r="A330" s="76"/>
       <c r="B330" s="76"/>
       <c r="C330" s="34"/>
-      <c r="D330" s="71"/>
+      <c r="D330" s="71" t="s">
+        <v>662</v>
+      </c>
       <c r="E330" s="72" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F330" s="140">
         <f>IFERROR(VLOOKUP(E330,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G330" s="138"/>
-      <c r="H330" s="132"/>
+      <c r="G330" s="187">
+        <f>SUM(F330:F337)</f>
+        <v>27411009.17</v>
+      </c>
+      <c r="H330" s="150"/>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="76"/>
       <c r="B331" s="76"/>
       <c r="C331" s="34"/>
-      <c r="D331" s="71" t="s">
-        <v>663</v>
-      </c>
-      <c r="E331" s="72" t="s">
+      <c r="D331" s="71"/>
+      <c r="E331" s="151" t="s">
         <v>664</v>
       </c>
       <c r="F331" s="140">
         <f>IFERROR(VLOOKUP(E331,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G331" s="187">
-        <f>SUM(F331:F338)</f>
-        <v>27411009.17</v>
-      </c>
-      <c r="H331" s="150"/>
+        <v>21735.54</v>
+      </c>
+      <c r="G331" s="138"/>
+      <c r="H331" s="150" t="s">
+        <v>665</v>
+      </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="76"/>
       <c r="B332" s="76"/>
       <c r="C332" s="34"/>
       <c r="D332" s="71"/>
-      <c r="E332" s="151" t="s">
-        <v>665</v>
+      <c r="E332" s="72" t="s">
+        <v>666</v>
       </c>
       <c r="F332" s="140">
         <f>IFERROR(VLOOKUP(E332,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>21735.54</v>
+        <v>4006957.04</v>
       </c>
       <c r="G332" s="138"/>
-      <c r="H332" s="150" t="s">
-        <v>666</v>
-      </c>
+      <c r="H332" s="150"/>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="76"/>
@@ -13098,7 +13094,7 @@
       </c>
       <c r="F333" s="140">
         <f>IFERROR(VLOOKUP(E333,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>4006957.04</v>
+        <v>23352516.59</v>
       </c>
       <c r="G333" s="138"/>
       <c r="H333" s="150"/>
@@ -13113,10 +13109,10 @@
       </c>
       <c r="F334" s="140">
         <f>IFERROR(VLOOKUP(E334,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>23352516.59</v>
+        <v>29800</v>
       </c>
       <c r="G334" s="138"/>
-      <c r="H334" s="150"/>
+      <c r="H334" s="68"/>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" s="76"/>
@@ -13128,7 +13124,6 @@
       </c>
       <c r="F335" s="140">
         <f>IFERROR(VLOOKUP(E335,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>29800</v>
       </c>
       <c r="G335" s="138"/>
       <c r="H335" s="68"/>
@@ -13165,15 +13160,15 @@
       <c r="A338" s="76"/>
       <c r="B338" s="76"/>
       <c r="C338" s="34"/>
-      <c r="D338" s="71"/>
-      <c r="E338" s="72" t="s">
+      <c r="D338" s="71" t="s">
         <v>672</v>
       </c>
-      <c r="F338" s="140">
-        <f>IFERROR(VLOOKUP(E338,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G338" s="138"/>
-      <c r="H338" s="68"/>
+      <c r="E338" s="71"/>
+      <c r="F338" s="140"/>
+      <c r="G338" s="138">
+        <f>+F338</f>
+      </c>
+      <c r="H338" s="132"/>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" s="76"/>
@@ -13182,10 +13177,14 @@
       <c r="D339" s="71" t="s">
         <v>673</v>
       </c>
-      <c r="E339" s="71"/>
-      <c r="F339" s="140"/>
+      <c r="E339" s="72" t="s">
+        <v>674</v>
+      </c>
+      <c r="F339" s="140">
+        <f>IFERROR(VLOOKUP(E339,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
       <c r="G339" s="138">
-        <f>+F339</f>
+        <f>+F339+F340+F341</f>
       </c>
       <c r="H339" s="132"/>
     </row>
@@ -13193,18 +13192,14 @@
       <c r="A340" s="76"/>
       <c r="B340" s="76"/>
       <c r="C340" s="34"/>
-      <c r="D340" s="71" t="s">
-        <v>674</v>
-      </c>
-      <c r="E340" s="72" t="s">
+      <c r="D340" s="71"/>
+      <c r="E340" s="71" t="s">
         <v>675</v>
       </c>
       <c r="F340" s="140">
         <f>IFERROR(VLOOKUP(E340,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G340" s="138">
-        <f>+F340+F341+F342</f>
-      </c>
+      <c r="G340" s="138"/>
       <c r="H340" s="132"/>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.25">
@@ -13225,34 +13220,41 @@
       <c r="A342" s="76"/>
       <c r="B342" s="76"/>
       <c r="C342" s="34"/>
-      <c r="D342" s="71"/>
-      <c r="E342" s="71" t="s">
+      <c r="D342" s="71" t="s">
         <v>677</v>
+      </c>
+      <c r="E342" s="72" t="s">
+        <v>678</v>
       </c>
       <c r="F342" s="140">
         <f>IFERROR(VLOOKUP(E342,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G342" s="138"/>
+      <c r="G342" s="187">
+        <f>SUM(F342:F350)</f>
+        <v>7596589.620000001</v>
+      </c>
       <c r="H342" s="132"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A343" s="76"/>
       <c r="B343" s="76"/>
       <c r="C343" s="34"/>
-      <c r="D343" s="71" t="s">
-        <v>678</v>
-      </c>
+      <c r="D343" s="71"/>
       <c r="E343" s="72" t="s">
         <v>679</v>
       </c>
       <c r="F343" s="140">
         <f>IFERROR(VLOOKUP(E343,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G343" s="187">
-        <f>SUM(F343:F351)</f>
-        <v>7596589.620000001</v>
-      </c>
+        <v>653893.77</v>
+      </c>
+      <c r="G343" s="138"/>
       <c r="H343" s="132"/>
+      <c r="I343" s="134"/>
+      <c r="J343" s="72"/>
+      <c r="K343" s="72"/>
+      <c r="L343" s="72"/>
+      <c r="M343" s="72"/>
+      <c r="N343" s="72"/>
     </row>
     <row r="344" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A344" s="76"/>
@@ -13264,7 +13266,6 @@
       </c>
       <c r="F344" s="140">
         <f>IFERROR(VLOOKUP(E344,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>653893.77</v>
       </c>
       <c r="G344" s="138"/>
       <c r="H344" s="132"/>
@@ -13275,7 +13276,7 @@
       <c r="M344" s="72"/>
       <c r="N344" s="72"/>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="76"/>
       <c r="B345" s="76"/>
       <c r="C345" s="34"/>
@@ -13285,15 +13286,10 @@
       </c>
       <c r="F345" s="140">
         <f>IFERROR(VLOOKUP(E345,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>5565333.850000001</v>
       </c>
       <c r="G345" s="138"/>
       <c r="H345" s="132"/>
-      <c r="I345" s="134"/>
-      <c r="J345" s="72"/>
-      <c r="K345" s="72"/>
-      <c r="L345" s="72"/>
-      <c r="M345" s="72"/>
-      <c r="N345" s="72"/>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="76"/>
@@ -13305,7 +13301,6 @@
       </c>
       <c r="F346" s="140">
         <f>IFERROR(VLOOKUP(E346,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>5565333.850000001</v>
       </c>
       <c r="G346" s="138"/>
       <c r="H346" s="132"/>
@@ -13357,55 +13352,56 @@
       <c r="B350" s="76"/>
       <c r="C350" s="34"/>
       <c r="D350" s="71"/>
-      <c r="E350" s="72" t="s">
+      <c r="E350" s="151" t="s">
         <v>686</v>
       </c>
       <c r="F350" s="140">
         <f>IFERROR(VLOOKUP(E350,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>1377362</v>
       </c>
       <c r="G350" s="138"/>
-      <c r="H350" s="132"/>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H350" s="68" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A351" s="76"/>
       <c r="B351" s="76"/>
       <c r="C351" s="34"/>
-      <c r="D351" s="71"/>
-      <c r="E351" s="151" t="s">
+      <c r="D351" s="71" t="s">
         <v>687</v>
+      </c>
+      <c r="E351" s="72" t="s">
+        <v>688</v>
       </c>
       <c r="F351" s="140">
         <f>IFERROR(VLOOKUP(E351,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>1377362</v>
-      </c>
-      <c r="G351" s="138"/>
-      <c r="H351" s="68" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+      </c>
+      <c r="G351" s="187">
+        <f>SUM(F351:F357)</f>
+        <v>8616654.57</v>
+      </c>
+      <c r="H351" s="68"/>
+      <c r="I351" s="164"/>
+      <c r="J351" s="72"/>
+      <c r="K351" s="72"/>
+      <c r="L351" s="72"/>
+      <c r="M351" s="72"/>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" s="76"/>
       <c r="B352" s="76"/>
       <c r="C352" s="34"/>
-      <c r="D352" s="71" t="s">
-        <v>688</v>
-      </c>
+      <c r="D352" s="71"/>
       <c r="E352" s="72" t="s">
         <v>689</v>
       </c>
       <c r="F352" s="140">
         <f>IFERROR(VLOOKUP(E352,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G352" s="187">
-        <f>SUM(F352:F358)</f>
-        <v>8616654.57</v>
-      </c>
+        <v>783143.51</v>
+      </c>
+      <c r="G352" s="138"/>
       <c r="H352" s="68"/>
-      <c r="I352" s="164"/>
-      <c r="J352" s="72"/>
-      <c r="K352" s="72"/>
-      <c r="L352" s="72"/>
-      <c r="M352" s="72"/>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" s="76"/>
@@ -13417,7 +13413,7 @@
       </c>
       <c r="F353" s="140">
         <f>IFERROR(VLOOKUP(E353,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>783143.51</v>
+        <v>7828411.890000001</v>
       </c>
       <c r="G353" s="138"/>
       <c r="H353" s="68"/>
@@ -13432,7 +13428,6 @@
       </c>
       <c r="F354" s="140">
         <f>IFERROR(VLOOKUP(E354,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>7828411.890000001</v>
       </c>
       <c r="G354" s="138"/>
       <c r="H354" s="68"/>
@@ -13447,6 +13442,7 @@
       </c>
       <c r="F355" s="140">
         <f>IFERROR(VLOOKUP(E355,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>5099.17</v>
       </c>
       <c r="G355" s="138"/>
       <c r="H355" s="68"/>
@@ -13461,7 +13457,6 @@
       </c>
       <c r="F356" s="140">
         <f>IFERROR(VLOOKUP(E356,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>5099.17</v>
       </c>
       <c r="G356" s="138"/>
       <c r="H356" s="68"/>
@@ -13484,28 +13479,28 @@
       <c r="A358" s="76"/>
       <c r="B358" s="76"/>
       <c r="C358" s="34"/>
-      <c r="D358" s="71"/>
-      <c r="E358" s="72" t="s">
+      <c r="D358" s="139" t="s">
         <v>695</v>
       </c>
-      <c r="F358" s="140">
-        <f>IFERROR(VLOOKUP(E358,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G358" s="138"/>
+      <c r="E358" s="72"/>
+      <c r="F358" s="140"/>
+      <c r="G358" s="138">
+        <f>+F358+F359+F360</f>
+      </c>
       <c r="H358" s="68"/>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" s="76"/>
       <c r="B359" s="76"/>
       <c r="C359" s="34"/>
-      <c r="D359" s="139" t="s">
+      <c r="D359" s="132"/>
+      <c r="E359" s="72" t="s">
         <v>696</v>
       </c>
-      <c r="E359" s="72"/>
-      <c r="F359" s="140"/>
-      <c r="G359" s="138">
-        <f>+F359+F360+F361</f>
-      </c>
+      <c r="F359" s="140">
+        <f>IFERROR(VLOOKUP(E359,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G359" s="138"/>
       <c r="H359" s="68"/>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.25">
@@ -13526,56 +13521,56 @@
       <c r="A361" s="76"/>
       <c r="B361" s="76"/>
       <c r="C361" s="34"/>
-      <c r="D361" s="132"/>
-      <c r="E361" s="72" t="s">
+      <c r="D361" s="139" t="s">
         <v>698</v>
       </c>
-      <c r="F361" s="140">
-        <f>IFERROR(VLOOKUP(E361,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G361" s="138"/>
+      <c r="E361" s="72"/>
+      <c r="F361" s="140"/>
+      <c r="G361" s="138">
+        <f>+F361+F362</f>
+      </c>
       <c r="H361" s="68"/>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" s="76"/>
       <c r="B362" s="76"/>
       <c r="C362" s="34"/>
-      <c r="D362" s="139" t="s">
-        <v>699</v>
-      </c>
-      <c r="E362" s="72"/>
-      <c r="F362" s="140"/>
-      <c r="G362" s="138">
-        <f>+F362+F363</f>
-      </c>
+      <c r="D362" s="139"/>
+      <c r="E362" s="72" t="s">
+        <v>698</v>
+      </c>
+      <c r="F362" s="140">
+        <f>IFERROR(VLOOKUP(E362,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G362" s="138"/>
       <c r="H362" s="68"/>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" s="76"/>
       <c r="B363" s="76"/>
       <c r="C363" s="34"/>
-      <c r="D363" s="139"/>
-      <c r="E363" s="72" t="s">
+      <c r="D363" s="71" t="s">
         <v>699</v>
       </c>
-      <c r="F363" s="140">
-        <f>IFERROR(VLOOKUP(E363,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G363" s="138"/>
-      <c r="H363" s="68"/>
+      <c r="E363" s="71"/>
+      <c r="F363" s="140"/>
+      <c r="G363" s="138">
+        <f>SUM(F363:F366)</f>
+      </c>
+      <c r="H363" s="132"/>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" s="76"/>
       <c r="B364" s="76"/>
       <c r="C364" s="34"/>
-      <c r="D364" s="71" t="s">
+      <c r="D364" s="71"/>
+      <c r="E364" s="72" t="s">
         <v>700</v>
       </c>
-      <c r="E364" s="71"/>
-      <c r="F364" s="140"/>
-      <c r="G364" s="138">
-        <f>SUM(F364:F367)</f>
-      </c>
+      <c r="F364" s="140">
+        <f>IFERROR(VLOOKUP(E364,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G364" s="138"/>
       <c r="H364" s="132"/>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
@@ -13610,14 +13605,14 @@
       <c r="A367" s="76"/>
       <c r="B367" s="76"/>
       <c r="C367" s="34"/>
-      <c r="D367" s="71"/>
-      <c r="E367" s="72" t="s">
+      <c r="D367" s="71" t="s">
         <v>703</v>
       </c>
-      <c r="F367" s="140">
-        <f>IFERROR(VLOOKUP(E367,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G367" s="138"/>
+      <c r="E367" s="188"/>
+      <c r="F367" s="140"/>
+      <c r="G367" s="138">
+        <f>+F367</f>
+      </c>
       <c r="H367" s="132"/>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.25">
@@ -13629,8 +13624,9 @@
       </c>
       <c r="E368" s="188"/>
       <c r="F368" s="140"/>
-      <c r="G368" s="138">
-        <f>+F368</f>
+      <c r="G368" s="187">
+        <f>SUM(F368:F373)</f>
+        <v>262653256.83999997</v>
       </c>
       <c r="H368" s="132"/>
     </row>
@@ -13638,15 +13634,14 @@
       <c r="A369" s="76"/>
       <c r="B369" s="76"/>
       <c r="C369" s="34"/>
-      <c r="D369" s="71" t="s">
+      <c r="D369" s="71"/>
+      <c r="E369" s="72" t="s">
         <v>705</v>
       </c>
-      <c r="E369" s="188"/>
-      <c r="F369" s="140"/>
-      <c r="G369" s="187">
-        <f>SUM(F369:F374)</f>
-        <v>262653256.83999997</v>
-      </c>
+      <c r="F369" s="140">
+        <f>IFERROR(VLOOKUP(E369,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G369" s="138"/>
       <c r="H369" s="132"/>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.25">
@@ -13659,6 +13654,7 @@
       </c>
       <c r="F370" s="140">
         <f>IFERROR(VLOOKUP(E370,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>216447896.76</v>
       </c>
       <c r="G370" s="138"/>
       <c r="H370" s="132"/>
@@ -13673,7 +13669,7 @@
       </c>
       <c r="F371" s="140">
         <f>IFERROR(VLOOKUP(E371,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>216447896.76</v>
+        <v>45688831.08</v>
       </c>
       <c r="G371" s="138"/>
       <c r="H371" s="132"/>
@@ -13688,7 +13684,7 @@
       </c>
       <c r="F372" s="140">
         <f>IFERROR(VLOOKUP(E372,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>45688831.08</v>
+        <v>516529</v>
       </c>
       <c r="G372" s="138"/>
       <c r="H372" s="132"/>
@@ -13703,7 +13699,6 @@
       </c>
       <c r="F373" s="140">
         <f>IFERROR(VLOOKUP(E373,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>516529</v>
       </c>
       <c r="G373" s="138"/>
       <c r="H373" s="132"/>
@@ -13712,29 +13707,29 @@
       <c r="A374" s="76"/>
       <c r="B374" s="76"/>
       <c r="C374" s="34"/>
-      <c r="D374" s="71"/>
-      <c r="E374" s="72" t="s">
+      <c r="D374" s="71" t="s">
         <v>710</v>
       </c>
-      <c r="F374" s="140">
-        <f>IFERROR(VLOOKUP(E374,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G374" s="138"/>
+      <c r="E374" s="76"/>
+      <c r="F374" s="140"/>
+      <c r="G374" s="187">
+        <f>SUM(F375:F383)</f>
+        <v>58572858.17</v>
+      </c>
       <c r="H374" s="132"/>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="76"/>
       <c r="B375" s="76"/>
       <c r="C375" s="34"/>
-      <c r="D375" s="71" t="s">
+      <c r="D375" s="71"/>
+      <c r="E375" s="72" t="s">
         <v>711</v>
       </c>
-      <c r="E375" s="76"/>
-      <c r="F375" s="140"/>
-      <c r="G375" s="187">
-        <f>SUM(F376:F384)</f>
-        <v>58572858.17</v>
-      </c>
+      <c r="F375" s="140">
+        <f>IFERROR(VLOOKUP(E375,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G375" s="138"/>
       <c r="H375" s="132"/>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.25">
@@ -13747,6 +13742,7 @@
       </c>
       <c r="F376" s="140">
         <f>IFERROR(VLOOKUP(E376,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>45070376.57</v>
       </c>
       <c r="G376" s="138"/>
       <c r="H376" s="132"/>
@@ -13761,7 +13757,6 @@
       </c>
       <c r="F377" s="140">
         <f>IFERROR(VLOOKUP(E377,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>45070376.57</v>
       </c>
       <c r="G377" s="138"/>
       <c r="H377" s="132"/>
@@ -13804,6 +13799,7 @@
       </c>
       <c r="F380" s="140">
         <f>IFERROR(VLOOKUP(E380,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>13502481.6</v>
       </c>
       <c r="G380" s="138"/>
       <c r="H380" s="132"/>
@@ -13818,7 +13814,6 @@
       </c>
       <c r="F381" s="140">
         <f>IFERROR(VLOOKUP(E381,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>13502481.6</v>
       </c>
       <c r="G381" s="138"/>
       <c r="H381" s="132"/>
@@ -13842,7 +13837,7 @@
       <c r="B383" s="76"/>
       <c r="C383" s="34"/>
       <c r="D383" s="71"/>
-      <c r="E383" s="72" t="s">
+      <c r="E383" s="151" t="s">
         <v>719</v>
       </c>
       <c r="F383" s="140">
@@ -13855,24 +13850,24 @@
       <c r="A384" s="76"/>
       <c r="B384" s="76"/>
       <c r="C384" s="34"/>
-      <c r="D384" s="71"/>
-      <c r="E384" s="151" t="s">
+      <c r="D384" s="71" t="s">
         <v>720</v>
       </c>
-      <c r="F384" s="140">
-        <f>IFERROR(VLOOKUP(E384,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G384" s="138"/>
+      <c r="E384" s="71"/>
+      <c r="F384" s="140"/>
+      <c r="G384" s="138">
+        <f>+F384</f>
+      </c>
       <c r="H384" s="132"/>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" s="76"/>
       <c r="B385" s="76"/>
       <c r="C385" s="34"/>
-      <c r="D385" s="71" t="s">
+      <c r="D385" s="139" t="s">
         <v>721</v>
       </c>
-      <c r="E385" s="71"/>
+      <c r="E385" s="72"/>
       <c r="F385" s="140"/>
       <c r="G385" s="138">
         <f>+F385</f>
@@ -13883,10 +13878,10 @@
       <c r="A386" s="76"/>
       <c r="B386" s="76"/>
       <c r="C386" s="34"/>
-      <c r="D386" s="139" t="s">
+      <c r="D386" s="71" t="s">
         <v>722</v>
       </c>
-      <c r="E386" s="72"/>
+      <c r="E386" s="71"/>
       <c r="F386" s="140"/>
       <c r="G386" s="138">
         <f>+F386</f>
@@ -13900,10 +13895,14 @@
       <c r="D387" s="71" t="s">
         <v>723</v>
       </c>
-      <c r="E387" s="71"/>
-      <c r="F387" s="140"/>
+      <c r="E387" s="72" t="s">
+        <v>724</v>
+      </c>
+      <c r="F387" s="140">
+        <f>IFERROR(VLOOKUP(E387,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
       <c r="G387" s="138">
-        <f>+F387</f>
+        <f>+F387+F388</f>
       </c>
       <c r="H387" s="132"/>
     </row>
@@ -13911,35 +13910,31 @@
       <c r="A388" s="76"/>
       <c r="B388" s="76"/>
       <c r="C388" s="34"/>
-      <c r="D388" s="71" t="s">
-        <v>724</v>
-      </c>
+      <c r="D388" s="71"/>
       <c r="E388" s="72" t="s">
         <v>725</v>
       </c>
       <c r="F388" s="140">
         <f>IFERROR(VLOOKUP(E388,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G388" s="138">
-        <f>+F388+F389</f>
-      </c>
+      <c r="G388" s="138"/>
       <c r="H388" s="132"/>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" s="76"/>
       <c r="B389" s="76"/>
       <c r="C389" s="34"/>
-      <c r="D389" s="71"/>
-      <c r="E389" s="72" t="s">
+      <c r="D389" s="71" t="s">
         <v>726</v>
       </c>
-      <c r="F389" s="140">
-        <f>IFERROR(VLOOKUP(E389,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G389" s="138"/>
+      <c r="E389" s="71"/>
+      <c r="F389" s="140"/>
+      <c r="G389" s="138">
+        <f>+F389</f>
+      </c>
       <c r="H389" s="132"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A390" s="76"/>
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
@@ -13948,24 +13943,31 @@
       </c>
       <c r="E390" s="71"/>
       <c r="F390" s="140"/>
-      <c r="G390" s="138">
-        <f>+F390</f>
+      <c r="G390" s="187">
+        <f>SUM(F390:F392)</f>
+        <v>9064800</v>
       </c>
       <c r="H390" s="132"/>
+      <c r="I390" s="134"/>
+      <c r="J390" s="132"/>
+      <c r="K390" s="72"/>
+      <c r="L390" s="72"/>
+      <c r="M390" s="72"/>
+      <c r="N390" s="72"/>
+      <c r="O390" s="72"/>
     </row>
     <row r="391" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A391" s="76"/>
       <c r="B391" s="76"/>
       <c r="C391" s="34"/>
-      <c r="D391" s="71" t="s">
+      <c r="D391" s="71"/>
+      <c r="E391" s="72" t="s">
         <v>728</v>
       </c>
-      <c r="E391" s="71"/>
-      <c r="F391" s="140"/>
-      <c r="G391" s="187">
-        <f>SUM(F391:F393)</f>
-        <v>9064800</v>
-      </c>
+      <c r="F391" s="140">
+        <f>IFERROR(VLOOKUP(E391,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G391" s="138"/>
       <c r="H391" s="132"/>
       <c r="I391" s="134"/>
       <c r="J391" s="132"/>
@@ -13985,6 +13987,7 @@
       </c>
       <c r="F392" s="140">
         <f>IFERROR(VLOOKUP(E392,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>9064800</v>
       </c>
       <c r="G392" s="138"/>
       <c r="H392" s="132"/>
@@ -13996,46 +13999,38 @@
       <c r="N392" s="72"/>
       <c r="O392" s="72"/>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" s="76"/>
       <c r="B393" s="76"/>
       <c r="C393" s="34"/>
-      <c r="D393" s="71"/>
+      <c r="D393" s="71" t="s">
+        <v>730</v>
+      </c>
       <c r="E393" s="72" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>9064800</v>
-      </c>
-      <c r="G393" s="138"/>
+        <v>5598557</v>
+      </c>
+      <c r="G393" s="138">
+        <f>+F393+F394+F395+F396</f>
+        <v>5598557</v>
+      </c>
       <c r="H393" s="132"/>
-      <c r="I393" s="134"/>
-      <c r="J393" s="132"/>
-      <c r="K393" s="72"/>
-      <c r="L393" s="72"/>
-      <c r="M393" s="72"/>
-      <c r="N393" s="72"/>
-      <c r="O393" s="72"/>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" s="76"/>
       <c r="B394" s="76"/>
       <c r="C394" s="34"/>
-      <c r="D394" s="71" t="s">
-        <v>731</v>
-      </c>
+      <c r="D394" s="71"/>
       <c r="E394" s="72" t="s">
         <v>732</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>5598557</v>
-      </c>
-      <c r="G394" s="138">
-        <f>+F394+F395+F396+F397</f>
-        <v>5598557</v>
-      </c>
+      </c>
+      <c r="G394" s="138"/>
       <c r="H394" s="132"/>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.25">
@@ -14070,89 +14065,89 @@
       <c r="A397" s="76"/>
       <c r="B397" s="76"/>
       <c r="C397" s="34"/>
-      <c r="D397" s="71"/>
-      <c r="E397" s="72" t="s">
+      <c r="D397" s="71" t="s">
         <v>735</v>
       </c>
-      <c r="F397" s="140">
-        <f>IFERROR(VLOOKUP(E397,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G397" s="138"/>
+      <c r="E397" s="188"/>
+      <c r="F397" s="140"/>
+      <c r="G397" s="138">
+        <f>SUM(F397:F398)</f>
+      </c>
       <c r="H397" s="132"/>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" s="76"/>
       <c r="B398" s="76"/>
       <c r="C398" s="34"/>
-      <c r="D398" s="71" t="s">
+      <c r="D398" s="139"/>
+      <c r="E398" s="72" t="s">
         <v>736</v>
       </c>
-      <c r="E398" s="188"/>
-      <c r="F398" s="140"/>
-      <c r="G398" s="138">
-        <f>SUM(F398:F399)</f>
-      </c>
-      <c r="H398" s="132"/>
+      <c r="F398" s="140">
+        <f>IFERROR(VLOOKUP(E398,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G398" s="138"/>
+      <c r="H398" s="72"/>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" s="76"/>
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
-      <c r="D399" s="139"/>
-      <c r="E399" s="72" t="s">
+      <c r="D399" s="71" t="s">
         <v>737</v>
       </c>
-      <c r="F399" s="140">
-        <f>IFERROR(VLOOKUP(E399,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G399" s="138"/>
-      <c r="H399" s="72"/>
+      <c r="E399" s="188"/>
+      <c r="F399" s="140"/>
+      <c r="G399" s="138">
+        <f>+F399+F400</f>
+      </c>
+      <c r="H399" s="132"/>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" s="76"/>
       <c r="B400" s="76"/>
       <c r="C400" s="34"/>
-      <c r="D400" s="71" t="s">
+      <c r="D400" s="71"/>
+      <c r="E400" s="72" t="s">
         <v>738</v>
       </c>
-      <c r="E400" s="188"/>
-      <c r="F400" s="140"/>
-      <c r="G400" s="138">
-        <f>+F400+F401</f>
-      </c>
+      <c r="F400" s="140">
+        <f>IFERROR(VLOOKUP(E400,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G400" s="138"/>
       <c r="H400" s="132"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" s="76"/>
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
-      <c r="D401" s="71"/>
-      <c r="E401" s="72" t="s">
+      <c r="D401" s="71" t="s">
         <v>739</v>
+      </c>
+      <c r="E401" s="71" t="s">
+        <v>740</v>
       </c>
       <c r="F401" s="140">
         <f>IFERROR(VLOOKUP(E401,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G401" s="138"/>
+        <v>276280951</v>
+      </c>
+      <c r="G401" s="187">
+        <f>+F401</f>
+        <v>276280951</v>
+      </c>
       <c r="H401" s="132"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" s="76"/>
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
       <c r="D402" s="71" t="s">
-        <v>740</v>
-      </c>
-      <c r="E402" s="71" t="s">
         <v>741</v>
       </c>
-      <c r="F402" s="140">
-        <f>IFERROR(VLOOKUP(E402,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>276280951</v>
-      </c>
-      <c r="G402" s="187">
-        <f>+F402</f>
-        <v>276280951</v>
+      <c r="E402" s="188"/>
+      <c r="F402" s="140"/>
+      <c r="G402" s="138">
+        <f>+F403+F404</f>
       </c>
       <c r="H402" s="132"/>
     </row>
@@ -14160,21 +14155,21 @@
       <c r="A403" s="76"/>
       <c r="B403" s="76"/>
       <c r="C403" s="34"/>
-      <c r="D403" s="71" t="s">
+      <c r="D403" s="71"/>
+      <c r="E403" s="72" t="s">
         <v>742</v>
       </c>
-      <c r="E403" s="188"/>
-      <c r="F403" s="140"/>
-      <c r="G403" s="138">
-        <f>+F404+F405</f>
-      </c>
+      <c r="F403" s="140">
+        <f>IFERROR(VLOOKUP(E403,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G403" s="138"/>
       <c r="H403" s="132"/>
     </row>
     <row r="404" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" s="76"/>
       <c r="B404" s="76"/>
       <c r="C404" s="34"/>
-      <c r="D404" s="71"/>
+      <c r="D404" s="76"/>
       <c r="E404" s="72" t="s">
         <v>743</v>
       </c>
@@ -14188,27 +14183,28 @@
       <c r="A405" s="76"/>
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
-      <c r="D405" s="76"/>
-      <c r="E405" s="72" t="s">
+      <c r="D405" s="71" t="s">
         <v>744</v>
       </c>
-      <c r="F405" s="140">
-        <f>IFERROR(VLOOKUP(E405,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G405" s="138"/>
+      <c r="E405" s="72"/>
+      <c r="F405" s="140"/>
+      <c r="G405" s="138">
+        <f>+F405</f>
+      </c>
       <c r="H405" s="132"/>
     </row>
-    <row r="406" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" s="76"/>
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
       <c r="D406" s="71" t="s">
         <v>745</v>
       </c>
-      <c r="E406" s="72"/>
+      <c r="E406" s="71"/>
       <c r="F406" s="140"/>
-      <c r="G406" s="138">
-        <f>+F406</f>
+      <c r="G406" s="187">
+        <f>SUM(F406:F412)</f>
+        <v>489482.99</v>
       </c>
       <c r="H406" s="132"/>
     </row>
@@ -14216,15 +14212,14 @@
       <c r="A407" s="76"/>
       <c r="B407" s="76"/>
       <c r="C407" s="34"/>
-      <c r="D407" s="71" t="s">
+      <c r="D407" s="71"/>
+      <c r="E407" s="151" t="s">
         <v>746</v>
       </c>
-      <c r="E407" s="71"/>
-      <c r="F407" s="140"/>
-      <c r="G407" s="187">
-        <f>SUM(F407:F413)</f>
-        <v>489482.99</v>
-      </c>
+      <c r="F407" s="140">
+        <f>IFERROR(VLOOKUP(E407,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G407" s="138"/>
       <c r="H407" s="132"/>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
@@ -14232,7 +14227,7 @@
       <c r="B408" s="76"/>
       <c r="C408" s="34"/>
       <c r="D408" s="71"/>
-      <c r="E408" s="151" t="s">
+      <c r="E408" s="72" t="s">
         <v>747</v>
       </c>
       <c r="F408" s="140">
@@ -14251,6 +14246,7 @@
       </c>
       <c r="F409" s="140">
         <f>IFERROR(VLOOKUP(E409,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>489482.99</v>
       </c>
       <c r="G409" s="138"/>
       <c r="H409" s="132"/>
@@ -14265,7 +14261,6 @@
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>489482.99</v>
       </c>
       <c r="G410" s="138"/>
       <c r="H410" s="132"/>
@@ -14275,7 +14270,7 @@
       <c r="B411" s="76"/>
       <c r="C411" s="34"/>
       <c r="D411" s="71"/>
-      <c r="E411" s="72" t="s">
+      <c r="E411" s="151" t="s">
         <v>750</v>
       </c>
       <c r="F411" s="140">
@@ -14289,7 +14284,7 @@
       <c r="B412" s="76"/>
       <c r="C412" s="34"/>
       <c r="D412" s="71"/>
-      <c r="E412" s="151" t="s">
+      <c r="E412" s="72" t="s">
         <v>751</v>
       </c>
       <c r="F412" s="140">
@@ -14298,37 +14293,44 @@
       <c r="G412" s="138"/>
       <c r="H412" s="132"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A413" s="76"/>
       <c r="B413" s="76"/>
       <c r="C413" s="34"/>
-      <c r="D413" s="71"/>
+      <c r="D413" s="139" t="s">
+        <v>752</v>
+      </c>
       <c r="E413" s="72" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F413" s="140">
         <f>IFERROR(VLOOKUP(E413,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G413" s="138"/>
+      <c r="G413" s="187">
+        <f>+F413+F414</f>
+        <v>236115665.5</v>
+      </c>
       <c r="H413" s="132"/>
+      <c r="I413" s="134"/>
+      <c r="J413" s="72"/>
+      <c r="K413" s="72"/>
+      <c r="L413" s="72"/>
+      <c r="M413" s="72"/>
+      <c r="N413" s="72"/>
     </row>
     <row r="414" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A414" s="76"/>
       <c r="B414" s="76"/>
       <c r="C414" s="34"/>
-      <c r="D414" s="139" t="s">
-        <v>753</v>
-      </c>
+      <c r="D414" s="139"/>
       <c r="E414" s="72" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G414" s="187">
-        <f>+F414+F415</f>
         <v>236115665.5</v>
       </c>
+      <c r="G414" s="138"/>
       <c r="H414" s="132"/>
       <c r="I414" s="134"/>
       <c r="J414" s="72"/>
@@ -14337,26 +14339,19 @@
       <c r="M414" s="72"/>
       <c r="N414" s="72"/>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" s="76"/>
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
-      <c r="D415" s="139"/>
-      <c r="E415" s="72" t="s">
-        <v>753</v>
-      </c>
-      <c r="F415" s="140">
-        <f>IFERROR(VLOOKUP(E415,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>236115665.5</v>
-      </c>
-      <c r="G415" s="138"/>
+      <c r="D415" s="139" t="s">
+        <v>754</v>
+      </c>
+      <c r="E415" s="72"/>
+      <c r="F415" s="140"/>
+      <c r="G415" s="138">
+        <f>+F415</f>
+      </c>
       <c r="H415" s="132"/>
-      <c r="I415" s="134"/>
-      <c r="J415" s="72"/>
-      <c r="K415" s="72"/>
-      <c r="L415" s="72"/>
-      <c r="M415" s="72"/>
-      <c r="N415" s="72"/>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" s="76"/>
@@ -14365,31 +14360,33 @@
       <c r="D416" s="139" t="s">
         <v>755</v>
       </c>
-      <c r="E416" s="72"/>
-      <c r="F416" s="140"/>
-      <c r="G416" s="138">
-        <f>+F416</f>
+      <c r="E416" s="151" t="s">
+        <v>756</v>
+      </c>
+      <c r="F416" s="140">
+        <f>IFERROR(VLOOKUP(E416,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G416" s="187">
+        <f>SUM(F416:F423)</f>
+        <v>3499846.7</v>
       </c>
       <c r="H416" s="132"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" s="76"/>
       <c r="B417" s="76"/>
       <c r="C417" s="34"/>
-      <c r="D417" s="139" t="s">
-        <v>756</v>
-      </c>
-      <c r="E417" s="151" t="s">
+      <c r="D417" s="139"/>
+      <c r="E417" s="72" t="s">
         <v>757</v>
       </c>
       <c r="F417" s="140">
         <f>IFERROR(VLOOKUP(E417,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G417" s="187">
-        <f>SUM(F417:F424)</f>
-        <v>3499846.7</v>
-      </c>
-      <c r="H417" s="132"/>
+        <v>3013363</v>
+      </c>
+      <c r="G417" s="138"/>
+      <c r="H417" s="72"/>
+      <c r="I417" s="164"/>
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" s="76"/>
@@ -14401,7 +14398,6 @@
       </c>
       <c r="F418" s="140">
         <f>IFERROR(VLOOKUP(E418,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>3013363</v>
       </c>
       <c r="G418" s="138"/>
       <c r="H418" s="72"/>
@@ -14417,6 +14413,7 @@
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>442383.7</v>
       </c>
       <c r="G419" s="138"/>
       <c r="H419" s="72"/>
@@ -14432,7 +14429,6 @@
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>442383.7</v>
       </c>
       <c r="G420" s="138"/>
       <c r="H420" s="72"/>
@@ -14473,32 +14469,35 @@
       <c r="B423" s="76"/>
       <c r="C423" s="34"/>
       <c r="D423" s="139"/>
-      <c r="E423" s="72" t="s">
-        <v>763</v>
+      <c r="E423" s="72" t="str">
+        <f>+Hoja1!A267</f>
+        <v>426880000 - Tasas Municipales Gs Campo</v>
       </c>
       <c r="F423" s="140">
         <f>IFERROR(VLOOKUP(E423,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>44100</v>
       </c>
       <c r="G423" s="138"/>
       <c r="H423" s="72"/>
       <c r="I423" s="164"/>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" s="76"/>
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
-      <c r="D424" s="139"/>
-      <c r="E424" s="72" t="str">
-        <f>+Hoja1!A267</f>
-        <v>426880000 - Tasas Municipales Gs Campo</v>
-      </c>
+      <c r="D424" s="71" t="s">
+        <v>763</v>
+      </c>
+      <c r="E424" s="71"/>
       <c r="F424" s="140">
-        <f>IFERROR(VLOOKUP(E424,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>44100</v>
-      </c>
-      <c r="G424" s="138"/>
-      <c r="H424" s="72"/>
-      <c r="I424" s="164"/>
+        <f>IFERROR(VLOOKUP(D424,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>51916602.99</v>
+      </c>
+      <c r="G424" s="187">
+        <f>+F424</f>
+        <v>51916602.99</v>
+      </c>
+      <c r="H424" s="132"/>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" s="76"/>
@@ -14508,13 +14507,10 @@
         <v>764</v>
       </c>
       <c r="E425" s="71"/>
-      <c r="F425" s="140">
-        <f>IFERROR(VLOOKUP(D425,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>51916602.99</v>
-      </c>
+      <c r="F425" s="140"/>
       <c r="G425" s="187">
-        <f>+F425</f>
-        <v>51916602.99</v>
+        <f>SUM(F426:F433)</f>
+        <v>768315.33</v>
       </c>
       <c r="H425" s="132"/>
     </row>
@@ -14522,27 +14518,27 @@
       <c r="A426" s="76"/>
       <c r="B426" s="76"/>
       <c r="C426" s="34"/>
-      <c r="D426" s="71" t="s">
+      <c r="D426" s="71"/>
+      <c r="E426" s="72" t="s">
         <v>765</v>
       </c>
-      <c r="E426" s="71"/>
-      <c r="F426" s="140"/>
-      <c r="G426" s="187">
-        <f>SUM(F427:F434)</f>
-        <v>768315.33</v>
-      </c>
+      <c r="F426" s="140">
+        <f>IFERROR(VLOOKUP(E426,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G426" s="138"/>
       <c r="H426" s="132"/>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" s="76"/>
       <c r="B427" s="76"/>
       <c r="C427" s="34"/>
-      <c r="D427" s="71"/>
-      <c r="E427" s="72" t="s">
+      <c r="D427" s="76"/>
+      <c r="E427" s="71" t="s">
         <v>766</v>
       </c>
       <c r="F427" s="140">
         <f>IFERROR(VLOOKUP(E427,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>615911.61</v>
       </c>
       <c r="G427" s="138"/>
       <c r="H427" s="132"/>
@@ -14557,7 +14553,7 @@
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>615911.61</v>
+        <v>152403.72</v>
       </c>
       <c r="G428" s="138"/>
       <c r="H428" s="132"/>
@@ -14572,7 +14568,6 @@
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>152403.72</v>
       </c>
       <c r="G429" s="138"/>
       <c r="H429" s="132"/>
@@ -14582,7 +14577,7 @@
       <c r="B430" s="76"/>
       <c r="C430" s="34"/>
       <c r="D430" s="76"/>
-      <c r="E430" s="71" t="s">
+      <c r="E430" s="72" t="s">
         <v>769</v>
       </c>
       <c r="F430" s="140">
@@ -14637,29 +14632,30 @@
       <c r="A434" s="76"/>
       <c r="B434" s="76"/>
       <c r="C434" s="34"/>
-      <c r="D434" s="76"/>
-      <c r="E434" s="72" t="s">
+      <c r="D434" s="71" t="s">
         <v>773</v>
       </c>
-      <c r="F434" s="140">
-        <f>IFERROR(VLOOKUP(E434,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G434" s="138"/>
+      <c r="E434" s="71"/>
+      <c r="F434" s="140"/>
+      <c r="G434" s="187">
+        <f>SUM(F434:F438)</f>
+        <v>17921832.18</v>
+      </c>
       <c r="H434" s="132"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" s="76"/>
       <c r="B435" s="76"/>
       <c r="C435" s="34"/>
-      <c r="D435" s="71" t="s">
+      <c r="D435" s="71"/>
+      <c r="E435" s="72" t="s">
         <v>774</v>
       </c>
-      <c r="E435" s="71"/>
-      <c r="F435" s="140"/>
-      <c r="G435" s="187">
-        <f>SUM(F435:F439)</f>
-        <v>17921832.18</v>
-      </c>
+      <c r="F435" s="140">
+        <f>IFERROR(VLOOKUP(E435,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>1413626.44</v>
+      </c>
+      <c r="G435" s="138"/>
       <c r="H435" s="132"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.25">
@@ -14672,7 +14668,7 @@
       </c>
       <c r="F436" s="140">
         <f>IFERROR(VLOOKUP(E436,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>1413626.44</v>
+        <v>16508205.74</v>
       </c>
       <c r="G436" s="138"/>
       <c r="H436" s="132"/>
@@ -14687,7 +14683,6 @@
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>16508205.74</v>
       </c>
       <c r="G437" s="138"/>
       <c r="H437" s="132"/>
@@ -14710,45 +14705,45 @@
       <c r="A439" s="76"/>
       <c r="B439" s="76"/>
       <c r="C439" s="34"/>
-      <c r="D439" s="71"/>
-      <c r="E439" s="72" t="s">
+      <c r="D439" s="71" t="s">
         <v>778</v>
       </c>
-      <c r="F439" s="140">
-        <f>IFERROR(VLOOKUP(E439,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G439" s="138"/>
+      <c r="E439" s="188"/>
+      <c r="F439" s="140"/>
+      <c r="G439" s="138">
+        <f>+F439</f>
+      </c>
       <c r="H439" s="132"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" s="76"/>
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
-      <c r="D440" s="71" t="s">
+      <c r="D440" s="139" t="s">
         <v>779</v>
       </c>
-      <c r="E440" s="188"/>
+      <c r="E440" s="76"/>
       <c r="F440" s="140"/>
       <c r="G440" s="138">
-        <f>+F440</f>
+        <f>SUM(F440:F442)</f>
       </c>
       <c r="H440" s="132"/>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" s="76"/>
       <c r="B441" s="76"/>
       <c r="C441" s="34"/>
-      <c r="D441" s="139" t="s">
+      <c r="D441" s="139"/>
+      <c r="E441" s="72" t="s">
         <v>780</v>
       </c>
-      <c r="E441" s="76"/>
-      <c r="F441" s="140"/>
-      <c r="G441" s="138">
-        <f>SUM(F441:F443)</f>
-      </c>
+      <c r="F441" s="140">
+        <f>IFERROR(VLOOKUP(E441,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G441" s="138"/>
       <c r="H441" s="132"/>
     </row>
-    <row r="442" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" s="76"/>
       <c r="B442" s="76"/>
       <c r="C442" s="34"/>
@@ -14766,44 +14761,46 @@
       <c r="A443" s="76"/>
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
-      <c r="D443" s="139"/>
-      <c r="E443" s="72" t="s">
+      <c r="D443" s="71" t="s">
         <v>782</v>
       </c>
-      <c r="F443" s="140">
-        <f>IFERROR(VLOOKUP(E443,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G443" s="138"/>
+      <c r="E443" s="188"/>
+      <c r="F443" s="140"/>
+      <c r="G443" s="187">
+        <f>SUM(F444:F447)</f>
+        <v>101483.28</v>
+      </c>
       <c r="H443" s="132"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" s="76"/>
       <c r="B444" s="76"/>
       <c r="C444" s="34"/>
-      <c r="D444" s="71" t="s">
+      <c r="D444" s="71"/>
+      <c r="E444" s="151" t="s">
         <v>783</v>
       </c>
-      <c r="E444" s="188"/>
-      <c r="F444" s="140"/>
-      <c r="G444" s="187">
-        <f>SUM(F445:F448)</f>
-        <v>101483.28</v>
-      </c>
+      <c r="F444" s="140">
+        <f>IFERROR(VLOOKUP(E444,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G444" s="138"/>
       <c r="H444" s="132"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A445" s="76"/>
       <c r="B445" s="76"/>
       <c r="C445" s="34"/>
       <c r="D445" s="71"/>
-      <c r="E445" s="151" t="s">
+      <c r="E445" s="72" t="s">
         <v>784</v>
       </c>
       <c r="F445" s="140">
         <f>IFERROR(VLOOKUP(E445,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>101483.28</v>
       </c>
       <c r="G445" s="138"/>
-      <c r="H445" s="132"/>
+      <c r="H445" s="72"/>
+      <c r="I445" s="164"/>
     </row>
     <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A446" s="76"/>
@@ -14815,7 +14812,6 @@
       </c>
       <c r="F446" s="140">
         <f>IFERROR(VLOOKUP(E446,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>101483.28</v>
       </c>
       <c r="G446" s="138"/>
       <c r="H446" s="72"/>
@@ -14836,34 +14832,33 @@
       <c r="H447" s="72"/>
       <c r="I447" s="164"/>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" s="76"/>
       <c r="B448" s="76"/>
       <c r="C448" s="34"/>
-      <c r="D448" s="71"/>
-      <c r="E448" s="72" t="s">
+      <c r="D448" s="196" t="s">
         <v>787</v>
       </c>
-      <c r="F448" s="140">
-        <f>IFERROR(VLOOKUP(E448,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G448" s="138"/>
-      <c r="H448" s="72"/>
-      <c r="I448" s="164"/>
+      <c r="E448" s="197"/>
+      <c r="F448" s="198"/>
+      <c r="G448" s="187">
+        <f>+F449+F450+F451</f>
+        <v>8441197.290000001</v>
+      </c>
+      <c r="H448" s="132"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" s="76"/>
       <c r="B449" s="76"/>
       <c r="C449" s="34"/>
-      <c r="D449" s="196" t="s">
+      <c r="D449" s="71"/>
+      <c r="E449" s="72" t="s">
         <v>788</v>
       </c>
-      <c r="E449" s="197"/>
-      <c r="F449" s="198"/>
-      <c r="G449" s="187">
-        <f>+F450+F451+F452</f>
-        <v>8441197.290000001</v>
-      </c>
+      <c r="F449" s="140">
+        <f>IFERROR(VLOOKUP(E449,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G449" s="138"/>
       <c r="H449" s="132"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.25">
@@ -14890,6 +14885,7 @@
       </c>
       <c r="F451" s="140">
         <f>IFERROR(VLOOKUP(E451,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>8441197.290000001</v>
       </c>
       <c r="G451" s="138"/>
       <c r="H451" s="132"/>
@@ -14898,30 +14894,30 @@
       <c r="A452" s="76"/>
       <c r="B452" s="76"/>
       <c r="C452" s="34"/>
-      <c r="D452" s="71"/>
-      <c r="E452" s="72" t="s">
+      <c r="D452" s="71" t="s">
         <v>791</v>
       </c>
-      <c r="F452" s="140">
-        <f>IFERROR(VLOOKUP(E452,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>8441197.290000001</v>
-      </c>
-      <c r="G452" s="138"/>
+      <c r="E452" s="188"/>
+      <c r="F452" s="140"/>
+      <c r="G452" s="187">
+        <f>SUM(F453:F456)</f>
+        <v>14667167.22</v>
+      </c>
       <c r="H452" s="132"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" s="76"/>
       <c r="B453" s="76"/>
       <c r="C453" s="34"/>
-      <c r="D453" s="71" t="s">
+      <c r="D453" s="71"/>
+      <c r="E453" s="72" t="s">
         <v>792</v>
       </c>
-      <c r="E453" s="188"/>
-      <c r="F453" s="140"/>
-      <c r="G453" s="187">
-        <f>SUM(F454:F457)</f>
-        <v>14667167.22</v>
-      </c>
+      <c r="F453" s="140">
+        <f>IFERROR(VLOOKUP(E453,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>299800</v>
+      </c>
+      <c r="G453" s="138"/>
       <c r="H453" s="132"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.25">
@@ -14934,7 +14930,7 @@
       </c>
       <c r="F454" s="140">
         <f>IFERROR(VLOOKUP(E454,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>299800</v>
+        <v>14367367.22</v>
       </c>
       <c r="G454" s="138"/>
       <c r="H454" s="132"/>
@@ -14949,7 +14945,6 @@
       </c>
       <c r="F455" s="140">
         <f>IFERROR(VLOOKUP(E455,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>14367367.22</v>
       </c>
       <c r="G455" s="138"/>
       <c r="H455" s="132"/>
@@ -14972,14 +14967,16 @@
       <c r="A457" s="76"/>
       <c r="B457" s="76"/>
       <c r="C457" s="34"/>
-      <c r="D457" s="71"/>
-      <c r="E457" s="72" t="s">
+      <c r="D457" s="71" t="s">
         <v>796</v>
       </c>
+      <c r="E457" s="71"/>
       <c r="F457" s="140">
-        <f>IFERROR(VLOOKUP(E457,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G457" s="138"/>
+        <f>IFERROR(VLOOKUP(D457,Hoja1!$A$86:$C$353,3,FALSE),)</f>
+      </c>
+      <c r="G457" s="138">
+        <f>+F457</f>
+      </c>
       <c r="H457" s="132"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.25">
@@ -15002,15 +14999,13 @@
       <c r="A459" s="76"/>
       <c r="B459" s="76"/>
       <c r="C459" s="34"/>
-      <c r="D459" s="71" t="s">
+      <c r="D459" s="139" t="s">
         <v>798</v>
       </c>
-      <c r="E459" s="71"/>
-      <c r="F459" s="140">
-        <f>IFERROR(VLOOKUP(D459,Hoja1!$A$86:$C$353,3,FALSE),)</f>
-      </c>
+      <c r="E459" s="72"/>
+      <c r="F459" s="140"/>
       <c r="G459" s="138">
-        <f>+F459</f>
+        <f>+SUM(F460:F461)</f>
       </c>
       <c r="H459" s="132"/>
     </row>
@@ -15018,14 +15013,14 @@
       <c r="A460" s="76"/>
       <c r="B460" s="76"/>
       <c r="C460" s="34"/>
-      <c r="D460" s="139" t="s">
+      <c r="D460" s="139"/>
+      <c r="E460" s="72" t="s">
         <v>799</v>
       </c>
-      <c r="E460" s="72"/>
-      <c r="F460" s="140"/>
-      <c r="G460" s="138">
-        <f>+SUM(F461:F462)</f>
-      </c>
+      <c r="F460" s="140">
+        <f>IFERROR(VLOOKUP(E460,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G460" s="138"/>
       <c r="H460" s="132"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.25">
@@ -15046,33 +15041,34 @@
       <c r="A462" s="76"/>
       <c r="B462" s="76"/>
       <c r="C462" s="34"/>
-      <c r="D462" s="139"/>
-      <c r="E462" s="72" t="s">
+      <c r="D462" s="71" t="s">
         <v>801</v>
+      </c>
+      <c r="E462" s="71" t="s">
+        <v>802</v>
       </c>
       <c r="F462" s="140">
         <f>IFERROR(VLOOKUP(E462,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G462" s="138"/>
-      <c r="H462" s="132"/>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G462" s="187">
+        <f>SUM(F462:F470)</f>
+        <v>15451043.76</v>
+      </c>
+      <c r="H462" s="150"/>
+    </row>
+    <row r="463" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" s="76"/>
       <c r="B463" s="76"/>
       <c r="C463" s="34"/>
-      <c r="D463" s="71" t="s">
-        <v>802</v>
-      </c>
-      <c r="E463" s="71" t="s">
+      <c r="D463" s="71"/>
+      <c r="E463" s="72" t="s">
         <v>803</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G463" s="187">
-        <f>SUM(F463:F471)</f>
-        <v>15451043.76</v>
-      </c>
+        <v>7468721</v>
+      </c>
+      <c r="G463" s="138"/>
       <c r="H463" s="150"/>
     </row>
     <row r="464" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -15085,12 +15081,12 @@
       </c>
       <c r="F464" s="140">
         <f>IFERROR(VLOOKUP(E464,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>7468721</v>
+        <v>7982322.76</v>
       </c>
       <c r="G464" s="138"/>
       <c r="H464" s="150"/>
     </row>
-    <row r="465" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" s="76"/>
       <c r="B465" s="76"/>
       <c r="C465" s="34"/>
@@ -15100,10 +15096,10 @@
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>7982322.76</v>
       </c>
       <c r="G465" s="138"/>
-      <c r="H465" s="150"/>
+      <c r="H465" s="72"/>
+      <c r="I465" s="164"/>
     </row>
     <row r="466" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="76"/>
@@ -15180,33 +15176,32 @@
       <c r="H470" s="72"/>
       <c r="I470" s="164"/>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" s="76"/>
       <c r="B471" s="76"/>
       <c r="C471" s="34"/>
-      <c r="D471" s="71"/>
-      <c r="E471" s="72" t="s">
+      <c r="D471" s="71" t="s">
         <v>811</v>
       </c>
-      <c r="F471" s="140">
-        <f>IFERROR(VLOOKUP(E471,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G471" s="138"/>
-      <c r="H471" s="72"/>
-      <c r="I471" s="164"/>
-    </row>
-    <row r="472" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E471" s="188"/>
+      <c r="F471" s="140"/>
+      <c r="G471" s="138">
+        <f>SUM(F471:F474)</f>
+      </c>
+      <c r="H471" s="132"/>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" s="76"/>
       <c r="B472" s="76"/>
       <c r="C472" s="34"/>
-      <c r="D472" s="71" t="s">
+      <c r="D472" s="71"/>
+      <c r="E472" s="72" t="s">
         <v>812</v>
       </c>
-      <c r="E472" s="188"/>
-      <c r="F472" s="140"/>
-      <c r="G472" s="138">
-        <f>SUM(F472:F475)</f>
-      </c>
+      <c r="F472" s="140">
+        <f>IFERROR(VLOOKUP(E472,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G472" s="138"/>
       <c r="H472" s="132"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
@@ -15241,21 +15236,23 @@
       <c r="A475" s="76"/>
       <c r="B475" s="76"/>
       <c r="C475" s="34"/>
-      <c r="D475" s="71"/>
-      <c r="E475" s="72" t="s">
+      <c r="D475" s="139" t="s">
         <v>815</v>
       </c>
+      <c r="E475" s="188"/>
       <c r="F475" s="140">
-        <f>IFERROR(VLOOKUP(E475,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G475" s="138"/>
+        <f>IFERROR(VLOOKUP(D475,Hoja1!$A$86:$C$353,5,FALSE),)</f>
+      </c>
+      <c r="G475" s="138">
+        <f>+F475</f>
+      </c>
       <c r="H475" s="132"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" s="76"/>
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
-      <c r="D476" s="139" t="s">
+      <c r="D476" s="71" t="s">
         <v>816</v>
       </c>
       <c r="E476" s="188"/>
@@ -15275,26 +15272,24 @@
         <v>817</v>
       </c>
       <c r="E477" s="188"/>
-      <c r="F477" s="140">
-        <f>IFERROR(VLOOKUP(D477,Hoja1!$A$86:$C$353,5,FALSE),)</f>
-      </c>
+      <c r="F477" s="140"/>
       <c r="G477" s="138">
-        <f>+F477</f>
+        <f>+F477+F478+F479</f>
       </c>
       <c r="H477" s="132"/>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" s="76"/>
       <c r="B478" s="76"/>
       <c r="C478" s="34"/>
-      <c r="D478" s="71" t="s">
+      <c r="D478" s="71"/>
+      <c r="E478" s="72" t="s">
         <v>818</v>
       </c>
-      <c r="E478" s="188"/>
-      <c r="F478" s="140"/>
-      <c r="G478" s="138">
-        <f>+F478+F479+F480</f>
-      </c>
+      <c r="F478" s="140">
+        <f>IFERROR(VLOOKUP(E478,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+      </c>
+      <c r="G478" s="138"/>
       <c r="H478" s="132"/>
     </row>
     <row r="479" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -15315,33 +15310,33 @@
       <c r="A480" s="76"/>
       <c r="B480" s="76"/>
       <c r="C480" s="34"/>
-      <c r="D480" s="71"/>
+      <c r="D480" s="71" t="s">
+        <v>820</v>
+      </c>
       <c r="E480" s="72" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F480" s="140">
         <f>IFERROR(VLOOKUP(E480,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G480" s="138"/>
+      <c r="G480" s="187">
+        <f>SUM(F480:F482)</f>
+        <v>4013596.99</v>
+      </c>
       <c r="H480" s="132"/>
     </row>
-    <row r="481" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" s="76"/>
       <c r="B481" s="76"/>
       <c r="C481" s="34"/>
-      <c r="D481" s="71" t="s">
-        <v>821</v>
-      </c>
+      <c r="D481" s="71"/>
       <c r="E481" s="72" t="s">
         <v>822</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
-      <c r="G481" s="187">
-        <f>SUM(F481:F483)</f>
-        <v>4013596.99</v>
-      </c>
+      <c r="G481" s="138"/>
       <c r="H481" s="132"/>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
@@ -15354,37 +15349,38 @@
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <v>4013596.99</v>
       </c>
       <c r="G482" s="138"/>
       <c r="H482" s="132"/>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A483" s="76"/>
       <c r="B483" s="76"/>
       <c r="C483" s="34"/>
-      <c r="D483" s="71"/>
+      <c r="D483" s="71" t="s">
+        <v>824</v>
+      </c>
       <c r="E483" s="72" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F483" s="140">
         <f>IFERROR(VLOOKUP(E483,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>4013596.99</v>
-      </c>
-      <c r="G483" s="138"/>
-      <c r="H483" s="132"/>
+      </c>
+      <c r="G483" s="138">
+        <f>+F483</f>
+      </c>
     </row>
     <row r="484" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A484" s="76"/>
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
       <c r="D484" s="71" t="s">
-        <v>825</v>
-      </c>
-      <c r="E484" s="72" t="s">
         <v>826</v>
       </c>
+      <c r="E484" s="71"/>
       <c r="F484" s="140">
-        <f>IFERROR(VLOOKUP(E484,Hoja1!$A$86:$E$377,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D484,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
       <c r="G484" s="138">
         <f>+F484</f>
@@ -15394,10 +15390,10 @@
       <c r="A485" s="76"/>
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
-      <c r="D485" s="71" t="s">
+      <c r="D485" s="139" t="s">
         <v>827</v>
       </c>
-      <c r="E485" s="71"/>
+      <c r="E485" s="72"/>
       <c r="F485" s="140">
         <f>IFERROR(VLOOKUP(D485,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15409,15 +15405,17 @@
       <c r="A486" s="76"/>
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
-      <c r="D486" s="139" t="s">
+      <c r="D486" s="71" t="s">
         <v>828</v>
       </c>
-      <c r="E486" s="72"/>
+      <c r="E486" s="68"/>
       <c r="F486" s="140">
         <f>IFERROR(VLOOKUP(D486,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G486" s="138">
+        <v>4150213.41</v>
+      </c>
+      <c r="G486" s="187">
         <f>+F486</f>
+        <v>4150213.41</v>
       </c>
     </row>
     <row r="487" spans="1:7" x14ac:dyDescent="0.25">
@@ -15427,14 +15425,12 @@
       <c r="D487" s="71" t="s">
         <v>829</v>
       </c>
-      <c r="E487" s="68"/>
+      <c r="E487" s="132"/>
       <c r="F487" s="140">
         <f>IFERROR(VLOOKUP(D487,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>4150213.41</v>
-      </c>
-      <c r="G487" s="187">
+      </c>
+      <c r="G487" s="138">
         <f>+F487</f>
-        <v>4150213.41</v>
       </c>
     </row>
     <row r="488" spans="1:7" x14ac:dyDescent="0.25">
@@ -15462,9 +15458,11 @@
       <c r="E489" s="132"/>
       <c r="F489" s="140">
         <f>IFERROR(VLOOKUP(D489,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G489" s="138">
+        <v>226987</v>
+      </c>
+      <c r="G489" s="187">
         <f>+F489</f>
+        <v>226987</v>
       </c>
     </row>
     <row r="490" spans="1:7" x14ac:dyDescent="0.25">
@@ -15477,28 +15475,26 @@
       <c r="E490" s="132"/>
       <c r="F490" s="140">
         <f>IFERROR(VLOOKUP(D490,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>226987</v>
+        <v>914304.7000000001</v>
       </c>
       <c r="G490" s="187">
         <f>+F490</f>
-        <v>226987</v>
+        <v>914304.7000000001</v>
       </c>
     </row>
     <row r="491" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A491" s="76"/>
       <c r="B491" s="76"/>
       <c r="C491" s="34"/>
-      <c r="D491" s="71" t="s">
+      <c r="D491" s="139" t="s">
         <v>833</v>
       </c>
       <c r="E491" s="132"/>
       <c r="F491" s="140">
         <f>IFERROR(VLOOKUP(D491,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>914304.7000000001</v>
-      </c>
-      <c r="G491" s="187">
+      </c>
+      <c r="G491" s="138">
         <f>+F491</f>
-        <v>914304.7000000001</v>
       </c>
     </row>
     <row r="492" spans="1:7" x14ac:dyDescent="0.25">
@@ -15508,7 +15504,7 @@
       <c r="D492" s="139" t="s">
         <v>834</v>
       </c>
-      <c r="E492" s="132"/>
+      <c r="E492" s="68"/>
       <c r="F492" s="140">
         <f>IFERROR(VLOOKUP(D492,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15523,7 +15519,7 @@
       <c r="D493" s="139" t="s">
         <v>835</v>
       </c>
-      <c r="E493" s="68"/>
+      <c r="E493" s="132"/>
       <c r="F493" s="140">
         <f>IFERROR(VLOOKUP(D493,Hoja1!$A$86:$E$377,5,FALSE),)</f>
       </c>
@@ -15568,32 +15564,33 @@
       <c r="D496" s="139" t="s">
         <v>838</v>
       </c>
-      <c r="E496" s="132"/>
+      <c r="E496" s="72" t="s">
+        <v>838</v>
+      </c>
       <c r="F496" s="140">
         <f>IFERROR(VLOOKUP(D496,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G496" s="138">
+        <v>358719.18</v>
+      </c>
+      <c r="G496" s="187">
         <f>+F496</f>
-      </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+        <v>358719.18</v>
+      </c>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" s="76"/>
       <c r="B497" s="76"/>
       <c r="C497" s="34"/>
       <c r="D497" s="139" t="s">
         <v>839</v>
       </c>
-      <c r="E497" s="72" t="s">
-        <v>839</v>
-      </c>
+      <c r="E497" s="132"/>
       <c r="F497" s="140">
         <f>IFERROR(VLOOKUP(D497,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-        <v>358719.18</v>
-      </c>
-      <c r="G497" s="187">
+      </c>
+      <c r="G497" s="138">
         <f>+F497</f>
-        <v>358719.18</v>
-      </c>
+      </c>
+      <c r="H497" s="162"/>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" s="76"/>
@@ -15643,7 +15640,7 @@
       </c>
       <c r="H500" s="162"/>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="76"/>
       <c r="B501" s="76"/>
       <c r="C501" s="34"/>
@@ -15657,7 +15654,6 @@
       <c r="G501" s="138">
         <f>+F501</f>
       </c>
-      <c r="H501" s="162"/>
     </row>
     <row r="502" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="76"/>
@@ -15674,19 +15670,19 @@
         <f>+F502</f>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A503" s="76"/>
       <c r="B503" s="76"/>
       <c r="C503" s="34"/>
-      <c r="D503" s="139" t="s">
-        <v>845</v>
-      </c>
+      <c r="D503" s="132"/>
       <c r="E503" s="132"/>
-      <c r="F503" s="140">
-        <f>IFERROR(VLOOKUP(D503,Hoja1!$A$86:$E$377,5,FALSE),)</f>
-      </c>
-      <c r="G503" s="138">
-        <f>+F503</f>
+      <c r="F503" s="162"/>
+      <c r="G503" s="133"/>
+      <c r="H503" s="199" t="s">
+        <v>55</v>
+      </c>
+      <c r="I503" s="199" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="504" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15694,123 +15690,117 @@
       <c r="B504" s="76"/>
       <c r="C504" s="34"/>
       <c r="D504" s="132"/>
-      <c r="E504" s="132"/>
-      <c r="F504" s="162"/>
-      <c r="G504" s="133"/>
-      <c r="H504" s="199" t="s">
-        <v>55</v>
-      </c>
-      <c r="I504" s="199" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="505" ht="13.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E504" s="200" t="s">
+        <v>845</v>
+      </c>
+      <c r="F504" s="201">
+        <f>SUM(F146:F502)</f>
+        <v>1672589124.2600002</v>
+      </c>
+      <c r="G504" s="202">
+        <f>SUM(G146:G502)</f>
+        <v>1672589124.26</v>
+      </c>
+      <c r="H504" s="199">
+        <f>+Resultados!C26</f>
+        <v>-1672589124.26</v>
+      </c>
+      <c r="I504" s="199">
+        <f>+H504+G504</f>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A505" s="76"/>
       <c r="B505" s="76"/>
       <c r="C505" s="34"/>
       <c r="D505" s="132"/>
-      <c r="E505" s="200" t="s">
+      <c r="E505" s="203" t="s">
         <v>846</v>
       </c>
-      <c r="F505" s="201">
-        <f>SUM(F146:F503)</f>
-        <v>1672589124.2600002</v>
-      </c>
-      <c r="G505" s="202">
-        <f>SUM(G146:G503)</f>
-        <v>1672589124.26</v>
-      </c>
-      <c r="H505" s="199">
-        <f>+Resultados!C26</f>
-        <v>-1672589124.26</v>
-      </c>
-      <c r="I505" s="199">
-        <f>+H505+G505</f>
-      </c>
-    </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F505" s="204">
+        <f>+-'Anexo II'!E103</f>
+        <v>-1609778933.7700005</v>
+      </c>
+      <c r="G505" s="205">
+        <f>+Hoja1!E318</f>
+        <v>1672589124.2599998</v>
+      </c>
+      <c r="H505" s="199"/>
+      <c r="I505" s="206"/>
+    </row>
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" s="76"/>
       <c r="B506" s="76"/>
       <c r="C506" s="34"/>
       <c r="D506" s="132"/>
-      <c r="E506" s="203" t="s">
+      <c r="E506" s="207" t="s">
         <v>847</v>
       </c>
-      <c r="F506" s="204">
-        <f>+-'Anexo II'!E103</f>
-        <v>-1609778933.7700005</v>
-      </c>
-      <c r="G506" s="205">
-        <f>+Hoja1!E318</f>
-        <v>1672589124.2599998</v>
-      </c>
-      <c r="H506" s="199"/>
-      <c r="I506" s="206"/>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F506" s="208">
+        <f>+F504+F505</f>
+        <v>62810190.48999977</v>
+      </c>
+      <c r="G506" s="209">
+        <f>+G505-G504</f>
+      </c>
+      <c r="H506" s="208"/>
+    </row>
+    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="76"/>
       <c r="B507" s="76"/>
       <c r="C507" s="34"/>
       <c r="D507" s="132"/>
-      <c r="E507" s="207" t="s">
+      <c r="E507" s="132"/>
+      <c r="F507" s="162">
+        <f>+F506-F280</f>
+        <v>-2.3096799850463867e-7</v>
+      </c>
+      <c r="G507" s="133"/>
+    </row>
+    <row r="508" ht="10.8" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="210"/>
+      <c r="B508" s="210"/>
+      <c r="C508" s="211"/>
+      <c r="D508" s="211"/>
+      <c r="E508" s="211" t="s">
         <v>848</v>
       </c>
-      <c r="F507" s="208">
-        <f>+F505+F506</f>
-        <v>62810190.48999977</v>
-      </c>
-      <c r="G507" s="209">
-        <f>+G506-G505</f>
-      </c>
-      <c r="H507" s="208"/>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A508" s="76"/>
-      <c r="B508" s="76"/>
-      <c r="C508" s="34"/>
-      <c r="D508" s="132"/>
-      <c r="E508" s="132"/>
-      <c r="F508" s="162">
-        <f>+F507-F281</f>
-        <v>-2.3096799850463867e-7</v>
-      </c>
-      <c r="G508" s="133"/>
-    </row>
-    <row r="509" ht="10.8" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="210"/>
-      <c r="B509" s="210"/>
-      <c r="C509" s="211"/>
-      <c r="D509" s="211"/>
-      <c r="E509" s="211" t="s">
-        <v>849</v>
-      </c>
-      <c r="F509" s="211">
-        <f>+F281-F507</f>
+      <c r="F508" s="211">
+        <f>+F280-F506</f>
         <v>2.3096799850463867e-7</v>
       </c>
-      <c r="G509" s="212"/>
-      <c r="H509" s="211"/>
-      <c r="I509" s="213"/>
-      <c r="J509" s="211"/>
-      <c r="K509" s="211"/>
-    </row>
-    <row r="510" ht="13.8" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="215"/>
-      <c r="B510" s="214"/>
-      <c r="C510" s="216"/>
-      <c r="D510" s="214"/>
-      <c r="E510" s="217"/>
-      <c r="F510" s="217"/>
-      <c r="G510" s="218">
-        <f>SUM(G3:G504)</f>
+      <c r="G508" s="212"/>
+      <c r="H508" s="211"/>
+      <c r="I508" s="213"/>
+      <c r="J508" s="211"/>
+      <c r="K508" s="211"/>
+    </row>
+    <row r="509" ht="13.8" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="215"/>
+      <c r="B509" s="214"/>
+      <c r="C509" s="216"/>
+      <c r="D509" s="214"/>
+      <c r="E509" s="217"/>
+      <c r="F509" s="217"/>
+      <c r="G509" s="218">
+        <f>SUM(G3:G503)</f>
         <v>-5.651381798088551e-7</v>
       </c>
-      <c r="H510" s="217"/>
-      <c r="I510" s="219"/>
-      <c r="J510" s="217"/>
-      <c r="K510" s="217"/>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H509" s="217"/>
+      <c r="I509" s="219"/>
+      <c r="J509" s="217"/>
+      <c r="K509" s="217"/>
+    </row>
+    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510" s="76"/>
+      <c r="B510" s="76"/>
+      <c r="C510" s="34"/>
+      <c r="D510" s="132"/>
+      <c r="E510" s="132"/>
+      <c r="F510" s="132"/>
+      <c r="G510" s="132"/>
+    </row>
+    <row r="511" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A511" s="76"/>
       <c r="B511" s="76"/>
       <c r="C511" s="34"/>
@@ -15818,6 +15808,10 @@
       <c r="E511" s="132"/>
       <c r="F511" s="132"/>
       <c r="G511" s="132"/>
+      <c r="H511" s="132"/>
+      <c r="I511" s="134"/>
+      <c r="J511" s="132"/>
+      <c r="K511" s="132"/>
     </row>
     <row r="512" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A512" s="76"/>
@@ -34135,19 +34129,6 @@
       <c r="I1920" s="134"/>
       <c r="J1920" s="132"/>
       <c r="K1920" s="132"/>
-    </row>
-    <row r="1921" spans="1:11" s="76" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1921" s="76"/>
-      <c r="B1921" s="76"/>
-      <c r="C1921" s="34"/>
-      <c r="D1921" s="132"/>
-      <c r="E1921" s="132"/>
-      <c r="F1921" s="132"/>
-      <c r="G1921" s="132"/>
-      <c r="H1921" s="132"/>
-      <c r="I1921" s="134"/>
-      <c r="J1921" s="132"/>
-      <c r="K1921" s="132"/>
     </row>
   </sheetData>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -34179,7 +34160,7 @@
       <c r="C1" s="222"/>
       <c r="D1" s="222"/>
       <c r="E1" s="223" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F1" s="224"/>
       <c r="G1" s="224"/>
@@ -34197,7 +34178,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="195"/>
@@ -34263,7 +34244,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B9" s="151"/>
       <c r="C9" s="195"/>
@@ -34668,7 +34649,7 @@
       <c r="E45" s="220"/>
       <c r="F45" s="220"/>
       <c r="G45" s="226" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H45" s="227" t="s">
         <v>445</v>
@@ -34800,7 +34781,7 @@
       <c r="D56" s="232"/>
       <c r="E56" s="232"/>
       <c r="F56" s="232" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G56" s="232"/>
     </row>
@@ -34824,7 +34805,7 @@
     </row>
     <row r="59" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="72" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="195"/>
@@ -34986,7 +34967,7 @@
     </row>
     <row r="77" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="72" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B77" s="151"/>
       <c r="C77" s="195"/>
@@ -34995,7 +34976,7 @@
     </row>
     <row r="78" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="72" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B78" s="151"/>
       <c r="C78" s="195"/>
@@ -35031,7 +35012,7 @@
     </row>
     <row r="82" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="72" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B82" s="151"/>
       <c r="C82" s="195"/>
@@ -35079,7 +35060,7 @@
     </row>
     <row r="87" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B87" s="151"/>
       <c r="C87" s="195"/>
@@ -35142,7 +35123,7 @@
     </row>
     <row r="94" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="72" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B94" s="151"/>
       <c r="C94" s="195"/>
@@ -35151,7 +35132,7 @@
     </row>
     <row r="95" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="72" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B95" s="151"/>
       <c r="C95" s="195"/>
@@ -35160,7 +35141,7 @@
     </row>
     <row r="96" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="72" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B96" s="151"/>
       <c r="C96" s="195"/>
@@ -35169,7 +35150,7 @@
     </row>
     <row r="97" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="72" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B97" s="151"/>
       <c r="C97" s="195"/>
@@ -35801,6 +35782,12 @@
       <c r="D182" s="225"/>
       <c r="E182" s="195"/>
     </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="220"/>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="220"/>
+    </row>
     <row r="185" hidden="1" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="151" t="s">
         <v>456</v>
@@ -35837,20 +35824,26 @@
       <c r="D188" s="195"/>
       <c r="E188" s="195"/>
     </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="220"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="220"/>
+    </row>
     <row r="191" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="221" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B191" s="233"/>
       <c r="C191" s="233"/>
       <c r="D191" s="233"/>
       <c r="E191" s="223" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="192" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="72" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B192" s="220"/>
       <c r="C192" s="195"/>
@@ -35894,7 +35887,7 @@
     </row>
     <row r="196" spans="1:5" s="234" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="235" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B196" s="236"/>
       <c r="C196" s="41"/>
@@ -35905,7 +35898,7 @@
     </row>
     <row r="197" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="72" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B197" s="151"/>
       <c r="C197" s="195"/>
@@ -35916,7 +35909,7 @@
     </row>
     <row r="198" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="72" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B198" s="151"/>
       <c r="C198" s="195"/>
@@ -35938,7 +35931,7 @@
     </row>
     <row r="200" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="72" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B200" s="151"/>
       <c r="C200" s="195"/>
@@ -35960,7 +35953,7 @@
     </row>
     <row r="202" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="72" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B202" s="151"/>
       <c r="C202" s="195"/>
@@ -35971,7 +35964,7 @@
     </row>
     <row r="203" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="72" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B203" s="151"/>
       <c r="C203" s="195"/>
@@ -35982,7 +35975,7 @@
     </row>
     <row r="204" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="72" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B204" s="151"/>
       <c r="C204" s="195"/>
@@ -35993,7 +35986,7 @@
     </row>
     <row r="205" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="72" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B205" s="151"/>
       <c r="C205" s="195"/>
@@ -36004,7 +35997,7 @@
     </row>
     <row r="206" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="72" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B206" s="151"/>
       <c r="C206" s="195"/>
@@ -36015,7 +36008,7 @@
     </row>
     <row r="207" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="72" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B207" s="151"/>
       <c r="C207" s="195"/>
@@ -36026,7 +36019,7 @@
     </row>
     <row r="208" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="72" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B208" s="151"/>
       <c r="C208" s="195"/>
@@ -36037,7 +36030,7 @@
     </row>
     <row r="209" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="72" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B209" s="151"/>
       <c r="C209" s="195"/>
@@ -36049,7 +36042,7 @@
     </row>
     <row r="210" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="72" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B210" s="151"/>
       <c r="C210" s="195"/>
@@ -36072,7 +36065,7 @@
     </row>
     <row r="212" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="72" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B212" s="151"/>
       <c r="C212" s="195"/>
@@ -36083,7 +36076,7 @@
     </row>
     <row r="213" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="72" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B213" s="151"/>
       <c r="C213" s="195"/>
@@ -36094,7 +36087,7 @@
     </row>
     <row r="214" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="72" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B214" s="151"/>
       <c r="C214" s="195"/>
@@ -36105,7 +36098,7 @@
     </row>
     <row r="215" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="72" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B215" s="151"/>
       <c r="C215" s="195"/>
@@ -36116,7 +36109,7 @@
     </row>
     <row r="216" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="72" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B216" s="151"/>
       <c r="C216" s="195"/>
@@ -36138,7 +36131,7 @@
     </row>
     <row r="218" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="72" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B218" s="151"/>
       <c r="C218" s="195"/>
@@ -36149,7 +36142,7 @@
     </row>
     <row r="219" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="72" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B219" s="151"/>
       <c r="C219" s="195"/>
@@ -36160,7 +36153,7 @@
     </row>
     <row r="220" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="72" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B220" s="151"/>
       <c r="C220" s="195"/>
@@ -36171,7 +36164,7 @@
     </row>
     <row r="221" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="72" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B221" s="151"/>
       <c r="C221" s="195"/>
@@ -36182,7 +36175,7 @@
     </row>
     <row r="222" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="72" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B222" s="151"/>
       <c r="C222" s="195"/>
@@ -36215,7 +36208,7 @@
     </row>
     <row r="225" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="72" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B225" s="151"/>
       <c r="C225" s="195"/>
@@ -36226,7 +36219,7 @@
     </row>
     <row r="226" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="72" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B226" s="151"/>
       <c r="C226" s="195"/>
@@ -36237,7 +36230,7 @@
     </row>
     <row r="227" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="72" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B227" s="151"/>
       <c r="C227" s="195"/>
@@ -36248,7 +36241,7 @@
     </row>
     <row r="228" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="72" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B228" s="151"/>
       <c r="C228" s="195"/>
@@ -36259,7 +36252,7 @@
     </row>
     <row r="229" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="72" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B229" s="151"/>
       <c r="C229" s="195"/>
@@ -36270,7 +36263,7 @@
     </row>
     <row r="230" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="72" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B230" s="151"/>
       <c r="C230" s="195"/>
@@ -36303,7 +36296,7 @@
     </row>
     <row r="233" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="72" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B233" s="151"/>
       <c r="C233" s="195"/>
@@ -36314,7 +36307,7 @@
     </row>
     <row r="234" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="72" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B234" s="151"/>
       <c r="C234" s="195"/>
@@ -36325,7 +36318,7 @@
     </row>
     <row r="235" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="72" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B235" s="151"/>
       <c r="C235" s="195"/>
@@ -36336,7 +36329,7 @@
     </row>
     <row r="236" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="72" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B236" s="151"/>
       <c r="C236" s="195"/>
@@ -36347,7 +36340,7 @@
     </row>
     <row r="237" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="72" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B237" s="151"/>
       <c r="C237" s="195"/>
@@ -36369,7 +36362,7 @@
     </row>
     <row r="239" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="72" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B239" s="151"/>
       <c r="C239" s="195"/>
@@ -36380,7 +36373,7 @@
     </row>
     <row r="240" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="72" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B240" s="151"/>
       <c r="C240" s="195"/>
@@ -36391,7 +36384,7 @@
     </row>
     <row r="241" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="72" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B241" s="151"/>
       <c r="C241" s="195"/>
@@ -36402,7 +36395,7 @@
     </row>
     <row r="242" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="72" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B242" s="151"/>
       <c r="C242" s="195"/>
@@ -36424,7 +36417,7 @@
     </row>
     <row r="244" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="72" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B244" s="151"/>
       <c r="C244" s="195"/>
@@ -36435,7 +36428,7 @@
     </row>
     <row r="245" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="72" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B245" s="151"/>
       <c r="C245" s="195"/>
@@ -36446,7 +36439,7 @@
     </row>
     <row r="246" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="72" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B246" s="151"/>
       <c r="C246" s="195"/>
@@ -36457,7 +36450,7 @@
     </row>
     <row r="247" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="72" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B247" s="151"/>
       <c r="C247" s="195"/>
@@ -36468,7 +36461,7 @@
     </row>
     <row r="248" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="72" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B248" s="151"/>
       <c r="C248" s="195"/>
@@ -36479,7 +36472,7 @@
     </row>
     <row r="249" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="72" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B249" s="151"/>
       <c r="C249" s="195"/>
@@ -36490,7 +36483,7 @@
     </row>
     <row r="250" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="72" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B250" s="151"/>
       <c r="C250" s="195"/>
@@ -36501,7 +36494,7 @@
     </row>
     <row r="251" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="72" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B251" s="151"/>
       <c r="C251" s="195"/>
@@ -36512,7 +36505,7 @@
     </row>
     <row r="252" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="72" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B252" s="151"/>
       <c r="C252" s="195"/>
@@ -36523,7 +36516,7 @@
     </row>
     <row r="253" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="72" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B253" s="151"/>
       <c r="C253" s="195"/>
@@ -36534,7 +36527,7 @@
     </row>
     <row r="254" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="72" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B254" s="151"/>
       <c r="C254" s="195"/>
@@ -36545,7 +36538,7 @@
     </row>
     <row r="255" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="72" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B255" s="151"/>
       <c r="C255" s="195"/>
@@ -36578,7 +36571,7 @@
     </row>
     <row r="258" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="72" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B258" s="151"/>
       <c r="C258" s="195"/>
@@ -36589,7 +36582,7 @@
     </row>
     <row r="259" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="72" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B259" s="151"/>
       <c r="C259" s="195"/>
@@ -36600,7 +36593,7 @@
     </row>
     <row r="260" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="72" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B260" s="151"/>
       <c r="C260" s="195"/>
@@ -36611,7 +36604,7 @@
     </row>
     <row r="261" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="72" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B261" s="151"/>
       <c r="C261" s="195"/>
@@ -36622,7 +36615,7 @@
     </row>
     <row r="262" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="72" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B262" s="151"/>
       <c r="C262" s="195"/>
@@ -36633,7 +36626,7 @@
     </row>
     <row r="263" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="72" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B263" s="151"/>
       <c r="C263" s="195"/>
@@ -36655,7 +36648,7 @@
     </row>
     <row r="265" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="72" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B265" s="151"/>
       <c r="C265" s="195"/>
@@ -36666,7 +36659,7 @@
     </row>
     <row r="266" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="72" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B266" s="151"/>
       <c r="C266" s="195"/>
@@ -36677,7 +36670,7 @@
     </row>
     <row r="267" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="72" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B267" s="151"/>
       <c r="C267" s="195"/>
@@ -36688,7 +36681,7 @@
     </row>
     <row r="268" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="72" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B268" s="151"/>
       <c r="C268" s="195"/>
@@ -36699,7 +36692,7 @@
     </row>
     <row r="269" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="72" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B269" s="151"/>
       <c r="C269" s="195"/>
@@ -36710,7 +36703,7 @@
     </row>
     <row r="270" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="72" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B270" s="151"/>
       <c r="C270" s="195"/>
@@ -36721,7 +36714,7 @@
     </row>
     <row r="271" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="72" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B271" s="151"/>
       <c r="C271" s="195"/>
@@ -36732,7 +36725,7 @@
     </row>
     <row r="272" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="72" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B272" s="151"/>
       <c r="C272" s="195"/>
@@ -36743,7 +36736,7 @@
     </row>
     <row r="273" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="72" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B273" s="151"/>
       <c r="C273" s="195"/>
@@ -36754,7 +36747,7 @@
     </row>
     <row r="274" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="72" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B274" s="151"/>
       <c r="C274" s="195"/>
@@ -36765,7 +36758,7 @@
     </row>
     <row r="275" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="72" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B275" s="151"/>
       <c r="C275" s="195"/>
@@ -36776,7 +36769,7 @@
     </row>
     <row r="276" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="72" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B276" s="151"/>
       <c r="C276" s="195"/>
@@ -36787,7 +36780,7 @@
     </row>
     <row r="277" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="72" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B277" s="151"/>
       <c r="C277" s="195"/>
@@ -36798,7 +36791,7 @@
     </row>
     <row r="278" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="72" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B278" s="151"/>
       <c r="C278" s="195"/>
@@ -36809,7 +36802,7 @@
     </row>
     <row r="279" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="72" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B279" s="151"/>
       <c r="C279" s="195"/>
@@ -36831,7 +36824,7 @@
     </row>
     <row r="281" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="72" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="195"/>
@@ -36842,7 +36835,7 @@
     </row>
     <row r="282" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="72" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B282" s="151"/>
       <c r="C282" s="195"/>
@@ -36853,7 +36846,7 @@
     </row>
     <row r="283" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="72" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B283" s="151"/>
       <c r="C283" s="195"/>
@@ -36864,7 +36857,7 @@
     </row>
     <row r="284" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="72" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B284" s="151"/>
       <c r="C284" s="195"/>
@@ -36875,7 +36868,7 @@
     </row>
     <row r="285" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="72" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B285" s="151"/>
       <c r="C285" s="195"/>
@@ -36897,7 +36890,7 @@
     </row>
     <row r="287" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="72" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B287" s="151"/>
       <c r="C287" s="195"/>
@@ -36908,7 +36901,7 @@
     </row>
     <row r="288" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="72" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B288" s="151"/>
       <c r="C288" s="195"/>
@@ -36919,7 +36912,7 @@
     </row>
     <row r="289" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="72" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B289" s="151"/>
       <c r="C289" s="195"/>
@@ -36930,7 +36923,7 @@
     </row>
     <row r="290" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="72" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B290" s="151"/>
       <c r="C290" s="195"/>
@@ -36941,7 +36934,7 @@
     </row>
     <row r="291" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="72" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B291" s="151"/>
       <c r="C291" s="195"/>
@@ -36952,7 +36945,7 @@
     </row>
     <row r="292" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="72" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B292" s="151"/>
       <c r="C292" s="195"/>
@@ -36964,7 +36957,7 @@
     </row>
     <row r="293" spans="1:6" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="72" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B293" s="151"/>
       <c r="C293" s="195"/>
@@ -36988,7 +36981,7 @@
     </row>
     <row r="295" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="72" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B295" s="151"/>
       <c r="C295" s="195"/>
@@ -36999,7 +36992,7 @@
     </row>
     <row r="296" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="72" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B296" s="151"/>
       <c r="C296" s="195"/>
@@ -37010,7 +37003,7 @@
     </row>
     <row r="297" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="72" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B297" s="151"/>
       <c r="C297" s="195"/>
@@ -37021,7 +37014,7 @@
     </row>
     <row r="298" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="72" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B298" s="151"/>
       <c r="C298" s="195"/>
@@ -37032,7 +37025,7 @@
     </row>
     <row r="299" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="72" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B299" s="151"/>
       <c r="C299" s="195"/>
@@ -37043,7 +37036,7 @@
     </row>
     <row r="300" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="72" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B300" s="151"/>
       <c r="C300" s="195"/>
@@ -37054,7 +37047,7 @@
     </row>
     <row r="301" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="72" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B301" s="151"/>
       <c r="C301" s="195"/>
@@ -37065,7 +37058,7 @@
     </row>
     <row r="302" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A302" s="72" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B302" s="151"/>
       <c r="C302" s="195"/>
@@ -37076,7 +37069,7 @@
     </row>
     <row r="303" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A303" s="72" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B303" s="151"/>
       <c r="C303" s="195"/>
@@ -37087,7 +37080,7 @@
     </row>
     <row r="304" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A304" s="72" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B304" s="151"/>
       <c r="C304" s="195"/>
@@ -37098,7 +37091,7 @@
     </row>
     <row r="305" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A305" s="72" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B305" s="151"/>
       <c r="C305" s="195"/>
@@ -37109,7 +37102,7 @@
     </row>
     <row r="306" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A306" s="72" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B306" s="151"/>
       <c r="C306" s="195"/>
@@ -37120,7 +37113,7 @@
     </row>
     <row r="307" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A307" s="72" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B307" s="151"/>
       <c r="C307" s="195"/>
@@ -37142,7 +37135,7 @@
     </row>
     <row r="309" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A309" s="151" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B309" s="151"/>
       <c r="C309" s="195"/>
@@ -37153,7 +37146,7 @@
     </row>
     <row r="310" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A310" s="151" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B310" s="151"/>
       <c r="C310" s="195"/>
@@ -37164,7 +37157,7 @@
     </row>
     <row r="311" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A311" s="151" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B311" s="151"/>
       <c r="C311" s="195"/>
@@ -37186,7 +37179,7 @@
     </row>
     <row r="313" spans="1:5" s="220" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A313" s="151" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B313" s="151"/>
       <c r="C313" s="195"/>
@@ -37197,7 +37190,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="72" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B314" s="151"/>
       <c r="C314" s="195"/>
@@ -37208,7 +37201,7 @@
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" s="72" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B315" s="151"/>
       <c r="C315" s="195"/>
@@ -37235,10 +37228,10 @@
       <c r="D317" s="225"/>
       <c r="E317" s="195"/>
       <c r="F317" s="238" t="s">
+        <v>867</v>
+      </c>
+      <c r="G317" s="239" t="s">
         <v>868</v>
-      </c>
-      <c r="G317" s="239" t="s">
-        <v>869</v>
       </c>
     </row>
     <row r="318" ht="10.2" customHeight="1" spans="1:7" s="235" customFormat="1" x14ac:dyDescent="0.25">
@@ -37463,7 +37456,7 @@
         <v>0</v>
       </c>
       <c r="H345" s="72" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.25">
@@ -37493,7 +37486,7 @@
       <c r="F347" s="220"/>
       <c r="G347" s="225"/>
       <c r="H347" s="72" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
@@ -37511,10 +37504,10 @@
       <c r="E349" s="140"/>
       <c r="F349" s="220"/>
       <c r="G349" s="244" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H349" s="245" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.25">
@@ -39816,7 +39809,7 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="18">
-        <f>-SALDOS!G281-SALDOS!G149</f>
+        <f>-SALDOS!G280-SALDOS!G149</f>
         <v>-62810190.49</v>
       </c>
       <c r="D17" s="19"/>
@@ -39838,7 +39831,7 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="18">
-        <f>-SALDOS!G484</f>
+        <f>-SALDOS!G483</f>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="870">
   <si>
     <t>ESTADO DE SITUACION PATRIMONIAL</t>
   </si>
@@ -413,9 +413,6 @@
     <t>Otros Activos</t>
   </si>
   <si>
-    <t>- Socios</t>
-  </si>
-  <si>
     <t>Activo No Corriente</t>
   </si>
   <si>
@@ -1353,9 +1350,6 @@
   </si>
   <si>
     <t>212020002 - Retenciones SUSS a pagar</t>
-  </si>
-  <si>
-    <t>21409000 - Retenciones SUSS a pagar</t>
   </si>
   <si>
     <t>21504000 - Cheques emitidos en cartera</t>
@@ -4397,7 +4391,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4410,7 +4404,7 @@
     </row>
     <row r="3" ht="11.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4420,7 +4414,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" ht="11.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4443,22 +4437,22 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="F6" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="G6" s="48" t="s">
         <v>196</v>
       </c>
-      <c r="G6" s="48" t="s">
-        <v>197</v>
-      </c>
       <c r="H6" s="48" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I6" s="115" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J6" s="116" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4466,25 +4460,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="55" t="s">
         <v>199</v>
       </c>
-      <c r="F7" s="55" t="s">
-        <v>200</v>
-      </c>
       <c r="G7" s="55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H7" s="55" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I7" s="117"/>
       <c r="J7" s="118" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4497,19 +4491,19 @@
         <v>NaN</v>
       </c>
       <c r="F8" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="G8" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="H8" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="I8" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="J8" s="122" t="s">
         <v>204</v>
-      </c>
-      <c r="J8" s="122" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="9" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4526,10 +4520,10 @@
     </row>
     <row r="10" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="71" t="s">
         <v>206</v>
-      </c>
-      <c r="B10" s="71" t="s">
-        <v>207</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4548,10 +4542,10 @@
     </row>
     <row r="11" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -4570,10 +4564,10 @@
     </row>
     <row r="12" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4592,10 +4586,10 @@
     </row>
     <row r="13" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4614,10 +4608,10 @@
     </row>
     <row r="14" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4636,10 +4630,10 @@
     </row>
     <row r="15" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -4658,10 +4652,10 @@
     </row>
     <row r="16" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -4680,10 +4674,10 @@
     </row>
     <row r="17" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -4702,10 +4696,10 @@
     </row>
     <row r="18" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -4724,10 +4718,10 @@
     </row>
     <row r="19" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -4746,10 +4740,10 @@
     </row>
     <row r="20" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -4768,10 +4762,10 @@
     </row>
     <row r="21" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -4793,10 +4787,10 @@
     </row>
     <row r="22" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -4815,10 +4809,10 @@
     </row>
     <row r="23" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -4834,10 +4828,10 @@
     </row>
     <row r="24" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -4856,10 +4850,10 @@
     </row>
     <row r="25" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B25" s="71" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -4878,10 +4872,10 @@
     </row>
     <row r="26" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -4900,10 +4894,10 @@
     </row>
     <row r="27" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B27" s="71" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -4919,10 +4913,10 @@
     </row>
     <row r="28" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4941,10 +4935,10 @@
     </row>
     <row r="29" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B29" s="71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -4960,10 +4954,10 @@
     </row>
     <row r="30" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B30" s="71" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -4982,10 +4976,10 @@
     </row>
     <row r="31" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B31" s="71" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -5004,10 +4998,10 @@
     </row>
     <row r="32" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B32" s="71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -5026,10 +5020,10 @@
     </row>
     <row r="33" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B33" s="71" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -5048,10 +5042,10 @@
     </row>
     <row r="34" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B34" s="71" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -5070,10 +5064,10 @@
     </row>
     <row r="35" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -5092,10 +5086,10 @@
     </row>
     <row r="36" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -5117,10 +5111,10 @@
     </row>
     <row r="37" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B37" s="71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -5139,10 +5133,10 @@
     </row>
     <row r="38" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B38" s="71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -5161,10 +5155,10 @@
     </row>
     <row r="39" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B39" s="71" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -5183,10 +5177,10 @@
     </row>
     <row r="40" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -5205,10 +5199,10 @@
     </row>
     <row r="41" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -5227,10 +5221,10 @@
     </row>
     <row r="42" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -5249,10 +5243,10 @@
     </row>
     <row r="43" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -5271,10 +5265,10 @@
     </row>
     <row r="44" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -5293,10 +5287,10 @@
     </row>
     <row r="45" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -5315,10 +5309,10 @@
     </row>
     <row r="46" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -5337,10 +5331,10 @@
     </row>
     <row r="47" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -5359,10 +5353,10 @@
     </row>
     <row r="48" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -5381,10 +5375,10 @@
     </row>
     <row r="49" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -5403,10 +5397,10 @@
     </row>
     <row r="50" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B50" s="71" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -5425,10 +5419,10 @@
     </row>
     <row r="51" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B51" s="71" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -5447,10 +5441,10 @@
     </row>
     <row r="52" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B52" s="71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -5472,10 +5466,10 @@
     </row>
     <row r="53" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B53" s="71" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -5494,10 +5488,10 @@
     </row>
     <row r="54" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B54" s="71" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -5516,10 +5510,10 @@
     </row>
     <row r="55" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -5538,10 +5532,10 @@
     </row>
     <row r="56" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -5560,10 +5554,10 @@
     </row>
     <row r="57" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -5582,10 +5576,10 @@
     </row>
     <row r="58" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -5604,10 +5598,10 @@
     </row>
     <row r="59" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -5626,10 +5620,10 @@
     </row>
     <row r="60" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B60" s="71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -5648,10 +5642,10 @@
     </row>
     <row r="61" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B61" s="71" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -5670,10 +5664,10 @@
     </row>
     <row r="62" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B62" s="71" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -5692,10 +5686,10 @@
     </row>
     <row r="63" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B63" s="71" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -5717,10 +5711,10 @@
     </row>
     <row r="64" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B64" s="71" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -5739,10 +5733,10 @@
     </row>
     <row r="65" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B65" s="71" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -5761,10 +5755,10 @@
     </row>
     <row r="66" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B66" s="71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -5780,10 +5774,10 @@
     </row>
     <row r="67" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B67" s="71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -5802,10 +5796,10 @@
     </row>
     <row r="68" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B68" s="71" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -5821,10 +5815,10 @@
     </row>
     <row r="69" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B69" s="71" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -5843,10 +5837,10 @@
     </row>
     <row r="70" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B70" s="71" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -5862,10 +5856,10 @@
     </row>
     <row r="71" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B71" s="71" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -5884,10 +5878,10 @@
     </row>
     <row r="72" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B72" s="71" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -5906,10 +5900,10 @@
     </row>
     <row r="73" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -5928,10 +5922,10 @@
     </row>
     <row r="74" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -5950,10 +5944,10 @@
     </row>
     <row r="75" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -5972,10 +5966,10 @@
     </row>
     <row r="76" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B76" s="71" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -5994,10 +5988,10 @@
     </row>
     <row r="77" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B77" s="71" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -6016,10 +6010,10 @@
     </row>
     <row r="78" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B78" s="71" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -6038,10 +6032,10 @@
     </row>
     <row r="79" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B79" s="71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -6060,10 +6054,10 @@
     </row>
     <row r="80" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B80" s="71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -6082,10 +6076,10 @@
     </row>
     <row r="81" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B81" s="71" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -6107,10 +6101,10 @@
     </row>
     <row r="82" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B82" s="71" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -6132,10 +6126,10 @@
     </row>
     <row r="83" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B83" s="71" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -6156,10 +6150,10 @@
     </row>
     <row r="84" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B84" s="71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -6178,10 +6172,10 @@
     </row>
     <row r="85" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B85" s="71" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -6200,10 +6194,10 @@
     </row>
     <row r="86" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B86" s="71" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -6222,10 +6216,10 @@
     </row>
     <row r="87" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B87" s="71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -6244,10 +6238,10 @@
     </row>
     <row r="88" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B88" s="71" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -6266,10 +6260,10 @@
     </row>
     <row r="89" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B89" s="71" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -6288,10 +6282,10 @@
     </row>
     <row r="90" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B90" s="71" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -6310,10 +6304,10 @@
     </row>
     <row r="91" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B91" s="71" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -6332,10 +6326,10 @@
     </row>
     <row r="92" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B92" s="71" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -6352,7 +6346,7 @@
     <row r="93" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="7"/>
       <c r="B93" s="71" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -6371,10 +6365,10 @@
     </row>
     <row r="94" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B94" s="71" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -6393,10 +6387,10 @@
     </row>
     <row r="95" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B95" s="71" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -6415,10 +6409,10 @@
     </row>
     <row r="96" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B96" s="71" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -6437,10 +6431,10 @@
     </row>
     <row r="97" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B97" s="71" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -6459,10 +6453,10 @@
     </row>
     <row r="98" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B98" s="71" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -6481,10 +6475,10 @@
     </row>
     <row r="99" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B99" s="71" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -6503,10 +6497,10 @@
     </row>
     <row r="100" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B100" s="71" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
@@ -6525,10 +6519,10 @@
     </row>
     <row r="101" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B101" s="71" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -6547,10 +6541,10 @@
     </row>
     <row r="102" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
@@ -6749,13 +6743,13 @@
       <c r="I1" s="77"/>
       <c r="J1" s="77"/>
       <c r="K1" s="78" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="13.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="80"/>
       <c r="C4" s="80"/>
@@ -6770,7 +6764,7 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="82" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B5" s="78"/>
       <c r="C5" s="78"/>
@@ -6818,13 +6812,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="90" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C8" s="90"/>
       <c r="D8" s="90"/>
       <c r="E8" s="90"/>
       <c r="F8" s="90" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G8" s="90"/>
       <c r="H8" s="90"/>
@@ -6835,26 +6829,26 @@
     <row r="9" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="92"/>
       <c r="B9" s="93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C9" s="93"/>
       <c r="D9" s="93"/>
       <c r="E9" s="93" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="93" t="s">
         <v>166</v>
-      </c>
-      <c r="F9" s="93" t="s">
-        <v>167</v>
       </c>
       <c r="G9" s="93"/>
       <c r="H9" s="94" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I9" s="95"/>
       <c r="J9" s="93" t="s">
+        <v>168</v>
+      </c>
+      <c r="K9" s="96" t="s">
         <v>169</v>
-      </c>
-      <c r="K9" s="96" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6862,59 +6856,59 @@
         <v>51</v>
       </c>
       <c r="B10" s="93" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="93" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="93" t="s">
+      <c r="D10" s="93" t="s">
         <v>172</v>
       </c>
-      <c r="D10" s="93" t="s">
+      <c r="E10" s="93" t="s">
         <v>173</v>
       </c>
-      <c r="E10" s="93" t="s">
+      <c r="F10" s="93" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="93" t="s">
+      <c r="G10" s="93" t="s">
         <v>175</v>
       </c>
-      <c r="G10" s="93" t="s">
+      <c r="H10" s="93" t="s">
         <v>176</v>
       </c>
-      <c r="H10" s="93" t="s">
+      <c r="I10" s="93" t="s">
         <v>177</v>
       </c>
-      <c r="I10" s="93" t="s">
+      <c r="J10" s="93" t="s">
         <v>178</v>
       </c>
-      <c r="J10" s="93" t="s">
+      <c r="K10" s="96" t="s">
         <v>179</v>
-      </c>
-      <c r="K10" s="96" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="92"/>
       <c r="B11" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C11" s="93"/>
       <c r="D11" s="93"/>
       <c r="E11" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F11" s="93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G11" s="93"/>
       <c r="H11" s="93"/>
       <c r="I11" s="93" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J11" s="93" t="s">
+        <v>180</v>
+      </c>
+      <c r="K11" s="96" t="s">
         <v>181</v>
-      </c>
-      <c r="K11" s="96" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6976,7 +6970,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="103" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B15" s="104">
         <v>7137147.140000001</v>
@@ -7021,7 +7015,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="103" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B16" s="104">
         <v>9983623.870000001</v>
@@ -7066,7 +7060,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="103" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B17" s="104">
         <v>2163642.25</v>
@@ -7111,7 +7105,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="103" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B18" s="104">
         <v>1676263.99</v>
@@ -7155,7 +7149,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="103" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B19" s="104">
         <v>5362126.44</v>
@@ -7199,7 +7193,7 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="103" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B20" s="104">
         <v>5117083.33</v>
@@ -7243,7 +7237,7 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="103" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B21" s="105">
         <v>20790195.080000002</v>
@@ -7288,7 +7282,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="103" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B22" s="104">
         <v>1598074.09</v>
@@ -7347,7 +7341,7 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="98" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B24" s="110">
         <f>SUM(B15:B23)</f>
@@ -7579,21 +7573,21 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="135" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="135" t="s">
         <v>298</v>
       </c>
-      <c r="B1" s="135" t="s">
+      <c r="C1" s="71" t="s">
         <v>299</v>
       </c>
-      <c r="C1" s="71" t="s">
+      <c r="D1" s="135" t="s">
         <v>300</v>
-      </c>
-      <c r="D1" s="135" t="s">
-        <v>301</v>
       </c>
       <c r="E1" s="135"/>
       <c r="F1" s="135"/>
       <c r="G1" s="136" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7611,10 +7605,10 @@
       <c r="A3" s="137"/>
       <c r="B3" s="137"/>
       <c r="C3" s="139" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E3" s="68"/>
       <c r="F3" s="140"/>
@@ -7627,10 +7621,10 @@
       <c r="A4" s="137"/>
       <c r="B4" s="137"/>
       <c r="C4" s="139" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D4" s="139" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E4" s="72"/>
       <c r="F4" s="140"/>
@@ -7643,10 +7637,10 @@
       <c r="A5" s="137"/>
       <c r="B5" s="137"/>
       <c r="C5" s="139" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" s="68"/>
       <c r="F5" s="140"/>
@@ -7659,10 +7653,10 @@
       <c r="A6" s="137"/>
       <c r="B6" s="137"/>
       <c r="C6" s="139" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="139" t="s">
         <v>306</v>
-      </c>
-      <c r="D6" s="139" t="s">
-        <v>307</v>
       </c>
       <c r="E6" s="68"/>
       <c r="F6" s="140"/>
@@ -7676,10 +7670,10 @@
       <c r="A7" s="137"/>
       <c r="B7" s="137"/>
       <c r="C7" s="72" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D7" s="139" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E7" s="68"/>
       <c r="F7" s="140"/>
@@ -7693,10 +7687,10 @@
       <c r="A8" s="137"/>
       <c r="B8" s="137"/>
       <c r="C8" s="139" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E8" s="68"/>
       <c r="F8" s="140"/>
@@ -7710,10 +7704,10 @@
       <c r="A9" s="137"/>
       <c r="B9" s="137"/>
       <c r="C9" s="139" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" s="139" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E9" s="68"/>
       <c r="F9" s="140"/>
@@ -7727,10 +7721,10 @@
       <c r="A10" s="137"/>
       <c r="B10" s="137"/>
       <c r="C10" s="139" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E10" s="68"/>
       <c r="F10" s="140"/>
@@ -7743,10 +7737,10 @@
       <c r="A11" s="137"/>
       <c r="B11" s="137"/>
       <c r="C11" s="139" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D11" s="139" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E11" s="71"/>
       <c r="F11" s="140"/>
@@ -7759,10 +7753,10 @@
       <c r="A12" s="137"/>
       <c r="B12" s="137"/>
       <c r="C12" s="139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D12" s="139" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E12" s="71"/>
       <c r="F12" s="140"/>
@@ -7787,10 +7781,10 @@
       <c r="A14" s="145"/>
       <c r="B14" s="145"/>
       <c r="C14" s="146" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D14" s="147" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E14" s="147"/>
       <c r="F14" s="140"/>
@@ -7807,10 +7801,10 @@
       <c r="A15" s="137"/>
       <c r="B15" s="137"/>
       <c r="C15" s="139" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E15" s="68"/>
       <c r="F15" s="140"/>
@@ -7823,10 +7817,10 @@
       <c r="A16" s="137"/>
       <c r="B16" s="137"/>
       <c r="C16" s="139" t="s">
+        <v>315</v>
+      </c>
+      <c r="D16" s="71" t="s">
         <v>316</v>
-      </c>
-      <c r="D16" s="71" t="s">
-        <v>317</v>
       </c>
       <c r="E16" s="68"/>
       <c r="F16" s="140"/>
@@ -7839,10 +7833,10 @@
       <c r="A17" s="137"/>
       <c r="B17" s="137"/>
       <c r="C17" s="139" t="s">
+        <v>317</v>
+      </c>
+      <c r="D17" s="71" t="s">
         <v>318</v>
-      </c>
-      <c r="D17" s="71" t="s">
-        <v>319</v>
       </c>
       <c r="E17" s="71"/>
       <c r="F17" s="140"/>
@@ -7856,10 +7850,10 @@
       <c r="A18" s="137"/>
       <c r="B18" s="137"/>
       <c r="C18" s="139" t="s">
+        <v>319</v>
+      </c>
+      <c r="D18" s="71" t="s">
         <v>320</v>
-      </c>
-      <c r="D18" s="71" t="s">
-        <v>321</v>
       </c>
       <c r="E18" s="68"/>
       <c r="F18" s="140"/>
@@ -7872,10 +7866,10 @@
       <c r="A19" s="137"/>
       <c r="B19" s="137"/>
       <c r="C19" s="139" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E19" s="68"/>
       <c r="F19" s="140"/>
@@ -7888,10 +7882,10 @@
       <c r="A20" s="137"/>
       <c r="B20" s="137"/>
       <c r="C20" s="139" t="s">
+        <v>322</v>
+      </c>
+      <c r="D20" s="71" t="s">
         <v>323</v>
-      </c>
-      <c r="D20" s="71" t="s">
-        <v>324</v>
       </c>
       <c r="E20" s="68"/>
       <c r="F20" s="140"/>
@@ -7904,10 +7898,10 @@
       <c r="A21" s="137"/>
       <c r="B21" s="137"/>
       <c r="C21" s="151" t="s">
+        <v>324</v>
+      </c>
+      <c r="D21" s="71" t="s">
         <v>325</v>
-      </c>
-      <c r="D21" s="71" t="s">
-        <v>326</v>
       </c>
       <c r="E21" s="71"/>
       <c r="F21" s="140"/>
@@ -7920,10 +7914,10 @@
       <c r="A22" s="137"/>
       <c r="B22" s="137"/>
       <c r="C22" s="139" t="s">
+        <v>326</v>
+      </c>
+      <c r="D22" s="71" t="s">
         <v>327</v>
-      </c>
-      <c r="D22" s="71" t="s">
-        <v>328</v>
       </c>
       <c r="E22" s="68"/>
       <c r="F22" s="140"/>
@@ -7936,10 +7930,10 @@
       <c r="A23" s="137"/>
       <c r="B23" s="137"/>
       <c r="C23" s="72" t="s">
+        <v>328</v>
+      </c>
+      <c r="D23" s="71" t="s">
         <v>329</v>
-      </c>
-      <c r="D23" s="71" t="s">
-        <v>330</v>
       </c>
       <c r="E23" s="68"/>
       <c r="F23" s="140"/>
@@ -7952,10 +7946,10 @@
       <c r="A24" s="137"/>
       <c r="B24" s="137"/>
       <c r="C24" s="139" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D24" s="71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E24" s="68"/>
       <c r="F24" s="140"/>
@@ -7968,10 +7962,10 @@
       <c r="A25" s="137"/>
       <c r="B25" s="137"/>
       <c r="C25" s="139" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D25" s="139" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E25" s="71"/>
       <c r="F25" s="140"/>
@@ -7984,10 +7978,10 @@
       <c r="A26" s="137"/>
       <c r="B26" s="137"/>
       <c r="C26" s="72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D26" s="139" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E26" s="71"/>
       <c r="F26" s="140"/>
@@ -8000,10 +7994,10 @@
       <c r="A27" s="137"/>
       <c r="B27" s="137"/>
       <c r="C27" s="139" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D27" s="139" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="140"/>
@@ -8016,10 +8010,10 @@
       <c r="A28" s="137"/>
       <c r="B28" s="137"/>
       <c r="C28" s="139" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D28" s="71" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="140"/>
@@ -8032,10 +8026,10 @@
       <c r="A29" s="137"/>
       <c r="B29" s="137"/>
       <c r="C29" s="151" t="s">
+        <v>335</v>
+      </c>
+      <c r="D29" s="71" t="s">
         <v>336</v>
-      </c>
-      <c r="D29" s="71" t="s">
-        <v>337</v>
       </c>
       <c r="E29" s="68"/>
       <c r="F29" s="140"/>
@@ -8048,10 +8042,10 @@
       <c r="A30" s="137"/>
       <c r="B30" s="137"/>
       <c r="C30" s="151" t="s">
+        <v>337</v>
+      </c>
+      <c r="D30" s="71" t="s">
         <v>338</v>
-      </c>
-      <c r="D30" s="71" t="s">
-        <v>339</v>
       </c>
       <c r="E30" s="150"/>
       <c r="F30" s="140"/>
@@ -8064,10 +8058,10 @@
       <c r="A31" s="137"/>
       <c r="B31" s="137"/>
       <c r="C31" s="139" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D31" s="139" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E31" s="68"/>
       <c r="F31" s="140"/>
@@ -8080,10 +8074,10 @@
       <c r="A32" s="137"/>
       <c r="B32" s="137"/>
       <c r="C32" s="139" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D32" s="139" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E32" s="68"/>
       <c r="F32" s="140"/>
@@ -8097,10 +8091,10 @@
       <c r="A33" s="137"/>
       <c r="B33" s="137"/>
       <c r="C33" s="139" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D33" s="139" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E33" s="72"/>
       <c r="F33" s="140"/>
@@ -8113,10 +8107,10 @@
       <c r="A34" s="137"/>
       <c r="B34" s="137"/>
       <c r="C34" s="139" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D34" s="71" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E34" s="71"/>
       <c r="F34" s="140"/>
@@ -8129,10 +8123,10 @@
       <c r="A35" s="137"/>
       <c r="B35" s="137"/>
       <c r="C35" s="139" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D35" s="71" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E35" s="71"/>
       <c r="F35" s="140"/>
@@ -8145,10 +8139,10 @@
       <c r="A36" s="137"/>
       <c r="B36" s="137"/>
       <c r="C36" s="139" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D36" s="139" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E36" s="72"/>
       <c r="F36" s="140"/>
@@ -8161,10 +8155,10 @@
       <c r="A37" s="137"/>
       <c r="B37" s="137"/>
       <c r="C37" s="139" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D37" s="139" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E37" s="68"/>
       <c r="F37" s="140"/>
@@ -8177,10 +8171,10 @@
       <c r="A38" s="137"/>
       <c r="B38" s="137"/>
       <c r="C38" s="139" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D38" s="139" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E38" s="72"/>
       <c r="F38" s="140"/>
@@ -8206,7 +8200,7 @@
       <c r="B40" s="137"/>
       <c r="C40" s="139"/>
       <c r="D40" s="71" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E40" s="71"/>
       <c r="F40" s="140"/>
@@ -8219,10 +8213,10 @@
       <c r="A41" s="137"/>
       <c r="B41" s="137"/>
       <c r="C41" s="151" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D41" s="71" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E41" s="71"/>
       <c r="F41" s="140"/>
@@ -8235,10 +8229,10 @@
       <c r="A42" s="137"/>
       <c r="B42" s="137"/>
       <c r="C42" s="151" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D42" s="71" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E42" s="68"/>
       <c r="F42" s="140"/>
@@ -8257,7 +8251,7 @@
       <c r="B43" s="137"/>
       <c r="C43" s="139"/>
       <c r="D43" s="139" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E43" s="72"/>
       <c r="F43" s="140"/>
@@ -8275,10 +8269,10 @@
       <c r="A44" s="137"/>
       <c r="B44" s="137"/>
       <c r="C44" s="153" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D44" s="154" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E44" s="155"/>
       <c r="F44" s="156"/>
@@ -8287,17 +8281,17 @@
         <v>7137147.140000001</v>
       </c>
       <c r="H44" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="137"/>
       <c r="B45" s="137"/>
       <c r="C45" s="153" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D45" s="154" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E45" s="155"/>
       <c r="F45" s="156"/>
@@ -8306,17 +8300,17 @@
         <v>2163642.25</v>
       </c>
       <c r="H45" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="137"/>
       <c r="B46" s="137"/>
       <c r="C46" s="153" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D46" s="154" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E46" s="155"/>
       <c r="F46" s="156"/>
@@ -8325,17 +8319,17 @@
         <v>1676263.99</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="137"/>
       <c r="B47" s="137"/>
       <c r="C47" s="153" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D47" s="154" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E47" s="155"/>
       <c r="F47" s="156"/>
@@ -8344,17 +8338,17 @@
         <v>8463010.92</v>
       </c>
       <c r="H47" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="137"/>
       <c r="B48" s="137"/>
       <c r="C48" s="153" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D48" s="153" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E48" s="155"/>
       <c r="F48" s="156"/>
@@ -8363,17 +8357,17 @@
         <v>5117083.33</v>
       </c>
       <c r="H48" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="137"/>
       <c r="B49" s="137"/>
       <c r="C49" s="158" t="s">
+        <v>357</v>
+      </c>
+      <c r="D49" s="154" t="s">
         <v>358</v>
-      </c>
-      <c r="D49" s="154" t="s">
-        <v>359</v>
       </c>
       <c r="E49" s="155"/>
       <c r="F49" s="156"/>
@@ -8382,7 +8376,7 @@
         <v>-3124708.59</v>
       </c>
       <c r="H49" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I49" s="134">
         <f>+'Anexo I'!J15</f>
@@ -8397,10 +8391,10 @@
       <c r="A50" s="137"/>
       <c r="B50" s="137"/>
       <c r="C50" s="158" t="s">
+        <v>359</v>
+      </c>
+      <c r="D50" s="154" t="s">
         <v>360</v>
-      </c>
-      <c r="D50" s="154" t="s">
-        <v>361</v>
       </c>
       <c r="E50" s="155"/>
       <c r="F50" s="156"/>
@@ -8409,7 +8403,7 @@
         <v>-1499006.23</v>
       </c>
       <c r="H50" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I50" s="134">
         <f>+'Anexo I'!J17</f>
@@ -8424,10 +8418,10 @@
       <c r="A51" s="137"/>
       <c r="B51" s="137"/>
       <c r="C51" s="158" t="s">
+        <v>361</v>
+      </c>
+      <c r="D51" s="154" t="s">
         <v>362</v>
-      </c>
-      <c r="D51" s="154" t="s">
-        <v>363</v>
       </c>
       <c r="E51" s="155"/>
       <c r="F51" s="156"/>
@@ -8436,7 +8430,7 @@
         <v>-776376.5700000001</v>
       </c>
       <c r="H51" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I51" s="134">
         <f>+'Anexo I'!J18</f>
@@ -8451,10 +8445,10 @@
       <c r="A52" s="137"/>
       <c r="B52" s="137"/>
       <c r="C52" s="153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D52" s="153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E52" s="155"/>
       <c r="F52" s="156"/>
@@ -8463,17 +8457,17 @@
         <v>20790195.080000002</v>
       </c>
       <c r="H52" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="137"/>
       <c r="B53" s="137"/>
       <c r="C53" s="158" t="s">
+        <v>364</v>
+      </c>
+      <c r="D53" s="154" t="s">
         <v>365</v>
-      </c>
-      <c r="D53" s="154" t="s">
-        <v>366</v>
       </c>
       <c r="E53" s="155"/>
       <c r="F53" s="156"/>
@@ -8482,7 +8476,7 @@
         <v>-4436234.05</v>
       </c>
       <c r="H53" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I53" s="134">
         <f>+'Anexo I'!J19</f>
@@ -8497,10 +8491,10 @@
       <c r="A54" s="137"/>
       <c r="B54" s="137"/>
       <c r="C54" s="158" t="s">
+        <v>366</v>
+      </c>
+      <c r="D54" s="154" t="s">
         <v>367</v>
-      </c>
-      <c r="D54" s="154" t="s">
-        <v>368</v>
       </c>
       <c r="E54" s="155"/>
       <c r="F54" s="156"/>
@@ -8509,7 +8503,7 @@
         <v>-5117083.33</v>
       </c>
       <c r="H54" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I54" s="134">
         <f>+'Anexo I'!J20</f>
@@ -8524,10 +8518,10 @@
       <c r="A55" s="137"/>
       <c r="B55" s="137"/>
       <c r="C55" s="158" t="s">
+        <v>368</v>
+      </c>
+      <c r="D55" s="154" t="s">
         <v>369</v>
-      </c>
-      <c r="D55" s="154" t="s">
-        <v>370</v>
       </c>
       <c r="E55" s="155"/>
       <c r="F55" s="156"/>
@@ -8536,7 +8530,7 @@
         <v>-19606049.32</v>
       </c>
       <c r="H55" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I55" s="134">
         <f>+'Anexo I'!J21</f>
@@ -8551,10 +8545,10 @@
       <c r="A56" s="137"/>
       <c r="B56" s="137"/>
       <c r="C56" s="153" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D56" s="153" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E56" s="155"/>
       <c r="F56" s="156"/>
@@ -8563,17 +8557,17 @@
         <v>23184450.990000002</v>
       </c>
       <c r="H56" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="137"/>
       <c r="B57" s="137"/>
       <c r="C57" s="158" t="s">
+        <v>371</v>
+      </c>
+      <c r="D57" s="154" t="s">
         <v>372</v>
-      </c>
-      <c r="D57" s="154" t="s">
-        <v>373</v>
       </c>
       <c r="E57" s="155"/>
       <c r="F57" s="156"/>
@@ -8582,7 +8576,7 @@
         <v>-10204568.26</v>
       </c>
       <c r="H57" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I57" s="134">
         <f>+'Anexo I'!J16</f>
@@ -8597,10 +8591,10 @@
       <c r="A58" s="137"/>
       <c r="B58" s="137"/>
       <c r="C58" s="153" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D58" s="153" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E58" s="155"/>
       <c r="F58" s="156"/>
@@ -8609,17 +8603,17 @@
         <v>1598074.09</v>
       </c>
       <c r="H58" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="137"/>
       <c r="B59" s="137"/>
       <c r="C59" s="158" t="s">
+        <v>374</v>
+      </c>
+      <c r="D59" s="154" t="s">
         <v>375</v>
-      </c>
-      <c r="D59" s="154" t="s">
-        <v>376</v>
       </c>
       <c r="E59" s="155"/>
       <c r="F59" s="156"/>
@@ -8628,7 +8622,7 @@
         <v>-617752.65</v>
       </c>
       <c r="H59" s="75" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I59" s="134">
         <f>+'Anexo I'!J22</f>
@@ -8645,10 +8639,10 @@
       <c r="A60" s="137"/>
       <c r="B60" s="137"/>
       <c r="C60" s="139" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E60" s="68"/>
       <c r="F60" s="140"/>
@@ -8666,10 +8660,10 @@
       <c r="A61" s="137"/>
       <c r="B61" s="137"/>
       <c r="C61" s="139" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D61" s="71" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E61" s="68"/>
       <c r="F61" s="140"/>
@@ -8683,7 +8677,7 @@
         <v>2158175704.5099998</v>
       </c>
       <c r="J61" s="142" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K61" s="132"/>
       <c r="L61" s="132"/>
@@ -8702,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="142" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K62" s="132"/>
       <c r="L62" s="132"/>
@@ -8712,7 +8706,7 @@
       <c r="B63" s="137"/>
       <c r="C63" s="139"/>
       <c r="D63" s="72" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E63" s="71"/>
       <c r="F63" s="140"/>
@@ -8730,7 +8724,7 @@
       <c r="B64" s="137"/>
       <c r="C64" s="139"/>
       <c r="D64" s="72" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E64" s="71"/>
       <c r="F64" s="140"/>
@@ -8748,7 +8742,7 @@
       <c r="B65" s="137"/>
       <c r="C65" s="139"/>
       <c r="D65" s="72" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E65" s="71"/>
       <c r="F65" s="140"/>
@@ -8766,7 +8760,7 @@
       <c r="B66" s="137"/>
       <c r="C66" s="139"/>
       <c r="D66" s="72" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E66" s="71"/>
       <c r="F66" s="140"/>
@@ -8784,7 +8778,7 @@
       <c r="B67" s="137"/>
       <c r="C67" s="139"/>
       <c r="D67" s="72" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E67" s="71"/>
       <c r="F67" s="140"/>
@@ -8802,7 +8796,7 @@
       <c r="B68" s="137"/>
       <c r="C68" s="139"/>
       <c r="D68" s="72" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E68" s="71"/>
       <c r="F68" s="140"/>
@@ -8820,7 +8814,7 @@
       <c r="B69" s="137"/>
       <c r="C69" s="139"/>
       <c r="D69" s="72" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E69" s="71"/>
       <c r="F69" s="140"/>
@@ -8838,7 +8832,7 @@
       <c r="B70" s="137"/>
       <c r="C70" s="139"/>
       <c r="D70" s="72" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E70" s="71"/>
       <c r="F70" s="140"/>
@@ -8856,7 +8850,7 @@
       <c r="B71" s="137"/>
       <c r="C71" s="139"/>
       <c r="D71" s="72" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E71" s="71"/>
       <c r="F71" s="140"/>
@@ -8874,7 +8868,7 @@
       <c r="B72" s="137"/>
       <c r="C72" s="139"/>
       <c r="D72" s="72" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E72" s="71"/>
       <c r="F72" s="140"/>
@@ -8892,7 +8886,7 @@
       <c r="B73" s="137"/>
       <c r="C73" s="139"/>
       <c r="D73" s="72" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E73" s="71"/>
       <c r="F73" s="140"/>
@@ -8910,7 +8904,7 @@
       <c r="B74" s="137"/>
       <c r="C74" s="139"/>
       <c r="D74" s="72" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E74" s="71"/>
       <c r="F74" s="140"/>
@@ -8928,7 +8922,7 @@
       <c r="B75" s="137"/>
       <c r="C75" s="139"/>
       <c r="D75" s="72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E75" s="71"/>
       <c r="F75" s="140"/>
@@ -8946,7 +8940,7 @@
       <c r="B76" s="137"/>
       <c r="C76" s="139"/>
       <c r="D76" s="72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E76" s="71"/>
       <c r="F76" s="140"/>
@@ -8964,7 +8958,7 @@
       <c r="B77" s="137"/>
       <c r="C77" s="139"/>
       <c r="D77" s="72" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E77" s="71"/>
       <c r="F77" s="140"/>
@@ -8982,7 +8976,7 @@
       <c r="B78" s="137"/>
       <c r="C78" s="139"/>
       <c r="D78" s="72" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E78" s="71"/>
       <c r="F78" s="140"/>
@@ -9000,7 +8994,7 @@
       <c r="B79" s="137"/>
       <c r="C79" s="139"/>
       <c r="D79" s="72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E79" s="71"/>
       <c r="F79" s="140"/>
@@ -9018,7 +9012,7 @@
       <c r="B80" s="137"/>
       <c r="C80" s="139"/>
       <c r="D80" s="72" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E80" s="71"/>
       <c r="F80" s="140"/>
@@ -9036,7 +9030,7 @@
       <c r="B81" s="137"/>
       <c r="C81" s="139"/>
       <c r="D81" s="72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E81" s="71"/>
       <c r="F81" s="140"/>
@@ -9054,7 +9048,7 @@
       <c r="B82" s="137"/>
       <c r="C82" s="139"/>
       <c r="D82" s="72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E82" s="71"/>
       <c r="F82" s="140"/>
@@ -9072,7 +9066,7 @@
       <c r="B83" s="137"/>
       <c r="C83" s="139"/>
       <c r="D83" s="72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E83" s="71"/>
       <c r="F83" s="140"/>
@@ -9090,7 +9084,7 @@
       <c r="B84" s="137"/>
       <c r="C84" s="139"/>
       <c r="D84" s="72" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E84" s="71"/>
       <c r="F84" s="140"/>
@@ -9108,7 +9102,7 @@
       <c r="B85" s="137"/>
       <c r="C85" s="139"/>
       <c r="D85" s="72" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E85" s="71"/>
       <c r="F85" s="140"/>
@@ -9126,7 +9120,7 @@
       <c r="B86" s="137"/>
       <c r="C86" s="139"/>
       <c r="D86" s="72" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E86" s="71"/>
       <c r="F86" s="140"/>
@@ -9144,7 +9138,7 @@
       <c r="B87" s="137"/>
       <c r="C87" s="139"/>
       <c r="D87" s="72" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E87" s="71"/>
       <c r="F87" s="140"/>
@@ -9162,7 +9156,7 @@
       <c r="B88" s="137"/>
       <c r="C88" s="139"/>
       <c r="D88" s="72" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E88" s="71"/>
       <c r="F88" s="140"/>
@@ -9180,7 +9174,7 @@
       <c r="B89" s="137"/>
       <c r="C89" s="139"/>
       <c r="D89" s="72" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E89" s="71"/>
       <c r="F89" s="140"/>
@@ -9198,7 +9192,7 @@
       <c r="B90" s="137"/>
       <c r="C90" s="139"/>
       <c r="D90" s="72" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E90" s="71"/>
       <c r="F90" s="140"/>
@@ -9216,7 +9210,7 @@
       <c r="B91" s="137"/>
       <c r="C91" s="139"/>
       <c r="D91" s="72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E91" s="71"/>
       <c r="F91" s="140"/>
@@ -9234,7 +9228,7 @@
       <c r="B92" s="137"/>
       <c r="C92" s="139"/>
       <c r="D92" s="72" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E92" s="71"/>
       <c r="F92" s="140"/>
@@ -9252,7 +9246,7 @@
       <c r="B93" s="137"/>
       <c r="C93" s="139"/>
       <c r="D93" s="72" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E93" s="71"/>
       <c r="F93" s="140"/>
@@ -9270,7 +9264,7 @@
       <c r="B94" s="137"/>
       <c r="C94" s="139"/>
       <c r="D94" s="72" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E94" s="71"/>
       <c r="F94" s="140"/>
@@ -9288,7 +9282,7 @@
       <c r="B95" s="137"/>
       <c r="C95" s="139"/>
       <c r="D95" s="72" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E95" s="71"/>
       <c r="F95" s="140"/>
@@ -9306,7 +9300,7 @@
       <c r="B96" s="137"/>
       <c r="C96" s="139"/>
       <c r="D96" s="72" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E96" s="71"/>
       <c r="F96" s="140"/>
@@ -9324,7 +9318,7 @@
       <c r="B97" s="137"/>
       <c r="C97" s="139"/>
       <c r="D97" s="72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E97" s="71"/>
       <c r="F97" s="140"/>
@@ -9342,7 +9336,7 @@
       <c r="B98" s="137"/>
       <c r="C98" s="139"/>
       <c r="D98" s="72" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E98" s="71"/>
       <c r="F98" s="140"/>
@@ -9360,7 +9354,7 @@
       <c r="B99" s="137"/>
       <c r="C99" s="139"/>
       <c r="D99" s="72" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E99" s="71"/>
       <c r="F99" s="140"/>
@@ -9378,7 +9372,7 @@
       <c r="B100" s="137"/>
       <c r="C100" s="139"/>
       <c r="D100" s="72" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E100" s="71"/>
       <c r="F100" s="140"/>
@@ -9396,7 +9390,7 @@
       <c r="B101" s="137"/>
       <c r="C101" s="139"/>
       <c r="D101" s="72" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E101" s="71"/>
       <c r="F101" s="140"/>
@@ -9414,7 +9408,7 @@
       <c r="B102" s="137"/>
       <c r="C102" s="139"/>
       <c r="D102" s="72" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E102" s="71"/>
       <c r="F102" s="140"/>
@@ -9432,7 +9426,7 @@
       <c r="B103" s="137"/>
       <c r="C103" s="139"/>
       <c r="D103" s="72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E103" s="71"/>
       <c r="F103" s="140"/>
@@ -9450,7 +9444,7 @@
       <c r="B104" s="137"/>
       <c r="C104" s="139"/>
       <c r="D104" s="72" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E104" s="71"/>
       <c r="F104" s="140"/>
@@ -9468,7 +9462,7 @@
       <c r="B105" s="137"/>
       <c r="C105" s="139"/>
       <c r="D105" s="72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E105" s="71"/>
       <c r="F105" s="140"/>
@@ -9486,7 +9480,7 @@
       <c r="B106" s="137"/>
       <c r="C106" s="139"/>
       <c r="D106" s="72" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E106" s="71"/>
       <c r="F106" s="140"/>
@@ -9504,7 +9498,7 @@
       <c r="B107" s="137"/>
       <c r="C107" s="139"/>
       <c r="D107" s="72" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E107" s="71"/>
       <c r="F107" s="140"/>
@@ -9522,7 +9516,7 @@
       <c r="B108" s="137"/>
       <c r="C108" s="139"/>
       <c r="D108" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E108" s="71"/>
       <c r="F108" s="140"/>
@@ -9540,7 +9534,7 @@
       <c r="B109" s="137"/>
       <c r="C109" s="139"/>
       <c r="D109" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E109" s="71"/>
       <c r="F109" s="140"/>
@@ -9558,7 +9552,7 @@
       <c r="B110" s="137"/>
       <c r="C110" s="139"/>
       <c r="D110" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E110" s="71"/>
       <c r="F110" s="140"/>
@@ -9576,7 +9570,7 @@
       <c r="B111" s="137"/>
       <c r="C111" s="139"/>
       <c r="D111" s="72" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E111" s="71"/>
       <c r="F111" s="140"/>
@@ -9594,7 +9588,7 @@
       <c r="B112" s="137"/>
       <c r="C112" s="139"/>
       <c r="D112" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E112" s="71"/>
       <c r="F112" s="140"/>
@@ -9612,7 +9606,7 @@
       <c r="B113" s="137"/>
       <c r="C113" s="139"/>
       <c r="D113" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E113" s="71"/>
       <c r="F113" s="140"/>
@@ -9630,7 +9624,7 @@
       <c r="B114" s="137"/>
       <c r="C114" s="139"/>
       <c r="D114" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E114" s="71"/>
       <c r="F114" s="140"/>
@@ -9653,7 +9647,7 @@
       <c r="G115" s="161"/>
       <c r="H115" s="74"/>
       <c r="I115" s="134" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J115" s="132"/>
       <c r="K115" s="132"/>
@@ -9673,7 +9667,7 @@
         <v>-106687518.28999999</v>
       </c>
       <c r="J116" s="142" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K116" s="132"/>
       <c r="L116" s="132"/>
@@ -9724,10 +9718,10 @@
       <c r="A120" s="137"/>
       <c r="B120" s="137"/>
       <c r="C120" s="151" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D120" s="71" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E120" s="71"/>
       <c r="F120" s="140"/>
@@ -9739,10 +9733,10 @@
       <c r="A121" s="137"/>
       <c r="B121" s="137"/>
       <c r="C121" s="72" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D121" s="139" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E121" s="68"/>
       <c r="F121" s="140"/>
@@ -9754,10 +9748,10 @@
       <c r="A122" s="137"/>
       <c r="B122" s="137"/>
       <c r="C122" s="139" t="s">
+        <v>436</v>
+      </c>
+      <c r="D122" s="71" t="s">
         <v>437</v>
-      </c>
-      <c r="D122" s="71" t="s">
-        <v>438</v>
       </c>
       <c r="E122" s="68"/>
       <c r="F122" s="140"/>
@@ -9770,7 +9764,7 @@
       <c r="B123" s="137"/>
       <c r="C123" s="139"/>
       <c r="D123" s="71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E123" s="71"/>
       <c r="F123" s="140"/>
@@ -9783,7 +9777,7 @@
       <c r="B124" s="137"/>
       <c r="C124" s="139"/>
       <c r="D124" s="71" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E124" s="71"/>
       <c r="F124" s="140"/>
@@ -9795,11 +9789,9 @@
       <c r="A125" s="137"/>
       <c r="B125" s="137"/>
       <c r="C125" s="139" t="s">
-        <v>441</v>
-      </c>
-      <c r="D125" s="71" t="s">
-        <v>442</v>
-      </c>
+        <v>440</v>
+      </c>
+      <c r="D125" s="71"/>
       <c r="E125" s="71"/>
       <c r="F125" s="140"/>
       <c r="G125" s="161">
@@ -9812,7 +9804,7 @@
       <c r="B126" s="137"/>
       <c r="C126" s="139"/>
       <c r="D126" s="71" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E126" s="71"/>
       <c r="F126" s="140"/>
@@ -9829,10 +9821,10 @@
       <c r="A127" s="137"/>
       <c r="B127" s="137"/>
       <c r="C127" s="139" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D127" s="139" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E127" s="68"/>
       <c r="F127" s="140"/>
@@ -9847,10 +9839,10 @@
       <c r="A128" s="137"/>
       <c r="B128" s="137"/>
       <c r="C128" s="139" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D128" s="139" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E128" s="68"/>
       <c r="F128" s="140"/>
@@ -9863,7 +9855,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="72" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="129" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9871,7 +9863,7 @@
       <c r="B129" s="137"/>
       <c r="C129" s="139"/>
       <c r="D129" s="139" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E129" s="68"/>
       <c r="F129" s="140"/>
@@ -9887,7 +9879,7 @@
       <c r="B130" s="137"/>
       <c r="C130" s="139"/>
       <c r="D130" s="139" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E130" s="68"/>
       <c r="F130" s="140"/>
@@ -9902,10 +9894,10 @@
       <c r="A131" s="137"/>
       <c r="B131" s="137"/>
       <c r="C131" s="72" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D131" s="139" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E131" s="68"/>
       <c r="F131" s="140"/>
@@ -9918,7 +9910,7 @@
       <c r="B132" s="137"/>
       <c r="C132" s="139"/>
       <c r="D132" s="71" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E132" s="71"/>
       <c r="F132" s="140"/>
@@ -9931,7 +9923,7 @@
       <c r="B133" s="137"/>
       <c r="C133" s="139"/>
       <c r="D133" s="139" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E133" s="71"/>
       <c r="F133" s="140"/>
@@ -9944,7 +9936,7 @@
       <c r="B134" s="137"/>
       <c r="C134" s="139"/>
       <c r="D134" s="139" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E134" s="71"/>
       <c r="F134" s="140"/>
@@ -9956,10 +9948,10 @@
       <c r="A135" s="137"/>
       <c r="B135" s="137"/>
       <c r="C135" s="139" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D135" s="139" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E135" s="71"/>
       <c r="F135" s="140"/>
@@ -9971,10 +9963,10 @@
       <c r="A136" s="137"/>
       <c r="B136" s="137"/>
       <c r="C136" s="72" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D136" s="135" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E136" s="71"/>
       <c r="F136" s="140"/>
@@ -9986,10 +9978,10 @@
       <c r="A137" s="167"/>
       <c r="B137" s="167"/>
       <c r="C137" s="168" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D137" s="169" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="E137" s="170"/>
       <c r="F137" s="171"/>
@@ -10018,10 +10010,10 @@
       <c r="A139" s="137"/>
       <c r="B139" s="137"/>
       <c r="C139" s="72" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D139" s="71" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E139" s="68"/>
       <c r="F139" s="140"/>
@@ -10034,10 +10026,10 @@
       <c r="A140" s="137"/>
       <c r="B140" s="137"/>
       <c r="C140" s="72" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D140" s="71" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E140" s="150"/>
       <c r="F140" s="140"/>
@@ -10051,10 +10043,10 @@
       <c r="A141" s="137"/>
       <c r="B141" s="137"/>
       <c r="C141" s="72" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D141" s="71" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E141" s="68"/>
       <c r="F141" s="140"/>
@@ -10067,7 +10059,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="J141" s="142" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K141" s="19"/>
       <c r="L141" s="132"/>
@@ -10076,10 +10068,10 @@
       <c r="A142" s="137"/>
       <c r="B142" s="137"/>
       <c r="C142" s="72" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D142" s="139" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E142" s="68"/>
       <c r="F142" s="140"/>
@@ -10092,7 +10084,7 @@
         <v>3354028747.869999</v>
       </c>
       <c r="J142" s="142" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K142" s="19"/>
       <c r="L142" s="132"/>
@@ -10102,7 +10094,7 @@
       <c r="B143" s="137"/>
       <c r="C143" s="72"/>
       <c r="D143" s="71" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E143" s="71"/>
       <c r="F143" s="140"/>
@@ -10116,7 +10108,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="142" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1" spans="1:14" s="166" customFormat="1" x14ac:dyDescent="0.25">
@@ -10156,7 +10148,7 @@
       <c r="B146" s="137"/>
       <c r="C146" s="139"/>
       <c r="D146" s="71" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E146" s="71"/>
       <c r="F146" s="140"/>
@@ -10172,7 +10164,7 @@
       <c r="B147" s="137"/>
       <c r="C147" s="139"/>
       <c r="D147" s="71" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E147" s="71"/>
       <c r="F147" s="140"/>
@@ -10186,7 +10178,7 @@
       <c r="B148" s="137"/>
       <c r="C148" s="139"/>
       <c r="D148" s="139" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E148" s="72"/>
       <c r="F148" s="140"/>
@@ -10200,7 +10192,7 @@
       <c r="B149" s="137"/>
       <c r="C149" s="139"/>
       <c r="D149" s="139" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E149" s="72"/>
       <c r="F149" s="140"/>
@@ -10214,10 +10206,10 @@
       <c r="B150" s="137"/>
       <c r="C150" s="139"/>
       <c r="D150" s="139" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E150" s="72" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F150" s="140"/>
       <c r="G150" s="138">
@@ -10230,7 +10222,7 @@
       <c r="B151" s="137"/>
       <c r="C151" s="139"/>
       <c r="D151" s="139" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E151" s="72"/>
       <c r="F151" s="140">
@@ -10247,7 +10239,7 @@
       <c r="B152" s="137"/>
       <c r="C152" s="139"/>
       <c r="D152" s="139" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E152" s="72"/>
       <c r="F152" s="140">
@@ -10264,7 +10256,7 @@
       <c r="B153" s="137"/>
       <c r="C153" s="139"/>
       <c r="D153" s="139" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E153" s="72"/>
       <c r="F153" s="140">
@@ -10276,7 +10268,7 @@
         <v>6840000</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10284,7 +10276,7 @@
       <c r="B154" s="137"/>
       <c r="C154" s="139"/>
       <c r="D154" s="71" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E154" s="71"/>
       <c r="F154" s="140">
@@ -10302,7 +10294,7 @@
       <c r="C155" s="139"/>
       <c r="D155" s="71"/>
       <c r="E155" s="72" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F155" s="140">
         <f>IFERROR(VLOOKUP(E155,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10318,7 +10310,7 @@
       <c r="C156" s="139"/>
       <c r="D156" s="71"/>
       <c r="E156" s="72" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F156" s="140">
         <f>IFERROR(VLOOKUP(E156,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10334,7 +10326,7 @@
       <c r="C157" s="139"/>
       <c r="D157" s="71"/>
       <c r="E157" s="72" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F157" s="140">
         <f>IFERROR(VLOOKUP(E157,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10350,7 +10342,7 @@
       <c r="C158" s="139"/>
       <c r="D158" s="71"/>
       <c r="E158" s="72" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F158" s="140">
         <f>IFERROR(VLOOKUP(E158,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10365,7 +10357,7 @@
       <c r="B159" s="137"/>
       <c r="C159" s="139"/>
       <c r="D159" s="71" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E159" s="71"/>
       <c r="F159" s="140"/>
@@ -10380,7 +10372,7 @@
       <c r="C160" s="139"/>
       <c r="D160" s="71"/>
       <c r="E160" s="72" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F160" s="140">
         <f>IFERROR(VLOOKUP(E160,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10394,7 +10386,7 @@
       <c r="C161" s="139"/>
       <c r="D161" s="71"/>
       <c r="E161" s="72" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F161" s="140">
         <f>IFERROR(VLOOKUP(E161,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10408,7 +10400,7 @@
       <c r="C162" s="139"/>
       <c r="D162" s="71"/>
       <c r="E162" s="72" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F162" s="140">
         <f>IFERROR(VLOOKUP(E162,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10422,7 +10414,7 @@
       <c r="C163" s="139"/>
       <c r="D163" s="71"/>
       <c r="E163" s="72" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F163" s="140">
         <f>IFERROR(VLOOKUP(E163,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10436,7 +10428,7 @@
       <c r="C164" s="139"/>
       <c r="D164" s="71"/>
       <c r="E164" s="72" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F164" s="140">
         <f>IFERROR(VLOOKUP(E164,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10450,7 +10442,7 @@
       <c r="C165" s="139"/>
       <c r="D165" s="71"/>
       <c r="E165" s="72" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F165" s="140">
         <f>IFERROR(VLOOKUP(E165,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10464,7 +10456,7 @@
       <c r="C166" s="139"/>
       <c r="D166" s="71"/>
       <c r="E166" s="72" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F166" s="140">
         <f>IFERROR(VLOOKUP(E166,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10478,7 +10470,7 @@
       <c r="C167" s="139"/>
       <c r="D167" s="71"/>
       <c r="E167" s="72" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F167" s="140">
         <f>IFERROR(VLOOKUP(E167,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10491,7 +10483,7 @@
       <c r="B168" s="137"/>
       <c r="C168" s="139"/>
       <c r="D168" s="71" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E168" s="188"/>
       <c r="F168" s="140">
@@ -10509,7 +10501,7 @@
       <c r="B169" s="137"/>
       <c r="C169" s="139"/>
       <c r="D169" s="71" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E169" s="188"/>
       <c r="F169" s="140">
@@ -10526,7 +10518,7 @@
       <c r="B170" s="137"/>
       <c r="C170" s="139"/>
       <c r="D170" s="71" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E170" s="188"/>
       <c r="F170" s="140">
@@ -10549,7 +10541,7 @@
       <c r="B171" s="137"/>
       <c r="C171" s="139"/>
       <c r="D171" s="71" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E171" s="188"/>
       <c r="F171" s="150"/>
@@ -10564,7 +10556,7 @@
       <c r="C172" s="139"/>
       <c r="D172" s="71"/>
       <c r="E172" s="72" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F172" s="140">
         <f>IFERROR(VLOOKUP(E172,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10578,7 +10570,7 @@
       <c r="C173" s="139"/>
       <c r="D173" s="71"/>
       <c r="E173" s="72" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F173" s="140">
         <f>IFERROR(VLOOKUP(E173,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10592,7 +10584,7 @@
       <c r="C174" s="139"/>
       <c r="D174" s="71"/>
       <c r="E174" s="72" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F174" s="140">
         <f>IFERROR(VLOOKUP(E174,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10606,7 +10598,7 @@
       <c r="C175" s="139"/>
       <c r="D175" s="71"/>
       <c r="E175" s="72" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F175" s="140">
         <f>IFERROR(VLOOKUP(E175,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10620,7 +10612,7 @@
       <c r="C176" s="139"/>
       <c r="D176" s="71"/>
       <c r="E176" s="72" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F176" s="140">
         <f>IFERROR(VLOOKUP(E176,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10634,7 +10626,7 @@
       <c r="C177" s="139"/>
       <c r="D177" s="71"/>
       <c r="E177" s="72" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F177" s="140">
         <f>IFERROR(VLOOKUP(E177,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10647,7 +10639,7 @@
       <c r="B178" s="137"/>
       <c r="C178" s="139"/>
       <c r="D178" s="71" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E178" s="71"/>
       <c r="F178" s="140">
@@ -10664,7 +10656,7 @@
       <c r="B179" s="137"/>
       <c r="C179" s="139"/>
       <c r="D179" s="71" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E179" s="71"/>
       <c r="F179" s="140"/>
@@ -10679,7 +10671,7 @@
       <c r="C180" s="139"/>
       <c r="D180" s="71"/>
       <c r="E180" s="72" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F180" s="140">
         <f>IFERROR(VLOOKUP(E180,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10693,7 +10685,7 @@
       <c r="C181" s="139"/>
       <c r="D181" s="71"/>
       <c r="E181" s="72" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F181" s="140">
         <f>IFERROR(VLOOKUP(E181,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10707,7 +10699,7 @@
       <c r="C182" s="139"/>
       <c r="D182" s="71"/>
       <c r="E182" s="72" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F182" s="140">
         <f>IFERROR(VLOOKUP(E182,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10721,7 +10713,7 @@
       <c r="C183" s="139"/>
       <c r="D183" s="71"/>
       <c r="E183" s="72" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F183" s="140">
         <f>IFERROR(VLOOKUP(E183,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10737,7 +10729,7 @@
       <c r="C184" s="139"/>
       <c r="D184" s="71"/>
       <c r="E184" s="72" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F184" s="140">
         <f>IFERROR(VLOOKUP(E184,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10763,7 +10755,7 @@
       <c r="B186" s="137"/>
       <c r="C186" s="139"/>
       <c r="D186" s="71" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E186" s="188"/>
       <c r="F186" s="140"/>
@@ -10777,10 +10769,10 @@
       <c r="B187" s="137"/>
       <c r="C187" s="139"/>
       <c r="D187" s="71" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E187" s="72" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F187" s="140">
         <f>IFERROR(VLOOKUP(E187,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10798,7 +10790,7 @@
       <c r="B188" s="137"/>
       <c r="C188" s="139"/>
       <c r="D188" s="71" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E188" s="76"/>
       <c r="F188" s="140"/>
@@ -10813,7 +10805,7 @@
       <c r="C189" s="139"/>
       <c r="D189" s="71"/>
       <c r="E189" s="72" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F189" s="140">
         <f>IFERROR(VLOOKUP(E189,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10827,7 +10819,7 @@
       <c r="C190" s="139"/>
       <c r="D190" s="71"/>
       <c r="E190" s="72" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F190" s="140">
         <f>IFERROR(VLOOKUP(E190,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10841,7 +10833,7 @@
       <c r="C191" s="139"/>
       <c r="D191" s="71"/>
       <c r="E191" s="72" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F191" s="140">
         <f>IFERROR(VLOOKUP(E191,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10855,7 +10847,7 @@
       <c r="C192" s="139"/>
       <c r="D192" s="71"/>
       <c r="E192" s="72" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F192" s="140">
         <f>IFERROR(VLOOKUP(E192,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10869,7 +10861,7 @@
       <c r="C193" s="139"/>
       <c r="D193" s="71"/>
       <c r="E193" s="72" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F193" s="140">
         <f>IFERROR(VLOOKUP(E193,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10883,7 +10875,7 @@
       <c r="C194" s="139"/>
       <c r="D194" s="71"/>
       <c r="E194" s="72" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F194" s="140">
         <f>IFERROR(VLOOKUP(E194,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10897,7 +10889,7 @@
       <c r="C195" s="139"/>
       <c r="D195" s="71"/>
       <c r="E195" s="72" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F195" s="140">
         <f>IFERROR(VLOOKUP(E195,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10911,7 +10903,7 @@
       <c r="C196" s="139"/>
       <c r="D196" s="71"/>
       <c r="E196" s="72" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F196" s="140">
         <f>IFERROR(VLOOKUP(E196,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10924,10 +10916,10 @@
       <c r="B197" s="137"/>
       <c r="C197" s="139"/>
       <c r="D197" s="139" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E197" s="72" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F197" s="140">
         <f>IFERROR(VLOOKUP(E197,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10944,7 +10936,7 @@
       <c r="C198" s="139"/>
       <c r="D198" s="139"/>
       <c r="E198" s="72" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F198" s="140">
         <f>IFERROR(VLOOKUP(E198,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10960,7 +10952,7 @@
       <c r="C199" s="139"/>
       <c r="D199" s="139"/>
       <c r="E199" s="72" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F199" s="140">
         <f>IFERROR(VLOOKUP(E199,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10975,10 +10967,10 @@
       <c r="B200" s="137"/>
       <c r="C200" s="139"/>
       <c r="D200" s="139" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E200" s="72" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F200" s="140">
         <f>IFERROR(VLOOKUP(E200,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10997,7 +10989,7 @@
       <c r="C201" s="139"/>
       <c r="D201" s="139"/>
       <c r="E201" s="72" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F201" s="140">
         <f>IFERROR(VLOOKUP(E201,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11012,7 +11004,7 @@
       <c r="B202" s="137"/>
       <c r="C202" s="139"/>
       <c r="D202" s="71" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E202" s="188"/>
       <c r="F202" s="140"/>
@@ -11033,10 +11025,10 @@
       <c r="B203" s="137"/>
       <c r="C203" s="139"/>
       <c r="D203" s="71" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E203" s="72" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F203" s="140">
         <f>IFERROR(VLOOKUP(E203,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11055,7 +11047,7 @@
       <c r="C204" s="139"/>
       <c r="D204" s="71"/>
       <c r="E204" s="71" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F204" s="140">
         <f>IFERROR(VLOOKUP(E204,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11068,7 +11060,7 @@
       <c r="B205" s="137"/>
       <c r="C205" s="139"/>
       <c r="D205" s="71" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E205" s="188"/>
       <c r="F205" s="140"/>
@@ -11083,7 +11075,7 @@
       <c r="C206" s="139"/>
       <c r="D206" s="71"/>
       <c r="E206" s="72" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F206" s="140">
         <f>IFERROR(VLOOKUP(E206,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11097,7 +11089,7 @@
       <c r="C207" s="139"/>
       <c r="D207" s="71"/>
       <c r="E207" s="188" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F207" s="140">
         <f>IFERROR(VLOOKUP(E207,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11110,7 +11102,7 @@
       <c r="B208" s="137"/>
       <c r="C208" s="139"/>
       <c r="D208" s="71" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E208" s="188"/>
       <c r="F208" s="140"/>
@@ -11125,7 +11117,7 @@
       <c r="C209" s="139"/>
       <c r="D209" s="71"/>
       <c r="E209" s="72" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F209" s="140">
         <f>IFERROR(VLOOKUP(E209,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11139,7 +11131,7 @@
       <c r="C210" s="139"/>
       <c r="D210" s="71"/>
       <c r="E210" s="72" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F210" s="140">
         <f>IFERROR(VLOOKUP(E210,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11155,7 +11147,7 @@
       <c r="C211" s="139"/>
       <c r="D211" s="71"/>
       <c r="E211" s="72" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F211" s="140">
         <f>IFERROR(VLOOKUP(E211,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11171,7 +11163,7 @@
       <c r="C212" s="139"/>
       <c r="D212" s="71"/>
       <c r="E212" s="72" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F212" s="140">
         <f>IFERROR(VLOOKUP(E212,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11186,7 +11178,7 @@
       <c r="B213" s="137"/>
       <c r="C213" s="139"/>
       <c r="D213" s="71" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E213" s="188"/>
       <c r="F213" s="140"/>
@@ -11202,7 +11194,7 @@
       <c r="C214" s="139"/>
       <c r="D214" s="71"/>
       <c r="E214" s="72" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F214" s="140">
         <f>IFERROR(VLOOKUP(E214,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11217,7 +11209,7 @@
       <c r="C215" s="139"/>
       <c r="D215" s="71"/>
       <c r="E215" s="72" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F215" s="140">
         <f>IFERROR(VLOOKUP(E215,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11232,7 +11224,7 @@
       <c r="C216" s="139"/>
       <c r="D216" s="71"/>
       <c r="E216" s="72" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F216" s="140">
         <f>IFERROR(VLOOKUP(E216,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11246,7 +11238,7 @@
       <c r="B217" s="137"/>
       <c r="C217" s="139"/>
       <c r="D217" s="71" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E217" s="188"/>
       <c r="F217" s="140"/>
@@ -11268,7 +11260,7 @@
       <c r="C218" s="139"/>
       <c r="D218" s="71"/>
       <c r="E218" s="72" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F218" s="140">
         <f>IFERROR(VLOOKUP(E218,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11282,7 +11274,7 @@
       <c r="C219" s="139"/>
       <c r="D219" s="71"/>
       <c r="E219" s="72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F219" s="140">
         <f>IFERROR(VLOOKUP(E219,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11296,7 +11288,7 @@
       <c r="C220" s="139"/>
       <c r="D220" s="71"/>
       <c r="E220" s="72" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F220" s="140">
         <f>IFERROR(VLOOKUP(E220,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11310,7 +11302,7 @@
       <c r="C221" s="139"/>
       <c r="D221" s="71"/>
       <c r="E221" s="72" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F221" s="140">
         <f>IFERROR(VLOOKUP(E221,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11324,7 +11316,7 @@
       <c r="C222" s="139"/>
       <c r="D222" s="71"/>
       <c r="E222" s="72" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F222" s="140">
         <f>IFERROR(VLOOKUP(E222,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11338,7 +11330,7 @@
       <c r="C223" s="139"/>
       <c r="D223" s="71"/>
       <c r="E223" s="72" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F223" s="140">
         <f>IFERROR(VLOOKUP(E223,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11354,7 +11346,7 @@
       <c r="C224" s="139"/>
       <c r="D224" s="71"/>
       <c r="E224" s="72" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F224" s="140">
         <f>IFERROR(VLOOKUP(E224,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11380,10 +11372,10 @@
       <c r="B226" s="137"/>
       <c r="C226" s="139"/>
       <c r="D226" s="71" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E226" s="72" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F226" s="140">
         <f>IFERROR(VLOOKUP(E226,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11402,7 +11394,7 @@
       <c r="C227" s="139"/>
       <c r="D227" s="71"/>
       <c r="E227" s="72" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F227" s="140">
         <f>IFERROR(VLOOKUP(E227,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11421,7 +11413,7 @@
       <c r="C228" s="139"/>
       <c r="D228" s="71"/>
       <c r="E228" s="72" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F228" s="140">
         <f>IFERROR(VLOOKUP(E228,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11453,10 +11445,10 @@
       <c r="B230" s="137"/>
       <c r="C230" s="139"/>
       <c r="D230" s="71" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E230" s="72" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F230" s="140">
         <f>IFERROR(VLOOKUP(E230,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11473,7 +11465,7 @@
       <c r="C231" s="139"/>
       <c r="D231" s="71"/>
       <c r="E231" s="72" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F231" s="140">
         <f>IFERROR(VLOOKUP(E231,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11486,7 +11478,7 @@
       <c r="B232" s="137"/>
       <c r="C232" s="139"/>
       <c r="D232" s="71" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E232" s="71"/>
       <c r="F232" s="140"/>
@@ -11500,7 +11492,7 @@
       <c r="B233" s="137"/>
       <c r="C233" s="139"/>
       <c r="D233" s="71" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E233" s="71"/>
       <c r="F233" s="140"/>
@@ -11514,10 +11506,10 @@
       <c r="B234" s="137"/>
       <c r="C234" s="139"/>
       <c r="D234" s="71" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E234" s="72" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F234" s="140">
         <f>IFERROR(VLOOKUP(E234,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11536,7 +11528,7 @@
       <c r="C235" s="139"/>
       <c r="D235" s="71"/>
       <c r="E235" s="72" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F235" s="140">
         <f>IFERROR(VLOOKUP(E235,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11552,7 +11544,7 @@
       <c r="C236" s="139"/>
       <c r="D236" s="71"/>
       <c r="E236" s="72" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F236" s="140">
         <f>IFERROR(VLOOKUP(E236,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11581,7 +11573,7 @@
       <c r="B238" s="137"/>
       <c r="C238" s="139"/>
       <c r="D238" s="71" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E238" s="71"/>
       <c r="F238" s="140"/>
@@ -11595,10 +11587,10 @@
       <c r="B239" s="137"/>
       <c r="C239" s="139"/>
       <c r="D239" s="71" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E239" s="71" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F239" s="140">
         <f>IFERROR(VLOOKUP(E239,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11615,7 +11607,7 @@
       <c r="C240" s="139"/>
       <c r="D240" s="71"/>
       <c r="E240" s="72" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F240" s="140">
         <f>IFERROR(VLOOKUP(E240,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11629,7 +11621,7 @@
       <c r="C241" s="139"/>
       <c r="D241" s="71"/>
       <c r="E241" s="151" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F241" s="140">
         <f>IFERROR(VLOOKUP(E241,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11643,7 +11635,7 @@
       <c r="C242" s="139"/>
       <c r="D242" s="71"/>
       <c r="E242" s="151" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F242" s="140">
         <f>IFERROR(VLOOKUP(E242,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11656,10 +11648,10 @@
       <c r="B243" s="137"/>
       <c r="C243" s="139"/>
       <c r="D243" s="71" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E243" s="72" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F243" s="140">
         <f>IFERROR(VLOOKUP(E243,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11678,7 +11670,7 @@
       <c r="C244" s="139"/>
       <c r="D244" s="71"/>
       <c r="E244" s="72" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F244" s="140">
         <f>IFERROR(VLOOKUP(E244,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11693,7 +11685,7 @@
       <c r="B245" s="137"/>
       <c r="C245" s="139"/>
       <c r="D245" s="71" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E245" s="71"/>
       <c r="F245" s="140"/>
@@ -11707,10 +11699,10 @@
       <c r="B246" s="137"/>
       <c r="C246" s="139"/>
       <c r="D246" s="71" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E246" s="72" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F246" s="140">
         <f>IFERROR(VLOOKUP(E246,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11727,7 +11719,7 @@
       <c r="C247" s="139"/>
       <c r="D247" s="71"/>
       <c r="E247" s="72" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F247" s="140">
         <f>IFERROR(VLOOKUP(E247,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11741,7 +11733,7 @@
       <c r="C248" s="139"/>
       <c r="D248" s="71"/>
       <c r="E248" s="72" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F248" s="140">
         <f>IFERROR(VLOOKUP(E248,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11755,7 +11747,7 @@
       <c r="C249" s="139"/>
       <c r="D249" s="71"/>
       <c r="E249" s="72" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F249" s="140">
         <f>IFERROR(VLOOKUP(E249,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11769,7 +11761,7 @@
       <c r="C250" s="139"/>
       <c r="D250" s="71"/>
       <c r="E250" s="72" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F250" s="140">
         <f>IFERROR(VLOOKUP(E250,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11783,7 +11775,7 @@
       <c r="C251" s="139"/>
       <c r="D251" s="71"/>
       <c r="E251" s="72" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F251" s="140">
         <f>IFERROR(VLOOKUP(E251,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11797,7 +11789,7 @@
       <c r="C252" s="139"/>
       <c r="D252" s="71"/>
       <c r="E252" s="72" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F252" s="140">
         <f>IFERROR(VLOOKUP(E252,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11811,7 +11803,7 @@
       <c r="C253" s="139"/>
       <c r="D253" s="71"/>
       <c r="E253" s="72" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F253" s="140">
         <f>IFERROR(VLOOKUP(E253,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11827,7 +11819,7 @@
       <c r="C254" s="139"/>
       <c r="D254" s="71"/>
       <c r="E254" s="72" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F254" s="140">
         <f>IFERROR(VLOOKUP(E254,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11843,7 +11835,7 @@
       <c r="C255" s="139"/>
       <c r="D255" s="71"/>
       <c r="E255" s="72" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F255" s="140">
         <f>IFERROR(VLOOKUP(E255,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11858,7 +11850,7 @@
       <c r="B256" s="137"/>
       <c r="C256" s="139"/>
       <c r="D256" s="139" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E256" s="188"/>
       <c r="F256" s="140"/>
@@ -11872,7 +11864,7 @@
       <c r="B257" s="137"/>
       <c r="C257" s="139"/>
       <c r="D257" s="71" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E257" s="188"/>
       <c r="F257" s="140"/>
@@ -11887,7 +11879,7 @@
       <c r="C258" s="139"/>
       <c r="D258" s="71"/>
       <c r="E258" s="151" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F258" s="140">
         <f>IFERROR(VLOOKUP(E258,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11901,7 +11893,7 @@
       <c r="C259" s="139"/>
       <c r="D259" s="71"/>
       <c r="E259" s="72" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F259" s="140">
         <f>IFERROR(VLOOKUP(E259,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11915,7 +11907,7 @@
       <c r="C260" s="139"/>
       <c r="D260" s="71"/>
       <c r="E260" s="72" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F260" s="140">
         <f>IFERROR(VLOOKUP(E260,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11929,7 +11921,7 @@
       <c r="C261" s="139"/>
       <c r="D261" s="71"/>
       <c r="E261" s="72" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F261" s="140">
         <f>IFERROR(VLOOKUP(E261,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11943,7 +11935,7 @@
       <c r="C262" s="139"/>
       <c r="D262" s="71"/>
       <c r="E262" s="72" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F262" s="140">
         <f>IFERROR(VLOOKUP(E262,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11956,7 +11948,7 @@
       <c r="B263" s="137"/>
       <c r="C263" s="139"/>
       <c r="D263" s="71" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E263" s="188"/>
       <c r="F263" s="140"/>
@@ -11974,10 +11966,10 @@
       <c r="B264" s="137"/>
       <c r="C264" s="139"/>
       <c r="D264" s="71" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E264" s="72" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F264" s="140">
         <f>IFERROR(VLOOKUP(E264,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11997,7 +11989,7 @@
       <c r="C265" s="139"/>
       <c r="D265" s="71"/>
       <c r="E265" s="72" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F265" s="140">
         <f>IFERROR(VLOOKUP(E265,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12014,7 +12006,7 @@
       <c r="C266" s="139"/>
       <c r="D266" s="71"/>
       <c r="E266" s="72" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F266" s="140">
         <f>IFERROR(VLOOKUP(E266,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12031,7 +12023,7 @@
       <c r="C267" s="139"/>
       <c r="D267" s="71"/>
       <c r="E267" s="72" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F267" s="140">
         <f>IFERROR(VLOOKUP(E267,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12048,7 +12040,7 @@
       <c r="C268" s="139"/>
       <c r="D268" s="71"/>
       <c r="E268" s="72" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F268" s="140">
         <f>IFERROR(VLOOKUP(E268,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12064,7 +12056,7 @@
       <c r="B269" s="76"/>
       <c r="C269" s="34"/>
       <c r="D269" s="71" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E269" s="188"/>
       <c r="F269" s="140"/>
@@ -12083,7 +12075,7 @@
       <c r="C270" s="34"/>
       <c r="D270" s="139"/>
       <c r="E270" s="72" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F270" s="140">
         <f>IFERROR(VLOOKUP(E270,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12101,7 +12093,7 @@
       <c r="C271" s="34"/>
       <c r="D271" s="139"/>
       <c r="E271" s="72" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F271" s="140">
         <f>IFERROR(VLOOKUP(E271,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12118,10 +12110,10 @@
       <c r="B272" s="76"/>
       <c r="C272" s="34"/>
       <c r="D272" s="71" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E272" s="72" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F272" s="140">
         <f>IFERROR(VLOOKUP(E272,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12138,7 +12130,7 @@
       <c r="C273" s="34"/>
       <c r="D273" s="71"/>
       <c r="E273" s="72" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F273" s="140">
         <f>IFERROR(VLOOKUP(E273,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12152,7 +12144,7 @@
       <c r="C274" s="34"/>
       <c r="D274" s="71"/>
       <c r="E274" s="72" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F274" s="140">
         <f>IFERROR(VLOOKUP(E274,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12166,7 +12158,7 @@
       <c r="C275" s="34"/>
       <c r="D275" s="71"/>
       <c r="E275" s="72" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F275" s="140">
         <f>IFERROR(VLOOKUP(E275,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12180,7 +12172,7 @@
       <c r="C276" s="34"/>
       <c r="D276" s="71"/>
       <c r="E276" s="151" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F276" s="140">
         <f>IFERROR(VLOOKUP(E276,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12194,7 +12186,7 @@
       <c r="C277" s="34"/>
       <c r="D277" s="71"/>
       <c r="E277" s="151" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F277" s="140">
         <f>IFERROR(VLOOKUP(E277,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12208,7 +12200,7 @@
       <c r="C278" s="34"/>
       <c r="D278" s="71"/>
       <c r="E278" s="151" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F278" s="140">
         <f>IFERROR(VLOOKUP(E278,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12222,7 +12214,7 @@
       <c r="C279" s="34"/>
       <c r="D279" s="71"/>
       <c r="E279" s="151" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F279" s="140">
         <f>IFERROR(VLOOKUP(E279,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12235,10 +12227,10 @@
       <c r="B280" s="76"/>
       <c r="C280" s="34"/>
       <c r="D280" s="191" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E280" s="192" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F280" s="193">
         <f>+Hoja1!E228+Hoja1!E229</f>
@@ -12249,7 +12241,7 @@
         <v>62810190.49</v>
       </c>
       <c r="H280" s="195" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="I280" s="134"/>
       <c r="J280" s="142"/>
@@ -12260,7 +12252,7 @@
       <c r="B281" s="76"/>
       <c r="C281" s="34"/>
       <c r="D281" s="71" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E281" s="71"/>
       <c r="F281" s="140">
@@ -12277,7 +12269,7 @@
       <c r="B282" s="76"/>
       <c r="C282" s="34"/>
       <c r="D282" s="71" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E282" s="71"/>
       <c r="F282" s="140">
@@ -12294,7 +12286,7 @@
       <c r="B283" s="76"/>
       <c r="C283" s="34"/>
       <c r="D283" s="139" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E283" s="139"/>
       <c r="F283" s="140">
@@ -12312,7 +12304,7 @@
       <c r="B284" s="76"/>
       <c r="C284" s="34"/>
       <c r="D284" s="139" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E284" s="139"/>
       <c r="F284" s="140"/>
@@ -12327,7 +12319,7 @@
       <c r="C285" s="34"/>
       <c r="D285" s="139"/>
       <c r="E285" s="72" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F285" s="140">
         <f>IFERROR(VLOOKUP(E285,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12341,7 +12333,7 @@
       <c r="C286" s="34"/>
       <c r="D286" s="139"/>
       <c r="E286" s="72" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F286" s="140">
         <f>IFERROR(VLOOKUP(E286,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12355,7 +12347,7 @@
       <c r="C287" s="34"/>
       <c r="D287" s="139"/>
       <c r="E287" s="139" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F287" s="140">
         <f>IFERROR(VLOOKUP(E287,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12369,7 +12361,7 @@
       <c r="C288" s="34"/>
       <c r="D288" s="139"/>
       <c r="E288" s="139" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F288" s="140">
         <f>IFERROR(VLOOKUP(E288,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12383,7 +12375,7 @@
       <c r="C289" s="34"/>
       <c r="D289" s="139"/>
       <c r="E289" s="139" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F289" s="140">
         <f>IFERROR(VLOOKUP(E289,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12397,7 +12389,7 @@
       <c r="C290" s="34"/>
       <c r="D290" s="139"/>
       <c r="E290" s="139" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F290" s="140">
         <f>IFERROR(VLOOKUP(E290,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12411,7 +12403,7 @@
       <c r="C291" s="34"/>
       <c r="D291" s="139"/>
       <c r="E291" s="72" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F291" s="140">
         <f>IFERROR(VLOOKUP(E291,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12425,7 +12417,7 @@
       <c r="C292" s="34"/>
       <c r="D292" s="139"/>
       <c r="E292" s="139" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F292" s="140">
         <f>IFERROR(VLOOKUP(E292,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12442,7 +12434,7 @@
       <c r="B293" s="76"/>
       <c r="C293" s="34"/>
       <c r="D293" s="71" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E293" s="71"/>
       <c r="F293" s="140"/>
@@ -12456,10 +12448,10 @@
       <c r="B294" s="76"/>
       <c r="C294" s="34"/>
       <c r="D294" s="71" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E294" s="72" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F294" s="140">
         <f>IFERROR(VLOOKUP(E294,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12481,7 +12473,7 @@
       <c r="C295" s="34"/>
       <c r="D295" s="71"/>
       <c r="E295" s="72" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F295" s="140">
         <f>IFERROR(VLOOKUP(E295,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12495,7 +12487,7 @@
       <c r="C296" s="34"/>
       <c r="D296" s="71"/>
       <c r="E296" s="72" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F296" s="140">
         <f>IFERROR(VLOOKUP(E296,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12509,7 +12501,7 @@
       <c r="C297" s="34"/>
       <c r="D297" s="71"/>
       <c r="E297" s="72" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F297" s="140">
         <f>IFERROR(VLOOKUP(E297,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12529,7 +12521,7 @@
       <c r="C298" s="34"/>
       <c r="D298" s="71"/>
       <c r="E298" s="72" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F298" s="140">
         <f>IFERROR(VLOOKUP(E298,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12549,7 +12541,7 @@
       <c r="C299" s="34"/>
       <c r="D299" s="71"/>
       <c r="E299" s="72" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F299" s="140">
         <f>IFERROR(VLOOKUP(E299,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12569,7 +12561,7 @@
       <c r="C300" s="34"/>
       <c r="D300" s="71"/>
       <c r="E300" s="72" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F300" s="140">
         <f>IFERROR(VLOOKUP(E300,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12589,7 +12581,7 @@
       <c r="C301" s="34"/>
       <c r="D301" s="71"/>
       <c r="E301" s="72" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F301" s="140">
         <f>IFERROR(VLOOKUP(E301,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12608,7 +12600,7 @@
       <c r="B302" s="76"/>
       <c r="C302" s="34"/>
       <c r="D302" s="71" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E302" s="188"/>
       <c r="F302" s="140"/>
@@ -12623,7 +12615,7 @@
       <c r="C303" s="34"/>
       <c r="D303" s="71"/>
       <c r="E303" s="72" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F303" s="140">
         <f>IFERROR(VLOOKUP(E303,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12637,7 +12629,7 @@
       <c r="C304" s="34"/>
       <c r="D304" s="71"/>
       <c r="E304" s="72" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F304" s="140">
         <f>IFERROR(VLOOKUP(E304,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12651,7 +12643,7 @@
       <c r="C305" s="34"/>
       <c r="D305" s="71"/>
       <c r="E305" s="72" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F305" s="140">
         <f>IFERROR(VLOOKUP(E305,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12664,7 +12656,7 @@
       <c r="B306" s="76"/>
       <c r="C306" s="34"/>
       <c r="D306" s="71" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E306" s="188"/>
       <c r="F306" s="140">
@@ -12682,7 +12674,7 @@
       <c r="C307" s="34"/>
       <c r="D307" s="71"/>
       <c r="E307" s="72" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F307" s="140">
         <f>IFERROR(VLOOKUP(E307,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12697,10 +12689,10 @@
       <c r="B308" s="76"/>
       <c r="C308" s="34"/>
       <c r="D308" s="139" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E308" s="72" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F308" s="140">
         <f>IFERROR(VLOOKUP(E308,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12718,10 +12710,10 @@
       <c r="B309" s="76"/>
       <c r="C309" s="34"/>
       <c r="D309" s="139" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E309" s="72" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F309" s="140">
         <f>IFERROR(VLOOKUP(E309,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12739,10 +12731,10 @@
       <c r="B310" s="76"/>
       <c r="C310" s="34"/>
       <c r="D310" s="71" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E310" s="72" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F310" s="140">
         <f>IFERROR(VLOOKUP(E310,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12758,7 +12750,7 @@
       <c r="B311" s="76"/>
       <c r="C311" s="34"/>
       <c r="D311" s="71" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E311" s="188"/>
       <c r="F311" s="140">
@@ -12776,7 +12768,7 @@
       <c r="C312" s="34"/>
       <c r="D312" s="71"/>
       <c r="E312" s="72" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F312" s="140">
         <f>IFERROR(VLOOKUP(E312,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12790,7 +12782,7 @@
       <c r="C313" s="34"/>
       <c r="D313" s="71"/>
       <c r="E313" s="72" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F313" s="140">
         <f>IFERROR(VLOOKUP(E313,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12803,7 +12795,7 @@
       <c r="B314" s="76"/>
       <c r="C314" s="34"/>
       <c r="D314" s="71" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E314" s="71"/>
       <c r="F314" s="140">
@@ -12820,10 +12812,10 @@
       <c r="B315" s="76"/>
       <c r="C315" s="34"/>
       <c r="D315" s="71" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E315" s="71" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F315" s="140">
         <f>IFERROR(VLOOKUP(E315,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12840,7 +12832,7 @@
       <c r="C316" s="34"/>
       <c r="D316" s="71"/>
       <c r="E316" s="72" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F316" s="140">
         <f>IFERROR(VLOOKUP(E316,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12853,7 +12845,7 @@
       <c r="B317" s="76"/>
       <c r="C317" s="34"/>
       <c r="D317" s="139" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E317" s="72"/>
       <c r="F317" s="140">
@@ -12871,7 +12863,7 @@
       <c r="B318" s="76"/>
       <c r="C318" s="34"/>
       <c r="D318" s="71" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E318" s="71"/>
       <c r="F318" s="140"/>
@@ -12887,7 +12879,7 @@
       <c r="C319" s="34"/>
       <c r="D319" s="71"/>
       <c r="E319" s="72" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F319" s="140">
         <f>IFERROR(VLOOKUP(E319,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12902,7 +12894,7 @@
       <c r="C320" s="34"/>
       <c r="D320" s="71"/>
       <c r="E320" s="72" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F320" s="140">
         <f>IFERROR(VLOOKUP(E320,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12917,7 +12909,7 @@
       <c r="C321" s="34"/>
       <c r="D321" s="71"/>
       <c r="E321" s="72" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F321" s="140">
         <f>IFERROR(VLOOKUP(E321,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12932,7 +12924,7 @@
       <c r="B322" s="76"/>
       <c r="C322" s="34"/>
       <c r="D322" s="71" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E322" s="188"/>
       <c r="F322" s="140"/>
@@ -12947,7 +12939,7 @@
       <c r="C323" s="34"/>
       <c r="D323" s="71"/>
       <c r="E323" s="72" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F323" s="140">
         <f>IFERROR(VLOOKUP(E323,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12961,7 +12953,7 @@
       <c r="C324" s="34"/>
       <c r="D324" s="71"/>
       <c r="E324" s="72" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F324" s="140">
         <f>IFERROR(VLOOKUP(E324,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12975,7 +12967,7 @@
       <c r="C325" s="34"/>
       <c r="D325" s="71"/>
       <c r="E325" s="72" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F325" s="140">
         <f>IFERROR(VLOOKUP(E325,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12989,7 +12981,7 @@
       <c r="C326" s="34"/>
       <c r="D326" s="71"/>
       <c r="E326" s="72" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F326" s="140">
         <f>IFERROR(VLOOKUP(E326,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13003,7 +12995,7 @@
       <c r="C327" s="34"/>
       <c r="D327" s="71"/>
       <c r="E327" s="72" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F327" s="140">
         <f>IFERROR(VLOOKUP(E327,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13017,7 +13009,7 @@
       <c r="C328" s="34"/>
       <c r="D328" s="71"/>
       <c r="E328" s="72" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F328" s="140">
         <f>IFERROR(VLOOKUP(E328,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13031,7 +13023,7 @@
       <c r="C329" s="34"/>
       <c r="D329" s="71"/>
       <c r="E329" s="72" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F329" s="140">
         <f>IFERROR(VLOOKUP(E329,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13044,10 +13036,10 @@
       <c r="B330" s="76"/>
       <c r="C330" s="34"/>
       <c r="D330" s="71" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E330" s="72" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F330" s="140">
         <f>IFERROR(VLOOKUP(E330,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13065,7 +13057,7 @@
       <c r="C331" s="34"/>
       <c r="D331" s="71"/>
       <c r="E331" s="151" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F331" s="140">
         <f>IFERROR(VLOOKUP(E331,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13073,7 +13065,7 @@
       </c>
       <c r="G331" s="138"/>
       <c r="H331" s="150" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="332" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13082,7 +13074,7 @@
       <c r="C332" s="34"/>
       <c r="D332" s="71"/>
       <c r="E332" s="72" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F332" s="140">
         <f>IFERROR(VLOOKUP(E332,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13097,7 +13089,7 @@
       <c r="C333" s="34"/>
       <c r="D333" s="71"/>
       <c r="E333" s="72" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F333" s="140">
         <f>IFERROR(VLOOKUP(E333,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13112,7 +13104,7 @@
       <c r="C334" s="34"/>
       <c r="D334" s="71"/>
       <c r="E334" s="72" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F334" s="140">
         <f>IFERROR(VLOOKUP(E334,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13127,7 +13119,7 @@
       <c r="C335" s="34"/>
       <c r="D335" s="71"/>
       <c r="E335" s="72" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F335" s="140">
         <f>IFERROR(VLOOKUP(E335,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13142,7 +13134,7 @@
       <c r="C336" s="34"/>
       <c r="D336" s="71"/>
       <c r="E336" s="72" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F336" s="140">
         <f>IFERROR(VLOOKUP(E336,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13157,7 +13149,7 @@
       <c r="C337" s="34"/>
       <c r="D337" s="71"/>
       <c r="E337" s="72" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F337" s="140">
         <f>IFERROR(VLOOKUP(E337,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13171,7 +13163,7 @@
       <c r="B338" s="76"/>
       <c r="C338" s="34"/>
       <c r="D338" s="71" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E338" s="71"/>
       <c r="F338" s="140"/>
@@ -13185,10 +13177,10 @@
       <c r="B339" s="76"/>
       <c r="C339" s="34"/>
       <c r="D339" s="71" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E339" s="72" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F339" s="140">
         <f>IFERROR(VLOOKUP(E339,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13205,7 +13197,7 @@
       <c r="C340" s="34"/>
       <c r="D340" s="71"/>
       <c r="E340" s="71" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F340" s="140">
         <f>IFERROR(VLOOKUP(E340,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13219,7 +13211,7 @@
       <c r="C341" s="34"/>
       <c r="D341" s="71"/>
       <c r="E341" s="71" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F341" s="140">
         <f>IFERROR(VLOOKUP(E341,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13232,10 +13224,10 @@
       <c r="B342" s="76"/>
       <c r="C342" s="34"/>
       <c r="D342" s="71" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E342" s="72" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F342" s="140">
         <f>IFERROR(VLOOKUP(E342,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13252,7 +13244,7 @@
       <c r="C343" s="34"/>
       <c r="D343" s="71"/>
       <c r="E343" s="72" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F343" s="140">
         <f>IFERROR(VLOOKUP(E343,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13273,7 +13265,7 @@
       <c r="C344" s="34"/>
       <c r="D344" s="71"/>
       <c r="E344" s="72" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F344" s="140">
         <f>IFERROR(VLOOKUP(E344,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13294,7 +13286,7 @@
       <c r="C345" s="34"/>
       <c r="D345" s="71"/>
       <c r="E345" s="72" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F345" s="140">
         <f>IFERROR(VLOOKUP(E345,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13308,7 +13300,7 @@
       <c r="C346" s="34"/>
       <c r="D346" s="71"/>
       <c r="E346" s="72" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F346" s="140">
         <f>IFERROR(VLOOKUP(E346,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13322,7 +13314,7 @@
       <c r="C347" s="34"/>
       <c r="D347" s="71"/>
       <c r="E347" s="72" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F347" s="140">
         <f>IFERROR(VLOOKUP(E347,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13336,7 +13328,7 @@
       <c r="C348" s="34"/>
       <c r="D348" s="71"/>
       <c r="E348" s="72" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F348" s="140">
         <f>IFERROR(VLOOKUP(E348,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13350,7 +13342,7 @@
       <c r="C349" s="34"/>
       <c r="D349" s="71"/>
       <c r="E349" s="72" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F349" s="140">
         <f>IFERROR(VLOOKUP(E349,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13364,7 +13356,7 @@
       <c r="C350" s="34"/>
       <c r="D350" s="71"/>
       <c r="E350" s="151" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F350" s="140">
         <f>IFERROR(VLOOKUP(E350,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13372,7 +13364,7 @@
       </c>
       <c r="G350" s="138"/>
       <c r="H350" s="68" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13380,10 +13372,10 @@
       <c r="B351" s="76"/>
       <c r="C351" s="34"/>
       <c r="D351" s="71" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E351" s="72" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F351" s="140">
         <f>IFERROR(VLOOKUP(E351,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13406,7 +13398,7 @@
       <c r="C352" s="34"/>
       <c r="D352" s="71"/>
       <c r="E352" s="72" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F352" s="140">
         <f>IFERROR(VLOOKUP(E352,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13421,7 +13413,7 @@
       <c r="C353" s="34"/>
       <c r="D353" s="71"/>
       <c r="E353" s="72" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F353" s="140">
         <f>IFERROR(VLOOKUP(E353,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13436,7 +13428,7 @@
       <c r="C354" s="34"/>
       <c r="D354" s="71"/>
       <c r="E354" s="72" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F354" s="140">
         <f>IFERROR(VLOOKUP(E354,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13451,7 +13443,7 @@
       <c r="C355" s="34"/>
       <c r="D355" s="71"/>
       <c r="E355" s="72" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F355" s="140">
         <f>IFERROR(VLOOKUP(E355,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13466,7 +13458,7 @@
       <c r="C356" s="34"/>
       <c r="D356" s="71"/>
       <c r="E356" s="72" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F356" s="140">
         <f>IFERROR(VLOOKUP(E356,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13481,7 +13473,7 @@
       <c r="C357" s="34"/>
       <c r="D357" s="71"/>
       <c r="E357" s="72" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F357" s="140">
         <f>IFERROR(VLOOKUP(E357,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13495,7 +13487,7 @@
       <c r="B358" s="76"/>
       <c r="C358" s="34"/>
       <c r="D358" s="139" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E358" s="72"/>
       <c r="F358" s="140"/>
@@ -13511,7 +13503,7 @@
       <c r="C359" s="34"/>
       <c r="D359" s="132"/>
       <c r="E359" s="72" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F359" s="140">
         <f>IFERROR(VLOOKUP(E359,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13526,7 +13518,7 @@
       <c r="C360" s="34"/>
       <c r="D360" s="132"/>
       <c r="E360" s="72" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="F360" s="140">
         <f>IFERROR(VLOOKUP(E360,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13540,7 +13532,7 @@
       <c r="B361" s="76"/>
       <c r="C361" s="34"/>
       <c r="D361" s="139" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E361" s="72"/>
       <c r="F361" s="140"/>
@@ -13556,7 +13548,7 @@
       <c r="C362" s="34"/>
       <c r="D362" s="139"/>
       <c r="E362" s="72" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F362" s="140">
         <f>IFERROR(VLOOKUP(E362,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13570,7 +13562,7 @@
       <c r="B363" s="76"/>
       <c r="C363" s="34"/>
       <c r="D363" s="71" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E363" s="71"/>
       <c r="F363" s="140"/>
@@ -13585,7 +13577,7 @@
       <c r="C364" s="34"/>
       <c r="D364" s="71"/>
       <c r="E364" s="72" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F364" s="140">
         <f>IFERROR(VLOOKUP(E364,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13599,7 +13591,7 @@
       <c r="C365" s="34"/>
       <c r="D365" s="71"/>
       <c r="E365" s="72" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="F365" s="140">
         <f>IFERROR(VLOOKUP(E365,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13613,7 +13605,7 @@
       <c r="C366" s="34"/>
       <c r="D366" s="71"/>
       <c r="E366" s="72" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F366" s="140">
         <f>IFERROR(VLOOKUP(E366,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13626,7 +13618,7 @@
       <c r="B367" s="76"/>
       <c r="C367" s="34"/>
       <c r="D367" s="71" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E367" s="188"/>
       <c r="F367" s="140"/>
@@ -13640,7 +13632,7 @@
       <c r="B368" s="76"/>
       <c r="C368" s="34"/>
       <c r="D368" s="71" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E368" s="188"/>
       <c r="F368" s="140"/>
@@ -13655,7 +13647,7 @@
       <c r="C369" s="34"/>
       <c r="D369" s="71"/>
       <c r="E369" s="72" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="F369" s="140">
         <f>IFERROR(VLOOKUP(E369,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13669,7 +13661,7 @@
       <c r="C370" s="34"/>
       <c r="D370" s="71"/>
       <c r="E370" s="72" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F370" s="140">
         <f>IFERROR(VLOOKUP(E370,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13683,7 +13675,7 @@
       <c r="C371" s="34"/>
       <c r="D371" s="71"/>
       <c r="E371" s="72" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="F371" s="140">
         <f>IFERROR(VLOOKUP(E371,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13697,7 +13689,7 @@
       <c r="C372" s="34"/>
       <c r="D372" s="71"/>
       <c r="E372" s="72" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F372" s="140">
         <f>IFERROR(VLOOKUP(E372,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13711,7 +13703,7 @@
       <c r="C373" s="34"/>
       <c r="D373" s="71"/>
       <c r="E373" s="72" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="F373" s="140">
         <f>IFERROR(VLOOKUP(E373,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13724,7 +13716,7 @@
       <c r="B374" s="76"/>
       <c r="C374" s="34"/>
       <c r="D374" s="71" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E374" s="76"/>
       <c r="F374" s="140"/>
@@ -13739,7 +13731,7 @@
       <c r="C375" s="34"/>
       <c r="D375" s="71"/>
       <c r="E375" s="72" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="F375" s="140">
         <f>IFERROR(VLOOKUP(E375,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13753,7 +13745,7 @@
       <c r="C376" s="34"/>
       <c r="D376" s="71"/>
       <c r="E376" s="72" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F376" s="140">
         <f>IFERROR(VLOOKUP(E376,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13767,7 +13759,7 @@
       <c r="C377" s="34"/>
       <c r="D377" s="71"/>
       <c r="E377" s="72" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="F377" s="140">
         <f>IFERROR(VLOOKUP(E377,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13781,7 +13773,7 @@
       <c r="C378" s="34"/>
       <c r="D378" s="71"/>
       <c r="E378" s="72" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F378" s="140">
         <f>IFERROR(VLOOKUP(E378,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13795,7 +13787,7 @@
       <c r="C379" s="34"/>
       <c r="D379" s="71"/>
       <c r="E379" s="72" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="F379" s="140">
         <f>IFERROR(VLOOKUP(E379,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13809,7 +13801,7 @@
       <c r="C380" s="34"/>
       <c r="D380" s="71"/>
       <c r="E380" s="72" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F380" s="140">
         <f>IFERROR(VLOOKUP(E380,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13823,7 +13815,7 @@
       <c r="C381" s="34"/>
       <c r="D381" s="71"/>
       <c r="E381" s="72" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="F381" s="140">
         <f>IFERROR(VLOOKUP(E381,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13837,7 +13829,7 @@
       <c r="C382" s="34"/>
       <c r="D382" s="71"/>
       <c r="E382" s="72" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F382" s="140">
         <f>IFERROR(VLOOKUP(E382,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13851,7 +13843,7 @@
       <c r="C383" s="34"/>
       <c r="D383" s="71"/>
       <c r="E383" s="151" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="F383" s="140">
         <f>IFERROR(VLOOKUP(E383,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13864,7 +13856,7 @@
       <c r="B384" s="76"/>
       <c r="C384" s="34"/>
       <c r="D384" s="71" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E384" s="71"/>
       <c r="F384" s="140"/>
@@ -13878,7 +13870,7 @@
       <c r="B385" s="76"/>
       <c r="C385" s="34"/>
       <c r="D385" s="139" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E385" s="72"/>
       <c r="F385" s="140"/>
@@ -13892,7 +13884,7 @@
       <c r="B386" s="76"/>
       <c r="C386" s="34"/>
       <c r="D386" s="71" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E386" s="71"/>
       <c r="F386" s="140"/>
@@ -13906,10 +13898,10 @@
       <c r="B387" s="76"/>
       <c r="C387" s="34"/>
       <c r="D387" s="71" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E387" s="72" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F387" s="140">
         <f>IFERROR(VLOOKUP(E387,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13926,7 +13918,7 @@
       <c r="C388" s="34"/>
       <c r="D388" s="71"/>
       <c r="E388" s="72" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F388" s="140">
         <f>IFERROR(VLOOKUP(E388,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13939,7 +13931,7 @@
       <c r="B389" s="76"/>
       <c r="C389" s="34"/>
       <c r="D389" s="71" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E389" s="71"/>
       <c r="F389" s="140"/>
@@ -13953,7 +13945,7 @@
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
       <c r="D390" s="71" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E390" s="71"/>
       <c r="F390" s="140"/>
@@ -13976,7 +13968,7 @@
       <c r="C391" s="34"/>
       <c r="D391" s="71"/>
       <c r="E391" s="72" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F391" s="140">
         <f>IFERROR(VLOOKUP(E391,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13998,7 +13990,7 @@
       <c r="C392" s="34"/>
       <c r="D392" s="71"/>
       <c r="E392" s="72" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="F392" s="140">
         <f>IFERROR(VLOOKUP(E392,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14019,10 +14011,10 @@
       <c r="B393" s="76"/>
       <c r="C393" s="34"/>
       <c r="D393" s="71" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E393" s="72" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14039,7 +14031,7 @@
       <c r="C394" s="34"/>
       <c r="D394" s="71"/>
       <c r="E394" s="72" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14053,7 +14045,7 @@
       <c r="C395" s="34"/>
       <c r="D395" s="71"/>
       <c r="E395" s="72" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="F395" s="140">
         <f>IFERROR(VLOOKUP(E395,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14067,7 +14059,7 @@
       <c r="C396" s="34"/>
       <c r="D396" s="71"/>
       <c r="E396" s="72" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F396" s="140">
         <f>IFERROR(VLOOKUP(E396,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14080,7 +14072,7 @@
       <c r="B397" s="76"/>
       <c r="C397" s="34"/>
       <c r="D397" s="71" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E397" s="188"/>
       <c r="F397" s="140"/>
@@ -14095,7 +14087,7 @@
       <c r="C398" s="34"/>
       <c r="D398" s="139"/>
       <c r="E398" s="72" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F398" s="140">
         <f>IFERROR(VLOOKUP(E398,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14109,7 +14101,7 @@
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
       <c r="D399" s="71" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E399" s="188"/>
       <c r="F399" s="140"/>
@@ -14124,7 +14116,7 @@
       <c r="C400" s="34"/>
       <c r="D400" s="71"/>
       <c r="E400" s="72" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F400" s="140">
         <f>IFERROR(VLOOKUP(E400,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14137,10 +14129,10 @@
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
       <c r="D401" s="71" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E401" s="71" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F401" s="140">
         <f>IFERROR(VLOOKUP(E401,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14156,7 +14148,7 @@
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
       <c r="D402" s="71" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E402" s="188"/>
       <c r="F402" s="140"/>
@@ -14171,7 +14163,7 @@
       <c r="C403" s="34"/>
       <c r="D403" s="71"/>
       <c r="E403" s="72" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F403" s="140">
         <f>IFERROR(VLOOKUP(E403,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14185,7 +14177,7 @@
       <c r="C404" s="34"/>
       <c r="D404" s="76"/>
       <c r="E404" s="72" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="F404" s="140">
         <f>IFERROR(VLOOKUP(E404,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14198,7 +14190,7 @@
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
       <c r="D405" s="71" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E405" s="72"/>
       <c r="F405" s="140"/>
@@ -14212,7 +14204,7 @@
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
       <c r="D406" s="71" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E406" s="71"/>
       <c r="F406" s="140"/>
@@ -14227,7 +14219,7 @@
       <c r="C407" s="34"/>
       <c r="D407" s="71"/>
       <c r="E407" s="151" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F407" s="140">
         <f>IFERROR(VLOOKUP(E407,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14241,7 +14233,7 @@
       <c r="C408" s="34"/>
       <c r="D408" s="71"/>
       <c r="E408" s="72" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="F408" s="140">
         <f>IFERROR(VLOOKUP(E408,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14255,7 +14247,7 @@
       <c r="C409" s="34"/>
       <c r="D409" s="71"/>
       <c r="E409" s="72" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F409" s="140">
         <f>IFERROR(VLOOKUP(E409,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14269,7 +14261,7 @@
       <c r="C410" s="34"/>
       <c r="D410" s="71"/>
       <c r="E410" s="72" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14283,7 +14275,7 @@
       <c r="C411" s="34"/>
       <c r="D411" s="71"/>
       <c r="E411" s="151" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F411" s="140">
         <f>IFERROR(VLOOKUP(E411,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14297,7 +14289,7 @@
       <c r="C412" s="34"/>
       <c r="D412" s="71"/>
       <c r="E412" s="72" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="F412" s="140">
         <f>IFERROR(VLOOKUP(E412,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14310,10 +14302,10 @@
       <c r="B413" s="76"/>
       <c r="C413" s="34"/>
       <c r="D413" s="139" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E413" s="72" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="F413" s="140">
         <f>IFERROR(VLOOKUP(E413,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14337,7 +14329,7 @@
       <c r="C414" s="34"/>
       <c r="D414" s="139"/>
       <c r="E414" s="72" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14357,7 +14349,7 @@
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
       <c r="D415" s="139" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E415" s="72"/>
       <c r="F415" s="140"/>
@@ -14371,10 +14363,10 @@
       <c r="B416" s="76"/>
       <c r="C416" s="34"/>
       <c r="D416" s="139" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E416" s="151" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F416" s="140">
         <f>IFERROR(VLOOKUP(E416,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14391,7 +14383,7 @@
       <c r="C417" s="34"/>
       <c r="D417" s="139"/>
       <c r="E417" s="72" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F417" s="140">
         <f>IFERROR(VLOOKUP(E417,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14407,7 +14399,7 @@
       <c r="C418" s="34"/>
       <c r="D418" s="139"/>
       <c r="E418" s="72" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="F418" s="140">
         <f>IFERROR(VLOOKUP(E418,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14423,7 +14415,7 @@
       <c r="C419" s="34"/>
       <c r="D419" s="139"/>
       <c r="E419" s="72" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14439,7 +14431,7 @@
       <c r="C420" s="34"/>
       <c r="D420" s="139"/>
       <c r="E420" s="72" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14455,7 +14447,7 @@
       <c r="C421" s="34"/>
       <c r="D421" s="139"/>
       <c r="E421" s="72" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F421" s="140">
         <f>IFERROR(VLOOKUP(E421,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14471,7 +14463,7 @@
       <c r="C422" s="34"/>
       <c r="D422" s="139"/>
       <c r="E422" s="72" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="F422" s="140">
         <f>IFERROR(VLOOKUP(E422,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14503,7 +14495,7 @@
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
       <c r="D424" s="71" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E424" s="71"/>
       <c r="F424" s="140">
@@ -14520,7 +14512,7 @@
       <c r="B425" s="76"/>
       <c r="C425" s="34"/>
       <c r="D425" s="71" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E425" s="71"/>
       <c r="F425" s="140"/>
@@ -14535,7 +14527,7 @@
       <c r="C426" s="34"/>
       <c r="D426" s="71"/>
       <c r="E426" s="72" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="F426" s="140">
         <f>IFERROR(VLOOKUP(E426,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14549,7 +14541,7 @@
       <c r="C427" s="34"/>
       <c r="D427" s="76"/>
       <c r="E427" s="71" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F427" s="140">
         <f>IFERROR(VLOOKUP(E427,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14563,7 +14555,7 @@
       <c r="C428" s="34"/>
       <c r="D428" s="76"/>
       <c r="E428" s="71" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14577,7 +14569,7 @@
       <c r="C429" s="34"/>
       <c r="D429" s="76"/>
       <c r="E429" s="71" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14591,7 +14583,7 @@
       <c r="C430" s="34"/>
       <c r="D430" s="76"/>
       <c r="E430" s="72" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F430" s="140">
         <f>IFERROR(VLOOKUP(E430,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14605,7 +14597,7 @@
       <c r="C431" s="34"/>
       <c r="D431" s="76"/>
       <c r="E431" s="72" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="F431" s="140">
         <f>IFERROR(VLOOKUP(E431,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14619,7 +14611,7 @@
       <c r="C432" s="34"/>
       <c r="D432" s="76"/>
       <c r="E432" s="72" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="F432" s="140">
         <f>IFERROR(VLOOKUP(E432,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14633,7 +14625,7 @@
       <c r="C433" s="34"/>
       <c r="D433" s="76"/>
       <c r="E433" s="72" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="F433" s="140">
         <f>IFERROR(VLOOKUP(E433,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14646,7 +14638,7 @@
       <c r="B434" s="76"/>
       <c r="C434" s="34"/>
       <c r="D434" s="71" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E434" s="71"/>
       <c r="F434" s="140"/>
@@ -14661,7 +14653,7 @@
       <c r="C435" s="34"/>
       <c r="D435" s="71"/>
       <c r="E435" s="72" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="F435" s="140">
         <f>IFERROR(VLOOKUP(E435,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14675,7 +14667,7 @@
       <c r="C436" s="34"/>
       <c r="D436" s="71"/>
       <c r="E436" s="72" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="F436" s="140">
         <f>IFERROR(VLOOKUP(E436,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14689,7 +14681,7 @@
       <c r="C437" s="34"/>
       <c r="D437" s="71"/>
       <c r="E437" s="72" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14703,7 +14695,7 @@
       <c r="C438" s="34"/>
       <c r="D438" s="71"/>
       <c r="E438" s="72" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="F438" s="140">
         <f>IFERROR(VLOOKUP(E438,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14716,7 +14708,7 @@
       <c r="B439" s="76"/>
       <c r="C439" s="34"/>
       <c r="D439" s="71" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E439" s="188"/>
       <c r="F439" s="140"/>
@@ -14730,7 +14722,7 @@
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
       <c r="D440" s="139" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E440" s="76"/>
       <c r="F440" s="140"/>
@@ -14745,7 +14737,7 @@
       <c r="C441" s="34"/>
       <c r="D441" s="139"/>
       <c r="E441" s="72" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="F441" s="140">
         <f>IFERROR(VLOOKUP(E441,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14759,7 +14751,7 @@
       <c r="C442" s="34"/>
       <c r="D442" s="139"/>
       <c r="E442" s="72" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="F442" s="140">
         <f>IFERROR(VLOOKUP(E442,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14772,7 +14764,7 @@
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
       <c r="D443" s="71" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E443" s="188"/>
       <c r="F443" s="140"/>
@@ -14787,7 +14779,7 @@
       <c r="C444" s="34"/>
       <c r="D444" s="71"/>
       <c r="E444" s="151" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="F444" s="140">
         <f>IFERROR(VLOOKUP(E444,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14801,7 +14793,7 @@
       <c r="C445" s="34"/>
       <c r="D445" s="71"/>
       <c r="E445" s="72" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="F445" s="140">
         <f>IFERROR(VLOOKUP(E445,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14817,7 +14809,7 @@
       <c r="C446" s="34"/>
       <c r="D446" s="71"/>
       <c r="E446" s="72" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="F446" s="140">
         <f>IFERROR(VLOOKUP(E446,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14833,7 +14825,7 @@
       <c r="C447" s="34"/>
       <c r="D447" s="71"/>
       <c r="E447" s="72" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="F447" s="140">
         <f>IFERROR(VLOOKUP(E447,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14848,7 +14840,7 @@
       <c r="B448" s="76"/>
       <c r="C448" s="34"/>
       <c r="D448" s="196" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E448" s="197"/>
       <c r="F448" s="198"/>
@@ -14863,7 +14855,7 @@
       <c r="C449" s="34"/>
       <c r="D449" s="71"/>
       <c r="E449" s="72" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="F449" s="140">
         <f>IFERROR(VLOOKUP(E449,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14877,7 +14869,7 @@
       <c r="C450" s="34"/>
       <c r="D450" s="71"/>
       <c r="E450" s="72" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="F450" s="140">
         <f>IFERROR(VLOOKUP(E450,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14891,7 +14883,7 @@
       <c r="C451" s="34"/>
       <c r="D451" s="71"/>
       <c r="E451" s="72" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F451" s="140">
         <f>IFERROR(VLOOKUP(E451,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14904,7 +14896,7 @@
       <c r="B452" s="76"/>
       <c r="C452" s="34"/>
       <c r="D452" s="71" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="E452" s="188"/>
       <c r="F452" s="140"/>
@@ -14919,7 +14911,7 @@
       <c r="C453" s="34"/>
       <c r="D453" s="71"/>
       <c r="E453" s="72" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F453" s="140">
         <f>IFERROR(VLOOKUP(E453,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14933,7 +14925,7 @@
       <c r="C454" s="34"/>
       <c r="D454" s="71"/>
       <c r="E454" s="72" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="F454" s="140">
         <f>IFERROR(VLOOKUP(E454,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14947,7 +14939,7 @@
       <c r="C455" s="34"/>
       <c r="D455" s="71"/>
       <c r="E455" s="72" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="F455" s="140">
         <f>IFERROR(VLOOKUP(E455,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14961,7 +14953,7 @@
       <c r="C456" s="34"/>
       <c r="D456" s="71"/>
       <c r="E456" s="72" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="F456" s="140">
         <f>IFERROR(VLOOKUP(E456,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14974,7 +14966,7 @@
       <c r="B457" s="76"/>
       <c r="C457" s="34"/>
       <c r="D457" s="71" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="E457" s="71"/>
       <c r="F457" s="140">
@@ -14991,7 +14983,7 @@
       <c r="B458" s="76"/>
       <c r="C458" s="34"/>
       <c r="D458" s="71" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E458" s="71"/>
       <c r="F458" s="140">
@@ -15008,7 +15000,7 @@
       <c r="B459" s="76"/>
       <c r="C459" s="34"/>
       <c r="D459" s="139" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="E459" s="72"/>
       <c r="F459" s="140"/>
@@ -15023,7 +15015,7 @@
       <c r="C460" s="34"/>
       <c r="D460" s="139"/>
       <c r="E460" s="72" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="F460" s="140">
         <f>IFERROR(VLOOKUP(E460,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15037,7 +15029,7 @@
       <c r="C461" s="34"/>
       <c r="D461" s="139"/>
       <c r="E461" s="72" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="F461" s="140">
         <f>IFERROR(VLOOKUP(E461,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15050,10 +15042,10 @@
       <c r="B462" s="76"/>
       <c r="C462" s="34"/>
       <c r="D462" s="71" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="E462" s="71" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F462" s="140">
         <f>IFERROR(VLOOKUP(E462,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15071,7 +15063,7 @@
       <c r="C463" s="34"/>
       <c r="D463" s="71"/>
       <c r="E463" s="72" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15086,7 +15078,7 @@
       <c r="C464" s="34"/>
       <c r="D464" s="71"/>
       <c r="E464" s="72" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="F464" s="140">
         <f>IFERROR(VLOOKUP(E464,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15101,7 +15093,7 @@
       <c r="C465" s="34"/>
       <c r="D465" s="71"/>
       <c r="E465" s="72" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15117,7 +15109,7 @@
       <c r="C466" s="34"/>
       <c r="D466" s="71"/>
       <c r="E466" s="72" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F466" s="140">
         <f>IFERROR(VLOOKUP(E466,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15133,7 +15125,7 @@
       <c r="C467" s="34"/>
       <c r="D467" s="71"/>
       <c r="E467" s="72" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F467" s="140">
         <f>IFERROR(VLOOKUP(E467,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15149,7 +15141,7 @@
       <c r="C468" s="34"/>
       <c r="D468" s="71"/>
       <c r="E468" s="72" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F468" s="140">
         <f>IFERROR(VLOOKUP(E468,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15165,7 +15157,7 @@
       <c r="C469" s="34"/>
       <c r="D469" s="71"/>
       <c r="E469" s="72" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F469" s="140">
         <f>IFERROR(VLOOKUP(E469,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15181,7 +15173,7 @@
       <c r="C470" s="34"/>
       <c r="D470" s="71"/>
       <c r="E470" s="72" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F470" s="140">
         <f>IFERROR(VLOOKUP(E470,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15196,7 +15188,7 @@
       <c r="B471" s="76"/>
       <c r="C471" s="34"/>
       <c r="D471" s="71" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="E471" s="188"/>
       <c r="F471" s="140"/>
@@ -15211,7 +15203,7 @@
       <c r="C472" s="34"/>
       <c r="D472" s="71"/>
       <c r="E472" s="72" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F472" s="140">
         <f>IFERROR(VLOOKUP(E472,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15225,7 +15217,7 @@
       <c r="C473" s="34"/>
       <c r="D473" s="71"/>
       <c r="E473" s="72" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F473" s="140">
         <f>IFERROR(VLOOKUP(E473,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15239,7 +15231,7 @@
       <c r="C474" s="34"/>
       <c r="D474" s="71"/>
       <c r="E474" s="72" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F474" s="140">
         <f>IFERROR(VLOOKUP(E474,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15252,7 +15244,7 @@
       <c r="B475" s="76"/>
       <c r="C475" s="34"/>
       <c r="D475" s="139" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E475" s="188"/>
       <c r="F475" s="140">
@@ -15269,7 +15261,7 @@
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
       <c r="D476" s="71" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="E476" s="188"/>
       <c r="F476" s="140">
@@ -15286,7 +15278,7 @@
       <c r="B477" s="76"/>
       <c r="C477" s="34"/>
       <c r="D477" s="71" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E477" s="188"/>
       <c r="F477" s="140"/>
@@ -15301,7 +15293,7 @@
       <c r="C478" s="34"/>
       <c r="D478" s="71"/>
       <c r="E478" s="72" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F478" s="140">
         <f>IFERROR(VLOOKUP(E478,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15315,7 +15307,7 @@
       <c r="C479" s="34"/>
       <c r="D479" s="71"/>
       <c r="E479" s="72" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F479" s="140">
         <f>IFERROR(VLOOKUP(E479,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15328,10 +15320,10 @@
       <c r="B480" s="76"/>
       <c r="C480" s="34"/>
       <c r="D480" s="71" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="E480" s="72" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F480" s="140">
         <f>IFERROR(VLOOKUP(E480,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15348,7 +15340,7 @@
       <c r="C481" s="34"/>
       <c r="D481" s="71"/>
       <c r="E481" s="72" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15362,7 +15354,7 @@
       <c r="C482" s="34"/>
       <c r="D482" s="71"/>
       <c r="E482" s="72" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15375,10 +15367,10 @@
       <c r="B483" s="76"/>
       <c r="C483" s="34"/>
       <c r="D483" s="71" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="E483" s="72" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F483" s="140">
         <f>IFERROR(VLOOKUP(E483,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15394,7 +15386,7 @@
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
       <c r="D484" s="71" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E484" s="71"/>
       <c r="F484" s="140">
@@ -15411,7 +15403,7 @@
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
       <c r="D485" s="139" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E485" s="72"/>
       <c r="F485" s="140">
@@ -15428,7 +15420,7 @@
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
       <c r="D486" s="71" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E486" s="68"/>
       <c r="F486" s="140">
@@ -15445,7 +15437,7 @@
       <c r="B487" s="76"/>
       <c r="C487" s="34"/>
       <c r="D487" s="71" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E487" s="132"/>
       <c r="F487" s="140">
@@ -15462,7 +15454,7 @@
       <c r="B488" s="76"/>
       <c r="C488" s="34"/>
       <c r="D488" s="71" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E488" s="132"/>
       <c r="F488" s="140">
@@ -15479,7 +15471,7 @@
       <c r="B489" s="76"/>
       <c r="C489" s="34"/>
       <c r="D489" s="71" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="E489" s="132"/>
       <c r="F489" s="140">
@@ -15496,7 +15488,7 @@
       <c r="B490" s="76"/>
       <c r="C490" s="34"/>
       <c r="D490" s="71" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="E490" s="132"/>
       <c r="F490" s="140">
@@ -15513,7 +15505,7 @@
       <c r="B491" s="76"/>
       <c r="C491" s="34"/>
       <c r="D491" s="139" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="E491" s="132"/>
       <c r="F491" s="140">
@@ -15530,7 +15522,7 @@
       <c r="B492" s="76"/>
       <c r="C492" s="34"/>
       <c r="D492" s="139" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E492" s="68"/>
       <c r="F492" s="140">
@@ -15547,7 +15539,7 @@
       <c r="B493" s="76"/>
       <c r="C493" s="34"/>
       <c r="D493" s="139" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E493" s="132"/>
       <c r="F493" s="140">
@@ -15564,7 +15556,7 @@
       <c r="B494" s="76"/>
       <c r="C494" s="34"/>
       <c r="D494" s="139" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E494" s="132"/>
       <c r="F494" s="140">
@@ -15581,7 +15573,7 @@
       <c r="B495" s="76"/>
       <c r="C495" s="34"/>
       <c r="D495" s="139" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E495" s="132"/>
       <c r="F495" s="140">
@@ -15598,10 +15590,10 @@
       <c r="B496" s="76"/>
       <c r="C496" s="34"/>
       <c r="D496" s="139" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E496" s="72" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="F496" s="140">
         <f>IFERROR(VLOOKUP(D496,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15617,7 +15609,7 @@
       <c r="B497" s="76"/>
       <c r="C497" s="34"/>
       <c r="D497" s="139" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E497" s="132"/>
       <c r="F497" s="140">
@@ -15635,7 +15627,7 @@
       <c r="B498" s="76"/>
       <c r="C498" s="34"/>
       <c r="D498" s="139" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="E498" s="132"/>
       <c r="F498" s="140">
@@ -15653,7 +15645,7 @@
       <c r="B499" s="76"/>
       <c r="C499" s="34"/>
       <c r="D499" s="139" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E499" s="132"/>
       <c r="F499" s="140">
@@ -15671,7 +15663,7 @@
       <c r="B500" s="76"/>
       <c r="C500" s="34"/>
       <c r="D500" s="139" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="E500" s="132"/>
       <c r="F500" s="140">
@@ -15689,7 +15681,7 @@
       <c r="B501" s="76"/>
       <c r="C501" s="34"/>
       <c r="D501" s="139" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="E501" s="132"/>
       <c r="F501" s="140">
@@ -15706,7 +15698,7 @@
       <c r="B502" s="76"/>
       <c r="C502" s="34"/>
       <c r="D502" s="139" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E502" s="132"/>
       <c r="F502" s="140">
@@ -15730,7 +15722,7 @@
         <v>55</v>
       </c>
       <c r="I503" s="199" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
     </row>
     <row r="504" ht="13.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15739,7 +15731,7 @@
       <c r="C504" s="34"/>
       <c r="D504" s="132"/>
       <c r="E504" s="200" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="F504" s="201">
         <f>SUM(F146:F502)</f>
@@ -15764,7 +15756,7 @@
       <c r="C505" s="34"/>
       <c r="D505" s="132"/>
       <c r="E505" s="203" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="F505" s="204">
         <f>+-'Anexo II'!E103</f>
@@ -15783,7 +15775,7 @@
       <c r="C506" s="34"/>
       <c r="D506" s="132"/>
       <c r="E506" s="207" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="F506" s="208">
         <f>+F504+F505</f>
@@ -15812,7 +15804,7 @@
       <c r="C508" s="211"/>
       <c r="D508" s="211"/>
       <c r="E508" s="211" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="F508" s="211">
         <f>+F280-F506</f>
@@ -28569,14 +28561,14 @@
       <c r="C1" s="222"/>
       <c r="D1" s="222"/>
       <c r="E1" s="223" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="F1" s="224"/>
       <c r="G1" s="224"/>
     </row>
     <row r="2" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="72" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B2" s="151"/>
       <c r="C2" s="195"/>
@@ -28587,7 +28579,7 @@
     </row>
     <row r="3" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="195"/>
@@ -28598,7 +28590,7 @@
     </row>
     <row r="4" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="72" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B4" s="151"/>
       <c r="C4" s="195"/>
@@ -28609,7 +28601,7 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="72" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B5" s="151"/>
       <c r="C5" s="195"/>
@@ -28620,7 +28612,7 @@
     </row>
     <row r="6" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B6" s="151"/>
       <c r="C6" s="195"/>
@@ -28631,7 +28623,7 @@
     </row>
     <row r="7" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="72" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B7" s="151"/>
       <c r="C7" s="195"/>
@@ -28642,7 +28634,7 @@
     </row>
     <row r="8" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="72" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B8" s="151"/>
       <c r="C8" s="195"/>
@@ -28653,7 +28645,7 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="B9" s="151"/>
       <c r="C9" s="195"/>
@@ -28664,7 +28656,7 @@
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="72" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B10" s="151"/>
       <c r="C10" s="195"/>
@@ -28675,7 +28667,7 @@
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="72" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B11" s="151"/>
       <c r="C11" s="195"/>
@@ -28686,7 +28678,7 @@
     </row>
     <row r="12" ht="12" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B12" s="151"/>
       <c r="C12" s="195"/>
@@ -28697,7 +28689,7 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="72" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B13" s="151"/>
       <c r="C13" s="195"/>
@@ -28708,7 +28700,7 @@
     </row>
     <row r="14" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="72" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B14" s="151"/>
       <c r="C14" s="195"/>
@@ -28719,7 +28711,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="72" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B15" s="151"/>
       <c r="C15" s="195"/>
@@ -28730,7 +28722,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="72" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B16" s="151"/>
       <c r="C16" s="195"/>
@@ -28741,7 +28733,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B17" s="151"/>
       <c r="C17" s="195"/>
@@ -28752,7 +28744,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="72" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B18" s="151"/>
       <c r="C18" s="195"/>
@@ -28763,7 +28755,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="72" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B19" s="151"/>
       <c r="C19" s="195"/>
@@ -28774,7 +28766,7 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="72" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B20" s="151"/>
       <c r="C20" s="195"/>
@@ -28785,7 +28777,7 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="72" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B21" s="151"/>
       <c r="C21" s="195"/>
@@ -28796,7 +28788,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="72" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B22" s="151"/>
       <c r="C22" s="195"/>
@@ -28807,7 +28799,7 @@
     </row>
     <row r="23" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B23" s="151"/>
       <c r="C23" s="195"/>
@@ -28818,7 +28810,7 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="72" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B24" s="195"/>
       <c r="C24" s="195"/>
@@ -28829,7 +28821,7 @@
     </row>
     <row r="25" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="72" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B25" s="195"/>
       <c r="C25" s="195"/>
@@ -28840,7 +28832,7 @@
     </row>
     <row r="26" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="72" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B26" s="151"/>
       <c r="C26" s="195"/>
@@ -28851,7 +28843,7 @@
     </row>
     <row r="27" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="72" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B27" s="151"/>
       <c r="C27" s="195"/>
@@ -28862,7 +28854,7 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="72" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
@@ -28873,7 +28865,7 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="72" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B29" s="151"/>
       <c r="C29" s="195"/>
@@ -28884,7 +28876,7 @@
     </row>
     <row r="30" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="72" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B30" s="151"/>
       <c r="C30" s="195"/>
@@ -28895,7 +28887,7 @@
     </row>
     <row r="31" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="72" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B31" s="151"/>
       <c r="C31" s="195"/>
@@ -28906,7 +28898,7 @@
     </row>
     <row r="32" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="72" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B32" s="151"/>
       <c r="C32" s="195"/>
@@ -28917,7 +28909,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="72" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B33" s="151"/>
       <c r="C33" s="195"/>
@@ -28928,7 +28920,7 @@
     </row>
     <row r="34" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="72" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B34" s="151"/>
       <c r="C34" s="195"/>
@@ -28939,7 +28931,7 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="72" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B35" s="151"/>
       <c r="C35" s="195"/>
@@ -28950,7 +28942,7 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="72" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B36" s="151"/>
       <c r="C36" s="195"/>
@@ -28961,7 +28953,7 @@
     </row>
     <row r="37" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="72" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B37" s="151"/>
       <c r="C37" s="195"/>
@@ -28972,7 +28964,7 @@
     </row>
     <row r="38" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="72" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B38" s="151"/>
       <c r="C38" s="195"/>
@@ -28983,7 +28975,7 @@
     </row>
     <row r="39" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="72" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="195"/>
@@ -28994,7 +28986,7 @@
     </row>
     <row r="40" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="72" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B40" s="151"/>
       <c r="C40" s="195"/>
@@ -29005,7 +28997,7 @@
     </row>
     <row r="41" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="72" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B41" s="151"/>
       <c r="C41" s="195"/>
@@ -29016,7 +29008,7 @@
     </row>
     <row r="42" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="72" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B42" s="151"/>
       <c r="C42" s="195"/>
@@ -29027,7 +29019,7 @@
     </row>
     <row r="43" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B43" s="151"/>
       <c r="C43" s="195"/>
@@ -29038,7 +29030,7 @@
     </row>
     <row r="44" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="72" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="220"/>
@@ -29049,7 +29041,7 @@
     </row>
     <row r="45" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="72" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B45" s="220"/>
       <c r="C45" s="220"/>
@@ -29060,7 +29052,7 @@
     </row>
     <row r="46" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="72" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B46" s="151"/>
       <c r="C46" s="195"/>
@@ -29077,10 +29069,10 @@
       <c r="E47" s="220"/>
       <c r="F47" s="220"/>
       <c r="G47" s="226" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="H47" s="227" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -29209,13 +29201,13 @@
       <c r="D58" s="232"/>
       <c r="E58" s="232"/>
       <c r="F58" s="232" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="G58" s="232"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="72" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="195"/>
@@ -29226,7 +29218,7 @@
     </row>
     <row r="60" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="72" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B60" s="151"/>
       <c r="C60" s="195"/>
@@ -29237,7 +29229,7 @@
     </row>
     <row r="61" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B61" s="151"/>
       <c r="C61" s="195"/>
@@ -29248,7 +29240,7 @@
     </row>
     <row r="62" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B62" s="151"/>
       <c r="C62" s="195"/>
@@ -29259,7 +29251,7 @@
     </row>
     <row r="63" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="72" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B63" s="151"/>
       <c r="C63" s="195"/>
@@ -29270,7 +29262,7 @@
     </row>
     <row r="64" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="72" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B64" s="151"/>
       <c r="C64" s="195"/>
@@ -29281,7 +29273,7 @@
     </row>
     <row r="65" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="72" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B65" s="151"/>
       <c r="C65" s="195"/>
@@ -29292,7 +29284,7 @@
     </row>
     <row r="66" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="72" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B66" s="151"/>
       <c r="C66" s="195"/>
@@ -29303,7 +29295,7 @@
     </row>
     <row r="67" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="72" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B67" s="151"/>
       <c r="C67" s="195"/>
@@ -29314,7 +29306,7 @@
     </row>
     <row r="68" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="72" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B68" s="151"/>
       <c r="C68" s="195"/>
@@ -29325,7 +29317,7 @@
     </row>
     <row r="69" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="72" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B69" s="151"/>
       <c r="C69" s="195"/>
@@ -29336,7 +29328,7 @@
     </row>
     <row r="70" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="72" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B70" s="151"/>
       <c r="C70" s="195"/>
@@ -29347,7 +29339,7 @@
     </row>
     <row r="71" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="72" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B71" s="151"/>
       <c r="C71" s="195"/>
@@ -29358,7 +29350,7 @@
     </row>
     <row r="72" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="72" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B72" s="151"/>
       <c r="C72" s="195"/>
@@ -29369,7 +29361,7 @@
     </row>
     <row r="73" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="72" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B73" s="151"/>
       <c r="C73" s="195"/>
@@ -29380,7 +29372,7 @@
     </row>
     <row r="74" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="72" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B74" s="151"/>
       <c r="C74" s="195"/>
@@ -29391,7 +29383,7 @@
     </row>
     <row r="75" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="72" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B75" s="151"/>
       <c r="C75" s="195"/>
@@ -29402,7 +29394,7 @@
     </row>
     <row r="76" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="72" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B76" s="151"/>
       <c r="C76" s="195"/>
@@ -29413,7 +29405,7 @@
     </row>
     <row r="77" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="72" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B77" s="151"/>
       <c r="C77" s="195"/>
@@ -29424,7 +29416,7 @@
     </row>
     <row r="78" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="72" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B78" s="151"/>
       <c r="C78" s="195"/>
@@ -29435,7 +29427,7 @@
     </row>
     <row r="79" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="72" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="B79" s="151"/>
       <c r="C79" s="195"/>
@@ -29446,7 +29438,7 @@
     </row>
     <row r="80" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="72" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="B80" s="151"/>
       <c r="C80" s="195"/>
@@ -29457,7 +29449,7 @@
     </row>
     <row r="81" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="72" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B81" s="151"/>
       <c r="C81" s="195"/>
@@ -29468,7 +29460,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="72" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B82" s="151"/>
       <c r="C82" s="195"/>
@@ -29479,7 +29471,7 @@
     </row>
     <row r="83" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="72" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B83" s="151"/>
       <c r="C83" s="195"/>
@@ -29490,7 +29482,7 @@
     </row>
     <row r="84" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="72" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B84" s="151"/>
       <c r="C84" s="195"/>
@@ -29501,7 +29493,7 @@
     </row>
     <row r="85" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="72" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B85" s="151"/>
       <c r="C85" s="195"/>
@@ -29512,7 +29504,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="72" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B86" s="151"/>
       <c r="C86" s="195"/>
@@ -29523,7 +29515,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B87" s="151"/>
       <c r="C87" s="195"/>
@@ -29534,7 +29526,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="72" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B88" s="151"/>
       <c r="C88" s="195"/>
@@ -29548,7 +29540,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="72" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="B89" s="151"/>
       <c r="C89" s="195"/>
@@ -29559,7 +29551,7 @@
     </row>
     <row r="90" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="72" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B90" s="151"/>
       <c r="C90" s="195"/>
@@ -29570,7 +29562,7 @@
     </row>
     <row r="91" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="72" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B91" s="151"/>
       <c r="C91" s="195"/>
@@ -29581,7 +29573,7 @@
     </row>
     <row r="92" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="72" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B92" s="151"/>
       <c r="C92" s="195"/>
@@ -29592,7 +29584,7 @@
     </row>
     <row r="93" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="72" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B93" s="151"/>
       <c r="C93" s="195"/>
@@ -29603,7 +29595,7 @@
     </row>
     <row r="94" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="72" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B94" s="151"/>
       <c r="C94" s="195"/>
@@ -29614,7 +29606,7 @@
     </row>
     <row r="95" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="72" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B95" s="151"/>
       <c r="C95" s="195"/>
@@ -29625,7 +29617,7 @@
     </row>
     <row r="96" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="72" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="B96" s="151"/>
       <c r="C96" s="195"/>
@@ -29636,7 +29628,7 @@
     </row>
     <row r="97" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="72" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B97" s="151"/>
       <c r="C97" s="195"/>
@@ -29647,7 +29639,7 @@
     </row>
     <row r="98" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="72" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="B98" s="151"/>
       <c r="C98" s="195"/>
@@ -29658,7 +29650,7 @@
     </row>
     <row r="99" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="72" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="B99" s="151"/>
       <c r="C99" s="195"/>
@@ -29669,7 +29661,7 @@
     </row>
     <row r="100" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="72" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B100" s="151"/>
       <c r="C100" s="195"/>
@@ -29680,7 +29672,7 @@
     </row>
     <row r="101" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="72" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B101" s="151"/>
       <c r="C101" s="195"/>
@@ -29691,7 +29683,7 @@
     </row>
     <row r="102" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="72" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B102" s="151"/>
       <c r="C102" s="195"/>
@@ -29702,7 +29694,7 @@
     </row>
     <row r="103" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="72" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B103" s="151"/>
       <c r="C103" s="195"/>
@@ -29713,7 +29705,7 @@
     </row>
     <row r="104" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="72" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B104" s="151"/>
       <c r="C104" s="195"/>
@@ -29724,7 +29716,7 @@
     </row>
     <row r="105" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B105" s="151"/>
       <c r="C105" s="195"/>
@@ -29735,7 +29727,7 @@
     </row>
     <row r="106" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="72" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B106" s="151"/>
       <c r="C106" s="195"/>
@@ -29746,7 +29738,7 @@
     </row>
     <row r="107" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="72" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B107" s="151"/>
       <c r="C107" s="195"/>
@@ -30205,7 +30197,7 @@
     </row>
     <row r="172" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="72" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B172" s="151"/>
       <c r="C172" s="195"/>
@@ -30216,7 +30208,7 @@
     </row>
     <row r="173" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="72" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B173" s="151"/>
       <c r="C173" s="195"/>
@@ -30227,7 +30219,7 @@
     </row>
     <row r="174" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="72" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B174" s="151"/>
       <c r="C174" s="195"/>
@@ -30238,7 +30230,7 @@
     </row>
     <row r="175" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="72" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B175" s="151"/>
       <c r="C175" s="195"/>
@@ -30249,7 +30241,7 @@
     </row>
     <row r="176" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="72" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B176" s="151"/>
       <c r="C176" s="195"/>
@@ -30260,7 +30252,7 @@
     </row>
     <row r="177" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="72" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B177" s="151"/>
       <c r="C177" s="195"/>
@@ -30271,7 +30263,7 @@
     </row>
     <row r="178" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="72" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B178" s="220"/>
       <c r="C178" s="220"/>
@@ -30282,7 +30274,7 @@
     </row>
     <row r="179" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="72" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B179" s="220"/>
       <c r="C179" s="220"/>
@@ -30293,7 +30285,7 @@
     </row>
     <row r="180" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="72" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B180" s="220"/>
       <c r="C180" s="220"/>
@@ -30304,7 +30296,7 @@
     </row>
     <row r="181" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="72" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B181" s="220"/>
       <c r="C181" s="220"/>
@@ -30315,7 +30307,7 @@
     </row>
     <row r="182" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="72" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B182" s="220"/>
       <c r="C182" s="220"/>
@@ -30326,7 +30318,7 @@
     </row>
     <row r="183" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="72" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B183" s="220"/>
       <c r="C183" s="220"/>
@@ -30337,7 +30329,7 @@
     </row>
     <row r="184" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="72" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B184" s="220"/>
       <c r="C184" s="220"/>
@@ -30348,7 +30340,7 @@
     </row>
     <row r="185" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="72" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B185" s="220"/>
       <c r="C185" s="220"/>
@@ -30359,7 +30351,7 @@
     </row>
     <row r="186" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="72" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B186" s="220"/>
       <c r="C186" s="220"/>
@@ -30370,7 +30362,7 @@
     </row>
     <row r="187" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="72" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B187" s="220"/>
       <c r="C187" s="220"/>
@@ -30381,7 +30373,7 @@
     </row>
     <row r="188" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="72" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B188" s="220"/>
       <c r="C188" s="220"/>
@@ -30392,7 +30384,7 @@
     </row>
     <row r="189" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="72" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B189" s="220"/>
       <c r="C189" s="220"/>
@@ -30403,7 +30395,7 @@
     </row>
     <row r="190" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="72" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B190" s="220"/>
       <c r="C190" s="220"/>
@@ -30414,7 +30406,7 @@
     </row>
     <row r="191" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="72" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B191" s="220"/>
       <c r="C191" s="220"/>
@@ -30425,7 +30417,7 @@
     </row>
     <row r="192" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="72" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B192" s="220"/>
       <c r="C192" s="220"/>
@@ -30436,7 +30428,7 @@
     </row>
     <row r="193" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="72" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B193" s="220"/>
       <c r="C193" s="220"/>
@@ -30447,7 +30439,7 @@
     </row>
     <row r="194" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="72" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B194" s="220"/>
       <c r="C194" s="220"/>
@@ -30458,7 +30450,7 @@
     </row>
     <row r="195" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="72" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B195" s="220"/>
       <c r="C195" s="220"/>
@@ -30469,7 +30461,7 @@
     </row>
     <row r="196" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="72" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B196" s="220"/>
       <c r="C196" s="220"/>
@@ -30480,7 +30472,7 @@
     </row>
     <row r="197" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="72" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B197" s="220"/>
       <c r="C197" s="220"/>
@@ -30491,7 +30483,7 @@
     </row>
     <row r="198" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="72" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B198" s="151"/>
       <c r="C198" s="195"/>
@@ -30550,7 +30542,7 @@
     </row>
     <row r="207" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="151" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B207" s="151"/>
       <c r="C207" s="195"/>
@@ -30561,7 +30553,7 @@
     </row>
     <row r="208" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="151" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B208" s="151"/>
       <c r="C208" s="195"/>
@@ -30572,7 +30564,7 @@
     </row>
     <row r="209" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="151" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B209" s="151"/>
       <c r="C209" s="195"/>
@@ -30583,7 +30575,7 @@
     </row>
     <row r="210" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="151" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B210" s="151"/>
       <c r="C210" s="195"/>
@@ -30600,18 +30592,18 @@
     </row>
     <row r="213" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="221" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B213" s="233"/>
       <c r="C213" s="233"/>
       <c r="D213" s="233"/>
       <c r="E213" s="223" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="72" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B214" s="220"/>
       <c r="C214" s="195"/>
@@ -30622,7 +30614,7 @@
     </row>
     <row r="215" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="72" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B215" s="151"/>
       <c r="C215" s="195"/>
@@ -30633,7 +30625,7 @@
     </row>
     <row r="216" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="72" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B216" s="151"/>
       <c r="C216" s="195"/>
@@ -30644,7 +30636,7 @@
     </row>
     <row r="217" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="72" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B217" s="151"/>
       <c r="C217" s="195"/>
@@ -30655,7 +30647,7 @@
     </row>
     <row r="218" ht="12.75" customHeight="1" spans="1:5" s="234" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="235" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B218" s="236"/>
       <c r="C218" s="41"/>
@@ -30666,7 +30658,7 @@
     </row>
     <row r="219" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="72" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B219" s="151"/>
       <c r="C219" s="195"/>
@@ -30677,7 +30669,7 @@
     </row>
     <row r="220" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="72" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B220" s="151"/>
       <c r="C220" s="195"/>
@@ -30688,7 +30680,7 @@
     </row>
     <row r="221" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="72" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B221" s="151"/>
       <c r="C221" s="195"/>
@@ -30699,7 +30691,7 @@
     </row>
     <row r="222" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="72" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B222" s="151"/>
       <c r="C222" s="195"/>
@@ -30710,7 +30702,7 @@
     </row>
     <row r="223" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="72" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B223" s="151"/>
       <c r="C223" s="195"/>
@@ -30721,7 +30713,7 @@
     </row>
     <row r="224" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="72" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="B224" s="151"/>
       <c r="C224" s="195"/>
@@ -30732,7 +30724,7 @@
     </row>
     <row r="225" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="72" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B225" s="151"/>
       <c r="C225" s="195"/>
@@ -30743,7 +30735,7 @@
     </row>
     <row r="226" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="72" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B226" s="151"/>
       <c r="C226" s="195"/>
@@ -30754,7 +30746,7 @@
     </row>
     <row r="227" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="72" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B227" s="151"/>
       <c r="C227" s="195"/>
@@ -30765,7 +30757,7 @@
     </row>
     <row r="228" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="72" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B228" s="151"/>
       <c r="C228" s="195"/>
@@ -30776,7 +30768,7 @@
     </row>
     <row r="229" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="72" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B229" s="151"/>
       <c r="C229" s="195"/>
@@ -30787,7 +30779,7 @@
     </row>
     <row r="230" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="72" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B230" s="151"/>
       <c r="C230" s="195"/>
@@ -30798,7 +30790,7 @@
     </row>
     <row r="231" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="72" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B231" s="151"/>
       <c r="C231" s="195"/>
@@ -30810,7 +30802,7 @@
     </row>
     <row r="232" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="72" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B232" s="151"/>
       <c r="C232" s="195"/>
@@ -30822,7 +30814,7 @@
     </row>
     <row r="233" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="72" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B233" s="151"/>
       <c r="C233" s="195"/>
@@ -30833,7 +30825,7 @@
     </row>
     <row r="234" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="72" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B234" s="151"/>
       <c r="C234" s="195"/>
@@ -30844,7 +30836,7 @@
     </row>
     <row r="235" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="72" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B235" s="151"/>
       <c r="C235" s="195"/>
@@ -30855,7 +30847,7 @@
     </row>
     <row r="236" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="72" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B236" s="151"/>
       <c r="C236" s="195"/>
@@ -30866,7 +30858,7 @@
     </row>
     <row r="237" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="72" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B237" s="151"/>
       <c r="C237" s="195"/>
@@ -30877,7 +30869,7 @@
     </row>
     <row r="238" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="72" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B238" s="151"/>
       <c r="C238" s="195"/>
@@ -30888,7 +30880,7 @@
     </row>
     <row r="239" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="72" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B239" s="151"/>
       <c r="C239" s="195"/>
@@ -30899,7 +30891,7 @@
     </row>
     <row r="240" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="72" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B240" s="151"/>
       <c r="C240" s="195"/>
@@ -30910,7 +30902,7 @@
     </row>
     <row r="241" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="72" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B241" s="151"/>
       <c r="C241" s="195"/>
@@ -30921,7 +30913,7 @@
     </row>
     <row r="242" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="72" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B242" s="151"/>
       <c r="C242" s="195"/>
@@ -30932,7 +30924,7 @@
     </row>
     <row r="243" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="72" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B243" s="151"/>
       <c r="C243" s="195"/>
@@ -30943,7 +30935,7 @@
     </row>
     <row r="244" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="72" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B244" s="151"/>
       <c r="C244" s="195"/>
@@ -30954,7 +30946,7 @@
     </row>
     <row r="245" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="72" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B245" s="151"/>
       <c r="C245" s="195"/>
@@ -30965,7 +30957,7 @@
     </row>
     <row r="246" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="72" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B246" s="151"/>
       <c r="C246" s="195"/>
@@ -30976,7 +30968,7 @@
     </row>
     <row r="247" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="72" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B247" s="151"/>
       <c r="C247" s="195"/>
@@ -30987,7 +30979,7 @@
     </row>
     <row r="248" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="72" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B248" s="151"/>
       <c r="C248" s="195"/>
@@ -30998,7 +30990,7 @@
     </row>
     <row r="249" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="72" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B249" s="151"/>
       <c r="C249" s="195"/>
@@ -31009,7 +31001,7 @@
     </row>
     <row r="250" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="72" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B250" s="151"/>
       <c r="C250" s="195"/>
@@ -31020,7 +31012,7 @@
     </row>
     <row r="251" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="72" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B251" s="151"/>
       <c r="C251" s="195"/>
@@ -31031,7 +31023,7 @@
     </row>
     <row r="252" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="72" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="B252" s="151"/>
       <c r="C252" s="195"/>
@@ -31042,7 +31034,7 @@
     </row>
     <row r="253" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="72" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B253" s="151"/>
       <c r="C253" s="195"/>
@@ -31053,7 +31045,7 @@
     </row>
     <row r="254" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="72" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B254" s="151"/>
       <c r="C254" s="195"/>
@@ -31064,7 +31056,7 @@
     </row>
     <row r="255" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="72" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B255" s="151"/>
       <c r="C255" s="195"/>
@@ -31075,7 +31067,7 @@
     </row>
     <row r="256" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="72" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="B256" s="151"/>
       <c r="C256" s="195"/>
@@ -31086,7 +31078,7 @@
     </row>
     <row r="257" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="72" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="B257" s="151"/>
       <c r="C257" s="195"/>
@@ -31097,7 +31089,7 @@
     </row>
     <row r="258" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="72" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B258" s="151"/>
       <c r="C258" s="195"/>
@@ -31108,7 +31100,7 @@
     </row>
     <row r="259" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="72" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B259" s="151"/>
       <c r="C259" s="195"/>
@@ -31119,7 +31111,7 @@
     </row>
     <row r="260" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="72" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B260" s="151"/>
       <c r="C260" s="195"/>
@@ -31130,7 +31122,7 @@
     </row>
     <row r="261" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="72" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B261" s="151"/>
       <c r="C261" s="195"/>
@@ -31141,7 +31133,7 @@
     </row>
     <row r="262" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="72" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="B262" s="151"/>
       <c r="C262" s="195"/>
@@ -31152,7 +31144,7 @@
     </row>
     <row r="263" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="72" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B263" s="151"/>
       <c r="C263" s="195"/>
@@ -31163,7 +31155,7 @@
     </row>
     <row r="264" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="72" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B264" s="151"/>
       <c r="C264" s="195"/>
@@ -31174,7 +31166,7 @@
     </row>
     <row r="265" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="72" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B265" s="151"/>
       <c r="C265" s="195"/>
@@ -31185,7 +31177,7 @@
     </row>
     <row r="266" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="72" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B266" s="151"/>
       <c r="C266" s="195"/>
@@ -31196,7 +31188,7 @@
     </row>
     <row r="267" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B267" s="151"/>
       <c r="C267" s="195"/>
@@ -31207,7 +31199,7 @@
     </row>
     <row r="268" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="72" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B268" s="151"/>
       <c r="C268" s="195"/>
@@ -31218,7 +31210,7 @@
     </row>
     <row r="269" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="72" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="B269" s="151"/>
       <c r="C269" s="195"/>
@@ -31229,7 +31221,7 @@
     </row>
     <row r="270" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="72" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="B270" s="151"/>
       <c r="C270" s="195"/>
@@ -31240,7 +31232,7 @@
     </row>
     <row r="271" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="72" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B271" s="151"/>
       <c r="C271" s="195"/>
@@ -31251,7 +31243,7 @@
     </row>
     <row r="272" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="72" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B272" s="151"/>
       <c r="C272" s="195"/>
@@ -31262,7 +31254,7 @@
     </row>
     <row r="273" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="72" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B273" s="151"/>
       <c r="C273" s="195"/>
@@ -31273,7 +31265,7 @@
     </row>
     <row r="274" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="72" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B274" s="151"/>
       <c r="C274" s="195"/>
@@ -31284,7 +31276,7 @@
     </row>
     <row r="275" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="72" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B275" s="151"/>
       <c r="C275" s="195"/>
@@ -31295,7 +31287,7 @@
     </row>
     <row r="276" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="72" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B276" s="151"/>
       <c r="C276" s="195"/>
@@ -31306,7 +31298,7 @@
     </row>
     <row r="277" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="72" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B277" s="151"/>
       <c r="C277" s="195"/>
@@ -31317,7 +31309,7 @@
     </row>
     <row r="278" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="72" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B278" s="151"/>
       <c r="C278" s="195"/>
@@ -31328,7 +31320,7 @@
     </row>
     <row r="279" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="72" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B279" s="151"/>
       <c r="C279" s="195"/>
@@ -31339,7 +31331,7 @@
     </row>
     <row r="280" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="72" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B280" s="151"/>
       <c r="C280" s="195"/>
@@ -31350,7 +31342,7 @@
     </row>
     <row r="281" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="72" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="195"/>
@@ -31361,7 +31353,7 @@
     </row>
     <row r="282" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="72" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B282" s="151"/>
       <c r="C282" s="195"/>
@@ -31372,7 +31364,7 @@
     </row>
     <row r="283" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="72" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B283" s="151"/>
       <c r="C283" s="195"/>
@@ -31383,7 +31375,7 @@
     </row>
     <row r="284" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="72" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B284" s="151"/>
       <c r="C284" s="195"/>
@@ -31394,7 +31386,7 @@
     </row>
     <row r="285" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="72" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B285" s="151"/>
       <c r="C285" s="195"/>
@@ -31405,7 +31397,7 @@
     </row>
     <row r="286" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="72" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B286" s="151"/>
       <c r="C286" s="195"/>
@@ -31416,7 +31408,7 @@
     </row>
     <row r="287" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="72" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B287" s="151"/>
       <c r="C287" s="195"/>
@@ -31427,7 +31419,7 @@
     </row>
     <row r="288" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="72" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="B288" s="151"/>
       <c r="C288" s="195"/>
@@ -31438,7 +31430,7 @@
     </row>
     <row r="289" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="72" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B289" s="151"/>
       <c r="C289" s="195"/>
@@ -31449,7 +31441,7 @@
     </row>
     <row r="290" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="72" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B290" s="151"/>
       <c r="C290" s="195"/>
@@ -31460,7 +31452,7 @@
     </row>
     <row r="291" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="72" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B291" s="151"/>
       <c r="C291" s="195"/>
@@ -31471,7 +31463,7 @@
     </row>
     <row r="292" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="72" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B292" s="151"/>
       <c r="C292" s="195"/>
@@ -31482,7 +31474,7 @@
     </row>
     <row r="293" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="72" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B293" s="151"/>
       <c r="C293" s="195"/>
@@ -31493,7 +31485,7 @@
     </row>
     <row r="294" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="72" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B294" s="151"/>
       <c r="C294" s="195"/>
@@ -31504,7 +31496,7 @@
     </row>
     <row r="295" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="72" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B295" s="151"/>
       <c r="C295" s="195"/>
@@ -31515,7 +31507,7 @@
     </row>
     <row r="296" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="72" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B296" s="151"/>
       <c r="C296" s="195"/>
@@ -31526,7 +31518,7 @@
     </row>
     <row r="297" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="72" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B297" s="151"/>
       <c r="C297" s="195"/>
@@ -31537,7 +31529,7 @@
     </row>
     <row r="298" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="72" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B298" s="151"/>
       <c r="C298" s="195"/>
@@ -31548,7 +31540,7 @@
     </row>
     <row r="299" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="72" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B299" s="151"/>
       <c r="C299" s="195"/>
@@ -31559,7 +31551,7 @@
     </row>
     <row r="300" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="72" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B300" s="151"/>
       <c r="C300" s="195"/>
@@ -31570,7 +31562,7 @@
     </row>
     <row r="301" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="72" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B301" s="151"/>
       <c r="C301" s="195"/>
@@ -31581,7 +31573,7 @@
     </row>
     <row r="302" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="72" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B302" s="151"/>
       <c r="C302" s="195"/>
@@ -31592,7 +31584,7 @@
     </row>
     <row r="303" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="72" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B303" s="151"/>
       <c r="C303" s="195"/>
@@ -31603,7 +31595,7 @@
     </row>
     <row r="304" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="72" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B304" s="151"/>
       <c r="C304" s="195"/>
@@ -31614,7 +31606,7 @@
     </row>
     <row r="305" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="72" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B305" s="151"/>
       <c r="C305" s="195"/>
@@ -31625,7 +31617,7 @@
     </row>
     <row r="306" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="72" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="B306" s="151"/>
       <c r="C306" s="195"/>
@@ -31636,7 +31628,7 @@
     </row>
     <row r="307" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="72" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B307" s="151"/>
       <c r="C307" s="195"/>
@@ -31647,7 +31639,7 @@
     </row>
     <row r="308" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="72" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B308" s="151"/>
       <c r="C308" s="195"/>
@@ -31658,7 +31650,7 @@
     </row>
     <row r="309" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="72" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B309" s="151"/>
       <c r="C309" s="195"/>
@@ -31669,7 +31661,7 @@
     </row>
     <row r="310" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="72" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B310" s="151"/>
       <c r="C310" s="195"/>
@@ -31680,7 +31672,7 @@
     </row>
     <row r="311" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="72" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B311" s="151"/>
       <c r="C311" s="195"/>
@@ -31691,7 +31683,7 @@
     </row>
     <row r="312" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="72" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B312" s="151"/>
       <c r="C312" s="195"/>
@@ -31702,7 +31694,7 @@
     </row>
     <row r="313" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="72" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B313" s="151"/>
       <c r="C313" s="195"/>
@@ -31713,7 +31705,7 @@
     </row>
     <row r="314" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="72" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B314" s="151"/>
       <c r="C314" s="195"/>
@@ -31725,7 +31717,7 @@
     </row>
     <row r="315" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="72" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B315" s="151"/>
       <c r="C315" s="195"/>
@@ -31737,7 +31729,7 @@
     </row>
     <row r="316" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="72" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B316" s="151"/>
       <c r="C316" s="195"/>
@@ -31749,7 +31741,7 @@
     </row>
     <row r="317" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="72" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B317" s="151"/>
       <c r="C317" s="195"/>
@@ -31760,7 +31752,7 @@
     </row>
     <row r="318" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="72" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B318" s="151"/>
       <c r="C318" s="195"/>
@@ -31771,7 +31763,7 @@
     </row>
     <row r="319" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="72" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B319" s="151"/>
       <c r="C319" s="195"/>
@@ -31782,7 +31774,7 @@
     </row>
     <row r="320" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="72" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B320" s="151"/>
       <c r="C320" s="195"/>
@@ -31793,7 +31785,7 @@
     </row>
     <row r="321" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="72" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B321" s="151"/>
       <c r="C321" s="195"/>
@@ -31804,7 +31796,7 @@
     </row>
     <row r="322" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="72" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B322" s="151"/>
       <c r="C322" s="195"/>
@@ -31815,7 +31807,7 @@
     </row>
     <row r="323" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="72" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B323" s="151"/>
       <c r="C323" s="195"/>
@@ -31826,7 +31818,7 @@
     </row>
     <row r="324" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="72" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B324" s="151"/>
       <c r="C324" s="195"/>
@@ -31837,7 +31829,7 @@
     </row>
     <row r="325" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="72" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B325" s="151"/>
       <c r="C325" s="195"/>
@@ -31848,7 +31840,7 @@
     </row>
     <row r="326" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="72" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B326" s="151"/>
       <c r="C326" s="195"/>
@@ -31859,7 +31851,7 @@
     </row>
     <row r="327" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="72" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B327" s="151"/>
       <c r="C327" s="195"/>
@@ -31870,7 +31862,7 @@
     </row>
     <row r="328" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="72" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B328" s="151"/>
       <c r="C328" s="195"/>
@@ -31881,7 +31873,7 @@
     </row>
     <row r="329" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="72" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B329" s="151"/>
       <c r="C329" s="195"/>
@@ -31892,7 +31884,7 @@
     </row>
     <row r="330" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="151" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B330" s="151"/>
       <c r="C330" s="195"/>
@@ -31903,7 +31895,7 @@
     </row>
     <row r="331" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="151" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B331" s="151"/>
       <c r="C331" s="195"/>
@@ -31914,7 +31906,7 @@
     </row>
     <row r="332" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="151" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B332" s="151"/>
       <c r="C332" s="195"/>
@@ -31925,7 +31917,7 @@
     </row>
     <row r="333" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="151" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B333" s="151"/>
       <c r="C333" s="195"/>
@@ -31936,7 +31928,7 @@
     </row>
     <row r="334" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="151" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B334" s="151"/>
       <c r="C334" s="195"/>
@@ -31947,7 +31939,7 @@
     </row>
     <row r="335" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="151" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B335" s="151"/>
       <c r="C335" s="195"/>
@@ -31958,7 +31950,7 @@
     </row>
     <row r="336" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="72" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B336" s="151"/>
       <c r="C336" s="195"/>
@@ -31969,7 +31961,7 @@
     </row>
     <row r="337" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="72" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B337" s="151"/>
       <c r="C337" s="195"/>
@@ -31980,7 +31972,7 @@
     </row>
     <row r="338" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="72" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B338" s="151"/>
       <c r="C338" s="195"/>
@@ -31996,10 +31988,10 @@
       <c r="D339" s="225"/>
       <c r="E339" s="195"/>
       <c r="F339" s="238" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G339" s="239" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="340" ht="10.15" customHeight="1" hidden="1" spans="1:7" s="235" customFormat="1" x14ac:dyDescent="0.25">
@@ -32207,7 +32199,7 @@
         <v>-476736080.9</v>
       </c>
       <c r="H366" s="220" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -32224,7 +32216,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="H367" s="72" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="368" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -32254,7 +32246,7 @@
       <c r="F369" s="220"/>
       <c r="G369" s="225"/>
       <c r="H369" s="72" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -32272,10 +32264,10 @@
       <c r="E371" s="140"/>
       <c r="F371" s="220"/>
       <c r="G371" s="244" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="H371" s="245" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="372" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -33143,14 +33135,9 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="19">
-        <f>+SALDOS!G39</f>
-        <v>0</v>
-      </c>
+      <c r="F54" s="19"/>
       <c r="G54" s="19"/>
     </row>
     <row r="55" ht="10.9" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -33177,7 +33164,7 @@
     <row r="57" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -33195,10 +33182,10 @@
     <row r="59" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="70" t="s">
         <v>130</v>
-      </c>
-      <c r="C59" s="70" t="s">
-        <v>131</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -33209,7 +33196,7 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="19">
@@ -33260,22 +33247,22 @@
     <row r="65" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="67" ht="11.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="70" t="s">
         <v>135</v>
-      </c>
-      <c r="C67" s="70" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="68" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -33283,7 +33270,7 @@
       <c r="B68" s="1"/>
       <c r="C68" s="70"/>
       <c r="D68" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="19">
@@ -33296,7 +33283,7 @@
       <c r="B69" s="1"/>
       <c r="C69" s="70"/>
       <c r="D69" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="19">
@@ -33309,7 +33296,7 @@
       <c r="B70" s="1"/>
       <c r="C70" s="70"/>
       <c r="D70" s="71" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="19">
@@ -33322,7 +33309,7 @@
       <c r="B71" s="1"/>
       <c r="C71" s="70"/>
       <c r="D71" s="71" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="19">
@@ -33347,10 +33334,10 @@
     <row r="73" ht="10.9" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" s="70" t="s">
         <v>141</v>
-      </c>
-      <c r="C73" s="70" t="s">
-        <v>142</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -33365,7 +33352,7 @@
       <c r="B74" s="10"/>
       <c r="C74" s="1"/>
       <c r="D74" s="71" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E74" s="76"/>
       <c r="F74" s="74">
@@ -33378,7 +33365,7 @@
       <c r="B75" s="10"/>
       <c r="C75" s="1"/>
       <c r="D75" s="71" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E75" s="76"/>
       <c r="F75" s="74">
@@ -33390,7 +33377,7 @@
       <c r="B76" s="10"/>
       <c r="C76" s="1"/>
       <c r="D76" s="71" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E76" s="76"/>
       <c r="F76" s="74">
@@ -33402,7 +33389,7 @@
       <c r="B77" s="10"/>
       <c r="C77" s="1"/>
       <c r="D77" s="71" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E77" s="76"/>
       <c r="F77" s="74">
@@ -33415,7 +33402,7 @@
       <c r="B78" s="10"/>
       <c r="C78" s="1"/>
       <c r="D78" s="71" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E78" s="76"/>
       <c r="F78" s="74">
@@ -33428,7 +33415,7 @@
       <c r="B79" s="10"/>
       <c r="C79" s="1"/>
       <c r="D79" s="71" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E79" s="76"/>
       <c r="F79" s="74">
@@ -33441,7 +33428,7 @@
       <c r="B80" s="10"/>
       <c r="C80" s="1"/>
       <c r="D80" s="72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E80" s="76"/>
       <c r="F80" s="74">
@@ -33454,7 +33441,7 @@
       <c r="B81" s="10"/>
       <c r="C81" s="1"/>
       <c r="D81" s="71" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E81" s="76"/>
       <c r="F81" s="74">
@@ -33467,7 +33454,7 @@
       <c r="B82" s="10"/>
       <c r="C82" s="1"/>
       <c r="D82" s="71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E82" s="76"/>
       <c r="F82" s="74">
@@ -33480,7 +33467,7 @@
       <c r="B83" s="10"/>
       <c r="C83" s="1"/>
       <c r="D83" s="71" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E83" s="76"/>
       <c r="F83" s="74">
@@ -33493,7 +33480,7 @@
       <c r="B84" s="10"/>
       <c r="C84" s="1"/>
       <c r="D84" s="71" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E84" s="76"/>
       <c r="F84" s="74">
@@ -33506,7 +33493,7 @@
       <c r="B85" s="10"/>
       <c r="C85" s="1"/>
       <c r="D85" s="71" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E85" s="76"/>
       <c r="F85" s="74">
@@ -33536,10 +33523,10 @@
     <row r="88" ht="13.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="70" t="s">
         <v>155</v>
-      </c>
-      <c r="C88" s="70" t="s">
-        <v>156</v>
       </c>
       <c r="D88" s="71"/>
       <c r="E88" s="76"/>
@@ -33550,7 +33537,7 @@
       <c r="B89" s="1"/>
       <c r="C89" s="70"/>
       <c r="D89" s="71" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E89" s="76"/>
       <c r="F89" s="74">
@@ -33563,7 +33550,7 @@
       <c r="B90" s="10"/>
       <c r="C90" s="1"/>
       <c r="D90" s="71" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E90" s="76"/>
       <c r="F90" s="74">
@@ -33576,7 +33563,7 @@
       <c r="B91" s="10"/>
       <c r="C91" s="1"/>
       <c r="D91" s="71" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E91" s="76"/>
       <c r="F91" s="74">
@@ -33589,7 +33576,7 @@
       <c r="B92" s="10"/>
       <c r="C92" s="1"/>
       <c r="D92" s="71" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E92" s="76"/>
       <c r="F92" s="74">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="870">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="871">
   <si>
     <t>ESTADO DE SITUACION PATRIMONIAL</t>
   </si>
@@ -1077,6 +1077,9 @@
   </si>
   <si>
     <t>122010000 - Depósito en garantía alquiler</t>
+  </si>
+  <si>
+    <t>123010000 - Titulos Públicos</t>
   </si>
   <si>
     <t>12301000 - Titulos Públicos</t>
@@ -8198,7 +8201,9 @@
     <row r="40" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="137"/>
       <c r="B40" s="137"/>
-      <c r="C40" s="139"/>
+      <c r="C40" s="151" t="s">
+        <v>347</v>
+      </c>
       <c r="D40" s="71" t="s">
         <v>347</v>
       </c>
@@ -8249,9 +8254,11 @@
     <row r="43" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="137"/>
       <c r="B43" s="137"/>
-      <c r="C43" s="139"/>
+      <c r="C43" s="151" t="s">
+        <v>350</v>
+      </c>
       <c r="D43" s="139" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E43" s="72"/>
       <c r="F43" s="140"/>
@@ -8269,10 +8276,10 @@
       <c r="A44" s="137"/>
       <c r="B44" s="137"/>
       <c r="C44" s="153" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D44" s="154" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E44" s="155"/>
       <c r="F44" s="156"/>
@@ -8281,17 +8288,17 @@
         <v>7137147.140000001</v>
       </c>
       <c r="H44" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="137"/>
       <c r="B45" s="137"/>
       <c r="C45" s="153" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D45" s="154" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E45" s="155"/>
       <c r="F45" s="156"/>
@@ -8300,17 +8307,17 @@
         <v>2163642.25</v>
       </c>
       <c r="H45" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="137"/>
       <c r="B46" s="137"/>
       <c r="C46" s="153" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D46" s="154" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E46" s="155"/>
       <c r="F46" s="156"/>
@@ -8319,17 +8326,17 @@
         <v>1676263.99</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="137"/>
       <c r="B47" s="137"/>
       <c r="C47" s="153" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D47" s="154" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E47" s="155"/>
       <c r="F47" s="156"/>
@@ -8338,17 +8345,17 @@
         <v>8463010.92</v>
       </c>
       <c r="H47" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="137"/>
       <c r="B48" s="137"/>
       <c r="C48" s="153" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D48" s="153" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E48" s="155"/>
       <c r="F48" s="156"/>
@@ -8357,17 +8364,17 @@
         <v>5117083.33</v>
       </c>
       <c r="H48" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="137"/>
       <c r="B49" s="137"/>
       <c r="C49" s="158" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D49" s="154" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E49" s="155"/>
       <c r="F49" s="156"/>
@@ -8376,7 +8383,7 @@
         <v>-3124708.59</v>
       </c>
       <c r="H49" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I49" s="134">
         <f>+'Anexo I'!J15</f>
@@ -8391,10 +8398,10 @@
       <c r="A50" s="137"/>
       <c r="B50" s="137"/>
       <c r="C50" s="158" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D50" s="154" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E50" s="155"/>
       <c r="F50" s="156"/>
@@ -8403,7 +8410,7 @@
         <v>-1499006.23</v>
       </c>
       <c r="H50" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I50" s="134">
         <f>+'Anexo I'!J17</f>
@@ -8418,10 +8425,10 @@
       <c r="A51" s="137"/>
       <c r="B51" s="137"/>
       <c r="C51" s="158" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D51" s="154" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E51" s="155"/>
       <c r="F51" s="156"/>
@@ -8430,7 +8437,7 @@
         <v>-776376.5700000001</v>
       </c>
       <c r="H51" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I51" s="134">
         <f>+'Anexo I'!J18</f>
@@ -8445,10 +8452,10 @@
       <c r="A52" s="137"/>
       <c r="B52" s="137"/>
       <c r="C52" s="153" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D52" s="153" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E52" s="155"/>
       <c r="F52" s="156"/>
@@ -8457,17 +8464,17 @@
         <v>20790195.080000002</v>
       </c>
       <c r="H52" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="137"/>
       <c r="B53" s="137"/>
       <c r="C53" s="158" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D53" s="154" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E53" s="155"/>
       <c r="F53" s="156"/>
@@ -8476,7 +8483,7 @@
         <v>-4436234.05</v>
       </c>
       <c r="H53" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I53" s="134">
         <f>+'Anexo I'!J19</f>
@@ -8491,10 +8498,10 @@
       <c r="A54" s="137"/>
       <c r="B54" s="137"/>
       <c r="C54" s="158" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D54" s="154" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E54" s="155"/>
       <c r="F54" s="156"/>
@@ -8503,7 +8510,7 @@
         <v>-5117083.33</v>
       </c>
       <c r="H54" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I54" s="134">
         <f>+'Anexo I'!J20</f>
@@ -8518,10 +8525,10 @@
       <c r="A55" s="137"/>
       <c r="B55" s="137"/>
       <c r="C55" s="158" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D55" s="154" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E55" s="155"/>
       <c r="F55" s="156"/>
@@ -8530,7 +8537,7 @@
         <v>-19606049.32</v>
       </c>
       <c r="H55" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I55" s="134">
         <f>+'Anexo I'!J21</f>
@@ -8545,10 +8552,10 @@
       <c r="A56" s="137"/>
       <c r="B56" s="137"/>
       <c r="C56" s="153" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D56" s="153" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E56" s="155"/>
       <c r="F56" s="156"/>
@@ -8557,17 +8564,17 @@
         <v>23184450.990000002</v>
       </c>
       <c r="H56" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="137"/>
       <c r="B57" s="137"/>
       <c r="C57" s="158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D57" s="154" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" s="155"/>
       <c r="F57" s="156"/>
@@ -8576,7 +8583,7 @@
         <v>-10204568.26</v>
       </c>
       <c r="H57" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I57" s="134">
         <f>+'Anexo I'!J16</f>
@@ -8591,10 +8598,10 @@
       <c r="A58" s="137"/>
       <c r="B58" s="137"/>
       <c r="C58" s="153" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D58" s="153" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E58" s="155"/>
       <c r="F58" s="156"/>
@@ -8603,17 +8610,17 @@
         <v>1598074.09</v>
       </c>
       <c r="H58" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="137"/>
       <c r="B59" s="137"/>
       <c r="C59" s="158" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D59" s="154" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E59" s="155"/>
       <c r="F59" s="156"/>
@@ -8622,7 +8629,7 @@
         <v>-617752.65</v>
       </c>
       <c r="H59" s="75" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I59" s="134">
         <f>+'Anexo I'!J22</f>
@@ -8639,10 +8646,10 @@
       <c r="A60" s="137"/>
       <c r="B60" s="137"/>
       <c r="C60" s="139" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E60" s="68"/>
       <c r="F60" s="140"/>
@@ -8660,10 +8667,10 @@
       <c r="A61" s="137"/>
       <c r="B61" s="137"/>
       <c r="C61" s="139" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D61" s="71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E61" s="68"/>
       <c r="F61" s="140"/>
@@ -8677,7 +8684,7 @@
         <v>2158175704.5099998</v>
       </c>
       <c r="J61" s="142" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K61" s="132"/>
       <c r="L61" s="132"/>
@@ -8696,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="142" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K62" s="132"/>
       <c r="L62" s="132"/>
@@ -8706,7 +8713,7 @@
       <c r="B63" s="137"/>
       <c r="C63" s="139"/>
       <c r="D63" s="72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E63" s="71"/>
       <c r="F63" s="140"/>
@@ -8724,7 +8731,7 @@
       <c r="B64" s="137"/>
       <c r="C64" s="139"/>
       <c r="D64" s="72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E64" s="71"/>
       <c r="F64" s="140"/>
@@ -8742,7 +8749,7 @@
       <c r="B65" s="137"/>
       <c r="C65" s="139"/>
       <c r="D65" s="72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E65" s="71"/>
       <c r="F65" s="140"/>
@@ -8760,7 +8767,7 @@
       <c r="B66" s="137"/>
       <c r="C66" s="139"/>
       <c r="D66" s="72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E66" s="71"/>
       <c r="F66" s="140"/>
@@ -8778,7 +8785,7 @@
       <c r="B67" s="137"/>
       <c r="C67" s="139"/>
       <c r="D67" s="72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E67" s="71"/>
       <c r="F67" s="140"/>
@@ -8796,7 +8803,7 @@
       <c r="B68" s="137"/>
       <c r="C68" s="139"/>
       <c r="D68" s="72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E68" s="71"/>
       <c r="F68" s="140"/>
@@ -8814,7 +8821,7 @@
       <c r="B69" s="137"/>
       <c r="C69" s="139"/>
       <c r="D69" s="72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E69" s="71"/>
       <c r="F69" s="140"/>
@@ -8832,7 +8839,7 @@
       <c r="B70" s="137"/>
       <c r="C70" s="139"/>
       <c r="D70" s="72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E70" s="71"/>
       <c r="F70" s="140"/>
@@ -8850,7 +8857,7 @@
       <c r="B71" s="137"/>
       <c r="C71" s="139"/>
       <c r="D71" s="72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E71" s="71"/>
       <c r="F71" s="140"/>
@@ -8868,7 +8875,7 @@
       <c r="B72" s="137"/>
       <c r="C72" s="139"/>
       <c r="D72" s="72" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E72" s="71"/>
       <c r="F72" s="140"/>
@@ -8886,7 +8893,7 @@
       <c r="B73" s="137"/>
       <c r="C73" s="139"/>
       <c r="D73" s="72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E73" s="71"/>
       <c r="F73" s="140"/>
@@ -8904,7 +8911,7 @@
       <c r="B74" s="137"/>
       <c r="C74" s="139"/>
       <c r="D74" s="72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E74" s="71"/>
       <c r="F74" s="140"/>
@@ -8922,7 +8929,7 @@
       <c r="B75" s="137"/>
       <c r="C75" s="139"/>
       <c r="D75" s="72" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E75" s="71"/>
       <c r="F75" s="140"/>
@@ -8940,7 +8947,7 @@
       <c r="B76" s="137"/>
       <c r="C76" s="139"/>
       <c r="D76" s="72" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E76" s="71"/>
       <c r="F76" s="140"/>
@@ -8958,7 +8965,7 @@
       <c r="B77" s="137"/>
       <c r="C77" s="139"/>
       <c r="D77" s="72" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E77" s="71"/>
       <c r="F77" s="140"/>
@@ -8976,7 +8983,7 @@
       <c r="B78" s="137"/>
       <c r="C78" s="139"/>
       <c r="D78" s="72" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E78" s="71"/>
       <c r="F78" s="140"/>
@@ -8994,7 +9001,7 @@
       <c r="B79" s="137"/>
       <c r="C79" s="139"/>
       <c r="D79" s="72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E79" s="71"/>
       <c r="F79" s="140"/>
@@ -9012,7 +9019,7 @@
       <c r="B80" s="137"/>
       <c r="C80" s="139"/>
       <c r="D80" s="72" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E80" s="71"/>
       <c r="F80" s="140"/>
@@ -9030,7 +9037,7 @@
       <c r="B81" s="137"/>
       <c r="C81" s="139"/>
       <c r="D81" s="72" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E81" s="71"/>
       <c r="F81" s="140"/>
@@ -9048,7 +9055,7 @@
       <c r="B82" s="137"/>
       <c r="C82" s="139"/>
       <c r="D82" s="72" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E82" s="71"/>
       <c r="F82" s="140"/>
@@ -9066,7 +9073,7 @@
       <c r="B83" s="137"/>
       <c r="C83" s="139"/>
       <c r="D83" s="72" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E83" s="71"/>
       <c r="F83" s="140"/>
@@ -9084,7 +9091,7 @@
       <c r="B84" s="137"/>
       <c r="C84" s="139"/>
       <c r="D84" s="72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E84" s="71"/>
       <c r="F84" s="140"/>
@@ -9102,7 +9109,7 @@
       <c r="B85" s="137"/>
       <c r="C85" s="139"/>
       <c r="D85" s="72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E85" s="71"/>
       <c r="F85" s="140"/>
@@ -9120,7 +9127,7 @@
       <c r="B86" s="137"/>
       <c r="C86" s="139"/>
       <c r="D86" s="72" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E86" s="71"/>
       <c r="F86" s="140"/>
@@ -9138,7 +9145,7 @@
       <c r="B87" s="137"/>
       <c r="C87" s="139"/>
       <c r="D87" s="72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E87" s="71"/>
       <c r="F87" s="140"/>
@@ -9156,7 +9163,7 @@
       <c r="B88" s="137"/>
       <c r="C88" s="139"/>
       <c r="D88" s="72" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E88" s="71"/>
       <c r="F88" s="140"/>
@@ -9174,7 +9181,7 @@
       <c r="B89" s="137"/>
       <c r="C89" s="139"/>
       <c r="D89" s="72" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E89" s="71"/>
       <c r="F89" s="140"/>
@@ -9192,7 +9199,7 @@
       <c r="B90" s="137"/>
       <c r="C90" s="139"/>
       <c r="D90" s="72" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E90" s="71"/>
       <c r="F90" s="140"/>
@@ -9210,7 +9217,7 @@
       <c r="B91" s="137"/>
       <c r="C91" s="139"/>
       <c r="D91" s="72" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E91" s="71"/>
       <c r="F91" s="140"/>
@@ -9228,7 +9235,7 @@
       <c r="B92" s="137"/>
       <c r="C92" s="139"/>
       <c r="D92" s="72" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E92" s="71"/>
       <c r="F92" s="140"/>
@@ -9246,7 +9253,7 @@
       <c r="B93" s="137"/>
       <c r="C93" s="139"/>
       <c r="D93" s="72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E93" s="71"/>
       <c r="F93" s="140"/>
@@ -9264,7 +9271,7 @@
       <c r="B94" s="137"/>
       <c r="C94" s="139"/>
       <c r="D94" s="72" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E94" s="71"/>
       <c r="F94" s="140"/>
@@ -9282,7 +9289,7 @@
       <c r="B95" s="137"/>
       <c r="C95" s="139"/>
       <c r="D95" s="72" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E95" s="71"/>
       <c r="F95" s="140"/>
@@ -9300,7 +9307,7 @@
       <c r="B96" s="137"/>
       <c r="C96" s="139"/>
       <c r="D96" s="72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E96" s="71"/>
       <c r="F96" s="140"/>
@@ -9318,7 +9325,7 @@
       <c r="B97" s="137"/>
       <c r="C97" s="139"/>
       <c r="D97" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E97" s="71"/>
       <c r="F97" s="140"/>
@@ -9336,7 +9343,7 @@
       <c r="B98" s="137"/>
       <c r="C98" s="139"/>
       <c r="D98" s="72" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E98" s="71"/>
       <c r="F98" s="140"/>
@@ -9354,7 +9361,7 @@
       <c r="B99" s="137"/>
       <c r="C99" s="139"/>
       <c r="D99" s="72" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E99" s="71"/>
       <c r="F99" s="140"/>
@@ -9372,7 +9379,7 @@
       <c r="B100" s="137"/>
       <c r="C100" s="139"/>
       <c r="D100" s="72" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E100" s="71"/>
       <c r="F100" s="140"/>
@@ -9390,7 +9397,7 @@
       <c r="B101" s="137"/>
       <c r="C101" s="139"/>
       <c r="D101" s="72" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E101" s="71"/>
       <c r="F101" s="140"/>
@@ -9408,7 +9415,7 @@
       <c r="B102" s="137"/>
       <c r="C102" s="139"/>
       <c r="D102" s="72" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E102" s="71"/>
       <c r="F102" s="140"/>
@@ -9426,7 +9433,7 @@
       <c r="B103" s="137"/>
       <c r="C103" s="139"/>
       <c r="D103" s="72" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E103" s="71"/>
       <c r="F103" s="140"/>
@@ -9444,7 +9451,7 @@
       <c r="B104" s="137"/>
       <c r="C104" s="139"/>
       <c r="D104" s="72" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E104" s="71"/>
       <c r="F104" s="140"/>
@@ -9462,7 +9469,7 @@
       <c r="B105" s="137"/>
       <c r="C105" s="139"/>
       <c r="D105" s="72" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E105" s="71"/>
       <c r="F105" s="140"/>
@@ -9480,7 +9487,7 @@
       <c r="B106" s="137"/>
       <c r="C106" s="139"/>
       <c r="D106" s="72" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E106" s="71"/>
       <c r="F106" s="140"/>
@@ -9498,7 +9505,7 @@
       <c r="B107" s="137"/>
       <c r="C107" s="139"/>
       <c r="D107" s="72" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E107" s="71"/>
       <c r="F107" s="140"/>
@@ -9516,7 +9523,7 @@
       <c r="B108" s="137"/>
       <c r="C108" s="139"/>
       <c r="D108" s="72" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E108" s="71"/>
       <c r="F108" s="140"/>
@@ -9534,7 +9541,7 @@
       <c r="B109" s="137"/>
       <c r="C109" s="139"/>
       <c r="D109" s="72" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E109" s="71"/>
       <c r="F109" s="140"/>
@@ -9552,7 +9559,7 @@
       <c r="B110" s="137"/>
       <c r="C110" s="139"/>
       <c r="D110" s="72" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E110" s="71"/>
       <c r="F110" s="140"/>
@@ -9570,7 +9577,7 @@
       <c r="B111" s="137"/>
       <c r="C111" s="139"/>
       <c r="D111" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E111" s="71"/>
       <c r="F111" s="140"/>
@@ -9588,7 +9595,7 @@
       <c r="B112" s="137"/>
       <c r="C112" s="139"/>
       <c r="D112" s="72" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E112" s="71"/>
       <c r="F112" s="140"/>
@@ -9606,7 +9613,7 @@
       <c r="B113" s="137"/>
       <c r="C113" s="139"/>
       <c r="D113" s="72" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E113" s="71"/>
       <c r="F113" s="140"/>
@@ -9624,7 +9631,7 @@
       <c r="B114" s="137"/>
       <c r="C114" s="139"/>
       <c r="D114" s="72" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E114" s="71"/>
       <c r="F114" s="140"/>
@@ -9647,7 +9654,7 @@
       <c r="G115" s="161"/>
       <c r="H115" s="74"/>
       <c r="I115" s="134" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J115" s="132"/>
       <c r="K115" s="132"/>
@@ -9667,7 +9674,7 @@
         <v>-106687518.28999999</v>
       </c>
       <c r="J116" s="142" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K116" s="132"/>
       <c r="L116" s="132"/>
@@ -9718,10 +9725,10 @@
       <c r="A120" s="137"/>
       <c r="B120" s="137"/>
       <c r="C120" s="151" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D120" s="71" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E120" s="71"/>
       <c r="F120" s="140"/>
@@ -9733,10 +9740,10 @@
       <c r="A121" s="137"/>
       <c r="B121" s="137"/>
       <c r="C121" s="72" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D121" s="139" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E121" s="68"/>
       <c r="F121" s="140"/>
@@ -9748,10 +9755,10 @@
       <c r="A122" s="137"/>
       <c r="B122" s="137"/>
       <c r="C122" s="139" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D122" s="71" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E122" s="68"/>
       <c r="F122" s="140"/>
@@ -9764,7 +9771,7 @@
       <c r="B123" s="137"/>
       <c r="C123" s="139"/>
       <c r="D123" s="71" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E123" s="71"/>
       <c r="F123" s="140"/>
@@ -9777,7 +9784,7 @@
       <c r="B124" s="137"/>
       <c r="C124" s="139"/>
       <c r="D124" s="71" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E124" s="71"/>
       <c r="F124" s="140"/>
@@ -9789,7 +9796,7 @@
       <c r="A125" s="137"/>
       <c r="B125" s="137"/>
       <c r="C125" s="139" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D125" s="71"/>
       <c r="E125" s="71"/>
@@ -9804,7 +9811,7 @@
       <c r="B126" s="137"/>
       <c r="C126" s="139"/>
       <c r="D126" s="71" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E126" s="71"/>
       <c r="F126" s="140"/>
@@ -9821,10 +9828,10 @@
       <c r="A127" s="137"/>
       <c r="B127" s="137"/>
       <c r="C127" s="139" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D127" s="139" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E127" s="68"/>
       <c r="F127" s="140"/>
@@ -9839,10 +9846,10 @@
       <c r="A128" s="137"/>
       <c r="B128" s="137"/>
       <c r="C128" s="139" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D128" s="139" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E128" s="68"/>
       <c r="F128" s="140"/>
@@ -9855,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="72" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="129" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9863,7 +9870,7 @@
       <c r="B129" s="137"/>
       <c r="C129" s="139"/>
       <c r="D129" s="139" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E129" s="68"/>
       <c r="F129" s="140"/>
@@ -9879,7 +9886,7 @@
       <c r="B130" s="137"/>
       <c r="C130" s="139"/>
       <c r="D130" s="139" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E130" s="68"/>
       <c r="F130" s="140"/>
@@ -9894,10 +9901,10 @@
       <c r="A131" s="137"/>
       <c r="B131" s="137"/>
       <c r="C131" s="72" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D131" s="139" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E131" s="68"/>
       <c r="F131" s="140"/>
@@ -9910,7 +9917,7 @@
       <c r="B132" s="137"/>
       <c r="C132" s="139"/>
       <c r="D132" s="71" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E132" s="71"/>
       <c r="F132" s="140"/>
@@ -9923,7 +9930,7 @@
       <c r="B133" s="137"/>
       <c r="C133" s="139"/>
       <c r="D133" s="139" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E133" s="71"/>
       <c r="F133" s="140"/>
@@ -9936,7 +9943,7 @@
       <c r="B134" s="137"/>
       <c r="C134" s="139"/>
       <c r="D134" s="139" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E134" s="71"/>
       <c r="F134" s="140"/>
@@ -9948,10 +9955,10 @@
       <c r="A135" s="137"/>
       <c r="B135" s="137"/>
       <c r="C135" s="139" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D135" s="139" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E135" s="71"/>
       <c r="F135" s="140"/>
@@ -9963,10 +9970,10 @@
       <c r="A136" s="137"/>
       <c r="B136" s="137"/>
       <c r="C136" s="72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D136" s="135" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E136" s="71"/>
       <c r="F136" s="140"/>
@@ -9978,10 +9985,10 @@
       <c r="A137" s="167"/>
       <c r="B137" s="167"/>
       <c r="C137" s="168" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D137" s="169" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E137" s="170"/>
       <c r="F137" s="171"/>
@@ -10010,10 +10017,10 @@
       <c r="A139" s="137"/>
       <c r="B139" s="137"/>
       <c r="C139" s="72" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D139" s="71" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E139" s="68"/>
       <c r="F139" s="140"/>
@@ -10026,10 +10033,10 @@
       <c r="A140" s="137"/>
       <c r="B140" s="137"/>
       <c r="C140" s="72" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D140" s="71" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E140" s="150"/>
       <c r="F140" s="140"/>
@@ -10043,10 +10050,10 @@
       <c r="A141" s="137"/>
       <c r="B141" s="137"/>
       <c r="C141" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D141" s="71" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E141" s="68"/>
       <c r="F141" s="140"/>
@@ -10059,7 +10066,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="J141" s="142" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K141" s="19"/>
       <c r="L141" s="132"/>
@@ -10068,10 +10075,10 @@
       <c r="A142" s="137"/>
       <c r="B142" s="137"/>
       <c r="C142" s="72" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D142" s="139" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E142" s="68"/>
       <c r="F142" s="140"/>
@@ -10084,7 +10091,7 @@
         <v>3354028747.869999</v>
       </c>
       <c r="J142" s="142" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K142" s="19"/>
       <c r="L142" s="132"/>
@@ -10094,7 +10101,7 @@
       <c r="B143" s="137"/>
       <c r="C143" s="72"/>
       <c r="D143" s="71" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E143" s="71"/>
       <c r="F143" s="140"/>
@@ -10108,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="142" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1" spans="1:14" s="166" customFormat="1" x14ac:dyDescent="0.25">
@@ -10148,7 +10155,7 @@
       <c r="B146" s="137"/>
       <c r="C146" s="139"/>
       <c r="D146" s="71" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E146" s="71"/>
       <c r="F146" s="140"/>
@@ -10164,7 +10171,7 @@
       <c r="B147" s="137"/>
       <c r="C147" s="139"/>
       <c r="D147" s="71" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E147" s="71"/>
       <c r="F147" s="140"/>
@@ -10178,7 +10185,7 @@
       <c r="B148" s="137"/>
       <c r="C148" s="139"/>
       <c r="D148" s="139" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E148" s="72"/>
       <c r="F148" s="140"/>
@@ -10192,7 +10199,7 @@
       <c r="B149" s="137"/>
       <c r="C149" s="139"/>
       <c r="D149" s="139" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E149" s="72"/>
       <c r="F149" s="140"/>
@@ -10206,10 +10213,10 @@
       <c r="B150" s="137"/>
       <c r="C150" s="139"/>
       <c r="D150" s="139" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E150" s="72" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F150" s="140"/>
       <c r="G150" s="138">
@@ -10222,7 +10229,7 @@
       <c r="B151" s="137"/>
       <c r="C151" s="139"/>
       <c r="D151" s="139" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E151" s="72"/>
       <c r="F151" s="140">
@@ -10239,7 +10246,7 @@
       <c r="B152" s="137"/>
       <c r="C152" s="139"/>
       <c r="D152" s="139" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E152" s="72"/>
       <c r="F152" s="140">
@@ -10256,7 +10263,7 @@
       <c r="B153" s="137"/>
       <c r="C153" s="139"/>
       <c r="D153" s="139" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E153" s="72"/>
       <c r="F153" s="140">
@@ -10268,7 +10275,7 @@
         <v>6840000</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10276,7 +10283,7 @@
       <c r="B154" s="137"/>
       <c r="C154" s="139"/>
       <c r="D154" s="71" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E154" s="71"/>
       <c r="F154" s="140">
@@ -10294,7 +10301,7 @@
       <c r="C155" s="139"/>
       <c r="D155" s="71"/>
       <c r="E155" s="72" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F155" s="140">
         <f>IFERROR(VLOOKUP(E155,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10310,7 +10317,7 @@
       <c r="C156" s="139"/>
       <c r="D156" s="71"/>
       <c r="E156" s="72" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F156" s="140">
         <f>IFERROR(VLOOKUP(E156,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10326,7 +10333,7 @@
       <c r="C157" s="139"/>
       <c r="D157" s="71"/>
       <c r="E157" s="72" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F157" s="140">
         <f>IFERROR(VLOOKUP(E157,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10342,7 +10349,7 @@
       <c r="C158" s="139"/>
       <c r="D158" s="71"/>
       <c r="E158" s="72" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F158" s="140">
         <f>IFERROR(VLOOKUP(E158,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10357,7 +10364,7 @@
       <c r="B159" s="137"/>
       <c r="C159" s="139"/>
       <c r="D159" s="71" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E159" s="71"/>
       <c r="F159" s="140"/>
@@ -10372,7 +10379,7 @@
       <c r="C160" s="139"/>
       <c r="D160" s="71"/>
       <c r="E160" s="72" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F160" s="140">
         <f>IFERROR(VLOOKUP(E160,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10386,7 +10393,7 @@
       <c r="C161" s="139"/>
       <c r="D161" s="71"/>
       <c r="E161" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F161" s="140">
         <f>IFERROR(VLOOKUP(E161,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10400,7 +10407,7 @@
       <c r="C162" s="139"/>
       <c r="D162" s="71"/>
       <c r="E162" s="72" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F162" s="140">
         <f>IFERROR(VLOOKUP(E162,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10414,7 +10421,7 @@
       <c r="C163" s="139"/>
       <c r="D163" s="71"/>
       <c r="E163" s="72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F163" s="140">
         <f>IFERROR(VLOOKUP(E163,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10428,7 +10435,7 @@
       <c r="C164" s="139"/>
       <c r="D164" s="71"/>
       <c r="E164" s="72" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F164" s="140">
         <f>IFERROR(VLOOKUP(E164,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10442,7 +10449,7 @@
       <c r="C165" s="139"/>
       <c r="D165" s="71"/>
       <c r="E165" s="72" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F165" s="140">
         <f>IFERROR(VLOOKUP(E165,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10456,7 +10463,7 @@
       <c r="C166" s="139"/>
       <c r="D166" s="71"/>
       <c r="E166" s="72" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F166" s="140">
         <f>IFERROR(VLOOKUP(E166,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10470,7 +10477,7 @@
       <c r="C167" s="139"/>
       <c r="D167" s="71"/>
       <c r="E167" s="72" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F167" s="140">
         <f>IFERROR(VLOOKUP(E167,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10483,7 +10490,7 @@
       <c r="B168" s="137"/>
       <c r="C168" s="139"/>
       <c r="D168" s="71" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E168" s="188"/>
       <c r="F168" s="140">
@@ -10501,7 +10508,7 @@
       <c r="B169" s="137"/>
       <c r="C169" s="139"/>
       <c r="D169" s="71" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E169" s="188"/>
       <c r="F169" s="140">
@@ -10518,7 +10525,7 @@
       <c r="B170" s="137"/>
       <c r="C170" s="139"/>
       <c r="D170" s="71" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E170" s="188"/>
       <c r="F170" s="140">
@@ -10541,7 +10548,7 @@
       <c r="B171" s="137"/>
       <c r="C171" s="139"/>
       <c r="D171" s="71" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E171" s="188"/>
       <c r="F171" s="150"/>
@@ -10556,7 +10563,7 @@
       <c r="C172" s="139"/>
       <c r="D172" s="71"/>
       <c r="E172" s="72" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F172" s="140">
         <f>IFERROR(VLOOKUP(E172,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10570,7 +10577,7 @@
       <c r="C173" s="139"/>
       <c r="D173" s="71"/>
       <c r="E173" s="72" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F173" s="140">
         <f>IFERROR(VLOOKUP(E173,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10584,7 +10591,7 @@
       <c r="C174" s="139"/>
       <c r="D174" s="71"/>
       <c r="E174" s="72" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F174" s="140">
         <f>IFERROR(VLOOKUP(E174,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10598,7 +10605,7 @@
       <c r="C175" s="139"/>
       <c r="D175" s="71"/>
       <c r="E175" s="72" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F175" s="140">
         <f>IFERROR(VLOOKUP(E175,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10612,7 +10619,7 @@
       <c r="C176" s="139"/>
       <c r="D176" s="71"/>
       <c r="E176" s="72" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F176" s="140">
         <f>IFERROR(VLOOKUP(E176,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10626,7 +10633,7 @@
       <c r="C177" s="139"/>
       <c r="D177" s="71"/>
       <c r="E177" s="72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F177" s="140">
         <f>IFERROR(VLOOKUP(E177,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10639,7 +10646,7 @@
       <c r="B178" s="137"/>
       <c r="C178" s="139"/>
       <c r="D178" s="71" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E178" s="71"/>
       <c r="F178" s="140">
@@ -10656,7 +10663,7 @@
       <c r="B179" s="137"/>
       <c r="C179" s="139"/>
       <c r="D179" s="71" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E179" s="71"/>
       <c r="F179" s="140"/>
@@ -10671,7 +10678,7 @@
       <c r="C180" s="139"/>
       <c r="D180" s="71"/>
       <c r="E180" s="72" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F180" s="140">
         <f>IFERROR(VLOOKUP(E180,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10685,7 +10692,7 @@
       <c r="C181" s="139"/>
       <c r="D181" s="71"/>
       <c r="E181" s="72" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F181" s="140">
         <f>IFERROR(VLOOKUP(E181,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10699,7 +10706,7 @@
       <c r="C182" s="139"/>
       <c r="D182" s="71"/>
       <c r="E182" s="72" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F182" s="140">
         <f>IFERROR(VLOOKUP(E182,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10713,7 +10720,7 @@
       <c r="C183" s="139"/>
       <c r="D183" s="71"/>
       <c r="E183" s="72" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F183" s="140">
         <f>IFERROR(VLOOKUP(E183,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10729,7 +10736,7 @@
       <c r="C184" s="139"/>
       <c r="D184" s="71"/>
       <c r="E184" s="72" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F184" s="140">
         <f>IFERROR(VLOOKUP(E184,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10755,7 +10762,7 @@
       <c r="B186" s="137"/>
       <c r="C186" s="139"/>
       <c r="D186" s="71" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E186" s="188"/>
       <c r="F186" s="140"/>
@@ -10769,10 +10776,10 @@
       <c r="B187" s="137"/>
       <c r="C187" s="139"/>
       <c r="D187" s="71" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E187" s="72" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F187" s="140">
         <f>IFERROR(VLOOKUP(E187,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10790,7 +10797,7 @@
       <c r="B188" s="137"/>
       <c r="C188" s="139"/>
       <c r="D188" s="71" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E188" s="76"/>
       <c r="F188" s="140"/>
@@ -10805,7 +10812,7 @@
       <c r="C189" s="139"/>
       <c r="D189" s="71"/>
       <c r="E189" s="72" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F189" s="140">
         <f>IFERROR(VLOOKUP(E189,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10819,7 +10826,7 @@
       <c r="C190" s="139"/>
       <c r="D190" s="71"/>
       <c r="E190" s="72" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F190" s="140">
         <f>IFERROR(VLOOKUP(E190,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10833,7 +10840,7 @@
       <c r="C191" s="139"/>
       <c r="D191" s="71"/>
       <c r="E191" s="72" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F191" s="140">
         <f>IFERROR(VLOOKUP(E191,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10847,7 +10854,7 @@
       <c r="C192" s="139"/>
       <c r="D192" s="71"/>
       <c r="E192" s="72" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F192" s="140">
         <f>IFERROR(VLOOKUP(E192,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10861,7 +10868,7 @@
       <c r="C193" s="139"/>
       <c r="D193" s="71"/>
       <c r="E193" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F193" s="140">
         <f>IFERROR(VLOOKUP(E193,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10875,7 +10882,7 @@
       <c r="C194" s="139"/>
       <c r="D194" s="71"/>
       <c r="E194" s="72" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F194" s="140">
         <f>IFERROR(VLOOKUP(E194,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10889,7 +10896,7 @@
       <c r="C195" s="139"/>
       <c r="D195" s="71"/>
       <c r="E195" s="72" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F195" s="140">
         <f>IFERROR(VLOOKUP(E195,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10903,7 +10910,7 @@
       <c r="C196" s="139"/>
       <c r="D196" s="71"/>
       <c r="E196" s="72" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F196" s="140">
         <f>IFERROR(VLOOKUP(E196,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10916,10 +10923,10 @@
       <c r="B197" s="137"/>
       <c r="C197" s="139"/>
       <c r="D197" s="139" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E197" s="72" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F197" s="140">
         <f>IFERROR(VLOOKUP(E197,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10936,7 +10943,7 @@
       <c r="C198" s="139"/>
       <c r="D198" s="139"/>
       <c r="E198" s="72" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F198" s="140">
         <f>IFERROR(VLOOKUP(E198,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10952,7 +10959,7 @@
       <c r="C199" s="139"/>
       <c r="D199" s="139"/>
       <c r="E199" s="72" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F199" s="140">
         <f>IFERROR(VLOOKUP(E199,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10967,10 +10974,10 @@
       <c r="B200" s="137"/>
       <c r="C200" s="139"/>
       <c r="D200" s="139" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E200" s="72" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F200" s="140">
         <f>IFERROR(VLOOKUP(E200,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10989,7 +10996,7 @@
       <c r="C201" s="139"/>
       <c r="D201" s="139"/>
       <c r="E201" s="72" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F201" s="140">
         <f>IFERROR(VLOOKUP(E201,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11004,7 +11011,7 @@
       <c r="B202" s="137"/>
       <c r="C202" s="139"/>
       <c r="D202" s="71" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E202" s="188"/>
       <c r="F202" s="140"/>
@@ -11025,10 +11032,10 @@
       <c r="B203" s="137"/>
       <c r="C203" s="139"/>
       <c r="D203" s="71" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E203" s="72" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F203" s="140">
         <f>IFERROR(VLOOKUP(E203,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11047,7 +11054,7 @@
       <c r="C204" s="139"/>
       <c r="D204" s="71"/>
       <c r="E204" s="71" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F204" s="140">
         <f>IFERROR(VLOOKUP(E204,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11060,7 +11067,7 @@
       <c r="B205" s="137"/>
       <c r="C205" s="139"/>
       <c r="D205" s="71" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E205" s="188"/>
       <c r="F205" s="140"/>
@@ -11075,7 +11082,7 @@
       <c r="C206" s="139"/>
       <c r="D206" s="71"/>
       <c r="E206" s="72" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F206" s="140">
         <f>IFERROR(VLOOKUP(E206,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11089,7 +11096,7 @@
       <c r="C207" s="139"/>
       <c r="D207" s="71"/>
       <c r="E207" s="188" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F207" s="140">
         <f>IFERROR(VLOOKUP(E207,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11102,7 +11109,7 @@
       <c r="B208" s="137"/>
       <c r="C208" s="139"/>
       <c r="D208" s="71" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E208" s="188"/>
       <c r="F208" s="140"/>
@@ -11117,7 +11124,7 @@
       <c r="C209" s="139"/>
       <c r="D209" s="71"/>
       <c r="E209" s="72" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F209" s="140">
         <f>IFERROR(VLOOKUP(E209,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11131,7 +11138,7 @@
       <c r="C210" s="139"/>
       <c r="D210" s="71"/>
       <c r="E210" s="72" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F210" s="140">
         <f>IFERROR(VLOOKUP(E210,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11147,7 +11154,7 @@
       <c r="C211" s="139"/>
       <c r="D211" s="71"/>
       <c r="E211" s="72" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F211" s="140">
         <f>IFERROR(VLOOKUP(E211,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11163,7 +11170,7 @@
       <c r="C212" s="139"/>
       <c r="D212" s="71"/>
       <c r="E212" s="72" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F212" s="140">
         <f>IFERROR(VLOOKUP(E212,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11178,7 +11185,7 @@
       <c r="B213" s="137"/>
       <c r="C213" s="139"/>
       <c r="D213" s="71" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E213" s="188"/>
       <c r="F213" s="140"/>
@@ -11194,7 +11201,7 @@
       <c r="C214" s="139"/>
       <c r="D214" s="71"/>
       <c r="E214" s="72" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F214" s="140">
         <f>IFERROR(VLOOKUP(E214,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11209,7 +11216,7 @@
       <c r="C215" s="139"/>
       <c r="D215" s="71"/>
       <c r="E215" s="72" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F215" s="140">
         <f>IFERROR(VLOOKUP(E215,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11224,7 +11231,7 @@
       <c r="C216" s="139"/>
       <c r="D216" s="71"/>
       <c r="E216" s="72" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F216" s="140">
         <f>IFERROR(VLOOKUP(E216,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11238,7 +11245,7 @@
       <c r="B217" s="137"/>
       <c r="C217" s="139"/>
       <c r="D217" s="71" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E217" s="188"/>
       <c r="F217" s="140"/>
@@ -11260,7 +11267,7 @@
       <c r="C218" s="139"/>
       <c r="D218" s="71"/>
       <c r="E218" s="72" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F218" s="140">
         <f>IFERROR(VLOOKUP(E218,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11274,7 +11281,7 @@
       <c r="C219" s="139"/>
       <c r="D219" s="71"/>
       <c r="E219" s="72" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F219" s="140">
         <f>IFERROR(VLOOKUP(E219,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11288,7 +11295,7 @@
       <c r="C220" s="139"/>
       <c r="D220" s="71"/>
       <c r="E220" s="72" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F220" s="140">
         <f>IFERROR(VLOOKUP(E220,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11302,7 +11309,7 @@
       <c r="C221" s="139"/>
       <c r="D221" s="71"/>
       <c r="E221" s="72" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F221" s="140">
         <f>IFERROR(VLOOKUP(E221,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11316,7 +11323,7 @@
       <c r="C222" s="139"/>
       <c r="D222" s="71"/>
       <c r="E222" s="72" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F222" s="140">
         <f>IFERROR(VLOOKUP(E222,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11330,7 +11337,7 @@
       <c r="C223" s="139"/>
       <c r="D223" s="71"/>
       <c r="E223" s="72" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F223" s="140">
         <f>IFERROR(VLOOKUP(E223,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11346,7 +11353,7 @@
       <c r="C224" s="139"/>
       <c r="D224" s="71"/>
       <c r="E224" s="72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F224" s="140">
         <f>IFERROR(VLOOKUP(E224,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11372,10 +11379,10 @@
       <c r="B226" s="137"/>
       <c r="C226" s="139"/>
       <c r="D226" s="71" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E226" s="72" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F226" s="140">
         <f>IFERROR(VLOOKUP(E226,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11394,7 +11401,7 @@
       <c r="C227" s="139"/>
       <c r="D227" s="71"/>
       <c r="E227" s="72" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F227" s="140">
         <f>IFERROR(VLOOKUP(E227,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11413,7 +11420,7 @@
       <c r="C228" s="139"/>
       <c r="D228" s="71"/>
       <c r="E228" s="72" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F228" s="140">
         <f>IFERROR(VLOOKUP(E228,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11445,10 +11452,10 @@
       <c r="B230" s="137"/>
       <c r="C230" s="139"/>
       <c r="D230" s="71" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E230" s="72" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F230" s="140">
         <f>IFERROR(VLOOKUP(E230,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11465,7 +11472,7 @@
       <c r="C231" s="139"/>
       <c r="D231" s="71"/>
       <c r="E231" s="72" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F231" s="140">
         <f>IFERROR(VLOOKUP(E231,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11478,7 +11485,7 @@
       <c r="B232" s="137"/>
       <c r="C232" s="139"/>
       <c r="D232" s="71" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E232" s="71"/>
       <c r="F232" s="140"/>
@@ -11492,7 +11499,7 @@
       <c r="B233" s="137"/>
       <c r="C233" s="139"/>
       <c r="D233" s="71" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E233" s="71"/>
       <c r="F233" s="140"/>
@@ -11506,10 +11513,10 @@
       <c r="B234" s="137"/>
       <c r="C234" s="139"/>
       <c r="D234" s="71" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E234" s="72" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F234" s="140">
         <f>IFERROR(VLOOKUP(E234,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11528,7 +11535,7 @@
       <c r="C235" s="139"/>
       <c r="D235" s="71"/>
       <c r="E235" s="72" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F235" s="140">
         <f>IFERROR(VLOOKUP(E235,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11544,7 +11551,7 @@
       <c r="C236" s="139"/>
       <c r="D236" s="71"/>
       <c r="E236" s="72" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F236" s="140">
         <f>IFERROR(VLOOKUP(E236,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11573,7 +11580,7 @@
       <c r="B238" s="137"/>
       <c r="C238" s="139"/>
       <c r="D238" s="71" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E238" s="71"/>
       <c r="F238" s="140"/>
@@ -11587,10 +11594,10 @@
       <c r="B239" s="137"/>
       <c r="C239" s="139"/>
       <c r="D239" s="71" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E239" s="71" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F239" s="140">
         <f>IFERROR(VLOOKUP(E239,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11607,7 +11614,7 @@
       <c r="C240" s="139"/>
       <c r="D240" s="71"/>
       <c r="E240" s="72" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F240" s="140">
         <f>IFERROR(VLOOKUP(E240,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11621,7 +11628,7 @@
       <c r="C241" s="139"/>
       <c r="D241" s="71"/>
       <c r="E241" s="151" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F241" s="140">
         <f>IFERROR(VLOOKUP(E241,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11635,7 +11642,7 @@
       <c r="C242" s="139"/>
       <c r="D242" s="71"/>
       <c r="E242" s="151" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F242" s="140">
         <f>IFERROR(VLOOKUP(E242,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11648,10 +11655,10 @@
       <c r="B243" s="137"/>
       <c r="C243" s="139"/>
       <c r="D243" s="71" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E243" s="72" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F243" s="140">
         <f>IFERROR(VLOOKUP(E243,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11670,7 +11677,7 @@
       <c r="C244" s="139"/>
       <c r="D244" s="71"/>
       <c r="E244" s="72" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F244" s="140">
         <f>IFERROR(VLOOKUP(E244,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11685,7 +11692,7 @@
       <c r="B245" s="137"/>
       <c r="C245" s="139"/>
       <c r="D245" s="71" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E245" s="71"/>
       <c r="F245" s="140"/>
@@ -11699,10 +11706,10 @@
       <c r="B246" s="137"/>
       <c r="C246" s="139"/>
       <c r="D246" s="71" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E246" s="72" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F246" s="140">
         <f>IFERROR(VLOOKUP(E246,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11719,7 +11726,7 @@
       <c r="C247" s="139"/>
       <c r="D247" s="71"/>
       <c r="E247" s="72" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F247" s="140">
         <f>IFERROR(VLOOKUP(E247,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11733,7 +11740,7 @@
       <c r="C248" s="139"/>
       <c r="D248" s="71"/>
       <c r="E248" s="72" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F248" s="140">
         <f>IFERROR(VLOOKUP(E248,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11747,7 +11754,7 @@
       <c r="C249" s="139"/>
       <c r="D249" s="71"/>
       <c r="E249" s="72" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F249" s="140">
         <f>IFERROR(VLOOKUP(E249,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11761,7 +11768,7 @@
       <c r="C250" s="139"/>
       <c r="D250" s="71"/>
       <c r="E250" s="72" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F250" s="140">
         <f>IFERROR(VLOOKUP(E250,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11775,7 +11782,7 @@
       <c r="C251" s="139"/>
       <c r="D251" s="71"/>
       <c r="E251" s="72" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F251" s="140">
         <f>IFERROR(VLOOKUP(E251,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11789,7 +11796,7 @@
       <c r="C252" s="139"/>
       <c r="D252" s="71"/>
       <c r="E252" s="72" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F252" s="140">
         <f>IFERROR(VLOOKUP(E252,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11803,7 +11810,7 @@
       <c r="C253" s="139"/>
       <c r="D253" s="71"/>
       <c r="E253" s="72" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F253" s="140">
         <f>IFERROR(VLOOKUP(E253,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11819,7 +11826,7 @@
       <c r="C254" s="139"/>
       <c r="D254" s="71"/>
       <c r="E254" s="72" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F254" s="140">
         <f>IFERROR(VLOOKUP(E254,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11835,7 +11842,7 @@
       <c r="C255" s="139"/>
       <c r="D255" s="71"/>
       <c r="E255" s="72" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F255" s="140">
         <f>IFERROR(VLOOKUP(E255,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11850,7 +11857,7 @@
       <c r="B256" s="137"/>
       <c r="C256" s="139"/>
       <c r="D256" s="139" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E256" s="188"/>
       <c r="F256" s="140"/>
@@ -11864,7 +11871,7 @@
       <c r="B257" s="137"/>
       <c r="C257" s="139"/>
       <c r="D257" s="71" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E257" s="188"/>
       <c r="F257" s="140"/>
@@ -11879,7 +11886,7 @@
       <c r="C258" s="139"/>
       <c r="D258" s="71"/>
       <c r="E258" s="151" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F258" s="140">
         <f>IFERROR(VLOOKUP(E258,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11893,7 +11900,7 @@
       <c r="C259" s="139"/>
       <c r="D259" s="71"/>
       <c r="E259" s="72" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F259" s="140">
         <f>IFERROR(VLOOKUP(E259,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11907,7 +11914,7 @@
       <c r="C260" s="139"/>
       <c r="D260" s="71"/>
       <c r="E260" s="72" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F260" s="140">
         <f>IFERROR(VLOOKUP(E260,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11921,7 +11928,7 @@
       <c r="C261" s="139"/>
       <c r="D261" s="71"/>
       <c r="E261" s="72" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F261" s="140">
         <f>IFERROR(VLOOKUP(E261,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11935,7 +11942,7 @@
       <c r="C262" s="139"/>
       <c r="D262" s="71"/>
       <c r="E262" s="72" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F262" s="140">
         <f>IFERROR(VLOOKUP(E262,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11948,7 +11955,7 @@
       <c r="B263" s="137"/>
       <c r="C263" s="139"/>
       <c r="D263" s="71" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E263" s="188"/>
       <c r="F263" s="140"/>
@@ -11966,10 +11973,10 @@
       <c r="B264" s="137"/>
       <c r="C264" s="139"/>
       <c r="D264" s="71" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E264" s="72" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F264" s="140">
         <f>IFERROR(VLOOKUP(E264,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11989,7 +11996,7 @@
       <c r="C265" s="139"/>
       <c r="D265" s="71"/>
       <c r="E265" s="72" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F265" s="140">
         <f>IFERROR(VLOOKUP(E265,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12006,7 +12013,7 @@
       <c r="C266" s="139"/>
       <c r="D266" s="71"/>
       <c r="E266" s="72" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F266" s="140">
         <f>IFERROR(VLOOKUP(E266,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12023,7 +12030,7 @@
       <c r="C267" s="139"/>
       <c r="D267" s="71"/>
       <c r="E267" s="72" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F267" s="140">
         <f>IFERROR(VLOOKUP(E267,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12040,7 +12047,7 @@
       <c r="C268" s="139"/>
       <c r="D268" s="71"/>
       <c r="E268" s="72" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F268" s="140">
         <f>IFERROR(VLOOKUP(E268,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12056,7 +12063,7 @@
       <c r="B269" s="76"/>
       <c r="C269" s="34"/>
       <c r="D269" s="71" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E269" s="188"/>
       <c r="F269" s="140"/>
@@ -12075,7 +12082,7 @@
       <c r="C270" s="34"/>
       <c r="D270" s="139"/>
       <c r="E270" s="72" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="F270" s="140">
         <f>IFERROR(VLOOKUP(E270,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12093,7 +12100,7 @@
       <c r="C271" s="34"/>
       <c r="D271" s="139"/>
       <c r="E271" s="72" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F271" s="140">
         <f>IFERROR(VLOOKUP(E271,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12110,10 +12117,10 @@
       <c r="B272" s="76"/>
       <c r="C272" s="34"/>
       <c r="D272" s="71" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E272" s="72" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F272" s="140">
         <f>IFERROR(VLOOKUP(E272,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12130,7 +12137,7 @@
       <c r="C273" s="34"/>
       <c r="D273" s="71"/>
       <c r="E273" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F273" s="140">
         <f>IFERROR(VLOOKUP(E273,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12144,7 +12151,7 @@
       <c r="C274" s="34"/>
       <c r="D274" s="71"/>
       <c r="E274" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F274" s="140">
         <f>IFERROR(VLOOKUP(E274,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12158,7 +12165,7 @@
       <c r="C275" s="34"/>
       <c r="D275" s="71"/>
       <c r="E275" s="72" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F275" s="140">
         <f>IFERROR(VLOOKUP(E275,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12172,7 +12179,7 @@
       <c r="C276" s="34"/>
       <c r="D276" s="71"/>
       <c r="E276" s="151" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F276" s="140">
         <f>IFERROR(VLOOKUP(E276,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12186,7 +12193,7 @@
       <c r="C277" s="34"/>
       <c r="D277" s="71"/>
       <c r="E277" s="151" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F277" s="140">
         <f>IFERROR(VLOOKUP(E277,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12200,7 +12207,7 @@
       <c r="C278" s="34"/>
       <c r="D278" s="71"/>
       <c r="E278" s="151" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F278" s="140">
         <f>IFERROR(VLOOKUP(E278,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12214,7 +12221,7 @@
       <c r="C279" s="34"/>
       <c r="D279" s="71"/>
       <c r="E279" s="151" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F279" s="140">
         <f>IFERROR(VLOOKUP(E279,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12227,10 +12234,10 @@
       <c r="B280" s="76"/>
       <c r="C280" s="34"/>
       <c r="D280" s="191" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E280" s="192" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F280" s="193">
         <f>+Hoja1!E228+Hoja1!E229</f>
@@ -12241,7 +12248,7 @@
         <v>62810190.49</v>
       </c>
       <c r="H280" s="195" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="I280" s="134"/>
       <c r="J280" s="142"/>
@@ -12252,7 +12259,7 @@
       <c r="B281" s="76"/>
       <c r="C281" s="34"/>
       <c r="D281" s="71" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E281" s="71"/>
       <c r="F281" s="140">
@@ -12269,7 +12276,7 @@
       <c r="B282" s="76"/>
       <c r="C282" s="34"/>
       <c r="D282" s="71" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E282" s="71"/>
       <c r="F282" s="140">
@@ -12286,7 +12293,7 @@
       <c r="B283" s="76"/>
       <c r="C283" s="34"/>
       <c r="D283" s="139" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E283" s="139"/>
       <c r="F283" s="140">
@@ -12304,7 +12311,7 @@
       <c r="B284" s="76"/>
       <c r="C284" s="34"/>
       <c r="D284" s="139" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E284" s="139"/>
       <c r="F284" s="140"/>
@@ -12319,7 +12326,7 @@
       <c r="C285" s="34"/>
       <c r="D285" s="139"/>
       <c r="E285" s="72" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F285" s="140">
         <f>IFERROR(VLOOKUP(E285,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12333,7 +12340,7 @@
       <c r="C286" s="34"/>
       <c r="D286" s="139"/>
       <c r="E286" s="72" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F286" s="140">
         <f>IFERROR(VLOOKUP(E286,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12347,7 +12354,7 @@
       <c r="C287" s="34"/>
       <c r="D287" s="139"/>
       <c r="E287" s="139" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F287" s="140">
         <f>IFERROR(VLOOKUP(E287,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12361,7 +12368,7 @@
       <c r="C288" s="34"/>
       <c r="D288" s="139"/>
       <c r="E288" s="139" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F288" s="140">
         <f>IFERROR(VLOOKUP(E288,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12375,7 +12382,7 @@
       <c r="C289" s="34"/>
       <c r="D289" s="139"/>
       <c r="E289" s="139" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F289" s="140">
         <f>IFERROR(VLOOKUP(E289,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12389,7 +12396,7 @@
       <c r="C290" s="34"/>
       <c r="D290" s="139"/>
       <c r="E290" s="139" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F290" s="140">
         <f>IFERROR(VLOOKUP(E290,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12403,7 +12410,7 @@
       <c r="C291" s="34"/>
       <c r="D291" s="139"/>
       <c r="E291" s="72" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F291" s="140">
         <f>IFERROR(VLOOKUP(E291,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12417,7 +12424,7 @@
       <c r="C292" s="34"/>
       <c r="D292" s="139"/>
       <c r="E292" s="139" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F292" s="140">
         <f>IFERROR(VLOOKUP(E292,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12434,7 +12441,7 @@
       <c r="B293" s="76"/>
       <c r="C293" s="34"/>
       <c r="D293" s="71" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E293" s="71"/>
       <c r="F293" s="140"/>
@@ -12448,10 +12455,10 @@
       <c r="B294" s="76"/>
       <c r="C294" s="34"/>
       <c r="D294" s="71" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E294" s="72" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="F294" s="140">
         <f>IFERROR(VLOOKUP(E294,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12473,7 +12480,7 @@
       <c r="C295" s="34"/>
       <c r="D295" s="71"/>
       <c r="E295" s="72" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F295" s="140">
         <f>IFERROR(VLOOKUP(E295,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12487,7 +12494,7 @@
       <c r="C296" s="34"/>
       <c r="D296" s="71"/>
       <c r="E296" s="72" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F296" s="140">
         <f>IFERROR(VLOOKUP(E296,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12501,7 +12508,7 @@
       <c r="C297" s="34"/>
       <c r="D297" s="71"/>
       <c r="E297" s="72" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F297" s="140">
         <f>IFERROR(VLOOKUP(E297,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12521,7 +12528,7 @@
       <c r="C298" s="34"/>
       <c r="D298" s="71"/>
       <c r="E298" s="72" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F298" s="140">
         <f>IFERROR(VLOOKUP(E298,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12541,7 +12548,7 @@
       <c r="C299" s="34"/>
       <c r="D299" s="71"/>
       <c r="E299" s="72" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F299" s="140">
         <f>IFERROR(VLOOKUP(E299,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12561,7 +12568,7 @@
       <c r="C300" s="34"/>
       <c r="D300" s="71"/>
       <c r="E300" s="72" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F300" s="140">
         <f>IFERROR(VLOOKUP(E300,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12581,7 +12588,7 @@
       <c r="C301" s="34"/>
       <c r="D301" s="71"/>
       <c r="E301" s="72" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F301" s="140">
         <f>IFERROR(VLOOKUP(E301,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12600,7 +12607,7 @@
       <c r="B302" s="76"/>
       <c r="C302" s="34"/>
       <c r="D302" s="71" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E302" s="188"/>
       <c r="F302" s="140"/>
@@ -12615,7 +12622,7 @@
       <c r="C303" s="34"/>
       <c r="D303" s="71"/>
       <c r="E303" s="72" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F303" s="140">
         <f>IFERROR(VLOOKUP(E303,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12629,7 +12636,7 @@
       <c r="C304" s="34"/>
       <c r="D304" s="71"/>
       <c r="E304" s="72" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F304" s="140">
         <f>IFERROR(VLOOKUP(E304,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12643,7 +12650,7 @@
       <c r="C305" s="34"/>
       <c r="D305" s="71"/>
       <c r="E305" s="72" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F305" s="140">
         <f>IFERROR(VLOOKUP(E305,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12656,7 +12663,7 @@
       <c r="B306" s="76"/>
       <c r="C306" s="34"/>
       <c r="D306" s="71" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E306" s="188"/>
       <c r="F306" s="140">
@@ -12674,7 +12681,7 @@
       <c r="C307" s="34"/>
       <c r="D307" s="71"/>
       <c r="E307" s="72" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F307" s="140">
         <f>IFERROR(VLOOKUP(E307,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12689,10 +12696,10 @@
       <c r="B308" s="76"/>
       <c r="C308" s="34"/>
       <c r="D308" s="139" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="E308" s="72" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F308" s="140">
         <f>IFERROR(VLOOKUP(E308,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12710,10 +12717,10 @@
       <c r="B309" s="76"/>
       <c r="C309" s="34"/>
       <c r="D309" s="139" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E309" s="72" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F309" s="140">
         <f>IFERROR(VLOOKUP(E309,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12731,10 +12738,10 @@
       <c r="B310" s="76"/>
       <c r="C310" s="34"/>
       <c r="D310" s="71" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E310" s="72" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="F310" s="140">
         <f>IFERROR(VLOOKUP(E310,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12750,7 +12757,7 @@
       <c r="B311" s="76"/>
       <c r="C311" s="34"/>
       <c r="D311" s="71" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E311" s="188"/>
       <c r="F311" s="140">
@@ -12768,7 +12775,7 @@
       <c r="C312" s="34"/>
       <c r="D312" s="71"/>
       <c r="E312" s="72" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F312" s="140">
         <f>IFERROR(VLOOKUP(E312,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12782,7 +12789,7 @@
       <c r="C313" s="34"/>
       <c r="D313" s="71"/>
       <c r="E313" s="72" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F313" s="140">
         <f>IFERROR(VLOOKUP(E313,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12795,7 +12802,7 @@
       <c r="B314" s="76"/>
       <c r="C314" s="34"/>
       <c r="D314" s="71" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E314" s="71"/>
       <c r="F314" s="140">
@@ -12812,10 +12819,10 @@
       <c r="B315" s="76"/>
       <c r="C315" s="34"/>
       <c r="D315" s="71" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E315" s="71" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="F315" s="140">
         <f>IFERROR(VLOOKUP(E315,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12832,7 +12839,7 @@
       <c r="C316" s="34"/>
       <c r="D316" s="71"/>
       <c r="E316" s="72" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F316" s="140">
         <f>IFERROR(VLOOKUP(E316,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12845,7 +12852,7 @@
       <c r="B317" s="76"/>
       <c r="C317" s="34"/>
       <c r="D317" s="139" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="E317" s="72"/>
       <c r="F317" s="140">
@@ -12863,7 +12870,7 @@
       <c r="B318" s="76"/>
       <c r="C318" s="34"/>
       <c r="D318" s="71" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E318" s="71"/>
       <c r="F318" s="140"/>
@@ -12879,7 +12886,7 @@
       <c r="C319" s="34"/>
       <c r="D319" s="71"/>
       <c r="E319" s="72" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F319" s="140">
         <f>IFERROR(VLOOKUP(E319,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12894,7 +12901,7 @@
       <c r="C320" s="34"/>
       <c r="D320" s="71"/>
       <c r="E320" s="72" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F320" s="140">
         <f>IFERROR(VLOOKUP(E320,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12909,7 +12916,7 @@
       <c r="C321" s="34"/>
       <c r="D321" s="71"/>
       <c r="E321" s="72" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F321" s="140">
         <f>IFERROR(VLOOKUP(E321,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12924,7 +12931,7 @@
       <c r="B322" s="76"/>
       <c r="C322" s="34"/>
       <c r="D322" s="71" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E322" s="188"/>
       <c r="F322" s="140"/>
@@ -12939,7 +12946,7 @@
       <c r="C323" s="34"/>
       <c r="D323" s="71"/>
       <c r="E323" s="72" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F323" s="140">
         <f>IFERROR(VLOOKUP(E323,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12953,7 +12960,7 @@
       <c r="C324" s="34"/>
       <c r="D324" s="71"/>
       <c r="E324" s="72" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F324" s="140">
         <f>IFERROR(VLOOKUP(E324,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12967,7 +12974,7 @@
       <c r="C325" s="34"/>
       <c r="D325" s="71"/>
       <c r="E325" s="72" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F325" s="140">
         <f>IFERROR(VLOOKUP(E325,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12981,7 +12988,7 @@
       <c r="C326" s="34"/>
       <c r="D326" s="71"/>
       <c r="E326" s="72" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F326" s="140">
         <f>IFERROR(VLOOKUP(E326,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12995,7 +13002,7 @@
       <c r="C327" s="34"/>
       <c r="D327" s="71"/>
       <c r="E327" s="72" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F327" s="140">
         <f>IFERROR(VLOOKUP(E327,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13009,7 +13016,7 @@
       <c r="C328" s="34"/>
       <c r="D328" s="71"/>
       <c r="E328" s="72" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F328" s="140">
         <f>IFERROR(VLOOKUP(E328,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13023,7 +13030,7 @@
       <c r="C329" s="34"/>
       <c r="D329" s="71"/>
       <c r="E329" s="72" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F329" s="140">
         <f>IFERROR(VLOOKUP(E329,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13036,10 +13043,10 @@
       <c r="B330" s="76"/>
       <c r="C330" s="34"/>
       <c r="D330" s="71" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E330" s="72" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="F330" s="140">
         <f>IFERROR(VLOOKUP(E330,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13057,7 +13064,7 @@
       <c r="C331" s="34"/>
       <c r="D331" s="71"/>
       <c r="E331" s="151" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F331" s="140">
         <f>IFERROR(VLOOKUP(E331,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13065,7 +13072,7 @@
       </c>
       <c r="G331" s="138"/>
       <c r="H331" s="150" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="332" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13074,7 +13081,7 @@
       <c r="C332" s="34"/>
       <c r="D332" s="71"/>
       <c r="E332" s="72" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="F332" s="140">
         <f>IFERROR(VLOOKUP(E332,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13089,7 +13096,7 @@
       <c r="C333" s="34"/>
       <c r="D333" s="71"/>
       <c r="E333" s="72" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F333" s="140">
         <f>IFERROR(VLOOKUP(E333,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13104,7 +13111,7 @@
       <c r="C334" s="34"/>
       <c r="D334" s="71"/>
       <c r="E334" s="72" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F334" s="140">
         <f>IFERROR(VLOOKUP(E334,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13119,7 +13126,7 @@
       <c r="C335" s="34"/>
       <c r="D335" s="71"/>
       <c r="E335" s="72" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F335" s="140">
         <f>IFERROR(VLOOKUP(E335,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13134,7 +13141,7 @@
       <c r="C336" s="34"/>
       <c r="D336" s="71"/>
       <c r="E336" s="72" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F336" s="140">
         <f>IFERROR(VLOOKUP(E336,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13149,7 +13156,7 @@
       <c r="C337" s="34"/>
       <c r="D337" s="71"/>
       <c r="E337" s="72" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F337" s="140">
         <f>IFERROR(VLOOKUP(E337,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13163,7 +13170,7 @@
       <c r="B338" s="76"/>
       <c r="C338" s="34"/>
       <c r="D338" s="71" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E338" s="71"/>
       <c r="F338" s="140"/>
@@ -13177,10 +13184,10 @@
       <c r="B339" s="76"/>
       <c r="C339" s="34"/>
       <c r="D339" s="71" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E339" s="72" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="F339" s="140">
         <f>IFERROR(VLOOKUP(E339,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13197,7 +13204,7 @@
       <c r="C340" s="34"/>
       <c r="D340" s="71"/>
       <c r="E340" s="71" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F340" s="140">
         <f>IFERROR(VLOOKUP(E340,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13211,7 +13218,7 @@
       <c r="C341" s="34"/>
       <c r="D341" s="71"/>
       <c r="E341" s="71" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F341" s="140">
         <f>IFERROR(VLOOKUP(E341,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13224,10 +13231,10 @@
       <c r="B342" s="76"/>
       <c r="C342" s="34"/>
       <c r="D342" s="71" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E342" s="72" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="F342" s="140">
         <f>IFERROR(VLOOKUP(E342,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13244,7 +13251,7 @@
       <c r="C343" s="34"/>
       <c r="D343" s="71"/>
       <c r="E343" s="72" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F343" s="140">
         <f>IFERROR(VLOOKUP(E343,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13265,7 +13272,7 @@
       <c r="C344" s="34"/>
       <c r="D344" s="71"/>
       <c r="E344" s="72" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F344" s="140">
         <f>IFERROR(VLOOKUP(E344,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13286,7 +13293,7 @@
       <c r="C345" s="34"/>
       <c r="D345" s="71"/>
       <c r="E345" s="72" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F345" s="140">
         <f>IFERROR(VLOOKUP(E345,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13300,7 +13307,7 @@
       <c r="C346" s="34"/>
       <c r="D346" s="71"/>
       <c r="E346" s="72" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F346" s="140">
         <f>IFERROR(VLOOKUP(E346,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13314,7 +13321,7 @@
       <c r="C347" s="34"/>
       <c r="D347" s="71"/>
       <c r="E347" s="72" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F347" s="140">
         <f>IFERROR(VLOOKUP(E347,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13328,7 +13335,7 @@
       <c r="C348" s="34"/>
       <c r="D348" s="71"/>
       <c r="E348" s="72" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F348" s="140">
         <f>IFERROR(VLOOKUP(E348,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13342,7 +13349,7 @@
       <c r="C349" s="34"/>
       <c r="D349" s="71"/>
       <c r="E349" s="72" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F349" s="140">
         <f>IFERROR(VLOOKUP(E349,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13356,7 +13363,7 @@
       <c r="C350" s="34"/>
       <c r="D350" s="71"/>
       <c r="E350" s="151" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F350" s="140">
         <f>IFERROR(VLOOKUP(E350,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13364,7 +13371,7 @@
       </c>
       <c r="G350" s="138"/>
       <c r="H350" s="68" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13372,10 +13379,10 @@
       <c r="B351" s="76"/>
       <c r="C351" s="34"/>
       <c r="D351" s="71" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E351" s="72" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F351" s="140">
         <f>IFERROR(VLOOKUP(E351,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13398,7 +13405,7 @@
       <c r="C352" s="34"/>
       <c r="D352" s="71"/>
       <c r="E352" s="72" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F352" s="140">
         <f>IFERROR(VLOOKUP(E352,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13413,7 +13420,7 @@
       <c r="C353" s="34"/>
       <c r="D353" s="71"/>
       <c r="E353" s="72" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F353" s="140">
         <f>IFERROR(VLOOKUP(E353,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13428,7 +13435,7 @@
       <c r="C354" s="34"/>
       <c r="D354" s="71"/>
       <c r="E354" s="72" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F354" s="140">
         <f>IFERROR(VLOOKUP(E354,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13443,7 +13450,7 @@
       <c r="C355" s="34"/>
       <c r="D355" s="71"/>
       <c r="E355" s="72" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F355" s="140">
         <f>IFERROR(VLOOKUP(E355,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13458,7 +13465,7 @@
       <c r="C356" s="34"/>
       <c r="D356" s="71"/>
       <c r="E356" s="72" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F356" s="140">
         <f>IFERROR(VLOOKUP(E356,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13473,7 +13480,7 @@
       <c r="C357" s="34"/>
       <c r="D357" s="71"/>
       <c r="E357" s="72" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F357" s="140">
         <f>IFERROR(VLOOKUP(E357,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13487,7 +13494,7 @@
       <c r="B358" s="76"/>
       <c r="C358" s="34"/>
       <c r="D358" s="139" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E358" s="72"/>
       <c r="F358" s="140"/>
@@ -13503,7 +13510,7 @@
       <c r="C359" s="34"/>
       <c r="D359" s="132"/>
       <c r="E359" s="72" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F359" s="140">
         <f>IFERROR(VLOOKUP(E359,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13518,7 +13525,7 @@
       <c r="C360" s="34"/>
       <c r="D360" s="132"/>
       <c r="E360" s="72" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F360" s="140">
         <f>IFERROR(VLOOKUP(E360,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13532,7 +13539,7 @@
       <c r="B361" s="76"/>
       <c r="C361" s="34"/>
       <c r="D361" s="139" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="E361" s="72"/>
       <c r="F361" s="140"/>
@@ -13548,7 +13555,7 @@
       <c r="C362" s="34"/>
       <c r="D362" s="139"/>
       <c r="E362" s="72" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F362" s="140">
         <f>IFERROR(VLOOKUP(E362,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13562,7 +13569,7 @@
       <c r="B363" s="76"/>
       <c r="C363" s="34"/>
       <c r="D363" s="71" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E363" s="71"/>
       <c r="F363" s="140"/>
@@ -13577,7 +13584,7 @@
       <c r="C364" s="34"/>
       <c r="D364" s="71"/>
       <c r="E364" s="72" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="F364" s="140">
         <f>IFERROR(VLOOKUP(E364,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13591,7 +13598,7 @@
       <c r="C365" s="34"/>
       <c r="D365" s="71"/>
       <c r="E365" s="72" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F365" s="140">
         <f>IFERROR(VLOOKUP(E365,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13605,7 +13612,7 @@
       <c r="C366" s="34"/>
       <c r="D366" s="71"/>
       <c r="E366" s="72" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F366" s="140">
         <f>IFERROR(VLOOKUP(E366,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13618,7 +13625,7 @@
       <c r="B367" s="76"/>
       <c r="C367" s="34"/>
       <c r="D367" s="71" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E367" s="188"/>
       <c r="F367" s="140"/>
@@ -13632,7 +13639,7 @@
       <c r="B368" s="76"/>
       <c r="C368" s="34"/>
       <c r="D368" s="71" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E368" s="188"/>
       <c r="F368" s="140"/>
@@ -13647,7 +13654,7 @@
       <c r="C369" s="34"/>
       <c r="D369" s="71"/>
       <c r="E369" s="72" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="F369" s="140">
         <f>IFERROR(VLOOKUP(E369,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13661,7 +13668,7 @@
       <c r="C370" s="34"/>
       <c r="D370" s="71"/>
       <c r="E370" s="72" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F370" s="140">
         <f>IFERROR(VLOOKUP(E370,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13675,7 +13682,7 @@
       <c r="C371" s="34"/>
       <c r="D371" s="71"/>
       <c r="E371" s="72" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F371" s="140">
         <f>IFERROR(VLOOKUP(E371,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13689,7 +13696,7 @@
       <c r="C372" s="34"/>
       <c r="D372" s="71"/>
       <c r="E372" s="72" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F372" s="140">
         <f>IFERROR(VLOOKUP(E372,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13703,7 +13710,7 @@
       <c r="C373" s="34"/>
       <c r="D373" s="71"/>
       <c r="E373" s="72" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F373" s="140">
         <f>IFERROR(VLOOKUP(E373,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13716,7 +13723,7 @@
       <c r="B374" s="76"/>
       <c r="C374" s="34"/>
       <c r="D374" s="71" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="E374" s="76"/>
       <c r="F374" s="140"/>
@@ -13731,7 +13738,7 @@
       <c r="C375" s="34"/>
       <c r="D375" s="71"/>
       <c r="E375" s="72" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="F375" s="140">
         <f>IFERROR(VLOOKUP(E375,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13745,7 +13752,7 @@
       <c r="C376" s="34"/>
       <c r="D376" s="71"/>
       <c r="E376" s="72" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F376" s="140">
         <f>IFERROR(VLOOKUP(E376,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13759,7 +13766,7 @@
       <c r="C377" s="34"/>
       <c r="D377" s="71"/>
       <c r="E377" s="72" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F377" s="140">
         <f>IFERROR(VLOOKUP(E377,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13773,7 +13780,7 @@
       <c r="C378" s="34"/>
       <c r="D378" s="71"/>
       <c r="E378" s="72" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F378" s="140">
         <f>IFERROR(VLOOKUP(E378,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13787,7 +13794,7 @@
       <c r="C379" s="34"/>
       <c r="D379" s="71"/>
       <c r="E379" s="72" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F379" s="140">
         <f>IFERROR(VLOOKUP(E379,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13801,7 +13808,7 @@
       <c r="C380" s="34"/>
       <c r="D380" s="71"/>
       <c r="E380" s="72" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F380" s="140">
         <f>IFERROR(VLOOKUP(E380,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13815,7 +13822,7 @@
       <c r="C381" s="34"/>
       <c r="D381" s="71"/>
       <c r="E381" s="72" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F381" s="140">
         <f>IFERROR(VLOOKUP(E381,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13829,7 +13836,7 @@
       <c r="C382" s="34"/>
       <c r="D382" s="71"/>
       <c r="E382" s="72" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F382" s="140">
         <f>IFERROR(VLOOKUP(E382,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13843,7 +13850,7 @@
       <c r="C383" s="34"/>
       <c r="D383" s="71"/>
       <c r="E383" s="151" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F383" s="140">
         <f>IFERROR(VLOOKUP(E383,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13856,7 +13863,7 @@
       <c r="B384" s="76"/>
       <c r="C384" s="34"/>
       <c r="D384" s="71" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E384" s="71"/>
       <c r="F384" s="140"/>
@@ -13870,7 +13877,7 @@
       <c r="B385" s="76"/>
       <c r="C385" s="34"/>
       <c r="D385" s="139" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E385" s="72"/>
       <c r="F385" s="140"/>
@@ -13884,7 +13891,7 @@
       <c r="B386" s="76"/>
       <c r="C386" s="34"/>
       <c r="D386" s="71" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E386" s="71"/>
       <c r="F386" s="140"/>
@@ -13898,10 +13905,10 @@
       <c r="B387" s="76"/>
       <c r="C387" s="34"/>
       <c r="D387" s="71" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E387" s="72" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="F387" s="140">
         <f>IFERROR(VLOOKUP(E387,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13918,7 +13925,7 @@
       <c r="C388" s="34"/>
       <c r="D388" s="71"/>
       <c r="E388" s="72" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F388" s="140">
         <f>IFERROR(VLOOKUP(E388,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13931,7 +13938,7 @@
       <c r="B389" s="76"/>
       <c r="C389" s="34"/>
       <c r="D389" s="71" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="E389" s="71"/>
       <c r="F389" s="140"/>
@@ -13945,7 +13952,7 @@
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
       <c r="D390" s="71" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E390" s="71"/>
       <c r="F390" s="140"/>
@@ -13968,7 +13975,7 @@
       <c r="C391" s="34"/>
       <c r="D391" s="71"/>
       <c r="E391" s="72" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F391" s="140">
         <f>IFERROR(VLOOKUP(E391,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13990,7 +13997,7 @@
       <c r="C392" s="34"/>
       <c r="D392" s="71"/>
       <c r="E392" s="72" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F392" s="140">
         <f>IFERROR(VLOOKUP(E392,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14011,10 +14018,10 @@
       <c r="B393" s="76"/>
       <c r="C393" s="34"/>
       <c r="D393" s="71" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E393" s="72" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14031,7 +14038,7 @@
       <c r="C394" s="34"/>
       <c r="D394" s="71"/>
       <c r="E394" s="72" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14045,7 +14052,7 @@
       <c r="C395" s="34"/>
       <c r="D395" s="71"/>
       <c r="E395" s="72" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F395" s="140">
         <f>IFERROR(VLOOKUP(E395,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14059,7 +14066,7 @@
       <c r="C396" s="34"/>
       <c r="D396" s="71"/>
       <c r="E396" s="72" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F396" s="140">
         <f>IFERROR(VLOOKUP(E396,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14072,7 +14079,7 @@
       <c r="B397" s="76"/>
       <c r="C397" s="34"/>
       <c r="D397" s="71" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="E397" s="188"/>
       <c r="F397" s="140"/>
@@ -14087,7 +14094,7 @@
       <c r="C398" s="34"/>
       <c r="D398" s="139"/>
       <c r="E398" s="72" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="F398" s="140">
         <f>IFERROR(VLOOKUP(E398,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14101,7 +14108,7 @@
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
       <c r="D399" s="71" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E399" s="188"/>
       <c r="F399" s="140"/>
@@ -14116,7 +14123,7 @@
       <c r="C400" s="34"/>
       <c r="D400" s="71"/>
       <c r="E400" s="72" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F400" s="140">
         <f>IFERROR(VLOOKUP(E400,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14129,10 +14136,10 @@
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
       <c r="D401" s="71" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="E401" s="71" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="F401" s="140">
         <f>IFERROR(VLOOKUP(E401,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14148,7 +14155,7 @@
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
       <c r="D402" s="71" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="E402" s="188"/>
       <c r="F402" s="140"/>
@@ -14163,7 +14170,7 @@
       <c r="C403" s="34"/>
       <c r="D403" s="71"/>
       <c r="E403" s="72" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F403" s="140">
         <f>IFERROR(VLOOKUP(E403,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14177,7 +14184,7 @@
       <c r="C404" s="34"/>
       <c r="D404" s="76"/>
       <c r="E404" s="72" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F404" s="140">
         <f>IFERROR(VLOOKUP(E404,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14190,7 +14197,7 @@
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
       <c r="D405" s="71" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="E405" s="72"/>
       <c r="F405" s="140"/>
@@ -14204,7 +14211,7 @@
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
       <c r="D406" s="71" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E406" s="71"/>
       <c r="F406" s="140"/>
@@ -14219,7 +14226,7 @@
       <c r="C407" s="34"/>
       <c r="D407" s="71"/>
       <c r="E407" s="151" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F407" s="140">
         <f>IFERROR(VLOOKUP(E407,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14233,7 +14240,7 @@
       <c r="C408" s="34"/>
       <c r="D408" s="71"/>
       <c r="E408" s="72" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F408" s="140">
         <f>IFERROR(VLOOKUP(E408,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14247,7 +14254,7 @@
       <c r="C409" s="34"/>
       <c r="D409" s="71"/>
       <c r="E409" s="72" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F409" s="140">
         <f>IFERROR(VLOOKUP(E409,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14261,7 +14268,7 @@
       <c r="C410" s="34"/>
       <c r="D410" s="71"/>
       <c r="E410" s="72" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14275,7 +14282,7 @@
       <c r="C411" s="34"/>
       <c r="D411" s="71"/>
       <c r="E411" s="151" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F411" s="140">
         <f>IFERROR(VLOOKUP(E411,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14289,7 +14296,7 @@
       <c r="C412" s="34"/>
       <c r="D412" s="71"/>
       <c r="E412" s="72" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F412" s="140">
         <f>IFERROR(VLOOKUP(E412,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14302,10 +14309,10 @@
       <c r="B413" s="76"/>
       <c r="C413" s="34"/>
       <c r="D413" s="139" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="E413" s="72" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F413" s="140">
         <f>IFERROR(VLOOKUP(E413,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14329,7 +14336,7 @@
       <c r="C414" s="34"/>
       <c r="D414" s="139"/>
       <c r="E414" s="72" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14349,7 +14356,7 @@
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
       <c r="D415" s="139" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="E415" s="72"/>
       <c r="F415" s="140"/>
@@ -14363,10 +14370,10 @@
       <c r="B416" s="76"/>
       <c r="C416" s="34"/>
       <c r="D416" s="139" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E416" s="151" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F416" s="140">
         <f>IFERROR(VLOOKUP(E416,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14383,7 +14390,7 @@
       <c r="C417" s="34"/>
       <c r="D417" s="139"/>
       <c r="E417" s="72" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F417" s="140">
         <f>IFERROR(VLOOKUP(E417,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14399,7 +14406,7 @@
       <c r="C418" s="34"/>
       <c r="D418" s="139"/>
       <c r="E418" s="72" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F418" s="140">
         <f>IFERROR(VLOOKUP(E418,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14415,7 +14422,7 @@
       <c r="C419" s="34"/>
       <c r="D419" s="139"/>
       <c r="E419" s="72" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14431,7 +14438,7 @@
       <c r="C420" s="34"/>
       <c r="D420" s="139"/>
       <c r="E420" s="72" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14447,7 +14454,7 @@
       <c r="C421" s="34"/>
       <c r="D421" s="139"/>
       <c r="E421" s="72" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F421" s="140">
         <f>IFERROR(VLOOKUP(E421,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14463,7 +14470,7 @@
       <c r="C422" s="34"/>
       <c r="D422" s="139"/>
       <c r="E422" s="72" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F422" s="140">
         <f>IFERROR(VLOOKUP(E422,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14495,7 +14502,7 @@
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
       <c r="D424" s="71" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E424" s="71"/>
       <c r="F424" s="140">
@@ -14512,7 +14519,7 @@
       <c r="B425" s="76"/>
       <c r="C425" s="34"/>
       <c r="D425" s="71" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E425" s="71"/>
       <c r="F425" s="140"/>
@@ -14527,7 +14534,7 @@
       <c r="C426" s="34"/>
       <c r="D426" s="71"/>
       <c r="E426" s="72" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="F426" s="140">
         <f>IFERROR(VLOOKUP(E426,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14541,7 +14548,7 @@
       <c r="C427" s="34"/>
       <c r="D427" s="76"/>
       <c r="E427" s="71" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F427" s="140">
         <f>IFERROR(VLOOKUP(E427,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14555,7 +14562,7 @@
       <c r="C428" s="34"/>
       <c r="D428" s="76"/>
       <c r="E428" s="71" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14569,7 +14576,7 @@
       <c r="C429" s="34"/>
       <c r="D429" s="76"/>
       <c r="E429" s="71" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14583,7 +14590,7 @@
       <c r="C430" s="34"/>
       <c r="D430" s="76"/>
       <c r="E430" s="72" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F430" s="140">
         <f>IFERROR(VLOOKUP(E430,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14597,7 +14604,7 @@
       <c r="C431" s="34"/>
       <c r="D431" s="76"/>
       <c r="E431" s="72" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F431" s="140">
         <f>IFERROR(VLOOKUP(E431,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14611,7 +14618,7 @@
       <c r="C432" s="34"/>
       <c r="D432" s="76"/>
       <c r="E432" s="72" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F432" s="140">
         <f>IFERROR(VLOOKUP(E432,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14625,7 +14632,7 @@
       <c r="C433" s="34"/>
       <c r="D433" s="76"/>
       <c r="E433" s="72" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F433" s="140">
         <f>IFERROR(VLOOKUP(E433,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14638,7 +14645,7 @@
       <c r="B434" s="76"/>
       <c r="C434" s="34"/>
       <c r="D434" s="71" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E434" s="71"/>
       <c r="F434" s="140"/>
@@ -14653,7 +14660,7 @@
       <c r="C435" s="34"/>
       <c r="D435" s="71"/>
       <c r="E435" s="72" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F435" s="140">
         <f>IFERROR(VLOOKUP(E435,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14667,7 +14674,7 @@
       <c r="C436" s="34"/>
       <c r="D436" s="71"/>
       <c r="E436" s="72" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F436" s="140">
         <f>IFERROR(VLOOKUP(E436,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14681,7 +14688,7 @@
       <c r="C437" s="34"/>
       <c r="D437" s="71"/>
       <c r="E437" s="72" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14695,7 +14702,7 @@
       <c r="C438" s="34"/>
       <c r="D438" s="71"/>
       <c r="E438" s="72" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F438" s="140">
         <f>IFERROR(VLOOKUP(E438,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14708,7 +14715,7 @@
       <c r="B439" s="76"/>
       <c r="C439" s="34"/>
       <c r="D439" s="71" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E439" s="188"/>
       <c r="F439" s="140"/>
@@ -14722,7 +14729,7 @@
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
       <c r="D440" s="139" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E440" s="76"/>
       <c r="F440" s="140"/>
@@ -14737,7 +14744,7 @@
       <c r="C441" s="34"/>
       <c r="D441" s="139"/>
       <c r="E441" s="72" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="F441" s="140">
         <f>IFERROR(VLOOKUP(E441,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14751,7 +14758,7 @@
       <c r="C442" s="34"/>
       <c r="D442" s="139"/>
       <c r="E442" s="72" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F442" s="140">
         <f>IFERROR(VLOOKUP(E442,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14764,7 +14771,7 @@
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
       <c r="D443" s="71" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="E443" s="188"/>
       <c r="F443" s="140"/>
@@ -14779,7 +14786,7 @@
       <c r="C444" s="34"/>
       <c r="D444" s="71"/>
       <c r="E444" s="151" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="F444" s="140">
         <f>IFERROR(VLOOKUP(E444,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14793,7 +14800,7 @@
       <c r="C445" s="34"/>
       <c r="D445" s="71"/>
       <c r="E445" s="72" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F445" s="140">
         <f>IFERROR(VLOOKUP(E445,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14809,7 +14816,7 @@
       <c r="C446" s="34"/>
       <c r="D446" s="71"/>
       <c r="E446" s="72" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F446" s="140">
         <f>IFERROR(VLOOKUP(E446,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14825,7 +14832,7 @@
       <c r="C447" s="34"/>
       <c r="D447" s="71"/>
       <c r="E447" s="72" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F447" s="140">
         <f>IFERROR(VLOOKUP(E447,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14840,7 +14847,7 @@
       <c r="B448" s="76"/>
       <c r="C448" s="34"/>
       <c r="D448" s="196" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="E448" s="197"/>
       <c r="F448" s="198"/>
@@ -14855,7 +14862,7 @@
       <c r="C449" s="34"/>
       <c r="D449" s="71"/>
       <c r="E449" s="72" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F449" s="140">
         <f>IFERROR(VLOOKUP(E449,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14869,7 +14876,7 @@
       <c r="C450" s="34"/>
       <c r="D450" s="71"/>
       <c r="E450" s="72" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F450" s="140">
         <f>IFERROR(VLOOKUP(E450,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14883,7 +14890,7 @@
       <c r="C451" s="34"/>
       <c r="D451" s="71"/>
       <c r="E451" s="72" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F451" s="140">
         <f>IFERROR(VLOOKUP(E451,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14896,7 +14903,7 @@
       <c r="B452" s="76"/>
       <c r="C452" s="34"/>
       <c r="D452" s="71" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E452" s="188"/>
       <c r="F452" s="140"/>
@@ -14911,7 +14918,7 @@
       <c r="C453" s="34"/>
       <c r="D453" s="71"/>
       <c r="E453" s="72" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F453" s="140">
         <f>IFERROR(VLOOKUP(E453,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14925,7 +14932,7 @@
       <c r="C454" s="34"/>
       <c r="D454" s="71"/>
       <c r="E454" s="72" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F454" s="140">
         <f>IFERROR(VLOOKUP(E454,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14939,7 +14946,7 @@
       <c r="C455" s="34"/>
       <c r="D455" s="71"/>
       <c r="E455" s="72" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F455" s="140">
         <f>IFERROR(VLOOKUP(E455,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14953,7 +14960,7 @@
       <c r="C456" s="34"/>
       <c r="D456" s="71"/>
       <c r="E456" s="72" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F456" s="140">
         <f>IFERROR(VLOOKUP(E456,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14966,7 +14973,7 @@
       <c r="B457" s="76"/>
       <c r="C457" s="34"/>
       <c r="D457" s="71" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E457" s="71"/>
       <c r="F457" s="140">
@@ -14983,7 +14990,7 @@
       <c r="B458" s="76"/>
       <c r="C458" s="34"/>
       <c r="D458" s="71" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E458" s="71"/>
       <c r="F458" s="140">
@@ -15000,7 +15007,7 @@
       <c r="B459" s="76"/>
       <c r="C459" s="34"/>
       <c r="D459" s="139" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E459" s="72"/>
       <c r="F459" s="140"/>
@@ -15015,7 +15022,7 @@
       <c r="C460" s="34"/>
       <c r="D460" s="139"/>
       <c r="E460" s="72" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F460" s="140">
         <f>IFERROR(VLOOKUP(E460,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15029,7 +15036,7 @@
       <c r="C461" s="34"/>
       <c r="D461" s="139"/>
       <c r="E461" s="72" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F461" s="140">
         <f>IFERROR(VLOOKUP(E461,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15042,10 +15049,10 @@
       <c r="B462" s="76"/>
       <c r="C462" s="34"/>
       <c r="D462" s="71" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E462" s="71" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="F462" s="140">
         <f>IFERROR(VLOOKUP(E462,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15063,7 +15070,7 @@
       <c r="C463" s="34"/>
       <c r="D463" s="71"/>
       <c r="E463" s="72" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15078,7 +15085,7 @@
       <c r="C464" s="34"/>
       <c r="D464" s="71"/>
       <c r="E464" s="72" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F464" s="140">
         <f>IFERROR(VLOOKUP(E464,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15093,7 +15100,7 @@
       <c r="C465" s="34"/>
       <c r="D465" s="71"/>
       <c r="E465" s="72" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15109,7 +15116,7 @@
       <c r="C466" s="34"/>
       <c r="D466" s="71"/>
       <c r="E466" s="72" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F466" s="140">
         <f>IFERROR(VLOOKUP(E466,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15125,7 +15132,7 @@
       <c r="C467" s="34"/>
       <c r="D467" s="71"/>
       <c r="E467" s="72" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F467" s="140">
         <f>IFERROR(VLOOKUP(E467,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15141,7 +15148,7 @@
       <c r="C468" s="34"/>
       <c r="D468" s="71"/>
       <c r="E468" s="72" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F468" s="140">
         <f>IFERROR(VLOOKUP(E468,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15157,7 +15164,7 @@
       <c r="C469" s="34"/>
       <c r="D469" s="71"/>
       <c r="E469" s="72" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F469" s="140">
         <f>IFERROR(VLOOKUP(E469,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15173,7 +15180,7 @@
       <c r="C470" s="34"/>
       <c r="D470" s="71"/>
       <c r="E470" s="72" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F470" s="140">
         <f>IFERROR(VLOOKUP(E470,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15188,7 +15195,7 @@
       <c r="B471" s="76"/>
       <c r="C471" s="34"/>
       <c r="D471" s="71" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E471" s="188"/>
       <c r="F471" s="140"/>
@@ -15203,7 +15210,7 @@
       <c r="C472" s="34"/>
       <c r="D472" s="71"/>
       <c r="E472" s="72" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F472" s="140">
         <f>IFERROR(VLOOKUP(E472,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15217,7 +15224,7 @@
       <c r="C473" s="34"/>
       <c r="D473" s="71"/>
       <c r="E473" s="72" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F473" s="140">
         <f>IFERROR(VLOOKUP(E473,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15231,7 +15238,7 @@
       <c r="C474" s="34"/>
       <c r="D474" s="71"/>
       <c r="E474" s="72" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F474" s="140">
         <f>IFERROR(VLOOKUP(E474,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15244,7 +15251,7 @@
       <c r="B475" s="76"/>
       <c r="C475" s="34"/>
       <c r="D475" s="139" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E475" s="188"/>
       <c r="F475" s="140">
@@ -15261,7 +15268,7 @@
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
       <c r="D476" s="71" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E476" s="188"/>
       <c r="F476" s="140">
@@ -15278,7 +15285,7 @@
       <c r="B477" s="76"/>
       <c r="C477" s="34"/>
       <c r="D477" s="71" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E477" s="188"/>
       <c r="F477" s="140"/>
@@ -15293,7 +15300,7 @@
       <c r="C478" s="34"/>
       <c r="D478" s="71"/>
       <c r="E478" s="72" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F478" s="140">
         <f>IFERROR(VLOOKUP(E478,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15307,7 +15314,7 @@
       <c r="C479" s="34"/>
       <c r="D479" s="71"/>
       <c r="E479" s="72" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F479" s="140">
         <f>IFERROR(VLOOKUP(E479,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15320,10 +15327,10 @@
       <c r="B480" s="76"/>
       <c r="C480" s="34"/>
       <c r="D480" s="71" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E480" s="72" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="F480" s="140">
         <f>IFERROR(VLOOKUP(E480,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15340,7 +15347,7 @@
       <c r="C481" s="34"/>
       <c r="D481" s="71"/>
       <c r="E481" s="72" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15354,7 +15361,7 @@
       <c r="C482" s="34"/>
       <c r="D482" s="71"/>
       <c r="E482" s="72" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15367,10 +15374,10 @@
       <c r="B483" s="76"/>
       <c r="C483" s="34"/>
       <c r="D483" s="71" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="E483" s="72" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="F483" s="140">
         <f>IFERROR(VLOOKUP(E483,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15386,7 +15393,7 @@
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
       <c r="D484" s="71" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E484" s="71"/>
       <c r="F484" s="140">
@@ -15403,7 +15410,7 @@
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
       <c r="D485" s="139" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E485" s="72"/>
       <c r="F485" s="140">
@@ -15420,7 +15427,7 @@
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
       <c r="D486" s="71" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E486" s="68"/>
       <c r="F486" s="140">
@@ -15437,7 +15444,7 @@
       <c r="B487" s="76"/>
       <c r="C487" s="34"/>
       <c r="D487" s="71" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E487" s="132"/>
       <c r="F487" s="140">
@@ -15454,7 +15461,7 @@
       <c r="B488" s="76"/>
       <c r="C488" s="34"/>
       <c r="D488" s="71" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E488" s="132"/>
       <c r="F488" s="140">
@@ -15471,7 +15478,7 @@
       <c r="B489" s="76"/>
       <c r="C489" s="34"/>
       <c r="D489" s="71" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E489" s="132"/>
       <c r="F489" s="140">
@@ -15488,7 +15495,7 @@
       <c r="B490" s="76"/>
       <c r="C490" s="34"/>
       <c r="D490" s="71" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E490" s="132"/>
       <c r="F490" s="140">
@@ -15505,7 +15512,7 @@
       <c r="B491" s="76"/>
       <c r="C491" s="34"/>
       <c r="D491" s="139" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E491" s="132"/>
       <c r="F491" s="140">
@@ -15522,7 +15529,7 @@
       <c r="B492" s="76"/>
       <c r="C492" s="34"/>
       <c r="D492" s="139" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E492" s="68"/>
       <c r="F492" s="140">
@@ -15539,7 +15546,7 @@
       <c r="B493" s="76"/>
       <c r="C493" s="34"/>
       <c r="D493" s="139" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E493" s="132"/>
       <c r="F493" s="140">
@@ -15556,7 +15563,7 @@
       <c r="B494" s="76"/>
       <c r="C494" s="34"/>
       <c r="D494" s="139" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E494" s="132"/>
       <c r="F494" s="140">
@@ -15573,7 +15580,7 @@
       <c r="B495" s="76"/>
       <c r="C495" s="34"/>
       <c r="D495" s="139" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E495" s="132"/>
       <c r="F495" s="140">
@@ -15590,10 +15597,10 @@
       <c r="B496" s="76"/>
       <c r="C496" s="34"/>
       <c r="D496" s="139" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E496" s="72" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F496" s="140">
         <f>IFERROR(VLOOKUP(D496,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15609,7 +15616,7 @@
       <c r="B497" s="76"/>
       <c r="C497" s="34"/>
       <c r="D497" s="139" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E497" s="132"/>
       <c r="F497" s="140">
@@ -15627,7 +15634,7 @@
       <c r="B498" s="76"/>
       <c r="C498" s="34"/>
       <c r="D498" s="139" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E498" s="132"/>
       <c r="F498" s="140">
@@ -15645,7 +15652,7 @@
       <c r="B499" s="76"/>
       <c r="C499" s="34"/>
       <c r="D499" s="139" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E499" s="132"/>
       <c r="F499" s="140">
@@ -15663,7 +15670,7 @@
       <c r="B500" s="76"/>
       <c r="C500" s="34"/>
       <c r="D500" s="139" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E500" s="132"/>
       <c r="F500" s="140">
@@ -15681,7 +15688,7 @@
       <c r="B501" s="76"/>
       <c r="C501" s="34"/>
       <c r="D501" s="139" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E501" s="132"/>
       <c r="F501" s="140">
@@ -15698,7 +15705,7 @@
       <c r="B502" s="76"/>
       <c r="C502" s="34"/>
       <c r="D502" s="139" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E502" s="132"/>
       <c r="F502" s="140">
@@ -15722,7 +15729,7 @@
         <v>55</v>
       </c>
       <c r="I503" s="199" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="504" ht="13.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15731,7 +15738,7 @@
       <c r="C504" s="34"/>
       <c r="D504" s="132"/>
       <c r="E504" s="200" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="F504" s="201">
         <f>SUM(F146:F502)</f>
@@ -15756,7 +15763,7 @@
       <c r="C505" s="34"/>
       <c r="D505" s="132"/>
       <c r="E505" s="203" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F505" s="204">
         <f>+-'Anexo II'!E103</f>
@@ -15775,7 +15782,7 @@
       <c r="C506" s="34"/>
       <c r="D506" s="132"/>
       <c r="E506" s="207" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F506" s="208">
         <f>+F504+F505</f>
@@ -15804,7 +15811,7 @@
       <c r="C508" s="211"/>
       <c r="D508" s="211"/>
       <c r="E508" s="211" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F508" s="211">
         <f>+F280-F506</f>
@@ -28561,7 +28568,7 @@
       <c r="C1" s="222"/>
       <c r="D1" s="222"/>
       <c r="E1" s="223" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F1" s="224"/>
       <c r="G1" s="224"/>
@@ -28579,7 +28586,7 @@
     </row>
     <row r="3" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="195"/>
@@ -28645,7 +28652,7 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B9" s="151"/>
       <c r="C9" s="195"/>
@@ -28843,7 +28850,7 @@
     </row>
     <row r="27" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="72" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B27" s="151"/>
       <c r="C27" s="195"/>
@@ -28854,7 +28861,7 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="72" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
@@ -28865,7 +28872,7 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B29" s="151"/>
       <c r="C29" s="195"/>
@@ -28876,7 +28883,7 @@
     </row>
     <row r="30" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="72" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B30" s="151"/>
       <c r="C30" s="195"/>
@@ -28887,7 +28894,7 @@
     </row>
     <row r="31" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B31" s="151"/>
       <c r="C31" s="195"/>
@@ -28898,7 +28905,7 @@
     </row>
     <row r="32" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="72" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B32" s="151"/>
       <c r="C32" s="195"/>
@@ -28909,7 +28916,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="72" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B33" s="151"/>
       <c r="C33" s="195"/>
@@ -28920,7 +28927,7 @@
     </row>
     <row r="34" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="72" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B34" s="151"/>
       <c r="C34" s="195"/>
@@ -28931,7 +28938,7 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B35" s="151"/>
       <c r="C35" s="195"/>
@@ -28942,7 +28949,7 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="72" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B36" s="151"/>
       <c r="C36" s="195"/>
@@ -28953,7 +28960,7 @@
     </row>
     <row r="37" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="72" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B37" s="151"/>
       <c r="C37" s="195"/>
@@ -28964,7 +28971,7 @@
     </row>
     <row r="38" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="72" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B38" s="151"/>
       <c r="C38" s="195"/>
@@ -28975,7 +28982,7 @@
     </row>
     <row r="39" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="72" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="195"/>
@@ -28986,7 +28993,7 @@
     </row>
     <row r="40" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="72" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B40" s="151"/>
       <c r="C40" s="195"/>
@@ -28997,7 +29004,7 @@
     </row>
     <row r="41" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="72" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B41" s="151"/>
       <c r="C41" s="195"/>
@@ -29008,7 +29015,7 @@
     </row>
     <row r="42" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="72" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" s="151"/>
       <c r="C42" s="195"/>
@@ -29019,7 +29026,7 @@
     </row>
     <row r="43" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="72" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B43" s="151"/>
       <c r="C43" s="195"/>
@@ -29030,7 +29037,7 @@
     </row>
     <row r="44" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="72" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="220"/>
@@ -29052,7 +29059,7 @@
     </row>
     <row r="46" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="72" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B46" s="151"/>
       <c r="C46" s="195"/>
@@ -29069,10 +29076,10 @@
       <c r="E47" s="220"/>
       <c r="F47" s="220"/>
       <c r="G47" s="226" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H47" s="227" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -29201,13 +29208,13 @@
       <c r="D58" s="232"/>
       <c r="E58" s="232"/>
       <c r="F58" s="232" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G58" s="232"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="72" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="195"/>
@@ -29218,7 +29225,7 @@
     </row>
     <row r="60" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B60" s="151"/>
       <c r="C60" s="195"/>
@@ -29229,7 +29236,7 @@
     </row>
     <row r="61" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B61" s="151"/>
       <c r="C61" s="195"/>
@@ -29240,7 +29247,7 @@
     </row>
     <row r="62" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B62" s="151"/>
       <c r="C62" s="195"/>
@@ -29251,7 +29258,7 @@
     </row>
     <row r="63" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B63" s="151"/>
       <c r="C63" s="195"/>
@@ -29262,7 +29269,7 @@
     </row>
     <row r="64" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B64" s="151"/>
       <c r="C64" s="195"/>
@@ -29273,7 +29280,7 @@
     </row>
     <row r="65" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B65" s="151"/>
       <c r="C65" s="195"/>
@@ -29284,7 +29291,7 @@
     </row>
     <row r="66" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B66" s="151"/>
       <c r="C66" s="195"/>
@@ -29295,7 +29302,7 @@
     </row>
     <row r="67" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B67" s="151"/>
       <c r="C67" s="195"/>
@@ -29306,7 +29313,7 @@
     </row>
     <row r="68" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="72" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B68" s="151"/>
       <c r="C68" s="195"/>
@@ -29317,7 +29324,7 @@
     </row>
     <row r="69" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B69" s="151"/>
       <c r="C69" s="195"/>
@@ -29328,7 +29335,7 @@
     </row>
     <row r="70" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B70" s="151"/>
       <c r="C70" s="195"/>
@@ -29339,7 +29346,7 @@
     </row>
     <row r="71" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="72" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B71" s="151"/>
       <c r="C71" s="195"/>
@@ -29350,7 +29357,7 @@
     </row>
     <row r="72" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="72" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B72" s="151"/>
       <c r="C72" s="195"/>
@@ -29361,7 +29368,7 @@
     </row>
     <row r="73" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="72" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B73" s="151"/>
       <c r="C73" s="195"/>
@@ -29372,7 +29379,7 @@
     </row>
     <row r="74" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B74" s="151"/>
       <c r="C74" s="195"/>
@@ -29383,7 +29390,7 @@
     </row>
     <row r="75" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="72" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B75" s="151"/>
       <c r="C75" s="195"/>
@@ -29394,7 +29401,7 @@
     </row>
     <row r="76" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="72" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B76" s="151"/>
       <c r="C76" s="195"/>
@@ -29405,7 +29412,7 @@
     </row>
     <row r="77" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="72" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B77" s="151"/>
       <c r="C77" s="195"/>
@@ -29416,7 +29423,7 @@
     </row>
     <row r="78" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="72" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B78" s="151"/>
       <c r="C78" s="195"/>
@@ -29427,7 +29434,7 @@
     </row>
     <row r="79" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="72" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B79" s="151"/>
       <c r="C79" s="195"/>
@@ -29438,7 +29445,7 @@
     </row>
     <row r="80" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="72" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B80" s="151"/>
       <c r="C80" s="195"/>
@@ -29449,7 +29456,7 @@
     </row>
     <row r="81" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B81" s="151"/>
       <c r="C81" s="195"/>
@@ -29460,7 +29467,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="72" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B82" s="151"/>
       <c r="C82" s="195"/>
@@ -29471,7 +29478,7 @@
     </row>
     <row r="83" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B83" s="151"/>
       <c r="C83" s="195"/>
@@ -29482,7 +29489,7 @@
     </row>
     <row r="84" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="72" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B84" s="151"/>
       <c r="C84" s="195"/>
@@ -29493,7 +29500,7 @@
     </row>
     <row r="85" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="72" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B85" s="151"/>
       <c r="C85" s="195"/>
@@ -29504,7 +29511,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="72" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B86" s="151"/>
       <c r="C86" s="195"/>
@@ -29515,7 +29522,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B87" s="151"/>
       <c r="C87" s="195"/>
@@ -29526,7 +29533,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="72" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B88" s="151"/>
       <c r="C88" s="195"/>
@@ -29540,7 +29547,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="72" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B89" s="151"/>
       <c r="C89" s="195"/>
@@ -29551,7 +29558,7 @@
     </row>
     <row r="90" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B90" s="151"/>
       <c r="C90" s="195"/>
@@ -29562,7 +29569,7 @@
     </row>
     <row r="91" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="72" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B91" s="151"/>
       <c r="C91" s="195"/>
@@ -29573,7 +29580,7 @@
     </row>
     <row r="92" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="72" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B92" s="151"/>
       <c r="C92" s="195"/>
@@ -29584,7 +29591,7 @@
     </row>
     <row r="93" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B93" s="151"/>
       <c r="C93" s="195"/>
@@ -29595,7 +29602,7 @@
     </row>
     <row r="94" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="72" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B94" s="151"/>
       <c r="C94" s="195"/>
@@ -29606,7 +29613,7 @@
     </row>
     <row r="95" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="72" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B95" s="151"/>
       <c r="C95" s="195"/>
@@ -29617,7 +29624,7 @@
     </row>
     <row r="96" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="72" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B96" s="151"/>
       <c r="C96" s="195"/>
@@ -29628,7 +29635,7 @@
     </row>
     <row r="97" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="72" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B97" s="151"/>
       <c r="C97" s="195"/>
@@ -29639,7 +29646,7 @@
     </row>
     <row r="98" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="72" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B98" s="151"/>
       <c r="C98" s="195"/>
@@ -29650,7 +29657,7 @@
     </row>
     <row r="99" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="72" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B99" s="151"/>
       <c r="C99" s="195"/>
@@ -29661,7 +29668,7 @@
     </row>
     <row r="100" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="72" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B100" s="151"/>
       <c r="C100" s="195"/>
@@ -29672,7 +29679,7 @@
     </row>
     <row r="101" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="72" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B101" s="151"/>
       <c r="C101" s="195"/>
@@ -29683,7 +29690,7 @@
     </row>
     <row r="102" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="72" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B102" s="151"/>
       <c r="C102" s="195"/>
@@ -29694,7 +29701,7 @@
     </row>
     <row r="103" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="72" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B103" s="151"/>
       <c r="C103" s="195"/>
@@ -29705,7 +29712,7 @@
     </row>
     <row r="104" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="72" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B104" s="151"/>
       <c r="C104" s="195"/>
@@ -29716,7 +29723,7 @@
     </row>
     <row r="105" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="72" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B105" s="151"/>
       <c r="C105" s="195"/>
@@ -29727,7 +29734,7 @@
     </row>
     <row r="106" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="72" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B106" s="151"/>
       <c r="C106" s="195"/>
@@ -29738,7 +29745,7 @@
     </row>
     <row r="107" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B107" s="151"/>
       <c r="C107" s="195"/>
@@ -30197,7 +30204,7 @@
     </row>
     <row r="172" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="72" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B172" s="151"/>
       <c r="C172" s="195"/>
@@ -30208,7 +30215,7 @@
     </row>
     <row r="173" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="72" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B173" s="151"/>
       <c r="C173" s="195"/>
@@ -30219,7 +30226,7 @@
     </row>
     <row r="174" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="72" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B174" s="151"/>
       <c r="C174" s="195"/>
@@ -30230,7 +30237,7 @@
     </row>
     <row r="175" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="72" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B175" s="151"/>
       <c r="C175" s="195"/>
@@ -30241,7 +30248,7 @@
     </row>
     <row r="176" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="72" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B176" s="151"/>
       <c r="C176" s="195"/>
@@ -30252,7 +30259,7 @@
     </row>
     <row r="177" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="72" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B177" s="151"/>
       <c r="C177" s="195"/>
@@ -30263,7 +30270,7 @@
     </row>
     <row r="178" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B178" s="220"/>
       <c r="C178" s="220"/>
@@ -30274,7 +30281,7 @@
     </row>
     <row r="179" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="72" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B179" s="220"/>
       <c r="C179" s="220"/>
@@ -30285,7 +30292,7 @@
     </row>
     <row r="180" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B180" s="220"/>
       <c r="C180" s="220"/>
@@ -30296,7 +30303,7 @@
     </row>
     <row r="181" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="72" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B181" s="220"/>
       <c r="C181" s="220"/>
@@ -30307,7 +30314,7 @@
     </row>
     <row r="182" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B182" s="220"/>
       <c r="C182" s="220"/>
@@ -30318,7 +30325,7 @@
     </row>
     <row r="183" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="72" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B183" s="220"/>
       <c r="C183" s="220"/>
@@ -30329,7 +30336,7 @@
     </row>
     <row r="184" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="72" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B184" s="220"/>
       <c r="C184" s="220"/>
@@ -30340,7 +30347,7 @@
     </row>
     <row r="185" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="72" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B185" s="220"/>
       <c r="C185" s="220"/>
@@ -30351,7 +30358,7 @@
     </row>
     <row r="186" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="72" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B186" s="220"/>
       <c r="C186" s="220"/>
@@ -30362,7 +30369,7 @@
     </row>
     <row r="187" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="72" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B187" s="220"/>
       <c r="C187" s="220"/>
@@ -30373,7 +30380,7 @@
     </row>
     <row r="188" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="72" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B188" s="220"/>
       <c r="C188" s="220"/>
@@ -30384,7 +30391,7 @@
     </row>
     <row r="189" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="72" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B189" s="220"/>
       <c r="C189" s="220"/>
@@ -30395,7 +30402,7 @@
     </row>
     <row r="190" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="72" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B190" s="220"/>
       <c r="C190" s="220"/>
@@ -30406,7 +30413,7 @@
     </row>
     <row r="191" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="72" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B191" s="220"/>
       <c r="C191" s="220"/>
@@ -30417,7 +30424,7 @@
     </row>
     <row r="192" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="72" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B192" s="220"/>
       <c r="C192" s="220"/>
@@ -30428,7 +30435,7 @@
     </row>
     <row r="193" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B193" s="220"/>
       <c r="C193" s="220"/>
@@ -30439,7 +30446,7 @@
     </row>
     <row r="194" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="72" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B194" s="220"/>
       <c r="C194" s="220"/>
@@ -30450,7 +30457,7 @@
     </row>
     <row r="195" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="72" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B195" s="220"/>
       <c r="C195" s="220"/>
@@ -30461,7 +30468,7 @@
     </row>
     <row r="196" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="72" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B196" s="220"/>
       <c r="C196" s="220"/>
@@ -30472,7 +30479,7 @@
     </row>
     <row r="197" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="72" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B197" s="220"/>
       <c r="C197" s="220"/>
@@ -30483,7 +30490,7 @@
     </row>
     <row r="198" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B198" s="151"/>
       <c r="C198" s="195"/>
@@ -30542,7 +30549,7 @@
     </row>
     <row r="207" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="151" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B207" s="151"/>
       <c r="C207" s="195"/>
@@ -30553,7 +30560,7 @@
     </row>
     <row r="208" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="151" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B208" s="151"/>
       <c r="C208" s="195"/>
@@ -30564,7 +30571,7 @@
     </row>
     <row r="209" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="151" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B209" s="151"/>
       <c r="C209" s="195"/>
@@ -30575,7 +30582,7 @@
     </row>
     <row r="210" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="151" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B210" s="151"/>
       <c r="C210" s="195"/>
@@ -30592,18 +30599,18 @@
     </row>
     <row r="213" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="221" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B213" s="233"/>
       <c r="C213" s="233"/>
       <c r="D213" s="233"/>
       <c r="E213" s="223" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="72" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B214" s="220"/>
       <c r="C214" s="195"/>
@@ -30614,7 +30621,7 @@
     </row>
     <row r="215" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="72" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B215" s="151"/>
       <c r="C215" s="195"/>
@@ -30625,7 +30632,7 @@
     </row>
     <row r="216" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="72" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B216" s="151"/>
       <c r="C216" s="195"/>
@@ -30636,7 +30643,7 @@
     </row>
     <row r="217" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="72" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B217" s="151"/>
       <c r="C217" s="195"/>
@@ -30647,7 +30654,7 @@
     </row>
     <row r="218" ht="12.75" customHeight="1" spans="1:5" s="234" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="235" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B218" s="236"/>
       <c r="C218" s="41"/>
@@ -30658,7 +30665,7 @@
     </row>
     <row r="219" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="72" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B219" s="151"/>
       <c r="C219" s="195"/>
@@ -30669,7 +30676,7 @@
     </row>
     <row r="220" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="72" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B220" s="151"/>
       <c r="C220" s="195"/>
@@ -30680,7 +30687,7 @@
     </row>
     <row r="221" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="72" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B221" s="151"/>
       <c r="C221" s="195"/>
@@ -30691,7 +30698,7 @@
     </row>
     <row r="222" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="72" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B222" s="151"/>
       <c r="C222" s="195"/>
@@ -30702,7 +30709,7 @@
     </row>
     <row r="223" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="72" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B223" s="151"/>
       <c r="C223" s="195"/>
@@ -30713,7 +30720,7 @@
     </row>
     <row r="224" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="72" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B224" s="151"/>
       <c r="C224" s="195"/>
@@ -30724,7 +30731,7 @@
     </row>
     <row r="225" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="72" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B225" s="151"/>
       <c r="C225" s="195"/>
@@ -30735,7 +30742,7 @@
     </row>
     <row r="226" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="72" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B226" s="151"/>
       <c r="C226" s="195"/>
@@ -30746,7 +30753,7 @@
     </row>
     <row r="227" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B227" s="151"/>
       <c r="C227" s="195"/>
@@ -30757,7 +30764,7 @@
     </row>
     <row r="228" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="72" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B228" s="151"/>
       <c r="C228" s="195"/>
@@ -30768,7 +30775,7 @@
     </row>
     <row r="229" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="72" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B229" s="151"/>
       <c r="C229" s="195"/>
@@ -30779,7 +30786,7 @@
     </row>
     <row r="230" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="72" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B230" s="151"/>
       <c r="C230" s="195"/>
@@ -30790,7 +30797,7 @@
     </row>
     <row r="231" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B231" s="151"/>
       <c r="C231" s="195"/>
@@ -30802,7 +30809,7 @@
     </row>
     <row r="232" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="72" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B232" s="151"/>
       <c r="C232" s="195"/>
@@ -30814,7 +30821,7 @@
     </row>
     <row r="233" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="72" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B233" s="151"/>
       <c r="C233" s="195"/>
@@ -30825,7 +30832,7 @@
     </row>
     <row r="234" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B234" s="151"/>
       <c r="C234" s="195"/>
@@ -30836,7 +30843,7 @@
     </row>
     <row r="235" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="72" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B235" s="151"/>
       <c r="C235" s="195"/>
@@ -30847,7 +30854,7 @@
     </row>
     <row r="236" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="72" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B236" s="151"/>
       <c r="C236" s="195"/>
@@ -30858,7 +30865,7 @@
     </row>
     <row r="237" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="72" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B237" s="151"/>
       <c r="C237" s="195"/>
@@ -30869,7 +30876,7 @@
     </row>
     <row r="238" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="72" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B238" s="151"/>
       <c r="C238" s="195"/>
@@ -30880,7 +30887,7 @@
     </row>
     <row r="239" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B239" s="151"/>
       <c r="C239" s="195"/>
@@ -30891,7 +30898,7 @@
     </row>
     <row r="240" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="72" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B240" s="151"/>
       <c r="C240" s="195"/>
@@ -30902,7 +30909,7 @@
     </row>
     <row r="241" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="72" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B241" s="151"/>
       <c r="C241" s="195"/>
@@ -30913,7 +30920,7 @@
     </row>
     <row r="242" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="72" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B242" s="151"/>
       <c r="C242" s="195"/>
@@ -30924,7 +30931,7 @@
     </row>
     <row r="243" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="72" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B243" s="151"/>
       <c r="C243" s="195"/>
@@ -30935,7 +30942,7 @@
     </row>
     <row r="244" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="72" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B244" s="151"/>
       <c r="C244" s="195"/>
@@ -30946,7 +30953,7 @@
     </row>
     <row r="245" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="72" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B245" s="151"/>
       <c r="C245" s="195"/>
@@ -30957,7 +30964,7 @@
     </row>
     <row r="246" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="72" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B246" s="151"/>
       <c r="C246" s="195"/>
@@ -30968,7 +30975,7 @@
     </row>
     <row r="247" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="72" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B247" s="151"/>
       <c r="C247" s="195"/>
@@ -30979,7 +30986,7 @@
     </row>
     <row r="248" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="72" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B248" s="151"/>
       <c r="C248" s="195"/>
@@ -30990,7 +30997,7 @@
     </row>
     <row r="249" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="72" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B249" s="151"/>
       <c r="C249" s="195"/>
@@ -31001,7 +31008,7 @@
     </row>
     <row r="250" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="72" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B250" s="151"/>
       <c r="C250" s="195"/>
@@ -31012,7 +31019,7 @@
     </row>
     <row r="251" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="72" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B251" s="151"/>
       <c r="C251" s="195"/>
@@ -31023,7 +31030,7 @@
     </row>
     <row r="252" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="72" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B252" s="151"/>
       <c r="C252" s="195"/>
@@ -31034,7 +31041,7 @@
     </row>
     <row r="253" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="72" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B253" s="151"/>
       <c r="C253" s="195"/>
@@ -31045,7 +31052,7 @@
     </row>
     <row r="254" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="72" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B254" s="151"/>
       <c r="C254" s="195"/>
@@ -31056,7 +31063,7 @@
     </row>
     <row r="255" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="72" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B255" s="151"/>
       <c r="C255" s="195"/>
@@ -31067,7 +31074,7 @@
     </row>
     <row r="256" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="72" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B256" s="151"/>
       <c r="C256" s="195"/>
@@ -31078,7 +31085,7 @@
     </row>
     <row r="257" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="72" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B257" s="151"/>
       <c r="C257" s="195"/>
@@ -31089,7 +31096,7 @@
     </row>
     <row r="258" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="72" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B258" s="151"/>
       <c r="C258" s="195"/>
@@ -31100,7 +31107,7 @@
     </row>
     <row r="259" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="72" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B259" s="151"/>
       <c r="C259" s="195"/>
@@ -31111,7 +31118,7 @@
     </row>
     <row r="260" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="72" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B260" s="151"/>
       <c r="C260" s="195"/>
@@ -31122,7 +31129,7 @@
     </row>
     <row r="261" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="72" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B261" s="151"/>
       <c r="C261" s="195"/>
@@ -31133,7 +31140,7 @@
     </row>
     <row r="262" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="72" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B262" s="151"/>
       <c r="C262" s="195"/>
@@ -31144,7 +31151,7 @@
     </row>
     <row r="263" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="72" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B263" s="151"/>
       <c r="C263" s="195"/>
@@ -31155,7 +31162,7 @@
     </row>
     <row r="264" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="72" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B264" s="151"/>
       <c r="C264" s="195"/>
@@ -31166,7 +31173,7 @@
     </row>
     <row r="265" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="72" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B265" s="151"/>
       <c r="C265" s="195"/>
@@ -31177,7 +31184,7 @@
     </row>
     <row r="266" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="72" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B266" s="151"/>
       <c r="C266" s="195"/>
@@ -31188,7 +31195,7 @@
     </row>
     <row r="267" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="72" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B267" s="151"/>
       <c r="C267" s="195"/>
@@ -31199,7 +31206,7 @@
     </row>
     <row r="268" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="72" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B268" s="151"/>
       <c r="C268" s="195"/>
@@ -31210,7 +31217,7 @@
     </row>
     <row r="269" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="72" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B269" s="151"/>
       <c r="C269" s="195"/>
@@ -31221,7 +31228,7 @@
     </row>
     <row r="270" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="72" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B270" s="151"/>
       <c r="C270" s="195"/>
@@ -31232,7 +31239,7 @@
     </row>
     <row r="271" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="72" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B271" s="151"/>
       <c r="C271" s="195"/>
@@ -31243,7 +31250,7 @@
     </row>
     <row r="272" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="72" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B272" s="151"/>
       <c r="C272" s="195"/>
@@ -31254,7 +31261,7 @@
     </row>
     <row r="273" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="72" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B273" s="151"/>
       <c r="C273" s="195"/>
@@ -31265,7 +31272,7 @@
     </row>
     <row r="274" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="72" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B274" s="151"/>
       <c r="C274" s="195"/>
@@ -31276,7 +31283,7 @@
     </row>
     <row r="275" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="72" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B275" s="151"/>
       <c r="C275" s="195"/>
@@ -31287,7 +31294,7 @@
     </row>
     <row r="276" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="72" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B276" s="151"/>
       <c r="C276" s="195"/>
@@ -31298,7 +31305,7 @@
     </row>
     <row r="277" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="72" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B277" s="151"/>
       <c r="C277" s="195"/>
@@ -31309,7 +31316,7 @@
     </row>
     <row r="278" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="72" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B278" s="151"/>
       <c r="C278" s="195"/>
@@ -31320,7 +31327,7 @@
     </row>
     <row r="279" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B279" s="151"/>
       <c r="C279" s="195"/>
@@ -31331,7 +31338,7 @@
     </row>
     <row r="280" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="72" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B280" s="151"/>
       <c r="C280" s="195"/>
@@ -31342,7 +31349,7 @@
     </row>
     <row r="281" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="72" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="195"/>
@@ -31353,7 +31360,7 @@
     </row>
     <row r="282" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="72" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B282" s="151"/>
       <c r="C282" s="195"/>
@@ -31364,7 +31371,7 @@
     </row>
     <row r="283" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="72" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B283" s="151"/>
       <c r="C283" s="195"/>
@@ -31375,7 +31382,7 @@
     </row>
     <row r="284" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="72" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B284" s="151"/>
       <c r="C284" s="195"/>
@@ -31386,7 +31393,7 @@
     </row>
     <row r="285" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="72" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B285" s="151"/>
       <c r="C285" s="195"/>
@@ -31397,7 +31404,7 @@
     </row>
     <row r="286" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="72" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B286" s="151"/>
       <c r="C286" s="195"/>
@@ -31408,7 +31415,7 @@
     </row>
     <row r="287" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="72" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B287" s="151"/>
       <c r="C287" s="195"/>
@@ -31419,7 +31426,7 @@
     </row>
     <row r="288" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="72" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B288" s="151"/>
       <c r="C288" s="195"/>
@@ -31430,7 +31437,7 @@
     </row>
     <row r="289" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="72" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B289" s="151"/>
       <c r="C289" s="195"/>
@@ -31441,7 +31448,7 @@
     </row>
     <row r="290" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="72" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B290" s="151"/>
       <c r="C290" s="195"/>
@@ -31452,7 +31459,7 @@
     </row>
     <row r="291" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="72" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B291" s="151"/>
       <c r="C291" s="195"/>
@@ -31463,7 +31470,7 @@
     </row>
     <row r="292" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="72" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B292" s="151"/>
       <c r="C292" s="195"/>
@@ -31474,7 +31481,7 @@
     </row>
     <row r="293" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="72" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B293" s="151"/>
       <c r="C293" s="195"/>
@@ -31485,7 +31492,7 @@
     </row>
     <row r="294" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="72" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B294" s="151"/>
       <c r="C294" s="195"/>
@@ -31496,7 +31503,7 @@
     </row>
     <row r="295" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="72" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B295" s="151"/>
       <c r="C295" s="195"/>
@@ -31507,7 +31514,7 @@
     </row>
     <row r="296" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="72" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B296" s="151"/>
       <c r="C296" s="195"/>
@@ -31518,7 +31525,7 @@
     </row>
     <row r="297" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="72" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B297" s="151"/>
       <c r="C297" s="195"/>
@@ -31529,7 +31536,7 @@
     </row>
     <row r="298" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="72" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B298" s="151"/>
       <c r="C298" s="195"/>
@@ -31540,7 +31547,7 @@
     </row>
     <row r="299" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="72" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B299" s="151"/>
       <c r="C299" s="195"/>
@@ -31551,7 +31558,7 @@
     </row>
     <row r="300" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="72" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B300" s="151"/>
       <c r="C300" s="195"/>
@@ -31562,7 +31569,7 @@
     </row>
     <row r="301" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="72" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B301" s="151"/>
       <c r="C301" s="195"/>
@@ -31573,7 +31580,7 @@
     </row>
     <row r="302" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="72" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B302" s="151"/>
       <c r="C302" s="195"/>
@@ -31584,7 +31591,7 @@
     </row>
     <row r="303" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="72" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B303" s="151"/>
       <c r="C303" s="195"/>
@@ -31595,7 +31602,7 @@
     </row>
     <row r="304" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="72" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B304" s="151"/>
       <c r="C304" s="195"/>
@@ -31606,7 +31613,7 @@
     </row>
     <row r="305" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="72" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B305" s="151"/>
       <c r="C305" s="195"/>
@@ -31617,7 +31624,7 @@
     </row>
     <row r="306" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="72" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B306" s="151"/>
       <c r="C306" s="195"/>
@@ -31628,7 +31635,7 @@
     </row>
     <row r="307" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="72" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B307" s="151"/>
       <c r="C307" s="195"/>
@@ -31639,7 +31646,7 @@
     </row>
     <row r="308" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="72" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B308" s="151"/>
       <c r="C308" s="195"/>
@@ -31650,7 +31657,7 @@
     </row>
     <row r="309" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="72" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B309" s="151"/>
       <c r="C309" s="195"/>
@@ -31661,7 +31668,7 @@
     </row>
     <row r="310" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="72" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B310" s="151"/>
       <c r="C310" s="195"/>
@@ -31672,7 +31679,7 @@
     </row>
     <row r="311" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="72" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B311" s="151"/>
       <c r="C311" s="195"/>
@@ -31683,7 +31690,7 @@
     </row>
     <row r="312" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="72" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B312" s="151"/>
       <c r="C312" s="195"/>
@@ -31694,7 +31701,7 @@
     </row>
     <row r="313" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="72" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B313" s="151"/>
       <c r="C313" s="195"/>
@@ -31705,7 +31712,7 @@
     </row>
     <row r="314" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="72" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B314" s="151"/>
       <c r="C314" s="195"/>
@@ -31717,7 +31724,7 @@
     </row>
     <row r="315" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="72" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B315" s="151"/>
       <c r="C315" s="195"/>
@@ -31729,7 +31736,7 @@
     </row>
     <row r="316" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="72" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B316" s="151"/>
       <c r="C316" s="195"/>
@@ -31741,7 +31748,7 @@
     </row>
     <row r="317" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="72" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B317" s="151"/>
       <c r="C317" s="195"/>
@@ -31752,7 +31759,7 @@
     </row>
     <row r="318" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="72" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B318" s="151"/>
       <c r="C318" s="195"/>
@@ -31763,7 +31770,7 @@
     </row>
     <row r="319" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="72" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B319" s="151"/>
       <c r="C319" s="195"/>
@@ -31774,7 +31781,7 @@
     </row>
     <row r="320" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="72" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B320" s="151"/>
       <c r="C320" s="195"/>
@@ -31785,7 +31792,7 @@
     </row>
     <row r="321" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="72" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B321" s="151"/>
       <c r="C321" s="195"/>
@@ -31796,7 +31803,7 @@
     </row>
     <row r="322" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="72" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B322" s="151"/>
       <c r="C322" s="195"/>
@@ -31807,7 +31814,7 @@
     </row>
     <row r="323" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="72" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B323" s="151"/>
       <c r="C323" s="195"/>
@@ -31818,7 +31825,7 @@
     </row>
     <row r="324" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="72" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B324" s="151"/>
       <c r="C324" s="195"/>
@@ -31829,7 +31836,7 @@
     </row>
     <row r="325" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="72" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B325" s="151"/>
       <c r="C325" s="195"/>
@@ -31840,7 +31847,7 @@
     </row>
     <row r="326" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="72" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B326" s="151"/>
       <c r="C326" s="195"/>
@@ -31851,7 +31858,7 @@
     </row>
     <row r="327" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="72" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B327" s="151"/>
       <c r="C327" s="195"/>
@@ -31862,7 +31869,7 @@
     </row>
     <row r="328" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="72" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B328" s="151"/>
       <c r="C328" s="195"/>
@@ -31873,7 +31880,7 @@
     </row>
     <row r="329" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="72" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B329" s="151"/>
       <c r="C329" s="195"/>
@@ -31884,7 +31891,7 @@
     </row>
     <row r="330" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="151" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B330" s="151"/>
       <c r="C330" s="195"/>
@@ -31895,7 +31902,7 @@
     </row>
     <row r="331" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="151" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B331" s="151"/>
       <c r="C331" s="195"/>
@@ -31906,7 +31913,7 @@
     </row>
     <row r="332" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="151" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B332" s="151"/>
       <c r="C332" s="195"/>
@@ -31917,7 +31924,7 @@
     </row>
     <row r="333" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="151" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B333" s="151"/>
       <c r="C333" s="195"/>
@@ -31928,7 +31935,7 @@
     </row>
     <row r="334" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="151" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B334" s="151"/>
       <c r="C334" s="195"/>
@@ -31939,7 +31946,7 @@
     </row>
     <row r="335" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="151" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B335" s="151"/>
       <c r="C335" s="195"/>
@@ -31950,7 +31957,7 @@
     </row>
     <row r="336" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="72" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B336" s="151"/>
       <c r="C336" s="195"/>
@@ -31961,7 +31968,7 @@
     </row>
     <row r="337" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="72" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B337" s="151"/>
       <c r="C337" s="195"/>
@@ -31972,7 +31979,7 @@
     </row>
     <row r="338" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="72" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B338" s="151"/>
       <c r="C338" s="195"/>
@@ -31988,10 +31995,10 @@
       <c r="D339" s="225"/>
       <c r="E339" s="195"/>
       <c r="F339" s="238" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="G339" s="239" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="340" ht="10.15" customHeight="1" hidden="1" spans="1:7" s="235" customFormat="1" x14ac:dyDescent="0.25">
@@ -32216,7 +32223,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="H367" s="72" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="368" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -32246,7 +32253,7 @@
       <c r="F369" s="220"/>
       <c r="G369" s="225"/>
       <c r="H369" s="72" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -32264,10 +32271,10 @@
       <c r="E371" s="140"/>
       <c r="F371" s="220"/>
       <c r="G371" s="244" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H371" s="245" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="372" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -473,7 +473,7 @@
     <t>- Tasa Seguridad e Higiene a pagar</t>
   </si>
   <si>
-    <t xml:space="preserve"> - Retención SUSS</t>
+    <t>- Patentes a pagar</t>
   </si>
   <si>
     <t>- Tasas Retributivas Mineras</t>
@@ -572,7 +572,7 @@
     <t>EJERCICIO</t>
   </si>
   <si>
-    <t>AL 31.5.26</t>
+    <t>AL 30.6.26</t>
   </si>
   <si>
     <t>- Muebles y Utiles</t>
@@ -6592,10 +6592,7 @@
         <f>SUM(I10:I102)</f>
         <v>0</v>
       </c>
-      <c r="J103" s="130" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="J103" s="130"/>
     </row>
     <row r="104" ht="10.9" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
@@ -34880,10 +34877,7 @@
         <f>+'Activo y Pasivo'!F18</f>
         <v>20554136.340000004</v>
       </c>
-      <c r="G8" s="17" t="e">
-        <f>+'Activo y Pasivo'!#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G8" s="17"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
@@ -34959,10 +34953,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="21" t="e">
-        <f>SUM(G8:G8)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G11" s="21"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -35085,10 +35076,7 @@
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="16"/>
-      <c r="G17" s="16" t="e">
-        <f>+#REF!</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G17" s="16"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="s">
         <v>21</v>
@@ -35131,10 +35119,7 @@
         <f>SUM(F15:F18)</f>
         <v>24748088.790000007</v>
       </c>
-      <c r="G19" s="23" t="e">
-        <f>SUM(G17:G18)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G19" s="23"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -35169,10 +35154,7 @@
         <f>+F12+F19</f>
         <v>2158175704.5099998</v>
       </c>
-      <c r="G21" s="30" t="e">
-        <f>+G11+G19</f>
-        <v>#REF!</v>
-      </c>
+      <c r="G21" s="30"/>
       <c r="H21" s="28"/>
       <c r="I21" s="29" t="s">
         <v>24</v>

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1353" uniqueCount="872">
   <si>
     <t>ESTADO DE SITUACION PATRIMONIAL</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>Otros Activos</t>
+  </si>
+  <si>
+    <t>- Socios</t>
   </si>
   <si>
     <t>Activo No Corriente</t>
@@ -4394,7 +4397,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -4407,7 +4410,7 @@
     </row>
     <row r="3" ht="11.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4417,7 +4420,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" ht="11.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -4440,22 +4443,22 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="48" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F6" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="H6" s="48" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" s="115" t="s">
+        <v>196</v>
+      </c>
+      <c r="J6" s="116" t="s">
         <v>195</v>
-      </c>
-      <c r="G6" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="H6" s="48" t="s">
-        <v>196</v>
-      </c>
-      <c r="I6" s="115" t="s">
-        <v>195</v>
-      </c>
-      <c r="J6" s="116" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4463,25 +4466,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="55" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G7" s="55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H7" s="55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I7" s="117"/>
       <c r="J7" s="118" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4494,19 +4497,19 @@
         <v>NaN</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J8" s="122" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4523,10 +4526,10 @@
     </row>
     <row r="10" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B10" s="71" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -4545,10 +4548,10 @@
     </row>
     <row r="11" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B11" s="71" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -4567,10 +4570,10 @@
     </row>
     <row r="12" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -4589,10 +4592,10 @@
     </row>
     <row r="13" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B13" s="71" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -4611,10 +4614,10 @@
     </row>
     <row r="14" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B14" s="71" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4633,10 +4636,10 @@
     </row>
     <row r="15" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -4655,10 +4658,10 @@
     </row>
     <row r="16" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B16" s="71" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -4677,10 +4680,10 @@
     </row>
     <row r="17" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B17" s="71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -4699,10 +4702,10 @@
     </row>
     <row r="18" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B18" s="71" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -4721,10 +4724,10 @@
     </row>
     <row r="19" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B19" s="71" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -4743,10 +4746,10 @@
     </row>
     <row r="20" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" s="71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -4765,10 +4768,10 @@
     </row>
     <row r="21" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B21" s="71" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
@@ -4790,10 +4793,10 @@
     </row>
     <row r="22" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B22" s="71" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
@@ -4812,10 +4815,10 @@
     </row>
     <row r="23" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B23" s="71" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -4831,10 +4834,10 @@
     </row>
     <row r="24" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B24" s="71" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -4853,10 +4856,10 @@
     </row>
     <row r="25" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B25" s="71" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -4875,10 +4878,10 @@
     </row>
     <row r="26" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B26" s="71" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -4897,10 +4900,10 @@
     </row>
     <row r="27" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B27" s="71" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -4916,10 +4919,10 @@
     </row>
     <row r="28" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B28" s="71" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -4938,10 +4941,10 @@
     </row>
     <row r="29" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B29" s="71" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -4957,10 +4960,10 @@
     </row>
     <row r="30" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B30" s="71" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -4979,10 +4982,10 @@
     </row>
     <row r="31" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B31" s="71" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -5001,10 +5004,10 @@
     </row>
     <row r="32" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B32" s="71" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -5023,10 +5026,10 @@
     </row>
     <row r="33" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B33" s="71" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -5045,10 +5048,10 @@
     </row>
     <row r="34" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B34" s="71" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -5067,10 +5070,10 @@
     </row>
     <row r="35" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
@@ -5089,10 +5092,10 @@
     </row>
     <row r="36" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -5114,10 +5117,10 @@
     </row>
     <row r="37" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B37" s="71" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -5136,10 +5139,10 @@
     </row>
     <row r="38" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B38" s="71" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -5158,10 +5161,10 @@
     </row>
     <row r="39" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" s="71" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -5180,10 +5183,10 @@
     </row>
     <row r="40" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
@@ -5202,10 +5205,10 @@
     </row>
     <row r="41" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
@@ -5224,10 +5227,10 @@
     </row>
     <row r="42" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
@@ -5246,10 +5249,10 @@
     </row>
     <row r="43" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
@@ -5268,10 +5271,10 @@
     </row>
     <row r="44" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
@@ -5290,10 +5293,10 @@
     </row>
     <row r="45" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -5312,10 +5315,10 @@
     </row>
     <row r="46" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -5334,10 +5337,10 @@
     </row>
     <row r="47" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
@@ -5356,10 +5359,10 @@
     </row>
     <row r="48" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -5378,10 +5381,10 @@
     </row>
     <row r="49" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -5400,10 +5403,10 @@
     </row>
     <row r="50" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B50" s="71" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -5422,10 +5425,10 @@
     </row>
     <row r="51" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B51" s="71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -5444,10 +5447,10 @@
     </row>
     <row r="52" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B52" s="71" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -5469,10 +5472,10 @@
     </row>
     <row r="53" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B53" s="71" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -5491,10 +5494,10 @@
     </row>
     <row r="54" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B54" s="71" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
@@ -5513,10 +5516,10 @@
     </row>
     <row r="55" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
@@ -5535,10 +5538,10 @@
     </row>
     <row r="56" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -5557,10 +5560,10 @@
     </row>
     <row r="57" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -5579,10 +5582,10 @@
     </row>
     <row r="58" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -5601,10 +5604,10 @@
     </row>
     <row r="59" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -5623,10 +5626,10 @@
     </row>
     <row r="60" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -5645,10 +5648,10 @@
     </row>
     <row r="61" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" s="71" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -5667,10 +5670,10 @@
     </row>
     <row r="62" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B62" s="71" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
@@ -5689,10 +5692,10 @@
     </row>
     <row r="63" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B63" s="71" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -5714,10 +5717,10 @@
     </row>
     <row r="64" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B64" s="71" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -5736,10 +5739,10 @@
     </row>
     <row r="65" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B65" s="71" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -5758,10 +5761,10 @@
     </row>
     <row r="66" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B66" s="71" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -5777,10 +5780,10 @@
     </row>
     <row r="67" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B67" s="71" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -5799,10 +5802,10 @@
     </row>
     <row r="68" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B68" s="71" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -5818,10 +5821,10 @@
     </row>
     <row r="69" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B69" s="71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -5840,10 +5843,10 @@
     </row>
     <row r="70" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B70" s="71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="71" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B71" s="71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -5881,10 +5884,10 @@
     </row>
     <row r="72" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B72" s="71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -5903,10 +5906,10 @@
     </row>
     <row r="73" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -5925,10 +5928,10 @@
     </row>
     <row r="74" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -5947,10 +5950,10 @@
     </row>
     <row r="75" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -5969,10 +5972,10 @@
     </row>
     <row r="76" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B76" s="71" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -5991,10 +5994,10 @@
     </row>
     <row r="77" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B77" s="71" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -6013,10 +6016,10 @@
     </row>
     <row r="78" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B78" s="71" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -6035,10 +6038,10 @@
     </row>
     <row r="79" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B79" s="71" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -6057,10 +6060,10 @@
     </row>
     <row r="80" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B80" s="71" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -6079,10 +6082,10 @@
     </row>
     <row r="81" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B81" s="71" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -6104,10 +6107,10 @@
     </row>
     <row r="82" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B82" s="71" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -6129,10 +6132,10 @@
     </row>
     <row r="83" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B83" s="71" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -6153,10 +6156,10 @@
     </row>
     <row r="84" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B84" s="71" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -6175,10 +6178,10 @@
     </row>
     <row r="85" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B85" s="71" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -6197,10 +6200,10 @@
     </row>
     <row r="86" ht="11.25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B86" s="71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -6219,10 +6222,10 @@
     </row>
     <row r="87" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B87" s="71" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -6241,10 +6244,10 @@
     </row>
     <row r="88" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B88" s="71" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -6263,10 +6266,10 @@
     </row>
     <row r="89" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B89" s="71" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -6285,10 +6288,10 @@
     </row>
     <row r="90" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B90" s="71" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -6307,10 +6310,10 @@
     </row>
     <row r="91" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B91" s="71" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -6329,10 +6332,10 @@
     </row>
     <row r="92" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B92" s="71" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -6349,7 +6352,7 @@
     <row r="93" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="7"/>
       <c r="B93" s="71" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -6368,10 +6371,10 @@
     </row>
     <row r="94" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B94" s="71" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
@@ -6390,10 +6393,10 @@
     </row>
     <row r="95" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B95" s="71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
@@ -6412,10 +6415,10 @@
     </row>
     <row r="96" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B96" s="71" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
@@ -6434,10 +6437,10 @@
     </row>
     <row r="97" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B97" s="71" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
@@ -6456,10 +6459,10 @@
     </row>
     <row r="98" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B98" s="71" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
@@ -6478,10 +6481,10 @@
     </row>
     <row r="99" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B99" s="71" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
@@ -6500,10 +6503,10 @@
     </row>
     <row r="100" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B100" s="71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
@@ -6522,10 +6525,10 @@
     </row>
     <row r="101" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B101" s="71" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
@@ -6544,10 +6547,10 @@
     </row>
     <row r="102" ht="10.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
@@ -6743,13 +6746,13 @@
       <c r="I1" s="77"/>
       <c r="J1" s="77"/>
       <c r="K1" s="78" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" ht="13.9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" ht="13.9" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="79" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B4" s="80"/>
       <c r="C4" s="80"/>
@@ -6764,7 +6767,7 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="82" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B5" s="78"/>
       <c r="C5" s="78"/>
@@ -6812,13 +6815,13 @@
         <v>2</v>
       </c>
       <c r="B8" s="90" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C8" s="90"/>
       <c r="D8" s="90"/>
       <c r="E8" s="90"/>
       <c r="F8" s="90" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G8" s="90"/>
       <c r="H8" s="90"/>
@@ -6829,26 +6832,26 @@
     <row r="9" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="92"/>
       <c r="B9" s="93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C9" s="93"/>
       <c r="D9" s="93"/>
       <c r="E9" s="93" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F9" s="93" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G9" s="93"/>
       <c r="H9" s="94" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I9" s="95"/>
       <c r="J9" s="93" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K9" s="96" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6856,59 +6859,59 @@
         <v>51</v>
       </c>
       <c r="B10" s="93" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C10" s="93" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" s="93" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E10" s="93" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F10" s="93" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G10" s="93" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H10" s="93" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I10" s="93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J10" s="93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K10" s="96" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="92"/>
       <c r="B11" s="93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C11" s="93"/>
       <c r="D11" s="93"/>
       <c r="E11" s="93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F11" s="93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G11" s="93"/>
       <c r="H11" s="93"/>
       <c r="I11" s="93" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J11" s="93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K11" s="96" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6970,7 +6973,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="103" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B15" s="104">
         <v>7137147.140000001</v>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="103" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B16" s="104">
         <v>9983623.870000001</v>
@@ -7060,7 +7063,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="103" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B17" s="104">
         <v>2163642.25</v>
@@ -7105,7 +7108,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="103" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B18" s="104">
         <v>1676263.99</v>
@@ -7149,7 +7152,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="103" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B19" s="104">
         <v>5362126.44</v>
@@ -7193,7 +7196,7 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="103" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" s="104">
         <v>5117083.33</v>
@@ -7237,7 +7240,7 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="103" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="105">
         <v>20790195.080000002</v>
@@ -7282,7 +7285,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="103" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B22" s="104">
         <v>1598074.09</v>
@@ -7341,7 +7344,7 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="98" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B24" s="110">
         <f>SUM(B15:B23)</f>
@@ -7573,21 +7576,21 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="135" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="135" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C1" s="71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D1" s="135" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E1" s="135"/>
       <c r="F1" s="135"/>
       <c r="G1" s="136" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7605,10 +7608,10 @@
       <c r="A3" s="137"/>
       <c r="B3" s="137"/>
       <c r="C3" s="139" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D3" s="71" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E3" s="68"/>
       <c r="F3" s="140"/>
@@ -7621,10 +7624,10 @@
       <c r="A4" s="137"/>
       <c r="B4" s="137"/>
       <c r="C4" s="139" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D4" s="139" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E4" s="72"/>
       <c r="F4" s="140"/>
@@ -7637,10 +7640,10 @@
       <c r="A5" s="137"/>
       <c r="B5" s="137"/>
       <c r="C5" s="139" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D5" s="71" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E5" s="68"/>
       <c r="F5" s="140"/>
@@ -7653,10 +7656,10 @@
       <c r="A6" s="137"/>
       <c r="B6" s="137"/>
       <c r="C6" s="139" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D6" s="139" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E6" s="68"/>
       <c r="F6" s="140"/>
@@ -7670,10 +7673,10 @@
       <c r="A7" s="137"/>
       <c r="B7" s="137"/>
       <c r="C7" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D7" s="139" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E7" s="68"/>
       <c r="F7" s="140"/>
@@ -7687,10 +7690,10 @@
       <c r="A8" s="137"/>
       <c r="B8" s="137"/>
       <c r="C8" s="139" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D8" s="139" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E8" s="68"/>
       <c r="F8" s="140"/>
@@ -7704,10 +7707,10 @@
       <c r="A9" s="137"/>
       <c r="B9" s="137"/>
       <c r="C9" s="139" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D9" s="139" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E9" s="68"/>
       <c r="F9" s="140"/>
@@ -7721,10 +7724,10 @@
       <c r="A10" s="137"/>
       <c r="B10" s="137"/>
       <c r="C10" s="139" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D10" s="71" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E10" s="68"/>
       <c r="F10" s="140"/>
@@ -7737,10 +7740,10 @@
       <c r="A11" s="137"/>
       <c r="B11" s="137"/>
       <c r="C11" s="139" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D11" s="139" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E11" s="71"/>
       <c r="F11" s="140"/>
@@ -7753,10 +7756,10 @@
       <c r="A12" s="137"/>
       <c r="B12" s="137"/>
       <c r="C12" s="139" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D12" s="139" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E12" s="71"/>
       <c r="F12" s="140"/>
@@ -7781,10 +7784,10 @@
       <c r="A14" s="145"/>
       <c r="B14" s="145"/>
       <c r="C14" s="146" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D14" s="147" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E14" s="147"/>
       <c r="F14" s="140"/>
@@ -7801,10 +7804,10 @@
       <c r="A15" s="137"/>
       <c r="B15" s="137"/>
       <c r="C15" s="139" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="D15" s="71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E15" s="68"/>
       <c r="F15" s="140"/>
@@ -7817,10 +7820,10 @@
       <c r="A16" s="137"/>
       <c r="B16" s="137"/>
       <c r="C16" s="139" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D16" s="71" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E16" s="68"/>
       <c r="F16" s="140"/>
@@ -7833,10 +7836,10 @@
       <c r="A17" s="137"/>
       <c r="B17" s="137"/>
       <c r="C17" s="139" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D17" s="71" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E17" s="71"/>
       <c r="F17" s="140"/>
@@ -7850,10 +7853,10 @@
       <c r="A18" s="137"/>
       <c r="B18" s="137"/>
       <c r="C18" s="139" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E18" s="68"/>
       <c r="F18" s="140"/>
@@ -7866,10 +7869,10 @@
       <c r="A19" s="137"/>
       <c r="B19" s="137"/>
       <c r="C19" s="139" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D19" s="71" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E19" s="68"/>
       <c r="F19" s="140"/>
@@ -7882,10 +7885,10 @@
       <c r="A20" s="137"/>
       <c r="B20" s="137"/>
       <c r="C20" s="139" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D20" s="71" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E20" s="68"/>
       <c r="F20" s="140"/>
@@ -7898,10 +7901,10 @@
       <c r="A21" s="137"/>
       <c r="B21" s="137"/>
       <c r="C21" s="151" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D21" s="71" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E21" s="71"/>
       <c r="F21" s="140"/>
@@ -7914,10 +7917,10 @@
       <c r="A22" s="137"/>
       <c r="B22" s="137"/>
       <c r="C22" s="139" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D22" s="71" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E22" s="68"/>
       <c r="F22" s="140"/>
@@ -7930,10 +7933,10 @@
       <c r="A23" s="137"/>
       <c r="B23" s="137"/>
       <c r="C23" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D23" s="71" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E23" s="68"/>
       <c r="F23" s="140"/>
@@ -7946,10 +7949,10 @@
       <c r="A24" s="137"/>
       <c r="B24" s="137"/>
       <c r="C24" s="139" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D24" s="71" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E24" s="68"/>
       <c r="F24" s="140"/>
@@ -7962,10 +7965,10 @@
       <c r="A25" s="137"/>
       <c r="B25" s="137"/>
       <c r="C25" s="139" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D25" s="139" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E25" s="71"/>
       <c r="F25" s="140"/>
@@ -7978,10 +7981,10 @@
       <c r="A26" s="137"/>
       <c r="B26" s="137"/>
       <c r="C26" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D26" s="139" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E26" s="71"/>
       <c r="F26" s="140"/>
@@ -7994,10 +7997,10 @@
       <c r="A27" s="137"/>
       <c r="B27" s="137"/>
       <c r="C27" s="139" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D27" s="139" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="140"/>
@@ -8010,10 +8013,10 @@
       <c r="A28" s="137"/>
       <c r="B28" s="137"/>
       <c r="C28" s="139" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D28" s="71" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="140"/>
@@ -8026,10 +8029,10 @@
       <c r="A29" s="137"/>
       <c r="B29" s="137"/>
       <c r="C29" s="151" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D29" s="71" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E29" s="68"/>
       <c r="F29" s="140"/>
@@ -8042,10 +8045,10 @@
       <c r="A30" s="137"/>
       <c r="B30" s="137"/>
       <c r="C30" s="151" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D30" s="71" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E30" s="150"/>
       <c r="F30" s="140"/>
@@ -8058,10 +8061,10 @@
       <c r="A31" s="137"/>
       <c r="B31" s="137"/>
       <c r="C31" s="139" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D31" s="139" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E31" s="68"/>
       <c r="F31" s="140"/>
@@ -8074,10 +8077,10 @@
       <c r="A32" s="137"/>
       <c r="B32" s="137"/>
       <c r="C32" s="139" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D32" s="139" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E32" s="68"/>
       <c r="F32" s="140"/>
@@ -8091,10 +8094,10 @@
       <c r="A33" s="137"/>
       <c r="B33" s="137"/>
       <c r="C33" s="139" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D33" s="139" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E33" s="72"/>
       <c r="F33" s="140"/>
@@ -8107,10 +8110,10 @@
       <c r="A34" s="137"/>
       <c r="B34" s="137"/>
       <c r="C34" s="139" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D34" s="71" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E34" s="71"/>
       <c r="F34" s="140"/>
@@ -8123,10 +8126,10 @@
       <c r="A35" s="137"/>
       <c r="B35" s="137"/>
       <c r="C35" s="139" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D35" s="71" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E35" s="71"/>
       <c r="F35" s="140"/>
@@ -8139,10 +8142,10 @@
       <c r="A36" s="137"/>
       <c r="B36" s="137"/>
       <c r="C36" s="139" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="D36" s="139" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E36" s="72"/>
       <c r="F36" s="140"/>
@@ -8155,10 +8158,10 @@
       <c r="A37" s="137"/>
       <c r="B37" s="137"/>
       <c r="C37" s="139" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D37" s="139" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E37" s="68"/>
       <c r="F37" s="140"/>
@@ -8171,10 +8174,10 @@
       <c r="A38" s="137"/>
       <c r="B38" s="137"/>
       <c r="C38" s="139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D38" s="139" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E38" s="72"/>
       <c r="F38" s="140"/>
@@ -8199,10 +8202,10 @@
       <c r="A40" s="137"/>
       <c r="B40" s="137"/>
       <c r="C40" s="151" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D40" s="71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E40" s="71"/>
       <c r="F40" s="140"/>
@@ -8215,10 +8218,10 @@
       <c r="A41" s="137"/>
       <c r="B41" s="137"/>
       <c r="C41" s="151" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D41" s="71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E41" s="71"/>
       <c r="F41" s="140"/>
@@ -8231,10 +8234,10 @@
       <c r="A42" s="137"/>
       <c r="B42" s="137"/>
       <c r="C42" s="151" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D42" s="71" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E42" s="68"/>
       <c r="F42" s="140"/>
@@ -8252,10 +8255,10 @@
       <c r="A43" s="137"/>
       <c r="B43" s="137"/>
       <c r="C43" s="151" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D43" s="139" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E43" s="72"/>
       <c r="F43" s="140"/>
@@ -8273,10 +8276,10 @@
       <c r="A44" s="137"/>
       <c r="B44" s="137"/>
       <c r="C44" s="153" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D44" s="154" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E44" s="155"/>
       <c r="F44" s="156"/>
@@ -8285,17 +8288,17 @@
         <v>7137147.140000001</v>
       </c>
       <c r="H44" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="45" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="137"/>
       <c r="B45" s="137"/>
       <c r="C45" s="153" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D45" s="154" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E45" s="155"/>
       <c r="F45" s="156"/>
@@ -8304,17 +8307,17 @@
         <v>2163642.25</v>
       </c>
       <c r="H45" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="46" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="137"/>
       <c r="B46" s="137"/>
       <c r="C46" s="153" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D46" s="154" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E46" s="155"/>
       <c r="F46" s="156"/>
@@ -8323,17 +8326,17 @@
         <v>1676263.99</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="47" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="137"/>
       <c r="B47" s="137"/>
       <c r="C47" s="153" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D47" s="154" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E47" s="155"/>
       <c r="F47" s="156"/>
@@ -8342,17 +8345,17 @@
         <v>8463010.92</v>
       </c>
       <c r="H47" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="137"/>
       <c r="B48" s="137"/>
       <c r="C48" s="153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D48" s="153" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E48" s="155"/>
       <c r="F48" s="156"/>
@@ -8361,17 +8364,17 @@
         <v>5117083.33</v>
       </c>
       <c r="H48" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="137"/>
       <c r="B49" s="137"/>
       <c r="C49" s="158" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D49" s="154" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E49" s="155"/>
       <c r="F49" s="156"/>
@@ -8380,7 +8383,7 @@
         <v>-3124708.59</v>
       </c>
       <c r="H49" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I49" s="134">
         <f>+'Anexo I'!J15</f>
@@ -8395,10 +8398,10 @@
       <c r="A50" s="137"/>
       <c r="B50" s="137"/>
       <c r="C50" s="158" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D50" s="154" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E50" s="155"/>
       <c r="F50" s="156"/>
@@ -8407,7 +8410,7 @@
         <v>-1499006.23</v>
       </c>
       <c r="H50" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I50" s="134">
         <f>+'Anexo I'!J17</f>
@@ -8422,10 +8425,10 @@
       <c r="A51" s="137"/>
       <c r="B51" s="137"/>
       <c r="C51" s="158" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D51" s="154" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E51" s="155"/>
       <c r="F51" s="156"/>
@@ -8434,7 +8437,7 @@
         <v>-776376.5700000001</v>
       </c>
       <c r="H51" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I51" s="134">
         <f>+'Anexo I'!J18</f>
@@ -8449,10 +8452,10 @@
       <c r="A52" s="137"/>
       <c r="B52" s="137"/>
       <c r="C52" s="153" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D52" s="153" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E52" s="155"/>
       <c r="F52" s="156"/>
@@ -8461,17 +8464,17 @@
         <v>20790195.080000002</v>
       </c>
       <c r="H52" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="137"/>
       <c r="B53" s="137"/>
       <c r="C53" s="158" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D53" s="154" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E53" s="155"/>
       <c r="F53" s="156"/>
@@ -8480,7 +8483,7 @@
         <v>-4436234.05</v>
       </c>
       <c r="H53" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I53" s="134">
         <f>+'Anexo I'!J19</f>
@@ -8495,10 +8498,10 @@
       <c r="A54" s="137"/>
       <c r="B54" s="137"/>
       <c r="C54" s="158" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D54" s="154" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E54" s="155"/>
       <c r="F54" s="156"/>
@@ -8507,7 +8510,7 @@
         <v>-5117083.33</v>
       </c>
       <c r="H54" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I54" s="134">
         <f>+'Anexo I'!J20</f>
@@ -8522,10 +8525,10 @@
       <c r="A55" s="137"/>
       <c r="B55" s="137"/>
       <c r="C55" s="158" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D55" s="154" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E55" s="155"/>
       <c r="F55" s="156"/>
@@ -8534,7 +8537,7 @@
         <v>-19606049.32</v>
       </c>
       <c r="H55" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I55" s="134">
         <f>+'Anexo I'!J21</f>
@@ -8549,10 +8552,10 @@
       <c r="A56" s="137"/>
       <c r="B56" s="137"/>
       <c r="C56" s="153" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D56" s="153" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E56" s="155"/>
       <c r="F56" s="156"/>
@@ -8561,17 +8564,17 @@
         <v>23184450.990000002</v>
       </c>
       <c r="H56" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="57" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="137"/>
       <c r="B57" s="137"/>
       <c r="C57" s="158" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D57" s="154" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E57" s="155"/>
       <c r="F57" s="156"/>
@@ -8580,7 +8583,7 @@
         <v>-10204568.26</v>
       </c>
       <c r="H57" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I57" s="134">
         <f>+'Anexo I'!J16</f>
@@ -8595,10 +8598,10 @@
       <c r="A58" s="137"/>
       <c r="B58" s="137"/>
       <c r="C58" s="153" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D58" s="153" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E58" s="155"/>
       <c r="F58" s="156"/>
@@ -8607,17 +8610,17 @@
         <v>1598074.09</v>
       </c>
       <c r="H58" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="59" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="137"/>
       <c r="B59" s="137"/>
       <c r="C59" s="158" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D59" s="154" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E59" s="155"/>
       <c r="F59" s="156"/>
@@ -8626,7 +8629,7 @@
         <v>-617752.65</v>
       </c>
       <c r="H59" s="75" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="I59" s="134">
         <f>+'Anexo I'!J22</f>
@@ -8643,10 +8646,10 @@
       <c r="A60" s="137"/>
       <c r="B60" s="137"/>
       <c r="C60" s="139" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D60" s="71" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E60" s="68"/>
       <c r="F60" s="140"/>
@@ -8664,10 +8667,10 @@
       <c r="A61" s="137"/>
       <c r="B61" s="137"/>
       <c r="C61" s="139" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D61" s="71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E61" s="68"/>
       <c r="F61" s="140"/>
@@ -8681,7 +8684,7 @@
         <v>2158175704.5099998</v>
       </c>
       <c r="J61" s="142" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K61" s="132"/>
       <c r="L61" s="132"/>
@@ -8700,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="142" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K62" s="132"/>
       <c r="L62" s="132"/>
@@ -8710,7 +8713,7 @@
       <c r="B63" s="137"/>
       <c r="C63" s="139"/>
       <c r="D63" s="72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E63" s="71"/>
       <c r="F63" s="140"/>
@@ -8728,7 +8731,7 @@
       <c r="B64" s="137"/>
       <c r="C64" s="139"/>
       <c r="D64" s="72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E64" s="71"/>
       <c r="F64" s="140"/>
@@ -8746,7 +8749,7 @@
       <c r="B65" s="137"/>
       <c r="C65" s="139"/>
       <c r="D65" s="72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E65" s="71"/>
       <c r="F65" s="140"/>
@@ -8764,7 +8767,7 @@
       <c r="B66" s="137"/>
       <c r="C66" s="139"/>
       <c r="D66" s="72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E66" s="71"/>
       <c r="F66" s="140"/>
@@ -8782,7 +8785,7 @@
       <c r="B67" s="137"/>
       <c r="C67" s="139"/>
       <c r="D67" s="72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E67" s="71"/>
       <c r="F67" s="140"/>
@@ -8800,7 +8803,7 @@
       <c r="B68" s="137"/>
       <c r="C68" s="139"/>
       <c r="D68" s="72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E68" s="71"/>
       <c r="F68" s="140"/>
@@ -8818,7 +8821,7 @@
       <c r="B69" s="137"/>
       <c r="C69" s="139"/>
       <c r="D69" s="72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E69" s="71"/>
       <c r="F69" s="140"/>
@@ -8836,7 +8839,7 @@
       <c r="B70" s="137"/>
       <c r="C70" s="139"/>
       <c r="D70" s="72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E70" s="71"/>
       <c r="F70" s="140"/>
@@ -8854,7 +8857,7 @@
       <c r="B71" s="137"/>
       <c r="C71" s="139"/>
       <c r="D71" s="72" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E71" s="71"/>
       <c r="F71" s="140"/>
@@ -8872,7 +8875,7 @@
       <c r="B72" s="137"/>
       <c r="C72" s="139"/>
       <c r="D72" s="72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E72" s="71"/>
       <c r="F72" s="140"/>
@@ -8890,7 +8893,7 @@
       <c r="B73" s="137"/>
       <c r="C73" s="139"/>
       <c r="D73" s="72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E73" s="71"/>
       <c r="F73" s="140"/>
@@ -8908,7 +8911,7 @@
       <c r="B74" s="137"/>
       <c r="C74" s="139"/>
       <c r="D74" s="72" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E74" s="71"/>
       <c r="F74" s="140"/>
@@ -8926,7 +8929,7 @@
       <c r="B75" s="137"/>
       <c r="C75" s="139"/>
       <c r="D75" s="72" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E75" s="71"/>
       <c r="F75" s="140"/>
@@ -8944,7 +8947,7 @@
       <c r="B76" s="137"/>
       <c r="C76" s="139"/>
       <c r="D76" s="72" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E76" s="71"/>
       <c r="F76" s="140"/>
@@ -8962,7 +8965,7 @@
       <c r="B77" s="137"/>
       <c r="C77" s="139"/>
       <c r="D77" s="72" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E77" s="71"/>
       <c r="F77" s="140"/>
@@ -8980,7 +8983,7 @@
       <c r="B78" s="137"/>
       <c r="C78" s="139"/>
       <c r="D78" s="72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E78" s="71"/>
       <c r="F78" s="140"/>
@@ -8998,7 +9001,7 @@
       <c r="B79" s="137"/>
       <c r="C79" s="139"/>
       <c r="D79" s="72" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E79" s="71"/>
       <c r="F79" s="140"/>
@@ -9016,7 +9019,7 @@
       <c r="B80" s="137"/>
       <c r="C80" s="139"/>
       <c r="D80" s="72" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E80" s="71"/>
       <c r="F80" s="140"/>
@@ -9034,7 +9037,7 @@
       <c r="B81" s="137"/>
       <c r="C81" s="139"/>
       <c r="D81" s="72" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E81" s="71"/>
       <c r="F81" s="140"/>
@@ -9052,7 +9055,7 @@
       <c r="B82" s="137"/>
       <c r="C82" s="139"/>
       <c r="D82" s="72" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E82" s="71"/>
       <c r="F82" s="140"/>
@@ -9070,7 +9073,7 @@
       <c r="B83" s="137"/>
       <c r="C83" s="139"/>
       <c r="D83" s="72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E83" s="71"/>
       <c r="F83" s="140"/>
@@ -9088,7 +9091,7 @@
       <c r="B84" s="137"/>
       <c r="C84" s="139"/>
       <c r="D84" s="72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E84" s="71"/>
       <c r="F84" s="140"/>
@@ -9106,7 +9109,7 @@
       <c r="B85" s="137"/>
       <c r="C85" s="139"/>
       <c r="D85" s="72" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E85" s="71"/>
       <c r="F85" s="140"/>
@@ -9124,7 +9127,7 @@
       <c r="B86" s="137"/>
       <c r="C86" s="139"/>
       <c r="D86" s="72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E86" s="71"/>
       <c r="F86" s="140"/>
@@ -9142,7 +9145,7 @@
       <c r="B87" s="137"/>
       <c r="C87" s="139"/>
       <c r="D87" s="72" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E87" s="71"/>
       <c r="F87" s="140"/>
@@ -9160,7 +9163,7 @@
       <c r="B88" s="137"/>
       <c r="C88" s="139"/>
       <c r="D88" s="72" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E88" s="71"/>
       <c r="F88" s="140"/>
@@ -9178,7 +9181,7 @@
       <c r="B89" s="137"/>
       <c r="C89" s="139"/>
       <c r="D89" s="72" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E89" s="71"/>
       <c r="F89" s="140"/>
@@ -9196,7 +9199,7 @@
       <c r="B90" s="137"/>
       <c r="C90" s="139"/>
       <c r="D90" s="72" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E90" s="71"/>
       <c r="F90" s="140"/>
@@ -9214,7 +9217,7 @@
       <c r="B91" s="137"/>
       <c r="C91" s="139"/>
       <c r="D91" s="72" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E91" s="71"/>
       <c r="F91" s="140"/>
@@ -9232,7 +9235,7 @@
       <c r="B92" s="137"/>
       <c r="C92" s="139"/>
       <c r="D92" s="72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E92" s="71"/>
       <c r="F92" s="140"/>
@@ -9250,7 +9253,7 @@
       <c r="B93" s="137"/>
       <c r="C93" s="139"/>
       <c r="D93" s="72" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E93" s="71"/>
       <c r="F93" s="140"/>
@@ -9268,7 +9271,7 @@
       <c r="B94" s="137"/>
       <c r="C94" s="139"/>
       <c r="D94" s="72" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E94" s="71"/>
       <c r="F94" s="140"/>
@@ -9286,7 +9289,7 @@
       <c r="B95" s="137"/>
       <c r="C95" s="139"/>
       <c r="D95" s="72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E95" s="71"/>
       <c r="F95" s="140"/>
@@ -9304,7 +9307,7 @@
       <c r="B96" s="137"/>
       <c r="C96" s="139"/>
       <c r="D96" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E96" s="71"/>
       <c r="F96" s="140"/>
@@ -9322,7 +9325,7 @@
       <c r="B97" s="137"/>
       <c r="C97" s="139"/>
       <c r="D97" s="72" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E97" s="71"/>
       <c r="F97" s="140"/>
@@ -9340,7 +9343,7 @@
       <c r="B98" s="137"/>
       <c r="C98" s="139"/>
       <c r="D98" s="72" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E98" s="71"/>
       <c r="F98" s="140"/>
@@ -9358,7 +9361,7 @@
       <c r="B99" s="137"/>
       <c r="C99" s="139"/>
       <c r="D99" s="72" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E99" s="71"/>
       <c r="F99" s="140"/>
@@ -9376,7 +9379,7 @@
       <c r="B100" s="137"/>
       <c r="C100" s="139"/>
       <c r="D100" s="72" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E100" s="71"/>
       <c r="F100" s="140"/>
@@ -9394,7 +9397,7 @@
       <c r="B101" s="137"/>
       <c r="C101" s="139"/>
       <c r="D101" s="72" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E101" s="71"/>
       <c r="F101" s="140"/>
@@ -9412,7 +9415,7 @@
       <c r="B102" s="137"/>
       <c r="C102" s="139"/>
       <c r="D102" s="72" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E102" s="71"/>
       <c r="F102" s="140"/>
@@ -9430,7 +9433,7 @@
       <c r="B103" s="137"/>
       <c r="C103" s="139"/>
       <c r="D103" s="72" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E103" s="71"/>
       <c r="F103" s="140"/>
@@ -9448,7 +9451,7 @@
       <c r="B104" s="137"/>
       <c r="C104" s="139"/>
       <c r="D104" s="72" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E104" s="71"/>
       <c r="F104" s="140"/>
@@ -9466,7 +9469,7 @@
       <c r="B105" s="137"/>
       <c r="C105" s="139"/>
       <c r="D105" s="72" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E105" s="71"/>
       <c r="F105" s="140"/>
@@ -9484,7 +9487,7 @@
       <c r="B106" s="137"/>
       <c r="C106" s="139"/>
       <c r="D106" s="72" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E106" s="71"/>
       <c r="F106" s="140"/>
@@ -9502,7 +9505,7 @@
       <c r="B107" s="137"/>
       <c r="C107" s="139"/>
       <c r="D107" s="72" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E107" s="71"/>
       <c r="F107" s="140"/>
@@ -9520,7 +9523,7 @@
       <c r="B108" s="137"/>
       <c r="C108" s="139"/>
       <c r="D108" s="72" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E108" s="71"/>
       <c r="F108" s="140"/>
@@ -9538,7 +9541,7 @@
       <c r="B109" s="137"/>
       <c r="C109" s="139"/>
       <c r="D109" s="72" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E109" s="71"/>
       <c r="F109" s="140"/>
@@ -9556,7 +9559,7 @@
       <c r="B110" s="137"/>
       <c r="C110" s="139"/>
       <c r="D110" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E110" s="71"/>
       <c r="F110" s="140"/>
@@ -9574,7 +9577,7 @@
       <c r="B111" s="137"/>
       <c r="C111" s="139"/>
       <c r="D111" s="72" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E111" s="71"/>
       <c r="F111" s="140"/>
@@ -9592,7 +9595,7 @@
       <c r="B112" s="137"/>
       <c r="C112" s="139"/>
       <c r="D112" s="72" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E112" s="71"/>
       <c r="F112" s="140"/>
@@ -9610,7 +9613,7 @@
       <c r="B113" s="137"/>
       <c r="C113" s="139"/>
       <c r="D113" s="72" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E113" s="71"/>
       <c r="F113" s="140"/>
@@ -9628,7 +9631,7 @@
       <c r="B114" s="137"/>
       <c r="C114" s="139"/>
       <c r="D114" s="72" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E114" s="71"/>
       <c r="F114" s="140"/>
@@ -9651,7 +9654,7 @@
       <c r="G115" s="161"/>
       <c r="H115" s="74"/>
       <c r="I115" s="134" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J115" s="132"/>
       <c r="K115" s="132"/>
@@ -9671,7 +9674,7 @@
         <v>-106687518.28999999</v>
       </c>
       <c r="J116" s="142" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K116" s="132"/>
       <c r="L116" s="132"/>
@@ -9722,10 +9725,10 @@
       <c r="A120" s="137"/>
       <c r="B120" s="137"/>
       <c r="C120" s="151" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D120" s="71" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E120" s="71"/>
       <c r="F120" s="140"/>
@@ -9737,10 +9740,10 @@
       <c r="A121" s="137"/>
       <c r="B121" s="137"/>
       <c r="C121" s="72" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D121" s="139" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E121" s="68"/>
       <c r="F121" s="140"/>
@@ -9752,10 +9755,10 @@
       <c r="A122" s="137"/>
       <c r="B122" s="137"/>
       <c r="C122" s="139" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D122" s="71" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E122" s="68"/>
       <c r="F122" s="140"/>
@@ -9768,7 +9771,7 @@
       <c r="B123" s="137"/>
       <c r="C123" s="139"/>
       <c r="D123" s="71" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E123" s="71"/>
       <c r="F123" s="140"/>
@@ -9781,7 +9784,7 @@
       <c r="B124" s="137"/>
       <c r="C124" s="139"/>
       <c r="D124" s="71" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E124" s="71"/>
       <c r="F124" s="140"/>
@@ -9793,7 +9796,7 @@
       <c r="A125" s="137"/>
       <c r="B125" s="137"/>
       <c r="C125" s="139" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D125" s="71"/>
       <c r="E125" s="71"/>
@@ -9808,7 +9811,7 @@
       <c r="B126" s="137"/>
       <c r="C126" s="139"/>
       <c r="D126" s="71" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E126" s="71"/>
       <c r="F126" s="140"/>
@@ -9825,10 +9828,10 @@
       <c r="A127" s="137"/>
       <c r="B127" s="137"/>
       <c r="C127" s="139" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D127" s="139" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E127" s="68"/>
       <c r="F127" s="140"/>
@@ -9843,10 +9846,10 @@
       <c r="A128" s="137"/>
       <c r="B128" s="137"/>
       <c r="C128" s="139" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D128" s="139" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E128" s="68"/>
       <c r="F128" s="140"/>
@@ -9859,7 +9862,7 @@
         <v>0</v>
       </c>
       <c r="J128" s="72" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9867,7 +9870,7 @@
       <c r="B129" s="137"/>
       <c r="C129" s="139"/>
       <c r="D129" s="139" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E129" s="68"/>
       <c r="F129" s="140"/>
@@ -9883,7 +9886,7 @@
       <c r="B130" s="137"/>
       <c r="C130" s="139"/>
       <c r="D130" s="139" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E130" s="68"/>
       <c r="F130" s="140"/>
@@ -9898,10 +9901,10 @@
       <c r="A131" s="137"/>
       <c r="B131" s="137"/>
       <c r="C131" s="72" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D131" s="139" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E131" s="68"/>
       <c r="F131" s="140"/>
@@ -9914,7 +9917,7 @@
       <c r="B132" s="137"/>
       <c r="C132" s="139"/>
       <c r="D132" s="71" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E132" s="71"/>
       <c r="F132" s="140"/>
@@ -9927,7 +9930,7 @@
       <c r="B133" s="137"/>
       <c r="C133" s="139"/>
       <c r="D133" s="139" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E133" s="71"/>
       <c r="F133" s="140"/>
@@ -9940,7 +9943,7 @@
       <c r="B134" s="137"/>
       <c r="C134" s="139"/>
       <c r="D134" s="139" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E134" s="71"/>
       <c r="F134" s="140"/>
@@ -9952,10 +9955,10 @@
       <c r="A135" s="137"/>
       <c r="B135" s="137"/>
       <c r="C135" s="139" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D135" s="139" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E135" s="71"/>
       <c r="F135" s="140"/>
@@ -9967,10 +9970,10 @@
       <c r="A136" s="137"/>
       <c r="B136" s="137"/>
       <c r="C136" s="72" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D136" s="135" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E136" s="71"/>
       <c r="F136" s="140"/>
@@ -9982,10 +9985,10 @@
       <c r="A137" s="167"/>
       <c r="B137" s="167"/>
       <c r="C137" s="168" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D137" s="169" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E137" s="170"/>
       <c r="F137" s="171"/>
@@ -10014,10 +10017,10 @@
       <c r="A139" s="137"/>
       <c r="B139" s="137"/>
       <c r="C139" s="72" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D139" s="71" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E139" s="68"/>
       <c r="F139" s="140"/>
@@ -10030,10 +10033,10 @@
       <c r="A140" s="137"/>
       <c r="B140" s="137"/>
       <c r="C140" s="72" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D140" s="71" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E140" s="150"/>
       <c r="F140" s="140"/>
@@ -10047,10 +10050,10 @@
       <c r="A141" s="137"/>
       <c r="B141" s="137"/>
       <c r="C141" s="72" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D141" s="71" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E141" s="68"/>
       <c r="F141" s="140"/>
@@ -10063,7 +10066,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="J141" s="142" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K141" s="19"/>
       <c r="L141" s="132"/>
@@ -10072,10 +10075,10 @@
       <c r="A142" s="137"/>
       <c r="B142" s="137"/>
       <c r="C142" s="72" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D142" s="139" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E142" s="68"/>
       <c r="F142" s="140"/>
@@ -10088,7 +10091,7 @@
         <v>3354028747.869999</v>
       </c>
       <c r="J142" s="142" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K142" s="19"/>
       <c r="L142" s="132"/>
@@ -10098,7 +10101,7 @@
       <c r="B143" s="137"/>
       <c r="C143" s="72"/>
       <c r="D143" s="71" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E143" s="71"/>
       <c r="F143" s="140"/>
@@ -10112,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="J143" s="142" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="144" ht="12.75" customHeight="1" spans="1:14" s="166" customFormat="1" x14ac:dyDescent="0.25">
@@ -10152,7 +10155,7 @@
       <c r="B146" s="137"/>
       <c r="C146" s="139"/>
       <c r="D146" s="71" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E146" s="71"/>
       <c r="F146" s="140"/>
@@ -10168,7 +10171,7 @@
       <c r="B147" s="137"/>
       <c r="C147" s="139"/>
       <c r="D147" s="71" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E147" s="71"/>
       <c r="F147" s="140"/>
@@ -10182,7 +10185,7 @@
       <c r="B148" s="137"/>
       <c r="C148" s="139"/>
       <c r="D148" s="139" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E148" s="72"/>
       <c r="F148" s="140"/>
@@ -10196,7 +10199,7 @@
       <c r="B149" s="137"/>
       <c r="C149" s="139"/>
       <c r="D149" s="139" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E149" s="72"/>
       <c r="F149" s="140"/>
@@ -10210,10 +10213,10 @@
       <c r="B150" s="137"/>
       <c r="C150" s="139"/>
       <c r="D150" s="139" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E150" s="72" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F150" s="140"/>
       <c r="G150" s="138">
@@ -10226,7 +10229,7 @@
       <c r="B151" s="137"/>
       <c r="C151" s="139"/>
       <c r="D151" s="139" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E151" s="72"/>
       <c r="F151" s="140">
@@ -10243,7 +10246,7 @@
       <c r="B152" s="137"/>
       <c r="C152" s="139"/>
       <c r="D152" s="139" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E152" s="72"/>
       <c r="F152" s="140">
@@ -10260,7 +10263,7 @@
       <c r="B153" s="137"/>
       <c r="C153" s="139"/>
       <c r="D153" s="139" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E153" s="72"/>
       <c r="F153" s="140">
@@ -10272,7 +10275,7 @@
         <v>6840000</v>
       </c>
       <c r="H153" s="34" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="154" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -10280,7 +10283,7 @@
       <c r="B154" s="137"/>
       <c r="C154" s="139"/>
       <c r="D154" s="71" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E154" s="71"/>
       <c r="F154" s="140">
@@ -10298,7 +10301,7 @@
       <c r="C155" s="139"/>
       <c r="D155" s="71"/>
       <c r="E155" s="72" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F155" s="140">
         <f>IFERROR(VLOOKUP(E155,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10314,7 +10317,7 @@
       <c r="C156" s="139"/>
       <c r="D156" s="71"/>
       <c r="E156" s="72" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F156" s="140">
         <f>IFERROR(VLOOKUP(E156,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10330,7 +10333,7 @@
       <c r="C157" s="139"/>
       <c r="D157" s="71"/>
       <c r="E157" s="72" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F157" s="140">
         <f>IFERROR(VLOOKUP(E157,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10346,7 +10349,7 @@
       <c r="C158" s="139"/>
       <c r="D158" s="71"/>
       <c r="E158" s="72" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F158" s="140">
         <f>IFERROR(VLOOKUP(E158,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10361,7 +10364,7 @@
       <c r="B159" s="137"/>
       <c r="C159" s="139"/>
       <c r="D159" s="71" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E159" s="71"/>
       <c r="F159" s="140"/>
@@ -10376,7 +10379,7 @@
       <c r="C160" s="139"/>
       <c r="D160" s="71"/>
       <c r="E160" s="72" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F160" s="140">
         <f>IFERROR(VLOOKUP(E160,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10390,7 +10393,7 @@
       <c r="C161" s="139"/>
       <c r="D161" s="71"/>
       <c r="E161" s="72" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F161" s="140">
         <f>IFERROR(VLOOKUP(E161,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10404,7 +10407,7 @@
       <c r="C162" s="139"/>
       <c r="D162" s="71"/>
       <c r="E162" s="72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F162" s="140">
         <f>IFERROR(VLOOKUP(E162,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10418,7 +10421,7 @@
       <c r="C163" s="139"/>
       <c r="D163" s="71"/>
       <c r="E163" s="72" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F163" s="140">
         <f>IFERROR(VLOOKUP(E163,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10432,7 +10435,7 @@
       <c r="C164" s="139"/>
       <c r="D164" s="71"/>
       <c r="E164" s="72" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F164" s="140">
         <f>IFERROR(VLOOKUP(E164,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10446,7 +10449,7 @@
       <c r="C165" s="139"/>
       <c r="D165" s="71"/>
       <c r="E165" s="72" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F165" s="140">
         <f>IFERROR(VLOOKUP(E165,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10460,7 +10463,7 @@
       <c r="C166" s="139"/>
       <c r="D166" s="71"/>
       <c r="E166" s="72" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F166" s="140">
         <f>IFERROR(VLOOKUP(E166,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10474,7 +10477,7 @@
       <c r="C167" s="139"/>
       <c r="D167" s="71"/>
       <c r="E167" s="72" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F167" s="140">
         <f>IFERROR(VLOOKUP(E167,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10487,7 +10490,7 @@
       <c r="B168" s="137"/>
       <c r="C168" s="139"/>
       <c r="D168" s="71" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E168" s="188"/>
       <c r="F168" s="140">
@@ -10505,7 +10508,7 @@
       <c r="B169" s="137"/>
       <c r="C169" s="139"/>
       <c r="D169" s="71" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E169" s="188"/>
       <c r="F169" s="140">
@@ -10522,7 +10525,7 @@
       <c r="B170" s="137"/>
       <c r="C170" s="139"/>
       <c r="D170" s="71" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E170" s="188"/>
       <c r="F170" s="140">
@@ -10545,7 +10548,7 @@
       <c r="B171" s="137"/>
       <c r="C171" s="139"/>
       <c r="D171" s="71" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E171" s="188"/>
       <c r="F171" s="150"/>
@@ -10560,7 +10563,7 @@
       <c r="C172" s="139"/>
       <c r="D172" s="71"/>
       <c r="E172" s="72" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F172" s="140">
         <f>IFERROR(VLOOKUP(E172,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10574,7 +10577,7 @@
       <c r="C173" s="139"/>
       <c r="D173" s="71"/>
       <c r="E173" s="72" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F173" s="140">
         <f>IFERROR(VLOOKUP(E173,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10588,7 +10591,7 @@
       <c r="C174" s="139"/>
       <c r="D174" s="71"/>
       <c r="E174" s="72" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F174" s="140">
         <f>IFERROR(VLOOKUP(E174,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10602,7 +10605,7 @@
       <c r="C175" s="139"/>
       <c r="D175" s="71"/>
       <c r="E175" s="72" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F175" s="140">
         <f>IFERROR(VLOOKUP(E175,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10616,7 +10619,7 @@
       <c r="C176" s="139"/>
       <c r="D176" s="71"/>
       <c r="E176" s="72" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F176" s="140">
         <f>IFERROR(VLOOKUP(E176,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10630,7 +10633,7 @@
       <c r="C177" s="139"/>
       <c r="D177" s="71"/>
       <c r="E177" s="72" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F177" s="140">
         <f>IFERROR(VLOOKUP(E177,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10643,7 +10646,7 @@
       <c r="B178" s="137"/>
       <c r="C178" s="139"/>
       <c r="D178" s="71" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E178" s="71"/>
       <c r="F178" s="140">
@@ -10660,7 +10663,7 @@
       <c r="B179" s="137"/>
       <c r="C179" s="139"/>
       <c r="D179" s="71" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E179" s="71"/>
       <c r="F179" s="140"/>
@@ -10675,7 +10678,7 @@
       <c r="C180" s="139"/>
       <c r="D180" s="71"/>
       <c r="E180" s="72" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F180" s="140">
         <f>IFERROR(VLOOKUP(E180,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10689,7 +10692,7 @@
       <c r="C181" s="139"/>
       <c r="D181" s="71"/>
       <c r="E181" s="72" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F181" s="140">
         <f>IFERROR(VLOOKUP(E181,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10703,7 +10706,7 @@
       <c r="C182" s="139"/>
       <c r="D182" s="71"/>
       <c r="E182" s="72" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F182" s="140">
         <f>IFERROR(VLOOKUP(E182,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10717,7 +10720,7 @@
       <c r="C183" s="139"/>
       <c r="D183" s="71"/>
       <c r="E183" s="72" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F183" s="140">
         <f>IFERROR(VLOOKUP(E183,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10733,7 +10736,7 @@
       <c r="C184" s="139"/>
       <c r="D184" s="71"/>
       <c r="E184" s="72" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F184" s="140">
         <f>IFERROR(VLOOKUP(E184,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10759,7 +10762,7 @@
       <c r="B186" s="137"/>
       <c r="C186" s="139"/>
       <c r="D186" s="71" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E186" s="188"/>
       <c r="F186" s="140"/>
@@ -10773,10 +10776,10 @@
       <c r="B187" s="137"/>
       <c r="C187" s="139"/>
       <c r="D187" s="71" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E187" s="72" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F187" s="140">
         <f>IFERROR(VLOOKUP(E187,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10794,7 +10797,7 @@
       <c r="B188" s="137"/>
       <c r="C188" s="139"/>
       <c r="D188" s="71" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E188" s="76"/>
       <c r="F188" s="140"/>
@@ -10809,7 +10812,7 @@
       <c r="C189" s="139"/>
       <c r="D189" s="71"/>
       <c r="E189" s="72" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F189" s="140">
         <f>IFERROR(VLOOKUP(E189,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10823,7 +10826,7 @@
       <c r="C190" s="139"/>
       <c r="D190" s="71"/>
       <c r="E190" s="72" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F190" s="140">
         <f>IFERROR(VLOOKUP(E190,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10837,7 +10840,7 @@
       <c r="C191" s="139"/>
       <c r="D191" s="71"/>
       <c r="E191" s="72" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F191" s="140">
         <f>IFERROR(VLOOKUP(E191,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10851,7 +10854,7 @@
       <c r="C192" s="139"/>
       <c r="D192" s="71"/>
       <c r="E192" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F192" s="140">
         <f>IFERROR(VLOOKUP(E192,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10865,7 +10868,7 @@
       <c r="C193" s="139"/>
       <c r="D193" s="71"/>
       <c r="E193" s="72" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F193" s="140">
         <f>IFERROR(VLOOKUP(E193,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10879,7 +10882,7 @@
       <c r="C194" s="139"/>
       <c r="D194" s="71"/>
       <c r="E194" s="72" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F194" s="140">
         <f>IFERROR(VLOOKUP(E194,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10893,7 +10896,7 @@
       <c r="C195" s="139"/>
       <c r="D195" s="71"/>
       <c r="E195" s="72" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F195" s="140">
         <f>IFERROR(VLOOKUP(E195,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10907,7 +10910,7 @@
       <c r="C196" s="139"/>
       <c r="D196" s="71"/>
       <c r="E196" s="72" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F196" s="140">
         <f>IFERROR(VLOOKUP(E196,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10920,10 +10923,10 @@
       <c r="B197" s="137"/>
       <c r="C197" s="139"/>
       <c r="D197" s="139" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E197" s="72" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F197" s="140">
         <f>IFERROR(VLOOKUP(E197,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10940,7 +10943,7 @@
       <c r="C198" s="139"/>
       <c r="D198" s="139"/>
       <c r="E198" s="72" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F198" s="140">
         <f>IFERROR(VLOOKUP(E198,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10956,7 +10959,7 @@
       <c r="C199" s="139"/>
       <c r="D199" s="139"/>
       <c r="E199" s="72" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F199" s="140">
         <f>IFERROR(VLOOKUP(E199,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10971,10 +10974,10 @@
       <c r="B200" s="137"/>
       <c r="C200" s="139"/>
       <c r="D200" s="139" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E200" s="72" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F200" s="140">
         <f>IFERROR(VLOOKUP(E200,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -10993,7 +10996,7 @@
       <c r="C201" s="139"/>
       <c r="D201" s="139"/>
       <c r="E201" s="72" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F201" s="140">
         <f>IFERROR(VLOOKUP(E201,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11008,7 +11011,7 @@
       <c r="B202" s="137"/>
       <c r="C202" s="139"/>
       <c r="D202" s="71" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E202" s="188"/>
       <c r="F202" s="140"/>
@@ -11029,10 +11032,10 @@
       <c r="B203" s="137"/>
       <c r="C203" s="139"/>
       <c r="D203" s="71" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E203" s="72" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F203" s="140">
         <f>IFERROR(VLOOKUP(E203,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11051,7 +11054,7 @@
       <c r="C204" s="139"/>
       <c r="D204" s="71"/>
       <c r="E204" s="71" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F204" s="140">
         <f>IFERROR(VLOOKUP(E204,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11064,7 +11067,7 @@
       <c r="B205" s="137"/>
       <c r="C205" s="139"/>
       <c r="D205" s="71" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E205" s="188"/>
       <c r="F205" s="140"/>
@@ -11079,7 +11082,7 @@
       <c r="C206" s="139"/>
       <c r="D206" s="71"/>
       <c r="E206" s="72" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F206" s="140">
         <f>IFERROR(VLOOKUP(E206,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11093,7 +11096,7 @@
       <c r="C207" s="139"/>
       <c r="D207" s="71"/>
       <c r="E207" s="188" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F207" s="140">
         <f>IFERROR(VLOOKUP(E207,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11106,7 +11109,7 @@
       <c r="B208" s="137"/>
       <c r="C208" s="139"/>
       <c r="D208" s="71" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E208" s="188"/>
       <c r="F208" s="140"/>
@@ -11121,7 +11124,7 @@
       <c r="C209" s="139"/>
       <c r="D209" s="71"/>
       <c r="E209" s="72" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F209" s="140">
         <f>IFERROR(VLOOKUP(E209,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11135,7 +11138,7 @@
       <c r="C210" s="139"/>
       <c r="D210" s="71"/>
       <c r="E210" s="72" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F210" s="140">
         <f>IFERROR(VLOOKUP(E210,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11151,7 +11154,7 @@
       <c r="C211" s="139"/>
       <c r="D211" s="71"/>
       <c r="E211" s="72" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F211" s="140">
         <f>IFERROR(VLOOKUP(E211,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11167,7 +11170,7 @@
       <c r="C212" s="139"/>
       <c r="D212" s="71"/>
       <c r="E212" s="72" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F212" s="140">
         <f>IFERROR(VLOOKUP(E212,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11182,7 +11185,7 @@
       <c r="B213" s="137"/>
       <c r="C213" s="139"/>
       <c r="D213" s="71" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E213" s="188"/>
       <c r="F213" s="140"/>
@@ -11198,7 +11201,7 @@
       <c r="C214" s="139"/>
       <c r="D214" s="71"/>
       <c r="E214" s="72" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F214" s="140">
         <f>IFERROR(VLOOKUP(E214,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11213,7 +11216,7 @@
       <c r="C215" s="139"/>
       <c r="D215" s="71"/>
       <c r="E215" s="72" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F215" s="140">
         <f>IFERROR(VLOOKUP(E215,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11228,7 +11231,7 @@
       <c r="C216" s="139"/>
       <c r="D216" s="71"/>
       <c r="E216" s="72" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F216" s="140">
         <f>IFERROR(VLOOKUP(E216,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11242,7 +11245,7 @@
       <c r="B217" s="137"/>
       <c r="C217" s="139"/>
       <c r="D217" s="71" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E217" s="188"/>
       <c r="F217" s="140"/>
@@ -11264,7 +11267,7 @@
       <c r="C218" s="139"/>
       <c r="D218" s="71"/>
       <c r="E218" s="72" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F218" s="140">
         <f>IFERROR(VLOOKUP(E218,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11278,7 +11281,7 @@
       <c r="C219" s="139"/>
       <c r="D219" s="71"/>
       <c r="E219" s="72" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F219" s="140">
         <f>IFERROR(VLOOKUP(E219,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11292,7 +11295,7 @@
       <c r="C220" s="139"/>
       <c r="D220" s="71"/>
       <c r="E220" s="72" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F220" s="140">
         <f>IFERROR(VLOOKUP(E220,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11306,7 +11309,7 @@
       <c r="C221" s="139"/>
       <c r="D221" s="71"/>
       <c r="E221" s="72" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F221" s="140">
         <f>IFERROR(VLOOKUP(E221,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11320,7 +11323,7 @@
       <c r="C222" s="139"/>
       <c r="D222" s="71"/>
       <c r="E222" s="72" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F222" s="140">
         <f>IFERROR(VLOOKUP(E222,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11334,7 +11337,7 @@
       <c r="C223" s="139"/>
       <c r="D223" s="71"/>
       <c r="E223" s="72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F223" s="140">
         <f>IFERROR(VLOOKUP(E223,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11350,7 +11353,7 @@
       <c r="C224" s="139"/>
       <c r="D224" s="71"/>
       <c r="E224" s="72" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F224" s="140">
         <f>IFERROR(VLOOKUP(E224,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11376,10 +11379,10 @@
       <c r="B226" s="137"/>
       <c r="C226" s="139"/>
       <c r="D226" s="71" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E226" s="72" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F226" s="140">
         <f>IFERROR(VLOOKUP(E226,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11398,7 +11401,7 @@
       <c r="C227" s="139"/>
       <c r="D227" s="71"/>
       <c r="E227" s="72" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F227" s="140">
         <f>IFERROR(VLOOKUP(E227,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11417,7 +11420,7 @@
       <c r="C228" s="139"/>
       <c r="D228" s="71"/>
       <c r="E228" s="72" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F228" s="140">
         <f>IFERROR(VLOOKUP(E228,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11449,10 +11452,10 @@
       <c r="B230" s="137"/>
       <c r="C230" s="139"/>
       <c r="D230" s="71" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E230" s="72" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F230" s="140">
         <f>IFERROR(VLOOKUP(E230,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11469,7 +11472,7 @@
       <c r="C231" s="139"/>
       <c r="D231" s="71"/>
       <c r="E231" s="72" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F231" s="140">
         <f>IFERROR(VLOOKUP(E231,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11482,7 +11485,7 @@
       <c r="B232" s="137"/>
       <c r="C232" s="139"/>
       <c r="D232" s="71" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E232" s="71"/>
       <c r="F232" s="140"/>
@@ -11496,7 +11499,7 @@
       <c r="B233" s="137"/>
       <c r="C233" s="139"/>
       <c r="D233" s="71" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E233" s="71"/>
       <c r="F233" s="140"/>
@@ -11510,10 +11513,10 @@
       <c r="B234" s="137"/>
       <c r="C234" s="139"/>
       <c r="D234" s="71" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E234" s="72" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F234" s="140">
         <f>IFERROR(VLOOKUP(E234,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11532,7 +11535,7 @@
       <c r="C235" s="139"/>
       <c r="D235" s="71"/>
       <c r="E235" s="72" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F235" s="140">
         <f>IFERROR(VLOOKUP(E235,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11548,7 +11551,7 @@
       <c r="C236" s="139"/>
       <c r="D236" s="71"/>
       <c r="E236" s="72" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F236" s="140">
         <f>IFERROR(VLOOKUP(E236,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11577,7 +11580,7 @@
       <c r="B238" s="137"/>
       <c r="C238" s="139"/>
       <c r="D238" s="71" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E238" s="71"/>
       <c r="F238" s="140"/>
@@ -11591,10 +11594,10 @@
       <c r="B239" s="137"/>
       <c r="C239" s="139"/>
       <c r="D239" s="71" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E239" s="71" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F239" s="140">
         <f>IFERROR(VLOOKUP(E239,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11611,7 +11614,7 @@
       <c r="C240" s="139"/>
       <c r="D240" s="71"/>
       <c r="E240" s="72" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F240" s="140">
         <f>IFERROR(VLOOKUP(E240,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11625,7 +11628,7 @@
       <c r="C241" s="139"/>
       <c r="D241" s="71"/>
       <c r="E241" s="151" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F241" s="140">
         <f>IFERROR(VLOOKUP(E241,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11639,7 +11642,7 @@
       <c r="C242" s="139"/>
       <c r="D242" s="71"/>
       <c r="E242" s="151" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F242" s="140">
         <f>IFERROR(VLOOKUP(E242,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11652,10 +11655,10 @@
       <c r="B243" s="137"/>
       <c r="C243" s="139"/>
       <c r="D243" s="71" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E243" s="72" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F243" s="140">
         <f>IFERROR(VLOOKUP(E243,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11674,7 +11677,7 @@
       <c r="C244" s="139"/>
       <c r="D244" s="71"/>
       <c r="E244" s="72" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F244" s="140">
         <f>IFERROR(VLOOKUP(E244,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11689,7 +11692,7 @@
       <c r="B245" s="137"/>
       <c r="C245" s="139"/>
       <c r="D245" s="71" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E245" s="71"/>
       <c r="F245" s="140"/>
@@ -11703,10 +11706,10 @@
       <c r="B246" s="137"/>
       <c r="C246" s="139"/>
       <c r="D246" s="71" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E246" s="72" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F246" s="140">
         <f>IFERROR(VLOOKUP(E246,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11723,7 +11726,7 @@
       <c r="C247" s="139"/>
       <c r="D247" s="71"/>
       <c r="E247" s="72" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F247" s="140">
         <f>IFERROR(VLOOKUP(E247,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11737,7 +11740,7 @@
       <c r="C248" s="139"/>
       <c r="D248" s="71"/>
       <c r="E248" s="72" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F248" s="140">
         <f>IFERROR(VLOOKUP(E248,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11751,7 +11754,7 @@
       <c r="C249" s="139"/>
       <c r="D249" s="71"/>
       <c r="E249" s="72" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F249" s="140">
         <f>IFERROR(VLOOKUP(E249,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11765,7 +11768,7 @@
       <c r="C250" s="139"/>
       <c r="D250" s="71"/>
       <c r="E250" s="72" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="F250" s="140">
         <f>IFERROR(VLOOKUP(E250,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11779,7 +11782,7 @@
       <c r="C251" s="139"/>
       <c r="D251" s="71"/>
       <c r="E251" s="72" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F251" s="140">
         <f>IFERROR(VLOOKUP(E251,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11793,7 +11796,7 @@
       <c r="C252" s="139"/>
       <c r="D252" s="71"/>
       <c r="E252" s="72" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F252" s="140">
         <f>IFERROR(VLOOKUP(E252,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11807,7 +11810,7 @@
       <c r="C253" s="139"/>
       <c r="D253" s="71"/>
       <c r="E253" s="72" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F253" s="140">
         <f>IFERROR(VLOOKUP(E253,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11823,7 +11826,7 @@
       <c r="C254" s="139"/>
       <c r="D254" s="71"/>
       <c r="E254" s="72" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F254" s="140">
         <f>IFERROR(VLOOKUP(E254,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11839,7 +11842,7 @@
       <c r="C255" s="139"/>
       <c r="D255" s="71"/>
       <c r="E255" s="72" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F255" s="140">
         <f>IFERROR(VLOOKUP(E255,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11854,7 +11857,7 @@
       <c r="B256" s="137"/>
       <c r="C256" s="139"/>
       <c r="D256" s="139" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E256" s="188"/>
       <c r="F256" s="140"/>
@@ -11868,7 +11871,7 @@
       <c r="B257" s="137"/>
       <c r="C257" s="139"/>
       <c r="D257" s="71" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E257" s="188"/>
       <c r="F257" s="140"/>
@@ -11883,7 +11886,7 @@
       <c r="C258" s="139"/>
       <c r="D258" s="71"/>
       <c r="E258" s="151" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="F258" s="140">
         <f>IFERROR(VLOOKUP(E258,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11897,7 +11900,7 @@
       <c r="C259" s="139"/>
       <c r="D259" s="71"/>
       <c r="E259" s="72" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F259" s="140">
         <f>IFERROR(VLOOKUP(E259,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11911,7 +11914,7 @@
       <c r="C260" s="139"/>
       <c r="D260" s="71"/>
       <c r="E260" s="72" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F260" s="140">
         <f>IFERROR(VLOOKUP(E260,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11925,7 +11928,7 @@
       <c r="C261" s="139"/>
       <c r="D261" s="71"/>
       <c r="E261" s="72" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F261" s="140">
         <f>IFERROR(VLOOKUP(E261,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11939,7 +11942,7 @@
       <c r="C262" s="139"/>
       <c r="D262" s="71"/>
       <c r="E262" s="72" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="F262" s="140">
         <f>IFERROR(VLOOKUP(E262,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11952,7 +11955,7 @@
       <c r="B263" s="137"/>
       <c r="C263" s="139"/>
       <c r="D263" s="71" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E263" s="188"/>
       <c r="F263" s="140"/>
@@ -11970,10 +11973,10 @@
       <c r="B264" s="137"/>
       <c r="C264" s="139"/>
       <c r="D264" s="71" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E264" s="72" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="F264" s="140">
         <f>IFERROR(VLOOKUP(E264,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -11993,7 +11996,7 @@
       <c r="C265" s="139"/>
       <c r="D265" s="71"/>
       <c r="E265" s="72" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F265" s="140">
         <f>IFERROR(VLOOKUP(E265,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12010,7 +12013,7 @@
       <c r="C266" s="139"/>
       <c r="D266" s="71"/>
       <c r="E266" s="72" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="F266" s="140">
         <f>IFERROR(VLOOKUP(E266,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12027,7 +12030,7 @@
       <c r="C267" s="139"/>
       <c r="D267" s="71"/>
       <c r="E267" s="72" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F267" s="140">
         <f>IFERROR(VLOOKUP(E267,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12044,7 +12047,7 @@
       <c r="C268" s="139"/>
       <c r="D268" s="71"/>
       <c r="E268" s="72" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="F268" s="140">
         <f>IFERROR(VLOOKUP(E268,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12060,7 +12063,7 @@
       <c r="B269" s="76"/>
       <c r="C269" s="34"/>
       <c r="D269" s="71" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E269" s="188"/>
       <c r="F269" s="140"/>
@@ -12079,7 +12082,7 @@
       <c r="C270" s="34"/>
       <c r="D270" s="139"/>
       <c r="E270" s="72" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F270" s="140">
         <f>IFERROR(VLOOKUP(E270,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12097,7 +12100,7 @@
       <c r="C271" s="34"/>
       <c r="D271" s="139"/>
       <c r="E271" s="72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="F271" s="140">
         <f>IFERROR(VLOOKUP(E271,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12114,10 +12117,10 @@
       <c r="B272" s="76"/>
       <c r="C272" s="34"/>
       <c r="D272" s="71" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E272" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F272" s="140">
         <f>IFERROR(VLOOKUP(E272,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12134,7 +12137,7 @@
       <c r="C273" s="34"/>
       <c r="D273" s="71"/>
       <c r="E273" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F273" s="140">
         <f>IFERROR(VLOOKUP(E273,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12148,7 +12151,7 @@
       <c r="C274" s="34"/>
       <c r="D274" s="71"/>
       <c r="E274" s="72" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="F274" s="140">
         <f>IFERROR(VLOOKUP(E274,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12162,7 +12165,7 @@
       <c r="C275" s="34"/>
       <c r="D275" s="71"/>
       <c r="E275" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F275" s="140">
         <f>IFERROR(VLOOKUP(E275,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12176,7 +12179,7 @@
       <c r="C276" s="34"/>
       <c r="D276" s="71"/>
       <c r="E276" s="151" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F276" s="140">
         <f>IFERROR(VLOOKUP(E276,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12190,7 +12193,7 @@
       <c r="C277" s="34"/>
       <c r="D277" s="71"/>
       <c r="E277" s="151" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F277" s="140">
         <f>IFERROR(VLOOKUP(E277,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12204,7 +12207,7 @@
       <c r="C278" s="34"/>
       <c r="D278" s="71"/>
       <c r="E278" s="151" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F278" s="140">
         <f>IFERROR(VLOOKUP(E278,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12218,7 +12221,7 @@
       <c r="C279" s="34"/>
       <c r="D279" s="71"/>
       <c r="E279" s="151" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F279" s="140">
         <f>IFERROR(VLOOKUP(E279,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12231,10 +12234,10 @@
       <c r="B280" s="76"/>
       <c r="C280" s="34"/>
       <c r="D280" s="191" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E280" s="192" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F280" s="193">
         <f>+Hoja1!E228+Hoja1!E229</f>
@@ -12245,7 +12248,7 @@
         <v>62810190.49</v>
       </c>
       <c r="H280" s="195" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I280" s="134"/>
       <c r="J280" s="142"/>
@@ -12256,7 +12259,7 @@
       <c r="B281" s="76"/>
       <c r="C281" s="34"/>
       <c r="D281" s="71" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E281" s="71"/>
       <c r="F281" s="140">
@@ -12273,7 +12276,7 @@
       <c r="B282" s="76"/>
       <c r="C282" s="34"/>
       <c r="D282" s="71" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="E282" s="71"/>
       <c r="F282" s="140">
@@ -12290,7 +12293,7 @@
       <c r="B283" s="76"/>
       <c r="C283" s="34"/>
       <c r="D283" s="139" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="E283" s="139"/>
       <c r="F283" s="140">
@@ -12308,7 +12311,7 @@
       <c r="B284" s="76"/>
       <c r="C284" s="34"/>
       <c r="D284" s="139" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E284" s="139"/>
       <c r="F284" s="140"/>
@@ -12323,7 +12326,7 @@
       <c r="C285" s="34"/>
       <c r="D285" s="139"/>
       <c r="E285" s="72" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F285" s="140">
         <f>IFERROR(VLOOKUP(E285,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12337,7 +12340,7 @@
       <c r="C286" s="34"/>
       <c r="D286" s="139"/>
       <c r="E286" s="72" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="F286" s="140">
         <f>IFERROR(VLOOKUP(E286,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12351,7 +12354,7 @@
       <c r="C287" s="34"/>
       <c r="D287" s="139"/>
       <c r="E287" s="139" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F287" s="140">
         <f>IFERROR(VLOOKUP(E287,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12365,7 +12368,7 @@
       <c r="C288" s="34"/>
       <c r="D288" s="139"/>
       <c r="E288" s="139" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F288" s="140">
         <f>IFERROR(VLOOKUP(E288,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12379,7 +12382,7 @@
       <c r="C289" s="34"/>
       <c r="D289" s="139"/>
       <c r="E289" s="139" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F289" s="140">
         <f>IFERROR(VLOOKUP(E289,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12393,7 +12396,7 @@
       <c r="C290" s="34"/>
       <c r="D290" s="139"/>
       <c r="E290" s="139" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="F290" s="140">
         <f>IFERROR(VLOOKUP(E290,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12407,7 +12410,7 @@
       <c r="C291" s="34"/>
       <c r="D291" s="139"/>
       <c r="E291" s="72" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F291" s="140">
         <f>IFERROR(VLOOKUP(E291,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12421,7 +12424,7 @@
       <c r="C292" s="34"/>
       <c r="D292" s="139"/>
       <c r="E292" s="139" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F292" s="140">
         <f>IFERROR(VLOOKUP(E292,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12438,7 +12441,7 @@
       <c r="B293" s="76"/>
       <c r="C293" s="34"/>
       <c r="D293" s="71" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E293" s="71"/>
       <c r="F293" s="140"/>
@@ -12452,10 +12455,10 @@
       <c r="B294" s="76"/>
       <c r="C294" s="34"/>
       <c r="D294" s="71" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E294" s="72" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F294" s="140">
         <f>IFERROR(VLOOKUP(E294,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12477,7 +12480,7 @@
       <c r="C295" s="34"/>
       <c r="D295" s="71"/>
       <c r="E295" s="72" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F295" s="140">
         <f>IFERROR(VLOOKUP(E295,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12491,7 +12494,7 @@
       <c r="C296" s="34"/>
       <c r="D296" s="71"/>
       <c r="E296" s="72" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F296" s="140">
         <f>IFERROR(VLOOKUP(E296,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12505,7 +12508,7 @@
       <c r="C297" s="34"/>
       <c r="D297" s="71"/>
       <c r="E297" s="72" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F297" s="140">
         <f>IFERROR(VLOOKUP(E297,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12525,7 +12528,7 @@
       <c r="C298" s="34"/>
       <c r="D298" s="71"/>
       <c r="E298" s="72" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F298" s="140">
         <f>IFERROR(VLOOKUP(E298,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12545,7 +12548,7 @@
       <c r="C299" s="34"/>
       <c r="D299" s="71"/>
       <c r="E299" s="72" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F299" s="140">
         <f>IFERROR(VLOOKUP(E299,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12565,7 +12568,7 @@
       <c r="C300" s="34"/>
       <c r="D300" s="71"/>
       <c r="E300" s="72" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F300" s="140">
         <f>IFERROR(VLOOKUP(E300,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12585,7 +12588,7 @@
       <c r="C301" s="34"/>
       <c r="D301" s="71"/>
       <c r="E301" s="72" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="F301" s="140">
         <f>IFERROR(VLOOKUP(E301,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12604,7 +12607,7 @@
       <c r="B302" s="76"/>
       <c r="C302" s="34"/>
       <c r="D302" s="71" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E302" s="188"/>
       <c r="F302" s="140"/>
@@ -12619,7 +12622,7 @@
       <c r="C303" s="34"/>
       <c r="D303" s="71"/>
       <c r="E303" s="72" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F303" s="140">
         <f>IFERROR(VLOOKUP(E303,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12633,7 +12636,7 @@
       <c r="C304" s="34"/>
       <c r="D304" s="71"/>
       <c r="E304" s="72" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="F304" s="140">
         <f>IFERROR(VLOOKUP(E304,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12647,7 +12650,7 @@
       <c r="C305" s="34"/>
       <c r="D305" s="71"/>
       <c r="E305" s="72" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="F305" s="140">
         <f>IFERROR(VLOOKUP(E305,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12660,7 +12663,7 @@
       <c r="B306" s="76"/>
       <c r="C306" s="34"/>
       <c r="D306" s="71" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E306" s="188"/>
       <c r="F306" s="140">
@@ -12678,7 +12681,7 @@
       <c r="C307" s="34"/>
       <c r="D307" s="71"/>
       <c r="E307" s="72" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="F307" s="140">
         <f>IFERROR(VLOOKUP(E307,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12693,10 +12696,10 @@
       <c r="B308" s="76"/>
       <c r="C308" s="34"/>
       <c r="D308" s="139" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E308" s="72" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F308" s="140">
         <f>IFERROR(VLOOKUP(E308,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12714,10 +12717,10 @@
       <c r="B309" s="76"/>
       <c r="C309" s="34"/>
       <c r="D309" s="139" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="E309" s="72" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F309" s="140">
         <f>IFERROR(VLOOKUP(E309,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12735,10 +12738,10 @@
       <c r="B310" s="76"/>
       <c r="C310" s="34"/>
       <c r="D310" s="71" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E310" s="72" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="F310" s="140">
         <f>IFERROR(VLOOKUP(E310,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12754,7 +12757,7 @@
       <c r="B311" s="76"/>
       <c r="C311" s="34"/>
       <c r="D311" s="71" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E311" s="188"/>
       <c r="F311" s="140">
@@ -12772,7 +12775,7 @@
       <c r="C312" s="34"/>
       <c r="D312" s="71"/>
       <c r="E312" s="72" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F312" s="140">
         <f>IFERROR(VLOOKUP(E312,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12786,7 +12789,7 @@
       <c r="C313" s="34"/>
       <c r="D313" s="71"/>
       <c r="E313" s="72" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="F313" s="140">
         <f>IFERROR(VLOOKUP(E313,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12799,7 +12802,7 @@
       <c r="B314" s="76"/>
       <c r="C314" s="34"/>
       <c r="D314" s="71" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="E314" s="71"/>
       <c r="F314" s="140">
@@ -12816,10 +12819,10 @@
       <c r="B315" s="76"/>
       <c r="C315" s="34"/>
       <c r="D315" s="71" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="E315" s="71" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="F315" s="140">
         <f>IFERROR(VLOOKUP(E315,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12836,7 +12839,7 @@
       <c r="C316" s="34"/>
       <c r="D316" s="71"/>
       <c r="E316" s="72" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="F316" s="140">
         <f>IFERROR(VLOOKUP(E316,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12849,7 +12852,7 @@
       <c r="B317" s="76"/>
       <c r="C317" s="34"/>
       <c r="D317" s="139" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E317" s="72"/>
       <c r="F317" s="140">
@@ -12867,7 +12870,7 @@
       <c r="B318" s="76"/>
       <c r="C318" s="34"/>
       <c r="D318" s="71" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="E318" s="71"/>
       <c r="F318" s="140"/>
@@ -12883,7 +12886,7 @@
       <c r="C319" s="34"/>
       <c r="D319" s="71"/>
       <c r="E319" s="72" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="F319" s="140">
         <f>IFERROR(VLOOKUP(E319,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12898,7 +12901,7 @@
       <c r="C320" s="34"/>
       <c r="D320" s="71"/>
       <c r="E320" s="72" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="F320" s="140">
         <f>IFERROR(VLOOKUP(E320,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12913,7 +12916,7 @@
       <c r="C321" s="34"/>
       <c r="D321" s="71"/>
       <c r="E321" s="72" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="F321" s="140">
         <f>IFERROR(VLOOKUP(E321,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12928,7 +12931,7 @@
       <c r="B322" s="76"/>
       <c r="C322" s="34"/>
       <c r="D322" s="71" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E322" s="188"/>
       <c r="F322" s="140"/>
@@ -12943,7 +12946,7 @@
       <c r="C323" s="34"/>
       <c r="D323" s="71"/>
       <c r="E323" s="72" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F323" s="140">
         <f>IFERROR(VLOOKUP(E323,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12957,7 +12960,7 @@
       <c r="C324" s="34"/>
       <c r="D324" s="71"/>
       <c r="E324" s="72" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F324" s="140">
         <f>IFERROR(VLOOKUP(E324,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12971,7 +12974,7 @@
       <c r="C325" s="34"/>
       <c r="D325" s="71"/>
       <c r="E325" s="72" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="F325" s="140">
         <f>IFERROR(VLOOKUP(E325,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12985,7 +12988,7 @@
       <c r="C326" s="34"/>
       <c r="D326" s="71"/>
       <c r="E326" s="72" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F326" s="140">
         <f>IFERROR(VLOOKUP(E326,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -12999,7 +13002,7 @@
       <c r="C327" s="34"/>
       <c r="D327" s="71"/>
       <c r="E327" s="72" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F327" s="140">
         <f>IFERROR(VLOOKUP(E327,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13013,7 +13016,7 @@
       <c r="C328" s="34"/>
       <c r="D328" s="71"/>
       <c r="E328" s="72" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F328" s="140">
         <f>IFERROR(VLOOKUP(E328,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13027,7 +13030,7 @@
       <c r="C329" s="34"/>
       <c r="D329" s="71"/>
       <c r="E329" s="72" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F329" s="140">
         <f>IFERROR(VLOOKUP(E329,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13040,10 +13043,10 @@
       <c r="B330" s="76"/>
       <c r="C330" s="34"/>
       <c r="D330" s="71" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E330" s="72" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="F330" s="140">
         <f>IFERROR(VLOOKUP(E330,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13061,7 +13064,7 @@
       <c r="C331" s="34"/>
       <c r="D331" s="71"/>
       <c r="E331" s="151" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F331" s="140">
         <f>IFERROR(VLOOKUP(E331,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13069,7 +13072,7 @@
       </c>
       <c r="G331" s="138"/>
       <c r="H331" s="150" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="332" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -13078,7 +13081,7 @@
       <c r="C332" s="34"/>
       <c r="D332" s="71"/>
       <c r="E332" s="72" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="F332" s="140">
         <f>IFERROR(VLOOKUP(E332,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13093,7 +13096,7 @@
       <c r="C333" s="34"/>
       <c r="D333" s="71"/>
       <c r="E333" s="72" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F333" s="140">
         <f>IFERROR(VLOOKUP(E333,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13108,7 +13111,7 @@
       <c r="C334" s="34"/>
       <c r="D334" s="71"/>
       <c r="E334" s="72" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F334" s="140">
         <f>IFERROR(VLOOKUP(E334,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13123,7 +13126,7 @@
       <c r="C335" s="34"/>
       <c r="D335" s="71"/>
       <c r="E335" s="72" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="F335" s="140">
         <f>IFERROR(VLOOKUP(E335,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13138,7 +13141,7 @@
       <c r="C336" s="34"/>
       <c r="D336" s="71"/>
       <c r="E336" s="72" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F336" s="140">
         <f>IFERROR(VLOOKUP(E336,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13153,7 +13156,7 @@
       <c r="C337" s="34"/>
       <c r="D337" s="71"/>
       <c r="E337" s="72" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F337" s="140">
         <f>IFERROR(VLOOKUP(E337,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13167,7 +13170,7 @@
       <c r="B338" s="76"/>
       <c r="C338" s="34"/>
       <c r="D338" s="71" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="E338" s="71"/>
       <c r="F338" s="140"/>
@@ -13181,10 +13184,10 @@
       <c r="B339" s="76"/>
       <c r="C339" s="34"/>
       <c r="D339" s="71" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E339" s="72" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F339" s="140">
         <f>IFERROR(VLOOKUP(E339,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13201,7 +13204,7 @@
       <c r="C340" s="34"/>
       <c r="D340" s="71"/>
       <c r="E340" s="71" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="F340" s="140">
         <f>IFERROR(VLOOKUP(E340,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13215,7 +13218,7 @@
       <c r="C341" s="34"/>
       <c r="D341" s="71"/>
       <c r="E341" s="71" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F341" s="140">
         <f>IFERROR(VLOOKUP(E341,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13228,10 +13231,10 @@
       <c r="B342" s="76"/>
       <c r="C342" s="34"/>
       <c r="D342" s="71" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="E342" s="72" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F342" s="140">
         <f>IFERROR(VLOOKUP(E342,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13248,7 +13251,7 @@
       <c r="C343" s="34"/>
       <c r="D343" s="71"/>
       <c r="E343" s="72" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="F343" s="140">
         <f>IFERROR(VLOOKUP(E343,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13269,7 +13272,7 @@
       <c r="C344" s="34"/>
       <c r="D344" s="71"/>
       <c r="E344" s="72" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F344" s="140">
         <f>IFERROR(VLOOKUP(E344,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13290,7 +13293,7 @@
       <c r="C345" s="34"/>
       <c r="D345" s="71"/>
       <c r="E345" s="72" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="F345" s="140">
         <f>IFERROR(VLOOKUP(E345,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13304,7 +13307,7 @@
       <c r="C346" s="34"/>
       <c r="D346" s="71"/>
       <c r="E346" s="72" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F346" s="140">
         <f>IFERROR(VLOOKUP(E346,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13318,7 +13321,7 @@
       <c r="C347" s="34"/>
       <c r="D347" s="71"/>
       <c r="E347" s="72" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F347" s="140">
         <f>IFERROR(VLOOKUP(E347,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13332,7 +13335,7 @@
       <c r="C348" s="34"/>
       <c r="D348" s="71"/>
       <c r="E348" s="72" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="F348" s="140">
         <f>IFERROR(VLOOKUP(E348,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13346,7 +13349,7 @@
       <c r="C349" s="34"/>
       <c r="D349" s="71"/>
       <c r="E349" s="72" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F349" s="140">
         <f>IFERROR(VLOOKUP(E349,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13360,7 +13363,7 @@
       <c r="C350" s="34"/>
       <c r="D350" s="71"/>
       <c r="E350" s="151" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F350" s="140">
         <f>IFERROR(VLOOKUP(E350,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13368,7 +13371,7 @@
       </c>
       <c r="G350" s="138"/>
       <c r="H350" s="68" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="351" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -13376,10 +13379,10 @@
       <c r="B351" s="76"/>
       <c r="C351" s="34"/>
       <c r="D351" s="71" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E351" s="72" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F351" s="140">
         <f>IFERROR(VLOOKUP(E351,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13402,7 +13405,7 @@
       <c r="C352" s="34"/>
       <c r="D352" s="71"/>
       <c r="E352" s="72" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F352" s="140">
         <f>IFERROR(VLOOKUP(E352,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13417,7 +13420,7 @@
       <c r="C353" s="34"/>
       <c r="D353" s="71"/>
       <c r="E353" s="72" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F353" s="140">
         <f>IFERROR(VLOOKUP(E353,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13432,7 +13435,7 @@
       <c r="C354" s="34"/>
       <c r="D354" s="71"/>
       <c r="E354" s="72" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F354" s="140">
         <f>IFERROR(VLOOKUP(E354,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13447,7 +13450,7 @@
       <c r="C355" s="34"/>
       <c r="D355" s="71"/>
       <c r="E355" s="72" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F355" s="140">
         <f>IFERROR(VLOOKUP(E355,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13462,7 +13465,7 @@
       <c r="C356" s="34"/>
       <c r="D356" s="71"/>
       <c r="E356" s="72" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="F356" s="140">
         <f>IFERROR(VLOOKUP(E356,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13477,7 +13480,7 @@
       <c r="C357" s="34"/>
       <c r="D357" s="71"/>
       <c r="E357" s="72" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="F357" s="140">
         <f>IFERROR(VLOOKUP(E357,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13491,7 +13494,7 @@
       <c r="B358" s="76"/>
       <c r="C358" s="34"/>
       <c r="D358" s="139" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E358" s="72"/>
       <c r="F358" s="140"/>
@@ -13507,7 +13510,7 @@
       <c r="C359" s="34"/>
       <c r="D359" s="132"/>
       <c r="E359" s="72" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="F359" s="140">
         <f>IFERROR(VLOOKUP(E359,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13522,7 +13525,7 @@
       <c r="C360" s="34"/>
       <c r="D360" s="132"/>
       <c r="E360" s="72" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="F360" s="140">
         <f>IFERROR(VLOOKUP(E360,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13536,7 +13539,7 @@
       <c r="B361" s="76"/>
       <c r="C361" s="34"/>
       <c r="D361" s="139" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="E361" s="72"/>
       <c r="F361" s="140"/>
@@ -13552,7 +13555,7 @@
       <c r="C362" s="34"/>
       <c r="D362" s="139"/>
       <c r="E362" s="72" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="F362" s="140">
         <f>IFERROR(VLOOKUP(E362,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13566,7 +13569,7 @@
       <c r="B363" s="76"/>
       <c r="C363" s="34"/>
       <c r="D363" s="71" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E363" s="71"/>
       <c r="F363" s="140"/>
@@ -13581,7 +13584,7 @@
       <c r="C364" s="34"/>
       <c r="D364" s="71"/>
       <c r="E364" s="72" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="F364" s="140">
         <f>IFERROR(VLOOKUP(E364,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13595,7 +13598,7 @@
       <c r="C365" s="34"/>
       <c r="D365" s="71"/>
       <c r="E365" s="72" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="F365" s="140">
         <f>IFERROR(VLOOKUP(E365,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13609,7 +13612,7 @@
       <c r="C366" s="34"/>
       <c r="D366" s="71"/>
       <c r="E366" s="72" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F366" s="140">
         <f>IFERROR(VLOOKUP(E366,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13622,7 +13625,7 @@
       <c r="B367" s="76"/>
       <c r="C367" s="34"/>
       <c r="D367" s="71" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="E367" s="188"/>
       <c r="F367" s="140"/>
@@ -13636,7 +13639,7 @@
       <c r="B368" s="76"/>
       <c r="C368" s="34"/>
       <c r="D368" s="71" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E368" s="188"/>
       <c r="F368" s="140"/>
@@ -13651,7 +13654,7 @@
       <c r="C369" s="34"/>
       <c r="D369" s="71"/>
       <c r="E369" s="72" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F369" s="140">
         <f>IFERROR(VLOOKUP(E369,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13665,7 +13668,7 @@
       <c r="C370" s="34"/>
       <c r="D370" s="71"/>
       <c r="E370" s="72" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="F370" s="140">
         <f>IFERROR(VLOOKUP(E370,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13679,7 +13682,7 @@
       <c r="C371" s="34"/>
       <c r="D371" s="71"/>
       <c r="E371" s="72" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F371" s="140">
         <f>IFERROR(VLOOKUP(E371,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13693,7 +13696,7 @@
       <c r="C372" s="34"/>
       <c r="D372" s="71"/>
       <c r="E372" s="72" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="F372" s="140">
         <f>IFERROR(VLOOKUP(E372,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13707,7 +13710,7 @@
       <c r="C373" s="34"/>
       <c r="D373" s="71"/>
       <c r="E373" s="72" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="F373" s="140">
         <f>IFERROR(VLOOKUP(E373,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13720,7 +13723,7 @@
       <c r="B374" s="76"/>
       <c r="C374" s="34"/>
       <c r="D374" s="71" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E374" s="76"/>
       <c r="F374" s="140"/>
@@ -13735,7 +13738,7 @@
       <c r="C375" s="34"/>
       <c r="D375" s="71"/>
       <c r="E375" s="72" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="F375" s="140">
         <f>IFERROR(VLOOKUP(E375,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13749,7 +13752,7 @@
       <c r="C376" s="34"/>
       <c r="D376" s="71"/>
       <c r="E376" s="72" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="F376" s="140">
         <f>IFERROR(VLOOKUP(E376,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13763,7 +13766,7 @@
       <c r="C377" s="34"/>
       <c r="D377" s="71"/>
       <c r="E377" s="72" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F377" s="140">
         <f>IFERROR(VLOOKUP(E377,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13777,7 +13780,7 @@
       <c r="C378" s="34"/>
       <c r="D378" s="71"/>
       <c r="E378" s="72" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="F378" s="140">
         <f>IFERROR(VLOOKUP(E378,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13791,7 +13794,7 @@
       <c r="C379" s="34"/>
       <c r="D379" s="71"/>
       <c r="E379" s="72" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="F379" s="140">
         <f>IFERROR(VLOOKUP(E379,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13805,7 +13808,7 @@
       <c r="C380" s="34"/>
       <c r="D380" s="71"/>
       <c r="E380" s="72" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F380" s="140">
         <f>IFERROR(VLOOKUP(E380,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13819,7 +13822,7 @@
       <c r="C381" s="34"/>
       <c r="D381" s="71"/>
       <c r="E381" s="72" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="F381" s="140">
         <f>IFERROR(VLOOKUP(E381,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13833,7 +13836,7 @@
       <c r="C382" s="34"/>
       <c r="D382" s="71"/>
       <c r="E382" s="72" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="F382" s="140">
         <f>IFERROR(VLOOKUP(E382,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13847,7 +13850,7 @@
       <c r="C383" s="34"/>
       <c r="D383" s="71"/>
       <c r="E383" s="151" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="F383" s="140">
         <f>IFERROR(VLOOKUP(E383,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13860,7 +13863,7 @@
       <c r="B384" s="76"/>
       <c r="C384" s="34"/>
       <c r="D384" s="71" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="E384" s="71"/>
       <c r="F384" s="140"/>
@@ -13874,7 +13877,7 @@
       <c r="B385" s="76"/>
       <c r="C385" s="34"/>
       <c r="D385" s="139" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="E385" s="72"/>
       <c r="F385" s="140"/>
@@ -13888,7 +13891,7 @@
       <c r="B386" s="76"/>
       <c r="C386" s="34"/>
       <c r="D386" s="71" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="E386" s="71"/>
       <c r="F386" s="140"/>
@@ -13902,10 +13905,10 @@
       <c r="B387" s="76"/>
       <c r="C387" s="34"/>
       <c r="D387" s="71" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E387" s="72" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="F387" s="140">
         <f>IFERROR(VLOOKUP(E387,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13922,7 +13925,7 @@
       <c r="C388" s="34"/>
       <c r="D388" s="71"/>
       <c r="E388" s="72" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="F388" s="140">
         <f>IFERROR(VLOOKUP(E388,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13935,7 +13938,7 @@
       <c r="B389" s="76"/>
       <c r="C389" s="34"/>
       <c r="D389" s="71" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E389" s="71"/>
       <c r="F389" s="140"/>
@@ -13949,7 +13952,7 @@
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
       <c r="D390" s="71" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E390" s="71"/>
       <c r="F390" s="140"/>
@@ -13972,7 +13975,7 @@
       <c r="C391" s="34"/>
       <c r="D391" s="71"/>
       <c r="E391" s="72" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="F391" s="140">
         <f>IFERROR(VLOOKUP(E391,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -13994,7 +13997,7 @@
       <c r="C392" s="34"/>
       <c r="D392" s="71"/>
       <c r="E392" s="72" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="F392" s="140">
         <f>IFERROR(VLOOKUP(E392,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14015,10 +14018,10 @@
       <c r="B393" s="76"/>
       <c r="C393" s="34"/>
       <c r="D393" s="71" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="E393" s="72" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14035,7 +14038,7 @@
       <c r="C394" s="34"/>
       <c r="D394" s="71"/>
       <c r="E394" s="72" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14049,7 +14052,7 @@
       <c r="C395" s="34"/>
       <c r="D395" s="71"/>
       <c r="E395" s="72" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F395" s="140">
         <f>IFERROR(VLOOKUP(E395,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14063,7 +14066,7 @@
       <c r="C396" s="34"/>
       <c r="D396" s="71"/>
       <c r="E396" s="72" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="F396" s="140">
         <f>IFERROR(VLOOKUP(E396,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14076,7 +14079,7 @@
       <c r="B397" s="76"/>
       <c r="C397" s="34"/>
       <c r="D397" s="71" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E397" s="188"/>
       <c r="F397" s="140"/>
@@ -14091,7 +14094,7 @@
       <c r="C398" s="34"/>
       <c r="D398" s="139"/>
       <c r="E398" s="72" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F398" s="140">
         <f>IFERROR(VLOOKUP(E398,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14105,7 +14108,7 @@
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
       <c r="D399" s="71" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="E399" s="188"/>
       <c r="F399" s="140"/>
@@ -14120,7 +14123,7 @@
       <c r="C400" s="34"/>
       <c r="D400" s="71"/>
       <c r="E400" s="72" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="F400" s="140">
         <f>IFERROR(VLOOKUP(E400,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14133,10 +14136,10 @@
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
       <c r="D401" s="71" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="E401" s="71" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F401" s="140">
         <f>IFERROR(VLOOKUP(E401,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14152,7 +14155,7 @@
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
       <c r="D402" s="71" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="E402" s="188"/>
       <c r="F402" s="140"/>
@@ -14167,7 +14170,7 @@
       <c r="C403" s="34"/>
       <c r="D403" s="71"/>
       <c r="E403" s="72" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="F403" s="140">
         <f>IFERROR(VLOOKUP(E403,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14181,7 +14184,7 @@
       <c r="C404" s="34"/>
       <c r="D404" s="76"/>
       <c r="E404" s="72" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F404" s="140">
         <f>IFERROR(VLOOKUP(E404,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14194,7 +14197,7 @@
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
       <c r="D405" s="71" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E405" s="72"/>
       <c r="F405" s="140"/>
@@ -14208,7 +14211,7 @@
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
       <c r="D406" s="71" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E406" s="71"/>
       <c r="F406" s="140"/>
@@ -14223,7 +14226,7 @@
       <c r="C407" s="34"/>
       <c r="D407" s="71"/>
       <c r="E407" s="151" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F407" s="140">
         <f>IFERROR(VLOOKUP(E407,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14237,7 +14240,7 @@
       <c r="C408" s="34"/>
       <c r="D408" s="71"/>
       <c r="E408" s="72" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="F408" s="140">
         <f>IFERROR(VLOOKUP(E408,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14251,7 +14254,7 @@
       <c r="C409" s="34"/>
       <c r="D409" s="71"/>
       <c r="E409" s="72" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="F409" s="140">
         <f>IFERROR(VLOOKUP(E409,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14265,7 +14268,7 @@
       <c r="C410" s="34"/>
       <c r="D410" s="71"/>
       <c r="E410" s="72" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14279,7 +14282,7 @@
       <c r="C411" s="34"/>
       <c r="D411" s="71"/>
       <c r="E411" s="151" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="F411" s="140">
         <f>IFERROR(VLOOKUP(E411,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14293,7 +14296,7 @@
       <c r="C412" s="34"/>
       <c r="D412" s="71"/>
       <c r="E412" s="72" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F412" s="140">
         <f>IFERROR(VLOOKUP(E412,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14306,10 +14309,10 @@
       <c r="B413" s="76"/>
       <c r="C413" s="34"/>
       <c r="D413" s="139" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E413" s="72" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F413" s="140">
         <f>IFERROR(VLOOKUP(E413,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14333,7 +14336,7 @@
       <c r="C414" s="34"/>
       <c r="D414" s="139"/>
       <c r="E414" s="72" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14353,7 +14356,7 @@
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
       <c r="D415" s="139" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E415" s="72"/>
       <c r="F415" s="140"/>
@@ -14367,10 +14370,10 @@
       <c r="B416" s="76"/>
       <c r="C416" s="34"/>
       <c r="D416" s="139" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E416" s="151" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F416" s="140">
         <f>IFERROR(VLOOKUP(E416,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14387,7 +14390,7 @@
       <c r="C417" s="34"/>
       <c r="D417" s="139"/>
       <c r="E417" s="72" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F417" s="140">
         <f>IFERROR(VLOOKUP(E417,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14403,7 +14406,7 @@
       <c r="C418" s="34"/>
       <c r="D418" s="139"/>
       <c r="E418" s="72" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F418" s="140">
         <f>IFERROR(VLOOKUP(E418,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14419,7 +14422,7 @@
       <c r="C419" s="34"/>
       <c r="D419" s="139"/>
       <c r="E419" s="72" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14435,7 +14438,7 @@
       <c r="C420" s="34"/>
       <c r="D420" s="139"/>
       <c r="E420" s="72" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14451,7 +14454,7 @@
       <c r="C421" s="34"/>
       <c r="D421" s="139"/>
       <c r="E421" s="72" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="F421" s="140">
         <f>IFERROR(VLOOKUP(E421,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14467,7 +14470,7 @@
       <c r="C422" s="34"/>
       <c r="D422" s="139"/>
       <c r="E422" s="72" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F422" s="140">
         <f>IFERROR(VLOOKUP(E422,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14499,7 +14502,7 @@
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
       <c r="D424" s="71" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E424" s="71"/>
       <c r="F424" s="140">
@@ -14516,7 +14519,7 @@
       <c r="B425" s="76"/>
       <c r="C425" s="34"/>
       <c r="D425" s="71" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="E425" s="71"/>
       <c r="F425" s="140"/>
@@ -14531,7 +14534,7 @@
       <c r="C426" s="34"/>
       <c r="D426" s="71"/>
       <c r="E426" s="72" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F426" s="140">
         <f>IFERROR(VLOOKUP(E426,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14545,7 +14548,7 @@
       <c r="C427" s="34"/>
       <c r="D427" s="76"/>
       <c r="E427" s="71" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F427" s="140">
         <f>IFERROR(VLOOKUP(E427,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14559,7 +14562,7 @@
       <c r="C428" s="34"/>
       <c r="D428" s="76"/>
       <c r="E428" s="71" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14573,7 +14576,7 @@
       <c r="C429" s="34"/>
       <c r="D429" s="76"/>
       <c r="E429" s="71" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14587,7 +14590,7 @@
       <c r="C430" s="34"/>
       <c r="D430" s="76"/>
       <c r="E430" s="72" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F430" s="140">
         <f>IFERROR(VLOOKUP(E430,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14601,7 +14604,7 @@
       <c r="C431" s="34"/>
       <c r="D431" s="76"/>
       <c r="E431" s="72" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="F431" s="140">
         <f>IFERROR(VLOOKUP(E431,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14615,7 +14618,7 @@
       <c r="C432" s="34"/>
       <c r="D432" s="76"/>
       <c r="E432" s="72" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F432" s="140">
         <f>IFERROR(VLOOKUP(E432,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14629,7 +14632,7 @@
       <c r="C433" s="34"/>
       <c r="D433" s="76"/>
       <c r="E433" s="72" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F433" s="140">
         <f>IFERROR(VLOOKUP(E433,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14642,7 +14645,7 @@
       <c r="B434" s="76"/>
       <c r="C434" s="34"/>
       <c r="D434" s="71" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="E434" s="71"/>
       <c r="F434" s="140"/>
@@ -14657,7 +14660,7 @@
       <c r="C435" s="34"/>
       <c r="D435" s="71"/>
       <c r="E435" s="72" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F435" s="140">
         <f>IFERROR(VLOOKUP(E435,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14671,7 +14674,7 @@
       <c r="C436" s="34"/>
       <c r="D436" s="71"/>
       <c r="E436" s="72" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F436" s="140">
         <f>IFERROR(VLOOKUP(E436,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14685,7 +14688,7 @@
       <c r="C437" s="34"/>
       <c r="D437" s="71"/>
       <c r="E437" s="72" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14699,7 +14702,7 @@
       <c r="C438" s="34"/>
       <c r="D438" s="71"/>
       <c r="E438" s="72" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="F438" s="140">
         <f>IFERROR(VLOOKUP(E438,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14712,7 +14715,7 @@
       <c r="B439" s="76"/>
       <c r="C439" s="34"/>
       <c r="D439" s="71" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="E439" s="188"/>
       <c r="F439" s="140"/>
@@ -14726,7 +14729,7 @@
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
       <c r="D440" s="139" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="E440" s="76"/>
       <c r="F440" s="140"/>
@@ -14741,7 +14744,7 @@
       <c r="C441" s="34"/>
       <c r="D441" s="139"/>
       <c r="E441" s="72" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="F441" s="140">
         <f>IFERROR(VLOOKUP(E441,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14755,7 +14758,7 @@
       <c r="C442" s="34"/>
       <c r="D442" s="139"/>
       <c r="E442" s="72" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="F442" s="140">
         <f>IFERROR(VLOOKUP(E442,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14768,7 +14771,7 @@
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
       <c r="D443" s="71" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="E443" s="188"/>
       <c r="F443" s="140"/>
@@ -14783,7 +14786,7 @@
       <c r="C444" s="34"/>
       <c r="D444" s="71"/>
       <c r="E444" s="151" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="F444" s="140">
         <f>IFERROR(VLOOKUP(E444,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14797,7 +14800,7 @@
       <c r="C445" s="34"/>
       <c r="D445" s="71"/>
       <c r="E445" s="72" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="F445" s="140">
         <f>IFERROR(VLOOKUP(E445,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14813,7 +14816,7 @@
       <c r="C446" s="34"/>
       <c r="D446" s="71"/>
       <c r="E446" s="72" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F446" s="140">
         <f>IFERROR(VLOOKUP(E446,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14829,7 +14832,7 @@
       <c r="C447" s="34"/>
       <c r="D447" s="71"/>
       <c r="E447" s="72" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="F447" s="140">
         <f>IFERROR(VLOOKUP(E447,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14844,7 +14847,7 @@
       <c r="B448" s="76"/>
       <c r="C448" s="34"/>
       <c r="D448" s="196" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E448" s="197"/>
       <c r="F448" s="198"/>
@@ -14859,7 +14862,7 @@
       <c r="C449" s="34"/>
       <c r="D449" s="71"/>
       <c r="E449" s="72" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F449" s="140">
         <f>IFERROR(VLOOKUP(E449,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14873,7 +14876,7 @@
       <c r="C450" s="34"/>
       <c r="D450" s="71"/>
       <c r="E450" s="72" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F450" s="140">
         <f>IFERROR(VLOOKUP(E450,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14887,7 +14890,7 @@
       <c r="C451" s="34"/>
       <c r="D451" s="71"/>
       <c r="E451" s="72" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="F451" s="140">
         <f>IFERROR(VLOOKUP(E451,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14900,7 +14903,7 @@
       <c r="B452" s="76"/>
       <c r="C452" s="34"/>
       <c r="D452" s="71" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="E452" s="188"/>
       <c r="F452" s="140"/>
@@ -14915,7 +14918,7 @@
       <c r="C453" s="34"/>
       <c r="D453" s="71"/>
       <c r="E453" s="72" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="F453" s="140">
         <f>IFERROR(VLOOKUP(E453,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14929,7 +14932,7 @@
       <c r="C454" s="34"/>
       <c r="D454" s="71"/>
       <c r="E454" s="72" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="F454" s="140">
         <f>IFERROR(VLOOKUP(E454,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14943,7 +14946,7 @@
       <c r="C455" s="34"/>
       <c r="D455" s="71"/>
       <c r="E455" s="72" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="F455" s="140">
         <f>IFERROR(VLOOKUP(E455,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14957,7 +14960,7 @@
       <c r="C456" s="34"/>
       <c r="D456" s="71"/>
       <c r="E456" s="72" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="F456" s="140">
         <f>IFERROR(VLOOKUP(E456,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -14970,7 +14973,7 @@
       <c r="B457" s="76"/>
       <c r="C457" s="34"/>
       <c r="D457" s="71" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="E457" s="71"/>
       <c r="F457" s="140">
@@ -14987,7 +14990,7 @@
       <c r="B458" s="76"/>
       <c r="C458" s="34"/>
       <c r="D458" s="71" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E458" s="71"/>
       <c r="F458" s="140">
@@ -15004,7 +15007,7 @@
       <c r="B459" s="76"/>
       <c r="C459" s="34"/>
       <c r="D459" s="139" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="E459" s="72"/>
       <c r="F459" s="140"/>
@@ -15019,7 +15022,7 @@
       <c r="C460" s="34"/>
       <c r="D460" s="139"/>
       <c r="E460" s="72" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="F460" s="140">
         <f>IFERROR(VLOOKUP(E460,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15033,7 +15036,7 @@
       <c r="C461" s="34"/>
       <c r="D461" s="139"/>
       <c r="E461" s="72" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="F461" s="140">
         <f>IFERROR(VLOOKUP(E461,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15046,10 +15049,10 @@
       <c r="B462" s="76"/>
       <c r="C462" s="34"/>
       <c r="D462" s="71" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="E462" s="71" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="F462" s="140">
         <f>IFERROR(VLOOKUP(E462,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15067,7 +15070,7 @@
       <c r="C463" s="34"/>
       <c r="D463" s="71"/>
       <c r="E463" s="72" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15082,7 +15085,7 @@
       <c r="C464" s="34"/>
       <c r="D464" s="71"/>
       <c r="E464" s="72" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="F464" s="140">
         <f>IFERROR(VLOOKUP(E464,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15097,7 +15100,7 @@
       <c r="C465" s="34"/>
       <c r="D465" s="71"/>
       <c r="E465" s="72" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15113,7 +15116,7 @@
       <c r="C466" s="34"/>
       <c r="D466" s="71"/>
       <c r="E466" s="72" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F466" s="140">
         <f>IFERROR(VLOOKUP(E466,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15129,7 +15132,7 @@
       <c r="C467" s="34"/>
       <c r="D467" s="71"/>
       <c r="E467" s="72" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F467" s="140">
         <f>IFERROR(VLOOKUP(E467,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15145,7 +15148,7 @@
       <c r="C468" s="34"/>
       <c r="D468" s="71"/>
       <c r="E468" s="72" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="F468" s="140">
         <f>IFERROR(VLOOKUP(E468,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15161,7 +15164,7 @@
       <c r="C469" s="34"/>
       <c r="D469" s="71"/>
       <c r="E469" s="72" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F469" s="140">
         <f>IFERROR(VLOOKUP(E469,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15177,7 +15180,7 @@
       <c r="C470" s="34"/>
       <c r="D470" s="71"/>
       <c r="E470" s="72" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="F470" s="140">
         <f>IFERROR(VLOOKUP(E470,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15192,7 +15195,7 @@
       <c r="B471" s="76"/>
       <c r="C471" s="34"/>
       <c r="D471" s="71" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E471" s="188"/>
       <c r="F471" s="140"/>
@@ -15207,7 +15210,7 @@
       <c r="C472" s="34"/>
       <c r="D472" s="71"/>
       <c r="E472" s="72" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="F472" s="140">
         <f>IFERROR(VLOOKUP(E472,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15221,7 +15224,7 @@
       <c r="C473" s="34"/>
       <c r="D473" s="71"/>
       <c r="E473" s="72" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="F473" s="140">
         <f>IFERROR(VLOOKUP(E473,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15235,7 +15238,7 @@
       <c r="C474" s="34"/>
       <c r="D474" s="71"/>
       <c r="E474" s="72" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="F474" s="140">
         <f>IFERROR(VLOOKUP(E474,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15248,7 +15251,7 @@
       <c r="B475" s="76"/>
       <c r="C475" s="34"/>
       <c r="D475" s="139" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="E475" s="188"/>
       <c r="F475" s="140">
@@ -15265,7 +15268,7 @@
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
       <c r="D476" s="71" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E476" s="188"/>
       <c r="F476" s="140">
@@ -15282,7 +15285,7 @@
       <c r="B477" s="76"/>
       <c r="C477" s="34"/>
       <c r="D477" s="71" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E477" s="188"/>
       <c r="F477" s="140"/>
@@ -15297,7 +15300,7 @@
       <c r="C478" s="34"/>
       <c r="D478" s="71"/>
       <c r="E478" s="72" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F478" s="140">
         <f>IFERROR(VLOOKUP(E478,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15311,7 +15314,7 @@
       <c r="C479" s="34"/>
       <c r="D479" s="71"/>
       <c r="E479" s="72" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="F479" s="140">
         <f>IFERROR(VLOOKUP(E479,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15324,10 +15327,10 @@
       <c r="B480" s="76"/>
       <c r="C480" s="34"/>
       <c r="D480" s="71" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="E480" s="72" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="F480" s="140">
         <f>IFERROR(VLOOKUP(E480,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15344,7 +15347,7 @@
       <c r="C481" s="34"/>
       <c r="D481" s="71"/>
       <c r="E481" s="72" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15358,7 +15361,7 @@
       <c r="C482" s="34"/>
       <c r="D482" s="71"/>
       <c r="E482" s="72" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15371,10 +15374,10 @@
       <c r="B483" s="76"/>
       <c r="C483" s="34"/>
       <c r="D483" s="71" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E483" s="72" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F483" s="140">
         <f>IFERROR(VLOOKUP(E483,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15390,7 +15393,7 @@
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
       <c r="D484" s="71" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="E484" s="71"/>
       <c r="F484" s="140">
@@ -15407,7 +15410,7 @@
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
       <c r="D485" s="139" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="E485" s="72"/>
       <c r="F485" s="140">
@@ -15424,7 +15427,7 @@
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
       <c r="D486" s="71" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E486" s="68"/>
       <c r="F486" s="140">
@@ -15441,7 +15444,7 @@
       <c r="B487" s="76"/>
       <c r="C487" s="34"/>
       <c r="D487" s="71" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="E487" s="132"/>
       <c r="F487" s="140">
@@ -15458,7 +15461,7 @@
       <c r="B488" s="76"/>
       <c r="C488" s="34"/>
       <c r="D488" s="71" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="E488" s="132"/>
       <c r="F488" s="140">
@@ -15475,7 +15478,7 @@
       <c r="B489" s="76"/>
       <c r="C489" s="34"/>
       <c r="D489" s="71" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E489" s="132"/>
       <c r="F489" s="140">
@@ -15492,7 +15495,7 @@
       <c r="B490" s="76"/>
       <c r="C490" s="34"/>
       <c r="D490" s="71" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="E490" s="132"/>
       <c r="F490" s="140">
@@ -15509,7 +15512,7 @@
       <c r="B491" s="76"/>
       <c r="C491" s="34"/>
       <c r="D491" s="139" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="E491" s="132"/>
       <c r="F491" s="140">
@@ -15526,7 +15529,7 @@
       <c r="B492" s="76"/>
       <c r="C492" s="34"/>
       <c r="D492" s="139" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="E492" s="68"/>
       <c r="F492" s="140">
@@ -15543,7 +15546,7 @@
       <c r="B493" s="76"/>
       <c r="C493" s="34"/>
       <c r="D493" s="139" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E493" s="132"/>
       <c r="F493" s="140">
@@ -15560,7 +15563,7 @@
       <c r="B494" s="76"/>
       <c r="C494" s="34"/>
       <c r="D494" s="139" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="E494" s="132"/>
       <c r="F494" s="140">
@@ -15577,7 +15580,7 @@
       <c r="B495" s="76"/>
       <c r="C495" s="34"/>
       <c r="D495" s="139" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E495" s="132"/>
       <c r="F495" s="140">
@@ -15594,10 +15597,10 @@
       <c r="B496" s="76"/>
       <c r="C496" s="34"/>
       <c r="D496" s="139" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="E496" s="72" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="F496" s="140">
         <f>IFERROR(VLOOKUP(D496,Hoja1!$A$2:$E$399,5,FALSE),)</f>
@@ -15613,7 +15616,7 @@
       <c r="B497" s="76"/>
       <c r="C497" s="34"/>
       <c r="D497" s="139" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="E497" s="132"/>
       <c r="F497" s="140">
@@ -15631,7 +15634,7 @@
       <c r="B498" s="76"/>
       <c r="C498" s="34"/>
       <c r="D498" s="139" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E498" s="132"/>
       <c r="F498" s="140">
@@ -15649,7 +15652,7 @@
       <c r="B499" s="76"/>
       <c r="C499" s="34"/>
       <c r="D499" s="139" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E499" s="132"/>
       <c r="F499" s="140">
@@ -15667,7 +15670,7 @@
       <c r="B500" s="76"/>
       <c r="C500" s="34"/>
       <c r="D500" s="139" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E500" s="132"/>
       <c r="F500" s="140">
@@ -15685,7 +15688,7 @@
       <c r="B501" s="76"/>
       <c r="C501" s="34"/>
       <c r="D501" s="139" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="E501" s="132"/>
       <c r="F501" s="140">
@@ -15702,7 +15705,7 @@
       <c r="B502" s="76"/>
       <c r="C502" s="34"/>
       <c r="D502" s="139" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="E502" s="132"/>
       <c r="F502" s="140">
@@ -15726,7 +15729,7 @@
         <v>55</v>
       </c>
       <c r="I503" s="199" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="504" ht="13.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -15735,7 +15738,7 @@
       <c r="C504" s="34"/>
       <c r="D504" s="132"/>
       <c r="E504" s="200" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="F504" s="201">
         <f>SUM(F146:F502)</f>
@@ -15760,7 +15763,7 @@
       <c r="C505" s="34"/>
       <c r="D505" s="132"/>
       <c r="E505" s="203" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="F505" s="204">
         <f>+-'Anexo II'!E103</f>
@@ -15779,7 +15782,7 @@
       <c r="C506" s="34"/>
       <c r="D506" s="132"/>
       <c r="E506" s="207" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F506" s="208">
         <f>+F504+F505</f>
@@ -15808,7 +15811,7 @@
       <c r="C508" s="211"/>
       <c r="D508" s="211"/>
       <c r="E508" s="211" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="F508" s="211">
         <f>+F280-F506</f>
@@ -28565,14 +28568,14 @@
       <c r="C1" s="222"/>
       <c r="D1" s="222"/>
       <c r="E1" s="223" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="F1" s="224"/>
       <c r="G1" s="224"/>
     </row>
     <row r="2" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="72" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B2" s="151"/>
       <c r="C2" s="195"/>
@@ -28583,7 +28586,7 @@
     </row>
     <row r="3" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="72" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B3" s="151"/>
       <c r="C3" s="195"/>
@@ -28594,7 +28597,7 @@
     </row>
     <row r="4" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="72" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B4" s="151"/>
       <c r="C4" s="195"/>
@@ -28605,7 +28608,7 @@
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="72" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B5" s="151"/>
       <c r="C5" s="195"/>
@@ -28616,7 +28619,7 @@
     </row>
     <row r="6" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="72" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="151"/>
       <c r="C6" s="195"/>
@@ -28627,7 +28630,7 @@
     </row>
     <row r="7" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="72" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B7" s="151"/>
       <c r="C7" s="195"/>
@@ -28638,7 +28641,7 @@
     </row>
     <row r="8" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="72" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B8" s="151"/>
       <c r="C8" s="195"/>
@@ -28649,7 +28652,7 @@
     </row>
     <row r="9" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B9" s="151"/>
       <c r="C9" s="195"/>
@@ -28660,7 +28663,7 @@
     </row>
     <row r="10" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B10" s="151"/>
       <c r="C10" s="195"/>
@@ -28671,7 +28674,7 @@
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="72" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B11" s="151"/>
       <c r="C11" s="195"/>
@@ -28682,7 +28685,7 @@
     </row>
     <row r="12" ht="12" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="72" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B12" s="151"/>
       <c r="C12" s="195"/>
@@ -28693,7 +28696,7 @@
     </row>
     <row r="13" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="72" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B13" s="151"/>
       <c r="C13" s="195"/>
@@ -28704,7 +28707,7 @@
     </row>
     <row r="14" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B14" s="151"/>
       <c r="C14" s="195"/>
@@ -28715,7 +28718,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B15" s="151"/>
       <c r="C15" s="195"/>
@@ -28726,7 +28729,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="72" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B16" s="151"/>
       <c r="C16" s="195"/>
@@ -28737,7 +28740,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="72" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B17" s="151"/>
       <c r="C17" s="195"/>
@@ -28748,7 +28751,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="72" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B18" s="151"/>
       <c r="C18" s="195"/>
@@ -28759,7 +28762,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="72" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B19" s="151"/>
       <c r="C19" s="195"/>
@@ -28770,7 +28773,7 @@
     </row>
     <row r="20" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="72" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B20" s="151"/>
       <c r="C20" s="195"/>
@@ -28781,7 +28784,7 @@
     </row>
     <row r="21" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="72" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B21" s="151"/>
       <c r="C21" s="195"/>
@@ -28792,7 +28795,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="72" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B22" s="151"/>
       <c r="C22" s="195"/>
@@ -28803,7 +28806,7 @@
     </row>
     <row r="23" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="72" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B23" s="151"/>
       <c r="C23" s="195"/>
@@ -28814,7 +28817,7 @@
     </row>
     <row r="24" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="72" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B24" s="195"/>
       <c r="C24" s="195"/>
@@ -28825,7 +28828,7 @@
     </row>
     <row r="25" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="72" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B25" s="195"/>
       <c r="C25" s="195"/>
@@ -28836,7 +28839,7 @@
     </row>
     <row r="26" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="72" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B26" s="151"/>
       <c r="C26" s="195"/>
@@ -28847,7 +28850,7 @@
     </row>
     <row r="27" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="72" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B27" s="151"/>
       <c r="C27" s="195"/>
@@ -28858,7 +28861,7 @@
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="72" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B28" s="72"/>
       <c r="C28" s="72"/>
@@ -28869,7 +28872,7 @@
     </row>
     <row r="29" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="72" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B29" s="151"/>
       <c r="C29" s="195"/>
@@ -28880,7 +28883,7 @@
     </row>
     <row r="30" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="72" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B30" s="151"/>
       <c r="C30" s="195"/>
@@ -28891,7 +28894,7 @@
     </row>
     <row r="31" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="72" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B31" s="151"/>
       <c r="C31" s="195"/>
@@ -28902,7 +28905,7 @@
     </row>
     <row r="32" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="72" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B32" s="151"/>
       <c r="C32" s="195"/>
@@ -28913,7 +28916,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="72" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B33" s="151"/>
       <c r="C33" s="195"/>
@@ -28924,7 +28927,7 @@
     </row>
     <row r="34" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="72" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B34" s="151"/>
       <c r="C34" s="195"/>
@@ -28935,7 +28938,7 @@
     </row>
     <row r="35" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="72" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B35" s="151"/>
       <c r="C35" s="195"/>
@@ -28946,7 +28949,7 @@
     </row>
     <row r="36" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B36" s="151"/>
       <c r="C36" s="195"/>
@@ -28957,7 +28960,7 @@
     </row>
     <row r="37" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="72" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B37" s="151"/>
       <c r="C37" s="195"/>
@@ -28968,7 +28971,7 @@
     </row>
     <row r="38" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="72" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B38" s="151"/>
       <c r="C38" s="195"/>
@@ -28979,7 +28982,7 @@
     </row>
     <row r="39" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="72" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B39" s="151"/>
       <c r="C39" s="195"/>
@@ -28990,7 +28993,7 @@
     </row>
     <row r="40" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="72" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B40" s="151"/>
       <c r="C40" s="195"/>
@@ -29001,7 +29004,7 @@
     </row>
     <row r="41" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="72" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B41" s="151"/>
       <c r="C41" s="195"/>
@@ -29012,7 +29015,7 @@
     </row>
     <row r="42" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="72" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B42" s="151"/>
       <c r="C42" s="195"/>
@@ -29023,7 +29026,7 @@
     </row>
     <row r="43" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="72" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B43" s="151"/>
       <c r="C43" s="195"/>
@@ -29034,7 +29037,7 @@
     </row>
     <row r="44" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="72" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="220"/>
@@ -29045,7 +29048,7 @@
     </row>
     <row r="45" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" s="220"/>
       <c r="C45" s="220"/>
@@ -29056,7 +29059,7 @@
     </row>
     <row r="46" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="72" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B46" s="151"/>
       <c r="C46" s="195"/>
@@ -29073,10 +29076,10 @@
       <c r="E47" s="220"/>
       <c r="F47" s="220"/>
       <c r="G47" s="226" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H47" s="227" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -29205,13 +29208,13 @@
       <c r="D58" s="232"/>
       <c r="E58" s="232"/>
       <c r="F58" s="232" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G58" s="232"/>
     </row>
     <row r="59" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="72" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B59" s="151"/>
       <c r="C59" s="195"/>
@@ -29222,7 +29225,7 @@
     </row>
     <row r="60" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="72" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B60" s="151"/>
       <c r="C60" s="195"/>
@@ -29233,7 +29236,7 @@
     </row>
     <row r="61" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="72" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B61" s="151"/>
       <c r="C61" s="195"/>
@@ -29244,7 +29247,7 @@
     </row>
     <row r="62" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B62" s="151"/>
       <c r="C62" s="195"/>
@@ -29255,7 +29258,7 @@
     </row>
     <row r="63" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="72" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B63" s="151"/>
       <c r="C63" s="195"/>
@@ -29266,7 +29269,7 @@
     </row>
     <row r="64" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B64" s="151"/>
       <c r="C64" s="195"/>
@@ -29277,7 +29280,7 @@
     </row>
     <row r="65" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B65" s="151"/>
       <c r="C65" s="195"/>
@@ -29288,7 +29291,7 @@
     </row>
     <row r="66" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B66" s="151"/>
       <c r="C66" s="195"/>
@@ -29299,7 +29302,7 @@
     </row>
     <row r="67" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="72" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B67" s="151"/>
       <c r="C67" s="195"/>
@@ -29310,7 +29313,7 @@
     </row>
     <row r="68" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B68" s="151"/>
       <c r="C68" s="195"/>
@@ -29321,7 +29324,7 @@
     </row>
     <row r="69" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B69" s="151"/>
       <c r="C69" s="195"/>
@@ -29332,7 +29335,7 @@
     </row>
     <row r="70" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="72" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B70" s="151"/>
       <c r="C70" s="195"/>
@@ -29343,7 +29346,7 @@
     </row>
     <row r="71" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="72" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B71" s="151"/>
       <c r="C71" s="195"/>
@@ -29354,7 +29357,7 @@
     </row>
     <row r="72" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="72" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B72" s="151"/>
       <c r="C72" s="195"/>
@@ -29365,7 +29368,7 @@
     </row>
     <row r="73" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="72" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B73" s="151"/>
       <c r="C73" s="195"/>
@@ -29376,7 +29379,7 @@
     </row>
     <row r="74" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="72" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B74" s="151"/>
       <c r="C74" s="195"/>
@@ -29387,7 +29390,7 @@
     </row>
     <row r="75" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="72" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B75" s="151"/>
       <c r="C75" s="195"/>
@@ -29398,7 +29401,7 @@
     </row>
     <row r="76" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="72" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B76" s="151"/>
       <c r="C76" s="195"/>
@@ -29409,7 +29412,7 @@
     </row>
     <row r="77" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="72" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B77" s="151"/>
       <c r="C77" s="195"/>
@@ -29420,7 +29423,7 @@
     </row>
     <row r="78" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="72" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B78" s="151"/>
       <c r="C78" s="195"/>
@@ -29431,7 +29434,7 @@
     </row>
     <row r="79" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="72" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B79" s="151"/>
       <c r="C79" s="195"/>
@@ -29442,7 +29445,7 @@
     </row>
     <row r="80" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="72" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B80" s="151"/>
       <c r="C80" s="195"/>
@@ -29453,7 +29456,7 @@
     </row>
     <row r="81" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="72" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B81" s="151"/>
       <c r="C81" s="195"/>
@@ -29464,7 +29467,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="72" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B82" s="151"/>
       <c r="C82" s="195"/>
@@ -29475,7 +29478,7 @@
     </row>
     <row r="83" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="72" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B83" s="151"/>
       <c r="C83" s="195"/>
@@ -29486,7 +29489,7 @@
     </row>
     <row r="84" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="72" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B84" s="151"/>
       <c r="C84" s="195"/>
@@ -29497,7 +29500,7 @@
     </row>
     <row r="85" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="72" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B85" s="151"/>
       <c r="C85" s="195"/>
@@ -29508,7 +29511,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="72" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B86" s="151"/>
       <c r="C86" s="195"/>
@@ -29519,7 +29522,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="72" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B87" s="151"/>
       <c r="C87" s="195"/>
@@ -29530,7 +29533,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1" hidden="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B88" s="151"/>
       <c r="C88" s="195"/>
@@ -29544,7 +29547,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="72" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B89" s="151"/>
       <c r="C89" s="195"/>
@@ -29555,7 +29558,7 @@
     </row>
     <row r="90" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="72" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B90" s="151"/>
       <c r="C90" s="195"/>
@@ -29566,7 +29569,7 @@
     </row>
     <row r="91" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="72" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B91" s="151"/>
       <c r="C91" s="195"/>
@@ -29577,7 +29580,7 @@
     </row>
     <row r="92" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="72" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B92" s="151"/>
       <c r="C92" s="195"/>
@@ -29588,7 +29591,7 @@
     </row>
     <row r="93" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="72" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B93" s="151"/>
       <c r="C93" s="195"/>
@@ -29599,7 +29602,7 @@
     </row>
     <row r="94" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="72" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B94" s="151"/>
       <c r="C94" s="195"/>
@@ -29610,7 +29613,7 @@
     </row>
     <row r="95" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="72" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B95" s="151"/>
       <c r="C95" s="195"/>
@@ -29621,7 +29624,7 @@
     </row>
     <row r="96" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="72" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B96" s="151"/>
       <c r="C96" s="195"/>
@@ -29632,7 +29635,7 @@
     </row>
     <row r="97" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="72" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B97" s="151"/>
       <c r="C97" s="195"/>
@@ -29643,7 +29646,7 @@
     </row>
     <row r="98" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="72" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B98" s="151"/>
       <c r="C98" s="195"/>
@@ -29654,7 +29657,7 @@
     </row>
     <row r="99" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="72" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B99" s="151"/>
       <c r="C99" s="195"/>
@@ -29665,7 +29668,7 @@
     </row>
     <row r="100" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="72" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B100" s="151"/>
       <c r="C100" s="195"/>
@@ -29676,7 +29679,7 @@
     </row>
     <row r="101" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B101" s="151"/>
       <c r="C101" s="195"/>
@@ -29687,7 +29690,7 @@
     </row>
     <row r="102" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="72" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B102" s="151"/>
       <c r="C102" s="195"/>
@@ -29698,7 +29701,7 @@
     </row>
     <row r="103" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="72" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B103" s="151"/>
       <c r="C103" s="195"/>
@@ -29709,7 +29712,7 @@
     </row>
     <row r="104" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="72" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B104" s="151"/>
       <c r="C104" s="195"/>
@@ -29720,7 +29723,7 @@
     </row>
     <row r="105" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="72" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B105" s="151"/>
       <c r="C105" s="195"/>
@@ -29731,7 +29734,7 @@
     </row>
     <row r="106" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="72" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B106" s="151"/>
       <c r="C106" s="195"/>
@@ -29742,7 +29745,7 @@
     </row>
     <row r="107" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="72" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B107" s="151"/>
       <c r="C107" s="195"/>
@@ -30201,7 +30204,7 @@
     </row>
     <row r="172" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="72" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B172" s="151"/>
       <c r="C172" s="195"/>
@@ -30212,7 +30215,7 @@
     </row>
     <row r="173" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="72" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B173" s="151"/>
       <c r="C173" s="195"/>
@@ -30223,7 +30226,7 @@
     </row>
     <row r="174" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="72" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B174" s="151"/>
       <c r="C174" s="195"/>
@@ -30234,7 +30237,7 @@
     </row>
     <row r="175" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="72" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B175" s="151"/>
       <c r="C175" s="195"/>
@@ -30245,7 +30248,7 @@
     </row>
     <row r="176" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="72" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B176" s="151"/>
       <c r="C176" s="195"/>
@@ -30256,7 +30259,7 @@
     </row>
     <row r="177" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="72" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B177" s="151"/>
       <c r="C177" s="195"/>
@@ -30267,7 +30270,7 @@
     </row>
     <row r="178" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="72" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B178" s="220"/>
       <c r="C178" s="220"/>
@@ -30278,7 +30281,7 @@
     </row>
     <row r="179" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="72" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B179" s="220"/>
       <c r="C179" s="220"/>
@@ -30289,7 +30292,7 @@
     </row>
     <row r="180" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="72" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B180" s="220"/>
       <c r="C180" s="220"/>
@@ -30300,7 +30303,7 @@
     </row>
     <row r="181" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="72" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B181" s="220"/>
       <c r="C181" s="220"/>
@@ -30311,7 +30314,7 @@
     </row>
     <row r="182" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="72" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B182" s="220"/>
       <c r="C182" s="220"/>
@@ -30322,7 +30325,7 @@
     </row>
     <row r="183" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="72" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B183" s="220"/>
       <c r="C183" s="220"/>
@@ -30333,7 +30336,7 @@
     </row>
     <row r="184" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="72" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B184" s="220"/>
       <c r="C184" s="220"/>
@@ -30344,7 +30347,7 @@
     </row>
     <row r="185" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="72" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B185" s="220"/>
       <c r="C185" s="220"/>
@@ -30355,7 +30358,7 @@
     </row>
     <row r="186" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="72" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B186" s="220"/>
       <c r="C186" s="220"/>
@@ -30366,7 +30369,7 @@
     </row>
     <row r="187" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="72" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B187" s="220"/>
       <c r="C187" s="220"/>
@@ -30377,7 +30380,7 @@
     </row>
     <row r="188" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="72" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B188" s="220"/>
       <c r="C188" s="220"/>
@@ -30388,7 +30391,7 @@
     </row>
     <row r="189" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="72" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B189" s="220"/>
       <c r="C189" s="220"/>
@@ -30399,7 +30402,7 @@
     </row>
     <row r="190" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="72" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B190" s="220"/>
       <c r="C190" s="220"/>
@@ -30410,7 +30413,7 @@
     </row>
     <row r="191" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="72" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B191" s="220"/>
       <c r="C191" s="220"/>
@@ -30421,7 +30424,7 @@
     </row>
     <row r="192" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="72" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B192" s="220"/>
       <c r="C192" s="220"/>
@@ -30432,7 +30435,7 @@
     </row>
     <row r="193" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="72" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B193" s="220"/>
       <c r="C193" s="220"/>
@@ -30443,7 +30446,7 @@
     </row>
     <row r="194" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="72" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B194" s="220"/>
       <c r="C194" s="220"/>
@@ -30454,7 +30457,7 @@
     </row>
     <row r="195" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" s="72" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B195" s="220"/>
       <c r="C195" s="220"/>
@@ -30465,7 +30468,7 @@
     </row>
     <row r="196" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" s="72" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B196" s="220"/>
       <c r="C196" s="220"/>
@@ -30476,7 +30479,7 @@
     </row>
     <row r="197" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" s="72" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B197" s="220"/>
       <c r="C197" s="220"/>
@@ -30487,7 +30490,7 @@
     </row>
     <row r="198" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" s="72" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B198" s="151"/>
       <c r="C198" s="195"/>
@@ -30546,7 +30549,7 @@
     </row>
     <row r="207" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" s="151" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B207" s="151"/>
       <c r="C207" s="195"/>
@@ -30557,7 +30560,7 @@
     </row>
     <row r="208" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" s="151" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B208" s="151"/>
       <c r="C208" s="195"/>
@@ -30568,7 +30571,7 @@
     </row>
     <row r="209" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" s="151" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B209" s="151"/>
       <c r="C209" s="195"/>
@@ -30579,7 +30582,7 @@
     </row>
     <row r="210" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" s="151" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B210" s="151"/>
       <c r="C210" s="195"/>
@@ -30596,18 +30599,18 @@
     </row>
     <row r="213" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="221" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B213" s="233"/>
       <c r="C213" s="233"/>
       <c r="D213" s="233"/>
       <c r="E213" s="223" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="214" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="72" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B214" s="220"/>
       <c r="C214" s="195"/>
@@ -30618,7 +30621,7 @@
     </row>
     <row r="215" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" s="72" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B215" s="151"/>
       <c r="C215" s="195"/>
@@ -30629,7 +30632,7 @@
     </row>
     <row r="216" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" s="72" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B216" s="151"/>
       <c r="C216" s="195"/>
@@ -30640,7 +30643,7 @@
     </row>
     <row r="217" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" s="72" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B217" s="151"/>
       <c r="C217" s="195"/>
@@ -30651,7 +30654,7 @@
     </row>
     <row r="218" ht="12.75" customHeight="1" spans="1:5" s="234" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="235" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B218" s="236"/>
       <c r="C218" s="41"/>
@@ -30662,7 +30665,7 @@
     </row>
     <row r="219" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" s="72" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B219" s="151"/>
       <c r="C219" s="195"/>
@@ -30673,7 +30676,7 @@
     </row>
     <row r="220" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" s="72" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B220" s="151"/>
       <c r="C220" s="195"/>
@@ -30684,7 +30687,7 @@
     </row>
     <row r="221" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" s="72" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B221" s="151"/>
       <c r="C221" s="195"/>
@@ -30695,7 +30698,7 @@
     </row>
     <row r="222" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="72" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B222" s="151"/>
       <c r="C222" s="195"/>
@@ -30706,7 +30709,7 @@
     </row>
     <row r="223" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="72" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B223" s="151"/>
       <c r="C223" s="195"/>
@@ -30717,7 +30720,7 @@
     </row>
     <row r="224" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="72" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B224" s="151"/>
       <c r="C224" s="195"/>
@@ -30728,7 +30731,7 @@
     </row>
     <row r="225" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="72" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B225" s="151"/>
       <c r="C225" s="195"/>
@@ -30739,7 +30742,7 @@
     </row>
     <row r="226" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="72" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B226" s="151"/>
       <c r="C226" s="195"/>
@@ -30750,7 +30753,7 @@
     </row>
     <row r="227" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" s="72" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B227" s="151"/>
       <c r="C227" s="195"/>
@@ -30761,7 +30764,7 @@
     </row>
     <row r="228" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" s="72" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B228" s="151"/>
       <c r="C228" s="195"/>
@@ -30772,7 +30775,7 @@
     </row>
     <row r="229" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" s="72" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B229" s="151"/>
       <c r="C229" s="195"/>
@@ -30783,7 +30786,7 @@
     </row>
     <row r="230" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" s="72" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B230" s="151"/>
       <c r="C230" s="195"/>
@@ -30794,7 +30797,7 @@
     </row>
     <row r="231" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="72" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B231" s="151"/>
       <c r="C231" s="195"/>
@@ -30806,7 +30809,7 @@
     </row>
     <row r="232" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="72" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B232" s="151"/>
       <c r="C232" s="195"/>
@@ -30818,7 +30821,7 @@
     </row>
     <row r="233" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="72" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B233" s="151"/>
       <c r="C233" s="195"/>
@@ -30829,7 +30832,7 @@
     </row>
     <row r="234" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="72" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B234" s="151"/>
       <c r="C234" s="195"/>
@@ -30840,7 +30843,7 @@
     </row>
     <row r="235" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" s="72" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B235" s="151"/>
       <c r="C235" s="195"/>
@@ -30851,7 +30854,7 @@
     </row>
     <row r="236" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" s="72" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B236" s="151"/>
       <c r="C236" s="195"/>
@@ -30862,7 +30865,7 @@
     </row>
     <row r="237" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" s="72" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B237" s="151"/>
       <c r="C237" s="195"/>
@@ -30873,7 +30876,7 @@
     </row>
     <row r="238" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" s="72" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B238" s="151"/>
       <c r="C238" s="195"/>
@@ -30884,7 +30887,7 @@
     </row>
     <row r="239" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" s="72" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B239" s="151"/>
       <c r="C239" s="195"/>
@@ -30895,7 +30898,7 @@
     </row>
     <row r="240" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" s="72" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B240" s="151"/>
       <c r="C240" s="195"/>
@@ -30906,7 +30909,7 @@
     </row>
     <row r="241" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" s="72" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B241" s="151"/>
       <c r="C241" s="195"/>
@@ -30917,7 +30920,7 @@
     </row>
     <row r="242" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="72" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B242" s="151"/>
       <c r="C242" s="195"/>
@@ -30928,7 +30931,7 @@
     </row>
     <row r="243" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="72" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B243" s="151"/>
       <c r="C243" s="195"/>
@@ -30939,7 +30942,7 @@
     </row>
     <row r="244" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="72" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B244" s="151"/>
       <c r="C244" s="195"/>
@@ -30950,7 +30953,7 @@
     </row>
     <row r="245" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="72" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B245" s="151"/>
       <c r="C245" s="195"/>
@@ -30961,7 +30964,7 @@
     </row>
     <row r="246" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="72" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B246" s="151"/>
       <c r="C246" s="195"/>
@@ -30972,7 +30975,7 @@
     </row>
     <row r="247" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" s="72" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B247" s="151"/>
       <c r="C247" s="195"/>
@@ -30983,7 +30986,7 @@
     </row>
     <row r="248" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" s="72" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B248" s="151"/>
       <c r="C248" s="195"/>
@@ -30994,7 +30997,7 @@
     </row>
     <row r="249" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" s="72" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B249" s="151"/>
       <c r="C249" s="195"/>
@@ -31005,7 +31008,7 @@
     </row>
     <row r="250" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" s="72" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B250" s="151"/>
       <c r="C250" s="195"/>
@@ -31016,7 +31019,7 @@
     </row>
     <row r="251" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="72" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B251" s="151"/>
       <c r="C251" s="195"/>
@@ -31027,7 +31030,7 @@
     </row>
     <row r="252" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="72" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B252" s="151"/>
       <c r="C252" s="195"/>
@@ -31038,7 +31041,7 @@
     </row>
     <row r="253" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="72" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B253" s="151"/>
       <c r="C253" s="195"/>
@@ -31049,7 +31052,7 @@
     </row>
     <row r="254" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="72" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B254" s="151"/>
       <c r="C254" s="195"/>
@@ -31060,7 +31063,7 @@
     </row>
     <row r="255" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" s="72" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B255" s="151"/>
       <c r="C255" s="195"/>
@@ -31071,7 +31074,7 @@
     </row>
     <row r="256" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" s="72" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B256" s="151"/>
       <c r="C256" s="195"/>
@@ -31082,7 +31085,7 @@
     </row>
     <row r="257" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" s="72" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B257" s="151"/>
       <c r="C257" s="195"/>
@@ -31093,7 +31096,7 @@
     </row>
     <row r="258" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" s="72" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B258" s="151"/>
       <c r="C258" s="195"/>
@@ -31104,7 +31107,7 @@
     </row>
     <row r="259" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" s="72" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B259" s="151"/>
       <c r="C259" s="195"/>
@@ -31115,7 +31118,7 @@
     </row>
     <row r="260" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" s="72" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B260" s="151"/>
       <c r="C260" s="195"/>
@@ -31126,7 +31129,7 @@
     </row>
     <row r="261" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" s="72" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B261" s="151"/>
       <c r="C261" s="195"/>
@@ -31137,7 +31140,7 @@
     </row>
     <row r="262" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="72" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B262" s="151"/>
       <c r="C262" s="195"/>
@@ -31148,7 +31151,7 @@
     </row>
     <row r="263" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="72" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B263" s="151"/>
       <c r="C263" s="195"/>
@@ -31159,7 +31162,7 @@
     </row>
     <row r="264" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="72" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B264" s="151"/>
       <c r="C264" s="195"/>
@@ -31170,7 +31173,7 @@
     </row>
     <row r="265" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="72" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B265" s="151"/>
       <c r="C265" s="195"/>
@@ -31181,7 +31184,7 @@
     </row>
     <row r="266" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="72" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B266" s="151"/>
       <c r="C266" s="195"/>
@@ -31192,7 +31195,7 @@
     </row>
     <row r="267" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" s="72" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B267" s="151"/>
       <c r="C267" s="195"/>
@@ -31203,7 +31206,7 @@
     </row>
     <row r="268" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" s="72" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B268" s="151"/>
       <c r="C268" s="195"/>
@@ -31214,7 +31217,7 @@
     </row>
     <row r="269" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" s="72" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B269" s="151"/>
       <c r="C269" s="195"/>
@@ -31225,7 +31228,7 @@
     </row>
     <row r="270" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" s="72" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B270" s="151"/>
       <c r="C270" s="195"/>
@@ -31236,7 +31239,7 @@
     </row>
     <row r="271" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="72" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B271" s="151"/>
       <c r="C271" s="195"/>
@@ -31247,7 +31250,7 @@
     </row>
     <row r="272" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="72" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B272" s="151"/>
       <c r="C272" s="195"/>
@@ -31258,7 +31261,7 @@
     </row>
     <row r="273" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="72" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B273" s="151"/>
       <c r="C273" s="195"/>
@@ -31269,7 +31272,7 @@
     </row>
     <row r="274" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="72" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B274" s="151"/>
       <c r="C274" s="195"/>
@@ -31280,7 +31283,7 @@
     </row>
     <row r="275" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" s="72" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B275" s="151"/>
       <c r="C275" s="195"/>
@@ -31291,7 +31294,7 @@
     </row>
     <row r="276" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" s="72" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B276" s="151"/>
       <c r="C276" s="195"/>
@@ -31302,7 +31305,7 @@
     </row>
     <row r="277" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" s="72" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B277" s="151"/>
       <c r="C277" s="195"/>
@@ -31313,7 +31316,7 @@
     </row>
     <row r="278" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" s="72" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B278" s="151"/>
       <c r="C278" s="195"/>
@@ -31324,7 +31327,7 @@
     </row>
     <row r="279" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" s="72" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B279" s="151"/>
       <c r="C279" s="195"/>
@@ -31335,7 +31338,7 @@
     </row>
     <row r="280" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" s="72" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B280" s="151"/>
       <c r="C280" s="195"/>
@@ -31346,7 +31349,7 @@
     </row>
     <row r="281" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" s="72" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B281" s="151"/>
       <c r="C281" s="195"/>
@@ -31357,7 +31360,7 @@
     </row>
     <row r="282" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="72" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B282" s="151"/>
       <c r="C282" s="195"/>
@@ -31368,7 +31371,7 @@
     </row>
     <row r="283" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="72" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B283" s="151"/>
       <c r="C283" s="195"/>
@@ -31379,7 +31382,7 @@
     </row>
     <row r="284" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="72" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B284" s="151"/>
       <c r="C284" s="195"/>
@@ -31390,7 +31393,7 @@
     </row>
     <row r="285" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B285" s="151"/>
       <c r="C285" s="195"/>
@@ -31401,7 +31404,7 @@
     </row>
     <row r="286" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="72" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B286" s="151"/>
       <c r="C286" s="195"/>
@@ -31412,7 +31415,7 @@
     </row>
     <row r="287" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" s="72" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B287" s="151"/>
       <c r="C287" s="195"/>
@@ -31423,7 +31426,7 @@
     </row>
     <row r="288" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" s="72" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B288" s="151"/>
       <c r="C288" s="195"/>
@@ -31434,7 +31437,7 @@
     </row>
     <row r="289" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" s="72" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B289" s="151"/>
       <c r="C289" s="195"/>
@@ -31445,7 +31448,7 @@
     </row>
     <row r="290" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" s="72" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B290" s="151"/>
       <c r="C290" s="195"/>
@@ -31456,7 +31459,7 @@
     </row>
     <row r="291" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="72" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B291" s="151"/>
       <c r="C291" s="195"/>
@@ -31467,7 +31470,7 @@
     </row>
     <row r="292" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="72" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B292" s="151"/>
       <c r="C292" s="195"/>
@@ -31478,7 +31481,7 @@
     </row>
     <row r="293" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="72" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B293" s="151"/>
       <c r="C293" s="195"/>
@@ -31489,7 +31492,7 @@
     </row>
     <row r="294" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="72" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B294" s="151"/>
       <c r="C294" s="195"/>
@@ -31500,7 +31503,7 @@
     </row>
     <row r="295" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" s="72" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B295" s="151"/>
       <c r="C295" s="195"/>
@@ -31511,7 +31514,7 @@
     </row>
     <row r="296" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" s="72" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B296" s="151"/>
       <c r="C296" s="195"/>
@@ -31522,7 +31525,7 @@
     </row>
     <row r="297" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" s="72" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B297" s="151"/>
       <c r="C297" s="195"/>
@@ -31533,7 +31536,7 @@
     </row>
     <row r="298" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" s="72" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B298" s="151"/>
       <c r="C298" s="195"/>
@@ -31544,7 +31547,7 @@
     </row>
     <row r="299" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" s="72" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B299" s="151"/>
       <c r="C299" s="195"/>
@@ -31555,7 +31558,7 @@
     </row>
     <row r="300" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" s="72" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B300" s="151"/>
       <c r="C300" s="195"/>
@@ -31566,7 +31569,7 @@
     </row>
     <row r="301" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" s="72" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B301" s="151"/>
       <c r="C301" s="195"/>
@@ -31577,7 +31580,7 @@
     </row>
     <row r="302" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="72" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B302" s="151"/>
       <c r="C302" s="195"/>
@@ -31588,7 +31591,7 @@
     </row>
     <row r="303" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="72" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B303" s="151"/>
       <c r="C303" s="195"/>
@@ -31599,7 +31602,7 @@
     </row>
     <row r="304" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="72" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B304" s="151"/>
       <c r="C304" s="195"/>
@@ -31610,7 +31613,7 @@
     </row>
     <row r="305" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="72" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B305" s="151"/>
       <c r="C305" s="195"/>
@@ -31621,7 +31624,7 @@
     </row>
     <row r="306" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="72" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B306" s="151"/>
       <c r="C306" s="195"/>
@@ -31632,7 +31635,7 @@
     </row>
     <row r="307" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" s="72" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B307" s="151"/>
       <c r="C307" s="195"/>
@@ -31643,7 +31646,7 @@
     </row>
     <row r="308" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" s="72" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B308" s="151"/>
       <c r="C308" s="195"/>
@@ -31654,7 +31657,7 @@
     </row>
     <row r="309" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" s="72" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B309" s="151"/>
       <c r="C309" s="195"/>
@@ -31665,7 +31668,7 @@
     </row>
     <row r="310" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" s="72" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B310" s="151"/>
       <c r="C310" s="195"/>
@@ -31676,7 +31679,7 @@
     </row>
     <row r="311" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="72" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B311" s="151"/>
       <c r="C311" s="195"/>
@@ -31687,7 +31690,7 @@
     </row>
     <row r="312" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="72" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B312" s="151"/>
       <c r="C312" s="195"/>
@@ -31698,7 +31701,7 @@
     </row>
     <row r="313" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="72" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B313" s="151"/>
       <c r="C313" s="195"/>
@@ -31709,7 +31712,7 @@
     </row>
     <row r="314" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="72" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B314" s="151"/>
       <c r="C314" s="195"/>
@@ -31721,7 +31724,7 @@
     </row>
     <row r="315" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="72" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B315" s="151"/>
       <c r="C315" s="195"/>
@@ -31733,7 +31736,7 @@
     </row>
     <row r="316" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="72" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B316" s="151"/>
       <c r="C316" s="195"/>
@@ -31745,7 +31748,7 @@
     </row>
     <row r="317" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" s="72" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B317" s="151"/>
       <c r="C317" s="195"/>
@@ -31756,7 +31759,7 @@
     </row>
     <row r="318" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" s="72" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B318" s="151"/>
       <c r="C318" s="195"/>
@@ -31767,7 +31770,7 @@
     </row>
     <row r="319" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" s="72" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B319" s="151"/>
       <c r="C319" s="195"/>
@@ -31778,7 +31781,7 @@
     </row>
     <row r="320" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" s="72" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B320" s="151"/>
       <c r="C320" s="195"/>
@@ -31789,7 +31792,7 @@
     </row>
     <row r="321" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" s="72" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B321" s="151"/>
       <c r="C321" s="195"/>
@@ -31800,7 +31803,7 @@
     </row>
     <row r="322" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="72" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B322" s="151"/>
       <c r="C322" s="195"/>
@@ -31811,7 +31814,7 @@
     </row>
     <row r="323" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="72" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B323" s="151"/>
       <c r="C323" s="195"/>
@@ -31822,7 +31825,7 @@
     </row>
     <row r="324" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="72" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B324" s="151"/>
       <c r="C324" s="195"/>
@@ -31833,7 +31836,7 @@
     </row>
     <row r="325" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="72" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B325" s="151"/>
       <c r="C325" s="195"/>
@@ -31844,7 +31847,7 @@
     </row>
     <row r="326" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="72" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B326" s="151"/>
       <c r="C326" s="195"/>
@@ -31855,7 +31858,7 @@
     </row>
     <row r="327" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" s="72" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B327" s="151"/>
       <c r="C327" s="195"/>
@@ -31866,7 +31869,7 @@
     </row>
     <row r="328" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" s="72" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B328" s="151"/>
       <c r="C328" s="195"/>
@@ -31877,7 +31880,7 @@
     </row>
     <row r="329" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" s="72" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B329" s="151"/>
       <c r="C329" s="195"/>
@@ -31888,7 +31891,7 @@
     </row>
     <row r="330" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" s="151" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B330" s="151"/>
       <c r="C330" s="195"/>
@@ -31899,7 +31902,7 @@
     </row>
     <row r="331" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="151" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B331" s="151"/>
       <c r="C331" s="195"/>
@@ -31910,7 +31913,7 @@
     </row>
     <row r="332" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="151" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B332" s="151"/>
       <c r="C332" s="195"/>
@@ -31921,7 +31924,7 @@
     </row>
     <row r="333" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="151" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B333" s="151"/>
       <c r="C333" s="195"/>
@@ -31932,7 +31935,7 @@
     </row>
     <row r="334" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="151" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B334" s="151"/>
       <c r="C334" s="195"/>
@@ -31943,7 +31946,7 @@
     </row>
     <row r="335" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" s="151" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B335" s="151"/>
       <c r="C335" s="195"/>
@@ -31954,7 +31957,7 @@
     </row>
     <row r="336" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" s="72" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B336" s="151"/>
       <c r="C336" s="195"/>
@@ -31965,7 +31968,7 @@
     </row>
     <row r="337" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" s="72" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B337" s="151"/>
       <c r="C337" s="195"/>
@@ -31976,7 +31979,7 @@
     </row>
     <row r="338" ht="12.75" customHeight="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" s="72" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B338" s="151"/>
       <c r="C338" s="195"/>
@@ -31992,10 +31995,10 @@
       <c r="D339" s="225"/>
       <c r="E339" s="195"/>
       <c r="F339" s="238" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G339" s="239" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="340" ht="10.15" customHeight="1" hidden="1" spans="1:7" s="235" customFormat="1" x14ac:dyDescent="0.25">
@@ -32203,7 +32206,7 @@
         <v>-476736080.9</v>
       </c>
       <c r="H366" s="220" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="367" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -32220,7 +32223,7 @@
         <v>-3354028747.869999</v>
       </c>
       <c r="H367" s="72" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="368" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -32250,7 +32253,7 @@
       <c r="F369" s="220"/>
       <c r="G369" s="225"/>
       <c r="H369" s="72" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="370" ht="12.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -32268,10 +32271,10 @@
       <c r="E371" s="140"/>
       <c r="F371" s="220"/>
       <c r="G371" s="244" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H371" s="245" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="372" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -33139,9 +33142,13 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
+      <c r="D54" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="E54" s="1"/>
-      <c r="F54" s="19"/>
+      <c r="F54" s="19">
+        <f>+SALDOS!G39</f>
+      </c>
       <c r="G54" s="19"/>
     </row>
     <row r="55" ht="10.9" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -33168,7 +33175,7 @@
     <row r="57" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
@@ -33186,10 +33193,10 @@
     <row r="59" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C59" s="70" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -33200,7 +33207,7 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="19">
@@ -33251,22 +33258,22 @@
     <row r="65" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" ht="11.25" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="67" ht="11.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C67" s="70" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="68" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -33274,7 +33281,7 @@
       <c r="B68" s="1"/>
       <c r="C68" s="70"/>
       <c r="D68" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="19">
@@ -33287,7 +33294,7 @@
       <c r="B69" s="1"/>
       <c r="C69" s="70"/>
       <c r="D69" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="19">
@@ -33300,7 +33307,7 @@
       <c r="B70" s="1"/>
       <c r="C70" s="70"/>
       <c r="D70" s="71" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="19">
@@ -33313,7 +33320,7 @@
       <c r="B71" s="1"/>
       <c r="C71" s="70"/>
       <c r="D71" s="71" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="19">
@@ -33338,10 +33345,10 @@
     <row r="73" ht="10.9" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C73" s="70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -33356,7 +33363,7 @@
       <c r="B74" s="10"/>
       <c r="C74" s="1"/>
       <c r="D74" s="71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E74" s="76"/>
       <c r="F74" s="74">
@@ -33369,7 +33376,7 @@
       <c r="B75" s="10"/>
       <c r="C75" s="1"/>
       <c r="D75" s="71" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E75" s="76"/>
       <c r="F75" s="74">
@@ -33381,7 +33388,7 @@
       <c r="B76" s="10"/>
       <c r="C76" s="1"/>
       <c r="D76" s="71" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E76" s="76"/>
       <c r="F76" s="74">
@@ -33393,7 +33400,7 @@
       <c r="B77" s="10"/>
       <c r="C77" s="1"/>
       <c r="D77" s="71" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E77" s="76"/>
       <c r="F77" s="74">
@@ -33406,7 +33413,7 @@
       <c r="B78" s="10"/>
       <c r="C78" s="1"/>
       <c r="D78" s="71" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E78" s="76"/>
       <c r="F78" s="74">
@@ -33419,7 +33426,7 @@
       <c r="B79" s="10"/>
       <c r="C79" s="1"/>
       <c r="D79" s="71" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E79" s="76"/>
       <c r="F79" s="74">
@@ -33432,7 +33439,7 @@
       <c r="B80" s="10"/>
       <c r="C80" s="1"/>
       <c r="D80" s="72" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E80" s="76"/>
       <c r="F80" s="74">
@@ -33445,7 +33452,7 @@
       <c r="B81" s="10"/>
       <c r="C81" s="1"/>
       <c r="D81" s="71" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E81" s="76"/>
       <c r="F81" s="74">
@@ -33458,7 +33465,7 @@
       <c r="B82" s="10"/>
       <c r="C82" s="1"/>
       <c r="D82" s="71" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E82" s="76"/>
       <c r="F82" s="74">
@@ -33471,7 +33478,7 @@
       <c r="B83" s="10"/>
       <c r="C83" s="1"/>
       <c r="D83" s="71" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E83" s="76"/>
       <c r="F83" s="74">
@@ -33484,7 +33491,7 @@
       <c r="B84" s="10"/>
       <c r="C84" s="1"/>
       <c r="D84" s="71" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E84" s="76"/>
       <c r="F84" s="74">
@@ -33497,7 +33504,7 @@
       <c r="B85" s="10"/>
       <c r="C85" s="1"/>
       <c r="D85" s="71" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E85" s="76"/>
       <c r="F85" s="74">
@@ -33527,10 +33534,10 @@
     <row r="88" ht="13.15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C88" s="70" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D88" s="71"/>
       <c r="E88" s="76"/>
@@ -33541,7 +33548,7 @@
       <c r="B89" s="1"/>
       <c r="C89" s="70"/>
       <c r="D89" s="71" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E89" s="76"/>
       <c r="F89" s="74">
@@ -33554,7 +33561,7 @@
       <c r="B90" s="10"/>
       <c r="C90" s="1"/>
       <c r="D90" s="71" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E90" s="76"/>
       <c r="F90" s="74">
@@ -33567,7 +33574,7 @@
       <c r="B91" s="10"/>
       <c r="C91" s="1"/>
       <c r="D91" s="71" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E91" s="76"/>
       <c r="F91" s="74">
@@ -33580,7 +33587,7 @@
       <c r="B92" s="10"/>
       <c r="C92" s="1"/>
       <c r="D92" s="71" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E92" s="76"/>
       <c r="F92" s="74">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -13,8 +13,8 @@
     <sheet sheetId="5" name="Activo y Pasivo" state="visible" r:id="rId7"/>
     <sheet sheetId="12" name="Anexo I" state="visible" r:id="rId8"/>
     <sheet sheetId="10" name="Anexo II" state="visible" r:id="rId9"/>
-    <sheet sheetId="14" name="SALDOS" state="hidden" r:id="rId10"/>
-    <sheet sheetId="15" name="Hoja1" state="hidden" r:id="rId11"/>
+    <sheet sheetId="14" name="Distribución por línea" state="hidden" r:id="rId10"/>
+    <sheet sheetId="15" name="Balance de sumas y saldos" state="hidden" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">SALDOS!$F$1:$F$110,SALDOS!$F$112:$F$510</definedName>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Anexo I'!$O15:$O23</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Anexo II'!$A2:$J113</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -4555,7 +4555,7 @@
       <c r="F10" s="124"/>
       <c r="G10" s="16"/>
       <c r="H10" s="19">
-        <f>+SALDOS!G323</f>
+        <f>+'Distribución por línea'!G323</f>
         <v>56235551.05</v>
       </c>
       <c r="I10" s="125"/>
@@ -4575,7 +4575,7 @@
         <v>283508619.32</v>
       </c>
       <c r="F11" s="124">
-        <f>+SALDOS!G369</f>
+        <f>+'Distribución por línea'!G369</f>
         <v>283508619.32</v>
       </c>
       <c r="G11" s="16"/>
@@ -4599,7 +4599,7 @@
       <c r="F12" s="124"/>
       <c r="G12" s="16"/>
       <c r="H12" s="19">
-        <f>+SALDOS!G375</f>
+        <f>+'Distribución por línea'!G375</f>
         <v>58572858.17</v>
       </c>
       <c r="I12" s="125"/>
@@ -4621,8 +4621,7 @@
       <c r="F13" s="124"/>
       <c r="G13" s="16"/>
       <c r="H13" s="19">
-        <f>+SALDOS!G258</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G258</f>
       </c>
       <c r="I13" s="125"/>
       <c r="J13" s="123"/>
@@ -4643,7 +4642,7 @@
       <c r="F14" s="124"/>
       <c r="G14" s="16"/>
       <c r="H14" s="19">
-        <f>+SALDOS!G303</f>
+        <f>+'Distribución por línea'!G303</f>
         <v>189946.28</v>
       </c>
       <c r="I14" s="125"/>
@@ -4665,8 +4664,7 @@
       <c r="F15" s="124"/>
       <c r="G15" s="16"/>
       <c r="H15" s="19">
-        <f>+SALDOS!G403</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G403</f>
       </c>
       <c r="I15" s="125"/>
       <c r="J15" s="123"/>
@@ -4687,7 +4685,7 @@
       <c r="F16" s="124"/>
       <c r="G16" s="16"/>
       <c r="H16" s="19">
-        <f>+SALDOS!G188</f>
+        <f>+'Distribución por línea'!G188</f>
         <v>30000</v>
       </c>
       <c r="I16" s="125"/>
@@ -4709,8 +4707,7 @@
       <c r="F17" s="124"/>
       <c r="G17" s="16"/>
       <c r="H17" s="19">
-        <f>+SALDOS!G315</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G315</f>
       </c>
       <c r="I17" s="125"/>
       <c r="J17" s="123"/>
@@ -4731,8 +4728,7 @@
       <c r="F18" s="124"/>
       <c r="G18" s="16"/>
       <c r="H18" s="19">
-        <f>+SALDOS!G359+SALDOS!G398</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G359+'Distribución por línea'!G398</f>
       </c>
       <c r="I18" s="125"/>
       <c r="J18" s="123"/>
@@ -4753,8 +4749,7 @@
       <c r="F19" s="124"/>
       <c r="G19" s="16"/>
       <c r="H19" s="19">
-        <f>+SALDOS!G362</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G362</f>
       </c>
       <c r="I19" s="125"/>
       <c r="J19" s="123"/>
@@ -4795,12 +4790,12 @@
         <v>77830748.92</v>
       </c>
       <c r="F21" s="124">
-        <f>+SALDOS!G171</f>
+        <f>+'Distribución por línea'!G171</f>
         <v>14820317.13</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="19">
-        <f>+SALDOS!G425</f>
+        <f>+'Distribución por línea'!G425</f>
         <v>63010431.79</v>
       </c>
       <c r="I21" s="125"/>
@@ -4822,7 +4817,7 @@
       <c r="F22" s="124"/>
       <c r="G22" s="16"/>
       <c r="H22" s="19">
-        <f>+SALDOS!G307+SALDOS!G309+SALDOS!G310+SALDOS!G308</f>
+        <f>+'Distribución por línea'!G307+'Distribución por línea'!G309+'Distribución por línea'!G310+'Distribución por línea'!G308</f>
         <v>48607846.6</v>
       </c>
       <c r="I22" s="125"/>
@@ -4861,8 +4856,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="124">
-        <f>+SALDOS!G203</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G203</f>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="19"/>
@@ -4885,7 +4879,7 @@
       <c r="F25" s="124"/>
       <c r="G25" s="16"/>
       <c r="H25" s="19">
-        <f>+SALDOS!G352</f>
+        <f>+'Distribución por línea'!G352</f>
         <v>9880231.91</v>
       </c>
       <c r="I25" s="125"/>
@@ -4907,7 +4901,7 @@
       <c r="F26" s="124"/>
       <c r="G26" s="16"/>
       <c r="H26" s="19">
-        <f>+SALDOS!G331</f>
+        <f>+'Distribución por línea'!G331</f>
         <v>31296828.740000002</v>
       </c>
       <c r="I26" s="125"/>
@@ -4946,7 +4940,7 @@
         <v>8552960.4</v>
       </c>
       <c r="F28" s="124">
-        <f>+SALDOS!G343+SALDOS!G496+SALDOS!G497</f>
+        <f>+'Distribución por línea'!G343+'Distribución por línea'!G496+'Distribución por línea'!G497</f>
         <v>8552960.4</v>
       </c>
       <c r="G28" s="16"/>
@@ -4989,8 +4983,7 @@
       <c r="F30" s="124"/>
       <c r="G30" s="16"/>
       <c r="H30" s="19">
-        <f>+SALDOS!G312</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G312</f>
       </c>
       <c r="I30" s="125"/>
       <c r="J30" s="123"/>
@@ -5009,8 +5002,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="124">
-        <f>+SALDOS!G240</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G240</f>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="19"/>
@@ -5033,8 +5025,7 @@
       <c r="F32" s="124"/>
       <c r="G32" s="16"/>
       <c r="H32" s="19">
-        <f>+SALDOS!G440</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G440</f>
       </c>
       <c r="I32" s="125"/>
       <c r="J32" s="123"/>
@@ -5053,8 +5044,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="124">
-        <f>+SALDOS!G472</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G472</f>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="19"/>
@@ -5075,7 +5065,7 @@
         <v>901685.37</v>
       </c>
       <c r="F34" s="126">
-        <f>+SALDOS!G407</f>
+        <f>+'Distribución por línea'!G407</f>
         <v>901685.37</v>
       </c>
       <c r="G34" s="16"/>
@@ -5097,7 +5087,7 @@
         <v>11129701.370000001</v>
       </c>
       <c r="F35" s="125">
-        <f>+SALDOS!G265</f>
+        <f>+'Distribución por línea'!G265</f>
         <v>11129701.370000001</v>
       </c>
       <c r="G35" s="16"/>
@@ -5119,12 +5109,12 @@
         <v>17028771.310000002</v>
       </c>
       <c r="F36" s="124">
-        <f>+SALDOS!G189</f>
+        <f>+'Distribución por línea'!G189</f>
         <v>11098092.88</v>
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="19">
-        <f>+SALDOS!G214+SALDOS!G394+SALDOS!G458</f>
+        <f>+'Distribución por línea'!G214+'Distribución por línea'!G394+'Distribución por línea'!G458</f>
         <v>5930678.43</v>
       </c>
       <c r="I36" s="125"/>
@@ -5144,7 +5134,7 @@
         <v>20016345.41</v>
       </c>
       <c r="F37" s="124">
-        <f>+SALDOS!G463</f>
+        <f>+'Distribución por línea'!G463</f>
         <v>20016345.41</v>
       </c>
       <c r="G37" s="16"/>
@@ -5168,8 +5158,7 @@
       <c r="F38" s="124"/>
       <c r="G38" s="16"/>
       <c r="H38" s="19">
-        <f>+SALDOS!G400+SALDOS!G441</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G400+'Distribución por línea'!G441</f>
       </c>
       <c r="I38" s="125"/>
       <c r="J38" s="123"/>
@@ -5190,7 +5179,7 @@
       <c r="F39" s="124"/>
       <c r="G39" s="16"/>
       <c r="H39" s="19">
-        <f>+SALDOS!G449</f>
+        <f>+'Distribución por línea'!G449</f>
         <v>8441197.290000001</v>
       </c>
       <c r="I39" s="125"/>
@@ -5210,7 +5199,7 @@
         <v>5964121.24</v>
       </c>
       <c r="F40" s="124">
-        <f>+SALDOS!G218</f>
+        <f>+'Distribución por línea'!G218</f>
         <v>5964121.24</v>
       </c>
       <c r="G40" s="16"/>
@@ -5232,8 +5221,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="124">
-        <f>+SALDOS!G239</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G239</f>
       </c>
       <c r="G41" s="16"/>
       <c r="H41" s="19"/>
@@ -5254,8 +5242,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="124">
-        <f>+SALDOS!G364</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G364</f>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="19"/>
@@ -5278,7 +5265,7 @@
       <c r="F43" s="124"/>
       <c r="G43" s="16"/>
       <c r="H43" s="19">
-        <f>+SALDOS!G316</f>
+        <f>+'Distribución por línea'!G316</f>
         <v>18512.4</v>
       </c>
       <c r="I43" s="125"/>
@@ -5300,8 +5287,7 @@
       <c r="F44" s="124"/>
       <c r="G44" s="16"/>
       <c r="H44" s="19">
-        <f>+SALDOS!G386</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G386</f>
       </c>
       <c r="I44" s="125"/>
       <c r="J44" s="123"/>
@@ -5320,7 +5306,7 @@
         <v>5267041.88</v>
       </c>
       <c r="F45" s="124">
-        <f>+SALDOS!G180</f>
+        <f>+'Distribución por línea'!G180</f>
         <v>5267041.88</v>
       </c>
       <c r="G45" s="16"/>
@@ -5342,8 +5328,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="124">
-        <f>+SALDOS!G460</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G460</f>
       </c>
       <c r="G46" s="16"/>
       <c r="H46" s="19"/>
@@ -5364,8 +5349,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="124">
-        <f>+SALDOS!G257</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G257</f>
       </c>
       <c r="G47" s="16"/>
       <c r="H47" s="19"/>
@@ -5388,7 +5372,7 @@
       <c r="F48" s="124"/>
       <c r="G48" s="16"/>
       <c r="H48" s="19">
-        <f>+SALDOS!G414</f>
+        <f>+'Distribución por línea'!G414</f>
         <v>236115665.5</v>
       </c>
       <c r="I48" s="125"/>
@@ -5408,8 +5392,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="124">
-        <f>+SALDOS!G234</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G234</f>
       </c>
       <c r="G49" s="16"/>
       <c r="H49" s="19"/>
@@ -5430,7 +5413,7 @@
         <v>14717993.67</v>
       </c>
       <c r="F50" s="124">
-        <f>+SALDOS!G453</f>
+        <f>+'Distribución por línea'!G453</f>
         <v>14717993.67</v>
       </c>
       <c r="G50" s="16"/>
@@ -5452,8 +5435,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="124">
-        <f>+SALDOS!G233</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G233</f>
       </c>
       <c r="G51" s="16"/>
       <c r="H51" s="19"/>
@@ -5474,12 +5456,12 @@
         <v>15921026</v>
       </c>
       <c r="F52" s="124">
-        <f>+SALDOS!G187+SALDOS!G231+SALDOS!G368+SALDOS!G387</f>
+        <f>+'Distribución por línea'!G187+'Distribución por línea'!G231+'Distribución por línea'!G368+'Distribución por línea'!G387</f>
         <v>39000</v>
       </c>
       <c r="G52" s="16"/>
       <c r="H52" s="19">
-        <f>+SALDOS!G391</f>
+        <f>+'Distribución por línea'!G391</f>
         <v>15882026</v>
       </c>
       <c r="I52" s="125"/>
@@ -5501,7 +5483,7 @@
       <c r="F53" s="124"/>
       <c r="G53" s="16"/>
       <c r="H53" s="19">
-        <f>+SALDOS!G295</f>
+        <f>+'Distribución por línea'!G295</f>
         <v>1099927.51</v>
       </c>
       <c r="I53" s="125"/>
@@ -5523,8 +5505,7 @@
       <c r="F54" s="124"/>
       <c r="G54" s="16"/>
       <c r="H54" s="19">
-        <f>+SALDOS!G311</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G311</f>
       </c>
       <c r="I54" s="125"/>
       <c r="J54" s="123"/>
@@ -5543,7 +5524,7 @@
         <v>180930770.69</v>
       </c>
       <c r="F55" s="124">
-        <f>+SALDOS!G160</f>
+        <f>+'Distribución por línea'!G160</f>
         <v>180930770.69</v>
       </c>
       <c r="G55" s="16"/>
@@ -5565,8 +5546,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="126">
-        <f>+SALDOS!G155</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G155</f>
       </c>
       <c r="G56" s="63"/>
       <c r="H56" s="16"/>
@@ -5587,7 +5567,7 @@
         <v>25426948.26</v>
       </c>
       <c r="F57" s="124">
-        <f>+SALDOS!G270</f>
+        <f>+'Distribución por línea'!G270</f>
         <v>25426948.26</v>
       </c>
       <c r="G57" s="19"/>
@@ -5609,7 +5589,7 @@
         <v>1884806.58</v>
       </c>
       <c r="F58" s="124">
-        <f>+SALDOS!G273+SALDOS!G283</f>
+        <f>+'Distribución por línea'!G273+'Distribución por línea'!G283</f>
         <v>1884806.58</v>
       </c>
       <c r="G58" s="19"/>
@@ -5631,7 +5611,7 @@
         <v>13001275.15</v>
       </c>
       <c r="F59" s="124">
-        <f>+SALDOS!G169+SALDOS!G284+SALDOS!G285+SALDOS!G494+SALDOS!F499</f>
+        <f>+'Distribución por línea'!G169+'Distribución por línea'!G284+'Distribución por línea'!G285+'Distribución por línea'!G494+'Distribución por línea'!F499</f>
         <v>13001275.15</v>
       </c>
       <c r="G59" s="17"/>
@@ -5653,7 +5633,7 @@
         <v>784842.52</v>
       </c>
       <c r="F60" s="124">
-        <f>+SALDOS!G426</f>
+        <f>+'Distribución por línea'!G426</f>
         <v>784842.52</v>
       </c>
       <c r="G60" s="16"/>
@@ -5677,8 +5657,7 @@
       <c r="F61" s="124"/>
       <c r="G61" s="16"/>
       <c r="H61" s="19">
-        <f>+SALDOS!G294</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G294</f>
       </c>
       <c r="I61" s="125"/>
       <c r="J61" s="123"/>
@@ -5697,7 +5676,7 @@
         <v>149263.11</v>
       </c>
       <c r="F62" s="124">
-        <f>+SALDOS!G247</f>
+        <f>+'Distribución por línea'!G247</f>
         <v>149263.11</v>
       </c>
       <c r="G62" s="16"/>
@@ -5719,12 +5698,12 @@
         <v>97742367</v>
       </c>
       <c r="F63" s="124">
-        <f>+SALDOS!G172+SALDOS!G339+SALDOS!G390+SALDOS!G340</f>
+        <f>+'Distribución por línea'!G172+'Distribución por línea'!G339+'Distribución por línea'!G390+'Distribución por línea'!G340</f>
         <v>1514958.41</v>
       </c>
       <c r="G63" s="16"/>
       <c r="H63" s="19">
-        <f>+SALDOS!G319</f>
+        <f>+'Distribución por línea'!G319</f>
         <v>96227408.59</v>
       </c>
       <c r="I63" s="125"/>
@@ -5746,7 +5725,7 @@
       <c r="F64" s="124"/>
       <c r="G64" s="16"/>
       <c r="H64" s="19">
-        <f>+SALDOS!G244</f>
+        <f>+'Distribución por línea'!G244</f>
         <v>143974.36000000002</v>
       </c>
       <c r="I64" s="125"/>
@@ -5766,8 +5745,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="124">
-        <f>+SALDOS!G478</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G478</f>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="19"/>
@@ -5807,7 +5785,7 @@
         <v>2052084.4000000001</v>
       </c>
       <c r="F67" s="124">
-        <f>+SALDOS!G227</f>
+        <f>+'Distribución por línea'!G227</f>
         <v>2052084.4000000001</v>
       </c>
       <c r="G67" s="16"/>
@@ -5850,8 +5828,7 @@
       <c r="F69" s="124"/>
       <c r="G69" s="16"/>
       <c r="H69" s="19">
-        <f>+SALDOS!G388</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G388</f>
       </c>
       <c r="I69" s="125"/>
       <c r="J69" s="123"/>
@@ -5889,8 +5866,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="124">
-        <f>+SALDOS!G235</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G235</f>
       </c>
       <c r="G71" s="16"/>
       <c r="H71" s="19"/>
@@ -5911,8 +5887,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="124">
-        <f>+SALDOS!G488</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G488</f>
       </c>
       <c r="G72" s="16"/>
       <c r="H72" s="19"/>
@@ -5933,7 +5908,7 @@
         <v>700000</v>
       </c>
       <c r="F73" s="124">
-        <f>+SALDOS!G209</f>
+        <f>+'Distribución por línea'!G209</f>
         <v>700000</v>
       </c>
       <c r="G73" s="16"/>
@@ -5955,7 +5930,7 @@
         <v>4714680.04</v>
       </c>
       <c r="F74" s="19">
-        <f>+SALDOS!G481</f>
+        <f>+'Distribución por línea'!G481</f>
         <v>4714680.04</v>
       </c>
       <c r="G74" s="16"/>
@@ -5977,8 +5952,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="125">
-        <f>+SALDOS!G206</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G206</f>
       </c>
       <c r="G75" s="16"/>
       <c r="H75" s="16"/>
@@ -5999,7 +5973,7 @@
         <v>17921832.18</v>
       </c>
       <c r="F76" s="124">
-        <f>+SALDOS!G435</f>
+        <f>+'Distribución por línea'!G435</f>
         <v>17921832.18</v>
       </c>
       <c r="G76" s="16"/>
@@ -6021,8 +5995,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="124">
-        <f>+SALDOS!G489</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G489</f>
       </c>
       <c r="G77" s="16"/>
       <c r="H77" s="19"/>
@@ -6045,8 +6018,7 @@
       <c r="F78" s="124"/>
       <c r="G78" s="16"/>
       <c r="H78" s="19">
-        <f>+SALDOS!G318</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G318</f>
       </c>
       <c r="I78" s="125"/>
       <c r="J78" s="123"/>
@@ -6067,8 +6039,7 @@
       <c r="F79" s="124"/>
       <c r="G79" s="16"/>
       <c r="H79" s="19">
-        <f>+SALDOS!G486</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G486</f>
       </c>
       <c r="I79" s="125"/>
       <c r="J79" s="123"/>
@@ -6089,7 +6060,7 @@
       <c r="F80" s="124"/>
       <c r="G80" s="16"/>
       <c r="H80" s="19">
-        <f>+SALDOS!G487</f>
+        <f>+'Distribución por línea'!G487</f>
         <v>4150213.41</v>
       </c>
       <c r="I80" s="125"/>
@@ -6109,12 +6080,12 @@
         <v>464005650.22</v>
       </c>
       <c r="F81" s="124">
-        <f>+SALDOS!G170</f>
+        <f>+'Distribución por línea'!G170</f>
         <v>149519366.67000002</v>
       </c>
       <c r="G81" s="16"/>
       <c r="H81" s="19">
-        <f>+SALDOS!G402</f>
+        <f>+'Distribución por línea'!G402</f>
         <v>314486283.55</v>
       </c>
       <c r="I81" s="125"/>
@@ -6134,12 +6105,11 @@
         <v>3799966.7</v>
       </c>
       <c r="F82" s="124">
-        <f>+SALDOS!G282+SALDOS!G198</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G282+'Distribución por línea'!G198</f>
       </c>
       <c r="G82" s="16"/>
       <c r="H82" s="19">
-        <f>+SALDOS!G417</f>
+        <f>+'Distribución por línea'!G417</f>
         <v>3799966.7</v>
       </c>
       <c r="I82" s="125"/>
@@ -6163,8 +6133,7 @@
       </c>
       <c r="G83" s="16"/>
       <c r="H83" s="19">
-        <f>+SALDOS!G149</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G149</f>
       </c>
       <c r="I83" s="125"/>
       <c r="J83" s="123"/>
@@ -6183,8 +6152,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="124">
-        <f>+SALDOS!G264</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G264</f>
       </c>
       <c r="G84" s="16"/>
       <c r="H84" s="19"/>
@@ -6205,8 +6173,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="124">
-        <f>+SALDOS!G385</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G385</f>
       </c>
       <c r="G85" s="16"/>
       <c r="H85" s="19"/>
@@ -6227,8 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="124">
-        <f>+SALDOS!G246</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G246</f>
       </c>
       <c r="G86" s="16"/>
       <c r="H86" s="19"/>
@@ -6249,8 +6215,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="16">
-        <f>+SALDOS!G179</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G179</f>
       </c>
       <c r="G87" s="16"/>
       <c r="H87" s="19"/>
@@ -6273,8 +6238,7 @@
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
       <c r="H88" s="19">
-        <f>+SALDOS!G416</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G416</f>
       </c>
       <c r="I88" s="125"/>
       <c r="J88" s="123"/>
@@ -6293,7 +6257,7 @@
         <v>101483.28</v>
       </c>
       <c r="F89" s="16">
-        <f>+SALDOS!G444</f>
+        <f>+'Distribución por línea'!G444</f>
         <v>101483.28</v>
       </c>
       <c r="G89" s="16"/>
@@ -6317,8 +6281,7 @@
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
       <c r="H90" s="19">
-        <f>+SALDOS!G476</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G476</f>
       </c>
       <c r="I90" s="125"/>
       <c r="J90" s="123"/>
@@ -6337,7 +6300,7 @@
         <v>6840000</v>
       </c>
       <c r="F91" s="16">
-        <f>+SALDOS!G154</f>
+        <f>+'Distribución por línea'!G154</f>
         <v>6840000</v>
       </c>
       <c r="G91" s="16"/>
@@ -6378,7 +6341,7 @@
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
       <c r="H93" s="19">
-        <f>+SALDOS!G490</f>
+        <f>+'Distribución por línea'!G490</f>
         <v>226987</v>
       </c>
       <c r="I93" s="125"/>
@@ -6400,7 +6363,7 @@
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
       <c r="H94" s="19">
-        <f>+SALDOS!G491+SALDOS!G492</f>
+        <f>+'Distribución por línea'!G491+'Distribución por línea'!G492</f>
         <v>914304.7000000001</v>
       </c>
       <c r="I94" s="125"/>
@@ -6420,7 +6383,7 @@
         <v>-3402540.6600000006</v>
       </c>
       <c r="F95" s="16">
-        <f>+SALDOS!G201</f>
+        <f>+'Distribución por línea'!G201</f>
         <v>-3402540.6600000006</v>
       </c>
       <c r="G95" s="16"/>
@@ -6444,8 +6407,7 @@
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
       <c r="H96" s="19">
-        <f>+SALDOS!G495</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G495</f>
       </c>
       <c r="I96" s="125"/>
       <c r="J96" s="123"/>
@@ -6466,8 +6428,7 @@
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
       <c r="H97" s="19">
-        <f>+SALDOS!F493</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!F493</f>
       </c>
       <c r="I97" s="125"/>
       <c r="J97" s="123"/>
@@ -6488,8 +6449,7 @@
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="19">
-        <f>+SALDOS!G498</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G498</f>
       </c>
       <c r="I98" s="125"/>
       <c r="J98" s="123"/>
@@ -6510,8 +6470,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="19">
-        <f>+SALDOS!G500</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G500</f>
       </c>
       <c r="I99" s="125"/>
       <c r="J99" s="123"/>
@@ -6532,8 +6491,7 @@
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="19">
-        <f>+SALDOS!G501</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G501</f>
       </c>
       <c r="I100" s="125"/>
       <c r="J100" s="123"/>
@@ -6554,8 +6512,7 @@
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="19">
-        <f>+SALDOS!G502</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G502</f>
       </c>
       <c r="I101" s="125"/>
       <c r="J101" s="123"/>
@@ -6576,8 +6533,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="19">
-        <f>+SALDOS!G503</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G503</f>
       </c>
       <c r="I102" s="125"/>
       <c r="J102" s="123"/>
@@ -7001,7 +6957,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="104">
-        <f>+SALDOS!G44</f>
+        <f>+'Distribución por línea'!G44</f>
         <v>7137147.140000001</v>
       </c>
       <c r="F15" s="105">
@@ -7019,7 +6975,7 @@
         <v>291287.4099999997</v>
       </c>
       <c r="J15" s="104">
-        <f>-SALDOS!G49</f>
+        <f>-'Distribución por línea'!G49</f>
         <v>3165901.61</v>
       </c>
       <c r="K15" s="107">
@@ -7046,7 +7002,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="104">
-        <f>+SALDOS!G56</f>
+        <f>+'Distribución por línea'!G56</f>
         <v>23184450.990000002</v>
       </c>
       <c r="F16" s="105">
@@ -7064,7 +7020,7 @@
         <v>1854144.9299999997</v>
       </c>
       <c r="J16" s="104">
-        <f>-SALDOS!G57</f>
+        <f>-'Distribución por línea'!G57</f>
         <v>10678252.36</v>
       </c>
       <c r="K16" s="107">
@@ -7091,7 +7047,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="104">
-        <f>+SALDOS!G45</f>
+        <f>+'Distribución por línea'!G45</f>
         <v>2163642.25</v>
       </c>
       <c r="F17" s="105">
@@ -7109,7 +7065,7 @@
         <v>98472.8500000001</v>
       </c>
       <c r="J17" s="104">
-        <f>-SALDOS!G50</f>
+        <f>-'Distribución por línea'!G50</f>
         <v>1513073.78</v>
       </c>
       <c r="K17" s="107">
@@ -7136,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="104">
-        <f>+SALDOS!G46</f>
+        <f>+'Distribución por línea'!G46</f>
         <v>1676263.99</v>
       </c>
       <c r="F18" s="105">
@@ -7153,7 +7109,7 @@
         <v>76152.37</v>
       </c>
       <c r="J18" s="104">
-        <f>-SALDOS!G51</f>
+        <f>-'Distribución por línea'!G51</f>
         <v>787255.48</v>
       </c>
       <c r="K18" s="107">
@@ -7180,7 +7136,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="104">
-        <f>+SALDOS!G47</f>
+        <f>+'Distribución por línea'!G47</f>
         <v>8463010.92</v>
       </c>
       <c r="F19" s="105">
@@ -7197,7 +7153,7 @@
         <v>579227.3799999999</v>
       </c>
       <c r="J19" s="104">
-        <f>-SALDOS!G53</f>
+        <f>-'Distribución por línea'!G53</f>
         <v>4535939.5</v>
       </c>
       <c r="K19" s="107">
@@ -7224,7 +7180,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="104">
-        <f>+SALDOS!G48</f>
+        <f>+'Distribución por línea'!G48</f>
         <v>5117083.33</v>
       </c>
       <c r="F20" s="105">
@@ -7241,7 +7197,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="104">
-        <f>-SALDOS!G54</f>
+        <f>-'Distribución por línea'!G54</f>
         <v>5117083.33</v>
       </c>
       <c r="K20" s="107">
@@ -7268,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="104">
-        <f>+SALDOS!G52</f>
+        <f>+'Distribución por línea'!G52</f>
         <v>20790195.080000002</v>
       </c>
       <c r="F21" s="105">
@@ -7286,7 +7242,7 @@
         <v>1358438.129999999</v>
       </c>
       <c r="J21" s="104">
-        <f>-SALDOS!G55</f>
+        <f>-'Distribución por línea'!G55</f>
         <v>19800111.91</v>
       </c>
       <c r="K21" s="107">
@@ -7313,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="104">
-        <f>+SALDOS!G58</f>
+        <f>+'Distribución por línea'!G58</f>
         <v>1598074.09</v>
       </c>
       <c r="F22" s="105">
@@ -7330,7 +7286,7 @@
         <v>91666.01000000001</v>
       </c>
       <c r="J22" s="104">
-        <f>-SALDOS!G59</f>
+        <f>-'Distribución por línea'!G59</f>
         <v>630796.53</v>
       </c>
       <c r="K22" s="107">
@@ -7631,7 +7587,7 @@
       <c r="E3" s="68"/>
       <c r="F3" s="140"/>
       <c r="G3" s="141">
-        <f>IFERROR(VLOOKUP(C3,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C3,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1500000</v>
       </c>
     </row>
@@ -7647,8 +7603,7 @@
       <c r="E4" s="72"/>
       <c r="F4" s="140"/>
       <c r="G4" s="141">
-        <f>IFERROR(VLOOKUP(C4,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C4,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7663,7 +7618,7 @@
       <c r="E5" s="68"/>
       <c r="F5" s="140"/>
       <c r="G5" s="141">
-        <f>IFERROR(VLOOKUP(C5,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C5,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>11928050.5</v>
       </c>
     </row>
@@ -7679,7 +7634,7 @@
       <c r="E6" s="68"/>
       <c r="F6" s="140"/>
       <c r="G6" s="141">
-        <f>IFERROR(VLOOKUP(C6,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C6,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>123812147.38</v>
       </c>
       <c r="H6" s="142"/>
@@ -7696,8 +7651,7 @@
       <c r="E7" s="68"/>
       <c r="F7" s="140"/>
       <c r="G7" s="141">
-        <f>IFERROR(VLOOKUP(C7,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C7,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H7" s="142"/>
     </row>
@@ -7713,7 +7667,7 @@
       <c r="E8" s="68"/>
       <c r="F8" s="140"/>
       <c r="G8" s="141">
-        <f>IFERROR(VLOOKUP(C8,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C8,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>15375551.48</v>
       </c>
       <c r="H8" s="142"/>
@@ -7730,7 +7684,7 @@
       <c r="E9" s="68"/>
       <c r="F9" s="140"/>
       <c r="G9" s="141">
-        <f>IFERROR(VLOOKUP(C9,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C9,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>7164.12</v>
       </c>
       <c r="H9" s="142"/>
@@ -7747,8 +7701,7 @@
       <c r="E10" s="68"/>
       <c r="F10" s="140"/>
       <c r="G10" s="141">
-        <f>IFERROR(VLOOKUP(C10,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C10,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7763,7 +7716,7 @@
       <c r="E11" s="71"/>
       <c r="F11" s="140"/>
       <c r="G11" s="141">
-        <f>IFERROR(VLOOKUP(C11,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C11,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>8472052.17</v>
       </c>
     </row>
@@ -7779,8 +7732,7 @@
       <c r="E12" s="71"/>
       <c r="F12" s="140"/>
       <c r="G12" s="141">
-        <f>IFERROR(VLOOKUP(C12,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C12,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7791,8 +7743,7 @@
       <c r="E13" s="139"/>
       <c r="F13" s="140"/>
       <c r="G13" s="143">
-        <f>IFERROR(VLOOKUP(C13,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C13,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1" spans="1:11" s="144" customFormat="1" x14ac:dyDescent="0.25">
@@ -7807,8 +7758,7 @@
       <c r="E14" s="147"/>
       <c r="F14" s="140"/>
       <c r="G14" s="143">
-        <f>IFERROR(VLOOKUP(C14,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C14,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H14" s="148"/>
       <c r="I14" s="149"/>
@@ -7827,7 +7777,7 @@
       <c r="E15" s="68"/>
       <c r="F15" s="140"/>
       <c r="G15" s="143">
-        <f>IFERROR(VLOOKUP(C15,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C15,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1673415069.26</v>
       </c>
     </row>
@@ -7843,8 +7793,7 @@
       <c r="E16" s="68"/>
       <c r="F16" s="140"/>
       <c r="G16" s="143">
-        <f>IFERROR(VLOOKUP(C16,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C16,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -7859,7 +7808,7 @@
       <c r="E17" s="71"/>
       <c r="F17" s="140"/>
       <c r="G17" s="143">
-        <f>IFERROR(VLOOKUP(C17,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C17,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1159.02</v>
       </c>
       <c r="H17" s="150"/>
@@ -7876,7 +7825,7 @@
       <c r="E18" s="68"/>
       <c r="F18" s="140"/>
       <c r="G18" s="143">
-        <f>IFERROR(VLOOKUP(C18,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C18,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>7898761.38</v>
       </c>
     </row>
@@ -7892,7 +7841,7 @@
       <c r="E19" s="68"/>
       <c r="F19" s="140"/>
       <c r="G19" s="143">
-        <f>IFERROR(VLOOKUP(C19,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C19,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>53327476.84</v>
       </c>
     </row>
@@ -7908,7 +7857,7 @@
       <c r="E20" s="68"/>
       <c r="F20" s="140"/>
       <c r="G20" s="143">
-        <f>IFERROR(VLOOKUP(C20,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C20,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>528747.09</v>
       </c>
     </row>
@@ -7924,8 +7873,7 @@
       <c r="E21" s="71"/>
       <c r="F21" s="140"/>
       <c r="G21" s="143">
-        <f>IFERROR(VLOOKUP(C21,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C21,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="22" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -7940,7 +7888,7 @@
       <c r="E22" s="68"/>
       <c r="F22" s="140"/>
       <c r="G22" s="143">
-        <f>IFERROR(VLOOKUP(C22,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C22,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>243686.59</v>
       </c>
     </row>
@@ -7956,7 +7904,7 @@
       <c r="E23" s="68"/>
       <c r="F23" s="140"/>
       <c r="G23" s="143">
-        <f>IFERROR(VLOOKUP(C23,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C23,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>203599.05000000002</v>
       </c>
     </row>
@@ -7972,7 +7920,7 @@
       <c r="E24" s="68"/>
       <c r="F24" s="140"/>
       <c r="G24" s="143">
-        <f>IFERROR(VLOOKUP(C24,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C24,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>45551974.83</v>
       </c>
     </row>
@@ -7988,7 +7936,7 @@
       <c r="E25" s="71"/>
       <c r="F25" s="140"/>
       <c r="G25" s="143">
-        <f>IFERROR(VLOOKUP(C25,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C25,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>26028040.72</v>
       </c>
     </row>
@@ -8004,8 +7952,7 @@
       <c r="E26" s="71"/>
       <c r="F26" s="140"/>
       <c r="G26" s="143">
-        <f>IFERROR(VLOOKUP(C26,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C26,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="27" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8020,8 +7967,7 @@
       <c r="E27" s="72"/>
       <c r="F27" s="140"/>
       <c r="G27" s="143">
-        <f>IFERROR(VLOOKUP(C27,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C27,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="28" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8036,8 +7982,7 @@
       <c r="E28" s="72"/>
       <c r="F28" s="140"/>
       <c r="G28" s="143">
-        <f>IFERROR(VLOOKUP(C28,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C28,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="29" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8052,7 +7997,7 @@
       <c r="E29" s="68"/>
       <c r="F29" s="140"/>
       <c r="G29" s="143">
-        <f>IFERROR(VLOOKUP(C29,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C29,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>111962569.93</v>
       </c>
     </row>
@@ -8068,7 +8013,7 @@
       <c r="E30" s="150"/>
       <c r="F30" s="140"/>
       <c r="G30" s="143">
-        <f>IFERROR(VLOOKUP(C30,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C30,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1068.39</v>
       </c>
     </row>
@@ -8084,7 +8029,7 @@
       <c r="E31" s="68"/>
       <c r="F31" s="140"/>
       <c r="G31" s="143">
-        <f>IFERROR(VLOOKUP(C31,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C31,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>5596322.17</v>
       </c>
     </row>
@@ -8100,8 +8045,7 @@
       <c r="E32" s="68"/>
       <c r="F32" s="140"/>
       <c r="G32" s="143">
-        <f>IFERROR(VLOOKUP(C32,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C32,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H32" s="72"/>
     </row>
@@ -8117,8 +8061,7 @@
       <c r="E33" s="72"/>
       <c r="F33" s="140"/>
       <c r="G33" s="143">
-        <f>IFERROR(VLOOKUP(C33,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C33,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="34" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8133,8 +8076,7 @@
       <c r="E34" s="71"/>
       <c r="F34" s="140"/>
       <c r="G34" s="143">
-        <f>IFERROR(VLOOKUP(C34,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C34,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="35" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8149,8 +8091,7 @@
       <c r="E35" s="71"/>
       <c r="F35" s="140"/>
       <c r="G35" s="143">
-        <f>IFERROR(VLOOKUP(C35,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C35,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="36" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8165,8 +8106,7 @@
       <c r="E36" s="72"/>
       <c r="F36" s="140"/>
       <c r="G36" s="143">
-        <f>IFERROR(VLOOKUP(C36,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C36,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="37" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8181,7 +8121,7 @@
       <c r="E37" s="68"/>
       <c r="F37" s="140"/>
       <c r="G37" s="143">
-        <f>IFERROR(VLOOKUP(C37,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C37,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>23499142.66</v>
       </c>
     </row>
@@ -8197,7 +8137,7 @@
       <c r="E38" s="72"/>
       <c r="F38" s="140"/>
       <c r="G38" s="143">
-        <f>IFERROR(VLOOKUP(C38,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C38,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>323000</v>
       </c>
     </row>
@@ -8209,8 +8149,7 @@
       <c r="E39" s="71"/>
       <c r="F39" s="140"/>
       <c r="G39" s="143">
-        <f>IFERROR(VLOOKUP(C39,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C39,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="40" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8225,8 +8164,7 @@
       <c r="E40" s="71"/>
       <c r="F40" s="140"/>
       <c r="G40" s="143">
-        <f>IFERROR(VLOOKUP(C40,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C40,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="41" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -8241,8 +8179,7 @@
       <c r="E41" s="71"/>
       <c r="F41" s="140"/>
       <c r="G41" s="143">
-        <f>IFERROR(VLOOKUP(C41,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C41,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
     </row>
     <row r="42" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8257,7 +8194,7 @@
       <c r="E42" s="68"/>
       <c r="F42" s="140"/>
       <c r="G42" s="143">
-        <f>IFERROR(VLOOKUP(C42,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C42,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>108200</v>
       </c>
       <c r="H42" s="132"/>
@@ -8278,8 +8215,7 @@
       <c r="E43" s="72"/>
       <c r="F43" s="140"/>
       <c r="G43" s="143">
-        <f>IFERROR(VLOOKUP(C43,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C43,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H43" s="132"/>
       <c r="I43" s="134"/>
@@ -8299,7 +8235,7 @@
       <c r="E44" s="155"/>
       <c r="F44" s="156"/>
       <c r="G44" s="157">
-        <f>IFERROR(VLOOKUP(C44,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C44,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>7137147.140000001</v>
       </c>
       <c r="H44" s="75" t="s">
@@ -8318,7 +8254,7 @@
       <c r="E45" s="155"/>
       <c r="F45" s="156"/>
       <c r="G45" s="157">
-        <f>IFERROR(VLOOKUP(C45,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C45,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>2163642.25</v>
       </c>
       <c r="H45" s="75" t="s">
@@ -8337,7 +8273,7 @@
       <c r="E46" s="155"/>
       <c r="F46" s="156"/>
       <c r="G46" s="157">
-        <f>IFERROR(VLOOKUP(C46,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C46,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1676263.99</v>
       </c>
       <c r="H46" s="75" t="s">
@@ -8356,7 +8292,7 @@
       <c r="E47" s="155"/>
       <c r="F47" s="156"/>
       <c r="G47" s="157">
-        <f>IFERROR(VLOOKUP(C47,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C47,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>8463010.92</v>
       </c>
       <c r="H47" s="75" t="s">
@@ -8375,7 +8311,7 @@
       <c r="E48" s="155"/>
       <c r="F48" s="156"/>
       <c r="G48" s="157">
-        <f>IFERROR(VLOOKUP(C48,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C48,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>5117083.33</v>
       </c>
       <c r="H48" s="75" t="s">
@@ -8394,7 +8330,7 @@
       <c r="E49" s="155"/>
       <c r="F49" s="156"/>
       <c r="G49" s="157">
-        <f>IFERROR(VLOOKUP(C49,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C49,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-3165901.61</v>
       </c>
       <c r="H49" s="75" t="s">
@@ -8421,7 +8357,7 @@
       <c r="E50" s="155"/>
       <c r="F50" s="156"/>
       <c r="G50" s="157">
-        <f>IFERROR(VLOOKUP(C50,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C50,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-1513073.78</v>
       </c>
       <c r="H50" s="75" t="s">
@@ -8448,7 +8384,7 @@
       <c r="E51" s="155"/>
       <c r="F51" s="156"/>
       <c r="G51" s="157">
-        <f>IFERROR(VLOOKUP(C51,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C51,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-787255.48</v>
       </c>
       <c r="H51" s="75" t="s">
@@ -8475,7 +8411,7 @@
       <c r="E52" s="155"/>
       <c r="F52" s="156"/>
       <c r="G52" s="157">
-        <f>IFERROR(VLOOKUP(C52,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C52,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>20790195.080000002</v>
       </c>
       <c r="H52" s="75" t="s">
@@ -8494,7 +8430,7 @@
       <c r="E53" s="155"/>
       <c r="F53" s="156"/>
       <c r="G53" s="157">
-        <f>IFERROR(VLOOKUP(C53,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C53,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-4535939.5</v>
       </c>
       <c r="H53" s="75" t="s">
@@ -8521,7 +8457,7 @@
       <c r="E54" s="155"/>
       <c r="F54" s="156"/>
       <c r="G54" s="157">
-        <f>IFERROR(VLOOKUP(C54,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C54,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-5117083.33</v>
       </c>
       <c r="H54" s="75" t="s">
@@ -8548,7 +8484,7 @@
       <c r="E55" s="155"/>
       <c r="F55" s="156"/>
       <c r="G55" s="157">
-        <f>IFERROR(VLOOKUP(C55,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C55,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-19800111.91</v>
       </c>
       <c r="H55" s="75" t="s">
@@ -8575,7 +8511,7 @@
       <c r="E56" s="155"/>
       <c r="F56" s="156"/>
       <c r="G56" s="157">
-        <f>IFERROR(VLOOKUP(C56,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C56,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>23184450.990000002</v>
       </c>
       <c r="H56" s="75" t="s">
@@ -8594,7 +8530,7 @@
       <c r="E57" s="155"/>
       <c r="F57" s="156"/>
       <c r="G57" s="157">
-        <f>IFERROR(VLOOKUP(C57,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C57,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-10678252.36</v>
       </c>
       <c r="H57" s="75" t="s">
@@ -8621,7 +8557,7 @@
       <c r="E58" s="155"/>
       <c r="F58" s="156"/>
       <c r="G58" s="157">
-        <f>IFERROR(VLOOKUP(C58,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C58,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>1598074.09</v>
       </c>
       <c r="H58" s="75" t="s">
@@ -8640,7 +8576,7 @@
       <c r="E59" s="155"/>
       <c r="F59" s="156"/>
       <c r="G59" s="157">
-        <f>IFERROR(VLOOKUP(C59,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C59,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>-630796.53</v>
       </c>
       <c r="H59" s="75" t="s">
@@ -8669,7 +8605,7 @@
       <c r="E60" s="68"/>
       <c r="F60" s="140"/>
       <c r="G60" s="143">
-        <f>IFERROR(VLOOKUP(C60,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C60,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>5439067</v>
       </c>
       <c r="H60" s="74"/>
@@ -8690,7 +8626,7 @@
       <c r="E61" s="68"/>
       <c r="F61" s="140"/>
       <c r="G61" s="143">
-        <f>IFERROR(VLOOKUP(C61,Hoja1!$A$2:$E$513,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(C61,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
         <v>32772165</v>
       </c>
       <c r="H61" s="74"/>
@@ -8714,8 +8650,7 @@
       <c r="G62" s="143"/>
       <c r="H62" s="74"/>
       <c r="I62" s="159">
-        <f>+Hoja1!E61-SALDOS!I61</f>
-        <v>0</v>
+        <f>+'Balance de sumas y saldos'!E61-'Distribución por línea'!I61</f>
       </c>
       <c r="J62" s="142" t="s">
         <v>381</v>
@@ -10134,8 +10069,7 @@
       <c r="E144" s="71"/>
       <c r="F144" s="140"/>
       <c r="G144" s="143">
-        <f>IFERROR(VLOOKUP(C144,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C144,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H144" s="68"/>
       <c r="I144" s="134">
@@ -10156,8 +10090,7 @@
       <c r="E145" s="170"/>
       <c r="F145" s="171"/>
       <c r="G145" s="184">
-        <f>IFERROR(VLOOKUP(C145,Hoja1!$A$2:$E$513,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(C145,'Balance de sumas y saldos'!$A$2:$E$513,5,FALSE),)</f>
       </c>
       <c r="H145" s="185"/>
       <c r="I145" s="174"/>
@@ -10261,8 +10194,7 @@
       </c>
       <c r="E152" s="72"/>
       <c r="F152" s="140">
-        <f>IFERROR(VLOOKUP(D152,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D152,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G152" s="138">
         <f>+F152</f>
@@ -10278,8 +10210,7 @@
       </c>
       <c r="E153" s="72"/>
       <c r="F153" s="140">
-        <f>IFERROR(VLOOKUP(D153,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D153,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G153" s="138">
         <f>+F153</f>
@@ -10295,7 +10226,7 @@
       </c>
       <c r="E154" s="72"/>
       <c r="F154" s="140">
-        <f>IFERROR(VLOOKUP(D154,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D154,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>6840000</v>
       </c>
       <c r="G154" s="138">
@@ -10315,8 +10246,7 @@
       </c>
       <c r="E155" s="71"/>
       <c r="F155" s="140">
-        <f>IFERROR(VLOOKUP(D155,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D155,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G155" s="138">
         <f>SUM(F156:F159)</f>
@@ -10332,8 +10262,7 @@
         <v>477</v>
       </c>
       <c r="F156" s="140">
-        <f>IFERROR(VLOOKUP(E156,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E156,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G156" s="138"/>
       <c r="H156" s="72"/>
@@ -10348,8 +10277,7 @@
         <v>478</v>
       </c>
       <c r="F157" s="140">
-        <f>IFERROR(VLOOKUP(E157,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E157,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G157" s="138"/>
       <c r="H157" s="72"/>
@@ -10364,8 +10292,7 @@
         <v>479</v>
       </c>
       <c r="F158" s="140">
-        <f>IFERROR(VLOOKUP(E158,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E158,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G158" s="138"/>
       <c r="H158" s="72"/>
@@ -10380,8 +10307,7 @@
         <v>480</v>
       </c>
       <c r="F159" s="140">
-        <f>IFERROR(VLOOKUP(E159,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E159,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G159" s="138"/>
       <c r="H159" s="72"/>
@@ -10410,8 +10336,7 @@
         <v>482</v>
       </c>
       <c r="F161" s="140">
-        <f>IFERROR(VLOOKUP(E161,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E161,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G161" s="138"/>
     </row>
@@ -10424,7 +10349,7 @@
         <v>483</v>
       </c>
       <c r="F162" s="140">
-        <f>IFERROR(VLOOKUP(E162,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E162,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>85328616.3</v>
       </c>
       <c r="G162" s="138"/>
@@ -10438,7 +10363,7 @@
         <v>484</v>
       </c>
       <c r="F163" s="140">
-        <f>IFERROR(VLOOKUP(E163,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E163,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>19677599.580000002</v>
       </c>
       <c r="G163" s="138"/>
@@ -10452,7 +10377,7 @@
         <v>485</v>
       </c>
       <c r="F164" s="140">
-        <f>IFERROR(VLOOKUP(E164,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E164,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>71304554.81</v>
       </c>
       <c r="G164" s="138"/>
@@ -10466,8 +10391,7 @@
         <v>486</v>
       </c>
       <c r="F165" s="140">
-        <f>IFERROR(VLOOKUP(E165,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E165,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G165" s="138"/>
     </row>
@@ -10480,8 +10404,7 @@
         <v>487</v>
       </c>
       <c r="F166" s="140">
-        <f>IFERROR(VLOOKUP(E166,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E166,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G166" s="138"/>
     </row>
@@ -10494,8 +10417,7 @@
         <v>488</v>
       </c>
       <c r="F167" s="140">
-        <f>IFERROR(VLOOKUP(E167,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E167,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G167" s="138"/>
     </row>
@@ -10508,7 +10430,7 @@
         <v>489</v>
       </c>
       <c r="F168" s="140">
-        <f>IFERROR(VLOOKUP(E168,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E168,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>4620000</v>
       </c>
       <c r="G168" s="138"/>
@@ -10522,7 +10444,7 @@
       </c>
       <c r="E169" s="188"/>
       <c r="F169" s="140">
-        <f>IFERROR(VLOOKUP(D169,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D169,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>13001275.15</v>
       </c>
       <c r="G169" s="187">
@@ -10540,7 +10462,7 @@
       </c>
       <c r="E170" s="188"/>
       <c r="F170" s="140">
-        <f>IFERROR(VLOOKUP(D170,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D170,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>149519366.67000002</v>
       </c>
       <c r="G170" s="187">
@@ -10557,7 +10479,7 @@
       </c>
       <c r="E171" s="188"/>
       <c r="F171" s="140">
-        <f>IFERROR(VLOOKUP(D171,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D171,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>14820317.13</v>
       </c>
       <c r="G171" s="187">
@@ -10594,7 +10516,7 @@
         <v>494</v>
       </c>
       <c r="F173" s="140">
-        <f>IFERROR(VLOOKUP(E173,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E173,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1504468.41</v>
       </c>
       <c r="G173" s="138"/>
@@ -10608,8 +10530,7 @@
         <v>495</v>
       </c>
       <c r="F174" s="140">
-        <f>IFERROR(VLOOKUP(E174,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E174,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G174" s="138"/>
     </row>
@@ -10622,7 +10543,7 @@
         <v>496</v>
       </c>
       <c r="F175" s="140">
-        <f>IFERROR(VLOOKUP(E175,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E175,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>10490</v>
       </c>
       <c r="G175" s="138"/>
@@ -10636,8 +10557,7 @@
         <v>497</v>
       </c>
       <c r="F176" s="140">
-        <f>IFERROR(VLOOKUP(E176,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E176,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G176" s="138"/>
     </row>
@@ -10650,8 +10570,7 @@
         <v>498</v>
       </c>
       <c r="F177" s="140">
-        <f>IFERROR(VLOOKUP(E177,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E177,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G177" s="138"/>
     </row>
@@ -10664,8 +10583,7 @@
         <v>499</v>
       </c>
       <c r="F178" s="140">
-        <f>IFERROR(VLOOKUP(E178,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E178,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G178" s="138"/>
     </row>
@@ -10678,8 +10596,7 @@
       </c>
       <c r="E179" s="71"/>
       <c r="F179" s="140">
-        <f>IFERROR(VLOOKUP(D179,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D179,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G179" s="138">
         <f>+F179</f>
@@ -10709,8 +10626,7 @@
         <v>502</v>
       </c>
       <c r="F181" s="140">
-        <f>IFERROR(VLOOKUP(E181,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E181,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G181" s="138"/>
     </row>
@@ -10723,7 +10639,7 @@
         <v>503</v>
       </c>
       <c r="F182" s="140">
-        <f>IFERROR(VLOOKUP(E182,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E182,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>5017041.88</v>
       </c>
       <c r="G182" s="138"/>
@@ -10737,8 +10653,7 @@
         <v>504</v>
       </c>
       <c r="F183" s="140">
-        <f>IFERROR(VLOOKUP(E183,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E183,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G183" s="138"/>
     </row>
@@ -10751,7 +10666,7 @@
         <v>505</v>
       </c>
       <c r="F184" s="140">
-        <f>IFERROR(VLOOKUP(E184,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E184,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>250000</v>
       </c>
       <c r="G184" s="138"/>
@@ -10767,8 +10682,7 @@
         <v>506</v>
       </c>
       <c r="F185" s="140">
-        <f>IFERROR(VLOOKUP(E185,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E185,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G185" s="138"/>
       <c r="H185" s="72"/>
@@ -10810,7 +10724,7 @@
         <v>509</v>
       </c>
       <c r="F188" s="140">
-        <f>IFERROR(VLOOKUP(E188,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E188,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>30000</v>
       </c>
       <c r="G188" s="138">
@@ -10843,7 +10757,7 @@
         <v>511</v>
       </c>
       <c r="F190" s="140">
-        <f>IFERROR(VLOOKUP(E190,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E190,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>9586509.540000001</v>
       </c>
       <c r="G190" s="138"/>
@@ -10857,8 +10771,7 @@
         <v>512</v>
       </c>
       <c r="F191" s="140">
-        <f>IFERROR(VLOOKUP(E191,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E191,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G191" s="138"/>
     </row>
@@ -10871,7 +10784,7 @@
         <v>513</v>
       </c>
       <c r="F192" s="140">
-        <f>IFERROR(VLOOKUP(E192,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E192,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1511583.34</v>
       </c>
       <c r="G192" s="138"/>
@@ -10885,8 +10798,7 @@
         <v>514</v>
       </c>
       <c r="F193" s="140">
-        <f>IFERROR(VLOOKUP(E193,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E193,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G193" s="138"/>
     </row>
@@ -10899,8 +10811,7 @@
         <v>515</v>
       </c>
       <c r="F194" s="140">
-        <f>IFERROR(VLOOKUP(E194,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E194,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G194" s="138"/>
     </row>
@@ -10913,8 +10824,7 @@
         <v>516</v>
       </c>
       <c r="F195" s="140">
-        <f>IFERROR(VLOOKUP(E195,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E195,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G195" s="138"/>
     </row>
@@ -10927,8 +10837,7 @@
         <v>517</v>
       </c>
       <c r="F196" s="140">
-        <f>IFERROR(VLOOKUP(E196,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E196,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G196" s="138"/>
     </row>
@@ -10941,8 +10850,7 @@
         <v>518</v>
       </c>
       <c r="F197" s="140">
-        <f>IFERROR(VLOOKUP(E197,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E197,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G197" s="138"/>
     </row>
@@ -10957,8 +10865,7 @@
         <v>520</v>
       </c>
       <c r="F198" s="140">
-        <f>IFERROR(VLOOKUP(E198,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E198,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G198" s="138">
         <f>+F198+F199+F200</f>
@@ -10974,8 +10881,7 @@
         <v>521</v>
       </c>
       <c r="F199" s="140">
-        <f>IFERROR(VLOOKUP(E199,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E199,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G199" s="138"/>
       <c r="H199" s="72"/>
@@ -10990,8 +10896,7 @@
         <v>522</v>
       </c>
       <c r="F200" s="140">
-        <f>IFERROR(VLOOKUP(E200,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E200,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G200" s="138"/>
       <c r="H200" s="72"/>
@@ -11008,7 +10913,7 @@
         <v>524</v>
       </c>
       <c r="F201" s="140">
-        <f>IFERROR(VLOOKUP(E201,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E201,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>-6355001.390000001</v>
       </c>
       <c r="G201" s="187">
@@ -11027,7 +10932,7 @@
         <v>525</v>
       </c>
       <c r="F202" s="140">
-        <f>IFERROR(VLOOKUP(E202,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E202,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>2952460.73</v>
       </c>
       <c r="G202" s="138"/>
@@ -11066,7 +10971,7 @@
         <v>528</v>
       </c>
       <c r="F204" s="140">
-        <f>IFERROR(VLOOKUP(E204,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E204,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>4349389.08</v>
       </c>
       <c r="G204" s="187">
@@ -11085,8 +10990,7 @@
         <v>527</v>
       </c>
       <c r="F205" s="140">
-        <f>IFERROR(VLOOKUP(E205,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E205,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G205" s="138"/>
     </row>
@@ -11113,8 +11017,7 @@
         <v>530</v>
       </c>
       <c r="F207" s="140">
-        <f>IFERROR(VLOOKUP(E207,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E207,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G207" s="138"/>
     </row>
@@ -11127,8 +11030,7 @@
         <v>531</v>
       </c>
       <c r="F208" s="140">
-        <f>IFERROR(VLOOKUP(E208,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E208,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G208" s="138"/>
     </row>
@@ -11155,8 +11057,7 @@
         <v>533</v>
       </c>
       <c r="F210" s="140">
-        <f>IFERROR(VLOOKUP(E210,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E210,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G210" s="138"/>
     </row>
@@ -11169,7 +11070,7 @@
         <v>534</v>
       </c>
       <c r="F211" s="140">
-        <f>IFERROR(VLOOKUP(E211,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E211,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>700000</v>
       </c>
       <c r="G211" s="138"/>
@@ -11185,8 +11086,7 @@
         <v>535</v>
       </c>
       <c r="F212" s="140">
-        <f>IFERROR(VLOOKUP(E212,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E212,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G212" s="138"/>
       <c r="H212" s="72"/>
@@ -11201,8 +11101,7 @@
         <v>536</v>
       </c>
       <c r="F213" s="140">
-        <f>IFERROR(VLOOKUP(E213,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E213,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G213" s="138"/>
       <c r="H213" s="72"/>
@@ -11232,7 +11131,7 @@
         <v>538</v>
       </c>
       <c r="F215" s="140">
-        <f>IFERROR(VLOOKUP(E215,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E215,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>332121.43</v>
       </c>
       <c r="G215" s="138"/>
@@ -11247,8 +11146,7 @@
         <v>539</v>
       </c>
       <c r="F216" s="140">
-        <f>IFERROR(VLOOKUP(E216,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E216,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G216" s="138"/>
       <c r="H216" s="150"/>
@@ -11262,8 +11160,7 @@
         <v>540</v>
       </c>
       <c r="F217" s="140">
-        <f>IFERROR(VLOOKUP(E217,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E217,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G217" s="138"/>
       <c r="H217" s="150"/>
@@ -11298,8 +11195,7 @@
         <v>542</v>
       </c>
       <c r="F219" s="140">
-        <f>IFERROR(VLOOKUP(E219,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E219,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G219" s="138"/>
     </row>
@@ -11312,7 +11208,7 @@
         <v>543</v>
       </c>
       <c r="F220" s="140">
-        <f>IFERROR(VLOOKUP(E220,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E220,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>3946013.02</v>
       </c>
       <c r="G220" s="138"/>
@@ -11326,8 +11222,7 @@
         <v>544</v>
       </c>
       <c r="F221" s="140">
-        <f>IFERROR(VLOOKUP(E221,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E221,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G221" s="138"/>
     </row>
@@ -11340,7 +11235,7 @@
         <v>545</v>
       </c>
       <c r="F222" s="140">
-        <f>IFERROR(VLOOKUP(E222,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E222,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1836290.04</v>
       </c>
       <c r="G222" s="138"/>
@@ -11354,8 +11249,7 @@
         <v>546</v>
       </c>
       <c r="F223" s="140">
-        <f>IFERROR(VLOOKUP(E223,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E223,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G223" s="138"/>
     </row>
@@ -11368,7 +11262,7 @@
         <v>547</v>
       </c>
       <c r="F224" s="140">
-        <f>IFERROR(VLOOKUP(E224,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E224,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>181818.18</v>
       </c>
       <c r="G224" s="138"/>
@@ -11384,8 +11278,7 @@
         <v>548</v>
       </c>
       <c r="F225" s="140">
-        <f>IFERROR(VLOOKUP(E225,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E225,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G225" s="138"/>
       <c r="H225" s="72"/>
@@ -11413,7 +11306,7 @@
         <v>550</v>
       </c>
       <c r="F227" s="140">
-        <f>IFERROR(VLOOKUP(E227,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E227,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>2052084.4000000001</v>
       </c>
       <c r="G227" s="187">
@@ -11432,8 +11325,7 @@
         <v>551</v>
       </c>
       <c r="F228" s="140">
-        <f>IFERROR(VLOOKUP(E228,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E228,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G228" s="138"/>
       <c r="H228" s="72"/>
@@ -11451,8 +11343,7 @@
         <v>552</v>
       </c>
       <c r="F229" s="140">
-        <f>IFERROR(VLOOKUP(E229,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E229,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G229" s="138"/>
       <c r="H229" s="72"/>
@@ -11486,7 +11377,7 @@
         <v>554</v>
       </c>
       <c r="F231" s="140">
-        <f>IFERROR(VLOOKUP(E231,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E231,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>39000</v>
       </c>
       <c r="G231" s="138">
@@ -11503,8 +11394,7 @@
         <v>555</v>
       </c>
       <c r="F232" s="140">
-        <f>IFERROR(VLOOKUP(E232,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E232,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G232" s="138"/>
     </row>
@@ -11547,8 +11437,7 @@
         <v>559</v>
       </c>
       <c r="F235" s="140">
-        <f>IFERROR(VLOOKUP(E235,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E235,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G235" s="138">
         <f>+SUM(F235:F238)</f>
@@ -11566,8 +11455,7 @@
         <v>560</v>
       </c>
       <c r="F236" s="140">
-        <f>IFERROR(VLOOKUP(E236,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E236,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G236" s="138"/>
       <c r="H236" s="72"/>
@@ -11582,8 +11470,7 @@
         <v>561</v>
       </c>
       <c r="F237" s="140">
-        <f>IFERROR(VLOOKUP(E237,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E237,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G237" s="138"/>
       <c r="H237" s="72"/>
@@ -11596,8 +11483,7 @@
       <c r="D238" s="71"/>
       <c r="E238" s="72"/>
       <c r="F238" s="140">
-        <f>IFERROR(VLOOKUP(E238,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E238,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G238" s="138"/>
       <c r="H238" s="72"/>
@@ -11628,8 +11514,7 @@
         <v>564</v>
       </c>
       <c r="F240" s="140">
-        <f>IFERROR(VLOOKUP(E240,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E240,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G240" s="138">
         <f>SUM(F240:F243)</f>
@@ -11645,8 +11530,7 @@
         <v>565</v>
       </c>
       <c r="F241" s="140">
-        <f>IFERROR(VLOOKUP(E241,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E241,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G241" s="138"/>
     </row>
@@ -11659,8 +11543,7 @@
         <v>566</v>
       </c>
       <c r="F242" s="140">
-        <f>IFERROR(VLOOKUP(E242,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E242,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G242" s="138"/>
     </row>
@@ -11673,8 +11556,7 @@
         <v>567</v>
       </c>
       <c r="F243" s="140">
-        <f>IFERROR(VLOOKUP(E243,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E243,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G243" s="138"/>
     </row>
@@ -11689,7 +11571,7 @@
         <v>569</v>
       </c>
       <c r="F244" s="140">
-        <f>IFERROR(VLOOKUP(E244,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E244,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>143974.36000000002</v>
       </c>
       <c r="G244" s="187">
@@ -11708,8 +11590,7 @@
         <v>570</v>
       </c>
       <c r="F245" s="140">
-        <f>IFERROR(VLOOKUP(E245,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E245,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G245" s="138"/>
       <c r="H245" s="72"/>
@@ -11740,8 +11621,7 @@
         <v>573</v>
       </c>
       <c r="F247" s="140">
-        <f>IFERROR(VLOOKUP(E247,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E247,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G247" s="187">
         <f>SUM(F247:F256)</f>
@@ -11757,8 +11637,7 @@
         <v>574</v>
       </c>
       <c r="F248" s="140">
-        <f>IFERROR(VLOOKUP(E248,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E248,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G248" s="138"/>
     </row>
@@ -11771,7 +11650,7 @@
         <v>575</v>
       </c>
       <c r="F249" s="140">
-        <f>IFERROR(VLOOKUP(E249,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E249,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>98618.72</v>
       </c>
       <c r="G249" s="138"/>
@@ -11785,8 +11664,7 @@
         <v>576</v>
       </c>
       <c r="F250" s="140">
-        <f>IFERROR(VLOOKUP(E250,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E250,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G250" s="138"/>
     </row>
@@ -11799,7 +11677,7 @@
         <v>577</v>
       </c>
       <c r="F251" s="140">
-        <f>IFERROR(VLOOKUP(E251,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E251,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>50644.39</v>
       </c>
       <c r="G251" s="138"/>
@@ -11813,8 +11691,7 @@
         <v>578</v>
       </c>
       <c r="F252" s="140">
-        <f>IFERROR(VLOOKUP(E252,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E252,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G252" s="138"/>
     </row>
@@ -11827,8 +11704,7 @@
         <v>579</v>
       </c>
       <c r="F253" s="140">
-        <f>IFERROR(VLOOKUP(E253,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E253,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G253" s="138"/>
     </row>
@@ -11841,8 +11717,7 @@
         <v>580</v>
       </c>
       <c r="F254" s="140">
-        <f>IFERROR(VLOOKUP(E254,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E254,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G254" s="138"/>
       <c r="H254" s="72"/>
@@ -11857,8 +11732,7 @@
         <v>581</v>
       </c>
       <c r="F255" s="140">
-        <f>IFERROR(VLOOKUP(E255,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E255,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G255" s="138"/>
       <c r="H255" s="72"/>
@@ -11873,8 +11747,7 @@
         <v>582</v>
       </c>
       <c r="F256" s="140">
-        <f>IFERROR(VLOOKUP(E256,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E256,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G256" s="138"/>
       <c r="H256" s="72"/>
@@ -11917,8 +11790,7 @@
         <v>585</v>
       </c>
       <c r="F259" s="140">
-        <f>IFERROR(VLOOKUP(E259,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E259,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G259" s="138"/>
     </row>
@@ -11931,8 +11803,7 @@
         <v>586</v>
       </c>
       <c r="F260" s="140">
-        <f>IFERROR(VLOOKUP(E260,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E260,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G260" s="138"/>
     </row>
@@ -11945,8 +11816,7 @@
         <v>587</v>
       </c>
       <c r="F261" s="140">
-        <f>IFERROR(VLOOKUP(E261,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E261,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G261" s="138"/>
     </row>
@@ -11959,8 +11829,7 @@
         <v>588</v>
       </c>
       <c r="F262" s="140">
-        <f>IFERROR(VLOOKUP(E262,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E262,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G262" s="138"/>
     </row>
@@ -11973,8 +11842,7 @@
         <v>589</v>
       </c>
       <c r="F263" s="140">
-        <f>IFERROR(VLOOKUP(E263,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E263,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G263" s="138"/>
     </row>
@@ -12007,8 +11875,7 @@
         <v>592</v>
       </c>
       <c r="F265" s="140">
-        <f>IFERROR(VLOOKUP(E265,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E265,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G265" s="187">
         <f>SUM(F265:F269)</f>
@@ -12027,7 +11894,7 @@
         <v>593</v>
       </c>
       <c r="F266" s="140">
-        <f>IFERROR(VLOOKUP(E266,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E266,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>11050897.370000001</v>
       </c>
       <c r="G266" s="138"/>
@@ -12044,7 +11911,7 @@
         <v>594</v>
       </c>
       <c r="F267" s="140">
-        <f>IFERROR(VLOOKUP(E267,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E267,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>78804</v>
       </c>
       <c r="G267" s="138"/>
@@ -12061,8 +11928,7 @@
         <v>595</v>
       </c>
       <c r="F268" s="140">
-        <f>IFERROR(VLOOKUP(E268,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E268,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G268" s="138"/>
       <c r="H268" s="132"/>
@@ -12078,8 +11944,7 @@
         <v>596</v>
       </c>
       <c r="F269" s="140">
-        <f>IFERROR(VLOOKUP(E269,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E269,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G269" s="138"/>
       <c r="H269" s="132"/>
@@ -12113,8 +11978,7 @@
         <v>598</v>
       </c>
       <c r="F271" s="140">
-        <f>IFERROR(VLOOKUP(E271,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E271,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G271" s="138"/>
       <c r="H271" s="68"/>
@@ -12131,7 +11995,7 @@
         <v>599</v>
       </c>
       <c r="F272" s="140">
-        <f>IFERROR(VLOOKUP(E272,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E272,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>25426948.26</v>
       </c>
       <c r="G272" s="138"/>
@@ -12151,7 +12015,7 @@
         <v>601</v>
       </c>
       <c r="F273" s="140">
-        <f>IFERROR(VLOOKUP(E273,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E273,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>739403</v>
       </c>
       <c r="G273" s="138">
@@ -12168,7 +12032,7 @@
         <v>602</v>
       </c>
       <c r="F274" s="140">
-        <f>IFERROR(VLOOKUP(E274,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E274,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1145403.58</v>
       </c>
       <c r="G274" s="138"/>
@@ -12182,8 +12046,7 @@
         <v>603</v>
       </c>
       <c r="F275" s="140">
-        <f>IFERROR(VLOOKUP(E275,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E275,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G275" s="138"/>
     </row>
@@ -12196,8 +12059,7 @@
         <v>604</v>
       </c>
       <c r="F276" s="140">
-        <f>IFERROR(VLOOKUP(E276,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E276,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G276" s="138"/>
     </row>
@@ -12210,8 +12072,7 @@
         <v>605</v>
       </c>
       <c r="F277" s="140">
-        <f>IFERROR(VLOOKUP(E277,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E277,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G277" s="138"/>
     </row>
@@ -12224,8 +12085,7 @@
         <v>606</v>
       </c>
       <c r="F278" s="140">
-        <f>IFERROR(VLOOKUP(E278,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E278,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G278" s="138"/>
     </row>
@@ -12238,8 +12098,7 @@
         <v>607</v>
       </c>
       <c r="F279" s="140">
-        <f>IFERROR(VLOOKUP(E279,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E279,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G279" s="138"/>
     </row>
@@ -12252,8 +12111,7 @@
         <v>608</v>
       </c>
       <c r="F280" s="140">
-        <f>IFERROR(VLOOKUP(E280,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E280,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G280" s="138"/>
     </row>
@@ -12268,7 +12126,7 @@
         <v>609</v>
       </c>
       <c r="F281" s="193">
-        <f>+Hoja1!E243+Hoja1!E244</f>
+        <f>+'Balance de sumas y saldos'!E243+'Balance de sumas y saldos'!E244</f>
         <v>65017428.77</v>
       </c>
       <c r="G281" s="194">
@@ -12291,8 +12149,7 @@
       </c>
       <c r="E282" s="71"/>
       <c r="F282" s="140">
-        <f>IFERROR(VLOOKUP(E282,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E282,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G282" s="138">
         <f>+F282</f>
@@ -12308,8 +12165,7 @@
       </c>
       <c r="E283" s="71"/>
       <c r="F283" s="140">
-        <f>IFERROR(VLOOKUP(D283,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D283,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G283" s="138">
         <f>+F283</f>
@@ -12325,8 +12181,7 @@
       </c>
       <c r="E284" s="139"/>
       <c r="F284" s="140">
-        <f>IFERROR(VLOOKUP(D284,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D284,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G284" s="138">
         <f>+F284</f>
@@ -12357,8 +12212,7 @@
         <v>615</v>
       </c>
       <c r="F286" s="140">
-        <f>IFERROR(VLOOKUP(E286,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E286,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G286" s="138"/>
     </row>
@@ -12371,8 +12225,7 @@
         <v>616</v>
       </c>
       <c r="F287" s="140">
-        <f>IFERROR(VLOOKUP(E287,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E287,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G287" s="138"/>
     </row>
@@ -12385,8 +12238,7 @@
         <v>617</v>
       </c>
       <c r="F288" s="140">
-        <f>IFERROR(VLOOKUP(E288,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E288,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G288" s="138"/>
     </row>
@@ -12399,8 +12251,7 @@
         <v>618</v>
       </c>
       <c r="F289" s="140">
-        <f>IFERROR(VLOOKUP(E289,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E289,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G289" s="138"/>
     </row>
@@ -12413,8 +12264,7 @@
         <v>619</v>
       </c>
       <c r="F290" s="140">
-        <f>IFERROR(VLOOKUP(E290,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E290,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G290" s="138"/>
     </row>
@@ -12427,8 +12277,7 @@
         <v>620</v>
       </c>
       <c r="F291" s="140">
-        <f>IFERROR(VLOOKUP(E291,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E291,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G291" s="138"/>
     </row>
@@ -12441,8 +12290,7 @@
         <v>621</v>
       </c>
       <c r="F292" s="140">
-        <f>IFERROR(VLOOKUP(E292,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E292,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G292" s="138"/>
     </row>
@@ -12455,8 +12303,7 @@
         <v>622</v>
       </c>
       <c r="F293" s="140">
-        <f>IFERROR(VLOOKUP(E293,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E293,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G293" s="138"/>
       <c r="H293" s="142"/>
@@ -12489,8 +12336,7 @@
         <v>625</v>
       </c>
       <c r="F295" s="140">
-        <f>IFERROR(VLOOKUP(E295,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E295,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G295" s="187">
         <f>SUM(F295:F302)</f>
@@ -12511,7 +12357,7 @@
         <v>626</v>
       </c>
       <c r="F296" s="140">
-        <f>IFERROR(VLOOKUP(E296,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E296,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1004059.51</v>
       </c>
       <c r="G296" s="138"/>
@@ -12525,7 +12371,7 @@
         <v>627</v>
       </c>
       <c r="F297" s="140">
-        <f>IFERROR(VLOOKUP(E297,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E297,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>95868</v>
       </c>
       <c r="G297" s="138"/>
@@ -12539,8 +12385,7 @@
         <v>628</v>
       </c>
       <c r="F298" s="140">
-        <f>IFERROR(VLOOKUP(E298,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E298,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G298" s="138"/>
       <c r="H298" s="132"/>
@@ -12559,8 +12404,7 @@
         <v>629</v>
       </c>
       <c r="F299" s="140">
-        <f>IFERROR(VLOOKUP(E299,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E299,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G299" s="138"/>
       <c r="H299" s="132"/>
@@ -12579,8 +12423,7 @@
         <v>630</v>
       </c>
       <c r="F300" s="140">
-        <f>IFERROR(VLOOKUP(E300,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E300,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G300" s="138"/>
       <c r="H300" s="132"/>
@@ -12599,8 +12442,7 @@
         <v>631</v>
       </c>
       <c r="F301" s="140">
-        <f>IFERROR(VLOOKUP(E301,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E301,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G301" s="138"/>
       <c r="H301" s="132"/>
@@ -12619,8 +12461,7 @@
         <v>632</v>
       </c>
       <c r="F302" s="140">
-        <f>IFERROR(VLOOKUP(E302,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E302,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G302" s="138"/>
       <c r="H302" s="132"/>
@@ -12653,8 +12494,7 @@
         <v>634</v>
       </c>
       <c r="F304" s="140">
-        <f>IFERROR(VLOOKUP(E304,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E304,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G304" s="138"/>
     </row>
@@ -12667,7 +12507,7 @@
         <v>635</v>
       </c>
       <c r="F305" s="140">
-        <f>IFERROR(VLOOKUP(E305,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E305,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>189946.28</v>
       </c>
       <c r="G305" s="138"/>
@@ -12681,8 +12521,7 @@
         <v>636</v>
       </c>
       <c r="F306" s="140">
-        <f>IFERROR(VLOOKUP(E306,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E306,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G306" s="138"/>
     </row>
@@ -12695,8 +12534,7 @@
       </c>
       <c r="E307" s="188"/>
       <c r="F307" s="140">
-        <f>IFERROR(VLOOKUP(E307,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E307,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G307" s="138">
         <f>+F308</f>
@@ -12712,8 +12550,7 @@
         <v>638</v>
       </c>
       <c r="F308" s="140">
-        <f>IFERROR(VLOOKUP(E308,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E308,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G308" s="138"/>
       <c r="H308" s="72"/>
@@ -12730,8 +12567,7 @@
         <v>639</v>
       </c>
       <c r="F309" s="140">
-        <f>IFERROR(VLOOKUP(E309,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E309,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G309" s="138">
         <f>+F309</f>
@@ -12751,7 +12587,7 @@
         <v>640</v>
       </c>
       <c r="F310" s="140">
-        <f>IFERROR(VLOOKUP(E310,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E310,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>48607846.6</v>
       </c>
       <c r="G310" s="187">
@@ -12772,8 +12608,7 @@
         <v>642</v>
       </c>
       <c r="F311" s="140">
-        <f>IFERROR(VLOOKUP(E311,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E311,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G311" s="138">
         <f>+F311</f>
@@ -12789,8 +12624,7 @@
       </c>
       <c r="E312" s="188"/>
       <c r="F312" s="140">
-        <f>IFERROR(VLOOKUP(E312,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E312,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G312" s="138">
         <f>SUM(F312:F314)</f>
@@ -12806,8 +12640,7 @@
         <v>644</v>
       </c>
       <c r="F313" s="140">
-        <f>IFERROR(VLOOKUP(E313,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E313,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G313" s="138"/>
     </row>
@@ -12820,8 +12653,7 @@
         <v>645</v>
       </c>
       <c r="F314" s="140">
-        <f>IFERROR(VLOOKUP(E314,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E314,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G314" s="138"/>
     </row>
@@ -12834,8 +12666,7 @@
       </c>
       <c r="E315" s="71"/>
       <c r="F315" s="140">
-        <f>IFERROR(VLOOKUP(E315,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E315,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G315" s="138">
         <f>+F315</f>
@@ -12853,8 +12684,7 @@
         <v>648</v>
       </c>
       <c r="F316" s="140">
-        <f>IFERROR(VLOOKUP(E316,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E316,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G316" s="187">
         <f>+F316+F317</f>
@@ -12870,7 +12700,7 @@
         <v>649</v>
       </c>
       <c r="F317" s="140">
-        <f>IFERROR(VLOOKUP(E317,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E317,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>18512.4</v>
       </c>
       <c r="G317" s="138"/>
@@ -12884,8 +12714,7 @@
       </c>
       <c r="E318" s="72"/>
       <c r="F318" s="140">
-        <f>IFERROR(VLOOKUP(E318,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E318,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G318" s="138">
         <f>+F318</f>
@@ -12917,7 +12746,7 @@
         <v>652</v>
       </c>
       <c r="F320" s="140">
-        <f>IFERROR(VLOOKUP(E320,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E320,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>96227408.59</v>
       </c>
       <c r="G320" s="143"/>
@@ -12932,8 +12761,7 @@
         <v>653</v>
       </c>
       <c r="F321" s="140">
-        <f>IFERROR(VLOOKUP(E321,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E321,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G321" s="138"/>
       <c r="H321" s="68"/>
@@ -12947,8 +12775,7 @@
         <v>654</v>
       </c>
       <c r="F322" s="140">
-        <f>IFERROR(VLOOKUP(E322,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E322,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G322" s="138"/>
       <c r="H322" s="68"/>
@@ -12977,7 +12804,7 @@
         <v>656</v>
       </c>
       <c r="F324" s="140">
-        <f>IFERROR(VLOOKUP(E324,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E324,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>218983.47</v>
       </c>
       <c r="G324" s="138"/>
@@ -12991,8 +12818,7 @@
         <v>657</v>
       </c>
       <c r="F325" s="140">
-        <f>IFERROR(VLOOKUP(E325,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E325,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G325" s="138"/>
     </row>
@@ -13005,7 +12831,7 @@
         <v>658</v>
       </c>
       <c r="F326" s="140">
-        <f>IFERROR(VLOOKUP(E326,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E326,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>56016567.58</v>
       </c>
       <c r="G326" s="138"/>
@@ -13019,8 +12845,7 @@
         <v>659</v>
       </c>
       <c r="F327" s="140">
-        <f>IFERROR(VLOOKUP(E327,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E327,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G327" s="138"/>
     </row>
@@ -13033,8 +12858,7 @@
         <v>660</v>
       </c>
       <c r="F328" s="140">
-        <f>IFERROR(VLOOKUP(E328,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E328,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G328" s="138"/>
     </row>
@@ -13047,8 +12871,7 @@
         <v>661</v>
       </c>
       <c r="F329" s="140">
-        <f>IFERROR(VLOOKUP(E329,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E329,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G329" s="138"/>
     </row>
@@ -13061,8 +12884,7 @@
         <v>662</v>
       </c>
       <c r="F330" s="140">
-        <f>IFERROR(VLOOKUP(E330,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E330,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G330" s="138"/>
     </row>
@@ -13077,8 +12899,7 @@
         <v>664</v>
       </c>
       <c r="F331" s="140">
-        <f>IFERROR(VLOOKUP(E331,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E331,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G331" s="187">
         <f>SUM(F331:F338)</f>
@@ -13095,7 +12916,7 @@
         <v>665</v>
       </c>
       <c r="F332" s="140">
-        <f>IFERROR(VLOOKUP(E332,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E332,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>21735.54</v>
       </c>
       <c r="G332" s="138"/>
@@ -13112,7 +12933,7 @@
         <v>667</v>
       </c>
       <c r="F333" s="140">
-        <f>IFERROR(VLOOKUP(E333,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E333,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>4589860.38</v>
       </c>
       <c r="G333" s="138"/>
@@ -13127,7 +12948,7 @@
         <v>668</v>
       </c>
       <c r="F334" s="140">
-        <f>IFERROR(VLOOKUP(E334,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E334,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>26655432.82</v>
       </c>
       <c r="G334" s="138"/>
@@ -13142,7 +12963,7 @@
         <v>669</v>
       </c>
       <c r="F335" s="140">
-        <f>IFERROR(VLOOKUP(E335,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E335,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>29800</v>
       </c>
       <c r="G335" s="138"/>
@@ -13157,8 +12978,7 @@
         <v>670</v>
       </c>
       <c r="F336" s="140">
-        <f>IFERROR(VLOOKUP(E336,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E336,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G336" s="138"/>
       <c r="H336" s="68"/>
@@ -13172,8 +12992,7 @@
         <v>671</v>
       </c>
       <c r="F337" s="140">
-        <f>IFERROR(VLOOKUP(E337,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E337,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G337" s="138"/>
       <c r="H337" s="68"/>
@@ -13187,8 +13006,7 @@
         <v>672</v>
       </c>
       <c r="F338" s="140">
-        <f>IFERROR(VLOOKUP(E338,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E338,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G338" s="138"/>
       <c r="H338" s="68"/>
@@ -13218,8 +13036,7 @@
         <v>675</v>
       </c>
       <c r="F340" s="140">
-        <f>IFERROR(VLOOKUP(E340,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E340,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G340" s="138">
         <f>+F340+F341+F342</f>
@@ -13235,8 +13052,7 @@
         <v>676</v>
       </c>
       <c r="F341" s="140">
-        <f>IFERROR(VLOOKUP(E341,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E341,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G341" s="138"/>
     </row>
@@ -13249,8 +13065,7 @@
         <v>677</v>
       </c>
       <c r="F342" s="140">
-        <f>IFERROR(VLOOKUP(E342,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E342,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G342" s="138"/>
     </row>
@@ -13265,8 +13080,7 @@
         <v>679</v>
       </c>
       <c r="F343" s="140">
-        <f>IFERROR(VLOOKUP(E343,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E343,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G343" s="187">
         <f>SUM(F343:F351)</f>
@@ -13282,7 +13096,7 @@
         <v>680</v>
       </c>
       <c r="F344" s="140">
-        <f>IFERROR(VLOOKUP(E344,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E344,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>653893.77</v>
       </c>
       <c r="G344" s="138"/>
@@ -13303,8 +13117,7 @@
         <v>681</v>
       </c>
       <c r="F345" s="140">
-        <f>IFERROR(VLOOKUP(E345,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E345,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G345" s="138"/>
       <c r="H345" s="132"/>
@@ -13324,7 +13137,7 @@
         <v>682</v>
       </c>
       <c r="F346" s="140">
-        <f>IFERROR(VLOOKUP(E346,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E346,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>6090934.65</v>
       </c>
       <c r="G346" s="138"/>
@@ -13338,8 +13151,7 @@
         <v>683</v>
       </c>
       <c r="F347" s="140">
-        <f>IFERROR(VLOOKUP(E347,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E347,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G347" s="138"/>
     </row>
@@ -13352,8 +13164,7 @@
         <v>684</v>
       </c>
       <c r="F348" s="140">
-        <f>IFERROR(VLOOKUP(E348,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E348,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G348" s="138"/>
     </row>
@@ -13366,8 +13177,7 @@
         <v>685</v>
       </c>
       <c r="F349" s="140">
-        <f>IFERROR(VLOOKUP(E349,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E349,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G349" s="138"/>
     </row>
@@ -13380,8 +13190,7 @@
         <v>686</v>
       </c>
       <c r="F350" s="140">
-        <f>IFERROR(VLOOKUP(E350,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E350,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G350" s="138"/>
     </row>
@@ -13394,7 +13203,7 @@
         <v>687</v>
       </c>
       <c r="F351" s="140">
-        <f>IFERROR(VLOOKUP(E351,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E351,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1449412.8</v>
       </c>
       <c r="G351" s="138"/>
@@ -13413,8 +13222,7 @@
         <v>689</v>
       </c>
       <c r="F352" s="140">
-        <f>IFERROR(VLOOKUP(E352,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E352,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G352" s="187">
         <f>SUM(F352:F358)</f>
@@ -13436,7 +13244,7 @@
         <v>690</v>
       </c>
       <c r="F353" s="140">
-        <f>IFERROR(VLOOKUP(E353,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E353,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1022000.89</v>
       </c>
       <c r="G353" s="138"/>
@@ -13451,7 +13259,7 @@
         <v>691</v>
       </c>
       <c r="F354" s="140">
-        <f>IFERROR(VLOOKUP(E354,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E354,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>8853131.85</v>
       </c>
       <c r="G354" s="138"/>
@@ -13466,8 +13274,7 @@
         <v>692</v>
       </c>
       <c r="F355" s="140">
-        <f>IFERROR(VLOOKUP(E355,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E355,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G355" s="138"/>
       <c r="H355" s="68"/>
@@ -13481,7 +13288,7 @@
         <v>693</v>
       </c>
       <c r="F356" s="140">
-        <f>IFERROR(VLOOKUP(E356,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E356,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>5099.17</v>
       </c>
       <c r="G356" s="138"/>
@@ -13496,8 +13303,7 @@
         <v>694</v>
       </c>
       <c r="F357" s="140">
-        <f>IFERROR(VLOOKUP(E357,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E357,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G357" s="138"/>
       <c r="H357" s="68"/>
@@ -13511,8 +13317,7 @@
         <v>695</v>
       </c>
       <c r="F358" s="140">
-        <f>IFERROR(VLOOKUP(E358,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E358,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G358" s="138"/>
       <c r="H358" s="68"/>
@@ -13541,8 +13346,7 @@
         <v>697</v>
       </c>
       <c r="F360" s="140">
-        <f>IFERROR(VLOOKUP(E360,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E360,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G360" s="138"/>
       <c r="H360" s="68"/>
@@ -13556,8 +13360,7 @@
         <v>698</v>
       </c>
       <c r="F361" s="140">
-        <f>IFERROR(VLOOKUP(E361,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E361,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G361" s="138"/>
       <c r="H361" s="68"/>
@@ -13586,8 +13389,7 @@
         <v>699</v>
       </c>
       <c r="F363" s="140">
-        <f>IFERROR(VLOOKUP(E363,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E363,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G363" s="138"/>
       <c r="H363" s="68"/>
@@ -13615,8 +13417,7 @@
         <v>701</v>
       </c>
       <c r="F365" s="140">
-        <f>IFERROR(VLOOKUP(E365,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E365,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G365" s="138"/>
     </row>
@@ -13629,8 +13430,7 @@
         <v>702</v>
       </c>
       <c r="F366" s="140">
-        <f>IFERROR(VLOOKUP(E366,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E366,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G366" s="138"/>
     </row>
@@ -13643,8 +13443,7 @@
         <v>703</v>
       </c>
       <c r="F367" s="140">
-        <f>IFERROR(VLOOKUP(E367,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E367,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G367" s="138"/>
     </row>
@@ -13685,8 +13484,7 @@
         <v>706</v>
       </c>
       <c r="F370" s="140">
-        <f>IFERROR(VLOOKUP(E370,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E370,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G370" s="138"/>
     </row>
@@ -13699,7 +13497,7 @@
         <v>707</v>
       </c>
       <c r="F371" s="140">
-        <f>IFERROR(VLOOKUP(E371,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E371,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>226261134.24</v>
       </c>
       <c r="G371" s="138"/>
@@ -13713,7 +13511,7 @@
         <v>708</v>
       </c>
       <c r="F372" s="140">
-        <f>IFERROR(VLOOKUP(E372,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E372,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>56730956.08</v>
       </c>
       <c r="G372" s="138"/>
@@ -13727,7 +13525,7 @@
         <v>709</v>
       </c>
       <c r="F373" s="140">
-        <f>IFERROR(VLOOKUP(E373,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E373,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>516529</v>
       </c>
       <c r="G373" s="138"/>
@@ -13741,8 +13539,7 @@
         <v>710</v>
       </c>
       <c r="F374" s="140">
-        <f>IFERROR(VLOOKUP(E374,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E374,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G374" s="138"/>
     </row>
@@ -13769,8 +13566,7 @@
         <v>712</v>
       </c>
       <c r="F376" s="140">
-        <f>IFERROR(VLOOKUP(E376,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E376,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G376" s="138"/>
     </row>
@@ -13783,7 +13579,7 @@
         <v>713</v>
       </c>
       <c r="F377" s="140">
-        <f>IFERROR(VLOOKUP(E377,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E377,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>45070376.57</v>
       </c>
       <c r="G377" s="138"/>
@@ -13797,8 +13593,7 @@
         <v>714</v>
       </c>
       <c r="F378" s="140">
-        <f>IFERROR(VLOOKUP(E378,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E378,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G378" s="138"/>
     </row>
@@ -13811,8 +13606,7 @@
         <v>715</v>
       </c>
       <c r="F379" s="140">
-        <f>IFERROR(VLOOKUP(E379,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E379,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G379" s="138"/>
     </row>
@@ -13825,8 +13619,7 @@
         <v>716</v>
       </c>
       <c r="F380" s="140">
-        <f>IFERROR(VLOOKUP(E380,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E380,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G380" s="138"/>
     </row>
@@ -13839,7 +13632,7 @@
         <v>717</v>
       </c>
       <c r="F381" s="140">
-        <f>IFERROR(VLOOKUP(E381,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E381,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>13502481.6</v>
       </c>
       <c r="G381" s="138"/>
@@ -13853,8 +13646,7 @@
         <v>718</v>
       </c>
       <c r="F382" s="140">
-        <f>IFERROR(VLOOKUP(E382,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E382,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G382" s="138"/>
     </row>
@@ -13867,8 +13659,7 @@
         <v>719</v>
       </c>
       <c r="F383" s="140">
-        <f>IFERROR(VLOOKUP(E383,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E383,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G383" s="138"/>
     </row>
@@ -13881,8 +13672,7 @@
         <v>720</v>
       </c>
       <c r="F384" s="140">
-        <f>IFERROR(VLOOKUP(E384,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E384,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G384" s="138"/>
     </row>
@@ -13939,8 +13729,7 @@
         <v>725</v>
       </c>
       <c r="F388" s="140">
-        <f>IFERROR(VLOOKUP(E388,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E388,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G388" s="138">
         <f>+F388+F389</f>
@@ -13956,8 +13745,7 @@
         <v>726</v>
       </c>
       <c r="F389" s="140">
-        <f>IFERROR(VLOOKUP(E389,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E389,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G389" s="138"/>
     </row>
@@ -14006,8 +13794,7 @@
         <v>729</v>
       </c>
       <c r="F392" s="140">
-        <f>IFERROR(VLOOKUP(E392,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E392,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G392" s="138"/>
       <c r="H392" s="132"/>
@@ -14028,7 +13815,7 @@
         <v>730</v>
       </c>
       <c r="F393" s="140">
-        <f>IFERROR(VLOOKUP(E393,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E393,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>15882026</v>
       </c>
       <c r="G393" s="138"/>
@@ -14052,7 +13839,7 @@
         <v>732</v>
       </c>
       <c r="F394" s="140">
-        <f>IFERROR(VLOOKUP(E394,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E394,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>5598557</v>
       </c>
       <c r="G394" s="138">
@@ -14069,8 +13856,7 @@
         <v>733</v>
       </c>
       <c r="F395" s="140">
-        <f>IFERROR(VLOOKUP(E395,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E395,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G395" s="138"/>
     </row>
@@ -14083,8 +13869,7 @@
         <v>734</v>
       </c>
       <c r="F396" s="140">
-        <f>IFERROR(VLOOKUP(E396,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E396,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G396" s="138"/>
     </row>
@@ -14097,8 +13882,7 @@
         <v>735</v>
       </c>
       <c r="F397" s="140">
-        <f>IFERROR(VLOOKUP(E397,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E397,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G397" s="138"/>
     </row>
@@ -14125,8 +13909,7 @@
         <v>737</v>
       </c>
       <c r="F399" s="140">
-        <f>IFERROR(VLOOKUP(E399,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E399,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G399" s="138"/>
       <c r="H399" s="72"/>
@@ -14154,8 +13937,7 @@
         <v>739</v>
       </c>
       <c r="F401" s="140">
-        <f>IFERROR(VLOOKUP(E401,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E401,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G401" s="138"/>
     </row>
@@ -14170,7 +13952,7 @@
         <v>741</v>
       </c>
       <c r="F402" s="140">
-        <f>IFERROR(VLOOKUP(E402,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E402,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>314486283.55</v>
       </c>
       <c r="G402" s="187">
@@ -14201,8 +13983,7 @@
         <v>743</v>
       </c>
       <c r="F404" s="140">
-        <f>IFERROR(VLOOKUP(E404,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E404,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G404" s="138"/>
     </row>
@@ -14215,8 +13996,7 @@
         <v>744</v>
       </c>
       <c r="F405" s="140">
-        <f>IFERROR(VLOOKUP(E405,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E405,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G405" s="138"/>
     </row>
@@ -14257,8 +14037,7 @@
         <v>747</v>
       </c>
       <c r="F408" s="140">
-        <f>IFERROR(VLOOKUP(E408,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E408,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G408" s="138"/>
     </row>
@@ -14271,8 +14050,7 @@
         <v>748</v>
       </c>
       <c r="F409" s="140">
-        <f>IFERROR(VLOOKUP(E409,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E409,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G409" s="138"/>
     </row>
@@ -14285,7 +14063,7 @@
         <v>749</v>
       </c>
       <c r="F410" s="140">
-        <f>IFERROR(VLOOKUP(E410,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E410,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>901685.37</v>
       </c>
       <c r="G410" s="138"/>
@@ -14299,8 +14077,7 @@
         <v>750</v>
       </c>
       <c r="F411" s="140">
-        <f>IFERROR(VLOOKUP(E411,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E411,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G411" s="138"/>
     </row>
@@ -14313,8 +14090,7 @@
         <v>751</v>
       </c>
       <c r="F412" s="140">
-        <f>IFERROR(VLOOKUP(E412,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E412,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G412" s="138"/>
     </row>
@@ -14327,8 +14103,7 @@
         <v>752</v>
       </c>
       <c r="F413" s="140">
-        <f>IFERROR(VLOOKUP(E413,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E413,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G413" s="138"/>
     </row>
@@ -14343,8 +14118,7 @@
         <v>754</v>
       </c>
       <c r="F414" s="140">
-        <f>IFERROR(VLOOKUP(E414,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E414,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G414" s="187">
         <f>+F414+F415</f>
@@ -14367,7 +14141,7 @@
         <v>753</v>
       </c>
       <c r="F415" s="140">
-        <f>IFERROR(VLOOKUP(E415,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E415,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>236115665.5</v>
       </c>
       <c r="G415" s="138"/>
@@ -14404,8 +14178,7 @@
         <v>757</v>
       </c>
       <c r="F417" s="140">
-        <f>IFERROR(VLOOKUP(E417,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E417,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G417" s="187">
         <f>SUM(F417:F424)</f>
@@ -14421,7 +14194,7 @@
         <v>758</v>
       </c>
       <c r="F418" s="140">
-        <f>IFERROR(VLOOKUP(E418,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E418,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>3313483</v>
       </c>
       <c r="G418" s="138"/>
@@ -14437,8 +14210,7 @@
         <v>759</v>
       </c>
       <c r="F419" s="140">
-        <f>IFERROR(VLOOKUP(E419,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E419,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G419" s="138"/>
       <c r="H419" s="72"/>
@@ -14453,7 +14225,7 @@
         <v>760</v>
       </c>
       <c r="F420" s="140">
-        <f>IFERROR(VLOOKUP(E420,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E420,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>442383.7</v>
       </c>
       <c r="G420" s="138"/>
@@ -14469,8 +14241,7 @@
         <v>761</v>
       </c>
       <c r="F421" s="140">
-        <f>IFERROR(VLOOKUP(E421,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E421,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G421" s="138"/>
       <c r="H421" s="72"/>
@@ -14485,8 +14256,7 @@
         <v>762</v>
       </c>
       <c r="F422" s="140">
-        <f>IFERROR(VLOOKUP(E422,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E422,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G422" s="138"/>
       <c r="H422" s="72"/>
@@ -14501,8 +14271,7 @@
         <v>763</v>
       </c>
       <c r="F423" s="140">
-        <f>IFERROR(VLOOKUP(E423,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E423,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G423" s="138"/>
       <c r="H423" s="72"/>
@@ -14514,11 +14283,11 @@
       <c r="C424" s="34"/>
       <c r="D424" s="139"/>
       <c r="E424" s="72" t="str">
-        <f>+Hoja1!A304</f>
+        <f>+'Balance de sumas y saldos'!A304</f>
         <v>426880000 - Tasas Municipales Gs Campo</v>
       </c>
       <c r="F424" s="140">
-        <f>IFERROR(VLOOKUP(E424,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E424,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>44100</v>
       </c>
       <c r="G424" s="138"/>
@@ -14534,7 +14303,7 @@
       </c>
       <c r="E425" s="71"/>
       <c r="F425" s="140">
-        <f>IFERROR(VLOOKUP(D425,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D425,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>63010431.79</v>
       </c>
       <c r="G425" s="187">
@@ -14565,8 +14334,7 @@
         <v>766</v>
       </c>
       <c r="F427" s="140">
-        <f>IFERROR(VLOOKUP(E427,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E427,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G427" s="138"/>
     </row>
@@ -14579,7 +14347,7 @@
         <v>767</v>
       </c>
       <c r="F428" s="140">
-        <f>IFERROR(VLOOKUP(E428,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E428,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>632438.8</v>
       </c>
       <c r="G428" s="138"/>
@@ -14593,7 +14361,7 @@
         <v>768</v>
       </c>
       <c r="F429" s="140">
-        <f>IFERROR(VLOOKUP(E429,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E429,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>152403.72</v>
       </c>
       <c r="G429" s="138"/>
@@ -14607,8 +14375,7 @@
         <v>769</v>
       </c>
       <c r="F430" s="140">
-        <f>IFERROR(VLOOKUP(E430,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E430,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G430" s="138"/>
     </row>
@@ -14621,8 +14388,7 @@
         <v>770</v>
       </c>
       <c r="F431" s="140">
-        <f>IFERROR(VLOOKUP(E431,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E431,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G431" s="138"/>
     </row>
@@ -14635,8 +14401,7 @@
         <v>771</v>
       </c>
       <c r="F432" s="140">
-        <f>IFERROR(VLOOKUP(E432,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E432,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G432" s="138"/>
     </row>
@@ -14649,8 +14414,7 @@
         <v>772</v>
       </c>
       <c r="F433" s="140">
-        <f>IFERROR(VLOOKUP(E433,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E433,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G433" s="138"/>
     </row>
@@ -14663,8 +14427,7 @@
         <v>773</v>
       </c>
       <c r="F434" s="140">
-        <f>IFERROR(VLOOKUP(E434,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E434,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G434" s="138"/>
     </row>
@@ -14691,7 +14454,7 @@
         <v>775</v>
       </c>
       <c r="F436" s="140">
-        <f>IFERROR(VLOOKUP(E436,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E436,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>1413626.44</v>
       </c>
       <c r="G436" s="138"/>
@@ -14705,7 +14468,7 @@
         <v>776</v>
       </c>
       <c r="F437" s="140">
-        <f>IFERROR(VLOOKUP(E437,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E437,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>16508205.74</v>
       </c>
       <c r="G437" s="138"/>
@@ -14719,8 +14482,7 @@
         <v>777</v>
       </c>
       <c r="F438" s="140">
-        <f>IFERROR(VLOOKUP(E438,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E438,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G438" s="138"/>
     </row>
@@ -14733,8 +14495,7 @@
         <v>778</v>
       </c>
       <c r="F439" s="140">
-        <f>IFERROR(VLOOKUP(E439,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E439,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G439" s="138"/>
     </row>
@@ -14775,8 +14536,7 @@
         <v>781</v>
       </c>
       <c r="F442" s="140">
-        <f>IFERROR(VLOOKUP(E442,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E442,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G442" s="138"/>
     </row>
@@ -14789,8 +14549,7 @@
         <v>782</v>
       </c>
       <c r="F443" s="140">
-        <f>IFERROR(VLOOKUP(E443,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E443,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G443" s="138"/>
     </row>
@@ -14817,8 +14576,7 @@
         <v>784</v>
       </c>
       <c r="F445" s="140">
-        <f>IFERROR(VLOOKUP(E445,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E445,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G445" s="138"/>
     </row>
@@ -14831,7 +14589,7 @@
         <v>785</v>
       </c>
       <c r="F446" s="140">
-        <f>IFERROR(VLOOKUP(E446,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E446,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>101483.28</v>
       </c>
       <c r="G446" s="138"/>
@@ -14847,8 +14605,7 @@
         <v>786</v>
       </c>
       <c r="F447" s="140">
-        <f>IFERROR(VLOOKUP(E447,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E447,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G447" s="138"/>
       <c r="H447" s="72"/>
@@ -14863,8 +14620,7 @@
         <v>787</v>
       </c>
       <c r="F448" s="140">
-        <f>IFERROR(VLOOKUP(E448,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E448,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G448" s="138"/>
       <c r="H448" s="72"/>
@@ -14893,8 +14649,7 @@
         <v>789</v>
       </c>
       <c r="F450" s="140">
-        <f>IFERROR(VLOOKUP(E450,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E450,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G450" s="138"/>
     </row>
@@ -14907,8 +14662,7 @@
         <v>790</v>
       </c>
       <c r="F451" s="140">
-        <f>IFERROR(VLOOKUP(E451,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E451,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G451" s="138"/>
     </row>
@@ -14921,7 +14675,7 @@
         <v>791</v>
       </c>
       <c r="F452" s="140">
-        <f>IFERROR(VLOOKUP(E452,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E452,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>8441197.290000001</v>
       </c>
       <c r="G452" s="138"/>
@@ -14949,7 +14703,7 @@
         <v>793</v>
       </c>
       <c r="F454" s="140">
-        <f>IFERROR(VLOOKUP(E454,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E454,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>299800</v>
       </c>
       <c r="G454" s="138"/>
@@ -14963,7 +14717,7 @@
         <v>794</v>
       </c>
       <c r="F455" s="140">
-        <f>IFERROR(VLOOKUP(E455,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E455,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>14418193.67</v>
       </c>
       <c r="G455" s="138"/>
@@ -14977,8 +14731,7 @@
         <v>795</v>
       </c>
       <c r="F456" s="140">
-        <f>IFERROR(VLOOKUP(E456,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E456,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G456" s="138"/>
     </row>
@@ -14991,8 +14744,7 @@
         <v>796</v>
       </c>
       <c r="F457" s="140">
-        <f>IFERROR(VLOOKUP(E457,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E457,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G457" s="138"/>
     </row>
@@ -15005,8 +14757,7 @@
       </c>
       <c r="E458" s="71"/>
       <c r="F458" s="140">
-        <f>IFERROR(VLOOKUP(D458,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D458,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G458" s="138">
         <f>+F458</f>
@@ -15022,8 +14773,7 @@
       </c>
       <c r="E459" s="71"/>
       <c r="F459" s="140">
-        <f>IFERROR(VLOOKUP(D459,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D459,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G459" s="138">
         <f>+F459</f>
@@ -15053,8 +14803,7 @@
         <v>800</v>
       </c>
       <c r="F461" s="140">
-        <f>IFERROR(VLOOKUP(E461,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E461,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G461" s="138"/>
     </row>
@@ -15067,8 +14816,7 @@
         <v>801</v>
       </c>
       <c r="F462" s="140">
-        <f>IFERROR(VLOOKUP(E462,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E462,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G462" s="138"/>
     </row>
@@ -15083,8 +14831,7 @@
         <v>803</v>
       </c>
       <c r="F463" s="140">
-        <f>IFERROR(VLOOKUP(E463,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E463,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G463" s="187">
         <f>SUM(F463:F471)</f>
@@ -15101,7 +14848,7 @@
         <v>804</v>
       </c>
       <c r="F464" s="140">
-        <f>IFERROR(VLOOKUP(E464,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E464,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>11218221</v>
       </c>
       <c r="G464" s="138"/>
@@ -15116,7 +14863,7 @@
         <v>805</v>
       </c>
       <c r="F465" s="140">
-        <f>IFERROR(VLOOKUP(E465,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E465,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>8798124.41</v>
       </c>
       <c r="G465" s="138"/>
@@ -15131,8 +14878,7 @@
         <v>806</v>
       </c>
       <c r="F466" s="140">
-        <f>IFERROR(VLOOKUP(E466,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E466,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G466" s="138"/>
       <c r="H466" s="72"/>
@@ -15147,8 +14893,7 @@
         <v>807</v>
       </c>
       <c r="F467" s="140">
-        <f>IFERROR(VLOOKUP(E467,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E467,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G467" s="138"/>
       <c r="H467" s="72"/>
@@ -15163,8 +14908,7 @@
         <v>808</v>
       </c>
       <c r="F468" s="140">
-        <f>IFERROR(VLOOKUP(E468,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E468,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G468" s="138"/>
       <c r="H468" s="72"/>
@@ -15179,8 +14923,7 @@
         <v>809</v>
       </c>
       <c r="F469" s="140">
-        <f>IFERROR(VLOOKUP(E469,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E469,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G469" s="138"/>
       <c r="H469" s="72"/>
@@ -15195,8 +14938,7 @@
         <v>810</v>
       </c>
       <c r="F470" s="140">
-        <f>IFERROR(VLOOKUP(E470,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E470,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G470" s="138"/>
       <c r="H470" s="72"/>
@@ -15211,8 +14953,7 @@
         <v>811</v>
       </c>
       <c r="F471" s="140">
-        <f>IFERROR(VLOOKUP(E471,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E471,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G471" s="138"/>
       <c r="H471" s="72"/>
@@ -15241,8 +14982,7 @@
         <v>813</v>
       </c>
       <c r="F473" s="140">
-        <f>IFERROR(VLOOKUP(E473,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E473,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G473" s="138"/>
     </row>
@@ -15255,8 +14995,7 @@
         <v>814</v>
       </c>
       <c r="F474" s="140">
-        <f>IFERROR(VLOOKUP(E474,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E474,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G474" s="138"/>
     </row>
@@ -15269,8 +15008,7 @@
         <v>815</v>
       </c>
       <c r="F475" s="140">
-        <f>IFERROR(VLOOKUP(E475,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E475,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G475" s="138"/>
     </row>
@@ -15283,8 +15021,7 @@
       </c>
       <c r="E476" s="188"/>
       <c r="F476" s="140">
-        <f>IFERROR(VLOOKUP(D476,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D476,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G476" s="138">
         <f>+F476</f>
@@ -15300,8 +15037,7 @@
       </c>
       <c r="E477" s="188"/>
       <c r="F477" s="140">
-        <f>IFERROR(VLOOKUP(D477,Hoja1!$A$2:$E$550,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D477,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G477" s="138">
         <f>+F477</f>
@@ -15331,8 +15067,7 @@
         <v>819</v>
       </c>
       <c r="F479" s="140">
-        <f>IFERROR(VLOOKUP(E479,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E479,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G479" s="138"/>
     </row>
@@ -15345,8 +15080,7 @@
         <v>820</v>
       </c>
       <c r="F480" s="140">
-        <f>IFERROR(VLOOKUP(E480,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E480,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G480" s="138"/>
     </row>
@@ -15361,8 +15095,7 @@
         <v>822</v>
       </c>
       <c r="F481" s="140">
-        <f>IFERROR(VLOOKUP(E481,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E481,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G481" s="187">
         <f>SUM(F481:F483)</f>
@@ -15378,8 +15111,7 @@
         <v>823</v>
       </c>
       <c r="F482" s="140">
-        <f>IFERROR(VLOOKUP(E482,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E482,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G482" s="138"/>
     </row>
@@ -15392,7 +15124,7 @@
         <v>824</v>
       </c>
       <c r="F483" s="140">
-        <f>IFERROR(VLOOKUP(E483,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E483,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>4714680.04</v>
       </c>
       <c r="G483" s="138"/>
@@ -15408,8 +15140,7 @@
         <v>826</v>
       </c>
       <c r="F484" s="140">
-        <f>IFERROR(VLOOKUP(E484,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(E484,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G484" s="138">
         <f>+F484</f>
@@ -15425,8 +15156,7 @@
       </c>
       <c r="E485" s="71"/>
       <c r="F485" s="140">
-        <f>IFERROR(VLOOKUP(D485,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D485,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G485" s="138">
         <f>+F485</f>
@@ -15442,8 +15172,7 @@
       </c>
       <c r="E486" s="72"/>
       <c r="F486" s="140">
-        <f>IFERROR(VLOOKUP(D486,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D486,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G486" s="138">
         <f>+F486</f>
@@ -15459,7 +15188,7 @@
       </c>
       <c r="E487" s="68"/>
       <c r="F487" s="140">
-        <f>IFERROR(VLOOKUP(D487,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D487,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>4150213.41</v>
       </c>
       <c r="G487" s="187">
@@ -15476,8 +15205,7 @@
       </c>
       <c r="E488" s="132"/>
       <c r="F488" s="140">
-        <f>IFERROR(VLOOKUP(D488,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D488,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G488" s="138">
         <f>+F488</f>
@@ -15493,8 +15221,7 @@
       </c>
       <c r="E489" s="132"/>
       <c r="F489" s="140">
-        <f>IFERROR(VLOOKUP(D489,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D489,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G489" s="138">
         <f>+F489</f>
@@ -15510,7 +15237,7 @@
       </c>
       <c r="E490" s="132"/>
       <c r="F490" s="140">
-        <f>IFERROR(VLOOKUP(D490,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D490,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>226987</v>
       </c>
       <c r="G490" s="187">
@@ -15527,7 +15254,7 @@
       </c>
       <c r="E491" s="132"/>
       <c r="F491" s="140">
-        <f>IFERROR(VLOOKUP(D491,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D491,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>914304.7000000001</v>
       </c>
       <c r="G491" s="187">
@@ -15544,8 +15271,7 @@
       </c>
       <c r="E492" s="132"/>
       <c r="F492" s="140">
-        <f>IFERROR(VLOOKUP(D492,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D492,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G492" s="138">
         <f>+F492</f>
@@ -15561,8 +15287,7 @@
       </c>
       <c r="E493" s="68"/>
       <c r="F493" s="140">
-        <f>IFERROR(VLOOKUP(D493,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D493,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G493" s="138">
         <f>+F493</f>
@@ -15578,8 +15303,7 @@
       </c>
       <c r="E494" s="132"/>
       <c r="F494" s="140">
-        <f>IFERROR(VLOOKUP(D494,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D494,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G494" s="138">
         <f>+F494</f>
@@ -15595,8 +15319,7 @@
       </c>
       <c r="E495" s="132"/>
       <c r="F495" s="140">
-        <f>IFERROR(VLOOKUP(D495,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D495,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G495" s="138">
         <f>+F495</f>
@@ -15612,8 +15335,7 @@
       </c>
       <c r="E496" s="132"/>
       <c r="F496" s="140">
-        <f>IFERROR(VLOOKUP(D496,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D496,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G496" s="138">
         <f>+F496</f>
@@ -15631,7 +15353,7 @@
         <v>839</v>
       </c>
       <c r="F497" s="140">
-        <f>IFERROR(VLOOKUP(D497,Hoja1!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D497,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
         <v>358719.18</v>
       </c>
       <c r="G497" s="187">
@@ -15648,8 +15370,7 @@
       </c>
       <c r="E498" s="132"/>
       <c r="F498" s="140">
-        <f>IFERROR(VLOOKUP(D498,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D498,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G498" s="138">
         <f>+F498</f>
@@ -15666,8 +15387,7 @@
       </c>
       <c r="E499" s="132"/>
       <c r="F499" s="140">
-        <f>IFERROR(VLOOKUP(D499,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D499,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G499" s="138">
         <f>+F499</f>
@@ -15684,8 +15404,7 @@
       </c>
       <c r="E500" s="132"/>
       <c r="F500" s="140">
-        <f>IFERROR(VLOOKUP(D500,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D500,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G500" s="138">
         <f>+F500</f>
@@ -15702,8 +15421,7 @@
       </c>
       <c r="E501" s="132"/>
       <c r="F501" s="140">
-        <f>IFERROR(VLOOKUP(D501,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D501,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G501" s="138">
         <f>+F501</f>
@@ -15720,8 +15438,7 @@
       </c>
       <c r="E502" s="132"/>
       <c r="F502" s="140">
-        <f>IFERROR(VLOOKUP(D502,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D502,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G502" s="138">
         <f>+F502</f>
@@ -15737,8 +15454,7 @@
       </c>
       <c r="E503" s="132"/>
       <c r="F503" s="140">
-        <f>IFERROR(VLOOKUP(D503,Hoja1!$A$2:$E$574,5,FALSE),)</f>
-        <v>0</v>
+        <f>IFERROR(VLOOKUP(D503,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G503" s="138">
         <f>+F503</f>
@@ -15798,7 +15514,7 @@
         <v>-1737765878.36</v>
       </c>
       <c r="G506" s="205">
-        <f>+Hoja1!E515</f>
+        <f>+'Balance de sumas y saldos'!E515</f>
         <v>1802783307.1299999</v>
       </c>
       <c r="H506" s="199"/>
@@ -29263,7 +28979,7 @@
         <v>2171896468.87</v>
       </c>
       <c r="F61" s="41">
-        <f>+SUM(SALDOS!G3:G61)</f>
+        <f>+SUM('Distribución por línea'!G3:G61)</f>
         <v>2171896468.87</v>
       </c>
       <c r="G61" s="41">
@@ -34506,7 +34222,7 @@
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="19">
-        <f>+SALDOS!G3</f>
+        <f>+'Distribución por línea'!G3</f>
         <v>1500000</v>
       </c>
     </row>
@@ -34519,8 +34235,7 @@
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="19">
-        <f>+SALDOS!G4</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G4</f>
       </c>
     </row>
     <row r="10" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -34532,7 +34247,7 @@
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="19">
-        <f>+SALDOS!G5</f>
+        <f>+'Distribución por línea'!G5</f>
         <v>11928050.5</v>
       </c>
       <c r="G10" s="34"/>
@@ -34546,7 +34261,7 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="19">
-        <f>+SALDOS!G11</f>
+        <f>+'Distribución por línea'!G11</f>
         <v>8472052.17</v>
       </c>
       <c r="G11" s="34"/>
@@ -34560,7 +34275,7 @@
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="19">
-        <f>+SALDOS!G6</f>
+        <f>+'Distribución por línea'!G6</f>
         <v>123812147.38</v>
       </c>
     </row>
@@ -34573,8 +34288,7 @@
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="19">
-        <f>+SALDOS!G7</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G7</f>
       </c>
     </row>
     <row r="14" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34586,7 +34300,7 @@
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="19">
-        <f>+SALDOS!G8</f>
+        <f>+'Distribución por línea'!G8</f>
         <v>15375551.48</v>
       </c>
     </row>
@@ -34599,7 +34313,7 @@
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="19">
-        <f>+SALDOS!G9</f>
+        <f>+'Distribución por línea'!G9</f>
         <v>7164.12</v>
       </c>
     </row>
@@ -34612,8 +34326,7 @@
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="19">
-        <f>+SALDOS!G12</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G12</f>
       </c>
     </row>
     <row r="17" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34625,8 +34338,7 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="19">
-        <f>+SALDOS!G10</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G10</f>
       </c>
     </row>
     <row r="18" ht="10.95" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34671,8 +34383,7 @@
       </c>
       <c r="E21" s="1"/>
       <c r="F21" s="19">
-        <f>+SALDOS!G40</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G40</f>
       </c>
     </row>
     <row r="22" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34684,8 +34395,7 @@
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="74">
-        <f>+SALDOS!G14</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G14</f>
       </c>
     </row>
     <row r="23" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34697,7 +34407,7 @@
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="74">
-        <f>+SALDOS!G15</f>
+        <f>+'Distribución por línea'!G15</f>
         <v>1673415069.26</v>
       </c>
     </row>
@@ -34710,7 +34420,7 @@
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="74">
-        <f>+SALDOS!G18</f>
+        <f>+'Distribución por línea'!G18</f>
         <v>7898761.38</v>
       </c>
     </row>
@@ -34723,8 +34433,7 @@
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="19">
-        <f>+SALDOS!G16</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G16</f>
       </c>
     </row>
     <row r="26" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34736,7 +34445,7 @@
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="19">
-        <f>+SALDOS!G17</f>
+        <f>+'Distribución por línea'!G17</f>
         <v>1159.02</v>
       </c>
     </row>
@@ -34749,7 +34458,7 @@
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="74">
-        <f>+SALDOS!G19</f>
+        <f>+'Distribución por línea'!G19</f>
         <v>53327476.84</v>
       </c>
     </row>
@@ -34762,7 +34471,7 @@
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="74">
-        <f>+SALDOS!G20</f>
+        <f>+'Distribución por línea'!G20</f>
         <v>528747.09</v>
       </c>
     </row>
@@ -34775,7 +34484,7 @@
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="74">
-        <f>+SALDOS!G25</f>
+        <f>+'Distribución por línea'!G25</f>
         <v>26028040.72</v>
       </c>
     </row>
@@ -34788,8 +34497,7 @@
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="74">
-        <f>+SALDOS!G26</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G26</f>
       </c>
     </row>
     <row r="31" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34801,8 +34509,7 @@
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="74">
-        <f>+SALDOS!G27</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G27</f>
       </c>
     </row>
     <row r="32" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34814,8 +34521,7 @@
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="74">
-        <f>+SALDOS!G28</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G28</f>
       </c>
     </row>
     <row r="33" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34827,7 +34533,7 @@
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="74">
-        <f>+SALDOS!G29</f>
+        <f>+'Distribución por línea'!G29</f>
         <v>111962569.93</v>
       </c>
     </row>
@@ -34840,7 +34546,7 @@
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="74">
-        <f>+SALDOS!G30</f>
+        <f>+'Distribución por línea'!G30</f>
         <v>1068.39</v>
       </c>
     </row>
@@ -34853,8 +34559,7 @@
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="74">
-        <f>+SALDOS!G33</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G33</f>
       </c>
     </row>
     <row r="36" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34866,7 +34571,7 @@
       </c>
       <c r="E36" s="75"/>
       <c r="F36" s="19">
-        <f>+SALDOS!G42</f>
+        <f>+'Distribución por línea'!G42</f>
         <v>108200</v>
       </c>
     </row>
@@ -34879,8 +34584,7 @@
       </c>
       <c r="E37" s="75"/>
       <c r="F37" s="19">
-        <f>+SALDOS!G41</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G41</f>
       </c>
     </row>
     <row r="38" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34892,8 +34596,7 @@
       </c>
       <c r="E38" s="75"/>
       <c r="F38" s="19">
-        <f>+SALDOS!G34</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G34</f>
       </c>
     </row>
     <row r="39" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34905,8 +34608,7 @@
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="19">
-        <f>+SALDOS!G35</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G35</f>
       </c>
     </row>
     <row r="40" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34918,8 +34620,7 @@
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="19">
-        <f>+SALDOS!G36</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G36</f>
       </c>
     </row>
     <row r="41" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34931,7 +34632,7 @@
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="19">
-        <f>+SALDOS!G37</f>
+        <f>+'Distribución por línea'!G37</f>
         <v>23499142.66</v>
       </c>
     </row>
@@ -34944,7 +34645,7 @@
       </c>
       <c r="E42" s="75"/>
       <c r="F42" s="19">
-        <f>+SALDOS!G38</f>
+        <f>+'Distribución por línea'!G38</f>
         <v>323000</v>
       </c>
       <c r="G42" s="1"/>
@@ -34959,7 +34660,7 @@
       </c>
       <c r="E43" s="75"/>
       <c r="F43" s="19">
-        <f>+SALDOS!G31</f>
+        <f>+'Distribución por línea'!G31</f>
         <v>5596322.17</v>
       </c>
     </row>
@@ -34972,8 +34673,7 @@
       </c>
       <c r="E44" s="75"/>
       <c r="F44" s="19">
-        <f>+SALDOS!G32</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G32</f>
       </c>
     </row>
     <row r="45" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34985,8 +34685,7 @@
       </c>
       <c r="E45" s="75"/>
       <c r="F45" s="19">
-        <f>+SALDOS!G21</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G21</f>
       </c>
     </row>
     <row r="46" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -34998,7 +34697,7 @@
       </c>
       <c r="E46" s="75"/>
       <c r="F46" s="19">
-        <f>+SALDOS!G22</f>
+        <f>+'Distribución por línea'!G22</f>
         <v>243686.59</v>
       </c>
     </row>
@@ -35011,7 +34710,7 @@
       </c>
       <c r="E47" s="75"/>
       <c r="F47" s="19">
-        <f>+SALDOS!G23</f>
+        <f>+'Distribución por línea'!G23</f>
         <v>203599.05000000002</v>
       </c>
     </row>
@@ -35024,7 +34723,7 @@
       </c>
       <c r="E48" s="75"/>
       <c r="F48" s="19">
-        <f>+SALDOS!G24</f>
+        <f>+'Distribución por línea'!G24</f>
         <v>45551974.83</v>
       </c>
     </row>
@@ -35037,7 +34736,7 @@
       </c>
       <c r="E49" s="75"/>
       <c r="F49" s="19">
-        <f>+SALDOS!G60</f>
+        <f>+'Distribución por línea'!G60</f>
         <v>5439067</v>
       </c>
     </row>
@@ -35050,7 +34749,7 @@
       </c>
       <c r="E50" s="75"/>
       <c r="F50" s="19">
-        <f>+SALDOS!G61</f>
+        <f>+'Distribución por línea'!G61</f>
         <v>32772165</v>
       </c>
     </row>
@@ -35095,7 +34794,7 @@
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="19">
-        <f>+SALDOS!G39</f>
+        <f>+'Distribución por línea'!G39</f>
       </c>
       <c r="G54" s="19"/>
     </row>
@@ -35159,8 +34858,7 @@
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="19">
-        <f>+SALDOS!G43</f>
-        <v>0</v>
+        <f>+'Distribución por línea'!G43</f>
       </c>
     </row>
     <row r="61" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -35233,7 +34931,7 @@
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="19">
-        <f>-SALDOS!I117</f>
+        <f>-'Distribución por línea'!I117</f>
         <v>55662512.260000005</v>
       </c>
     </row>
@@ -35246,8 +34944,7 @@
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="19">
-        <f>-SALDOS!G127</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G127</f>
       </c>
     </row>
     <row r="70" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35259,8 +34956,7 @@
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="19">
-        <f>-SALDOS!G130</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G130</f>
       </c>
     </row>
     <row r="71" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35272,8 +34968,7 @@
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="19">
-        <f>-SALDOS!G135</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G135</f>
       </c>
     </row>
     <row r="72" ht="10.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -35315,7 +35010,7 @@
       </c>
       <c r="E74" s="76"/>
       <c r="F74" s="74">
-        <f>-SALDOS!G122</f>
+        <f>-'Distribución por línea'!G122</f>
         <v>202495033.97</v>
       </c>
     </row>
@@ -35352,8 +35047,7 @@
       </c>
       <c r="E77" s="76"/>
       <c r="F77" s="74">
-        <f>-SALDOS!G125</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G125</f>
       </c>
     </row>
     <row r="78" ht="13.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35365,8 +35059,7 @@
       </c>
       <c r="E78" s="76"/>
       <c r="F78" s="74">
-        <f>-SALDOS!G124-SALDOS!G133</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G124-'Distribución por línea'!G133</f>
       </c>
     </row>
     <row r="79" ht="13.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35378,7 +35071,7 @@
       </c>
       <c r="E79" s="76"/>
       <c r="F79" s="74">
-        <f>-SALDOS!G137</f>
+        <f>-'Distribución por línea'!G137</f>
         <v>19744</v>
       </c>
     </row>
@@ -35391,8 +35084,7 @@
       </c>
       <c r="E80" s="76"/>
       <c r="F80" s="74">
-        <f>-SALDOS!G138</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G138</f>
       </c>
     </row>
     <row r="81" ht="13.2" customHeight="1" hidden="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35404,8 +35096,7 @@
       </c>
       <c r="E81" s="76"/>
       <c r="F81" s="74">
-        <f>-SALDOS!G134</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G134</f>
       </c>
     </row>
     <row r="82" ht="13.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35417,7 +35108,7 @@
       </c>
       <c r="E82" s="76"/>
       <c r="F82" s="74">
-        <f>-SALDOS!G136</f>
+        <f>-'Distribución por línea'!G136</f>
         <v>1335.23</v>
       </c>
     </row>
@@ -35430,7 +35121,7 @@
       </c>
       <c r="E83" s="76"/>
       <c r="F83" s="74">
-        <f>-SALDOS!G128</f>
+        <f>-'Distribución por línea'!G128</f>
         <v>45551975</v>
       </c>
     </row>
@@ -35443,7 +35134,7 @@
       </c>
       <c r="E84" s="76"/>
       <c r="F84" s="74">
-        <f>-SALDOS!G129</f>
+        <f>-'Distribución por línea'!G129</f>
         <v>772433.68</v>
       </c>
     </row>
@@ -35456,7 +35147,7 @@
       </c>
       <c r="E85" s="76"/>
       <c r="F85" s="74">
-        <f>-SALDOS!G132</f>
+        <f>-'Distribución por línea'!G132</f>
         <v>38362895.27</v>
       </c>
     </row>
@@ -35500,8 +35191,7 @@
       </c>
       <c r="E89" s="76"/>
       <c r="F89" s="74">
-        <f>-SALDOS!G121</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G121</f>
       </c>
     </row>
     <row r="90" ht="13.2" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -35513,7 +35203,7 @@
       </c>
       <c r="E90" s="76"/>
       <c r="F90" s="74">
-        <f>-SALDOS!G123</f>
+        <f>-'Distribución por línea'!G123</f>
         <v>16429293.860000001</v>
       </c>
     </row>
@@ -35526,7 +35216,7 @@
       </c>
       <c r="E91" s="76"/>
       <c r="F91" s="74">
-        <f>-SALDOS!G126</f>
+        <f>-'Distribución por línea'!G126</f>
         <v>46084.86</v>
       </c>
     </row>
@@ -35539,8 +35229,7 @@
       </c>
       <c r="E92" s="76"/>
       <c r="F92" s="74">
-        <f>-SALDOS!G131</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G131</f>
       </c>
     </row>
     <row r="93" ht="10.95" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -35875,7 +35564,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="62">
-        <f>+-SALDOS!G142-SALDOS!G143</f>
+        <f>+-'Distribución por línea'!G142-'Distribución por línea'!G143</f>
         <v>-11494616744.130001</v>
       </c>
       <c r="K12" s="16">
@@ -36521,7 +36210,7 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="18">
-        <f>-SALDOS!G281-SALDOS!G150</f>
+        <f>-'Distribución por línea'!G281-'Distribución por línea'!G150</f>
         <v>-65017428.77</v>
       </c>
       <c r="D17" s="19"/>
@@ -36533,8 +36222,7 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="18">
-        <f>-SALDOS!G151-SALDOS!G152-SALDOS!G153</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G151-'Distribución por línea'!G152-'Distribución por línea'!G153</f>
       </c>
     </row>
     <row r="19" ht="11.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -36543,8 +36231,7 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="18">
-        <f>-SALDOS!G484</f>
-        <v>0</v>
+        <f>-'Distribución por línea'!G484</f>
       </c>
     </row>
     <row r="20" ht="11.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">

--- a/informe-c/base_pesos.xlsx
+++ b/informe-c/base_pesos.xlsx
@@ -4555,8 +4555,7 @@
       <c r="F10" s="124"/>
       <c r="G10" s="16"/>
       <c r="H10" s="19">
-        <f>+'Distribución por línea'!G323</f>
-        <v>56235551.05</v>
+        <f>+'Distribución por línea'!G335</f>
       </c>
       <c r="I10" s="125"/>
       <c r="J10" s="123"/>
@@ -4575,8 +4574,7 @@
         <v>283508619.32</v>
       </c>
       <c r="F11" s="124">
-        <f>+'Distribución por línea'!G369</f>
-        <v>283508619.32</v>
+        <f>+'Distribución por línea'!G385</f>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="19"/>
@@ -4599,8 +4597,7 @@
       <c r="F12" s="124"/>
       <c r="G12" s="16"/>
       <c r="H12" s="19">
-        <f>+'Distribución por línea'!G375</f>
-        <v>58572858.17</v>
+        <f>+'Distribución por línea'!G391</f>
       </c>
       <c r="I12" s="125"/>
       <c r="J12" s="123"/>
@@ -4621,7 +4618,7 @@
       <c r="F13" s="124"/>
       <c r="G13" s="16"/>
       <c r="H13" s="19">
-        <f>+'Distribución por línea'!G258</f>
+        <f>+'Distribución por línea'!G266</f>
       </c>
       <c r="I13" s="125"/>
       <c r="J13" s="123"/>
@@ -4642,8 +4639,7 @@
       <c r="F14" s="124"/>
       <c r="G14" s="16"/>
       <c r="H14" s="19">
-        <f>+'Distribución por línea'!G303</f>
-        <v>189946.28</v>
+        <f>+'Distribución por línea'!G314</f>
       </c>
       <c r="I14" s="125"/>
       <c r="J14" s="123"/>
@@ -4664,7 +4660,7 @@
       <c r="F15" s="124"/>
       <c r="G15" s="16"/>
       <c r="H15" s="19">
-        <f>+'Distribución por línea'!G403</f>
+        <f>+'Distribución por línea'!G421</f>
       </c>
       <c r="I15" s="125"/>
       <c r="J15" s="123"/>
@@ -4707,7 +4703,7 @@
       <c r="F17" s="124"/>
       <c r="G17" s="16"/>
       <c r="H17" s="19">
-        <f>+'Distribución por línea'!G315</f>
+        <f>+'Distribución por línea'!G326</f>
       </c>
       <c r="I17" s="125"/>
       <c r="J17" s="123"/>
@@ -4728,7 +4724,7 @@
       <c r="F18" s="124"/>
       <c r="G18" s="16"/>
       <c r="H18" s="19">
-        <f>+'Distribución por línea'!G359+'Distribución por línea'!G398</f>
+        <f>+'Distribución por línea'!G375+'Distribución por línea'!G416</f>
       </c>
       <c r="I18" s="125"/>
       <c r="J18" s="123"/>
@@ -4749,7 +4745,7 @@
       <c r="F19" s="124"/>
       <c r="G19" s="16"/>
       <c r="H19" s="19">
-        <f>+'Distribución por línea'!G362</f>
+        <f>+'Distribución por línea'!G378</f>
       </c>
       <c r="I19" s="125"/>
       <c r="J19" s="123"/>
@@ -4795,8 +4791,7 @@
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="19">
-        <f>+'Distribución por línea'!G425</f>
-        <v>63010431.79</v>
+        <f>+'Distribución por línea'!G445</f>
       </c>
       <c r="I21" s="125"/>
       <c r="J21" s="123"/>
@@ -4817,8 +4812,7 @@
       <c r="F22" s="124"/>
       <c r="G22" s="16"/>
       <c r="H22" s="19">
-        <f>+'Distribución por línea'!G307+'Distribución por línea'!G309+'Distribución por línea'!G310+'Distribución por línea'!G308</f>
-        <v>48607846.6</v>
+        <f>+'Distribución por línea'!G318+'Distribución por línea'!G320+'Distribución por línea'!G321+'Distribución por línea'!G319</f>
       </c>
       <c r="I22" s="125"/>
       <c r="J22" s="123"/>
@@ -4856,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="124">
-        <f>+'Distribución por línea'!G203</f>
+        <f>+'Distribución por línea'!G205</f>
       </c>
       <c r="G24" s="16"/>
       <c r="H24" s="19"/>
@@ -4879,8 +4873,7 @@
       <c r="F25" s="124"/>
       <c r="G25" s="16"/>
       <c r="H25" s="19">
-        <f>+'Distribución por línea'!G352</f>
-        <v>9880231.91</v>
+        <f>+'Distribución por línea'!G367</f>
       </c>
       <c r="I25" s="125"/>
       <c r="J25" s="123"/>
@@ -4901,8 +4894,7 @@
       <c r="F26" s="124"/>
       <c r="G26" s="16"/>
       <c r="H26" s="19">
-        <f>+'Distribución por línea'!G331</f>
-        <v>31296828.740000002</v>
+        <f>+'Distribución por línea'!G343</f>
       </c>
       <c r="I26" s="125"/>
       <c r="J26" s="123"/>
@@ -4940,8 +4932,7 @@
         <v>8552960.4</v>
       </c>
       <c r="F28" s="124">
-        <f>+'Distribución por línea'!G343+'Distribución por línea'!G496+'Distribución por línea'!G497</f>
-        <v>8552960.4</v>
+        <f>+'Distribución por línea'!G357+'Distribución por línea'!G518+'Distribución por línea'!G519</f>
       </c>
       <c r="G28" s="16"/>
       <c r="H28" s="19"/>
@@ -4983,7 +4974,7 @@
       <c r="F30" s="124"/>
       <c r="G30" s="16"/>
       <c r="H30" s="19">
-        <f>+'Distribución por línea'!G312</f>
+        <f>+'Distribución por línea'!G323</f>
       </c>
       <c r="I30" s="125"/>
       <c r="J30" s="123"/>
@@ -5002,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="124">
-        <f>+'Distribución por línea'!G240</f>
+        <f>+'Distribución por línea'!G245</f>
       </c>
       <c r="G31" s="16"/>
       <c r="H31" s="19"/>
@@ -5025,7 +5016,7 @@
       <c r="F32" s="124"/>
       <c r="G32" s="16"/>
       <c r="H32" s="19">
-        <f>+'Distribución por línea'!G440</f>
+        <f>+'Distribución por línea'!G460</f>
       </c>
       <c r="I32" s="125"/>
       <c r="J32" s="123"/>
@@ -5044,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="124">
-        <f>+'Distribución por línea'!G472</f>
+        <f>+'Distribución por línea'!G493</f>
       </c>
       <c r="G33" s="16"/>
       <c r="H33" s="19"/>
@@ -5065,8 +5056,7 @@
         <v>901685.37</v>
       </c>
       <c r="F34" s="126">
-        <f>+'Distribución por línea'!G407</f>
-        <v>901685.37</v>
+        <f>+'Distribución por línea'!G425</f>
       </c>
       <c r="G34" s="16"/>
       <c r="H34" s="19"/>
@@ -5087,8 +5077,7 @@
         <v>11129701.370000001</v>
       </c>
       <c r="F35" s="125">
-        <f>+'Distribución por línea'!G265</f>
-        <v>11129701.370000001</v>
+        <f>+'Distribución por línea'!G273</f>
       </c>
       <c r="G35" s="16"/>
       <c r="H35" s="16"/>
@@ -5114,8 +5103,7 @@
       </c>
       <c r="G36" s="16"/>
       <c r="H36" s="19">
-        <f>+'Distribución por línea'!G214+'Distribución por línea'!G394+'Distribución por línea'!G458</f>
-        <v>5930678.43</v>
+        <f>+'Distribución por línea'!G216+'Distribución por línea'!G411+'Distribución por línea'!G478</f>
       </c>
       <c r="I36" s="125"/>
       <c r="J36" s="123"/>
@@ -5134,8 +5122,7 @@
         <v>20016345.41</v>
       </c>
       <c r="F37" s="124">
-        <f>+'Distribución por línea'!G463</f>
-        <v>20016345.41</v>
+        <f>+'Distribución por línea'!G483</f>
       </c>
       <c r="G37" s="16"/>
       <c r="H37" s="19"/>
@@ -5158,7 +5145,7 @@
       <c r="F38" s="124"/>
       <c r="G38" s="16"/>
       <c r="H38" s="19">
-        <f>+'Distribución por línea'!G400+'Distribución por línea'!G441</f>
+        <f>+'Distribución por línea'!G418+'Distribución por línea'!G461</f>
       </c>
       <c r="I38" s="125"/>
       <c r="J38" s="123"/>
@@ -5179,8 +5166,7 @@
       <c r="F39" s="124"/>
       <c r="G39" s="16"/>
       <c r="H39" s="19">
-        <f>+'Distribución por línea'!G449</f>
-        <v>8441197.290000001</v>
+        <f>+'Distribución por línea'!G469</f>
       </c>
       <c r="I39" s="125"/>
       <c r="J39" s="123"/>
@@ -5199,8 +5185,7 @@
         <v>5964121.24</v>
       </c>
       <c r="F40" s="124">
-        <f>+'Distribución por línea'!G218</f>
-        <v>5964121.24</v>
+        <f>+'Distribución por línea'!G220</f>
       </c>
       <c r="G40" s="16"/>
       <c r="H40" s="19"/>
@@ -5221,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="124">
-        <f>+'Distribución por línea'!G239</f>
+        <f>+'Distribución por línea'!G244</f>
       </c>
       <c r="G41" s="16"/>
       <c r="H41" s="19"/>
@@ -5242,7 +5227,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="124">
-        <f>+'Distribución por línea'!G364</f>
+        <f>+'Distribución por línea'!G380</f>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="19"/>
@@ -5265,8 +5250,7 @@
       <c r="F43" s="124"/>
       <c r="G43" s="16"/>
       <c r="H43" s="19">
-        <f>+'Distribución por línea'!G316</f>
-        <v>18512.4</v>
+        <f>+'Distribución por línea'!G327</f>
       </c>
       <c r="I43" s="125"/>
       <c r="J43" s="123"/>
@@ -5287,7 +5271,7 @@
       <c r="F44" s="124"/>
       <c r="G44" s="16"/>
       <c r="H44" s="19">
-        <f>+'Distribución por línea'!G386</f>
+        <f>+'Distribución por línea'!G402</f>
       </c>
       <c r="I44" s="125"/>
       <c r="J44" s="123"/>
@@ -5328,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="124">
-        <f>+'Distribución por línea'!G460</f>
+        <f>+'Distribución por línea'!G480</f>
       </c>
       <c r="G46" s="16"/>
       <c r="H46" s="19"/>
@@ -5349,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="124">
-        <f>+'Distribución por línea'!G257</f>
+        <f>+'Distribución por línea'!G265</f>
       </c>
       <c r="G47" s="16"/>
       <c r="H47" s="19"/>
@@ -5372,8 +5356,7 @@
       <c r="F48" s="124"/>
       <c r="G48" s="16"/>
       <c r="H48" s="19">
-        <f>+'Distribución por línea'!G414</f>
-        <v>236115665.5</v>
+        <f>+'Distribución por línea'!G432</f>
       </c>
       <c r="I48" s="125"/>
       <c r="J48" s="123"/>
@@ -5392,7 +5375,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="124">
-        <f>+'Distribución por línea'!G234</f>
+        <f>+'Distribución por línea'!G238</f>
       </c>
       <c r="G49" s="16"/>
       <c r="H49" s="19"/>
@@ -5413,8 +5396,7 @@
         <v>14717993.67</v>
       </c>
       <c r="F50" s="124">
-        <f>+'Distribución por línea'!G453</f>
-        <v>14717993.67</v>
+        <f>+'Distribución por línea'!G473</f>
       </c>
       <c r="G50" s="16"/>
       <c r="H50" s="19"/>
@@ -5435,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="124">
-        <f>+'Distribución por línea'!G233</f>
+        <f>+'Distribución por línea'!G237</f>
       </c>
       <c r="G51" s="16"/>
       <c r="H51" s="19"/>
@@ -5456,13 +5438,11 @@
         <v>15921026</v>
       </c>
       <c r="F52" s="124">
-        <f>+'Distribución por línea'!G187+'Distribución por línea'!G231+'Distribución por línea'!G368+'Distribución por línea'!G387</f>
-        <v>39000</v>
+        <f>+'Distribución por línea'!G187+'Distribución por línea'!G234+'Distribución por línea'!G384+'Distribución por línea'!G403</f>
       </c>
       <c r="G52" s="16"/>
       <c r="H52" s="19">
-        <f>+'Distribución por línea'!G391</f>
-        <v>15882026</v>
+        <f>+'Distribución por línea'!G408</f>
       </c>
       <c r="I52" s="125"/>
       <c r="J52" s="123"/>
@@ -5483,8 +5463,7 @@
       <c r="F53" s="124"/>
       <c r="G53" s="16"/>
       <c r="H53" s="19">
-        <f>+'Distribución por línea'!G295</f>
-        <v>1099927.51</v>
+        <f>+'Distribución por línea'!G305</f>
       </c>
       <c r="I53" s="125"/>
       <c r="J53" s="123"/>
@@ -5505,7 +5484,7 @@
       <c r="F54" s="124"/>
       <c r="G54" s="16"/>
       <c r="H54" s="19">
-        <f>+'Distribución por línea'!G311</f>
+        <f>+'Distribución por línea'!G322</f>
       </c>
       <c r="I54" s="125"/>
       <c r="J54" s="123"/>
@@ -5567,8 +5546,7 @@
         <v>25426948.26</v>
       </c>
       <c r="F57" s="124">
-        <f>+'Distribución por línea'!G270</f>
-        <v>25426948.26</v>
+        <f>+'Distribución por línea'!G279</f>
       </c>
       <c r="G57" s="19"/>
       <c r="H57" s="16"/>
@@ -5589,8 +5567,7 @@
         <v>1884806.58</v>
       </c>
       <c r="F58" s="124">
-        <f>+'Distribución por línea'!G273+'Distribución por línea'!G283</f>
-        <v>1884806.58</v>
+        <f>+'Distribución por línea'!G282+'Distribución por línea'!G293</f>
       </c>
       <c r="G58" s="19"/>
       <c r="H58" s="16"/>
@@ -5611,8 +5588,7 @@
         <v>13001275.15</v>
       </c>
       <c r="F59" s="124">
-        <f>+'Distribución por línea'!G169+'Distribución por línea'!G284+'Distribución por línea'!G285+'Distribución por línea'!G494+'Distribución por línea'!F499</f>
-        <v>13001275.15</v>
+        <f>+'Distribución por línea'!G169+'Distribución por línea'!G294+'Distribución por línea'!G295+'Distribución por línea'!G516+'Distribución por línea'!F521</f>
       </c>
       <c r="G59" s="17"/>
       <c r="H59" s="16"/>
@@ -5633,8 +5609,7 @@
         <v>784842.52</v>
       </c>
       <c r="F60" s="124">
-        <f>+'Distribución por línea'!G426</f>
-        <v>784842.52</v>
+        <f>+'Distribución por línea'!G446</f>
       </c>
       <c r="G60" s="16"/>
       <c r="H60" s="19"/>
@@ -5657,7 +5632,7 @@
       <c r="F61" s="124"/>
       <c r="G61" s="16"/>
       <c r="H61" s="19">
-        <f>+'Distribución por línea'!G294</f>
+        <f>+'Distribución por línea'!G304</f>
       </c>
       <c r="I61" s="125"/>
       <c r="J61" s="123"/>
@@ -5676,8 +5651,7 @@
         <v>149263.11</v>
       </c>
       <c r="F62" s="124">
-        <f>+'Distribución por línea'!G247</f>
-        <v>149263.11</v>
+        <f>+'Distribución por línea'!G254</f>
       </c>
       <c r="G62" s="16"/>
       <c r="H62" s="19"/>
@@ -5698,13 +5672,11 @@
         <v>97742367</v>
       </c>
       <c r="F63" s="124">
-        <f>+'Distribución por línea'!G172+'Distribución por línea'!G339+'Distribución por línea'!G390+'Distribución por línea'!G340</f>
-        <v>1514958.41</v>
+        <f>+'Distribución por línea'!G172+'Distribución por línea'!G352+'Distribución por línea'!G407+'Distribución por línea'!G353</f>
       </c>
       <c r="G63" s="16"/>
       <c r="H63" s="19">
-        <f>+'Distribución por línea'!G319</f>
-        <v>96227408.59</v>
+        <f>+'Distribución por línea'!G331</f>
       </c>
       <c r="I63" s="125"/>
       <c r="J63" s="123"/>
@@ -5725,8 +5697,7 @@
       <c r="F64" s="124"/>
       <c r="G64" s="16"/>
       <c r="H64" s="19">
-        <f>+'Distribución por línea'!G244</f>
-        <v>143974.36000000002</v>
+        <f>+'Distribución por línea'!G250</f>
       </c>
       <c r="I64" s="125"/>
       <c r="J64" s="123"/>
@@ -5745,7 +5716,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="124">
-        <f>+'Distribución por línea'!G478</f>
+        <f>+'Distribución por línea'!G499</f>
       </c>
       <c r="G65" s="16"/>
       <c r="H65" s="19"/>
@@ -5785,8 +5756,7 @@
         <v>2052084.4000000001</v>
       </c>
       <c r="F67" s="124">
-        <f>+'Distribución por línea'!G227</f>
-        <v>2052084.4000000001</v>
+        <f>+'Distribución por línea'!G229</f>
       </c>
       <c r="G67" s="16"/>
       <c r="H67" s="19"/>
@@ -5828,7 +5798,7 @@
       <c r="F69" s="124"/>
       <c r="G69" s="16"/>
       <c r="H69" s="19">
-        <f>+'Distribución por línea'!G388</f>
+        <f>+'Distribución por línea'!G404</f>
       </c>
       <c r="I69" s="125"/>
       <c r="J69" s="123"/>
@@ -5866,7 +5836,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="124">
-        <f>+'Distribución por línea'!G235</f>
+        <f>+'Distribución por línea'!G239</f>
       </c>
       <c r="G71" s="16"/>
       <c r="H71" s="19"/>
@@ -5887,7 +5857,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="124">
-        <f>+'Distribución por línea'!G488</f>
+        <f>+'Distribución por línea'!G510</f>
       </c>
       <c r="G72" s="16"/>
       <c r="H72" s="19"/>
@@ -5908,8 +5878,7 @@
         <v>700000</v>
       </c>
       <c r="F73" s="124">
-        <f>+'Distribución por línea'!G209</f>
-        <v>700000</v>
+        <f>+'Distribución por línea'!G211</f>
       </c>
       <c r="G73" s="16"/>
       <c r="H73" s="19"/>
@@ -5930,8 +5899,7 @@
         <v>4714680.04</v>
       </c>
       <c r="F74" s="19">
-        <f>+'Distribución por línea'!G481</f>
-        <v>4714680.04</v>
+        <f>+'Distribución por línea'!G502</f>
       </c>
       <c r="G74" s="16"/>
       <c r="H74" s="19"/>
@@ -5952,7 +5920,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="125">
-        <f>+'Distribución por línea'!G206</f>
+        <f>+'Distribución por línea'!G208</f>
       </c>
       <c r="G75" s="16"/>
       <c r="H75" s="16"/>
@@ -5973,8 +5941,7 @@
         <v>17921832.18</v>
       </c>
       <c r="F76" s="124">
-        <f>+'Distribución por línea'!G435</f>
-        <v>17921832.18</v>
+        <f>+'Distribución por línea'!G455</f>
       </c>
       <c r="G76" s="16"/>
       <c r="H76" s="19"/>
@@ -5995,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="124">
-        <f>+'Distribución por línea'!G489</f>
+        <f>+'Distribución por línea'!G511</f>
       </c>
       <c r="G77" s="16"/>
       <c r="H77" s="19"/>
@@ -6018,7 +5985,7 @@
       <c r="F78" s="124"/>
       <c r="G78" s="16"/>
       <c r="H78" s="19">
-        <f>+'Distribución por línea'!G318</f>
+        <f>+'Distribución por línea'!G330</f>
       </c>
       <c r="I78" s="125"/>
       <c r="J78" s="123"/>
@@ -6039,7 +6006,7 @@
       <c r="F79" s="124"/>
       <c r="G79" s="16"/>
       <c r="H79" s="19">
-        <f>+'Distribución por línea'!G486</f>
+        <f>+'Distribución por línea'!G508</f>
       </c>
       <c r="I79" s="125"/>
       <c r="J79" s="123"/>
@@ -6060,8 +6027,7 @@
       <c r="F80" s="124"/>
       <c r="G80" s="16"/>
       <c r="H80" s="19">
-        <f>+'Distribución por línea'!G487</f>
-        <v>4150213.41</v>
+        <f>+'Distribución por línea'!G509</f>
       </c>
       <c r="I80" s="125"/>
       <c r="J80" s="123"/>
@@ -6085,8 +6051,7 @@
       </c>
       <c r="G81" s="16"/>
       <c r="H81" s="19">
-        <f>+'Distribución por línea'!G402</f>
-        <v>314486283.55</v>
+        <f>+'Distribución por línea'!G420</f>
       </c>
       <c r="I81" s="125"/>
       <c r="J81" s="123"/>
@@ -6105,12 +6070,11 @@
         <v>3799966.7</v>
       </c>
       <c r="F82" s="124">
-        <f>+'Distribución por línea'!G282+'Distribución por línea'!G198</f>
+        <f>+'Distribución por línea'!G292+'Distribución por línea'!G198</f>
       </c>
       <c r="G82" s="16"/>
       <c r="H82" s="19">
-        <f>+'Distribución por línea'!G417</f>
-        <v>3799966.7</v>
+        <f>+'Distribución por línea'!G436</f>
       </c>
       <c r="I82" s="125"/>
       <c r="J82" s="123"/>
@@ -6152,7 +6116,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="124">
-        <f>+'Distribución por línea'!G264</f>
+        <f>+'Distribución por línea'!G272</f>
       </c>
       <c r="G84" s="16"/>
       <c r="H84" s="19"/>
@@ -6173,7 +6137,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="124">
-        <f>+'Distribución por línea'!G385</f>
+        <f>+'Distribución por línea'!G401</f>
       </c>
       <c r="G85" s="16"/>
       <c r="H85" s="19"/>
@@ -6194,7 +6158,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="124">
-        <f>+'Distribución por línea'!G246</f>
+        <f>+'Distribución por línea'!G253</f>
       </c>
       <c r="G86" s="16"/>
       <c r="H86" s="19"/>
@@ -6238,7 +6202,7 @@
       <c r="F88" s="16"/>
       <c r="G88" s="16"/>
       <c r="H88" s="19">
-        <f>+'Distribución por línea'!G416</f>
+        <f>+'Distribución por línea'!G435</f>
       </c>
       <c r="I88" s="125"/>
       <c r="J88" s="123"/>
@@ -6257,8 +6221,7 @@
         <v>101483.28</v>
       </c>
       <c r="F89" s="16">
-        <f>+'Distribución por línea'!G444</f>
-        <v>101483.28</v>
+        <f>+'Distribución por línea'!G464</f>
       </c>
       <c r="G89" s="16"/>
       <c r="H89" s="19"/>
@@ -6281,7 +6244,7 @@
       <c r="F90" s="16"/>
       <c r="G90" s="16"/>
       <c r="H90" s="19">
-        <f>+'Distribución por línea'!G476</f>
+        <f>+'Distribución por línea'!G497</f>
       </c>
       <c r="I90" s="125"/>
       <c r="J90" s="123"/>
@@ -6341,8 +6304,7 @@
       <c r="F93" s="16"/>
       <c r="G93" s="16"/>
       <c r="H93" s="19">
-        <f>+'Distribución por línea'!G490</f>
-        <v>226987</v>
+        <f>+'Distribución por línea'!G512</f>
       </c>
       <c r="I93" s="125"/>
       <c r="J93" s="123"/>
@@ -6363,8 +6325,7 @@
       <c r="F94" s="16"/>
       <c r="G94" s="16"/>
       <c r="H94" s="19">
-        <f>+'Distribución por línea'!G491+'Distribución por línea'!G492</f>
-        <v>914304.7000000001</v>
+        <f>+'Distribución por línea'!G513+'Distribución por línea'!G514</f>
       </c>
       <c r="I94" s="125"/>
       <c r="J94" s="123"/>
@@ -6383,8 +6344,7 @@
         <v>-3402540.6600000006</v>
       </c>
       <c r="F95" s="16">
-        <f>+'Distribución por línea'!G201</f>
-        <v>-3402540.6600000006</v>
+        <f>+'Distribución por línea'!G202</f>
       </c>
       <c r="G95" s="16"/>
       <c r="H95" s="19"/>
@@ -6407,7 +6367,7 @@
       <c r="F96" s="16"/>
       <c r="G96" s="16"/>
       <c r="H96" s="19">
-        <f>+'Distribución por línea'!G495</f>
+        <f>+'Distribución por línea'!G517</f>
       </c>
       <c r="I96" s="125"/>
       <c r="J96" s="123"/>
@@ -6428,7 +6388,7 @@
       <c r="F97" s="16"/>
       <c r="G97" s="16"/>
       <c r="H97" s="19">
-        <f>+'Distribución por línea'!F493</f>
+        <f>+'Distribución por línea'!F515</f>
       </c>
       <c r="I97" s="125"/>
       <c r="J97" s="123"/>
@@ -6449,7 +6409,7 @@
       <c r="F98" s="16"/>
       <c r="G98" s="16"/>
       <c r="H98" s="19">
-        <f>+'Distribución por línea'!G498</f>
+        <f>+'Distribución por línea'!G520</f>
       </c>
       <c r="I98" s="125"/>
       <c r="J98" s="123"/>
@@ -6470,7 +6430,7 @@
       <c r="F99" s="16"/>
       <c r="G99" s="16"/>
       <c r="H99" s="19">
-        <f>+'Distribución por línea'!G500</f>
+        <f>+'Distribución por línea'!G522</f>
       </c>
       <c r="I99" s="125"/>
       <c r="J99" s="123"/>
@@ -6491,7 +6451,7 @@
       <c r="F100" s="16"/>
       <c r="G100" s="16"/>
       <c r="H100" s="19">
-        <f>+'Distribución por línea'!G501</f>
+        <f>+'Distribución por línea'!G523</f>
       </c>
       <c r="I100" s="125"/>
       <c r="J100" s="123"/>
@@ -6512,7 +6472,7 @@
       <c r="F101" s="16"/>
       <c r="G101" s="16"/>
       <c r="H101" s="19">
-        <f>+'Distribución por línea'!G502</f>
+        <f>+'Distribución por línea'!G524</f>
       </c>
       <c r="I101" s="125"/>
       <c r="J101" s="123"/>
@@ -6533,7 +6493,7 @@
       <c r="F102" s="16"/>
       <c r="G102" s="16"/>
       <c r="H102" s="19">
-        <f>+'Distribución por línea'!G503</f>
+        <f>+'Distribución por línea'!G525</f>
       </c>
       <c r="I102" s="125"/>
       <c r="J102" s="123"/>
@@ -7527,7 +7487,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1921"/>
+  <dimension ref="A1:O1943"/>
   <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11.44140625" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="76" customWidth="1"/>
@@ -10861,31 +10821,19 @@
       <c r="D198" s="139" t="s">
         <v>519</v>
       </c>
-      <c r="E198" s="72" t="s">
+      <c r="E198" s="72"/>
+      <c r="F198" s="140"/>
+      <c r="G198" s="138">
+        <f>+F199+F200+F201</f>
+      </c>
+    </row>
+    <row r="199" ht="12.75" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="E199" s="72" t="s">
         <v>520</v>
-      </c>
-      <c r="F198" s="140">
-        <f>IFERROR(VLOOKUP(E198,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G198" s="138">
-        <f>+F198+F199+F200</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="137"/>
-      <c r="B199" s="137"/>
-      <c r="C199" s="139"/>
-      <c r="D199" s="139"/>
-      <c r="E199" s="72" t="s">
-        <v>521</v>
       </c>
       <c r="F199" s="140">
         <f>IFERROR(VLOOKUP(E199,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G199" s="138"/>
-      <c r="H199" s="72"/>
-      <c r="I199" s="164"/>
     </row>
     <row r="200" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="137"/>
@@ -10893,7 +10841,7 @@
       <c r="C200" s="139"/>
       <c r="D200" s="139"/>
       <c r="E200" s="72" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F200" s="140">
         <f>IFERROR(VLOOKUP(E200,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -10906,20 +10854,14 @@
       <c r="A201" s="137"/>
       <c r="B201" s="137"/>
       <c r="C201" s="139"/>
-      <c r="D201" s="139" t="s">
-        <v>523</v>
-      </c>
+      <c r="D201" s="139"/>
       <c r="E201" s="72" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F201" s="140">
         <f>IFERROR(VLOOKUP(E201,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>-6355001.390000001</v>
-      </c>
-      <c r="G201" s="187">
-        <f>SUM(F201:F202)</f>
-        <v>-3402540.6600000006</v>
-      </c>
+      </c>
+      <c r="G201" s="138"/>
       <c r="H201" s="72"/>
       <c r="I201" s="164"/>
     </row>
@@ -10927,94 +10869,90 @@
       <c r="A202" s="137"/>
       <c r="B202" s="137"/>
       <c r="C202" s="139"/>
-      <c r="D202" s="139"/>
-      <c r="E202" s="72" t="s">
-        <v>525</v>
-      </c>
-      <c r="F202" s="140">
-        <f>IFERROR(VLOOKUP(E202,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>2952460.73</v>
-      </c>
-      <c r="G202" s="138"/>
+      <c r="D202" s="139" t="s">
+        <v>523</v>
+      </c>
+      <c r="E202" s="72"/>
+      <c r="F202" s="140"/>
+      <c r="G202" s="187">
+        <f>SUM(F203:F204)</f>
+      </c>
       <c r="H202" s="72"/>
       <c r="I202" s="164"/>
     </row>
-    <row r="203" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="137"/>
-      <c r="B203" s="137"/>
-      <c r="C203" s="139"/>
-      <c r="D203" s="71" t="s">
-        <v>526</v>
-      </c>
-      <c r="E203" s="188"/>
-      <c r="F203" s="140"/>
-      <c r="G203" s="138">
-        <f>+F203</f>
-        <v>0</v>
-      </c>
-      <c r="H203" s="132"/>
-      <c r="I203" s="134"/>
-      <c r="J203" s="72"/>
-      <c r="K203" s="72"/>
-      <c r="L203" s="72"/>
-      <c r="M203" s="72"/>
-      <c r="N203" s="72"/>
+    <row r="203" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="76"/>
+      <c r="B203" s="76"/>
+      <c r="C203" s="34"/>
+      <c r="D203" s="132"/>
+      <c r="E203" s="72" t="s">
+        <v>524</v>
+      </c>
+      <c r="F203" s="140">
+        <f>IFERROR(VLOOKUP(E203,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
     </row>
     <row r="204" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="137"/>
       <c r="B204" s="137"/>
       <c r="C204" s="139"/>
-      <c r="D204" s="71" t="s">
-        <v>527</v>
-      </c>
+      <c r="D204" s="139"/>
       <c r="E204" s="72" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="F204" s="140">
         <f>IFERROR(VLOOKUP(E204,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>4349389.08</v>
-      </c>
-      <c r="G204" s="187">
-        <f>+F204</f>
-        <v>4349389.08</v>
-      </c>
+      </c>
+      <c r="G204" s="138"/>
       <c r="H204" s="72"/>
       <c r="I204" s="164"/>
     </row>
-    <row r="205" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" s="137"/>
       <c r="B205" s="137"/>
       <c r="C205" s="139"/>
-      <c r="D205" s="71"/>
-      <c r="E205" s="71" t="s">
-        <v>527</v>
-      </c>
-      <c r="F205" s="140">
-        <f>IFERROR(VLOOKUP(E205,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G205" s="138"/>
-    </row>
-    <row r="206" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D205" s="71" t="s">
+        <v>526</v>
+      </c>
+      <c r="E205" s="188"/>
+      <c r="F205" s="140"/>
+      <c r="G205" s="138">
+        <f>+F205</f>
+      </c>
+      <c r="H205" s="132"/>
+      <c r="I205" s="134"/>
+      <c r="J205" s="72"/>
+      <c r="K205" s="72"/>
+      <c r="L205" s="72"/>
+      <c r="M205" s="72"/>
+      <c r="N205" s="72"/>
+    </row>
+    <row r="206" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="137"/>
       <c r="B206" s="137"/>
       <c r="C206" s="139"/>
       <c r="D206" s="71" t="s">
-        <v>529</v>
-      </c>
-      <c r="E206" s="188"/>
-      <c r="F206" s="140"/>
-      <c r="G206" s="138">
-        <f>+F207</f>
-        <v>0</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="E206" s="72" t="s">
+        <v>528</v>
+      </c>
+      <c r="F206" s="140">
+        <f>IFERROR(VLOOKUP(E206,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G206" s="187">
+        <f>+F206</f>
+      </c>
+      <c r="H206" s="72"/>
+      <c r="I206" s="164"/>
     </row>
     <row r="207" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="137"/>
       <c r="B207" s="137"/>
       <c r="C207" s="139"/>
       <c r="D207" s="71"/>
-      <c r="E207" s="72" t="s">
-        <v>530</v>
+      <c r="E207" s="71" t="s">
+        <v>527</v>
       </c>
       <c r="F207" s="140">
         <f>IFERROR(VLOOKUP(E207,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11025,72 +10963,66 @@
       <c r="A208" s="137"/>
       <c r="B208" s="137"/>
       <c r="C208" s="139"/>
-      <c r="D208" s="71"/>
-      <c r="E208" s="188" t="s">
-        <v>531</v>
-      </c>
-      <c r="F208" s="140">
-        <f>IFERROR(VLOOKUP(E208,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G208" s="138"/>
+      <c r="D208" s="71" t="s">
+        <v>529</v>
+      </c>
+      <c r="E208" s="188"/>
+      <c r="F208" s="140"/>
+      <c r="G208" s="138">
+        <f>+F209</f>
+      </c>
     </row>
     <row r="209" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" s="137"/>
       <c r="B209" s="137"/>
       <c r="C209" s="139"/>
-      <c r="D209" s="71" t="s">
-        <v>532</v>
-      </c>
-      <c r="E209" s="188"/>
-      <c r="F209" s="140"/>
-      <c r="G209" s="138">
-        <f>SUM(F210:F213)</f>
-        <v>700000</v>
-      </c>
+      <c r="D209" s="71"/>
+      <c r="E209" s="72" t="s">
+        <v>530</v>
+      </c>
+      <c r="F209" s="140">
+        <f>IFERROR(VLOOKUP(E209,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G209" s="138"/>
     </row>
     <row r="210" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" s="137"/>
       <c r="B210" s="137"/>
       <c r="C210" s="139"/>
       <c r="D210" s="71"/>
-      <c r="E210" s="72" t="s">
-        <v>533</v>
+      <c r="E210" s="188" t="s">
+        <v>531</v>
       </c>
       <c r="F210" s="140">
         <f>IFERROR(VLOOKUP(E210,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G210" s="138"/>
     </row>
-    <row r="211" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" s="137"/>
       <c r="B211" s="137"/>
       <c r="C211" s="139"/>
-      <c r="D211" s="71"/>
-      <c r="E211" s="72" t="s">
-        <v>534</v>
-      </c>
-      <c r="F211" s="140">
-        <f>IFERROR(VLOOKUP(E211,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>700000</v>
-      </c>
-      <c r="G211" s="138"/>
-      <c r="H211" s="72"/>
-      <c r="I211" s="164"/>
-    </row>
-    <row r="212" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D211" s="71" t="s">
+        <v>532</v>
+      </c>
+      <c r="E211" s="188"/>
+      <c r="F211" s="140"/>
+      <c r="G211" s="138">
+        <f>SUM(F212:F215)</f>
+      </c>
+    </row>
+    <row r="212" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" s="137"/>
       <c r="B212" s="137"/>
       <c r="C212" s="139"/>
       <c r="D212" s="71"/>
       <c r="E212" s="72" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F212" s="140">
         <f>IFERROR(VLOOKUP(E212,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G212" s="138"/>
-      <c r="H212" s="72"/>
-      <c r="I212" s="164"/>
     </row>
     <row r="213" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="137"/>
@@ -11098,7 +11030,7 @@
       <c r="C213" s="139"/>
       <c r="D213" s="71"/>
       <c r="E213" s="72" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F213" s="140">
         <f>IFERROR(VLOOKUP(E213,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11107,48 +11039,48 @@
       <c r="H213" s="72"/>
       <c r="I213" s="164"/>
     </row>
-    <row r="214" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="137"/>
       <c r="B214" s="137"/>
       <c r="C214" s="139"/>
-      <c r="D214" s="71" t="s">
-        <v>537</v>
-      </c>
-      <c r="E214" s="188"/>
-      <c r="F214" s="140"/>
-      <c r="G214" s="187">
-        <f>SUM(F214:F217)</f>
-        <v>332121.43</v>
-      </c>
-      <c r="H214" s="150"/>
-    </row>
-    <row r="215" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D214" s="71"/>
+      <c r="E214" s="72" t="s">
+        <v>535</v>
+      </c>
+      <c r="F214" s="140">
+        <f>IFERROR(VLOOKUP(E214,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G214" s="138"/>
+      <c r="H214" s="72"/>
+      <c r="I214" s="164"/>
+    </row>
+    <row r="215" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="137"/>
       <c r="B215" s="137"/>
       <c r="C215" s="139"/>
       <c r="D215" s="71"/>
       <c r="E215" s="72" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F215" s="140">
         <f>IFERROR(VLOOKUP(E215,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>332121.43</v>
       </c>
       <c r="G215" s="138"/>
-      <c r="H215" s="150"/>
+      <c r="H215" s="72"/>
+      <c r="I215" s="164"/>
     </row>
     <row r="216" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="137"/>
       <c r="B216" s="137"/>
       <c r="C216" s="139"/>
-      <c r="D216" s="71"/>
-      <c r="E216" s="72" t="s">
-        <v>539</v>
-      </c>
-      <c r="F216" s="140">
-        <f>IFERROR(VLOOKUP(E216,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G216" s="138"/>
+      <c r="D216" s="71" t="s">
+        <v>537</v>
+      </c>
+      <c r="E216" s="188"/>
+      <c r="F216" s="140"/>
+      <c r="G216" s="187">
+        <f>SUM(F216:F219)</f>
+      </c>
       <c r="H216" s="150"/>
     </row>
     <row r="217" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -11157,7 +11089,7 @@
       <c r="C217" s="139"/>
       <c r="D217" s="71"/>
       <c r="E217" s="72" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F217" s="140">
         <f>IFERROR(VLOOKUP(E217,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11165,53 +11097,53 @@
       <c r="G217" s="138"/>
       <c r="H217" s="150"/>
     </row>
-    <row r="218" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="137"/>
       <c r="B218" s="137"/>
       <c r="C218" s="139"/>
-      <c r="D218" s="71" t="s">
-        <v>541</v>
-      </c>
-      <c r="E218" s="188"/>
-      <c r="F218" s="140"/>
-      <c r="G218" s="187">
-        <f>SUM(F218:F225)</f>
-        <v>5964121.24</v>
-      </c>
-      <c r="H218" s="132"/>
-      <c r="I218" s="134"/>
-      <c r="J218" s="72"/>
-      <c r="K218" s="72"/>
-      <c r="L218" s="72"/>
-      <c r="M218" s="72"/>
-      <c r="N218" s="72"/>
-    </row>
-    <row r="219" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D218" s="71"/>
+      <c r="E218" s="72" t="s">
+        <v>539</v>
+      </c>
+      <c r="F218" s="140">
+        <f>IFERROR(VLOOKUP(E218,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G218" s="138"/>
+      <c r="H218" s="150"/>
+    </row>
+    <row r="219" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="137"/>
       <c r="B219" s="137"/>
       <c r="C219" s="139"/>
       <c r="D219" s="71"/>
       <c r="E219" s="72" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F219" s="140">
         <f>IFERROR(VLOOKUP(E219,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G219" s="138"/>
-    </row>
-    <row r="220" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H219" s="150"/>
+    </row>
+    <row r="220" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" s="137"/>
       <c r="B220" s="137"/>
       <c r="C220" s="139"/>
-      <c r="D220" s="71"/>
-      <c r="E220" s="72" t="s">
-        <v>543</v>
-      </c>
-      <c r="F220" s="140">
-        <f>IFERROR(VLOOKUP(E220,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>3946013.02</v>
-      </c>
-      <c r="G220" s="138"/>
+      <c r="D220" s="71" t="s">
+        <v>541</v>
+      </c>
+      <c r="E220" s="188"/>
+      <c r="F220" s="140"/>
+      <c r="G220" s="187">
+        <f>SUM(F220:F227)</f>
+      </c>
+      <c r="H220" s="132"/>
+      <c r="I220" s="134"/>
+      <c r="J220" s="72"/>
+      <c r="K220" s="72"/>
+      <c r="L220" s="72"/>
+      <c r="M220" s="72"/>
+      <c r="N220" s="72"/>
     </row>
     <row r="221" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" s="137"/>
@@ -11219,7 +11151,7 @@
       <c r="C221" s="139"/>
       <c r="D221" s="71"/>
       <c r="E221" s="72" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F221" s="140">
         <f>IFERROR(VLOOKUP(E221,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11232,11 +11164,10 @@
       <c r="C222" s="139"/>
       <c r="D222" s="71"/>
       <c r="E222" s="72" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F222" s="140">
         <f>IFERROR(VLOOKUP(E222,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1836290.04</v>
       </c>
       <c r="G222" s="138"/>
     </row>
@@ -11246,51 +11177,50 @@
       <c r="C223" s="139"/>
       <c r="D223" s="71"/>
       <c r="E223" s="72" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F223" s="140">
         <f>IFERROR(VLOOKUP(E223,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G223" s="138"/>
     </row>
-    <row r="224" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" s="137"/>
       <c r="B224" s="137"/>
       <c r="C224" s="139"/>
       <c r="D224" s="71"/>
       <c r="E224" s="72" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F224" s="140">
         <f>IFERROR(VLOOKUP(E224,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>181818.18</v>
       </c>
       <c r="G224" s="138"/>
-      <c r="H224" s="72"/>
-      <c r="I224" s="164"/>
-    </row>
-    <row r="225" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" s="137"/>
       <c r="B225" s="137"/>
       <c r="C225" s="139"/>
       <c r="D225" s="71"/>
       <c r="E225" s="72" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F225" s="140">
         <f>IFERROR(VLOOKUP(E225,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G225" s="138"/>
-      <c r="H225" s="72"/>
-      <c r="I225" s="164"/>
     </row>
     <row r="226" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="137"/>
       <c r="B226" s="137"/>
       <c r="C226" s="139"/>
       <c r="D226" s="71"/>
-      <c r="E226" s="72"/>
-      <c r="F226" s="140"/>
+      <c r="E226" s="72" t="s">
+        <v>547</v>
+      </c>
+      <c r="F226" s="140">
+        <f>IFERROR(VLOOKUP(E226,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
       <c r="G226" s="138"/>
       <c r="H226" s="72"/>
       <c r="I226" s="164"/>
@@ -11299,342 +11229,297 @@
       <c r="A227" s="137"/>
       <c r="B227" s="137"/>
       <c r="C227" s="139"/>
-      <c r="D227" s="71" t="s">
-        <v>549</v>
-      </c>
+      <c r="D227" s="71"/>
       <c r="E227" s="72" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F227" s="140">
         <f>IFERROR(VLOOKUP(E227,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>2052084.4000000001</v>
-      </c>
-      <c r="G227" s="187">
-        <f>SUM(F227:F229)</f>
-        <v>2052084.4000000001</v>
-      </c>
+      </c>
+      <c r="G227" s="138"/>
       <c r="H227" s="72"/>
       <c r="I227" s="164"/>
     </row>
-    <row r="228" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="228" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="137"/>
       <c r="B228" s="137"/>
       <c r="C228" s="139"/>
       <c r="D228" s="71"/>
-      <c r="E228" s="72" t="s">
-        <v>551</v>
-      </c>
-      <c r="F228" s="140">
-        <f>IFERROR(VLOOKUP(E228,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+      <c r="E228" s="72"/>
+      <c r="F228" s="140"/>
       <c r="G228" s="138"/>
       <c r="H228" s="72"/>
       <c r="I228" s="164"/>
-      <c r="J228" s="72"/>
-      <c r="K228" s="72"/>
-      <c r="L228" s="72"/>
-    </row>
-    <row r="229" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="137"/>
       <c r="B229" s="137"/>
       <c r="C229" s="139"/>
-      <c r="D229" s="71"/>
-      <c r="E229" s="72" t="s">
-        <v>552</v>
-      </c>
-      <c r="F229" s="140">
-        <f>IFERROR(VLOOKUP(E229,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G229" s="138"/>
+      <c r="D229" s="71" t="s">
+        <v>549</v>
+      </c>
+      <c r="E229" s="72"/>
+      <c r="F229" s="140"/>
+      <c r="G229" s="187">
+        <f>SUM(F230:F232)</f>
+      </c>
       <c r="H229" s="72"/>
       <c r="I229" s="164"/>
-      <c r="J229" s="72"/>
-      <c r="K229" s="72"/>
-      <c r="L229" s="72"/>
-    </row>
-    <row r="230" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A230" s="137"/>
-      <c r="B230" s="137"/>
-      <c r="C230" s="139"/>
-      <c r="D230" s="71"/>
-      <c r="E230" s="72"/>
-      <c r="F230" s="140"/>
-      <c r="G230" s="138"/>
-      <c r="H230" s="72"/>
-      <c r="I230" s="164"/>
-      <c r="J230" s="72"/>
-      <c r="K230" s="72"/>
-      <c r="L230" s="72"/>
-    </row>
-    <row r="231" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" s="76"/>
+      <c r="B230" s="76"/>
+      <c r="C230" s="34"/>
+      <c r="D230" s="132"/>
+      <c r="E230" s="72" t="s">
+        <v>550</v>
+      </c>
+      <c r="F230" s="140">
+        <f>IFERROR(VLOOKUP(E230,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+    </row>
+    <row r="231" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A231" s="137"/>
       <c r="B231" s="137"/>
       <c r="C231" s="139"/>
-      <c r="D231" s="71" t="s">
-        <v>553</v>
-      </c>
+      <c r="D231" s="71"/>
       <c r="E231" s="72" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F231" s="140">
         <f>IFERROR(VLOOKUP(E231,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>39000</v>
-      </c>
-      <c r="G231" s="138">
-        <f>SUM(F231:F232)</f>
-        <v>39000</v>
-      </c>
-    </row>
-    <row r="232" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      </c>
+      <c r="G231" s="138"/>
+      <c r="H231" s="72"/>
+      <c r="I231" s="164"/>
+      <c r="J231" s="72"/>
+      <c r="K231" s="72"/>
+      <c r="L231" s="72"/>
+    </row>
+    <row r="232" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A232" s="137"/>
       <c r="B232" s="137"/>
       <c r="C232" s="139"/>
       <c r="D232" s="71"/>
       <c r="E232" s="72" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="F232" s="140">
         <f>IFERROR(VLOOKUP(E232,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G232" s="138"/>
-    </row>
-    <row r="233" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H232" s="72"/>
+      <c r="I232" s="164"/>
+      <c r="J232" s="72"/>
+      <c r="K232" s="72"/>
+      <c r="L232" s="72"/>
+    </row>
+    <row r="233" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A233" s="137"/>
       <c r="B233" s="137"/>
       <c r="C233" s="139"/>
-      <c r="D233" s="71" t="s">
-        <v>556</v>
-      </c>
-      <c r="E233" s="71"/>
+      <c r="D233" s="71"/>
+      <c r="E233" s="72"/>
       <c r="F233" s="140"/>
-      <c r="G233" s="138">
-        <f>+F233</f>
-        <v>0</v>
-      </c>
+      <c r="G233" s="138"/>
+      <c r="H233" s="72"/>
+      <c r="I233" s="164"/>
+      <c r="J233" s="72"/>
+      <c r="K233" s="72"/>
+      <c r="L233" s="72"/>
     </row>
     <row r="234" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" s="137"/>
       <c r="B234" s="137"/>
       <c r="C234" s="139"/>
       <c r="D234" s="71" t="s">
-        <v>557</v>
-      </c>
-      <c r="E234" s="71"/>
+        <v>553</v>
+      </c>
+      <c r="E234" s="72"/>
       <c r="F234" s="140"/>
       <c r="G234" s="138">
-        <f>+F234</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="235" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="137"/>
-      <c r="B235" s="137"/>
-      <c r="C235" s="139"/>
-      <c r="D235" s="71" t="s">
-        <v>558</v>
-      </c>
+        <f>SUM(F235:F236)</f>
+      </c>
+    </row>
+    <row r="235" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" s="76"/>
+      <c r="B235" s="76"/>
+      <c r="C235" s="34"/>
+      <c r="D235" s="132"/>
       <c r="E235" s="72" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="F235" s="140">
         <f>IFERROR(VLOOKUP(E235,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G235" s="138">
-        <f>+SUM(F235:F238)</f>
-        <v>0</v>
-      </c>
-      <c r="H235" s="72"/>
-      <c r="I235" s="164"/>
-    </row>
-    <row r="236" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" s="137"/>
       <c r="B236" s="137"/>
       <c r="C236" s="139"/>
       <c r="D236" s="71"/>
       <c r="E236" s="72" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="F236" s="140">
         <f>IFERROR(VLOOKUP(E236,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G236" s="138"/>
-      <c r="H236" s="72"/>
-      <c r="I236" s="164"/>
-    </row>
-    <row r="237" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" s="137"/>
       <c r="B237" s="137"/>
       <c r="C237" s="139"/>
-      <c r="D237" s="71"/>
-      <c r="E237" s="72" t="s">
-        <v>561</v>
-      </c>
-      <c r="F237" s="140">
-        <f>IFERROR(VLOOKUP(E237,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G237" s="138"/>
-      <c r="H237" s="72"/>
-      <c r="I237" s="164"/>
-    </row>
-    <row r="238" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D237" s="71" t="s">
+        <v>556</v>
+      </c>
+      <c r="E237" s="71"/>
+      <c r="F237" s="140"/>
+      <c r="G237" s="138">
+        <f>+F237</f>
+      </c>
+    </row>
+    <row r="238" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" s="137"/>
       <c r="B238" s="137"/>
       <c r="C238" s="139"/>
-      <c r="D238" s="71"/>
-      <c r="E238" s="72"/>
-      <c r="F238" s="140">
-        <f>IFERROR(VLOOKUP(E238,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G238" s="138"/>
-      <c r="H238" s="72"/>
-      <c r="I238" s="164"/>
-    </row>
-    <row r="239" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D238" s="71" t="s">
+        <v>557</v>
+      </c>
+      <c r="E238" s="71"/>
+      <c r="F238" s="140"/>
+      <c r="G238" s="138">
+        <f>+F238</f>
+      </c>
+    </row>
+    <row r="239" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="137"/>
       <c r="B239" s="137"/>
       <c r="C239" s="139"/>
       <c r="D239" s="71" t="s">
-        <v>562</v>
-      </c>
-      <c r="E239" s="71"/>
+        <v>558</v>
+      </c>
+      <c r="E239" s="72"/>
       <c r="F239" s="140"/>
       <c r="G239" s="138">
-        <f>+F239</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A240" s="137"/>
-      <c r="B240" s="137"/>
-      <c r="C240" s="139"/>
-      <c r="D240" s="71" t="s">
-        <v>563</v>
-      </c>
-      <c r="E240" s="71" t="s">
-        <v>564</v>
+        <f>+SUM(F240:F243)</f>
+      </c>
+      <c r="H239" s="72"/>
+      <c r="I239" s="164"/>
+    </row>
+    <row r="240" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" s="76"/>
+      <c r="B240" s="76"/>
+      <c r="C240" s="34"/>
+      <c r="D240" s="132"/>
+      <c r="E240" s="72" t="s">
+        <v>559</v>
       </c>
       <c r="F240" s="140">
         <f>IFERROR(VLOOKUP(E240,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G240" s="138">
-        <f>SUM(F240:F243)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="241" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="137"/>
       <c r="B241" s="137"/>
       <c r="C241" s="139"/>
       <c r="D241" s="71"/>
       <c r="E241" s="72" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F241" s="140">
         <f>IFERROR(VLOOKUP(E241,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G241" s="138"/>
-    </row>
-    <row r="242" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H241" s="72"/>
+      <c r="I241" s="164"/>
+    </row>
+    <row r="242" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="137"/>
       <c r="B242" s="137"/>
       <c r="C242" s="139"/>
       <c r="D242" s="71"/>
-      <c r="E242" s="151" t="s">
-        <v>566</v>
+      <c r="E242" s="72" t="s">
+        <v>561</v>
       </c>
       <c r="F242" s="140">
         <f>IFERROR(VLOOKUP(E242,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G242" s="138"/>
-    </row>
-    <row r="243" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H242" s="72"/>
+      <c r="I242" s="164"/>
+    </row>
+    <row r="243" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="137"/>
       <c r="B243" s="137"/>
       <c r="C243" s="139"/>
       <c r="D243" s="71"/>
-      <c r="E243" s="151" t="s">
-        <v>567</v>
-      </c>
+      <c r="E243" s="72"/>
       <c r="F243" s="140">
-        <f>IFERROR(VLOOKUP(E243,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(E243,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G243" s="138"/>
-    </row>
-    <row r="244" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H243" s="72"/>
+      <c r="I243" s="164"/>
+    </row>
+    <row r="244" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" s="137"/>
       <c r="B244" s="137"/>
       <c r="C244" s="139"/>
       <c r="D244" s="71" t="s">
-        <v>568</v>
-      </c>
-      <c r="E244" s="72" t="s">
-        <v>569</v>
-      </c>
-      <c r="F244" s="140">
-        <f>IFERROR(VLOOKUP(E244,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>143974.36000000002</v>
-      </c>
-      <c r="G244" s="187">
-        <f>+F244+F245</f>
-        <v>143974.36000000002</v>
-      </c>
-      <c r="H244" s="72"/>
-      <c r="I244" s="164"/>
-    </row>
-    <row r="245" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+      <c r="E244" s="71"/>
+      <c r="F244" s="140"/>
+      <c r="G244" s="138">
+        <f>+F244</f>
+      </c>
+    </row>
+    <row r="245" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" s="137"/>
       <c r="B245" s="137"/>
       <c r="C245" s="139"/>
-      <c r="D245" s="71"/>
-      <c r="E245" s="72" t="s">
-        <v>570</v>
-      </c>
-      <c r="F245" s="140">
-        <f>IFERROR(VLOOKUP(E245,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G245" s="138"/>
-      <c r="H245" s="72"/>
-      <c r="I245" s="164"/>
-    </row>
-    <row r="246" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A246" s="137"/>
-      <c r="B246" s="137"/>
-      <c r="C246" s="139"/>
-      <c r="D246" s="71" t="s">
-        <v>571</v>
-      </c>
-      <c r="E246" s="71"/>
-      <c r="F246" s="140"/>
-      <c r="G246" s="138">
-        <f>+F246</f>
-        <v>0</v>
+      <c r="D245" s="71" t="s">
+        <v>563</v>
+      </c>
+      <c r="E245" s="71"/>
+      <c r="F245" s="140"/>
+      <c r="G245" s="138">
+        <f>SUM(F246:F249)</f>
+      </c>
+    </row>
+    <row r="246" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" s="76"/>
+      <c r="B246" s="76"/>
+      <c r="C246" s="34"/>
+      <c r="D246" s="132"/>
+      <c r="E246" s="71" t="s">
+        <v>564</v>
+      </c>
+      <c r="F246" s="140">
+        <f>IFERROR(VLOOKUP(E246,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
     </row>
     <row r="247" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="137"/>
       <c r="B247" s="137"/>
       <c r="C247" s="139"/>
-      <c r="D247" s="71" t="s">
-        <v>572</v>
-      </c>
+      <c r="D247" s="71"/>
       <c r="E247" s="72" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="F247" s="140">
         <f>IFERROR(VLOOKUP(E247,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G247" s="187">
-        <f>SUM(F247:F256)</f>
-        <v>149263.11</v>
-      </c>
+      <c r="G247" s="138"/>
     </row>
     <row r="248" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" s="137"/>
       <c r="B248" s="137"/>
       <c r="C248" s="139"/>
       <c r="D248" s="71"/>
-      <c r="E248" s="72" t="s">
-        <v>574</v>
+      <c r="E248" s="151" t="s">
+        <v>566</v>
       </c>
       <c r="F248" s="140">
         <f>IFERROR(VLOOKUP(E248,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11646,148 +11531,140 @@
       <c r="B249" s="137"/>
       <c r="C249" s="139"/>
       <c r="D249" s="71"/>
-      <c r="E249" s="72" t="s">
-        <v>575</v>
+      <c r="E249" s="151" t="s">
+        <v>567</v>
       </c>
       <c r="F249" s="140">
         <f>IFERROR(VLOOKUP(E249,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>98618.72</v>
       </c>
       <c r="G249" s="138"/>
     </row>
-    <row r="250" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="137"/>
       <c r="B250" s="137"/>
       <c r="C250" s="139"/>
-      <c r="D250" s="71"/>
-      <c r="E250" s="72" t="s">
-        <v>576</v>
-      </c>
-      <c r="F250" s="140">
-        <f>IFERROR(VLOOKUP(E250,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G250" s="138"/>
-    </row>
-    <row r="251" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A251" s="137"/>
-      <c r="B251" s="137"/>
-      <c r="C251" s="139"/>
-      <c r="D251" s="71"/>
+      <c r="D250" s="71" t="s">
+        <v>568</v>
+      </c>
+      <c r="E250" s="72"/>
+      <c r="F250" s="140"/>
+      <c r="G250" s="187">
+        <f>+F251+F252</f>
+      </c>
+      <c r="H250" s="72"/>
+      <c r="I250" s="164"/>
+    </row>
+    <row r="251" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" s="76"/>
+      <c r="B251" s="76"/>
+      <c r="C251" s="34"/>
+      <c r="D251" s="132"/>
       <c r="E251" s="72" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="F251" s="140">
         <f>IFERROR(VLOOKUP(E251,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>50644.39</v>
-      </c>
-      <c r="G251" s="138"/>
-    </row>
-    <row r="252" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="252" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="137"/>
       <c r="B252" s="137"/>
       <c r="C252" s="139"/>
       <c r="D252" s="71"/>
       <c r="E252" s="72" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="F252" s="140">
         <f>IFERROR(VLOOKUP(E252,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G252" s="138"/>
+      <c r="H252" s="72"/>
+      <c r="I252" s="164"/>
     </row>
     <row r="253" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" s="137"/>
       <c r="B253" s="137"/>
       <c r="C253" s="139"/>
-      <c r="D253" s="71"/>
-      <c r="E253" s="72" t="s">
-        <v>579</v>
-      </c>
-      <c r="F253" s="140">
-        <f>IFERROR(VLOOKUP(E253,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G253" s="138"/>
-    </row>
-    <row r="254" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D253" s="71" t="s">
+        <v>571</v>
+      </c>
+      <c r="E253" s="71"/>
+      <c r="F253" s="140"/>
+      <c r="G253" s="138">
+        <f>+F253</f>
+      </c>
+    </row>
+    <row r="254" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" s="137"/>
       <c r="B254" s="137"/>
       <c r="C254" s="139"/>
-      <c r="D254" s="71"/>
-      <c r="E254" s="72" t="s">
-        <v>580</v>
-      </c>
-      <c r="F254" s="140">
-        <f>IFERROR(VLOOKUP(E254,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G254" s="138"/>
-      <c r="H254" s="72"/>
-      <c r="I254" s="164"/>
-    </row>
-    <row r="255" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A255" s="137"/>
-      <c r="B255" s="137"/>
-      <c r="C255" s="139"/>
-      <c r="D255" s="71"/>
+      <c r="D254" s="71" t="s">
+        <v>572</v>
+      </c>
+      <c r="E254" s="72"/>
+      <c r="F254" s="140"/>
+      <c r="G254" s="187">
+        <f>SUM(F255:F264)</f>
+      </c>
+    </row>
+    <row r="255" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" s="76"/>
+      <c r="B255" s="76"/>
+      <c r="C255" s="34"/>
+      <c r="D255" s="132"/>
       <c r="E255" s="72" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="F255" s="140">
         <f>IFERROR(VLOOKUP(E255,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G255" s="138"/>
-      <c r="H255" s="72"/>
-      <c r="I255" s="164"/>
-    </row>
-    <row r="256" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="137"/>
       <c r="B256" s="137"/>
       <c r="C256" s="139"/>
       <c r="D256" s="71"/>
       <c r="E256" s="72" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="F256" s="140">
         <f>IFERROR(VLOOKUP(E256,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G256" s="138"/>
-      <c r="H256" s="72"/>
-      <c r="I256" s="164"/>
     </row>
     <row r="257" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="137"/>
       <c r="B257" s="137"/>
       <c r="C257" s="139"/>
-      <c r="D257" s="139" t="s">
-        <v>583</v>
-      </c>
-      <c r="E257" s="188"/>
-      <c r="F257" s="140"/>
-      <c r="G257" s="138">
-        <f>+F257</f>
-        <v>0</v>
-      </c>
+      <c r="D257" s="71"/>
+      <c r="E257" s="72" t="s">
+        <v>575</v>
+      </c>
+      <c r="F257" s="140">
+        <f>IFERROR(VLOOKUP(E257,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G257" s="138"/>
     </row>
     <row r="258" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" s="137"/>
       <c r="B258" s="137"/>
       <c r="C258" s="139"/>
-      <c r="D258" s="71" t="s">
-        <v>584</v>
-      </c>
-      <c r="E258" s="188"/>
-      <c r="F258" s="140"/>
-      <c r="G258" s="138">
-        <f>SUM(F258:F263)</f>
-        <v>0</v>
-      </c>
+      <c r="D258" s="71"/>
+      <c r="E258" s="72" t="s">
+        <v>576</v>
+      </c>
+      <c r="F258" s="140">
+        <f>IFERROR(VLOOKUP(E258,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G258" s="138"/>
     </row>
     <row r="259" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" s="137"/>
       <c r="B259" s="137"/>
       <c r="C259" s="139"/>
       <c r="D259" s="71"/>
-      <c r="E259" s="151" t="s">
-        <v>585</v>
+      <c r="E259" s="72" t="s">
+        <v>577</v>
       </c>
       <c r="F259" s="140">
         <f>IFERROR(VLOOKUP(E259,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11800,7 +11677,7 @@
       <c r="C260" s="139"/>
       <c r="D260" s="71"/>
       <c r="E260" s="72" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="F260" s="140">
         <f>IFERROR(VLOOKUP(E260,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -11813,883 +11690,818 @@
       <c r="C261" s="139"/>
       <c r="D261" s="71"/>
       <c r="E261" s="72" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="F261" s="140">
         <f>IFERROR(VLOOKUP(E261,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G261" s="138"/>
     </row>
-    <row r="262" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="137"/>
       <c r="B262" s="137"/>
       <c r="C262" s="139"/>
       <c r="D262" s="71"/>
       <c r="E262" s="72" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="F262" s="140">
         <f>IFERROR(VLOOKUP(E262,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G262" s="138"/>
-    </row>
-    <row r="263" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H262" s="72"/>
+      <c r="I262" s="164"/>
+    </row>
+    <row r="263" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="137"/>
       <c r="B263" s="137"/>
       <c r="C263" s="139"/>
       <c r="D263" s="71"/>
       <c r="E263" s="72" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="F263" s="140">
         <f>IFERROR(VLOOKUP(E263,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G263" s="138"/>
-    </row>
-    <row r="264" ht="12" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H263" s="72"/>
+      <c r="I263" s="164"/>
+    </row>
+    <row r="264" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="137"/>
       <c r="B264" s="137"/>
       <c r="C264" s="139"/>
-      <c r="D264" s="71" t="s">
-        <v>590</v>
-      </c>
-      <c r="E264" s="188"/>
-      <c r="F264" s="140"/>
-      <c r="G264" s="138">
-        <f>+F264</f>
-        <v>0</v>
-      </c>
-      <c r="H264" s="142"/>
-      <c r="I264" s="134"/>
-      <c r="J264" s="142"/>
-      <c r="K264" s="142"/>
-    </row>
-    <row r="265" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D264" s="71"/>
+      <c r="E264" s="72" t="s">
+        <v>582</v>
+      </c>
+      <c r="F264" s="140">
+        <f>IFERROR(VLOOKUP(E264,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G264" s="138"/>
+      <c r="H264" s="72"/>
+      <c r="I264" s="164"/>
+    </row>
+    <row r="265" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="137"/>
       <c r="B265" s="137"/>
       <c r="C265" s="139"/>
-      <c r="D265" s="71" t="s">
-        <v>591</v>
-      </c>
-      <c r="E265" s="72" t="s">
-        <v>592</v>
-      </c>
-      <c r="F265" s="140">
-        <f>IFERROR(VLOOKUP(E265,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G265" s="187">
-        <f>SUM(F265:F269)</f>
-        <v>11129701.370000001</v>
-      </c>
-      <c r="H265" s="132"/>
-      <c r="I265" s="134"/>
-      <c r="J265" s="152"/>
-    </row>
-    <row r="266" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D265" s="139" t="s">
+        <v>583</v>
+      </c>
+      <c r="E265" s="188"/>
+      <c r="F265" s="140"/>
+      <c r="G265" s="138">
+        <f>+F265</f>
+      </c>
+    </row>
+    <row r="266" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" s="137"/>
       <c r="B266" s="137"/>
       <c r="C266" s="139"/>
-      <c r="D266" s="71"/>
-      <c r="E266" s="72" t="s">
-        <v>593</v>
-      </c>
-      <c r="F266" s="140">
-        <f>IFERROR(VLOOKUP(E266,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>11050897.370000001</v>
-      </c>
-      <c r="G266" s="138"/>
-      <c r="H266" s="132"/>
-      <c r="I266" s="134"/>
-      <c r="J266" s="152"/>
-    </row>
-    <row r="267" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D266" s="71" t="s">
+        <v>584</v>
+      </c>
+      <c r="E266" s="188"/>
+      <c r="F266" s="140"/>
+      <c r="G266" s="138">
+        <f>SUM(F266:F271)</f>
+      </c>
+    </row>
+    <row r="267" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" s="137"/>
       <c r="B267" s="137"/>
       <c r="C267" s="139"/>
       <c r="D267" s="71"/>
-      <c r="E267" s="72" t="s">
-        <v>594</v>
+      <c r="E267" s="151" t="s">
+        <v>585</v>
       </c>
       <c r="F267" s="140">
         <f>IFERROR(VLOOKUP(E267,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>78804</v>
       </c>
       <c r="G267" s="138"/>
-      <c r="H267" s="132"/>
-      <c r="I267" s="134"/>
-      <c r="J267" s="152"/>
-    </row>
-    <row r="268" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" s="137"/>
       <c r="B268" s="137"/>
       <c r="C268" s="139"/>
       <c r="D268" s="71"/>
       <c r="E268" s="72" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="F268" s="140">
         <f>IFERROR(VLOOKUP(E268,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G268" s="138"/>
-      <c r="H268" s="132"/>
-      <c r="I268" s="134"/>
-      <c r="J268" s="152"/>
-    </row>
-    <row r="269" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="137"/>
       <c r="B269" s="137"/>
       <c r="C269" s="139"/>
       <c r="D269" s="71"/>
       <c r="E269" s="72" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="F269" s="140">
         <f>IFERROR(VLOOKUP(E269,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G269" s="138"/>
-      <c r="H269" s="132"/>
-      <c r="I269" s="134"/>
-      <c r="J269" s="152"/>
-    </row>
-    <row r="270" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A270" s="76"/>
-      <c r="B270" s="76"/>
-      <c r="C270" s="34"/>
-      <c r="D270" s="71" t="s">
-        <v>597</v>
-      </c>
-      <c r="E270" s="188"/>
-      <c r="F270" s="140"/>
-      <c r="G270" s="187">
-        <f>SUM(F270:F272)</f>
-        <v>25426948.26</v>
-      </c>
-      <c r="H270" s="68"/>
-      <c r="I270" s="189"/>
-      <c r="J270" s="132"/>
-      <c r="K270" s="190"/>
-    </row>
-    <row r="271" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A271" s="76"/>
-      <c r="B271" s="76"/>
-      <c r="C271" s="34"/>
-      <c r="D271" s="139"/>
+    </row>
+    <row r="270" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" s="137"/>
+      <c r="B270" s="137"/>
+      <c r="C270" s="139"/>
+      <c r="D270" s="71"/>
+      <c r="E270" s="72" t="s">
+        <v>588</v>
+      </c>
+      <c r="F270" s="140">
+        <f>IFERROR(VLOOKUP(E270,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G270" s="138"/>
+    </row>
+    <row r="271" ht="12" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A271" s="137"/>
+      <c r="B271" s="137"/>
+      <c r="C271" s="139"/>
+      <c r="D271" s="71"/>
       <c r="E271" s="72" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="F271" s="140">
         <f>IFERROR(VLOOKUP(E271,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G271" s="138"/>
-      <c r="H271" s="68"/>
-      <c r="I271" s="189"/>
-      <c r="J271" s="132"/>
-      <c r="K271" s="190"/>
-    </row>
-    <row r="272" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A272" s="76"/>
-      <c r="B272" s="76"/>
-      <c r="C272" s="34"/>
-      <c r="D272" s="139"/>
-      <c r="E272" s="72" t="s">
-        <v>599</v>
-      </c>
-      <c r="F272" s="140">
-        <f>IFERROR(VLOOKUP(E272,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>25426948.26</v>
-      </c>
-      <c r="G272" s="138"/>
-      <c r="H272" s="68"/>
-      <c r="I272" s="164"/>
-      <c r="J272" s="132"/>
-      <c r="K272" s="190"/>
-    </row>
-    <row r="273" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A273" s="76"/>
-      <c r="B273" s="76"/>
-      <c r="C273" s="34"/>
+    </row>
+    <row r="272" ht="12" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A272" s="137"/>
+      <c r="B272" s="137"/>
+      <c r="C272" s="139"/>
+      <c r="D272" s="71" t="s">
+        <v>590</v>
+      </c>
+      <c r="E272" s="188"/>
+      <c r="F272" s="140"/>
+      <c r="G272" s="138">
+        <f>+F272</f>
+      </c>
+      <c r="H272" s="142"/>
+      <c r="I272" s="134"/>
+      <c r="J272" s="142"/>
+      <c r="K272" s="142"/>
+    </row>
+    <row r="273" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A273" s="137"/>
+      <c r="B273" s="137"/>
+      <c r="C273" s="139"/>
       <c r="D273" s="71" t="s">
-        <v>600</v>
-      </c>
-      <c r="E273" s="72" t="s">
-        <v>601</v>
-      </c>
-      <c r="F273" s="140">
-        <f>IFERROR(VLOOKUP(E273,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>739403</v>
-      </c>
-      <c r="G273" s="138">
-        <f>SUM(F273:F280)</f>
-        <v>1884806.58</v>
-      </c>
-    </row>
-    <row r="274" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+      <c r="E273" s="72"/>
+      <c r="F273" s="140"/>
+      <c r="G273" s="187">
+        <f>SUM(F274:F278)</f>
+      </c>
+      <c r="H273" s="132"/>
+      <c r="I273" s="134"/>
+      <c r="J273" s="152"/>
+    </row>
+    <row r="274" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="76"/>
       <c r="B274" s="76"/>
       <c r="C274" s="34"/>
-      <c r="D274" s="71"/>
+      <c r="D274" s="132"/>
       <c r="E274" s="72" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="F274" s="140">
         <f>IFERROR(VLOOKUP(E274,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1145403.58</v>
-      </c>
-      <c r="G274" s="138"/>
-    </row>
-    <row r="275" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A275" s="76"/>
-      <c r="B275" s="76"/>
-      <c r="C275" s="34"/>
+      </c>
+    </row>
+    <row r="275" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A275" s="137"/>
+      <c r="B275" s="137"/>
+      <c r="C275" s="139"/>
       <c r="D275" s="71"/>
       <c r="E275" s="72" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="F275" s="140">
         <f>IFERROR(VLOOKUP(E275,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G275" s="138"/>
-    </row>
-    <row r="276" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A276" s="76"/>
-      <c r="B276" s="76"/>
-      <c r="C276" s="34"/>
+      <c r="H275" s="132"/>
+      <c r="I275" s="134"/>
+      <c r="J275" s="152"/>
+    </row>
+    <row r="276" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A276" s="137"/>
+      <c r="B276" s="137"/>
+      <c r="C276" s="139"/>
       <c r="D276" s="71"/>
       <c r="E276" s="72" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="F276" s="140">
         <f>IFERROR(VLOOKUP(E276,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G276" s="138"/>
-    </row>
-    <row r="277" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A277" s="76"/>
-      <c r="B277" s="76"/>
-      <c r="C277" s="34"/>
+      <c r="H276" s="132"/>
+      <c r="I276" s="134"/>
+      <c r="J276" s="152"/>
+    </row>
+    <row r="277" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A277" s="137"/>
+      <c r="B277" s="137"/>
+      <c r="C277" s="139"/>
       <c r="D277" s="71"/>
-      <c r="E277" s="151" t="s">
-        <v>605</v>
+      <c r="E277" s="72" t="s">
+        <v>595</v>
       </c>
       <c r="F277" s="140">
         <f>IFERROR(VLOOKUP(E277,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G277" s="138"/>
-    </row>
-    <row r="278" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A278" s="76"/>
-      <c r="B278" s="76"/>
-      <c r="C278" s="34"/>
+      <c r="H277" s="132"/>
+      <c r="I277" s="134"/>
+      <c r="J277" s="152"/>
+    </row>
+    <row r="278" ht="12.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A278" s="137"/>
+      <c r="B278" s="137"/>
+      <c r="C278" s="139"/>
       <c r="D278" s="71"/>
-      <c r="E278" s="151" t="s">
-        <v>606</v>
+      <c r="E278" s="72" t="s">
+        <v>596</v>
       </c>
       <c r="F278" s="140">
         <f>IFERROR(VLOOKUP(E278,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G278" s="138"/>
-    </row>
-    <row r="279" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H278" s="132"/>
+      <c r="I278" s="134"/>
+      <c r="J278" s="152"/>
+    </row>
+    <row r="279" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A279" s="76"/>
       <c r="B279" s="76"/>
       <c r="C279" s="34"/>
-      <c r="D279" s="71"/>
-      <c r="E279" s="151" t="s">
-        <v>607</v>
-      </c>
-      <c r="F279" s="140">
-        <f>IFERROR(VLOOKUP(E279,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G279" s="138"/>
-    </row>
-    <row r="280" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D279" s="71" t="s">
+        <v>597</v>
+      </c>
+      <c r="E279" s="188"/>
+      <c r="F279" s="140"/>
+      <c r="G279" s="187">
+        <f>SUM(F279:F281)</f>
+      </c>
+      <c r="H279" s="68"/>
+      <c r="I279" s="189"/>
+      <c r="J279" s="132"/>
+      <c r="K279" s="190"/>
+    </row>
+    <row r="280" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" s="76"/>
       <c r="B280" s="76"/>
       <c r="C280" s="34"/>
-      <c r="D280" s="71"/>
-      <c r="E280" s="151" t="s">
-        <v>608</v>
+      <c r="D280" s="139"/>
+      <c r="E280" s="72" t="s">
+        <v>598</v>
       </c>
       <c r="F280" s="140">
         <f>IFERROR(VLOOKUP(E280,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G280" s="138"/>
-    </row>
-    <row r="281" ht="12.6" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H280" s="68"/>
+      <c r="I280" s="189"/>
+      <c r="J280" s="132"/>
+      <c r="K280" s="190"/>
+    </row>
+    <row r="281" ht="14.4" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" s="76"/>
       <c r="B281" s="76"/>
       <c r="C281" s="34"/>
-      <c r="D281" s="191" t="s">
-        <v>609</v>
-      </c>
-      <c r="E281" s="192" t="s">
-        <v>609</v>
-      </c>
-      <c r="F281" s="193">
-        <f>+'Balance de sumas y saldos'!E243+'Balance de sumas y saldos'!E244</f>
-        <v>65017428.77</v>
-      </c>
-      <c r="G281" s="194">
-        <f>+F281</f>
-        <v>65017428.77</v>
-      </c>
-      <c r="H281" s="195" t="s">
-        <v>610</v>
-      </c>
-      <c r="I281" s="134"/>
-      <c r="J281" s="142"/>
-      <c r="K281" s="142"/>
+      <c r="D281" s="139"/>
+      <c r="E281" s="72" t="s">
+        <v>599</v>
+      </c>
+      <c r="F281" s="140">
+        <f>IFERROR(VLOOKUP(E281,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G281" s="138"/>
+      <c r="H281" s="68"/>
+      <c r="I281" s="164"/>
+      <c r="J281" s="132"/>
+      <c r="K281" s="190"/>
     </row>
     <row r="282" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="76"/>
       <c r="B282" s="76"/>
       <c r="C282" s="34"/>
       <c r="D282" s="71" t="s">
-        <v>611</v>
-      </c>
-      <c r="E282" s="71"/>
-      <c r="F282" s="140">
-        <f>IFERROR(VLOOKUP(E282,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="E282" s="72"/>
+      <c r="F282" s="140"/>
       <c r="G282" s="138">
-        <f>+F282</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>SUM(F283:F290)</f>
+      </c>
+    </row>
+    <row r="283" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="76"/>
       <c r="B283" s="76"/>
       <c r="C283" s="34"/>
-      <c r="D283" s="71" t="s">
-        <v>612</v>
-      </c>
-      <c r="E283" s="71"/>
+      <c r="D283" s="132"/>
+      <c r="E283" s="72" t="s">
+        <v>601</v>
+      </c>
       <c r="F283" s="140">
-        <f>IFERROR(VLOOKUP(D283,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G283" s="138">
-        <f>+F283</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E283,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+    </row>
+    <row r="284" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="76"/>
       <c r="B284" s="76"/>
       <c r="C284" s="34"/>
-      <c r="D284" s="139" t="s">
-        <v>613</v>
-      </c>
-      <c r="E284" s="139"/>
+      <c r="D284" s="71"/>
+      <c r="E284" s="72" t="s">
+        <v>602</v>
+      </c>
       <c r="F284" s="140">
-        <f>IFERROR(VLOOKUP(D284,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G284" s="138">
-        <f>+F284</f>
-        <v>0</v>
-      </c>
-      <c r="H284" s="152"/>
+        <f>IFERROR(VLOOKUP(E284,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G284" s="138"/>
     </row>
     <row r="285" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="76"/>
       <c r="B285" s="76"/>
       <c r="C285" s="34"/>
-      <c r="D285" s="139" t="s">
-        <v>614</v>
-      </c>
-      <c r="E285" s="139"/>
-      <c r="F285" s="140"/>
-      <c r="G285" s="138">
-        <f>SUM(F285:F293)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D285" s="71"/>
+      <c r="E285" s="72" t="s">
+        <v>603</v>
+      </c>
+      <c r="F285" s="140">
+        <f>IFERROR(VLOOKUP(E285,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G285" s="138"/>
+    </row>
+    <row r="286" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="76"/>
       <c r="B286" s="76"/>
       <c r="C286" s="34"/>
-      <c r="D286" s="139"/>
+      <c r="D286" s="71"/>
       <c r="E286" s="72" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="F286" s="140">
         <f>IFERROR(VLOOKUP(E286,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G286" s="138"/>
     </row>
-    <row r="287" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="76"/>
       <c r="B287" s="76"/>
       <c r="C287" s="34"/>
-      <c r="D287" s="139"/>
-      <c r="E287" s="72" t="s">
-        <v>616</v>
+      <c r="D287" s="71"/>
+      <c r="E287" s="151" t="s">
+        <v>605</v>
       </c>
       <c r="F287" s="140">
         <f>IFERROR(VLOOKUP(E287,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G287" s="138"/>
     </row>
-    <row r="288" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="76"/>
       <c r="B288" s="76"/>
       <c r="C288" s="34"/>
-      <c r="D288" s="139"/>
-      <c r="E288" s="139" t="s">
-        <v>617</v>
+      <c r="D288" s="71"/>
+      <c r="E288" s="151" t="s">
+        <v>606</v>
       </c>
       <c r="F288" s="140">
         <f>IFERROR(VLOOKUP(E288,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G288" s="138"/>
     </row>
-    <row r="289" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="76"/>
       <c r="B289" s="76"/>
       <c r="C289" s="34"/>
-      <c r="D289" s="139"/>
-      <c r="E289" s="139" t="s">
-        <v>618</v>
+      <c r="D289" s="71"/>
+      <c r="E289" s="151" t="s">
+        <v>607</v>
       </c>
       <c r="F289" s="140">
         <f>IFERROR(VLOOKUP(E289,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G289" s="138"/>
     </row>
-    <row r="290" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A290" s="76"/>
       <c r="B290" s="76"/>
       <c r="C290" s="34"/>
-      <c r="D290" s="139"/>
-      <c r="E290" s="139" t="s">
-        <v>619</v>
+      <c r="D290" s="71"/>
+      <c r="E290" s="151" t="s">
+        <v>608</v>
       </c>
       <c r="F290" s="140">
         <f>IFERROR(VLOOKUP(E290,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G290" s="138"/>
     </row>
-    <row r="291" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" ht="12.6" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" s="76"/>
       <c r="B291" s="76"/>
       <c r="C291" s="34"/>
-      <c r="D291" s="139"/>
-      <c r="E291" s="139" t="s">
-        <v>620</v>
-      </c>
-      <c r="F291" s="140">
-        <f>IFERROR(VLOOKUP(E291,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G291" s="138"/>
-    </row>
-    <row r="292" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D291" s="191" t="s">
+        <v>609</v>
+      </c>
+      <c r="E291" s="192" t="s">
+        <v>609</v>
+      </c>
+      <c r="F291" s="193">
+        <f>+'Balance de sumas y saldos'!E243+'Balance de sumas y saldos'!E244</f>
+        <v>65017428.77</v>
+      </c>
+      <c r="G291" s="194">
+        <f>+F291</f>
+      </c>
+      <c r="H291" s="195" t="s">
+        <v>610</v>
+      </c>
+      <c r="I291" s="134"/>
+      <c r="J291" s="142"/>
+      <c r="K291" s="142"/>
+    </row>
+    <row r="292" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="76"/>
       <c r="B292" s="76"/>
       <c r="C292" s="34"/>
-      <c r="D292" s="139"/>
-      <c r="E292" s="72" t="s">
-        <v>621</v>
-      </c>
+      <c r="D292" s="71" t="s">
+        <v>611</v>
+      </c>
+      <c r="E292" s="71"/>
       <c r="F292" s="140">
         <f>IFERROR(VLOOKUP(E292,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G292" s="138"/>
-    </row>
-    <row r="293" ht="13.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G292" s="138">
+        <f>+F292</f>
+      </c>
+    </row>
+    <row r="293" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="76"/>
       <c r="B293" s="76"/>
       <c r="C293" s="34"/>
-      <c r="D293" s="139"/>
-      <c r="E293" s="139" t="s">
-        <v>622</v>
-      </c>
+      <c r="D293" s="71" t="s">
+        <v>612</v>
+      </c>
+      <c r="E293" s="71"/>
       <c r="F293" s="140">
-        <f>IFERROR(VLOOKUP(E293,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G293" s="138"/>
-      <c r="H293" s="142"/>
-      <c r="I293" s="134"/>
-      <c r="J293" s="142"/>
-      <c r="K293" s="142"/>
-    </row>
-    <row r="294" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(D293,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
+      </c>
+      <c r="G293" s="138">
+        <f>+F293</f>
+      </c>
+    </row>
+    <row r="294" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="76"/>
       <c r="B294" s="76"/>
       <c r="C294" s="34"/>
-      <c r="D294" s="71" t="s">
-        <v>623</v>
-      </c>
-      <c r="E294" s="71"/>
-      <c r="F294" s="140"/>
+      <c r="D294" s="139" t="s">
+        <v>613</v>
+      </c>
+      <c r="E294" s="139"/>
+      <c r="F294" s="140">
+        <f>IFERROR(VLOOKUP(D294,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
+      </c>
       <c r="G294" s="138">
         <f>+F294</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      </c>
+      <c r="H294" s="152"/>
+    </row>
+    <row r="295" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="76"/>
       <c r="B295" s="76"/>
       <c r="C295" s="34"/>
-      <c r="D295" s="71" t="s">
-        <v>624</v>
-      </c>
-      <c r="E295" s="72" t="s">
-        <v>625</v>
-      </c>
-      <c r="F295" s="140">
-        <f>IFERROR(VLOOKUP(E295,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G295" s="187">
-        <f>SUM(F295:F302)</f>
-        <v>1099927.51</v>
-      </c>
-      <c r="H295" s="72"/>
-      <c r="I295" s="164"/>
-      <c r="J295" s="72"/>
-      <c r="K295" s="72"/>
-      <c r="L295" s="72"/>
-    </row>
-    <row r="296" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D295" s="139" t="s">
+        <v>614</v>
+      </c>
+      <c r="E295" s="139"/>
+      <c r="F295" s="140"/>
+      <c r="G295" s="138">
+        <f>SUM(F295:F303)</f>
+      </c>
+    </row>
+    <row r="296" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="76"/>
       <c r="B296" s="76"/>
       <c r="C296" s="34"/>
-      <c r="D296" s="71"/>
+      <c r="D296" s="139"/>
       <c r="E296" s="72" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F296" s="140">
         <f>IFERROR(VLOOKUP(E296,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1004059.51</v>
       </c>
       <c r="G296" s="138"/>
     </row>
-    <row r="297" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="76"/>
       <c r="B297" s="76"/>
       <c r="C297" s="34"/>
-      <c r="D297" s="71"/>
+      <c r="D297" s="139"/>
       <c r="E297" s="72" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F297" s="140">
         <f>IFERROR(VLOOKUP(E297,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>95868</v>
       </c>
       <c r="G297" s="138"/>
     </row>
-    <row r="298" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="298" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="76"/>
       <c r="B298" s="76"/>
       <c r="C298" s="34"/>
-      <c r="D298" s="71"/>
-      <c r="E298" s="72" t="s">
-        <v>628</v>
+      <c r="D298" s="139"/>
+      <c r="E298" s="139" t="s">
+        <v>617</v>
       </c>
       <c r="F298" s="140">
         <f>IFERROR(VLOOKUP(E298,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G298" s="138"/>
-      <c r="H298" s="132"/>
-      <c r="I298" s="164"/>
-      <c r="J298" s="72"/>
-      <c r="K298" s="72"/>
-      <c r="L298" s="72"/>
-      <c r="M298" s="72"/>
-    </row>
-    <row r="299" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="76"/>
       <c r="B299" s="76"/>
       <c r="C299" s="34"/>
-      <c r="D299" s="71"/>
-      <c r="E299" s="72" t="s">
-        <v>629</v>
+      <c r="D299" s="139"/>
+      <c r="E299" s="139" t="s">
+        <v>618</v>
       </c>
       <c r="F299" s="140">
         <f>IFERROR(VLOOKUP(E299,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G299" s="138"/>
-      <c r="H299" s="132"/>
-      <c r="I299" s="164"/>
-      <c r="J299" s="72"/>
-      <c r="K299" s="72"/>
-      <c r="L299" s="72"/>
-      <c r="M299" s="72"/>
-    </row>
-    <row r="300" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A300" s="76"/>
       <c r="B300" s="76"/>
       <c r="C300" s="34"/>
-      <c r="D300" s="71"/>
-      <c r="E300" s="72" t="s">
-        <v>630</v>
+      <c r="D300" s="139"/>
+      <c r="E300" s="139" t="s">
+        <v>619</v>
       </c>
       <c r="F300" s="140">
         <f>IFERROR(VLOOKUP(E300,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G300" s="138"/>
-      <c r="H300" s="132"/>
-      <c r="I300" s="164"/>
-      <c r="J300" s="72"/>
-      <c r="K300" s="72"/>
-      <c r="L300" s="72"/>
-      <c r="M300" s="72"/>
-    </row>
-    <row r="301" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="76"/>
       <c r="B301" s="76"/>
       <c r="C301" s="34"/>
-      <c r="D301" s="71"/>
-      <c r="E301" s="72" t="s">
-        <v>631</v>
+      <c r="D301" s="139"/>
+      <c r="E301" s="139" t="s">
+        <v>620</v>
       </c>
       <c r="F301" s="140">
         <f>IFERROR(VLOOKUP(E301,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G301" s="138"/>
-      <c r="H301" s="132"/>
-      <c r="I301" s="164"/>
-      <c r="J301" s="72"/>
-      <c r="K301" s="72"/>
-      <c r="L301" s="72"/>
-      <c r="M301" s="72"/>
-    </row>
-    <row r="302" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="76"/>
       <c r="B302" s="76"/>
       <c r="C302" s="34"/>
-      <c r="D302" s="71"/>
+      <c r="D302" s="139"/>
       <c r="E302" s="72" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="F302" s="140">
         <f>IFERROR(VLOOKUP(E302,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G302" s="138"/>
-      <c r="H302" s="132"/>
-      <c r="I302" s="164"/>
-      <c r="J302" s="72"/>
-      <c r="K302" s="72"/>
-      <c r="L302" s="72"/>
-      <c r="M302" s="72"/>
-    </row>
-    <row r="303" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" ht="13.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="76"/>
       <c r="B303" s="76"/>
       <c r="C303" s="34"/>
-      <c r="D303" s="71" t="s">
-        <v>633</v>
-      </c>
-      <c r="E303" s="188"/>
-      <c r="F303" s="140"/>
-      <c r="G303" s="187">
-        <f>SUM(F303:F306)</f>
-        <v>189946.28</v>
-      </c>
+      <c r="D303" s="139"/>
+      <c r="E303" s="139" t="s">
+        <v>622</v>
+      </c>
+      <c r="F303" s="140">
+        <f>IFERROR(VLOOKUP(E303,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G303" s="138"/>
+      <c r="H303" s="142"/>
+      <c r="I303" s="134"/>
+      <c r="J303" s="142"/>
+      <c r="K303" s="142"/>
     </row>
     <row r="304" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="76"/>
       <c r="B304" s="76"/>
       <c r="C304" s="34"/>
-      <c r="D304" s="71"/>
-      <c r="E304" s="72" t="s">
-        <v>634</v>
-      </c>
-      <c r="F304" s="140">
-        <f>IFERROR(VLOOKUP(E304,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G304" s="138"/>
-    </row>
-    <row r="305" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D304" s="71" t="s">
+        <v>623</v>
+      </c>
+      <c r="E304" s="71"/>
+      <c r="F304" s="140"/>
+      <c r="G304" s="138">
+        <f>+F304</f>
+      </c>
+    </row>
+    <row r="305" ht="12.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A305" s="76"/>
       <c r="B305" s="76"/>
       <c r="C305" s="34"/>
-      <c r="D305" s="71"/>
-      <c r="E305" s="72" t="s">
-        <v>635</v>
-      </c>
-      <c r="F305" s="140">
-        <f>IFERROR(VLOOKUP(E305,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>189946.28</v>
-      </c>
-      <c r="G305" s="138"/>
-    </row>
-    <row r="306" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D305" s="71" t="s">
+        <v>624</v>
+      </c>
+      <c r="E305" s="72"/>
+      <c r="F305" s="140"/>
+      <c r="G305" s="187">
+        <f>SUM(F306:F313)</f>
+      </c>
+      <c r="H305" s="72"/>
+      <c r="I305" s="164"/>
+      <c r="J305" s="72"/>
+      <c r="K305" s="72"/>
+      <c r="L305" s="72"/>
+    </row>
+    <row r="306" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="76"/>
       <c r="B306" s="76"/>
       <c r="C306" s="34"/>
-      <c r="D306" s="71"/>
+      <c r="D306" s="132"/>
       <c r="E306" s="72" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="F306" s="140">
         <f>IFERROR(VLOOKUP(E306,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G306" s="138"/>
     </row>
     <row r="307" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="76"/>
       <c r="B307" s="76"/>
       <c r="C307" s="34"/>
-      <c r="D307" s="71" t="s">
-        <v>637</v>
-      </c>
-      <c r="E307" s="188"/>
+      <c r="D307" s="71"/>
+      <c r="E307" s="72" t="s">
+        <v>626</v>
+      </c>
       <c r="F307" s="140">
         <f>IFERROR(VLOOKUP(E307,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G307" s="138">
-        <f>+F308</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="308" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G307" s="138"/>
+    </row>
+    <row r="308" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="76"/>
       <c r="B308" s="76"/>
       <c r="C308" s="34"/>
       <c r="D308" s="71"/>
       <c r="E308" s="72" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="F308" s="140">
         <f>IFERROR(VLOOKUP(E308,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G308" s="138"/>
-      <c r="H308" s="72"/>
-      <c r="I308" s="164"/>
-    </row>
-    <row r="309" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A309" s="76"/>
       <c r="B309" s="76"/>
       <c r="C309" s="34"/>
-      <c r="D309" s="139" t="s">
-        <v>639</v>
-      </c>
+      <c r="D309" s="71"/>
       <c r="E309" s="72" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="F309" s="140">
         <f>IFERROR(VLOOKUP(E309,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G309" s="138">
-        <f>+F309</f>
-        <v>0</v>
-      </c>
-      <c r="H309" s="72"/>
+      <c r="G309" s="138"/>
+      <c r="H309" s="132"/>
       <c r="I309" s="164"/>
-    </row>
-    <row r="310" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J309" s="72"/>
+      <c r="K309" s="72"/>
+      <c r="L309" s="72"/>
+      <c r="M309" s="72"/>
+    </row>
+    <row r="310" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A310" s="76"/>
       <c r="B310" s="76"/>
       <c r="C310" s="34"/>
-      <c r="D310" s="139" t="s">
-        <v>640</v>
-      </c>
+      <c r="D310" s="71"/>
       <c r="E310" s="72" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="F310" s="140">
         <f>IFERROR(VLOOKUP(E310,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>48607846.6</v>
-      </c>
-      <c r="G310" s="187">
-        <f>+F310</f>
-        <v>48607846.6</v>
-      </c>
-      <c r="H310" s="72"/>
+      </c>
+      <c r="G310" s="138"/>
+      <c r="H310" s="132"/>
       <c r="I310" s="164"/>
-    </row>
-    <row r="311" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J310" s="72"/>
+      <c r="K310" s="72"/>
+      <c r="L310" s="72"/>
+      <c r="M310" s="72"/>
+    </row>
+    <row r="311" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A311" s="76"/>
       <c r="B311" s="76"/>
       <c r="C311" s="34"/>
-      <c r="D311" s="71" t="s">
-        <v>641</v>
-      </c>
+      <c r="D311" s="71"/>
       <c r="E311" s="72" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="F311" s="140">
         <f>IFERROR(VLOOKUP(E311,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G311" s="138">
-        <f>+F311</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="312" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G311" s="138"/>
+      <c r="H311" s="132"/>
+      <c r="I311" s="164"/>
+      <c r="J311" s="72"/>
+      <c r="K311" s="72"/>
+      <c r="L311" s="72"/>
+      <c r="M311" s="72"/>
+    </row>
+    <row r="312" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A312" s="76"/>
       <c r="B312" s="76"/>
       <c r="C312" s="34"/>
-      <c r="D312" s="71" t="s">
-        <v>643</v>
-      </c>
-      <c r="E312" s="188"/>
+      <c r="D312" s="71"/>
+      <c r="E312" s="72" t="s">
+        <v>631</v>
+      </c>
       <c r="F312" s="140">
         <f>IFERROR(VLOOKUP(E312,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G312" s="138">
-        <f>SUM(F312:F314)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="313" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G312" s="138"/>
+      <c r="H312" s="132"/>
+      <c r="I312" s="164"/>
+      <c r="J312" s="72"/>
+      <c r="K312" s="72"/>
+      <c r="L312" s="72"/>
+      <c r="M312" s="72"/>
+    </row>
+    <row r="313" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A313" s="76"/>
       <c r="B313" s="76"/>
       <c r="C313" s="34"/>
       <c r="D313" s="71"/>
       <c r="E313" s="72" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="F313" s="140">
         <f>IFERROR(VLOOKUP(E313,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G313" s="138"/>
+      <c r="H313" s="132"/>
+      <c r="I313" s="164"/>
+      <c r="J313" s="72"/>
+      <c r="K313" s="72"/>
+      <c r="L313" s="72"/>
+      <c r="M313" s="72"/>
     </row>
     <row r="314" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="76"/>
       <c r="B314" s="76"/>
       <c r="C314" s="34"/>
-      <c r="D314" s="71"/>
-      <c r="E314" s="72" t="s">
-        <v>645</v>
-      </c>
-      <c r="F314" s="140">
-        <f>IFERROR(VLOOKUP(E314,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G314" s="138"/>
+      <c r="D314" s="71" t="s">
+        <v>633</v>
+      </c>
+      <c r="E314" s="188"/>
+      <c r="F314" s="140"/>
+      <c r="G314" s="187">
+        <f>SUM(F314:F317)</f>
+      </c>
     </row>
     <row r="315" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="76"/>
       <c r="B315" s="76"/>
       <c r="C315" s="34"/>
-      <c r="D315" s="71" t="s">
-        <v>646</v>
-      </c>
-      <c r="E315" s="71"/>
+      <c r="D315" s="71"/>
+      <c r="E315" s="72" t="s">
+        <v>634</v>
+      </c>
       <c r="F315" s="140">
         <f>IFERROR(VLOOKUP(E315,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G315" s="138">
-        <f>+F315</f>
-        <v>0</v>
-      </c>
+      <c r="G315" s="138"/>
     </row>
     <row r="316" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="76"/>
       <c r="B316" s="76"/>
       <c r="C316" s="34"/>
-      <c r="D316" s="71" t="s">
-        <v>647</v>
-      </c>
-      <c r="E316" s="71" t="s">
-        <v>648</v>
+      <c r="D316" s="71"/>
+      <c r="E316" s="72" t="s">
+        <v>635</v>
       </c>
       <c r="F316" s="140">
         <f>IFERROR(VLOOKUP(E316,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G316" s="187">
-        <f>+F316+F317</f>
-        <v>18512.4</v>
-      </c>
+      <c r="G316" s="138"/>
     </row>
     <row r="317" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="76"/>
@@ -12697,102 +12509,111 @@
       <c r="C317" s="34"/>
       <c r="D317" s="71"/>
       <c r="E317" s="72" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="F317" s="140">
         <f>IFERROR(VLOOKUP(E317,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>18512.4</v>
       </c>
       <c r="G317" s="138"/>
     </row>
-    <row r="318" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="76"/>
       <c r="B318" s="76"/>
       <c r="C318" s="34"/>
-      <c r="D318" s="139" t="s">
-        <v>650</v>
-      </c>
-      <c r="E318" s="72"/>
+      <c r="D318" s="71" t="s">
+        <v>637</v>
+      </c>
+      <c r="E318" s="188"/>
       <c r="F318" s="140">
         <f>IFERROR(VLOOKUP(E318,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G318" s="138">
-        <f>+F318</f>
-        <v>0</v>
-      </c>
-      <c r="H318" s="68"/>
-    </row>
-    <row r="319" ht="12.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>+F319</f>
+      </c>
+    </row>
+    <row r="319" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" s="76"/>
       <c r="B319" s="76"/>
       <c r="C319" s="34"/>
-      <c r="D319" s="71" t="s">
-        <v>651</v>
-      </c>
-      <c r="E319" s="71"/>
-      <c r="F319" s="140"/>
-      <c r="G319" s="187">
-        <f>SUM(F319:F322)</f>
-        <v>96227408.59</v>
-      </c>
-      <c r="H319" s="68"/>
-    </row>
-    <row r="320" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D319" s="71"/>
+      <c r="E319" s="72" t="s">
+        <v>638</v>
+      </c>
+      <c r="F319" s="140">
+        <f>IFERROR(VLOOKUP(E319,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G319" s="138"/>
+      <c r="H319" s="72"/>
+      <c r="I319" s="164"/>
+    </row>
+    <row r="320" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" s="76"/>
       <c r="B320" s="76"/>
       <c r="C320" s="34"/>
-      <c r="D320" s="71"/>
+      <c r="D320" s="139" t="s">
+        <v>639</v>
+      </c>
       <c r="E320" s="72" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="F320" s="140">
         <f>IFERROR(VLOOKUP(E320,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>96227408.59</v>
-      </c>
-      <c r="G320" s="143"/>
-      <c r="H320" s="68"/>
-    </row>
-    <row r="321" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      </c>
+      <c r="G320" s="138">
+        <f>+F320</f>
+      </c>
+      <c r="H320" s="72"/>
+      <c r="I320" s="164"/>
+    </row>
+    <row r="321" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" s="76"/>
       <c r="B321" s="76"/>
       <c r="C321" s="34"/>
-      <c r="D321" s="71"/>
+      <c r="D321" s="139" t="s">
+        <v>640</v>
+      </c>
       <c r="E321" s="72" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="F321" s="140">
         <f>IFERROR(VLOOKUP(E321,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G321" s="138"/>
-      <c r="H321" s="68"/>
-    </row>
-    <row r="322" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G321" s="187">
+        <f>+F321</f>
+      </c>
+      <c r="H321" s="72"/>
+      <c r="I321" s="164"/>
+    </row>
+    <row r="322" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="76"/>
       <c r="B322" s="76"/>
       <c r="C322" s="34"/>
-      <c r="D322" s="71"/>
+      <c r="D322" s="71" t="s">
+        <v>641</v>
+      </c>
       <c r="E322" s="72" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="F322" s="140">
         <f>IFERROR(VLOOKUP(E322,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G322" s="138"/>
-      <c r="H322" s="68"/>
-      <c r="I322" s="159"/>
+      <c r="G322" s="138">
+        <f>+F322</f>
+      </c>
     </row>
     <row r="323" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="76"/>
       <c r="B323" s="76"/>
       <c r="C323" s="34"/>
       <c r="D323" s="71" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="E323" s="188"/>
-      <c r="F323" s="140"/>
-      <c r="G323" s="187">
-        <f>SUM(F323:F330)</f>
-        <v>56235551.05</v>
+      <c r="F323" s="140">
+        <f>IFERROR(VLOOKUP(E323,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G323" s="138">
+        <f>SUM(F323:F325)</f>
       </c>
     </row>
     <row r="324" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -12801,11 +12622,10 @@
       <c r="C324" s="34"/>
       <c r="D324" s="71"/>
       <c r="E324" s="72" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="F324" s="140">
         <f>IFERROR(VLOOKUP(E324,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>218983.47</v>
       </c>
       <c r="G324" s="138"/>
     </row>
@@ -12815,7 +12635,7 @@
       <c r="C325" s="34"/>
       <c r="D325" s="71"/>
       <c r="E325" s="72" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="F325" s="140">
         <f>IFERROR(VLOOKUP(E325,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -12826,41 +12646,41 @@
       <c r="A326" s="76"/>
       <c r="B326" s="76"/>
       <c r="C326" s="34"/>
-      <c r="D326" s="71"/>
-      <c r="E326" s="72" t="s">
-        <v>658</v>
-      </c>
+      <c r="D326" s="71" t="s">
+        <v>646</v>
+      </c>
+      <c r="E326" s="71"/>
       <c r="F326" s="140">
         <f>IFERROR(VLOOKUP(E326,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>56016567.58</v>
-      </c>
-      <c r="G326" s="138"/>
+      </c>
+      <c r="G326" s="138">
+        <f>+F326</f>
+      </c>
     </row>
     <row r="327" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="76"/>
       <c r="B327" s="76"/>
       <c r="C327" s="34"/>
-      <c r="D327" s="71"/>
-      <c r="E327" s="72" t="s">
-        <v>659</v>
-      </c>
-      <c r="F327" s="140">
-        <f>IFERROR(VLOOKUP(E327,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G327" s="138"/>
-    </row>
-    <row r="328" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D327" s="71" t="s">
+        <v>647</v>
+      </c>
+      <c r="E327" s="71"/>
+      <c r="F327" s="140"/>
+      <c r="G327" s="187">
+        <f>+F328+F329</f>
+      </c>
+    </row>
+    <row r="328" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="76"/>
       <c r="B328" s="76"/>
       <c r="C328" s="34"/>
-      <c r="D328" s="71"/>
-      <c r="E328" s="72" t="s">
-        <v>660</v>
+      <c r="D328" s="132"/>
+      <c r="E328" s="71" t="s">
+        <v>648</v>
       </c>
       <c r="F328" s="140">
         <f>IFERROR(VLOOKUP(E328,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G328" s="138"/>
     </row>
     <row r="329" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="76"/>
@@ -12868,61 +12688,56 @@
       <c r="C329" s="34"/>
       <c r="D329" s="71"/>
       <c r="E329" s="72" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="F329" s="140">
         <f>IFERROR(VLOOKUP(E329,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G329" s="138"/>
     </row>
-    <row r="330" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" s="76"/>
       <c r="B330" s="76"/>
       <c r="C330" s="34"/>
-      <c r="D330" s="71"/>
-      <c r="E330" s="72" t="s">
-        <v>662</v>
-      </c>
+      <c r="D330" s="139" t="s">
+        <v>650</v>
+      </c>
+      <c r="E330" s="72"/>
       <c r="F330" s="140">
         <f>IFERROR(VLOOKUP(E330,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G330" s="138"/>
-    </row>
-    <row r="331" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G330" s="138">
+        <f>+F330</f>
+      </c>
+      <c r="H330" s="68"/>
+    </row>
+    <row r="331" ht="12.6" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" s="76"/>
       <c r="B331" s="76"/>
       <c r="C331" s="34"/>
       <c r="D331" s="71" t="s">
-        <v>663</v>
-      </c>
-      <c r="E331" s="72" t="s">
-        <v>664</v>
-      </c>
-      <c r="F331" s="140">
-        <f>IFERROR(VLOOKUP(E331,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="E331" s="71"/>
+      <c r="F331" s="140"/>
       <c r="G331" s="187">
-        <f>SUM(F331:F338)</f>
-        <v>31296828.740000002</v>
-      </c>
-      <c r="H331" s="150"/>
+        <f>SUM(F331:F334)</f>
+      </c>
+      <c r="H331" s="68"/>
     </row>
     <row r="332" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" s="76"/>
       <c r="B332" s="76"/>
       <c r="C332" s="34"/>
       <c r="D332" s="71"/>
-      <c r="E332" s="151" t="s">
-        <v>665</v>
+      <c r="E332" s="72" t="s">
+        <v>652</v>
       </c>
       <c r="F332" s="140">
         <f>IFERROR(VLOOKUP(E332,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>21735.54</v>
-      </c>
-      <c r="G332" s="138"/>
-      <c r="H332" s="150" t="s">
-        <v>666</v>
-      </c>
+      </c>
+      <c r="G332" s="143"/>
+      <c r="H332" s="68"/>
     </row>
     <row r="333" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" s="76"/>
@@ -12930,126 +12745,114 @@
       <c r="C333" s="34"/>
       <c r="D333" s="71"/>
       <c r="E333" s="72" t="s">
-        <v>667</v>
+        <v>653</v>
       </c>
       <c r="F333" s="140">
         <f>IFERROR(VLOOKUP(E333,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>4589860.38</v>
       </c>
       <c r="G333" s="138"/>
-      <c r="H333" s="150"/>
-    </row>
-    <row r="334" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H333" s="68"/>
+    </row>
+    <row r="334" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="76"/>
       <c r="B334" s="76"/>
       <c r="C334" s="34"/>
       <c r="D334" s="71"/>
       <c r="E334" s="72" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="F334" s="140">
         <f>IFERROR(VLOOKUP(E334,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>26655432.82</v>
       </c>
       <c r="G334" s="138"/>
-      <c r="H334" s="150"/>
-    </row>
-    <row r="335" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H334" s="68"/>
+      <c r="I334" s="159"/>
+    </row>
+    <row r="335" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="76"/>
       <c r="B335" s="76"/>
       <c r="C335" s="34"/>
-      <c r="D335" s="71"/>
-      <c r="E335" s="72" t="s">
-        <v>669</v>
-      </c>
-      <c r="F335" s="140">
-        <f>IFERROR(VLOOKUP(E335,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>29800</v>
-      </c>
-      <c r="G335" s="138"/>
-      <c r="H335" s="68"/>
-    </row>
-    <row r="336" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D335" s="71" t="s">
+        <v>655</v>
+      </c>
+      <c r="E335" s="188"/>
+      <c r="F335" s="140"/>
+      <c r="G335" s="187">
+        <f>SUM(F335:F342)</f>
+      </c>
+    </row>
+    <row r="336" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="76"/>
       <c r="B336" s="76"/>
       <c r="C336" s="34"/>
       <c r="D336" s="71"/>
       <c r="E336" s="72" t="s">
-        <v>670</v>
+        <v>656</v>
       </c>
       <c r="F336" s="140">
         <f>IFERROR(VLOOKUP(E336,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G336" s="138"/>
-      <c r="H336" s="68"/>
-    </row>
-    <row r="337" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="76"/>
       <c r="B337" s="76"/>
       <c r="C337" s="34"/>
       <c r="D337" s="71"/>
       <c r="E337" s="72" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="F337" s="140">
         <f>IFERROR(VLOOKUP(E337,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G337" s="138"/>
-      <c r="H337" s="68"/>
-    </row>
-    <row r="338" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="76"/>
       <c r="B338" s="76"/>
       <c r="C338" s="34"/>
       <c r="D338" s="71"/>
       <c r="E338" s="72" t="s">
-        <v>672</v>
+        <v>658</v>
       </c>
       <c r="F338" s="140">
         <f>IFERROR(VLOOKUP(E338,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G338" s="138"/>
-      <c r="H338" s="68"/>
     </row>
     <row r="339" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="76"/>
       <c r="B339" s="76"/>
       <c r="C339" s="34"/>
-      <c r="D339" s="71" t="s">
-        <v>673</v>
-      </c>
-      <c r="E339" s="71"/>
-      <c r="F339" s="140"/>
-      <c r="G339" s="138">
-        <f>+F339</f>
-        <v>0</v>
-      </c>
+      <c r="D339" s="71"/>
+      <c r="E339" s="72" t="s">
+        <v>659</v>
+      </c>
+      <c r="F339" s="140">
+        <f>IFERROR(VLOOKUP(E339,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G339" s="138"/>
     </row>
     <row r="340" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="76"/>
       <c r="B340" s="76"/>
       <c r="C340" s="34"/>
-      <c r="D340" s="71" t="s">
-        <v>674</v>
-      </c>
+      <c r="D340" s="71"/>
       <c r="E340" s="72" t="s">
-        <v>675</v>
+        <v>660</v>
       </c>
       <c r="F340" s="140">
         <f>IFERROR(VLOOKUP(E340,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G340" s="138">
-        <f>+F340+F341+F342</f>
-        <v>0</v>
-      </c>
+      <c r="G340" s="138"/>
     </row>
     <row r="341" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="76"/>
       <c r="B341" s="76"/>
       <c r="C341" s="34"/>
       <c r="D341" s="71"/>
-      <c r="E341" s="71" t="s">
-        <v>676</v>
+      <c r="E341" s="72" t="s">
+        <v>661</v>
       </c>
       <c r="F341" s="140">
         <f>IFERROR(VLOOKUP(E341,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13061,352 +12864,320 @@
       <c r="B342" s="76"/>
       <c r="C342" s="34"/>
       <c r="D342" s="71"/>
-      <c r="E342" s="71" t="s">
-        <v>677</v>
+      <c r="E342" s="72" t="s">
+        <v>662</v>
       </c>
       <c r="F342" s="140">
         <f>IFERROR(VLOOKUP(E342,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G342" s="138"/>
     </row>
-    <row r="343" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" s="76"/>
       <c r="B343" s="76"/>
       <c r="C343" s="34"/>
       <c r="D343" s="71" t="s">
-        <v>678</v>
-      </c>
-      <c r="E343" s="72" t="s">
-        <v>679</v>
-      </c>
-      <c r="F343" s="140">
-        <f>IFERROR(VLOOKUP(E343,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="E343" s="72"/>
+      <c r="F343" s="140"/>
       <c r="G343" s="187">
-        <f>SUM(F343:F351)</f>
-        <v>8194241.22</v>
-      </c>
-    </row>
-    <row r="344" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <f>SUM(F344:F351)</f>
+      </c>
+      <c r="H343" s="150"/>
+    </row>
+    <row r="344" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="76"/>
       <c r="B344" s="76"/>
       <c r="C344" s="34"/>
-      <c r="D344" s="71"/>
+      <c r="D344" s="132"/>
       <c r="E344" s="72" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="F344" s="140">
         <f>IFERROR(VLOOKUP(E344,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>653893.77</v>
-      </c>
-      <c r="G344" s="138"/>
-      <c r="H344" s="132"/>
-      <c r="I344" s="134"/>
-      <c r="J344" s="72"/>
-      <c r="K344" s="72"/>
-      <c r="L344" s="72"/>
-      <c r="M344" s="72"/>
-      <c r="N344" s="72"/>
-    </row>
-    <row r="345" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="345" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" s="76"/>
       <c r="B345" s="76"/>
       <c r="C345" s="34"/>
       <c r="D345" s="71"/>
-      <c r="E345" s="72" t="s">
-        <v>681</v>
+      <c r="E345" s="151" t="s">
+        <v>665</v>
       </c>
       <c r="F345" s="140">
         <f>IFERROR(VLOOKUP(E345,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G345" s="138"/>
-      <c r="H345" s="132"/>
-      <c r="I345" s="134"/>
-      <c r="J345" s="72"/>
-      <c r="K345" s="72"/>
-      <c r="L345" s="72"/>
-      <c r="M345" s="72"/>
-      <c r="N345" s="72"/>
-    </row>
-    <row r="346" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H345" s="150" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="346" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" s="76"/>
       <c r="B346" s="76"/>
       <c r="C346" s="34"/>
       <c r="D346" s="71"/>
       <c r="E346" s="72" t="s">
-        <v>682</v>
+        <v>667</v>
       </c>
       <c r="F346" s="140">
         <f>IFERROR(VLOOKUP(E346,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>6090934.65</v>
       </c>
       <c r="G346" s="138"/>
-    </row>
-    <row r="347" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H346" s="150"/>
+    </row>
+    <row r="347" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" s="76"/>
       <c r="B347" s="76"/>
       <c r="C347" s="34"/>
       <c r="D347" s="71"/>
       <c r="E347" s="72" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="F347" s="140">
         <f>IFERROR(VLOOKUP(E347,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G347" s="138"/>
-    </row>
-    <row r="348" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H347" s="150"/>
+    </row>
+    <row r="348" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" s="76"/>
       <c r="B348" s="76"/>
       <c r="C348" s="34"/>
       <c r="D348" s="71"/>
       <c r="E348" s="72" t="s">
-        <v>684</v>
+        <v>669</v>
       </c>
       <c r="F348" s="140">
         <f>IFERROR(VLOOKUP(E348,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G348" s="138"/>
-    </row>
-    <row r="349" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H348" s="68"/>
+    </row>
+    <row r="349" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" s="76"/>
       <c r="B349" s="76"/>
       <c r="C349" s="34"/>
       <c r="D349" s="71"/>
       <c r="E349" s="72" t="s">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="F349" s="140">
         <f>IFERROR(VLOOKUP(E349,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G349" s="138"/>
-    </row>
-    <row r="350" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H349" s="68"/>
+    </row>
+    <row r="350" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" s="76"/>
       <c r="B350" s="76"/>
       <c r="C350" s="34"/>
       <c r="D350" s="71"/>
       <c r="E350" s="72" t="s">
-        <v>686</v>
+        <v>671</v>
       </c>
       <c r="F350" s="140">
         <f>IFERROR(VLOOKUP(E350,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G350" s="138"/>
+      <c r="H350" s="68"/>
     </row>
     <row r="351" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" s="76"/>
       <c r="B351" s="76"/>
       <c r="C351" s="34"/>
       <c r="D351" s="71"/>
-      <c r="E351" s="151" t="s">
-        <v>687</v>
+      <c r="E351" s="72" t="s">
+        <v>672</v>
       </c>
       <c r="F351" s="140">
         <f>IFERROR(VLOOKUP(E351,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1449412.8</v>
       </c>
       <c r="G351" s="138"/>
-      <c r="H351" s="68" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="352" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H351" s="68"/>
+    </row>
+    <row r="352" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="76"/>
       <c r="B352" s="76"/>
       <c r="C352" s="34"/>
       <c r="D352" s="71" t="s">
-        <v>688</v>
-      </c>
-      <c r="E352" s="72" t="s">
-        <v>689</v>
-      </c>
-      <c r="F352" s="140">
-        <f>IFERROR(VLOOKUP(E352,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G352" s="187">
-        <f>SUM(F352:F358)</f>
-        <v>9880231.91</v>
-      </c>
-      <c r="H352" s="68"/>
-      <c r="I352" s="164"/>
-      <c r="J352" s="72"/>
-      <c r="K352" s="72"/>
-      <c r="L352" s="72"/>
-      <c r="M352" s="72"/>
-    </row>
-    <row r="353" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <v>673</v>
+      </c>
+      <c r="E352" s="71"/>
+      <c r="F352" s="140"/>
+      <c r="G352" s="138">
+        <f>+F352</f>
+      </c>
+    </row>
+    <row r="353" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A353" s="76"/>
       <c r="B353" s="76"/>
       <c r="C353" s="34"/>
-      <c r="D353" s="71"/>
-      <c r="E353" s="72" t="s">
-        <v>690</v>
-      </c>
-      <c r="F353" s="140">
-        <f>IFERROR(VLOOKUP(E353,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1022000.89</v>
-      </c>
-      <c r="G353" s="138"/>
-      <c r="H353" s="68"/>
-    </row>
-    <row r="354" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D353" s="71" t="s">
+        <v>674</v>
+      </c>
+      <c r="E353" s="72"/>
+      <c r="F353" s="140"/>
+      <c r="G353" s="138">
+        <f>+F354+F355+F356</f>
+      </c>
+    </row>
+    <row r="354" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="76"/>
       <c r="B354" s="76"/>
       <c r="C354" s="34"/>
-      <c r="D354" s="71"/>
+      <c r="D354" s="132"/>
       <c r="E354" s="72" t="s">
-        <v>691</v>
+        <v>675</v>
       </c>
       <c r="F354" s="140">
         <f>IFERROR(VLOOKUP(E354,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>8853131.85</v>
-      </c>
-      <c r="G354" s="138"/>
-      <c r="H354" s="68"/>
-    </row>
-    <row r="355" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="355" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="76"/>
       <c r="B355" s="76"/>
       <c r="C355" s="34"/>
       <c r="D355" s="71"/>
-      <c r="E355" s="72" t="s">
-        <v>692</v>
+      <c r="E355" s="71" t="s">
+        <v>676</v>
       </c>
       <c r="F355" s="140">
         <f>IFERROR(VLOOKUP(E355,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G355" s="138"/>
-      <c r="H355" s="68"/>
-    </row>
-    <row r="356" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="76"/>
       <c r="B356" s="76"/>
       <c r="C356" s="34"/>
       <c r="D356" s="71"/>
-      <c r="E356" s="72" t="s">
-        <v>693</v>
+      <c r="E356" s="71" t="s">
+        <v>677</v>
       </c>
       <c r="F356" s="140">
         <f>IFERROR(VLOOKUP(E356,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>5099.17</v>
       </c>
       <c r="G356" s="138"/>
-      <c r="H356" s="68"/>
-    </row>
-    <row r="357" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="76"/>
       <c r="B357" s="76"/>
       <c r="C357" s="34"/>
-      <c r="D357" s="71"/>
-      <c r="E357" s="72" t="s">
-        <v>694</v>
-      </c>
-      <c r="F357" s="140">
-        <f>IFERROR(VLOOKUP(E357,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G357" s="138"/>
-      <c r="H357" s="68"/>
-    </row>
-    <row r="358" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D357" s="71" t="s">
+        <v>678</v>
+      </c>
+      <c r="E357" s="72"/>
+      <c r="F357" s="140"/>
+      <c r="G357" s="187">
+        <f>SUM(F358:F366)</f>
+      </c>
+    </row>
+    <row r="358" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="76"/>
       <c r="B358" s="76"/>
       <c r="C358" s="34"/>
-      <c r="D358" s="71"/>
+      <c r="D358" s="132"/>
       <c r="E358" s="72" t="s">
-        <v>695</v>
+        <v>679</v>
       </c>
       <c r="F358" s="140">
         <f>IFERROR(VLOOKUP(E358,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G358" s="138"/>
-      <c r="H358" s="68"/>
-    </row>
-    <row r="359" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A359" s="76"/>
       <c r="B359" s="76"/>
       <c r="C359" s="34"/>
-      <c r="D359" s="139" t="s">
-        <v>696</v>
-      </c>
-      <c r="E359" s="72"/>
-      <c r="F359" s="140"/>
-      <c r="G359" s="138">
-        <f>+F359+F360+F361</f>
-        <v>0</v>
-      </c>
-      <c r="H359" s="68"/>
-    </row>
-    <row r="360" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D359" s="71"/>
+      <c r="E359" s="72" t="s">
+        <v>680</v>
+      </c>
+      <c r="F359" s="140">
+        <f>IFERROR(VLOOKUP(E359,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G359" s="138"/>
+      <c r="H359" s="132"/>
+      <c r="I359" s="134"/>
+      <c r="J359" s="72"/>
+      <c r="K359" s="72"/>
+      <c r="L359" s="72"/>
+      <c r="M359" s="72"/>
+      <c r="N359" s="72"/>
+    </row>
+    <row r="360" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A360" s="76"/>
       <c r="B360" s="76"/>
       <c r="C360" s="34"/>
-      <c r="D360" s="132"/>
+      <c r="D360" s="71"/>
       <c r="E360" s="72" t="s">
-        <v>697</v>
+        <v>681</v>
       </c>
       <c r="F360" s="140">
         <f>IFERROR(VLOOKUP(E360,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G360" s="138"/>
-      <c r="H360" s="68"/>
-    </row>
-    <row r="361" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H360" s="132"/>
+      <c r="I360" s="134"/>
+      <c r="J360" s="72"/>
+      <c r="K360" s="72"/>
+      <c r="L360" s="72"/>
+      <c r="M360" s="72"/>
+      <c r="N360" s="72"/>
+    </row>
+    <row r="361" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="76"/>
       <c r="B361" s="76"/>
       <c r="C361" s="34"/>
-      <c r="D361" s="132"/>
+      <c r="D361" s="71"/>
       <c r="E361" s="72" t="s">
-        <v>698</v>
+        <v>682</v>
       </c>
       <c r="F361" s="140">
         <f>IFERROR(VLOOKUP(E361,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G361" s="138"/>
-      <c r="H361" s="68"/>
-    </row>
-    <row r="362" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A362" s="76"/>
       <c r="B362" s="76"/>
       <c r="C362" s="34"/>
-      <c r="D362" s="139" t="s">
-        <v>699</v>
-      </c>
-      <c r="E362" s="72"/>
-      <c r="F362" s="140"/>
-      <c r="G362" s="138">
-        <f>+F362+F363</f>
-        <v>0</v>
-      </c>
-      <c r="H362" s="68"/>
-    </row>
-    <row r="363" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D362" s="71"/>
+      <c r="E362" s="72" t="s">
+        <v>683</v>
+      </c>
+      <c r="F362" s="140">
+        <f>IFERROR(VLOOKUP(E362,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G362" s="138"/>
+    </row>
+    <row r="363" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="76"/>
       <c r="B363" s="76"/>
       <c r="C363" s="34"/>
-      <c r="D363" s="139"/>
+      <c r="D363" s="71"/>
       <c r="E363" s="72" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="F363" s="140">
         <f>IFERROR(VLOOKUP(E363,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G363" s="138"/>
-      <c r="H363" s="68"/>
     </row>
     <row r="364" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="76"/>
       <c r="B364" s="76"/>
       <c r="C364" s="34"/>
-      <c r="D364" s="71" t="s">
-        <v>700</v>
-      </c>
-      <c r="E364" s="71"/>
-      <c r="F364" s="140"/>
-      <c r="G364" s="138">
-        <f>SUM(F364:F367)</f>
-        <v>0</v>
-      </c>
+      <c r="D364" s="71"/>
+      <c r="E364" s="72" t="s">
+        <v>685</v>
+      </c>
+      <c r="F364" s="140">
+        <f>IFERROR(VLOOKUP(E364,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G364" s="138"/>
     </row>
     <row r="365" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="76"/>
@@ -13414,214 +13185,226 @@
       <c r="C365" s="34"/>
       <c r="D365" s="71"/>
       <c r="E365" s="72" t="s">
-        <v>701</v>
+        <v>686</v>
       </c>
       <c r="F365" s="140">
         <f>IFERROR(VLOOKUP(E365,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G365" s="138"/>
     </row>
-    <row r="366" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" s="76"/>
       <c r="B366" s="76"/>
       <c r="C366" s="34"/>
       <c r="D366" s="71"/>
-      <c r="E366" s="72" t="s">
-        <v>702</v>
+      <c r="E366" s="151" t="s">
+        <v>687</v>
       </c>
       <c r="F366" s="140">
         <f>IFERROR(VLOOKUP(E366,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G366" s="138"/>
-    </row>
-    <row r="367" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H366" s="68" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="367" ht="12.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A367" s="76"/>
       <c r="B367" s="76"/>
       <c r="C367" s="34"/>
-      <c r="D367" s="71"/>
-      <c r="E367" s="72" t="s">
-        <v>703</v>
-      </c>
-      <c r="F367" s="140">
-        <f>IFERROR(VLOOKUP(E367,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G367" s="138"/>
-    </row>
-    <row r="368" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D367" s="71" t="s">
+        <v>688</v>
+      </c>
+      <c r="E367" s="72"/>
+      <c r="F367" s="140"/>
+      <c r="G367" s="187">
+        <f>SUM(F368:F374)</f>
+      </c>
+      <c r="H367" s="68"/>
+      <c r="I367" s="164"/>
+      <c r="J367" s="72"/>
+      <c r="K367" s="72"/>
+      <c r="L367" s="72"/>
+      <c r="M367" s="72"/>
+    </row>
+    <row r="368" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="76"/>
       <c r="B368" s="76"/>
       <c r="C368" s="34"/>
-      <c r="D368" s="71" t="s">
-        <v>704</v>
-      </c>
-      <c r="E368" s="188"/>
-      <c r="F368" s="140"/>
-      <c r="G368" s="138">
-        <f>+F368</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="369" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D368" s="132"/>
+      <c r="E368" s="72" t="s">
+        <v>689</v>
+      </c>
+      <c r="F368" s="140">
+        <f>IFERROR(VLOOKUP(E368,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+    </row>
+    <row r="369" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" s="76"/>
       <c r="B369" s="76"/>
       <c r="C369" s="34"/>
-      <c r="D369" s="71" t="s">
-        <v>705</v>
-      </c>
-      <c r="E369" s="188"/>
-      <c r="F369" s="140"/>
-      <c r="G369" s="187">
-        <f>SUM(F369:F374)</f>
-        <v>283508619.32</v>
-      </c>
-    </row>
-    <row r="370" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D369" s="71"/>
+      <c r="E369" s="72" t="s">
+        <v>690</v>
+      </c>
+      <c r="F369" s="140">
+        <f>IFERROR(VLOOKUP(E369,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G369" s="138"/>
+      <c r="H369" s="68"/>
+    </row>
+    <row r="370" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" s="76"/>
       <c r="B370" s="76"/>
       <c r="C370" s="34"/>
       <c r="D370" s="71"/>
       <c r="E370" s="72" t="s">
-        <v>706</v>
+        <v>691</v>
       </c>
       <c r="F370" s="140">
         <f>IFERROR(VLOOKUP(E370,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G370" s="138"/>
-    </row>
-    <row r="371" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H370" s="68"/>
+    </row>
+    <row r="371" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" s="76"/>
       <c r="B371" s="76"/>
       <c r="C371" s="34"/>
       <c r="D371" s="71"/>
       <c r="E371" s="72" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="F371" s="140">
         <f>IFERROR(VLOOKUP(E371,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>226261134.24</v>
       </c>
       <c r="G371" s="138"/>
-    </row>
-    <row r="372" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H371" s="68"/>
+    </row>
+    <row r="372" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" s="76"/>
       <c r="B372" s="76"/>
       <c r="C372" s="34"/>
       <c r="D372" s="71"/>
       <c r="E372" s="72" t="s">
-        <v>708</v>
+        <v>693</v>
       </c>
       <c r="F372" s="140">
         <f>IFERROR(VLOOKUP(E372,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>56730956.08</v>
       </c>
       <c r="G372" s="138"/>
-    </row>
-    <row r="373" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H372" s="68"/>
+    </row>
+    <row r="373" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" s="76"/>
       <c r="B373" s="76"/>
       <c r="C373" s="34"/>
       <c r="D373" s="71"/>
       <c r="E373" s="72" t="s">
-        <v>709</v>
+        <v>694</v>
       </c>
       <c r="F373" s="140">
         <f>IFERROR(VLOOKUP(E373,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>516529</v>
       </c>
       <c r="G373" s="138"/>
-    </row>
-    <row r="374" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H373" s="68"/>
+    </row>
+    <row r="374" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" s="76"/>
       <c r="B374" s="76"/>
       <c r="C374" s="34"/>
       <c r="D374" s="71"/>
       <c r="E374" s="72" t="s">
-        <v>710</v>
+        <v>695</v>
       </c>
       <c r="F374" s="140">
         <f>IFERROR(VLOOKUP(E374,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G374" s="138"/>
-    </row>
-    <row r="375" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H374" s="68"/>
+    </row>
+    <row r="375" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" s="76"/>
       <c r="B375" s="76"/>
       <c r="C375" s="34"/>
-      <c r="D375" s="71" t="s">
-        <v>711</v>
-      </c>
-      <c r="E375" s="76"/>
+      <c r="D375" s="139" t="s">
+        <v>696</v>
+      </c>
+      <c r="E375" s="72"/>
       <c r="F375" s="140"/>
-      <c r="G375" s="187">
-        <f>SUM(F376:F384)</f>
-        <v>58572858.17</v>
-      </c>
-    </row>
-    <row r="376" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G375" s="138">
+        <f>+F375+F376+F377</f>
+      </c>
+      <c r="H375" s="68"/>
+    </row>
+    <row r="376" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" s="76"/>
       <c r="B376" s="76"/>
       <c r="C376" s="34"/>
-      <c r="D376" s="71"/>
+      <c r="D376" s="132"/>
       <c r="E376" s="72" t="s">
-        <v>712</v>
+        <v>697</v>
       </c>
       <c r="F376" s="140">
         <f>IFERROR(VLOOKUP(E376,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G376" s="138"/>
-    </row>
-    <row r="377" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H376" s="68"/>
+    </row>
+    <row r="377" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" s="76"/>
       <c r="B377" s="76"/>
       <c r="C377" s="34"/>
-      <c r="D377" s="71"/>
+      <c r="D377" s="132"/>
       <c r="E377" s="72" t="s">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="F377" s="140">
         <f>IFERROR(VLOOKUP(E377,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>45070376.57</v>
       </c>
       <c r="G377" s="138"/>
-    </row>
-    <row r="378" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H377" s="68"/>
+    </row>
+    <row r="378" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" s="76"/>
       <c r="B378" s="76"/>
       <c r="C378" s="34"/>
-      <c r="D378" s="71"/>
-      <c r="E378" s="72" t="s">
-        <v>714</v>
-      </c>
-      <c r="F378" s="140">
-        <f>IFERROR(VLOOKUP(E378,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G378" s="138"/>
-    </row>
-    <row r="379" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D378" s="139" t="s">
+        <v>699</v>
+      </c>
+      <c r="E378" s="72"/>
+      <c r="F378" s="140"/>
+      <c r="G378" s="138">
+        <f>+F378+F379</f>
+      </c>
+      <c r="H378" s="68"/>
+    </row>
+    <row r="379" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" s="76"/>
       <c r="B379" s="76"/>
       <c r="C379" s="34"/>
-      <c r="D379" s="71"/>
+      <c r="D379" s="139"/>
       <c r="E379" s="72" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="F379" s="140">
         <f>IFERROR(VLOOKUP(E379,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G379" s="138"/>
+      <c r="H379" s="68"/>
     </row>
     <row r="380" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A380" s="76"/>
       <c r="B380" s="76"/>
       <c r="C380" s="34"/>
-      <c r="D380" s="71"/>
-      <c r="E380" s="72" t="s">
-        <v>716</v>
-      </c>
-      <c r="F380" s="140">
-        <f>IFERROR(VLOOKUP(E380,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G380" s="138"/>
+      <c r="D380" s="71" t="s">
+        <v>700</v>
+      </c>
+      <c r="E380" s="71"/>
+      <c r="F380" s="140"/>
+      <c r="G380" s="138">
+        <f>SUM(F380:F383)</f>
+      </c>
     </row>
     <row r="381" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="76"/>
@@ -13629,11 +13412,10 @@
       <c r="C381" s="34"/>
       <c r="D381" s="71"/>
       <c r="E381" s="72" t="s">
-        <v>717</v>
+        <v>701</v>
       </c>
       <c r="F381" s="140">
         <f>IFERROR(VLOOKUP(E381,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>13502481.6</v>
       </c>
       <c r="G381" s="138"/>
     </row>
@@ -13643,7 +13425,7 @@
       <c r="C382" s="34"/>
       <c r="D382" s="71"/>
       <c r="E382" s="72" t="s">
-        <v>718</v>
+        <v>702</v>
       </c>
       <c r="F382" s="140">
         <f>IFERROR(VLOOKUP(E382,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13656,7 +13438,7 @@
       <c r="C383" s="34"/>
       <c r="D383" s="71"/>
       <c r="E383" s="72" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="F383" s="140">
         <f>IFERROR(VLOOKUP(E383,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13667,74 +13449,66 @@
       <c r="A384" s="76"/>
       <c r="B384" s="76"/>
       <c r="C384" s="34"/>
-      <c r="D384" s="71"/>
-      <c r="E384" s="151" t="s">
-        <v>720</v>
-      </c>
-      <c r="F384" s="140">
-        <f>IFERROR(VLOOKUP(E384,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G384" s="138"/>
+      <c r="D384" s="71" t="s">
+        <v>704</v>
+      </c>
+      <c r="E384" s="188"/>
+      <c r="F384" s="140"/>
+      <c r="G384" s="138">
+        <f>+F384</f>
+      </c>
     </row>
     <row r="385" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="76"/>
       <c r="B385" s="76"/>
       <c r="C385" s="34"/>
       <c r="D385" s="71" t="s">
-        <v>721</v>
-      </c>
-      <c r="E385" s="71"/>
+        <v>705</v>
+      </c>
+      <c r="E385" s="188"/>
       <c r="F385" s="140"/>
-      <c r="G385" s="138">
-        <f>+F385</f>
-        <v>0</v>
+      <c r="G385" s="187">
+        <f>SUM(F385:F390)</f>
       </c>
     </row>
     <row r="386" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="76"/>
       <c r="B386" s="76"/>
       <c r="C386" s="34"/>
-      <c r="D386" s="139" t="s">
-        <v>722</v>
-      </c>
-      <c r="E386" s="72"/>
-      <c r="F386" s="140"/>
-      <c r="G386" s="138">
-        <f>+F386</f>
-        <v>0</v>
-      </c>
+      <c r="D386" s="71"/>
+      <c r="E386" s="72" t="s">
+        <v>706</v>
+      </c>
+      <c r="F386" s="140">
+        <f>IFERROR(VLOOKUP(E386,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G386" s="138"/>
     </row>
     <row r="387" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="76"/>
       <c r="B387" s="76"/>
       <c r="C387" s="34"/>
-      <c r="D387" s="71" t="s">
-        <v>723</v>
-      </c>
-      <c r="E387" s="71"/>
-      <c r="F387" s="140"/>
-      <c r="G387" s="138">
-        <f>+F387</f>
-        <v>0</v>
-      </c>
+      <c r="D387" s="71"/>
+      <c r="E387" s="72" t="s">
+        <v>707</v>
+      </c>
+      <c r="F387" s="140">
+        <f>IFERROR(VLOOKUP(E387,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G387" s="138"/>
     </row>
     <row r="388" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="76"/>
       <c r="B388" s="76"/>
       <c r="C388" s="34"/>
-      <c r="D388" s="71" t="s">
-        <v>724</v>
-      </c>
+      <c r="D388" s="71"/>
       <c r="E388" s="72" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="F388" s="140">
         <f>IFERROR(VLOOKUP(E388,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G388" s="138">
-        <f>+F388+F389</f>
-        <v>0</v>
-      </c>
+      <c r="G388" s="138"/>
     </row>
     <row r="389" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="76"/>
@@ -13742,7 +13516,7 @@
       <c r="C389" s="34"/>
       <c r="D389" s="71"/>
       <c r="E389" s="72" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="F389" s="140">
         <f>IFERROR(VLOOKUP(E389,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13753,99 +13527,66 @@
       <c r="A390" s="76"/>
       <c r="B390" s="76"/>
       <c r="C390" s="34"/>
-      <c r="D390" s="71" t="s">
-        <v>727</v>
-      </c>
-      <c r="E390" s="71"/>
-      <c r="F390" s="140"/>
-      <c r="G390" s="138">
-        <f>+F390</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D390" s="71"/>
+      <c r="E390" s="72" t="s">
+        <v>710</v>
+      </c>
+      <c r="F390" s="140">
+        <f>IFERROR(VLOOKUP(E390,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G390" s="138"/>
+    </row>
+    <row r="391" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="76"/>
       <c r="B391" s="76"/>
       <c r="C391" s="34"/>
       <c r="D391" s="71" t="s">
-        <v>728</v>
-      </c>
-      <c r="E391" s="71"/>
+        <v>711</v>
+      </c>
+      <c r="E391" s="76"/>
       <c r="F391" s="140"/>
       <c r="G391" s="187">
-        <f>SUM(F391:F393)</f>
-        <v>15882026</v>
-      </c>
-      <c r="H391" s="132"/>
-      <c r="I391" s="134"/>
-      <c r="J391" s="132"/>
-      <c r="K391" s="72"/>
-      <c r="L391" s="72"/>
-      <c r="M391" s="72"/>
-      <c r="N391" s="72"/>
-      <c r="O391" s="72"/>
-    </row>
-    <row r="392" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+        <f>SUM(F392:F400)</f>
+      </c>
+    </row>
+    <row r="392" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" s="76"/>
       <c r="B392" s="76"/>
       <c r="C392" s="34"/>
       <c r="D392" s="71"/>
       <c r="E392" s="72" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="F392" s="140">
         <f>IFERROR(VLOOKUP(E392,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G392" s="138"/>
-      <c r="H392" s="132"/>
-      <c r="I392" s="134"/>
-      <c r="J392" s="132"/>
-      <c r="K392" s="72"/>
-      <c r="L392" s="72"/>
-      <c r="M392" s="72"/>
-      <c r="N392" s="72"/>
-      <c r="O392" s="72"/>
-    </row>
-    <row r="393" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" s="76"/>
       <c r="B393" s="76"/>
       <c r="C393" s="34"/>
       <c r="D393" s="71"/>
       <c r="E393" s="72" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="F393" s="140">
         <f>IFERROR(VLOOKUP(E393,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>15882026</v>
       </c>
       <c r="G393" s="138"/>
-      <c r="H393" s="132"/>
-      <c r="I393" s="134"/>
-      <c r="J393" s="132"/>
-      <c r="K393" s="72"/>
-      <c r="L393" s="72"/>
-      <c r="M393" s="72"/>
-      <c r="N393" s="72"/>
-      <c r="O393" s="72"/>
     </row>
     <row r="394" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A394" s="76"/>
       <c r="B394" s="76"/>
       <c r="C394" s="34"/>
-      <c r="D394" s="71" t="s">
-        <v>731</v>
-      </c>
+      <c r="D394" s="71"/>
       <c r="E394" s="72" t="s">
-        <v>732</v>
+        <v>714</v>
       </c>
       <c r="F394" s="140">
         <f>IFERROR(VLOOKUP(E394,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>5598557</v>
-      </c>
-      <c r="G394" s="138">
-        <f>+F394+F395+F396+F397</f>
-        <v>5598557</v>
-      </c>
+      </c>
+      <c r="G394" s="138"/>
     </row>
     <row r="395" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A395" s="76"/>
@@ -13853,7 +13594,7 @@
       <c r="C395" s="34"/>
       <c r="D395" s="71"/>
       <c r="E395" s="72" t="s">
-        <v>733</v>
+        <v>715</v>
       </c>
       <c r="F395" s="140">
         <f>IFERROR(VLOOKUP(E395,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13866,7 +13607,7 @@
       <c r="C396" s="34"/>
       <c r="D396" s="71"/>
       <c r="E396" s="72" t="s">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="F396" s="140">
         <f>IFERROR(VLOOKUP(E396,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13879,7 +13620,7 @@
       <c r="C397" s="34"/>
       <c r="D397" s="71"/>
       <c r="E397" s="72" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="F397" s="140">
         <f>IFERROR(VLOOKUP(E397,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -13890,74 +13631,65 @@
       <c r="A398" s="76"/>
       <c r="B398" s="76"/>
       <c r="C398" s="34"/>
-      <c r="D398" s="71" t="s">
-        <v>736</v>
-      </c>
-      <c r="E398" s="188"/>
-      <c r="F398" s="140"/>
-      <c r="G398" s="138">
-        <f>SUM(F398:F399)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="399" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D398" s="71"/>
+      <c r="E398" s="72" t="s">
+        <v>718</v>
+      </c>
+      <c r="F398" s="140">
+        <f>IFERROR(VLOOKUP(E398,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G398" s="138"/>
+    </row>
+    <row r="399" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A399" s="76"/>
       <c r="B399" s="76"/>
       <c r="C399" s="34"/>
-      <c r="D399" s="139"/>
+      <c r="D399" s="71"/>
       <c r="E399" s="72" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="F399" s="140">
         <f>IFERROR(VLOOKUP(E399,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G399" s="138"/>
-      <c r="H399" s="72"/>
     </row>
     <row r="400" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A400" s="76"/>
       <c r="B400" s="76"/>
       <c r="C400" s="34"/>
-      <c r="D400" s="71" t="s">
-        <v>738</v>
-      </c>
-      <c r="E400" s="188"/>
-      <c r="F400" s="140"/>
-      <c r="G400" s="138">
-        <f>+F400+F401</f>
-        <v>0</v>
-      </c>
+      <c r="D400" s="71"/>
+      <c r="E400" s="151" t="s">
+        <v>720</v>
+      </c>
+      <c r="F400" s="140">
+        <f>IFERROR(VLOOKUP(E400,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G400" s="138"/>
     </row>
     <row r="401" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A401" s="76"/>
       <c r="B401" s="76"/>
       <c r="C401" s="34"/>
-      <c r="D401" s="71"/>
-      <c r="E401" s="72" t="s">
-        <v>739</v>
-      </c>
-      <c r="F401" s="140">
-        <f>IFERROR(VLOOKUP(E401,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G401" s="138"/>
+      <c r="D401" s="71" t="s">
+        <v>721</v>
+      </c>
+      <c r="E401" s="71"/>
+      <c r="F401" s="140"/>
+      <c r="G401" s="138">
+        <f>+F401</f>
+      </c>
     </row>
     <row r="402" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A402" s="76"/>
       <c r="B402" s="76"/>
       <c r="C402" s="34"/>
-      <c r="D402" s="71" t="s">
-        <v>740</v>
-      </c>
-      <c r="E402" s="71" t="s">
-        <v>741</v>
-      </c>
-      <c r="F402" s="140">
-        <f>IFERROR(VLOOKUP(E402,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>314486283.55</v>
-      </c>
-      <c r="G402" s="187">
+      <c r="D402" s="139" t="s">
+        <v>722</v>
+      </c>
+      <c r="E402" s="72"/>
+      <c r="F402" s="140"/>
+      <c r="G402" s="138">
         <f>+F402</f>
-        <v>314486283.55</v>
       </c>
     </row>
     <row r="403" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -13965,134 +13697,152 @@
       <c r="B403" s="76"/>
       <c r="C403" s="34"/>
       <c r="D403" s="71" t="s">
-        <v>742</v>
-      </c>
-      <c r="E403" s="188"/>
+        <v>723</v>
+      </c>
+      <c r="E403" s="71"/>
       <c r="F403" s="140"/>
       <c r="G403" s="138">
-        <f>+F404+F405</f>
-        <v>0</v>
+        <f>+F403</f>
       </c>
     </row>
     <row r="404" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A404" s="76"/>
       <c r="B404" s="76"/>
       <c r="C404" s="34"/>
-      <c r="D404" s="71"/>
-      <c r="E404" s="72" t="s">
-        <v>743</v>
-      </c>
-      <c r="F404" s="140">
-        <f>IFERROR(VLOOKUP(E404,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G404" s="138"/>
-    </row>
-    <row r="405" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D404" s="71" t="s">
+        <v>724</v>
+      </c>
+      <c r="E404" s="72"/>
+      <c r="F404" s="140"/>
+      <c r="G404" s="138">
+        <f>+F405+F406</f>
+      </c>
+    </row>
+    <row r="405" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="76"/>
       <c r="B405" s="76"/>
       <c r="C405" s="34"/>
-      <c r="D405" s="76"/>
+      <c r="D405" s="132"/>
       <c r="E405" s="72" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="F405" s="140">
         <f>IFERROR(VLOOKUP(E405,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G405" s="138"/>
     </row>
     <row r="406" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A406" s="76"/>
       <c r="B406" s="76"/>
       <c r="C406" s="34"/>
-      <c r="D406" s="71" t="s">
-        <v>745</v>
-      </c>
-      <c r="E406" s="72"/>
-      <c r="F406" s="140"/>
-      <c r="G406" s="138">
-        <f>+F406</f>
-        <v>0</v>
-      </c>
+      <c r="D406" s="71"/>
+      <c r="E406" s="72" t="s">
+        <v>726</v>
+      </c>
+      <c r="F406" s="140">
+        <f>IFERROR(VLOOKUP(E406,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G406" s="138"/>
     </row>
     <row r="407" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A407" s="76"/>
       <c r="B407" s="76"/>
       <c r="C407" s="34"/>
       <c r="D407" s="71" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="E407" s="71"/>
       <c r="F407" s="140"/>
-      <c r="G407" s="187">
-        <f>SUM(F407:F413)</f>
-        <v>901685.37</v>
-      </c>
-    </row>
-    <row r="408" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G407" s="138">
+        <f>+F407</f>
+      </c>
+    </row>
+    <row r="408" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A408" s="76"/>
       <c r="B408" s="76"/>
       <c r="C408" s="34"/>
-      <c r="D408" s="71"/>
-      <c r="E408" s="151" t="s">
-        <v>747</v>
-      </c>
-      <c r="F408" s="140">
-        <f>IFERROR(VLOOKUP(E408,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G408" s="138"/>
-    </row>
-    <row r="409" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D408" s="71" t="s">
+        <v>728</v>
+      </c>
+      <c r="E408" s="71"/>
+      <c r="F408" s="140"/>
+      <c r="G408" s="187">
+        <f>SUM(F408:F410)</f>
+      </c>
+      <c r="H408" s="132"/>
+      <c r="I408" s="134"/>
+      <c r="J408" s="132"/>
+      <c r="K408" s="72"/>
+      <c r="L408" s="72"/>
+      <c r="M408" s="72"/>
+      <c r="N408" s="72"/>
+      <c r="O408" s="72"/>
+    </row>
+    <row r="409" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A409" s="76"/>
       <c r="B409" s="76"/>
       <c r="C409" s="34"/>
       <c r="D409" s="71"/>
       <c r="E409" s="72" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="F409" s="140">
         <f>IFERROR(VLOOKUP(E409,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G409" s="138"/>
-    </row>
-    <row r="410" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H409" s="132"/>
+      <c r="I409" s="134"/>
+      <c r="J409" s="132"/>
+      <c r="K409" s="72"/>
+      <c r="L409" s="72"/>
+      <c r="M409" s="72"/>
+      <c r="N409" s="72"/>
+      <c r="O409" s="72"/>
+    </row>
+    <row r="410" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A410" s="76"/>
       <c r="B410" s="76"/>
       <c r="C410" s="34"/>
       <c r="D410" s="71"/>
       <c r="E410" s="72" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="F410" s="140">
         <f>IFERROR(VLOOKUP(E410,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>901685.37</v>
       </c>
       <c r="G410" s="138"/>
+      <c r="H410" s="132"/>
+      <c r="I410" s="134"/>
+      <c r="J410" s="132"/>
+      <c r="K410" s="72"/>
+      <c r="L410" s="72"/>
+      <c r="M410" s="72"/>
+      <c r="N410" s="72"/>
+      <c r="O410" s="72"/>
     </row>
     <row r="411" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A411" s="76"/>
       <c r="B411" s="76"/>
       <c r="C411" s="34"/>
-      <c r="D411" s="71"/>
-      <c r="E411" s="72" t="s">
-        <v>750</v>
-      </c>
-      <c r="F411" s="140">
-        <f>IFERROR(VLOOKUP(E411,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G411" s="138"/>
-    </row>
-    <row r="412" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D411" s="71" t="s">
+        <v>731</v>
+      </c>
+      <c r="E411" s="72"/>
+      <c r="F411" s="140"/>
+      <c r="G411" s="138">
+        <f>+F412+F413+F414+F415</f>
+      </c>
+    </row>
+    <row r="412" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="76"/>
       <c r="B412" s="76"/>
       <c r="C412" s="34"/>
-      <c r="D412" s="71"/>
-      <c r="E412" s="151" t="s">
-        <v>751</v>
+      <c r="D412" s="132"/>
+      <c r="E412" s="72" t="s">
+        <v>732</v>
       </c>
       <c r="F412" s="140">
         <f>IFERROR(VLOOKUP(E412,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G412" s="138"/>
     </row>
     <row r="413" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A413" s="76"/>
@@ -14100,230 +13850,186 @@
       <c r="C413" s="34"/>
       <c r="D413" s="71"/>
       <c r="E413" s="72" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="F413" s="140">
         <f>IFERROR(VLOOKUP(E413,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G413" s="138"/>
     </row>
-    <row r="414" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A414" s="76"/>
       <c r="B414" s="76"/>
       <c r="C414" s="34"/>
-      <c r="D414" s="139" t="s">
-        <v>753</v>
-      </c>
+      <c r="D414" s="71"/>
       <c r="E414" s="72" t="s">
-        <v>754</v>
+        <v>734</v>
       </c>
       <c r="F414" s="140">
         <f>IFERROR(VLOOKUP(E414,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G414" s="187">
-        <f>+F414+F415</f>
-        <v>236115665.5</v>
-      </c>
-      <c r="H414" s="132"/>
-      <c r="I414" s="134"/>
-      <c r="J414" s="72"/>
-      <c r="K414" s="72"/>
-      <c r="L414" s="72"/>
-      <c r="M414" s="72"/>
-      <c r="N414" s="72"/>
-    </row>
-    <row r="415" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G414" s="138"/>
+    </row>
+    <row r="415" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A415" s="76"/>
       <c r="B415" s="76"/>
       <c r="C415" s="34"/>
-      <c r="D415" s="139"/>
+      <c r="D415" s="71"/>
       <c r="E415" s="72" t="s">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="F415" s="140">
         <f>IFERROR(VLOOKUP(E415,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>236115665.5</v>
       </c>
       <c r="G415" s="138"/>
-      <c r="H415" s="132"/>
-      <c r="I415" s="134"/>
-      <c r="J415" s="72"/>
-      <c r="K415" s="72"/>
-      <c r="L415" s="72"/>
-      <c r="M415" s="72"/>
-      <c r="N415" s="72"/>
     </row>
     <row r="416" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A416" s="76"/>
       <c r="B416" s="76"/>
       <c r="C416" s="34"/>
-      <c r="D416" s="139" t="s">
-        <v>755</v>
-      </c>
-      <c r="E416" s="72"/>
+      <c r="D416" s="71" t="s">
+        <v>736</v>
+      </c>
+      <c r="E416" s="188"/>
       <c r="F416" s="140"/>
       <c r="G416" s="138">
-        <f>+F416</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="417" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>SUM(F416:F417)</f>
+      </c>
+    </row>
+    <row r="417" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" s="76"/>
       <c r="B417" s="76"/>
       <c r="C417" s="34"/>
-      <c r="D417" s="139" t="s">
-        <v>756</v>
-      </c>
-      <c r="E417" s="151" t="s">
-        <v>757</v>
+      <c r="D417" s="139"/>
+      <c r="E417" s="72" t="s">
+        <v>737</v>
       </c>
       <c r="F417" s="140">
         <f>IFERROR(VLOOKUP(E417,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G417" s="187">
-        <f>SUM(F417:F424)</f>
-        <v>3799966.7</v>
-      </c>
-    </row>
-    <row r="418" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G417" s="138"/>
+      <c r="H417" s="72"/>
+    </row>
+    <row r="418" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A418" s="76"/>
       <c r="B418" s="76"/>
       <c r="C418" s="34"/>
-      <c r="D418" s="139"/>
-      <c r="E418" s="72" t="s">
-        <v>758</v>
-      </c>
-      <c r="F418" s="140">
-        <f>IFERROR(VLOOKUP(E418,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>3313483</v>
-      </c>
-      <c r="G418" s="138"/>
-      <c r="H418" s="72"/>
-      <c r="I418" s="164"/>
-    </row>
-    <row r="419" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D418" s="71" t="s">
+        <v>738</v>
+      </c>
+      <c r="E418" s="188"/>
+      <c r="F418" s="140"/>
+      <c r="G418" s="138">
+        <f>+F418+F419</f>
+      </c>
+    </row>
+    <row r="419" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A419" s="76"/>
       <c r="B419" s="76"/>
       <c r="C419" s="34"/>
-      <c r="D419" s="139"/>
+      <c r="D419" s="71"/>
       <c r="E419" s="72" t="s">
-        <v>759</v>
+        <v>739</v>
       </c>
       <c r="F419" s="140">
         <f>IFERROR(VLOOKUP(E419,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G419" s="138"/>
-      <c r="H419" s="72"/>
-      <c r="I419" s="164"/>
-    </row>
-    <row r="420" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A420" s="76"/>
       <c r="B420" s="76"/>
       <c r="C420" s="34"/>
-      <c r="D420" s="139"/>
-      <c r="E420" s="72" t="s">
-        <v>760</v>
+      <c r="D420" s="71" t="s">
+        <v>740</v>
+      </c>
+      <c r="E420" s="71" t="s">
+        <v>741</v>
       </c>
       <c r="F420" s="140">
         <f>IFERROR(VLOOKUP(E420,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>442383.7</v>
-      </c>
-      <c r="G420" s="138"/>
-      <c r="H420" s="72"/>
-      <c r="I420" s="164"/>
-    </row>
-    <row r="421" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      </c>
+      <c r="G420" s="187">
+        <f>+F420</f>
+      </c>
+    </row>
+    <row r="421" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A421" s="76"/>
       <c r="B421" s="76"/>
       <c r="C421" s="34"/>
-      <c r="D421" s="139"/>
-      <c r="E421" s="72" t="s">
-        <v>761</v>
-      </c>
-      <c r="F421" s="140">
-        <f>IFERROR(VLOOKUP(E421,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G421" s="138"/>
-      <c r="H421" s="72"/>
-      <c r="I421" s="164"/>
-    </row>
-    <row r="422" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D421" s="71" t="s">
+        <v>742</v>
+      </c>
+      <c r="E421" s="188"/>
+      <c r="F421" s="140"/>
+      <c r="G421" s="138">
+        <f>+F422+F423</f>
+      </c>
+    </row>
+    <row r="422" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A422" s="76"/>
       <c r="B422" s="76"/>
       <c r="C422" s="34"/>
-      <c r="D422" s="139"/>
+      <c r="D422" s="71"/>
       <c r="E422" s="72" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="F422" s="140">
         <f>IFERROR(VLOOKUP(E422,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G422" s="138"/>
-      <c r="H422" s="72"/>
-      <c r="I422" s="164"/>
-    </row>
-    <row r="423" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A423" s="76"/>
       <c r="B423" s="76"/>
       <c r="C423" s="34"/>
-      <c r="D423" s="139"/>
+      <c r="D423" s="76"/>
       <c r="E423" s="72" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="F423" s="140">
         <f>IFERROR(VLOOKUP(E423,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G423" s="138"/>
-      <c r="H423" s="72"/>
-      <c r="I423" s="164"/>
-    </row>
-    <row r="424" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A424" s="76"/>
       <c r="B424" s="76"/>
       <c r="C424" s="34"/>
-      <c r="D424" s="139"/>
-      <c r="E424" s="72" t="str">
-        <f>+'Balance de sumas y saldos'!A304</f>
-        <v>426880000 - Tasas Municipales Gs Campo</v>
-      </c>
-      <c r="F424" s="140">
-        <f>IFERROR(VLOOKUP(E424,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>44100</v>
-      </c>
-      <c r="G424" s="138"/>
-      <c r="H424" s="72"/>
-      <c r="I424" s="164"/>
+      <c r="D424" s="71" t="s">
+        <v>745</v>
+      </c>
+      <c r="E424" s="72"/>
+      <c r="F424" s="140"/>
+      <c r="G424" s="138">
+        <f>+F424</f>
+      </c>
     </row>
     <row r="425" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A425" s="76"/>
       <c r="B425" s="76"/>
       <c r="C425" s="34"/>
       <c r="D425" s="71" t="s">
-        <v>764</v>
+        <v>746</v>
       </c>
       <c r="E425" s="71"/>
-      <c r="F425" s="140">
-        <f>IFERROR(VLOOKUP(D425,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>63010431.79</v>
-      </c>
+      <c r="F425" s="140"/>
       <c r="G425" s="187">
-        <f>+F425</f>
-        <v>63010431.79</v>
+        <f>SUM(F425:F431)</f>
       </c>
     </row>
     <row r="426" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A426" s="76"/>
       <c r="B426" s="76"/>
       <c r="C426" s="34"/>
-      <c r="D426" s="71" t="s">
-        <v>765</v>
-      </c>
-      <c r="E426" s="71"/>
-      <c r="F426" s="140"/>
-      <c r="G426" s="187">
-        <f>SUM(F427:F434)</f>
-        <v>784842.52</v>
-      </c>
+      <c r="D426" s="71"/>
+      <c r="E426" s="151" t="s">
+        <v>747</v>
+      </c>
+      <c r="F426" s="140">
+        <f>IFERROR(VLOOKUP(E426,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G426" s="138"/>
     </row>
     <row r="427" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A427" s="76"/>
@@ -14331,7 +14037,7 @@
       <c r="C427" s="34"/>
       <c r="D427" s="71"/>
       <c r="E427" s="72" t="s">
-        <v>766</v>
+        <v>748</v>
       </c>
       <c r="F427" s="140">
         <f>IFERROR(VLOOKUP(E427,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14342,13 +14048,12 @@
       <c r="A428" s="76"/>
       <c r="B428" s="76"/>
       <c r="C428" s="34"/>
-      <c r="D428" s="76"/>
-      <c r="E428" s="71" t="s">
-        <v>767</v>
+      <c r="D428" s="71"/>
+      <c r="E428" s="72" t="s">
+        <v>749</v>
       </c>
       <c r="F428" s="140">
         <f>IFERROR(VLOOKUP(E428,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>632438.8</v>
       </c>
       <c r="G428" s="138"/>
     </row>
@@ -14356,13 +14061,12 @@
       <c r="A429" s="76"/>
       <c r="B429" s="76"/>
       <c r="C429" s="34"/>
-      <c r="D429" s="76"/>
-      <c r="E429" s="71" t="s">
-        <v>768</v>
+      <c r="D429" s="71"/>
+      <c r="E429" s="72" t="s">
+        <v>750</v>
       </c>
       <c r="F429" s="140">
         <f>IFERROR(VLOOKUP(E429,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>152403.72</v>
       </c>
       <c r="G429" s="138"/>
     </row>
@@ -14370,9 +14074,9 @@
       <c r="A430" s="76"/>
       <c r="B430" s="76"/>
       <c r="C430" s="34"/>
-      <c r="D430" s="76"/>
-      <c r="E430" s="71" t="s">
-        <v>769</v>
+      <c r="D430" s="71"/>
+      <c r="E430" s="151" t="s">
+        <v>751</v>
       </c>
       <c r="F430" s="140">
         <f>IFERROR(VLOOKUP(E430,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14383,270 +14087,285 @@
       <c r="A431" s="76"/>
       <c r="B431" s="76"/>
       <c r="C431" s="34"/>
-      <c r="D431" s="76"/>
+      <c r="D431" s="71"/>
       <c r="E431" s="72" t="s">
-        <v>770</v>
+        <v>752</v>
       </c>
       <c r="F431" s="140">
         <f>IFERROR(VLOOKUP(E431,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G431" s="138"/>
     </row>
-    <row r="432" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A432" s="76"/>
       <c r="B432" s="76"/>
       <c r="C432" s="34"/>
-      <c r="D432" s="76"/>
-      <c r="E432" s="72" t="s">
-        <v>771</v>
-      </c>
-      <c r="F432" s="140">
-        <f>IFERROR(VLOOKUP(E432,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G432" s="138"/>
-    </row>
-    <row r="433" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D432" s="139" t="s">
+        <v>753</v>
+      </c>
+      <c r="E432" s="72"/>
+      <c r="F432" s="140"/>
+      <c r="G432" s="187">
+        <f>+F433+F434</f>
+      </c>
+      <c r="H432" s="132"/>
+      <c r="I432" s="134"/>
+      <c r="J432" s="72"/>
+      <c r="K432" s="72"/>
+      <c r="L432" s="72"/>
+      <c r="M432" s="72"/>
+      <c r="N432" s="72"/>
+    </row>
+    <row r="433" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="76"/>
       <c r="B433" s="76"/>
       <c r="C433" s="34"/>
-      <c r="D433" s="76"/>
+      <c r="D433" s="132"/>
       <c r="E433" s="72" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
       <c r="F433" s="140">
         <f>IFERROR(VLOOKUP(E433,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G433" s="138"/>
-    </row>
-    <row r="434" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A434" s="76"/>
       <c r="B434" s="76"/>
       <c r="C434" s="34"/>
-      <c r="D434" s="76"/>
+      <c r="D434" s="139"/>
       <c r="E434" s="72" t="s">
-        <v>773</v>
+        <v>753</v>
       </c>
       <c r="F434" s="140">
         <f>IFERROR(VLOOKUP(E434,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G434" s="138"/>
+      <c r="H434" s="132"/>
+      <c r="I434" s="134"/>
+      <c r="J434" s="72"/>
+      <c r="K434" s="72"/>
+      <c r="L434" s="72"/>
+      <c r="M434" s="72"/>
+      <c r="N434" s="72"/>
     </row>
     <row r="435" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A435" s="76"/>
       <c r="B435" s="76"/>
       <c r="C435" s="34"/>
-      <c r="D435" s="71" t="s">
-        <v>774</v>
-      </c>
-      <c r="E435" s="71"/>
+      <c r="D435" s="139" t="s">
+        <v>755</v>
+      </c>
+      <c r="E435" s="72"/>
       <c r="F435" s="140"/>
-      <c r="G435" s="187">
-        <f>SUM(F435:F439)</f>
-        <v>17921832.18</v>
+      <c r="G435" s="138">
+        <f>+F435</f>
       </c>
     </row>
     <row r="436" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A436" s="76"/>
       <c r="B436" s="76"/>
       <c r="C436" s="34"/>
-      <c r="D436" s="71"/>
-      <c r="E436" s="72" t="s">
-        <v>775</v>
-      </c>
-      <c r="F436" s="140">
-        <f>IFERROR(VLOOKUP(E436,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>1413626.44</v>
-      </c>
-      <c r="G436" s="138"/>
-    </row>
-    <row r="437" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D436" s="139" t="s">
+        <v>756</v>
+      </c>
+      <c r="E436" s="151"/>
+      <c r="F436" s="140"/>
+      <c r="G436" s="187">
+        <f>SUM(F437:F444)</f>
+      </c>
+    </row>
+    <row r="437" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="76"/>
       <c r="B437" s="76"/>
       <c r="C437" s="34"/>
-      <c r="D437" s="71"/>
-      <c r="E437" s="72" t="s">
-        <v>776</v>
+      <c r="D437" s="132"/>
+      <c r="E437" s="151" t="s">
+        <v>757</v>
       </c>
       <c r="F437" s="140">
         <f>IFERROR(VLOOKUP(E437,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>16508205.74</v>
-      </c>
-      <c r="G437" s="138"/>
-    </row>
-    <row r="438" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="438" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" s="76"/>
       <c r="B438" s="76"/>
       <c r="C438" s="34"/>
-      <c r="D438" s="71"/>
+      <c r="D438" s="139"/>
       <c r="E438" s="72" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="F438" s="140">
         <f>IFERROR(VLOOKUP(E438,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G438" s="138"/>
-    </row>
-    <row r="439" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H438" s="72"/>
+      <c r="I438" s="164"/>
+    </row>
+    <row r="439" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" s="76"/>
       <c r="B439" s="76"/>
       <c r="C439" s="34"/>
-      <c r="D439" s="71"/>
+      <c r="D439" s="139"/>
       <c r="E439" s="72" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="F439" s="140">
         <f>IFERROR(VLOOKUP(E439,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G439" s="138"/>
-    </row>
-    <row r="440" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H439" s="72"/>
+      <c r="I439" s="164"/>
+    </row>
+    <row r="440" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A440" s="76"/>
       <c r="B440" s="76"/>
       <c r="C440" s="34"/>
-      <c r="D440" s="71" t="s">
-        <v>779</v>
-      </c>
-      <c r="E440" s="188"/>
-      <c r="F440" s="140"/>
-      <c r="G440" s="138">
-        <f>+F440</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="441" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D440" s="139"/>
+      <c r="E440" s="72" t="s">
+        <v>760</v>
+      </c>
+      <c r="F440" s="140">
+        <f>IFERROR(VLOOKUP(E440,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G440" s="138"/>
+      <c r="H440" s="72"/>
+      <c r="I440" s="164"/>
+    </row>
+    <row r="441" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" s="76"/>
       <c r="B441" s="76"/>
       <c r="C441" s="34"/>
-      <c r="D441" s="139" t="s">
-        <v>780</v>
-      </c>
-      <c r="E441" s="76"/>
-      <c r="F441" s="140"/>
-      <c r="G441" s="138">
-        <f>SUM(F441:F443)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="442" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D441" s="139"/>
+      <c r="E441" s="72" t="s">
+        <v>761</v>
+      </c>
+      <c r="F441" s="140">
+        <f>IFERROR(VLOOKUP(E441,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G441" s="138"/>
+      <c r="H441" s="72"/>
+      <c r="I441" s="164"/>
+    </row>
+    <row r="442" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" s="76"/>
       <c r="B442" s="76"/>
       <c r="C442" s="34"/>
       <c r="D442" s="139"/>
       <c r="E442" s="72" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="F442" s="140">
         <f>IFERROR(VLOOKUP(E442,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G442" s="138"/>
-    </row>
-    <row r="443" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H442" s="72"/>
+      <c r="I442" s="164"/>
+    </row>
+    <row r="443" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A443" s="76"/>
       <c r="B443" s="76"/>
       <c r="C443" s="34"/>
       <c r="D443" s="139"/>
       <c r="E443" s="72" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="F443" s="140">
         <f>IFERROR(VLOOKUP(E443,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G443" s="138"/>
-    </row>
-    <row r="444" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H443" s="72"/>
+      <c r="I443" s="164"/>
+    </row>
+    <row r="444" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A444" s="76"/>
       <c r="B444" s="76"/>
       <c r="C444" s="34"/>
-      <c r="D444" s="71" t="s">
-        <v>783</v>
-      </c>
-      <c r="E444" s="188"/>
-      <c r="F444" s="140"/>
-      <c r="G444" s="187">
-        <f>SUM(F445:F448)</f>
-        <v>101483.28</v>
-      </c>
+      <c r="D444" s="139"/>
+      <c r="E444" s="72" t="str">
+        <f>+'Balance de sumas y saldos'!A304</f>
+        <v>426880000 - Tasas Municipales Gs Campo</v>
+      </c>
+      <c r="F444" s="140">
+        <f>IFERROR(VLOOKUP(E444,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G444" s="138"/>
+      <c r="H444" s="72"/>
+      <c r="I444" s="164"/>
     </row>
     <row r="445" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A445" s="76"/>
       <c r="B445" s="76"/>
       <c r="C445" s="34"/>
-      <c r="D445" s="71"/>
-      <c r="E445" s="151" t="s">
-        <v>784</v>
-      </c>
+      <c r="D445" s="71" t="s">
+        <v>764</v>
+      </c>
+      <c r="E445" s="71"/>
       <c r="F445" s="140">
-        <f>IFERROR(VLOOKUP(E445,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G445" s="138"/>
-    </row>
-    <row r="446" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(D445,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G445" s="187">
+        <f>+F445</f>
+      </c>
+    </row>
+    <row r="446" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A446" s="76"/>
       <c r="B446" s="76"/>
       <c r="C446" s="34"/>
-      <c r="D446" s="71"/>
-      <c r="E446" s="72" t="s">
-        <v>785</v>
-      </c>
-      <c r="F446" s="140">
-        <f>IFERROR(VLOOKUP(E446,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>101483.28</v>
-      </c>
-      <c r="G446" s="138"/>
-      <c r="H446" s="72"/>
-      <c r="I446" s="164"/>
-    </row>
-    <row r="447" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D446" s="71" t="s">
+        <v>765</v>
+      </c>
+      <c r="E446" s="71"/>
+      <c r="F446" s="140"/>
+      <c r="G446" s="187">
+        <f>SUM(F447:F454)</f>
+      </c>
+    </row>
+    <row r="447" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A447" s="76"/>
       <c r="B447" s="76"/>
       <c r="C447" s="34"/>
       <c r="D447" s="71"/>
       <c r="E447" s="72" t="s">
-        <v>786</v>
+        <v>766</v>
       </c>
       <c r="F447" s="140">
         <f>IFERROR(VLOOKUP(E447,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G447" s="138"/>
-      <c r="H447" s="72"/>
-      <c r="I447" s="164"/>
-    </row>
-    <row r="448" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A448" s="76"/>
       <c r="B448" s="76"/>
       <c r="C448" s="34"/>
-      <c r="D448" s="71"/>
-      <c r="E448" s="72" t="s">
-        <v>787</v>
+      <c r="D448" s="76"/>
+      <c r="E448" s="71" t="s">
+        <v>767</v>
       </c>
       <c r="F448" s="140">
         <f>IFERROR(VLOOKUP(E448,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G448" s="138"/>
-      <c r="H448" s="72"/>
-      <c r="I448" s="164"/>
     </row>
     <row r="449" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A449" s="76"/>
       <c r="B449" s="76"/>
       <c r="C449" s="34"/>
-      <c r="D449" s="196" t="s">
-        <v>788</v>
-      </c>
-      <c r="E449" s="197"/>
-      <c r="F449" s="198"/>
-      <c r="G449" s="187">
-        <f>+F450+F451+F452</f>
-        <v>8441197.290000001</v>
-      </c>
+      <c r="D449" s="76"/>
+      <c r="E449" s="71" t="s">
+        <v>768</v>
+      </c>
+      <c r="F449" s="140">
+        <f>IFERROR(VLOOKUP(E449,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G449" s="138"/>
     </row>
     <row r="450" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A450" s="76"/>
       <c r="B450" s="76"/>
       <c r="C450" s="34"/>
-      <c r="D450" s="71"/>
-      <c r="E450" s="72" t="s">
-        <v>789</v>
+      <c r="D450" s="76"/>
+      <c r="E450" s="71" t="s">
+        <v>769</v>
       </c>
       <c r="F450" s="140">
         <f>IFERROR(VLOOKUP(E450,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14657,9 +14376,9 @@
       <c r="A451" s="76"/>
       <c r="B451" s="76"/>
       <c r="C451" s="34"/>
-      <c r="D451" s="71"/>
+      <c r="D451" s="76"/>
       <c r="E451" s="72" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="F451" s="140">
         <f>IFERROR(VLOOKUP(E451,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14670,13 +14389,12 @@
       <c r="A452" s="76"/>
       <c r="B452" s="76"/>
       <c r="C452" s="34"/>
-      <c r="D452" s="71"/>
+      <c r="D452" s="76"/>
       <c r="E452" s="72" t="s">
-        <v>791</v>
+        <v>771</v>
       </c>
       <c r="F452" s="140">
         <f>IFERROR(VLOOKUP(E452,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>8441197.290000001</v>
       </c>
       <c r="G452" s="138"/>
     </row>
@@ -14684,27 +14402,25 @@
       <c r="A453" s="76"/>
       <c r="B453" s="76"/>
       <c r="C453" s="34"/>
-      <c r="D453" s="71" t="s">
-        <v>792</v>
-      </c>
-      <c r="E453" s="188"/>
-      <c r="F453" s="140"/>
-      <c r="G453" s="187">
-        <f>SUM(F454:F457)</f>
-        <v>14717993.67</v>
-      </c>
+      <c r="D453" s="76"/>
+      <c r="E453" s="72" t="s">
+        <v>772</v>
+      </c>
+      <c r="F453" s="140">
+        <f>IFERROR(VLOOKUP(E453,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G453" s="138"/>
     </row>
     <row r="454" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A454" s="76"/>
       <c r="B454" s="76"/>
       <c r="C454" s="34"/>
-      <c r="D454" s="71"/>
+      <c r="D454" s="76"/>
       <c r="E454" s="72" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="F454" s="140">
         <f>IFERROR(VLOOKUP(E454,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>299800</v>
       </c>
       <c r="G454" s="138"/>
     </row>
@@ -14712,15 +14428,14 @@
       <c r="A455" s="76"/>
       <c r="B455" s="76"/>
       <c r="C455" s="34"/>
-      <c r="D455" s="71"/>
-      <c r="E455" s="72" t="s">
-        <v>794</v>
-      </c>
-      <c r="F455" s="140">
-        <f>IFERROR(VLOOKUP(E455,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>14418193.67</v>
-      </c>
-      <c r="G455" s="138"/>
+      <c r="D455" s="71" t="s">
+        <v>774</v>
+      </c>
+      <c r="E455" s="71"/>
+      <c r="F455" s="140"/>
+      <c r="G455" s="187">
+        <f>SUM(F455:F459)</f>
+      </c>
     </row>
     <row r="456" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A456" s="76"/>
@@ -14728,7 +14443,7 @@
       <c r="C456" s="34"/>
       <c r="D456" s="71"/>
       <c r="E456" s="72" t="s">
-        <v>795</v>
+        <v>775</v>
       </c>
       <c r="F456" s="140">
         <f>IFERROR(VLOOKUP(E456,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14741,7 +14456,7 @@
       <c r="C457" s="34"/>
       <c r="D457" s="71"/>
       <c r="E457" s="72" t="s">
-        <v>796</v>
+        <v>776</v>
       </c>
       <c r="F457" s="140">
         <f>IFERROR(VLOOKUP(E457,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14752,122 +14467,105 @@
       <c r="A458" s="76"/>
       <c r="B458" s="76"/>
       <c r="C458" s="34"/>
-      <c r="D458" s="71" t="s">
-        <v>797</v>
-      </c>
-      <c r="E458" s="71"/>
+      <c r="D458" s="71"/>
+      <c r="E458" s="72" t="s">
+        <v>777</v>
+      </c>
       <c r="F458" s="140">
-        <f>IFERROR(VLOOKUP(D458,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G458" s="138">
-        <f>+F458</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E458,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G458" s="138"/>
     </row>
     <row r="459" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A459" s="76"/>
       <c r="B459" s="76"/>
       <c r="C459" s="34"/>
-      <c r="D459" s="71" t="s">
-        <v>798</v>
-      </c>
-      <c r="E459" s="71"/>
+      <c r="D459" s="71"/>
+      <c r="E459" s="72" t="s">
+        <v>778</v>
+      </c>
       <c r="F459" s="140">
-        <f>IFERROR(VLOOKUP(D459,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G459" s="138">
-        <f>+F459</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E459,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G459" s="138"/>
     </row>
     <row r="460" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A460" s="76"/>
       <c r="B460" s="76"/>
       <c r="C460" s="34"/>
-      <c r="D460" s="139" t="s">
-        <v>799</v>
-      </c>
-      <c r="E460" s="72"/>
+      <c r="D460" s="71" t="s">
+        <v>779</v>
+      </c>
+      <c r="E460" s="188"/>
       <c r="F460" s="140"/>
       <c r="G460" s="138">
-        <f>+SUM(F461:F462)</f>
-        <v>0</v>
+        <f>+F460</f>
       </c>
     </row>
     <row r="461" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A461" s="76"/>
       <c r="B461" s="76"/>
       <c r="C461" s="34"/>
-      <c r="D461" s="139"/>
-      <c r="E461" s="72" t="s">
-        <v>800</v>
-      </c>
-      <c r="F461" s="140">
-        <f>IFERROR(VLOOKUP(E461,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G461" s="138"/>
-    </row>
-    <row r="462" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D461" s="139" t="s">
+        <v>780</v>
+      </c>
+      <c r="E461" s="76"/>
+      <c r="F461" s="140"/>
+      <c r="G461" s="138">
+        <f>SUM(F461:F463)</f>
+      </c>
+    </row>
+    <row r="462" ht="13.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A462" s="76"/>
       <c r="B462" s="76"/>
       <c r="C462" s="34"/>
       <c r="D462" s="139"/>
       <c r="E462" s="72" t="s">
-        <v>801</v>
+        <v>781</v>
       </c>
       <c r="F462" s="140">
         <f>IFERROR(VLOOKUP(E462,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G462" s="138"/>
     </row>
-    <row r="463" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="463" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A463" s="76"/>
       <c r="B463" s="76"/>
       <c r="C463" s="34"/>
-      <c r="D463" s="71" t="s">
-        <v>802</v>
-      </c>
-      <c r="E463" s="71" t="s">
-        <v>803</v>
+      <c r="D463" s="139"/>
+      <c r="E463" s="72" t="s">
+        <v>782</v>
       </c>
       <c r="F463" s="140">
         <f>IFERROR(VLOOKUP(E463,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G463" s="187">
-        <f>SUM(F463:F471)</f>
-        <v>20016345.41</v>
-      </c>
-      <c r="H463" s="150"/>
-    </row>
-    <row r="464" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G463" s="138"/>
+    </row>
+    <row r="464" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A464" s="76"/>
       <c r="B464" s="76"/>
       <c r="C464" s="34"/>
-      <c r="D464" s="71"/>
-      <c r="E464" s="72" t="s">
-        <v>804</v>
-      </c>
-      <c r="F464" s="140">
-        <f>IFERROR(VLOOKUP(E464,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>11218221</v>
-      </c>
-      <c r="G464" s="138"/>
-      <c r="H464" s="150"/>
-    </row>
-    <row r="465" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D464" s="71" t="s">
+        <v>783</v>
+      </c>
+      <c r="E464" s="188"/>
+      <c r="F464" s="140"/>
+      <c r="G464" s="187">
+        <f>SUM(F465:F468)</f>
+      </c>
+    </row>
+    <row r="465" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A465" s="76"/>
       <c r="B465" s="76"/>
       <c r="C465" s="34"/>
       <c r="D465" s="71"/>
-      <c r="E465" s="72" t="s">
-        <v>805</v>
+      <c r="E465" s="151" t="s">
+        <v>784</v>
       </c>
       <c r="F465" s="140">
         <f>IFERROR(VLOOKUP(E465,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>8798124.41</v>
       </c>
       <c r="G465" s="138"/>
-      <c r="H465" s="150"/>
     </row>
     <row r="466" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A466" s="76"/>
@@ -14875,7 +14573,7 @@
       <c r="C466" s="34"/>
       <c r="D466" s="71"/>
       <c r="E466" s="72" t="s">
-        <v>806</v>
+        <v>785</v>
       </c>
       <c r="F466" s="140">
         <f>IFERROR(VLOOKUP(E466,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14890,7 +14588,7 @@
       <c r="C467" s="34"/>
       <c r="D467" s="71"/>
       <c r="E467" s="72" t="s">
-        <v>807</v>
+        <v>786</v>
       </c>
       <c r="F467" s="140">
         <f>IFERROR(VLOOKUP(E467,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14905,7 +14603,7 @@
       <c r="C468" s="34"/>
       <c r="D468" s="71"/>
       <c r="E468" s="72" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="F468" s="140">
         <f>IFERROR(VLOOKUP(E468,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -14914,77 +14612,70 @@
       <c r="H468" s="72"/>
       <c r="I468" s="164"/>
     </row>
-    <row r="469" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A469" s="76"/>
       <c r="B469" s="76"/>
       <c r="C469" s="34"/>
-      <c r="D469" s="71"/>
-      <c r="E469" s="72" t="s">
-        <v>809</v>
-      </c>
-      <c r="F469" s="140">
-        <f>IFERROR(VLOOKUP(E469,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G469" s="138"/>
-      <c r="H469" s="72"/>
-      <c r="I469" s="164"/>
-    </row>
-    <row r="470" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D469" s="196" t="s">
+        <v>788</v>
+      </c>
+      <c r="E469" s="197"/>
+      <c r="F469" s="198"/>
+      <c r="G469" s="187">
+        <f>+F470+F471+F472</f>
+      </c>
+    </row>
+    <row r="470" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A470" s="76"/>
       <c r="B470" s="76"/>
       <c r="C470" s="34"/>
       <c r="D470" s="71"/>
       <c r="E470" s="72" t="s">
-        <v>810</v>
+        <v>789</v>
       </c>
       <c r="F470" s="140">
         <f>IFERROR(VLOOKUP(E470,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G470" s="138"/>
-      <c r="H470" s="72"/>
-      <c r="I470" s="164"/>
-    </row>
-    <row r="471" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A471" s="76"/>
       <c r="B471" s="76"/>
       <c r="C471" s="34"/>
       <c r="D471" s="71"/>
       <c r="E471" s="72" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="F471" s="140">
         <f>IFERROR(VLOOKUP(E471,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G471" s="138"/>
-      <c r="H471" s="72"/>
-      <c r="I471" s="164"/>
-    </row>
-    <row r="472" ht="10.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A472" s="76"/>
       <c r="B472" s="76"/>
       <c r="C472" s="34"/>
-      <c r="D472" s="71" t="s">
-        <v>812</v>
-      </c>
-      <c r="E472" s="188"/>
-      <c r="F472" s="140"/>
-      <c r="G472" s="138">
-        <f>SUM(F472:F475)</f>
-        <v>0</v>
-      </c>
+      <c r="D472" s="71"/>
+      <c r="E472" s="72" t="s">
+        <v>791</v>
+      </c>
+      <c r="F472" s="140">
+        <f>IFERROR(VLOOKUP(E472,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G472" s="138"/>
     </row>
     <row r="473" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A473" s="76"/>
       <c r="B473" s="76"/>
       <c r="C473" s="34"/>
-      <c r="D473" s="71"/>
-      <c r="E473" s="72" t="s">
-        <v>813</v>
-      </c>
-      <c r="F473" s="140">
-        <f>IFERROR(VLOOKUP(E473,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G473" s="138"/>
+      <c r="D473" s="71" t="s">
+        <v>792</v>
+      </c>
+      <c r="E473" s="188"/>
+      <c r="F473" s="140"/>
+      <c r="G473" s="187">
+        <f>SUM(F474:F477)</f>
+      </c>
     </row>
     <row r="474" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A474" s="76"/>
@@ -14992,7 +14683,7 @@
       <c r="C474" s="34"/>
       <c r="D474" s="71"/>
       <c r="E474" s="72" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="F474" s="140">
         <f>IFERROR(VLOOKUP(E474,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -15005,7 +14696,7 @@
       <c r="C475" s="34"/>
       <c r="D475" s="71"/>
       <c r="E475" s="72" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="F475" s="140">
         <f>IFERROR(VLOOKUP(E475,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
@@ -15016,743 +14707,792 @@
       <c r="A476" s="76"/>
       <c r="B476" s="76"/>
       <c r="C476" s="34"/>
-      <c r="D476" s="139" t="s">
-        <v>816</v>
-      </c>
-      <c r="E476" s="188"/>
+      <c r="D476" s="71"/>
+      <c r="E476" s="72" t="s">
+        <v>795</v>
+      </c>
       <c r="F476" s="140">
-        <f>IFERROR(VLOOKUP(D476,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G476" s="138">
-        <f>+F476</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E476,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G476" s="138"/>
     </row>
     <row r="477" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A477" s="76"/>
       <c r="B477" s="76"/>
       <c r="C477" s="34"/>
-      <c r="D477" s="71" t="s">
-        <v>817</v>
-      </c>
-      <c r="E477" s="188"/>
+      <c r="D477" s="71"/>
+      <c r="E477" s="72" t="s">
+        <v>796</v>
+      </c>
       <c r="F477" s="140">
-        <f>IFERROR(VLOOKUP(D477,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
-      </c>
-      <c r="G477" s="138">
-        <f>+F477</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E477,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G477" s="138"/>
     </row>
     <row r="478" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A478" s="76"/>
       <c r="B478" s="76"/>
       <c r="C478" s="34"/>
       <c r="D478" s="71" t="s">
-        <v>818</v>
-      </c>
-      <c r="E478" s="188"/>
-      <c r="F478" s="140"/>
+        <v>797</v>
+      </c>
+      <c r="E478" s="71"/>
+      <c r="F478" s="140">
+        <f>IFERROR(VLOOKUP(D478,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
+      </c>
       <c r="G478" s="138">
-        <f>+F478+F479+F480</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="479" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>+F478</f>
+      </c>
+    </row>
+    <row r="479" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A479" s="76"/>
       <c r="B479" s="76"/>
       <c r="C479" s="34"/>
-      <c r="D479" s="71"/>
-      <c r="E479" s="72" t="s">
-        <v>819</v>
-      </c>
+      <c r="D479" s="71" t="s">
+        <v>798</v>
+      </c>
+      <c r="E479" s="71"/>
       <c r="F479" s="140">
-        <f>IFERROR(VLOOKUP(E479,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G479" s="138"/>
-    </row>
-    <row r="480" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(D479,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
+      </c>
+      <c r="G479" s="138">
+        <f>+F479</f>
+      </c>
+    </row>
+    <row r="480" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A480" s="76"/>
       <c r="B480" s="76"/>
       <c r="C480" s="34"/>
-      <c r="D480" s="71"/>
-      <c r="E480" s="72" t="s">
-        <v>820</v>
-      </c>
-      <c r="F480" s="140">
-        <f>IFERROR(VLOOKUP(E480,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G480" s="138"/>
-    </row>
-    <row r="481" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D480" s="139" t="s">
+        <v>799</v>
+      </c>
+      <c r="E480" s="72"/>
+      <c r="F480" s="140"/>
+      <c r="G480" s="138">
+        <f>+SUM(F481:F482)</f>
+      </c>
+    </row>
+    <row r="481" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A481" s="76"/>
       <c r="B481" s="76"/>
       <c r="C481" s="34"/>
-      <c r="D481" s="71" t="s">
-        <v>821</v>
-      </c>
+      <c r="D481" s="139"/>
       <c r="E481" s="72" t="s">
-        <v>822</v>
+        <v>800</v>
       </c>
       <c r="F481" s="140">
         <f>IFERROR(VLOOKUP(E481,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G481" s="187">
-        <f>SUM(F481:F483)</f>
-        <v>4714680.04</v>
-      </c>
+      <c r="G481" s="138"/>
     </row>
     <row r="482" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A482" s="76"/>
       <c r="B482" s="76"/>
       <c r="C482" s="34"/>
-      <c r="D482" s="71"/>
+      <c r="D482" s="139"/>
       <c r="E482" s="72" t="s">
-        <v>823</v>
+        <v>801</v>
       </c>
       <c r="F482" s="140">
         <f>IFERROR(VLOOKUP(E482,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
       <c r="G482" s="138"/>
     </row>
-    <row r="483" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" s="76"/>
       <c r="B483" s="76"/>
       <c r="C483" s="34"/>
-      <c r="D483" s="71"/>
-      <c r="E483" s="72" t="s">
-        <v>824</v>
-      </c>
-      <c r="F483" s="140">
-        <f>IFERROR(VLOOKUP(E483,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>4714680.04</v>
-      </c>
-      <c r="G483" s="138"/>
-    </row>
-    <row r="484" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D483" s="71" t="s">
+        <v>802</v>
+      </c>
+      <c r="E483" s="71"/>
+      <c r="F483" s="140"/>
+      <c r="G483" s="187">
+        <f>SUM(F484:F492)</f>
+      </c>
+      <c r="H483" s="150"/>
+    </row>
+    <row r="484" ht="11.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="76"/>
       <c r="B484" s="76"/>
       <c r="C484" s="34"/>
-      <c r="D484" s="71" t="s">
-        <v>825</v>
-      </c>
-      <c r="E484" s="72" t="s">
-        <v>826</v>
+      <c r="D484" s="132"/>
+      <c r="E484" s="71" t="s">
+        <v>803</v>
       </c>
       <c r="F484" s="140">
         <f>IFERROR(VLOOKUP(E484,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
       </c>
-      <c r="G484" s="138">
-        <f>+F484</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="485" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" s="76"/>
       <c r="B485" s="76"/>
       <c r="C485" s="34"/>
-      <c r="D485" s="71" t="s">
-        <v>827</v>
-      </c>
-      <c r="E485" s="71"/>
+      <c r="D485" s="71"/>
+      <c r="E485" s="72" t="s">
+        <v>804</v>
+      </c>
       <c r="F485" s="140">
-        <f>IFERROR(VLOOKUP(D485,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G485" s="138">
-        <f>+F485</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="486" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E485,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G485" s="138"/>
+      <c r="H485" s="150"/>
+    </row>
+    <row r="486" ht="11.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" s="76"/>
       <c r="B486" s="76"/>
       <c r="C486" s="34"/>
-      <c r="D486" s="139" t="s">
-        <v>828</v>
-      </c>
-      <c r="E486" s="72"/>
+      <c r="D486" s="71"/>
+      <c r="E486" s="72" t="s">
+        <v>805</v>
+      </c>
       <c r="F486" s="140">
-        <f>IFERROR(VLOOKUP(D486,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G486" s="138">
-        <f>+F486</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="487" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E486,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G486" s="138"/>
+      <c r="H486" s="150"/>
+    </row>
+    <row r="487" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A487" s="76"/>
       <c r="B487" s="76"/>
       <c r="C487" s="34"/>
-      <c r="D487" s="71" t="s">
-        <v>829</v>
-      </c>
-      <c r="E487" s="68"/>
+      <c r="D487" s="71"/>
+      <c r="E487" s="72" t="s">
+        <v>806</v>
+      </c>
       <c r="F487" s="140">
-        <f>IFERROR(VLOOKUP(D487,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>4150213.41</v>
-      </c>
-      <c r="G487" s="187">
-        <f>+F487</f>
-        <v>4150213.41</v>
-      </c>
-    </row>
-    <row r="488" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E487,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G487" s="138"/>
+      <c r="H487" s="72"/>
+      <c r="I487" s="164"/>
+    </row>
+    <row r="488" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A488" s="76"/>
       <c r="B488" s="76"/>
       <c r="C488" s="34"/>
-      <c r="D488" s="71" t="s">
-        <v>830</v>
-      </c>
-      <c r="E488" s="132"/>
+      <c r="D488" s="71"/>
+      <c r="E488" s="72" t="s">
+        <v>807</v>
+      </c>
       <c r="F488" s="140">
-        <f>IFERROR(VLOOKUP(D488,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G488" s="138">
-        <f>+F488</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="489" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E488,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G488" s="138"/>
+      <c r="H488" s="72"/>
+      <c r="I488" s="164"/>
+    </row>
+    <row r="489" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A489" s="76"/>
       <c r="B489" s="76"/>
       <c r="C489" s="34"/>
-      <c r="D489" s="71" t="s">
-        <v>831</v>
-      </c>
-      <c r="E489" s="132"/>
+      <c r="D489" s="71"/>
+      <c r="E489" s="72" t="s">
+        <v>808</v>
+      </c>
       <c r="F489" s="140">
-        <f>IFERROR(VLOOKUP(D489,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G489" s="138">
-        <f>+F489</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="490" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E489,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G489" s="138"/>
+      <c r="H489" s="72"/>
+      <c r="I489" s="164"/>
+    </row>
+    <row r="490" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A490" s="76"/>
       <c r="B490" s="76"/>
       <c r="C490" s="34"/>
-      <c r="D490" s="71" t="s">
-        <v>832</v>
-      </c>
-      <c r="E490" s="132"/>
+      <c r="D490" s="71"/>
+      <c r="E490" s="72" t="s">
+        <v>809</v>
+      </c>
       <c r="F490" s="140">
-        <f>IFERROR(VLOOKUP(D490,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>226987</v>
-      </c>
-      <c r="G490" s="187">
-        <f>+F490</f>
-        <v>226987</v>
-      </c>
-    </row>
-    <row r="491" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E490,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G490" s="138"/>
+      <c r="H490" s="72"/>
+      <c r="I490" s="164"/>
+    </row>
+    <row r="491" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A491" s="76"/>
       <c r="B491" s="76"/>
       <c r="C491" s="34"/>
-      <c r="D491" s="71" t="s">
-        <v>833</v>
-      </c>
-      <c r="E491" s="132"/>
+      <c r="D491" s="71"/>
+      <c r="E491" s="72" t="s">
+        <v>810</v>
+      </c>
       <c r="F491" s="140">
-        <f>IFERROR(VLOOKUP(D491,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>914304.7000000001</v>
-      </c>
-      <c r="G491" s="187">
-        <f>+F491</f>
-        <v>914304.7000000001</v>
-      </c>
-    </row>
-    <row r="492" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E491,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G491" s="138"/>
+      <c r="H491" s="72"/>
+      <c r="I491" s="164"/>
+    </row>
+    <row r="492" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A492" s="76"/>
       <c r="B492" s="76"/>
       <c r="C492" s="34"/>
-      <c r="D492" s="139" t="s">
-        <v>834</v>
-      </c>
-      <c r="E492" s="132"/>
+      <c r="D492" s="71"/>
+      <c r="E492" s="72" t="s">
+        <v>811</v>
+      </c>
       <c r="F492" s="140">
-        <f>IFERROR(VLOOKUP(D492,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G492" s="138">
-        <f>+F492</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E492,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G492" s="138"/>
+      <c r="H492" s="72"/>
+      <c r="I492" s="164"/>
+    </row>
+    <row r="493" ht="10.95" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A493" s="76"/>
       <c r="B493" s="76"/>
       <c r="C493" s="34"/>
-      <c r="D493" s="139" t="s">
-        <v>835</v>
-      </c>
-      <c r="E493" s="68"/>
-      <c r="F493" s="140">
-        <f>IFERROR(VLOOKUP(D493,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+      <c r="D493" s="71" t="s">
+        <v>812</v>
+      </c>
+      <c r="E493" s="188"/>
+      <c r="F493" s="140"/>
       <c r="G493" s="138">
-        <f>+F493</f>
-        <v>0</v>
+        <f>SUM(F493:F496)</f>
       </c>
     </row>
     <row r="494" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A494" s="76"/>
       <c r="B494" s="76"/>
       <c r="C494" s="34"/>
-      <c r="D494" s="139" t="s">
-        <v>836</v>
-      </c>
-      <c r="E494" s="132"/>
+      <c r="D494" s="71"/>
+      <c r="E494" s="72" t="s">
+        <v>813</v>
+      </c>
       <c r="F494" s="140">
-        <f>IFERROR(VLOOKUP(D494,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G494" s="138">
-        <f>+F494</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E494,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G494" s="138"/>
     </row>
     <row r="495" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A495" s="76"/>
       <c r="B495" s="76"/>
       <c r="C495" s="34"/>
-      <c r="D495" s="139" t="s">
-        <v>837</v>
-      </c>
-      <c r="E495" s="132"/>
+      <c r="D495" s="71"/>
+      <c r="E495" s="72" t="s">
+        <v>814</v>
+      </c>
       <c r="F495" s="140">
-        <f>IFERROR(VLOOKUP(D495,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G495" s="138">
-        <f>+F495</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E495,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G495" s="138"/>
     </row>
     <row r="496" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A496" s="76"/>
       <c r="B496" s="76"/>
       <c r="C496" s="34"/>
-      <c r="D496" s="139" t="s">
-        <v>838</v>
-      </c>
-      <c r="E496" s="132"/>
+      <c r="D496" s="71"/>
+      <c r="E496" s="72" t="s">
+        <v>815</v>
+      </c>
       <c r="F496" s="140">
-        <f>IFERROR(VLOOKUP(D496,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G496" s="138">
-        <f>+F496</f>
-        <v>0</v>
-      </c>
+        <f>IFERROR(VLOOKUP(E496,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G496" s="138"/>
     </row>
     <row r="497" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A497" s="76"/>
       <c r="B497" s="76"/>
       <c r="C497" s="34"/>
       <c r="D497" s="139" t="s">
-        <v>839</v>
-      </c>
-      <c r="E497" s="72" t="s">
-        <v>839</v>
-      </c>
+        <v>816</v>
+      </c>
+      <c r="E497" s="188"/>
       <c r="F497" s="140">
-        <f>IFERROR(VLOOKUP(D497,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-        <v>358719.18</v>
-      </c>
-      <c r="G497" s="187">
+        <f>IFERROR(VLOOKUP(D497,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
+      </c>
+      <c r="G497" s="138">
         <f>+F497</f>
-        <v>358719.18</v>
-      </c>
-    </row>
-    <row r="498" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="498" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A498" s="76"/>
       <c r="B498" s="76"/>
       <c r="C498" s="34"/>
-      <c r="D498" s="139" t="s">
-        <v>840</v>
-      </c>
-      <c r="E498" s="132"/>
+      <c r="D498" s="71" t="s">
+        <v>817</v>
+      </c>
+      <c r="E498" s="188"/>
       <c r="F498" s="140">
-        <f>IFERROR(VLOOKUP(D498,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+        <f>IFERROR(VLOOKUP(D498,'Balance de sumas y saldos'!$A$2:$E$550,5,FALSE),)</f>
       </c>
       <c r="G498" s="138">
         <f>+F498</f>
-        <v>0</v>
-      </c>
-      <c r="H498" s="162"/>
-    </row>
-    <row r="499" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      </c>
+    </row>
+    <row r="499" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A499" s="76"/>
       <c r="B499" s="76"/>
       <c r="C499" s="34"/>
-      <c r="D499" s="139" t="s">
-        <v>841</v>
-      </c>
-      <c r="E499" s="132"/>
-      <c r="F499" s="140">
-        <f>IFERROR(VLOOKUP(D499,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
+      <c r="D499" s="71" t="s">
+        <v>818</v>
+      </c>
+      <c r="E499" s="188"/>
+      <c r="F499" s="140"/>
       <c r="G499" s="138">
-        <f>+F499</f>
-        <v>0</v>
-      </c>
-      <c r="H499" s="162"/>
-    </row>
-    <row r="500" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>+F499+F500+F501</f>
+      </c>
+    </row>
+    <row r="500" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A500" s="76"/>
       <c r="B500" s="76"/>
       <c r="C500" s="34"/>
-      <c r="D500" s="139" t="s">
-        <v>842</v>
-      </c>
-      <c r="E500" s="132"/>
+      <c r="D500" s="71"/>
+      <c r="E500" s="72" t="s">
+        <v>819</v>
+      </c>
       <c r="F500" s="140">
-        <f>IFERROR(VLOOKUP(D500,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G500" s="138">
-        <f>+F500</f>
-        <v>0</v>
-      </c>
-      <c r="H500" s="162"/>
-    </row>
-    <row r="501" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E500,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G500" s="138"/>
+    </row>
+    <row r="501" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A501" s="76"/>
       <c r="B501" s="76"/>
       <c r="C501" s="34"/>
-      <c r="D501" s="139" t="s">
-        <v>843</v>
-      </c>
-      <c r="E501" s="132"/>
+      <c r="D501" s="71"/>
+      <c r="E501" s="72" t="s">
+        <v>820</v>
+      </c>
       <c r="F501" s="140">
-        <f>IFERROR(VLOOKUP(D501,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G501" s="138">
-        <f>+F501</f>
-        <v>0</v>
-      </c>
-      <c r="H501" s="162"/>
-    </row>
-    <row r="502" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E501,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G501" s="138"/>
+    </row>
+    <row r="502" ht="11.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A502" s="76"/>
       <c r="B502" s="76"/>
       <c r="C502" s="34"/>
-      <c r="D502" s="139" t="s">
-        <v>844</v>
-      </c>
-      <c r="E502" s="132"/>
-      <c r="F502" s="140">
-        <f>IFERROR(VLOOKUP(D502,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G502" s="138">
-        <f>+F502</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="503" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D502" s="71" t="s">
+        <v>821</v>
+      </c>
+      <c r="E502" s="72"/>
+      <c r="F502" s="140"/>
+      <c r="G502" s="187">
+        <f>SUM(F503:F505)</f>
+      </c>
+    </row>
+    <row r="503" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="76"/>
       <c r="B503" s="76"/>
       <c r="C503" s="34"/>
-      <c r="D503" s="139" t="s">
-        <v>845</v>
-      </c>
-      <c r="E503" s="132"/>
+      <c r="D503" s="132"/>
+      <c r="E503" s="72" t="s">
+        <v>822</v>
+      </c>
       <c r="F503" s="140">
-        <f>IFERROR(VLOOKUP(D503,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
-      </c>
-      <c r="G503" s="138">
-        <f>+F503</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="504" ht="13.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <f>IFERROR(VLOOKUP(E503,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+    </row>
+    <row r="504" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A504" s="76"/>
       <c r="B504" s="76"/>
       <c r="C504" s="34"/>
-      <c r="D504" s="132"/>
-      <c r="E504" s="132"/>
-      <c r="F504" s="162"/>
-      <c r="G504" s="133"/>
-      <c r="H504" s="199" t="s">
-        <v>55</v>
-      </c>
-      <c r="I504" s="199" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="505" ht="13.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D504" s="71"/>
+      <c r="E504" s="72" t="s">
+        <v>823</v>
+      </c>
+      <c r="F504" s="140">
+        <f>IFERROR(VLOOKUP(E504,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G504" s="138"/>
+    </row>
+    <row r="505" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A505" s="76"/>
       <c r="B505" s="76"/>
       <c r="C505" s="34"/>
-      <c r="D505" s="132"/>
-      <c r="E505" s="200" t="s">
-        <v>846</v>
-      </c>
-      <c r="F505" s="201">
-        <f>SUM(F147:F503)</f>
-        <v>1802783307.13</v>
-      </c>
-      <c r="G505" s="202">
-        <f>SUM(G147:G503)</f>
-        <v>1802783307.13</v>
-      </c>
-      <c r="H505" s="199">
-        <f>+Resultados!C26</f>
-        <v>-1802783307.13</v>
-      </c>
-      <c r="I505" s="199">
-        <f>+H505+G505</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="506" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D505" s="71"/>
+      <c r="E505" s="72" t="s">
+        <v>824</v>
+      </c>
+      <c r="F505" s="140">
+        <f>IFERROR(VLOOKUP(E505,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G505" s="138"/>
+    </row>
+    <row r="506" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A506" s="76"/>
       <c r="B506" s="76"/>
       <c r="C506" s="34"/>
-      <c r="D506" s="132"/>
-      <c r="E506" s="203" t="s">
-        <v>847</v>
-      </c>
-      <c r="F506" s="204">
-        <f>+-'Anexo II'!E103</f>
-        <v>-1737765878.36</v>
-      </c>
-      <c r="G506" s="205">
-        <f>+'Balance de sumas y saldos'!E515</f>
-        <v>1802783307.1299999</v>
-      </c>
-      <c r="H506" s="199"/>
-      <c r="I506" s="206"/>
-    </row>
-    <row r="507" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D506" s="71" t="s">
+        <v>825</v>
+      </c>
+      <c r="E506" s="72" t="s">
+        <v>826</v>
+      </c>
+      <c r="F506" s="140">
+        <f>IFERROR(VLOOKUP(E506,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G506" s="138">
+        <f>+F506</f>
+      </c>
+    </row>
+    <row r="507" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A507" s="76"/>
       <c r="B507" s="76"/>
       <c r="C507" s="34"/>
-      <c r="D507" s="132"/>
-      <c r="E507" s="207" t="s">
-        <v>848</v>
-      </c>
-      <c r="F507" s="208">
-        <f>+F505+F506</f>
-        <v>65017428.77000022</v>
-      </c>
-      <c r="G507" s="209">
-        <f>+G506-G505</f>
-        <v>0</v>
-      </c>
-      <c r="H507" s="208"/>
-    </row>
-    <row r="508" ht="12.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D507" s="71" t="s">
+        <v>827</v>
+      </c>
+      <c r="E507" s="71"/>
+      <c r="F507" s="140">
+        <f>IFERROR(VLOOKUP(D507,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G507" s="138">
+        <f>+F507</f>
+      </c>
+    </row>
+    <row r="508" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A508" s="76"/>
       <c r="B508" s="76"/>
       <c r="C508" s="34"/>
-      <c r="D508" s="132"/>
-      <c r="E508" s="132"/>
-      <c r="F508" s="162">
-        <f>+F507-F281</f>
-        <v>2.1606683731079102e-7</v>
-      </c>
-    </row>
-    <row r="509" ht="10.95" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="210"/>
-      <c r="B509" s="210"/>
-      <c r="C509" s="211"/>
-      <c r="D509" s="211"/>
-      <c r="E509" s="211" t="s">
-        <v>849</v>
-      </c>
-      <c r="F509" s="211">
-        <f>+F281-F507</f>
-        <v>-2.1606683731079102e-7</v>
-      </c>
-      <c r="G509" s="212"/>
-      <c r="H509" s="211"/>
-      <c r="I509" s="213"/>
-      <c r="J509" s="211"/>
-      <c r="K509" s="211"/>
-    </row>
-    <row r="510" ht="13.95" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A510" s="215"/>
-      <c r="B510" s="214"/>
-      <c r="C510" s="216"/>
-      <c r="D510" s="217"/>
-      <c r="E510" s="217"/>
-      <c r="F510" s="217"/>
-      <c r="G510" s="218">
-        <f>SUM(G3:G504)</f>
-        <v>9.147333912551403e-7</v>
-      </c>
-      <c r="H510" s="217"/>
-      <c r="I510" s="219"/>
-      <c r="J510" s="217"/>
-      <c r="K510" s="217"/>
+      <c r="D508" s="139" t="s">
+        <v>828</v>
+      </c>
+      <c r="E508" s="72"/>
+      <c r="F508" s="140">
+        <f>IFERROR(VLOOKUP(D508,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G508" s="138">
+        <f>+F508</f>
+      </c>
+    </row>
+    <row r="509" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A509" s="76"/>
+      <c r="B509" s="76"/>
+      <c r="C509" s="34"/>
+      <c r="D509" s="71" t="s">
+        <v>829</v>
+      </c>
+      <c r="E509" s="68"/>
+      <c r="F509" s="140">
+        <f>IFERROR(VLOOKUP(D509,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G509" s="187">
+        <f>+F509</f>
+      </c>
+    </row>
+    <row r="510" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A510" s="76"/>
+      <c r="B510" s="76"/>
+      <c r="C510" s="34"/>
+      <c r="D510" s="71" t="s">
+        <v>830</v>
+      </c>
+      <c r="E510" s="132"/>
+      <c r="F510" s="140">
+        <f>IFERROR(VLOOKUP(D510,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G510" s="138">
+        <f>+F510</f>
+      </c>
     </row>
     <row r="511" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A511" s="76"/>
       <c r="B511" s="76"/>
       <c r="C511" s="34"/>
-      <c r="D511" s="132"/>
+      <c r="D511" s="71" t="s">
+        <v>831</v>
+      </c>
       <c r="E511" s="132"/>
-      <c r="F511" s="132"/>
-      <c r="G511" s="132"/>
+      <c r="F511" s="140">
+        <f>IFERROR(VLOOKUP(D511,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G511" s="138">
+        <f>+F511</f>
+      </c>
     </row>
     <row r="512" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A512" s="76"/>
       <c r="B512" s="76"/>
       <c r="C512" s="34"/>
-      <c r="D512" s="132"/>
+      <c r="D512" s="71" t="s">
+        <v>832</v>
+      </c>
       <c r="E512" s="132"/>
-      <c r="F512" s="132"/>
-      <c r="G512" s="132"/>
+      <c r="F512" s="140">
+        <f>IFERROR(VLOOKUP(D512,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G512" s="187">
+        <f>+F512</f>
+      </c>
     </row>
     <row r="513" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A513" s="76"/>
       <c r="B513" s="76"/>
       <c r="C513" s="34"/>
-      <c r="D513" s="132"/>
+      <c r="D513" s="71" t="s">
+        <v>833</v>
+      </c>
       <c r="E513" s="132"/>
-      <c r="F513" s="132"/>
-      <c r="G513" s="132"/>
+      <c r="F513" s="140">
+        <f>IFERROR(VLOOKUP(D513,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G513" s="187">
+        <f>+F513</f>
+      </c>
     </row>
     <row r="514" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A514" s="76"/>
       <c r="B514" s="76"/>
       <c r="C514" s="34"/>
-      <c r="D514" s="132"/>
+      <c r="D514" s="139" t="s">
+        <v>834</v>
+      </c>
       <c r="E514" s="132"/>
-      <c r="F514" s="132"/>
-      <c r="G514" s="132"/>
+      <c r="F514" s="140">
+        <f>IFERROR(VLOOKUP(D514,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G514" s="138">
+        <f>+F514</f>
+      </c>
     </row>
     <row r="515" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A515" s="76"/>
       <c r="B515" s="76"/>
       <c r="C515" s="34"/>
-      <c r="D515" s="132"/>
-      <c r="E515" s="132"/>
-      <c r="F515" s="132"/>
-      <c r="G515" s="132"/>
+      <c r="D515" s="139" t="s">
+        <v>835</v>
+      </c>
+      <c r="E515" s="68"/>
+      <c r="F515" s="140">
+        <f>IFERROR(VLOOKUP(D515,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G515" s="138">
+        <f>+F515</f>
+      </c>
     </row>
     <row r="516" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A516" s="76"/>
       <c r="B516" s="76"/>
       <c r="C516" s="34"/>
-      <c r="D516" s="132"/>
+      <c r="D516" s="139" t="s">
+        <v>836</v>
+      </c>
       <c r="E516" s="132"/>
-      <c r="F516" s="132"/>
-      <c r="G516" s="132"/>
+      <c r="F516" s="140">
+        <f>IFERROR(VLOOKUP(D516,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G516" s="138">
+        <f>+F516</f>
+      </c>
     </row>
     <row r="517" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A517" s="76"/>
       <c r="B517" s="76"/>
       <c r="C517" s="34"/>
-      <c r="D517" s="132"/>
+      <c r="D517" s="139" t="s">
+        <v>837</v>
+      </c>
       <c r="E517" s="132"/>
-      <c r="F517" s="132"/>
-      <c r="G517" s="132"/>
+      <c r="F517" s="140">
+        <f>IFERROR(VLOOKUP(D517,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G517" s="138">
+        <f>+F517</f>
+      </c>
     </row>
     <row r="518" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A518" s="76"/>
       <c r="B518" s="76"/>
       <c r="C518" s="34"/>
-      <c r="D518" s="132"/>
+      <c r="D518" s="139" t="s">
+        <v>838</v>
+      </c>
       <c r="E518" s="132"/>
-      <c r="F518" s="132"/>
-      <c r="G518" s="132"/>
+      <c r="F518" s="140">
+        <f>IFERROR(VLOOKUP(D518,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G518" s="138">
+        <f>+F518</f>
+      </c>
     </row>
     <row r="519" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A519" s="76"/>
       <c r="B519" s="76"/>
       <c r="C519" s="34"/>
-      <c r="D519" s="132"/>
-      <c r="E519" s="132"/>
-      <c r="F519" s="132"/>
-      <c r="G519" s="132"/>
-    </row>
-    <row r="520" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D519" s="139" t="s">
+        <v>839</v>
+      </c>
+      <c r="E519" s="72" t="s">
+        <v>839</v>
+      </c>
+      <c r="F519" s="140">
+        <f>IFERROR(VLOOKUP(D519,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G519" s="187">
+        <f>+F519</f>
+      </c>
+    </row>
+    <row r="520" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" s="76"/>
       <c r="B520" s="76"/>
       <c r="C520" s="34"/>
-      <c r="D520" s="132"/>
+      <c r="D520" s="139" t="s">
+        <v>840</v>
+      </c>
       <c r="E520" s="132"/>
-      <c r="F520" s="132"/>
-      <c r="G520" s="132"/>
-    </row>
-    <row r="521" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F520" s="140">
+        <f>IFERROR(VLOOKUP(D520,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G520" s="138">
+        <f>+F520</f>
+      </c>
+      <c r="H520" s="162"/>
+    </row>
+    <row r="521" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" s="76"/>
       <c r="B521" s="76"/>
       <c r="C521" s="34"/>
-      <c r="D521" s="132"/>
+      <c r="D521" s="139" t="s">
+        <v>841</v>
+      </c>
       <c r="E521" s="132"/>
-      <c r="F521" s="132"/>
-      <c r="G521" s="132"/>
-    </row>
-    <row r="522" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F521" s="140">
+        <f>IFERROR(VLOOKUP(D521,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G521" s="138">
+        <f>+F521</f>
+      </c>
+      <c r="H521" s="162"/>
+    </row>
+    <row r="522" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" s="76"/>
       <c r="B522" s="76"/>
       <c r="C522" s="34"/>
-      <c r="D522" s="132"/>
+      <c r="D522" s="139" t="s">
+        <v>842</v>
+      </c>
       <c r="E522" s="132"/>
-      <c r="F522" s="132"/>
-      <c r="G522" s="132"/>
-    </row>
-    <row r="523" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F522" s="140">
+        <f>IFERROR(VLOOKUP(D522,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G522" s="138">
+        <f>+F522</f>
+      </c>
+      <c r="H522" s="162"/>
+    </row>
+    <row r="523" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" s="76"/>
       <c r="B523" s="76"/>
       <c r="C523" s="34"/>
-      <c r="D523" s="132"/>
+      <c r="D523" s="139" t="s">
+        <v>843</v>
+      </c>
       <c r="E523" s="132"/>
-      <c r="F523" s="132"/>
-      <c r="G523" s="132"/>
+      <c r="F523" s="140">
+        <f>IFERROR(VLOOKUP(D523,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G523" s="138">
+        <f>+F523</f>
+      </c>
+      <c r="H523" s="162"/>
     </row>
     <row r="524" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A524" s="76"/>
       <c r="B524" s="76"/>
       <c r="C524" s="34"/>
-      <c r="D524" s="132"/>
+      <c r="D524" s="139" t="s">
+        <v>844</v>
+      </c>
       <c r="E524" s="132"/>
-      <c r="F524" s="132"/>
-      <c r="G524" s="132"/>
+      <c r="F524" s="140">
+        <f>IFERROR(VLOOKUP(D524,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G524" s="138">
+        <f>+F524</f>
+      </c>
     </row>
     <row r="525" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A525" s="76"/>
       <c r="B525" s="76"/>
       <c r="C525" s="34"/>
-      <c r="D525" s="132"/>
+      <c r="D525" s="139" t="s">
+        <v>845</v>
+      </c>
       <c r="E525" s="132"/>
-      <c r="F525" s="132"/>
-      <c r="G525" s="132"/>
-    </row>
-    <row r="526" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F525" s="140">
+        <f>IFERROR(VLOOKUP(D525,'Balance de sumas y saldos'!$A$2:$E$574,5,FALSE),)</f>
+      </c>
+      <c r="G525" s="138">
+        <f>+F525</f>
+      </c>
+    </row>
+    <row r="526" ht="13.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" s="76"/>
       <c r="B526" s="76"/>
       <c r="C526" s="34"/>
       <c r="D526" s="132"/>
       <c r="E526" s="132"/>
-      <c r="F526" s="132"/>
-      <c r="G526" s="132"/>
-    </row>
-    <row r="527" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F526" s="162"/>
+      <c r="G526" s="133"/>
+      <c r="H526" s="199" t="s">
+        <v>55</v>
+      </c>
+      <c r="I526" s="199" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="527" ht="13.95" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" s="76"/>
       <c r="B527" s="76"/>
       <c r="C527" s="34"/>
       <c r="D527" s="132"/>
-      <c r="E527" s="132"/>
-      <c r="F527" s="132"/>
-      <c r="G527" s="132"/>
-    </row>
-    <row r="528" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E527" s="200" t="s">
+        <v>846</v>
+      </c>
+      <c r="F527" s="201">
+        <f>SUM(F147:F525)</f>
+      </c>
+      <c r="G527" s="202">
+        <f>SUM(G147:G525)</f>
+      </c>
+      <c r="H527" s="199">
+        <f>+Resultados!C26</f>
+        <v>-1802783307.13</v>
+      </c>
+      <c r="I527" s="199">
+        <f>+H527+G527</f>
+      </c>
+    </row>
+    <row r="528" ht="12.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" s="76"/>
       <c r="B528" s="76"/>
       <c r="C528" s="34"/>
       <c r="D528" s="132"/>
-      <c r="E528" s="132"/>
-      <c r="F528" s="132"/>
-      <c r="G528" s="132"/>
-    </row>
-    <row r="529" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E528" s="203" t="s">
+        <v>847</v>
+      </c>
+      <c r="F528" s="204">
+        <f>+-'Anexo II'!E103</f>
+        <v>-1737765878.36</v>
+      </c>
+      <c r="G528" s="205">
+        <f>+'Balance de sumas y saldos'!E515</f>
+        <v>1802783307.1299999</v>
+      </c>
+      <c r="H528" s="199"/>
+      <c r="I528" s="206"/>
+    </row>
+    <row r="529" ht="12.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" s="76"/>
       <c r="B529" s="76"/>
       <c r="C529" s="34"/>
       <c r="D529" s="132"/>
-      <c r="E529" s="132"/>
-      <c r="F529" s="132"/>
-      <c r="G529" s="132"/>
+      <c r="E529" s="207" t="s">
+        <v>848</v>
+      </c>
+      <c r="F529" s="208">
+        <f>+F527+F528</f>
+      </c>
+      <c r="G529" s="209">
+        <f>+G528-G527</f>
+      </c>
+      <c r="H529" s="208"/>
     </row>
     <row r="530" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A530" s="76"/>
@@ -15760,26 +15500,42 @@
       <c r="C530" s="34"/>
       <c r="D530" s="132"/>
       <c r="E530" s="132"/>
-      <c r="F530" s="132"/>
-      <c r="G530" s="132"/>
-    </row>
-    <row r="531" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A531" s="76"/>
-      <c r="B531" s="76"/>
-      <c r="C531" s="34"/>
-      <c r="D531" s="132"/>
-      <c r="E531" s="132"/>
-      <c r="F531" s="132"/>
-      <c r="G531" s="132"/>
-    </row>
-    <row r="532" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A532" s="76"/>
-      <c r="B532" s="76"/>
-      <c r="C532" s="34"/>
-      <c r="D532" s="132"/>
-      <c r="E532" s="132"/>
-      <c r="F532" s="132"/>
-      <c r="G532" s="132"/>
+      <c r="F530" s="162">
+        <f>+F529-F291</f>
+      </c>
+      <c r="G530" s="133"/>
+    </row>
+    <row r="531" ht="10.95" customHeight="1" spans="1:11" s="210" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="210"/>
+      <c r="B531" s="210"/>
+      <c r="C531" s="211"/>
+      <c r="D531" s="211"/>
+      <c r="E531" s="211" t="s">
+        <v>849</v>
+      </c>
+      <c r="F531" s="211">
+        <f>+F291-F529</f>
+      </c>
+      <c r="G531" s="212"/>
+      <c r="H531" s="211"/>
+      <c r="I531" s="213"/>
+      <c r="J531" s="211"/>
+      <c r="K531" s="211"/>
+    </row>
+    <row r="532" ht="13.95" customHeight="1" spans="1:11" s="214" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="215"/>
+      <c r="B532" s="214"/>
+      <c r="C532" s="216"/>
+      <c r="D532" s="217"/>
+      <c r="E532" s="217"/>
+      <c r="F532" s="217"/>
+      <c r="G532" s="218">
+        <f>SUM(G3:G526)</f>
+      </c>
+      <c r="H532" s="217"/>
+      <c r="I532" s="219"/>
+      <c r="J532" s="217"/>
+      <c r="K532" s="217"/>
     </row>
     <row r="533" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A533" s="76"/>
@@ -28281,6 +28037,204 @@
       <c r="E1921" s="132"/>
       <c r="F1921" s="132"/>
       <c r="G1921" s="132"/>
+    </row>
+    <row r="1922" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1922" s="76"/>
+      <c r="B1922" s="76"/>
+      <c r="C1922" s="34"/>
+      <c r="D1922" s="132"/>
+      <c r="E1922" s="132"/>
+      <c r="F1922" s="132"/>
+      <c r="G1922" s="132"/>
+    </row>
+    <row r="1923" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1923" s="76"/>
+      <c r="B1923" s="76"/>
+      <c r="C1923" s="34"/>
+      <c r="D1923" s="132"/>
+      <c r="E1923" s="132"/>
+      <c r="F1923" s="132"/>
+      <c r="G1923" s="132"/>
+    </row>
+    <row r="1924" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1924" s="76"/>
+      <c r="B1924" s="76"/>
+      <c r="C1924" s="34"/>
+      <c r="D1924" s="132"/>
+      <c r="E1924" s="132"/>
+      <c r="F1924" s="132"/>
+      <c r="G1924" s="132"/>
+    </row>
+    <row r="1925" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1925" s="76"/>
+      <c r="B1925" s="76"/>
+      <c r="C1925" s="34"/>
+      <c r="D1925" s="132"/>
+      <c r="E1925" s="132"/>
+      <c r="F1925" s="132"/>
+      <c r="G1925" s="132"/>
+    </row>
+    <row r="1926" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1926" s="76"/>
+      <c r="B1926" s="76"/>
+      <c r="C1926" s="34"/>
+      <c r="D1926" s="132"/>
+      <c r="E1926" s="132"/>
+      <c r="F1926" s="132"/>
+      <c r="G1926" s="132"/>
+    </row>
+    <row r="1927" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1927" s="76"/>
+      <c r="B1927" s="76"/>
+      <c r="C1927" s="34"/>
+      <c r="D1927" s="132"/>
+      <c r="E1927" s="132"/>
+      <c r="F1927" s="132"/>
+      <c r="G1927" s="132"/>
+    </row>
+    <row r="1928" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1928" s="76"/>
+      <c r="B1928" s="76"/>
+      <c r="C1928" s="34"/>
+      <c r="D1928" s="132"/>
+      <c r="E1928" s="132"/>
+      <c r="F1928" s="132"/>
+      <c r="G1928" s="132"/>
+    </row>
+    <row r="1929" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1929" s="76"/>
+      <c r="B1929" s="76"/>
+      <c r="C1929" s="34"/>
+      <c r="D1929" s="132"/>
+      <c r="E1929" s="132"/>
+      <c r="F1929" s="132"/>
+      <c r="G1929" s="132"/>
+    </row>
+    <row r="1930" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1930" s="76"/>
+      <c r="B1930" s="76"/>
+      <c r="C1930" s="34"/>
+      <c r="D1930" s="132"/>
+      <c r="E1930" s="132"/>
+      <c r="F1930" s="132"/>
+      <c r="G1930" s="132"/>
+    </row>
+    <row r="1931" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1931" s="76"/>
+      <c r="B1931" s="76"/>
+      <c r="C1931" s="34"/>
+      <c r="D1931" s="132"/>
+      <c r="E1931" s="132"/>
+      <c r="F1931" s="132"/>
+      <c r="G1931" s="132"/>
+    </row>
+    <row r="1932" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1932" s="76"/>
+      <c r="B1932" s="76"/>
+      <c r="C1932" s="34"/>
+      <c r="D1932" s="132"/>
+      <c r="E1932" s="132"/>
+      <c r="F1932" s="132"/>
+      <c r="G1932" s="132"/>
+    </row>
+    <row r="1933" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1933" s="76"/>
+      <c r="B1933" s="76"/>
+      <c r="C1933" s="34"/>
+      <c r="D1933" s="132"/>
+      <c r="E1933" s="132"/>
+      <c r="F1933" s="132"/>
+      <c r="G1933" s="132"/>
+    </row>
+    <row r="1934" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1934" s="76"/>
+      <c r="B1934" s="76"/>
+      <c r="C1934" s="34"/>
+      <c r="D1934" s="132"/>
+      <c r="E1934" s="132"/>
+      <c r="F1934" s="132"/>
+      <c r="G1934" s="132"/>
+    </row>
+    <row r="1935" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1935" s="76"/>
+      <c r="B1935" s="76"/>
+      <c r="C1935" s="34"/>
+      <c r="D1935" s="132"/>
+      <c r="E1935" s="132"/>
+      <c r="F1935" s="132"/>
+      <c r="G1935" s="132"/>
+    </row>
+    <row r="1936" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1936" s="76"/>
+      <c r="B1936" s="76"/>
+      <c r="C1936" s="34"/>
+      <c r="D1936" s="132"/>
+      <c r="E1936" s="132"/>
+      <c r="F1936" s="132"/>
+      <c r="G1936" s="132"/>
+    </row>
+    <row r="1937" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1937" s="76"/>
+      <c r="B1937" s="76"/>
+      <c r="C1937" s="34"/>
+      <c r="D1937" s="132"/>
+      <c r="E1937" s="132"/>
+      <c r="F1937" s="132"/>
+      <c r="G1937" s="132"/>
+    </row>
+    <row r="1938" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1938" s="76"/>
+      <c r="B1938" s="76"/>
+      <c r="C1938" s="34"/>
+      <c r="D1938" s="132"/>
+      <c r="E1938" s="132"/>
+      <c r="F1938" s="132"/>
+      <c r="G1938" s="132"/>
+    </row>
+    <row r="1939" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1939" s="76"/>
+      <c r="B1939" s="76"/>
+      <c r="C1939" s="34"/>
+      <c r="D1939" s="132"/>
+      <c r="E1939" s="132"/>
+      <c r="F1939" s="132"/>
+      <c r="G1939" s="132"/>
+    </row>
+    <row r="1940" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1940" s="76"/>
+      <c r="B1940" s="76"/>
+      <c r="C1940" s="34"/>
+      <c r="D1940" s="132"/>
+      <c r="E1940" s="132"/>
+      <c r="F1940" s="132"/>
+      <c r="G1940" s="132"/>
+    </row>
+    <row r="1941" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1941" s="76"/>
+      <c r="B1941" s="76"/>
+      <c r="C1941" s="34"/>
+      <c r="D1941" s="132"/>
+      <c r="E1941" s="132"/>
+      <c r="F1941" s="132"/>
+      <c r="G1941" s="132"/>
+    </row>
+    <row r="1942" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1942" s="76"/>
+      <c r="B1942" s="76"/>
+      <c r="C1942" s="34"/>
+      <c r="D1942" s="132"/>
+      <c r="E1942" s="132"/>
+      <c r="F1942" s="132"/>
+      <c r="G1942" s="132"/>
+    </row>
+    <row r="1943" ht="12.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1943" s="76"/>
+      <c r="B1943" s="76"/>
+      <c r="C1943" s="34"/>
+      <c r="D1943" s="132"/>
+      <c r="E1943" s="132"/>
+      <c r="F1943" s="132"/>
+      <c r="G1943" s="132"/>
     </row>
   </sheetData>
   <pageMargins left="0.7480314960629921" right="0.7480314960629921" top="0.1968503937007874" bottom="0.1968503937007874" header="0" footer="0"/>
@@ -36210,8 +36164,7 @@
       </c>
       <c r="B17" s="26"/>
       <c r="C17" s="18">
-        <f>-'Distribución por línea'!G281-'Distribución por línea'!G150</f>
-        <v>-65017428.77</v>
+        <f>-'Distribución por línea'!G291-'Distribución por línea'!G150</f>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -36231,7 +36184,7 @@
       </c>
       <c r="B19" s="26"/>
       <c r="C19" s="18">
-        <f>-'Distribución por línea'!G484</f>
+        <f>-'Distribución por línea'!G506</f>
       </c>
     </row>
     <row r="20" ht="11.25" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
